--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Connection" sheetId="1" state="visible" r:id="rId3"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="337">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -1362,7 +1362,16 @@
     <t xml:space="preserve">binary32, binary64, binary128, binary256</t>
   </si>
   <si>
-    <t xml:space="preserve">4+</t>
+    <t xml:space="preserve">ByteCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte length of string.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0+</t>
   </si>
   <si>
     <r>
@@ -1447,6 +1456,9 @@
   </si>
   <si>
     <t xml:space="preserve">Values are comma delimited, without spaces. Ending comma is ignored.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4+</t>
   </si>
   <si>
     <t xml:space="preserve">Date/Time (numeric)</t>
@@ -6085,7 +6097,7 @@
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="107"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="107" t="s">
         <v>137</v>
       </c>
@@ -6095,12 +6107,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="107" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="107" t="s">
         <v>140</v>
       </c>
@@ -6108,17 +6120,17 @@
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="107"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="107" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="107" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="107" t="s">
         <v>143</v>
       </c>
@@ -7095,7 +7107,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="168" t="s">
         <v>206</v>
       </c>
@@ -7431,7 +7443,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="18.74"/>
@@ -7893,114 +7905,118 @@
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A17" s="195"/>
-      <c r="D17" s="200"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="48"/>
       <c r="E17" s="105"/>
       <c r="F17" s="105"/>
       <c r="G17" s="49"/>
-      <c r="H17" s="200"/>
-      <c r="I17" s="105"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="105"/>
       <c r="K17" s="49"/>
-      <c r="L17" s="126" t="s">
+      <c r="L17" s="126"/>
+      <c r="M17" s="196"/>
+      <c r="N17" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="O17" s="197" t="s">
+        <v>238</v>
+      </c>
+      <c r="P17" s="198" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A18" s="195"/>
+      <c r="D18" s="200"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="200"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="126" t="s">
         <v>226</v>
       </c>
-      <c r="M17" s="10"/>
-      <c r="N17" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O17" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="P17" s="202" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="188" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="189" t="str">
-        <f aca="false">DEC2HEX(C18,2)</f>
+      <c r="M18" s="10"/>
+      <c r="N18" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="P18" s="202" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="188" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="189" t="str">
+        <f aca="false">DEC2HEX(C19,2)</f>
         <v>04</v>
       </c>
-      <c r="C18" s="151" t="n">
-        <f aca="false">IF(D18=1,128,0)+IF(E18=1,64,0)+IF(F18=1,32,0)+IF(G18=1,16,0)+IF(H18=1,8,0)+IF(I18=1,4,0)+IF(J18=1,2,0)+IF(K18=1,1,0)</f>
+      <c r="C19" s="151" t="n">
+        <f aca="false">IF(D19=1,128,0)+IF(E19=1,64,0)+IF(F19=1,32,0)+IF(G19=1,16,0)+IF(H19=1,8,0)+IF(I19=1,4,0)+IF(J19=1,2,0)+IF(K19=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="D18" s="190"/>
-      <c r="E18" s="151"/>
-      <c r="F18" s="151"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="191"/>
-      <c r="M18" s="192" t="s">
-        <v>240</v>
-      </c>
-      <c r="N18" s="191"/>
-      <c r="O18" s="192"/>
-      <c r="P18" s="194"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A19" s="195"/>
-      <c r="D19" s="200"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105" t="s">
-        <v>220</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O19" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="P19" s="198"/>
+      <c r="D19" s="190"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="152"/>
+      <c r="H19" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="191"/>
+      <c r="M19" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="N19" s="191"/>
+      <c r="O19" s="192"/>
+      <c r="P19" s="194"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A20" s="195"/>
       <c r="D20" s="200"/>
-      <c r="E20" s="105" t="s">
-        <v>223</v>
-      </c>
-      <c r="F20" s="105"/>
-      <c r="G20" s="49"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105" t="s">
+        <v>220</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>220</v>
+      </c>
       <c r="H20" s="105"/>
       <c r="I20" s="105"/>
       <c r="J20" s="105"/>
       <c r="K20" s="49"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="N20" s="10"/>
-      <c r="O20" s="127"/>
-      <c r="P20" s="198" t="s">
-        <v>242</v>
-      </c>
+      <c r="L20" s="126"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="P20" s="198"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A21" s="195"/>
       <c r="D21" s="200"/>
-      <c r="E21" s="105"/>
+      <c r="E21" s="105" t="s">
+        <v>223</v>
+      </c>
       <c r="F21" s="105"/>
       <c r="G21" s="49"/>
       <c r="H21" s="105"/>
@@ -8008,120 +8024,120 @@
       <c r="J21" s="105"/>
       <c r="K21" s="49"/>
       <c r="L21" s="127"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="O21" s="127" t="s">
-        <v>67</v>
-      </c>
-      <c r="P21" s="198"/>
+      <c r="M21" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="N21" s="10"/>
+      <c r="O21" s="127"/>
+      <c r="P21" s="198" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A22" s="195"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="105"/>
-      <c r="D22" s="48" t="s">
-        <v>225</v>
-      </c>
+      <c r="D22" s="200"/>
       <c r="E22" s="105"/>
       <c r="F22" s="105"/>
       <c r="G22" s="49"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="12"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
       <c r="J22" s="105"/>
       <c r="K22" s="49"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="196" t="s">
-        <v>226</v>
-      </c>
-      <c r="O22" s="197"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="O22" s="127" t="s">
+        <v>67</v>
+      </c>
       <c r="P22" s="198"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A23" s="195"/>
-      <c r="D23" s="200"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="48" t="s">
+        <v>225</v>
+      </c>
       <c r="E23" s="105"/>
       <c r="F23" s="105"/>
       <c r="G23" s="49"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="105"/>
       <c r="K23" s="49"/>
-      <c r="L23" s="126" t="s">
+      <c r="L23" s="126"/>
+      <c r="M23" s="196" t="s">
         <v>226</v>
       </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="P23" s="198" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="188" t="s">
-        <v>246</v>
-      </c>
-      <c r="B24" s="189" t="str">
-        <f aca="false">DEC2HEX(C24,2)</f>
+      <c r="O23" s="197"/>
+      <c r="P23" s="198"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A24" s="195"/>
+      <c r="D24" s="200"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="126" t="s">
+        <v>226</v>
+      </c>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="P24" s="198" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="188" t="s">
+        <v>249</v>
+      </c>
+      <c r="B25" s="189" t="str">
+        <f aca="false">DEC2HEX(C25,2)</f>
         <v>05</v>
       </c>
-      <c r="C24" s="151" t="n">
-        <f aca="false">IF(D24=1,128,0)+IF(E24=1,64,0)+IF(F24=1,32,0)+IF(G24=1,16,0)+IF(H24=1,8,0)+IF(I24=1,4,0)+IF(J24=1,2,0)+IF(K24=1,1,0)</f>
+      <c r="C25" s="151" t="n">
+        <f aca="false">IF(D25=1,128,0)+IF(E25=1,64,0)+IF(F25=1,32,0)+IF(G25=1,16,0)+IF(H25=1,8,0)+IF(I25=1,4,0)+IF(J25=1,2,0)+IF(K25=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="D24" s="190"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="191"/>
-      <c r="M24" s="192" t="s">
-        <v>247</v>
-      </c>
-      <c r="N24" s="191"/>
-      <c r="O24" s="192"/>
-      <c r="P24" s="194"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A25" s="195"/>
-      <c r="D25" s="200"/>
-      <c r="E25" s="105" t="s">
-        <v>223</v>
-      </c>
-      <c r="F25" s="105"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="N25" s="10"/>
-      <c r="O25" s="127"/>
-      <c r="P25" s="198" t="s">
-        <v>248</v>
-      </c>
+      <c r="D25" s="190"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="152"/>
+      <c r="H25" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="191"/>
+      <c r="M25" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="N25" s="191"/>
+      <c r="O25" s="192"/>
+      <c r="P25" s="194"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A26" s="195"/>
       <c r="D26" s="200"/>
-      <c r="E26" s="105"/>
+      <c r="E26" s="105" t="s">
+        <v>223</v>
+      </c>
       <c r="F26" s="105"/>
       <c r="G26" s="49"/>
       <c r="H26" s="105"/>
@@ -8129,116 +8145,117 @@
       <c r="J26" s="105"/>
       <c r="K26" s="49"/>
       <c r="L26" s="127"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="O26" s="127" t="s">
-        <v>67</v>
-      </c>
-      <c r="P26" s="198"/>
+      <c r="M26" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="N26" s="10"/>
+      <c r="O26" s="127"/>
+      <c r="P26" s="198" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A27" s="195"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="48" t="s">
-        <v>225</v>
-      </c>
+      <c r="D27" s="200"/>
       <c r="E27" s="105"/>
       <c r="F27" s="105"/>
       <c r="G27" s="49"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="12"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
       <c r="J27" s="105"/>
       <c r="K27" s="49"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="196" t="s">
-        <v>226</v>
-      </c>
-      <c r="O27" s="197"/>
+      <c r="L27" s="127"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="O27" s="127" t="s">
+        <v>67</v>
+      </c>
       <c r="P27" s="198"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A28" s="195"/>
-      <c r="D28" s="200"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="48" t="s">
+        <v>225</v>
+      </c>
       <c r="E28" s="105"/>
       <c r="F28" s="105"/>
       <c r="G28" s="49"/>
-      <c r="H28" s="200"/>
-      <c r="I28" s="105"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="12"/>
       <c r="J28" s="105"/>
       <c r="K28" s="49"/>
-      <c r="L28" s="126" t="s">
+      <c r="L28" s="126"/>
+      <c r="M28" s="196" t="s">
         <v>226</v>
       </c>
-      <c r="M28" s="10"/>
-      <c r="N28" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="P28" s="202" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="188" t="s">
-        <v>249</v>
-      </c>
-      <c r="B29" s="189" t="str">
-        <f aca="false">DEC2HEX(C29,2)</f>
+      <c r="O28" s="197"/>
+      <c r="P28" s="198"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A29" s="195"/>
+      <c r="D29" s="200"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="200"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="126" t="s">
+        <v>226</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="N29" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="P29" s="202" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="188" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="189" t="str">
+        <f aca="false">DEC2HEX(C30,2)</f>
         <v>06</v>
       </c>
-      <c r="C29" s="151" t="n">
-        <f aca="false">IF(D29=1,128,0)+IF(E29=1,64,0)+IF(F29=1,32,0)+IF(G29=1,16,0)+IF(H29=1,8,0)+IF(I29=1,4,0)+IF(J29=1,2,0)+IF(K29=1,1,0)</f>
+      <c r="C30" s="151" t="n">
+        <f aca="false">IF(D30=1,128,0)+IF(E30=1,64,0)+IF(F30=1,32,0)+IF(G30=1,16,0)+IF(H30=1,8,0)+IF(I30=1,4,0)+IF(J30=1,2,0)+IF(K30=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="D29" s="190"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="152"/>
-      <c r="H29" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="191"/>
-      <c r="M29" s="192" t="s">
-        <v>250</v>
-      </c>
-      <c r="N29" s="191"/>
-      <c r="O29" s="192"/>
-      <c r="P29" s="203" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A30" s="195"/>
-      <c r="D30" s="200"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="105"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="105"/>
-      <c r="K30" s="49"/>
-      <c r="M30" s="127" t="s">
-        <v>252</v>
-      </c>
-      <c r="P30" s="198"/>
+      <c r="D30" s="190"/>
+      <c r="E30" s="151"/>
+      <c r="F30" s="151"/>
+      <c r="G30" s="152"/>
+      <c r="H30" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="191"/>
+      <c r="M30" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="N30" s="191"/>
+      <c r="O30" s="192"/>
+      <c r="P30" s="203" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A31" s="195"/>
@@ -8248,14 +8265,14 @@
         <v>0</v>
       </c>
       <c r="G31" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="105"/>
       <c r="I31" s="105"/>
       <c r="J31" s="105"/>
       <c r="K31" s="49"/>
-      <c r="M31" s="196" t="s">
-        <v>253</v>
+      <c r="M31" s="127" t="s">
+        <v>256</v>
       </c>
       <c r="P31" s="198"/>
     </row>
@@ -8264,17 +8281,17 @@
       <c r="D32" s="200"/>
       <c r="E32" s="105"/>
       <c r="F32" s="105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="105"/>
       <c r="I32" s="105"/>
       <c r="J32" s="105"/>
       <c r="K32" s="49"/>
       <c r="M32" s="196" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P32" s="198"/>
     </row>
@@ -8286,134 +8303,132 @@
         <v>1</v>
       </c>
       <c r="G33" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="105"/>
       <c r="I33" s="105"/>
       <c r="J33" s="105"/>
       <c r="K33" s="49"/>
-      <c r="M33" s="10" t="s">
-        <v>255</v>
+      <c r="M33" s="196" t="s">
+        <v>258</v>
       </c>
       <c r="P33" s="198"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A34" s="195"/>
       <c r="D34" s="200"/>
-      <c r="E34" s="105" t="s">
-        <v>256</v>
-      </c>
-      <c r="F34" s="105"/>
-      <c r="G34" s="49"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="49" t="n">
+        <v>1</v>
+      </c>
       <c r="H34" s="105"/>
       <c r="I34" s="105"/>
       <c r="J34" s="105"/>
       <c r="K34" s="49"/>
-      <c r="M34" s="127" t="s">
-        <v>257</v>
-      </c>
-      <c r="P34" s="198" t="s">
-        <v>258</v>
-      </c>
+      <c r="M34" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="P34" s="198"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A35" s="195"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="48" t="s">
-        <v>225</v>
-      </c>
-      <c r="E35" s="105"/>
+      <c r="D35" s="200"/>
+      <c r="E35" s="105" t="s">
+        <v>260</v>
+      </c>
       <c r="F35" s="105"/>
       <c r="G35" s="49"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="12"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
       <c r="J35" s="105"/>
       <c r="K35" s="49"/>
-      <c r="L35" s="126"/>
-      <c r="M35" s="196" t="s">
-        <v>226</v>
-      </c>
-      <c r="O35" s="197"/>
-      <c r="P35" s="198"/>
+      <c r="M35" s="127" t="s">
+        <v>261</v>
+      </c>
+      <c r="P35" s="198" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A36" s="195"/>
-      <c r="D36" s="200"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="48" t="s">
+        <v>225</v>
+      </c>
       <c r="E36" s="105"/>
       <c r="F36" s="105"/>
       <c r="G36" s="49"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="105"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="12"/>
       <c r="J36" s="105"/>
       <c r="K36" s="49"/>
-      <c r="L36" s="126" t="s">
+      <c r="L36" s="126"/>
+      <c r="M36" s="196" t="s">
         <v>226</v>
       </c>
-      <c r="M36" s="127"/>
-      <c r="O36" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="P36" s="198" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="188" t="s">
-        <v>261</v>
-      </c>
-      <c r="B37" s="189" t="str">
-        <f aca="false">DEC2HEX(C37,2)</f>
+      <c r="O36" s="197"/>
+      <c r="P36" s="198"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A37" s="195"/>
+      <c r="D37" s="200"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="126" t="s">
+        <v>226</v>
+      </c>
+      <c r="M37" s="127"/>
+      <c r="O37" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="P37" s="198" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="188" t="s">
+        <v>265</v>
+      </c>
+      <c r="B38" s="189" t="str">
+        <f aca="false">DEC2HEX(C38,2)</f>
         <v>07</v>
       </c>
-      <c r="C37" s="151" t="n">
-        <f aca="false">IF(D37=1,128,0)+IF(E37=1,64,0)+IF(F37=1,32,0)+IF(G37=1,16,0)+IF(H37=1,8,0)+IF(I37=1,4,0)+IF(J37=1,2,0)+IF(K37=1,1,0)</f>
+      <c r="C38" s="151" t="n">
+        <f aca="false">IF(D38=1,128,0)+IF(E38=1,64,0)+IF(F38=1,32,0)+IF(G38=1,16,0)+IF(H38=1,8,0)+IF(I38=1,4,0)+IF(J38=1,2,0)+IF(K38=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="D37" s="190"/>
-      <c r="E37" s="151"/>
-      <c r="F37" s="151"/>
-      <c r="G37" s="152"/>
-      <c r="H37" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="191"/>
-      <c r="M37" s="192" t="s">
-        <v>262</v>
-      </c>
-      <c r="N37" s="191"/>
-      <c r="O37" s="192"/>
-      <c r="P37" s="194"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A38" s="195"/>
-      <c r="D38" s="200"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="105"/>
-      <c r="I38" s="105"/>
-      <c r="J38" s="105"/>
-      <c r="K38" s="49"/>
-      <c r="M38" s="127" t="s">
-        <v>263</v>
-      </c>
-      <c r="P38" s="204" t="s">
-        <v>264</v>
-      </c>
+      <c r="D38" s="190"/>
+      <c r="E38" s="151"/>
+      <c r="F38" s="151"/>
+      <c r="G38" s="152"/>
+      <c r="H38" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="191"/>
+      <c r="M38" s="192" t="s">
+        <v>266</v>
+      </c>
+      <c r="N38" s="191"/>
+      <c r="O38" s="192"/>
+      <c r="P38" s="194"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A39" s="195"/>
@@ -8423,17 +8438,17 @@
         <v>0</v>
       </c>
       <c r="G39" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="105"/>
       <c r="I39" s="105"/>
       <c r="J39" s="105"/>
       <c r="K39" s="49"/>
-      <c r="M39" s="196" t="s">
-        <v>253</v>
+      <c r="M39" s="127" t="s">
+        <v>267</v>
       </c>
       <c r="P39" s="204" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -8441,20 +8456,20 @@
       <c r="D40" s="200"/>
       <c r="E40" s="105"/>
       <c r="F40" s="105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="105"/>
       <c r="I40" s="105"/>
       <c r="J40" s="105"/>
       <c r="K40" s="49"/>
       <c r="M40" s="196" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P40" s="204" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -8465,33 +8480,38 @@
         <v>1</v>
       </c>
       <c r="G41" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="105"/>
       <c r="I41" s="105"/>
       <c r="J41" s="105"/>
       <c r="K41" s="49"/>
-      <c r="M41" s="10" t="s">
-        <v>255</v>
+      <c r="M41" s="196" t="s">
+        <v>258</v>
       </c>
       <c r="P41" s="204" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A42" s="195"/>
       <c r="D42" s="200"/>
       <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="49"/>
+      <c r="F42" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="49" t="n">
+        <v>1</v>
+      </c>
       <c r="H42" s="105"/>
       <c r="I42" s="105"/>
       <c r="J42" s="105"/>
       <c r="K42" s="49"/>
-      <c r="M42" s="10"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="205" t="s">
-        <v>268</v>
+      <c r="M42" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="P42" s="204" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -8507,7 +8527,7 @@
       <c r="M43" s="10"/>
       <c r="O43" s="1"/>
       <c r="P43" s="205" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -8523,35 +8543,32 @@
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
       <c r="P44" s="205" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A45" s="195"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="48" t="s">
-        <v>225</v>
-      </c>
+      <c r="D45" s="200"/>
       <c r="E45" s="105"/>
       <c r="F45" s="105"/>
       <c r="G45" s="49"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="12"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
       <c r="J45" s="105"/>
       <c r="K45" s="49"/>
-      <c r="L45" s="126"/>
-      <c r="M45" s="196" t="s">
-        <v>226</v>
-      </c>
-      <c r="O45" s="197"/>
-      <c r="P45" s="198"/>
+      <c r="M45" s="10"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="205" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A46" s="195"/>
       <c r="B46" s="16"/>
       <c r="C46" s="105"/>
-      <c r="D46" s="48"/>
+      <c r="D46" s="48" t="s">
+        <v>225</v>
+      </c>
       <c r="E46" s="105"/>
       <c r="F46" s="105"/>
       <c r="G46" s="49"/>
@@ -8559,207 +8576,200 @@
       <c r="I46" s="12"/>
       <c r="J46" s="105"/>
       <c r="K46" s="49"/>
-      <c r="L46" s="196" t="s">
+      <c r="L46" s="126"/>
+      <c r="M46" s="196" t="s">
         <v>226</v>
       </c>
-      <c r="M46" s="196"/>
-      <c r="N46" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="O46" s="197" t="s">
-        <v>272</v>
-      </c>
+      <c r="O46" s="197"/>
       <c r="P46" s="198"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="206"/>
-      <c r="B47" s="207"/>
-      <c r="C47" s="130"/>
-      <c r="D47" s="129"/>
-      <c r="E47" s="130"/>
-      <c r="F47" s="130"/>
-      <c r="G47" s="133"/>
-      <c r="H47" s="130"/>
-      <c r="I47" s="130"/>
-      <c r="J47" s="130"/>
-      <c r="K47" s="133"/>
+      <c r="A47" s="195"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="105"/>
+      <c r="K47" s="49"/>
       <c r="L47" s="196" t="s">
         <v>226</v>
       </c>
-      <c r="M47" s="208"/>
-      <c r="N47" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P47" s="202" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="188" t="s">
-        <v>273</v>
-      </c>
-      <c r="B48" s="189" t="str">
-        <f aca="false">DEC2HEX(C48,2)</f>
+      <c r="M47" s="196"/>
+      <c r="N47" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="O47" s="197" t="s">
+        <v>276</v>
+      </c>
+      <c r="P47" s="198"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A48" s="206"/>
+      <c r="B48" s="207"/>
+      <c r="C48" s="130"/>
+      <c r="D48" s="129"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="133"/>
+      <c r="H48" s="130"/>
+      <c r="I48" s="130"/>
+      <c r="J48" s="130"/>
+      <c r="K48" s="133"/>
+      <c r="L48" s="196" t="s">
+        <v>226</v>
+      </c>
+      <c r="M48" s="208"/>
+      <c r="N48" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="P48" s="202" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="188" t="s">
+        <v>277</v>
+      </c>
+      <c r="B49" s="189" t="str">
+        <f aca="false">DEC2HEX(C49,2)</f>
         <v>0A</v>
       </c>
-      <c r="C48" s="151" t="n">
-        <f aca="false">IF(D48=1,128,0)+IF(E48=1,64,0)+IF(F48=1,32,0)+IF(G48=1,16,0)+IF(H48=1,8,0)+IF(I48=1,4,0)+IF(J48=1,2,0)+IF(K48=1,1,0)</f>
+      <c r="C49" s="151" t="n">
+        <f aca="false">IF(D49=1,128,0)+IF(E49=1,64,0)+IF(F49=1,32,0)+IF(G49=1,16,0)+IF(H49=1,8,0)+IF(I49=1,4,0)+IF(J49=1,2,0)+IF(K49=1,1,0)</f>
         <v>10</v>
       </c>
-      <c r="D48" s="190"/>
-      <c r="E48" s="151"/>
-      <c r="F48" s="151"/>
-      <c r="G48" s="152"/>
-      <c r="H48" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="191"/>
-      <c r="M48" s="192" t="s">
-        <v>274</v>
-      </c>
-      <c r="N48" s="191"/>
-      <c r="O48" s="192"/>
-      <c r="P48" s="194"/>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A49" s="195"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="48" t="s">
-        <v>225</v>
-      </c>
-      <c r="E49" s="105"/>
-      <c r="F49" s="105"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="105"/>
-      <c r="K49" s="49"/>
-      <c r="L49" s="126"/>
-      <c r="M49" s="196" t="s">
-        <v>226</v>
-      </c>
-      <c r="O49" s="197"/>
-      <c r="P49" s="198"/>
+      <c r="D49" s="190"/>
+      <c r="E49" s="151"/>
+      <c r="F49" s="151"/>
+      <c r="G49" s="152"/>
+      <c r="H49" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="191"/>
+      <c r="M49" s="192" t="s">
+        <v>278</v>
+      </c>
+      <c r="N49" s="191"/>
+      <c r="O49" s="192"/>
+      <c r="P49" s="194"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A50" s="195"/>
-      <c r="D50" s="200"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="48" t="s">
+        <v>225</v>
+      </c>
       <c r="E50" s="105"/>
       <c r="F50" s="105"/>
       <c r="G50" s="49"/>
-      <c r="H50" s="105"/>
-      <c r="I50" s="105"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="12"/>
       <c r="J50" s="105"/>
       <c r="K50" s="49"/>
-      <c r="L50" s="196" t="s">
+      <c r="L50" s="126"/>
+      <c r="M50" s="196" t="s">
         <v>226</v>
       </c>
-      <c r="M50" s="127"/>
-      <c r="N50" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="O50" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="P50" s="198" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="188" t="s">
-        <v>277</v>
-      </c>
-      <c r="B51" s="189" t="str">
-        <f aca="false">DEC2HEX(C51,2)</f>
+      <c r="O50" s="197"/>
+      <c r="P50" s="198"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A51" s="195"/>
+      <c r="D51" s="200"/>
+      <c r="E51" s="105"/>
+      <c r="F51" s="105"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="105"/>
+      <c r="I51" s="105"/>
+      <c r="J51" s="105"/>
+      <c r="K51" s="49"/>
+      <c r="L51" s="196" t="s">
+        <v>226</v>
+      </c>
+      <c r="M51" s="127"/>
+      <c r="N51" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="P51" s="198" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="188" t="s">
+        <v>281</v>
+      </c>
+      <c r="B52" s="189" t="str">
+        <f aca="false">DEC2HEX(C52,2)</f>
         <v>0C</v>
       </c>
-      <c r="C51" s="151" t="n">
-        <f aca="false">IF(D51=1,128,0)+IF(E51=1,64,0)+IF(F51=1,32,0)+IF(G51=1,16,0)+IF(H51=1,8,0)+IF(I51=1,4,0)+IF(J51=1,2,0)+IF(K51=1,1,0)</f>
+      <c r="C52" s="151" t="n">
+        <f aca="false">IF(D52=1,128,0)+IF(E52=1,64,0)+IF(F52=1,32,0)+IF(G52=1,16,0)+IF(H52=1,8,0)+IF(I52=1,4,0)+IF(J52=1,2,0)+IF(K52=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="D51" s="190"/>
-      <c r="E51" s="151"/>
-      <c r="F51" s="151"/>
-      <c r="G51" s="152"/>
-      <c r="H51" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="151" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="191"/>
-      <c r="M51" s="191" t="s">
-        <v>278</v>
-      </c>
-      <c r="N51" s="191"/>
-      <c r="O51" s="192"/>
-      <c r="P51" s="194"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A52" s="195"/>
-      <c r="D52" s="200" t="s">
-        <v>225</v>
-      </c>
-      <c r="E52" s="105"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="105"/>
-      <c r="I52" s="105"/>
-      <c r="J52" s="105"/>
-      <c r="K52" s="49"/>
-      <c r="M52" s="196" t="s">
-        <v>226</v>
-      </c>
-      <c r="N52" s="196"/>
-      <c r="O52" s="126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="198"/>
+      <c r="D52" s="190"/>
+      <c r="E52" s="151"/>
+      <c r="F52" s="151"/>
+      <c r="G52" s="152"/>
+      <c r="H52" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="191"/>
+      <c r="M52" s="191" t="s">
+        <v>282</v>
+      </c>
+      <c r="N52" s="191"/>
+      <c r="O52" s="192"/>
+      <c r="P52" s="194"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A53" s="195"/>
-      <c r="D53" s="200"/>
+      <c r="D53" s="200" t="s">
+        <v>225</v>
+      </c>
       <c r="E53" s="105"/>
       <c r="F53" s="105"/>
-      <c r="G53" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="G53" s="49"/>
       <c r="H53" s="105"/>
       <c r="I53" s="105"/>
       <c r="J53" s="105"/>
       <c r="K53" s="49"/>
-      <c r="L53" s="196" t="s">
+      <c r="M53" s="196" t="s">
         <v>226</v>
-      </c>
-      <c r="M53" s="196" t="s">
-        <v>279</v>
       </c>
       <c r="N53" s="196"/>
       <c r="O53" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="P53" s="198" t="s">
-        <v>280</v>
-      </c>
+      <c r="P53" s="198"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A54" s="195"/>
@@ -8767,7 +8777,7 @@
       <c r="E54" s="105"/>
       <c r="F54" s="105"/>
       <c r="G54" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" s="105"/>
       <c r="I54" s="105"/>
@@ -8777,54 +8787,65 @@
         <v>226</v>
       </c>
       <c r="M54" s="196" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N54" s="196"/>
       <c r="O54" s="126" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="198" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="188"/>
-      <c r="B55" s="189" t="str">
-        <f aca="false">DEC2HEX(C55,2)</f>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A55" s="195"/>
+      <c r="D55" s="200"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="105"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="105"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="196" t="s">
+        <v>226</v>
+      </c>
+      <c r="M55" s="196" t="s">
+        <v>285</v>
+      </c>
+      <c r="N55" s="196"/>
+      <c r="O55" s="126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="198" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="188"/>
+      <c r="B56" s="189" t="str">
+        <f aca="false">DEC2HEX(C56,2)</f>
         <v>00</v>
       </c>
-      <c r="C55" s="151" t="n">
-        <f aca="false">IF(D55=1,128,0)+IF(E55=1,64,0)+IF(F55=1,32,0)+IF(G55=1,16,0)+IF(H55=1,8,0)+IF(I55=1,4,0)+IF(J55=1,2,0)+IF(K55=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="190"/>
-      <c r="E55" s="151"/>
-      <c r="F55" s="151"/>
-      <c r="G55" s="152"/>
-      <c r="H55" s="151"/>
-      <c r="I55" s="151"/>
-      <c r="J55" s="151"/>
-      <c r="K55" s="152"/>
-      <c r="L55" s="191"/>
-      <c r="M55" s="191"/>
-      <c r="N55" s="191"/>
-      <c r="O55" s="192"/>
-      <c r="P55" s="194"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A56" s="195"/>
-      <c r="D56" s="200"/>
-      <c r="E56" s="105"/>
-      <c r="F56" s="105"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="105"/>
-      <c r="I56" s="105"/>
-      <c r="J56" s="105"/>
-      <c r="K56" s="49"/>
-      <c r="M56" s="196"/>
-      <c r="N56" s="196"/>
-      <c r="O56" s="126"/>
-      <c r="P56" s="198"/>
+      <c r="C56" s="151" t="n">
+        <f aca="false">IF(D56=1,128,0)+IF(E56=1,64,0)+IF(F56=1,32,0)+IF(G56=1,16,0)+IF(H56=1,8,0)+IF(I56=1,4,0)+IF(J56=1,2,0)+IF(K56=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="190"/>
+      <c r="E56" s="151"/>
+      <c r="F56" s="151"/>
+      <c r="G56" s="152"/>
+      <c r="H56" s="151"/>
+      <c r="I56" s="151"/>
+      <c r="J56" s="151"/>
+      <c r="K56" s="152"/>
+      <c r="L56" s="191"/>
+      <c r="M56" s="191"/>
+      <c r="N56" s="191"/>
+      <c r="O56" s="192"/>
+      <c r="P56" s="194"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A57" s="195"/>
@@ -8871,7 +8892,7 @@
       <c r="O59" s="126"/>
       <c r="P59" s="198"/>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A60" s="195"/>
       <c r="D60" s="200"/>
       <c r="E60" s="105"/>
@@ -8887,126 +8908,99 @@
       <c r="P60" s="198"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="188" t="s">
+      <c r="A61" s="195"/>
+      <c r="D61" s="200"/>
+      <c r="E61" s="105"/>
+      <c r="F61" s="105"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="105"/>
+      <c r="I61" s="105"/>
+      <c r="J61" s="105"/>
+      <c r="K61" s="49"/>
+      <c r="M61" s="196"/>
+      <c r="N61" s="196"/>
+      <c r="O61" s="126"/>
+      <c r="P61" s="198"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="188" t="s">
         <v>206</v>
       </c>
-      <c r="B61" s="189"/>
-      <c r="C61" s="151"/>
-      <c r="D61" s="190"/>
-      <c r="E61" s="151"/>
-      <c r="F61" s="151"/>
-      <c r="G61" s="152"/>
-      <c r="H61" s="190"/>
-      <c r="I61" s="151"/>
-      <c r="J61" s="151"/>
-      <c r="K61" s="152"/>
-      <c r="L61" s="192"/>
-      <c r="M61" s="191"/>
-      <c r="N61" s="191"/>
-      <c r="O61" s="192"/>
-      <c r="P61" s="194"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A62" s="209" t="s">
-        <v>283</v>
-      </c>
-      <c r="B62" s="183" t="str">
-        <f aca="false">DEC2HEX(C62,2)</f>
+      <c r="B62" s="189"/>
+      <c r="C62" s="151"/>
+      <c r="D62" s="190"/>
+      <c r="E62" s="151"/>
+      <c r="F62" s="151"/>
+      <c r="G62" s="152"/>
+      <c r="H62" s="190"/>
+      <c r="I62" s="151"/>
+      <c r="J62" s="151"/>
+      <c r="K62" s="152"/>
+      <c r="L62" s="192"/>
+      <c r="M62" s="191"/>
+      <c r="N62" s="191"/>
+      <c r="O62" s="192"/>
+      <c r="P62" s="194"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A63" s="209" t="s">
+        <v>287</v>
+      </c>
+      <c r="B63" s="183" t="str">
+        <f aca="false">DEC2HEX(C63,2)</f>
         <v>00</v>
       </c>
-      <c r="C62" s="210" t="n">
-        <f aca="false">IF(D62=1,128,0)+IF(E62=1,64,0)+IF(F62=1,32,0)+IF(G62=1,16,0)+IF(H62=1,8,0)+IF(I62=1,4,0)+IF(J62=1,2,0)+IF(K62=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="213"/>
-      <c r="M62" s="214"/>
-      <c r="N62" s="214"/>
-      <c r="O62" s="213"/>
-      <c r="P62" s="215"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A63" s="195" t="s">
-        <v>284</v>
-      </c>
-      <c r="B63" s="20" t="str">
-        <f aca="false">DEC2HEX(C63,2)</f>
-        <v>40</v>
-      </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="210" t="n">
         <f aca="false">IF(D63=1,128,0)+IF(E63=1,64,0)+IF(F63=1,32,0)+IF(G63=1,16,0)+IF(H63=1,8,0)+IF(I63=1,4,0)+IF(J63=1,2,0)+IF(K63=1,1,0)</f>
-        <v>64</v>
-      </c>
-      <c r="D63" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="126"/>
-      <c r="M63" s="196"/>
-      <c r="N63" s="196"/>
-      <c r="O63" s="126"/>
-      <c r="P63" s="198"/>
+        <v>0</v>
+      </c>
+      <c r="D63" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="213"/>
+      <c r="M63" s="214"/>
+      <c r="N63" s="214"/>
+      <c r="O63" s="213"/>
+      <c r="P63" s="215"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A64" s="195" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B64" s="20" t="str">
         <f aca="false">DEC2HEX(C64,2)</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C64" s="2" t="n">
         <f aca="false">IF(D64=1,128,0)+IF(E64=1,64,0)+IF(F64=1,32,0)+IF(G64=1,16,0)+IF(H64=1,8,0)+IF(I64=1,4,0)+IF(J64=1,2,0)+IF(K64=1,1,0)</f>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="D64" s="48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="105" t="n">
         <v>0</v>
@@ -9033,530 +9027,530 @@
       <c r="P64" s="198"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A65" s="206" t="s">
-        <v>286</v>
-      </c>
-      <c r="B65" s="207" t="str">
+      <c r="A65" s="195" t="s">
+        <v>289</v>
+      </c>
+      <c r="B65" s="20" t="str">
         <f aca="false">DEC2HEX(C65,2)</f>
+        <v>80</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <f aca="false">IF(D65=1,128,0)+IF(E65=1,64,0)+IF(F65=1,32,0)+IF(G65=1,16,0)+IF(H65=1,8,0)+IF(I65=1,4,0)+IF(J65=1,2,0)+IF(K65=1,1,0)</f>
+        <v>128</v>
+      </c>
+      <c r="D65" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="126"/>
+      <c r="M65" s="196"/>
+      <c r="N65" s="196"/>
+      <c r="O65" s="126"/>
+      <c r="P65" s="198"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A66" s="206" t="s">
+        <v>290</v>
+      </c>
+      <c r="B66" s="207" t="str">
+        <f aca="false">DEC2HEX(C66,2)</f>
         <v>C0</v>
       </c>
-      <c r="C65" s="130" t="n">
-        <f aca="false">IF(D65=1,128,0)+IF(E65=1,64,0)+IF(F65=1,32,0)+IF(G65=1,16,0)+IF(H65=1,8,0)+IF(I65=1,4,0)+IF(J65=1,2,0)+IF(K65=1,1,0)</f>
+      <c r="C66" s="130" t="n">
+        <f aca="false">IF(D66=1,128,0)+IF(E66=1,64,0)+IF(F66=1,32,0)+IF(G66=1,16,0)+IF(H66=1,8,0)+IF(I66=1,4,0)+IF(J66=1,2,0)+IF(K66=1,1,0)</f>
         <v>192</v>
       </c>
-      <c r="D65" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="216"/>
-      <c r="M65" s="217"/>
-      <c r="N65" s="217"/>
-      <c r="O65" s="208"/>
-      <c r="P65" s="218"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A66" s="209" t="s">
-        <v>287</v>
-      </c>
-      <c r="B66" s="183" t="str">
-        <f aca="false">DEC2HEX(C66,2)</f>
+      <c r="D66" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="216"/>
+      <c r="M66" s="217"/>
+      <c r="N66" s="217"/>
+      <c r="O66" s="208"/>
+      <c r="P66" s="218"/>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A67" s="209" t="s">
+        <v>291</v>
+      </c>
+      <c r="B67" s="183" t="str">
+        <f aca="false">DEC2HEX(C67,2)</f>
         <v>01</v>
       </c>
-      <c r="C66" s="210" t="n">
-        <f aca="false">IF(D66=1,128,0)+IF(E66=1,64,0)+IF(F66=1,32,0)+IF(G66=1,16,0)+IF(H66=1,8,0)+IF(I66=1,4,0)+IF(J66=1,2,0)+IF(K66=1,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D66" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="210" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="212" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" s="219"/>
-      <c r="M66" s="214"/>
-      <c r="N66" s="214"/>
-      <c r="O66" s="213"/>
-      <c r="P66" s="215"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A67" s="195" t="s">
-        <v>288</v>
-      </c>
-      <c r="B67" s="20" t="str">
-        <f aca="false">DEC2HEX(C67,2)</f>
-        <v>41</v>
-      </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="210" t="n">
         <f aca="false">IF(D67=1,128,0)+IF(E67=1,64,0)+IF(F67=1,32,0)+IF(G67=1,16,0)+IF(H67=1,8,0)+IF(I67=1,4,0)+IF(J67=1,2,0)+IF(K67=1,1,0)</f>
-        <v>65</v>
-      </c>
-      <c r="D67" s="200" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="220"/>
-      <c r="P67" s="198"/>
+        <v>1</v>
+      </c>
+      <c r="D67" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="219"/>
+      <c r="M67" s="214"/>
+      <c r="N67" s="214"/>
+      <c r="O67" s="213"/>
+      <c r="P67" s="215"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A68" s="195" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B68" s="20" t="str">
         <f aca="false">DEC2HEX(C68,2)</f>
-        <v>C1</v>
+        <v>41</v>
       </c>
       <c r="C68" s="2" t="n">
         <f aca="false">IF(D68=1,128,0)+IF(E68=1,64,0)+IF(F68=1,32,0)+IF(G68=1,16,0)+IF(H68=1,8,0)+IF(I68=1,4,0)+IF(J68=1,2,0)+IF(K68=1,1,0)</f>
+        <v>65</v>
+      </c>
+      <c r="D68" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" s="220"/>
+      <c r="P68" s="198"/>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A69" s="195" t="s">
+        <v>293</v>
+      </c>
+      <c r="B69" s="20" t="str">
+        <f aca="false">DEC2HEX(C69,2)</f>
+        <v>C1</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <f aca="false">IF(D69=1,128,0)+IF(E69=1,64,0)+IF(F69=1,32,0)+IF(G69=1,16,0)+IF(H69=1,8,0)+IF(I69=1,4,0)+IF(J69=1,2,0)+IF(K69=1,1,0)</f>
         <v>193</v>
       </c>
-      <c r="D68" s="200" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="220"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="126"/>
-      <c r="P68" s="198"/>
-    </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A69" s="206" t="s">
-        <v>290</v>
-      </c>
-      <c r="B69" s="207" t="str">
-        <f aca="false">DEC2HEX(C69,2)</f>
+      <c r="D69" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" s="220"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="126"/>
+      <c r="P69" s="198"/>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A70" s="206" t="s">
+        <v>294</v>
+      </c>
+      <c r="B70" s="207" t="str">
+        <f aca="false">DEC2HEX(C70,2)</f>
         <v>03</v>
       </c>
-      <c r="C69" s="130" t="n">
-        <f aca="false">IF(D69=1,128,0)+IF(E69=1,64,0)+IF(F69=1,32,0)+IF(G69=1,16,0)+IF(H69=1,8,0)+IF(I69=1,4,0)+IF(J69=1,2,0)+IF(K69=1,1,0)</f>
+      <c r="C70" s="130" t="n">
+        <f aca="false">IF(D70=1,128,0)+IF(E70=1,64,0)+IF(F70=1,32,0)+IF(G70=1,16,0)+IF(H70=1,8,0)+IF(I70=1,4,0)+IF(J70=1,2,0)+IF(K70=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="D69" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="208"/>
-      <c r="M69" s="217"/>
-      <c r="N69" s="217"/>
-      <c r="O69" s="208"/>
-      <c r="P69" s="218"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A70" s="209" t="s">
-        <v>291</v>
-      </c>
-      <c r="B70" s="183" t="str">
-        <f aca="false">DEC2HEX(C70,2)</f>
+      <c r="D70" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="208"/>
+      <c r="M70" s="217"/>
+      <c r="N70" s="217"/>
+      <c r="O70" s="208"/>
+      <c r="P70" s="218"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A71" s="209" t="s">
+        <v>295</v>
+      </c>
+      <c r="B71" s="183" t="str">
+        <f aca="false">DEC2HEX(C71,2)</f>
         <v>04</v>
       </c>
-      <c r="C70" s="210" t="n">
-        <f aca="false">IF(D70=1,128,0)+IF(E70=1,64,0)+IF(F70=1,32,0)+IF(G70=1,16,0)+IF(H70=1,8,0)+IF(I70=1,4,0)+IF(J70=1,2,0)+IF(K70=1,1,0)</f>
+      <c r="C71" s="210" t="n">
+        <f aca="false">IF(D71=1,128,0)+IF(E71=1,64,0)+IF(F71=1,32,0)+IF(G71=1,16,0)+IF(H71=1,8,0)+IF(I71=1,4,0)+IF(J71=1,2,0)+IF(K71=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="D70" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="175" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="213"/>
-      <c r="M70" s="214"/>
-      <c r="N70" s="214"/>
-      <c r="O70" s="213"/>
-      <c r="P70" s="215" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="195" t="s">
-        <v>293</v>
-      </c>
-      <c r="B71" s="20" t="str">
-        <f aca="false">DEC2HEX(C71,2)</f>
+      <c r="D71" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="213"/>
+      <c r="M71" s="214"/>
+      <c r="N71" s="214"/>
+      <c r="O71" s="213"/>
+      <c r="P71" s="215" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A72" s="195" t="s">
+        <v>297</v>
+      </c>
+      <c r="B72" s="20" t="str">
+        <f aca="false">DEC2HEX(C72,2)</f>
         <v>14</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <f aca="false">IF(D71=1,128,0)+IF(E71=1,64,0)+IF(F71=1,32,0)+IF(G71=1,16,0)+IF(H71=1,8,0)+IF(I71=1,4,0)+IF(J71=1,2,0)+IF(K71=1,1,0)</f>
+      <c r="C72" s="2" t="n">
+        <f aca="false">IF(D72=1,128,0)+IF(E72=1,64,0)+IF(F72=1,32,0)+IF(G72=1,16,0)+IF(H72=1,8,0)+IF(I72=1,4,0)+IF(J72=1,2,0)+IF(K72=1,1,0)</f>
         <v>20</v>
       </c>
-      <c r="D71" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="126"/>
-      <c r="M71" s="196"/>
-      <c r="N71" s="196"/>
-      <c r="O71" s="126"/>
-      <c r="P71" s="198" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="206" t="s">
-        <v>295</v>
-      </c>
-      <c r="B72" s="207" t="str">
-        <f aca="false">DEC2HEX(C72,2)</f>
+      <c r="D72" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="126"/>
+      <c r="M72" s="196"/>
+      <c r="N72" s="196"/>
+      <c r="O72" s="126"/>
+      <c r="P72" s="198" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A73" s="206" t="s">
+        <v>299</v>
+      </c>
+      <c r="B73" s="207" t="str">
+        <f aca="false">DEC2HEX(C73,2)</f>
         <v>54</v>
       </c>
-      <c r="C72" s="130" t="n">
-        <f aca="false">IF(D72=1,128,0)+IF(E72=1,64,0)+IF(F72=1,32,0)+IF(G72=1,16,0)+IF(H72=1,8,0)+IF(I72=1,4,0)+IF(J72=1,2,0)+IF(K72=1,1,0)</f>
+      <c r="C73" s="130" t="n">
+        <f aca="false">IF(D73=1,128,0)+IF(E73=1,64,0)+IF(F73=1,32,0)+IF(G73=1,16,0)+IF(H73=1,8,0)+IF(I73=1,4,0)+IF(J73=1,2,0)+IF(K73=1,1,0)</f>
         <v>84</v>
       </c>
-      <c r="D72" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="208"/>
-      <c r="M72" s="217"/>
-      <c r="N72" s="217"/>
-      <c r="O72" s="208"/>
-      <c r="P72" s="218" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="209" t="s">
-        <v>297</v>
-      </c>
-      <c r="B73" s="183" t="str">
-        <f aca="false">DEC2HEX(C73,2)</f>
+      <c r="D73" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="208"/>
+      <c r="M73" s="217"/>
+      <c r="N73" s="217"/>
+      <c r="O73" s="208"/>
+      <c r="P73" s="218" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A74" s="209" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="183" t="str">
+        <f aca="false">DEC2HEX(C74,2)</f>
         <v>05</v>
       </c>
-      <c r="C73" s="210" t="n">
-        <f aca="false">IF(D73=1,128,0)+IF(E73=1,64,0)+IF(F73=1,32,0)+IF(G73=1,16,0)+IF(H73=1,8,0)+IF(I73=1,4,0)+IF(J73=1,2,0)+IF(K73=1,1,0)</f>
+      <c r="C74" s="210" t="n">
+        <f aca="false">IF(D74=1,128,0)+IF(E74=1,64,0)+IF(F74=1,32,0)+IF(G74=1,16,0)+IF(H74=1,8,0)+IF(I74=1,4,0)+IF(J74=1,2,0)+IF(K74=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="D73" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="175" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="212" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="213"/>
-      <c r="M73" s="214"/>
-      <c r="N73" s="214"/>
-      <c r="O73" s="213"/>
-      <c r="P73" s="215" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="206" t="s">
-        <v>299</v>
-      </c>
-      <c r="B74" s="207" t="str">
-        <f aca="false">DEC2HEX(C74,2)</f>
+      <c r="D74" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="213"/>
+      <c r="M74" s="214"/>
+      <c r="N74" s="214"/>
+      <c r="O74" s="213"/>
+      <c r="P74" s="215" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A75" s="206" t="s">
+        <v>303</v>
+      </c>
+      <c r="B75" s="207" t="str">
+        <f aca="false">DEC2HEX(C75,2)</f>
         <v>15</v>
       </c>
-      <c r="C74" s="130" t="n">
-        <f aca="false">IF(D74=1,128,0)+IF(E74=1,64,0)+IF(F74=1,32,0)+IF(G74=1,16,0)+IF(H74=1,8,0)+IF(I74=1,4,0)+IF(J74=1,2,0)+IF(K74=1,1,0)</f>
+      <c r="C75" s="130" t="n">
+        <f aca="false">IF(D75=1,128,0)+IF(E75=1,64,0)+IF(F75=1,32,0)+IF(G75=1,16,0)+IF(H75=1,8,0)+IF(I75=1,4,0)+IF(J75=1,2,0)+IF(K75=1,1,0)</f>
         <v>21</v>
       </c>
-      <c r="D74" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="208"/>
-      <c r="M74" s="217"/>
-      <c r="N74" s="217"/>
-      <c r="O74" s="208"/>
-      <c r="P74" s="218" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="209" t="s">
-        <v>301</v>
-      </c>
-      <c r="B75" s="183" t="str">
-        <f aca="false">DEC2HEX(C75,2)</f>
+      <c r="D75" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="208"/>
+      <c r="M75" s="217"/>
+      <c r="N75" s="217"/>
+      <c r="O75" s="208"/>
+      <c r="P75" s="218" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A76" s="209" t="s">
+        <v>305</v>
+      </c>
+      <c r="B76" s="183" t="str">
+        <f aca="false">DEC2HEX(C76,2)</f>
         <v>46</v>
       </c>
-      <c r="C75" s="210" t="n">
-        <f aca="false">IF(D75=1,128,0)+IF(E75=1,64,0)+IF(F75=1,32,0)+IF(G75=1,16,0)+IF(H75=1,8,0)+IF(I75=1,4,0)+IF(J75=1,2,0)+IF(K75=1,1,0)</f>
+      <c r="C76" s="210" t="n">
+        <f aca="false">IF(D76=1,128,0)+IF(E76=1,64,0)+IF(F76=1,32,0)+IF(G76=1,16,0)+IF(H76=1,8,0)+IF(I76=1,4,0)+IF(J76=1,2,0)+IF(K76=1,1,0)</f>
         <v>70</v>
       </c>
-      <c r="D75" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="175" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="175" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="175" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="213"/>
-      <c r="M75" s="214"/>
-      <c r="N75" s="214"/>
-      <c r="O75" s="213"/>
-      <c r="P75" s="215"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="195" t="s">
-        <v>302</v>
-      </c>
-      <c r="B76" s="16" t="str">
-        <f aca="false">DEC2HEX(C76,2)</f>
-        <v>56</v>
-      </c>
-      <c r="C76" s="105" t="n">
-        <f aca="false">IF(D76=1,128,0)+IF(E76=1,64,0)+IF(F76=1,32,0)+IF(G76=1,16,0)+IF(H76=1,8,0)+IF(I76=1,4,0)+IF(J76=1,2,0)+IF(K76=1,1,0)</f>
-        <v>86</v>
-      </c>
-      <c r="D76" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="126"/>
-      <c r="M76" s="196"/>
-      <c r="N76" s="196"/>
-      <c r="O76" s="126"/>
-      <c r="P76" s="198"/>
+      <c r="D76" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="213"/>
+      <c r="M76" s="214"/>
+      <c r="N76" s="214"/>
+      <c r="O76" s="213"/>
+      <c r="P76" s="215"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A77" s="195" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B77" s="16" t="str">
         <f aca="false">DEC2HEX(C77,2)</f>
-        <v>C7</v>
+        <v>56</v>
       </c>
       <c r="C77" s="105" t="n">
         <f aca="false">IF(D77=1,128,0)+IF(E77=1,64,0)+IF(F77=1,32,0)+IF(G77=1,16,0)+IF(H77=1,8,0)+IF(I77=1,4,0)+IF(J77=1,2,0)+IF(K77=1,1,0)</f>
-        <v>199</v>
+        <v>86</v>
       </c>
       <c r="D77" s="48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" s="105" t="n">
         <v>1</v>
@@ -9565,7 +9559,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="48" t="n">
         <v>0</v>
@@ -9577,7 +9571,7 @@
         <v>1</v>
       </c>
       <c r="K77" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="126"/>
       <c r="M77" s="196"/>
@@ -9586,215 +9580,257 @@
       <c r="P77" s="198"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="206" t="s">
-        <v>304</v>
-      </c>
-      <c r="B78" s="207" t="str">
+      <c r="A78" s="195" t="s">
+        <v>307</v>
+      </c>
+      <c r="B78" s="16" t="str">
         <f aca="false">DEC2HEX(C78,2)</f>
+        <v>C7</v>
+      </c>
+      <c r="C78" s="105" t="n">
+        <f aca="false">IF(D78=1,128,0)+IF(E78=1,64,0)+IF(F78=1,32,0)+IF(G78=1,16,0)+IF(H78=1,8,0)+IF(I78=1,4,0)+IF(J78=1,2,0)+IF(K78=1,1,0)</f>
+        <v>199</v>
+      </c>
+      <c r="D78" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="126"/>
+      <c r="M78" s="196"/>
+      <c r="N78" s="196"/>
+      <c r="O78" s="126"/>
+      <c r="P78" s="198"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A79" s="206" t="s">
+        <v>308</v>
+      </c>
+      <c r="B79" s="207" t="str">
+        <f aca="false">DEC2HEX(C79,2)</f>
         <v>D7</v>
       </c>
-      <c r="C78" s="130" t="n">
-        <f aca="false">IF(D78=1,128,0)+IF(E78=1,64,0)+IF(F78=1,32,0)+IF(G78=1,16,0)+IF(H78=1,8,0)+IF(I78=1,4,0)+IF(J78=1,2,0)+IF(K78=1,1,0)</f>
+      <c r="C79" s="130" t="n">
+        <f aca="false">IF(D79=1,128,0)+IF(E79=1,64,0)+IF(F79=1,32,0)+IF(G79=1,16,0)+IF(H79=1,8,0)+IF(I79=1,4,0)+IF(J79=1,2,0)+IF(K79=1,1,0)</f>
         <v>215</v>
       </c>
-      <c r="D78" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="208"/>
-      <c r="M78" s="217"/>
-      <c r="N78" s="217"/>
-      <c r="O78" s="208"/>
-      <c r="P78" s="218"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="209" t="s">
-        <v>305</v>
-      </c>
-      <c r="B79" s="183" t="str">
-        <f aca="false">DEC2HEX(C79,2)</f>
+      <c r="D79" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="208"/>
+      <c r="M79" s="217"/>
+      <c r="N79" s="217"/>
+      <c r="O79" s="208"/>
+      <c r="P79" s="218"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A80" s="209" t="s">
+        <v>309</v>
+      </c>
+      <c r="B80" s="183" t="str">
+        <f aca="false">DEC2HEX(C80,2)</f>
         <v>0C</v>
       </c>
-      <c r="C79" s="210" t="n">
-        <f aca="false">IF(D79=1,128,0)+IF(E79=1,64,0)+IF(F79=1,32,0)+IF(G79=1,16,0)+IF(H79=1,8,0)+IF(I79=1,4,0)+IF(J79=1,2,0)+IF(K79=1,1,0)</f>
+      <c r="C80" s="210" t="n">
+        <f aca="false">IF(D80=1,128,0)+IF(E80=1,64,0)+IF(F80=1,32,0)+IF(G80=1,16,0)+IF(H80=1,8,0)+IF(I80=1,4,0)+IF(J80=1,2,0)+IF(K80=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="D79" s="211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="211" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" s="175" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="213"/>
-      <c r="M79" s="214"/>
-      <c r="N79" s="214"/>
-      <c r="O79" s="213"/>
-      <c r="P79" s="215"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="206" t="s">
-        <v>306</v>
-      </c>
-      <c r="B80" s="207" t="str">
-        <f aca="false">DEC2HEX(C80,2)</f>
+      <c r="D80" s="211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="213"/>
+      <c r="M80" s="214"/>
+      <c r="N80" s="214"/>
+      <c r="O80" s="213"/>
+      <c r="P80" s="215"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A81" s="206" t="s">
+        <v>310</v>
+      </c>
+      <c r="B81" s="207" t="str">
+        <f aca="false">DEC2HEX(C81,2)</f>
         <v>8C</v>
       </c>
-      <c r="C80" s="130" t="n">
-        <f aca="false">IF(D80=1,128,0)+IF(E80=1,64,0)+IF(F80=1,32,0)+IF(G80=1,16,0)+IF(H80=1,8,0)+IF(I80=1,4,0)+IF(J80=1,2,0)+IF(K80=1,1,0)</f>
+      <c r="C81" s="130" t="n">
+        <f aca="false">IF(D81=1,128,0)+IF(E81=1,64,0)+IF(F81=1,32,0)+IF(G81=1,16,0)+IF(H81=1,8,0)+IF(I81=1,4,0)+IF(J81=1,2,0)+IF(K81=1,1,0)</f>
         <v>140</v>
       </c>
-      <c r="D80" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="208"/>
-      <c r="M80" s="217"/>
-      <c r="N80" s="217"/>
-      <c r="O80" s="208"/>
-      <c r="P80" s="218"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="195"/>
-      <c r="B81" s="16" t="str">
-        <f aca="false">DEC2HEX(C81,2)</f>
-        <v>00</v>
-      </c>
-      <c r="C81" s="105" t="n">
-        <f aca="false">IF(D81=1,128,0)+IF(E81=1,64,0)+IF(F81=1,32,0)+IF(G81=1,16,0)+IF(H81=1,8,0)+IF(I81=1,4,0)+IF(J81=1,2,0)+IF(K81=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D81" s="48"/>
-      <c r="E81" s="105"/>
-      <c r="F81" s="105"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="105"/>
-      <c r="J81" s="105"/>
-      <c r="K81" s="49"/>
-      <c r="L81" s="126"/>
-      <c r="M81" s="196"/>
-      <c r="N81" s="196"/>
-      <c r="O81" s="126"/>
-      <c r="P81" s="198"/>
+      <c r="D81" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="208"/>
+      <c r="M81" s="217"/>
+      <c r="N81" s="217"/>
+      <c r="O81" s="208"/>
+      <c r="P81" s="218"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="206"/>
-      <c r="B82" s="207" t="str">
+      <c r="A82" s="195"/>
+      <c r="B82" s="16" t="str">
         <f aca="false">DEC2HEX(C82,2)</f>
         <v>00</v>
       </c>
-      <c r="C82" s="130" t="n">
+      <c r="C82" s="105" t="n">
         <f aca="false">IF(D82=1,128,0)+IF(E82=1,64,0)+IF(F82=1,32,0)+IF(G82=1,16,0)+IF(H82=1,8,0)+IF(I82=1,4,0)+IF(J82=1,2,0)+IF(K82=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D82" s="129"/>
-      <c r="E82" s="130"/>
-      <c r="F82" s="130"/>
-      <c r="G82" s="133"/>
-      <c r="H82" s="129"/>
-      <c r="I82" s="130"/>
-      <c r="J82" s="130"/>
-      <c r="K82" s="133"/>
-      <c r="L82" s="208"/>
-      <c r="M82" s="217"/>
-      <c r="N82" s="217"/>
-      <c r="O82" s="208"/>
-      <c r="P82" s="218"/>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L83" s="127"/>
+      <c r="D82" s="48"/>
+      <c r="E82" s="105"/>
+      <c r="F82" s="105"/>
+      <c r="G82" s="49"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="105"/>
+      <c r="J82" s="105"/>
+      <c r="K82" s="49"/>
+      <c r="L82" s="126"/>
+      <c r="M82" s="196"/>
+      <c r="N82" s="196"/>
+      <c r="O82" s="126"/>
+      <c r="P82" s="198"/>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A83" s="206"/>
+      <c r="B83" s="207" t="str">
+        <f aca="false">DEC2HEX(C83,2)</f>
+        <v>00</v>
+      </c>
+      <c r="C83" s="130" t="n">
+        <f aca="false">IF(D83=1,128,0)+IF(E83=1,64,0)+IF(F83=1,32,0)+IF(G83=1,16,0)+IF(H83=1,8,0)+IF(I83=1,4,0)+IF(J83=1,2,0)+IF(K83=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="129"/>
+      <c r="E83" s="130"/>
+      <c r="F83" s="130"/>
+      <c r="G83" s="133"/>
+      <c r="H83" s="129"/>
+      <c r="I83" s="130"/>
+      <c r="J83" s="130"/>
+      <c r="K83" s="133"/>
+      <c r="L83" s="208"/>
+      <c r="M83" s="217"/>
+      <c r="N83" s="217"/>
+      <c r="O83" s="208"/>
+      <c r="P83" s="218"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="3"/>
-      <c r="O84" s="221"/>
-      <c r="P84" s="3"/>
+      <c r="L84" s="127"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>308</v>
+        <v>311</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="221"/>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="P12" r:id="rId1" location="Basic_and_interchange_formats" display="https://en.wikipedia.org/wiki/IEEE_754#Basic_and_interchange_formats"/>
-    <hyperlink ref="P38" r:id="rId2" location="Durations" display="https://en.wikipedia.org/wiki/ISO_8601#Durations"/>
-    <hyperlink ref="P39" r:id="rId3" location="time" display="http://www.w3.org/TR/xmlschema-2/#time"/>
-    <hyperlink ref="P40" r:id="rId4" location="date" display="http://www.w3.org/TR/xmlschema-2/#date"/>
-    <hyperlink ref="P41" r:id="rId5" location="dateTime" display="http://www.w3.org/TR/xmlschema-2/#dateTime"/>
-    <hyperlink ref="P50" r:id="rId6" display="https://learn.microsoft.com/en-us/office/vba/language/reference/user-interface-help/currency-data-type"/>
+    <hyperlink ref="P39" r:id="rId2" location="Durations" display="https://en.wikipedia.org/wiki/ISO_8601#Durations"/>
+    <hyperlink ref="P40" r:id="rId3" location="time" display="http://www.w3.org/TR/xmlschema-2/#time"/>
+    <hyperlink ref="P41" r:id="rId4" location="date" display="http://www.w3.org/TR/xmlschema-2/#date"/>
+    <hyperlink ref="P42" r:id="rId5" location="dateTime" display="http://www.w3.org/TR/xmlschema-2/#dateTime"/>
+    <hyperlink ref="P51" r:id="rId6" display="https://learn.microsoft.com/en-us/office/vba/language/reference/user-interface-help/currency-data-type"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9823,7 +9859,7 @@
         <v>220</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>50</v>
@@ -9838,12 +9874,12 @@
         <v>114</v>
       </c>
       <c r="G1" s="222" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H1" s="222"/>
       <c r="I1" s="222"/>
       <c r="J1" s="222" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9857,26 +9893,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>114</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9890,13 +9926,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>114</v>
@@ -9906,10 +9942,10 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9926,25 +9962,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9961,25 +9997,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9993,28 +10029,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10028,28 +10064,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10063,26 +10099,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>114</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10096,13 +10132,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>114</v>
@@ -10112,10 +10148,10 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10129,28 +10165,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10164,28 +10200,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10199,28 +10235,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10234,28 +10270,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Connection" sheetId="1" state="visible" r:id="rId3"/>
@@ -2424,7 +2424,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="225">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2725,11 +2725,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2761,7 +2757,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4197,7 +4193,7 @@
       <c r="P13" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="Q13" s="75"/>
+      <c r="Q13" s="55"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A14" s="47"/>
@@ -4222,7 +4218,7 @@
       <c r="N14" s="52"/>
       <c r="O14" s="46"/>
       <c r="P14" s="54"/>
-      <c r="Q14" s="76" t="s">
+      <c r="Q14" s="75" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4247,32 +4243,32 @@
       <c r="N15" s="52"/>
       <c r="O15" s="46"/>
       <c r="P15" s="54"/>
-      <c r="Q15" s="76" t="s">
+      <c r="Q15" s="75" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="79" t="s">
+      <c r="A16" s="76"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="77"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="76"/>
       <c r="I16" s="48"/>
       <c r="J16" s="49"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="82" t="s">
+      <c r="K16" s="80"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="N16" s="78"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="83"/>
-      <c r="Q16" s="84" t="s">
+      <c r="N16" s="77"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="83" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4335,42 +4331,42 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A18" s="85"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="88"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="87"/>
       <c r="I18" s="48"/>
       <c r="J18" s="49"/>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="89"/>
-      <c r="O18" s="87"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="93"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="86"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="92"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A19" s="94"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="77"/>
+      <c r="A19" s="93"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="76"/>
       <c r="I19" s="48"/>
       <c r="J19" s="49"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="97"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="96"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="30" t="s">
@@ -4429,101 +4425,101 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="85"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="89"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="88"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="88"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="87"/>
       <c r="I21" s="48"/>
       <c r="J21" s="49"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="100" t="s">
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="N21" s="89" t="s">
+      <c r="N21" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="O21" s="98" t="s">
+      <c r="O21" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="P21" s="101" t="s">
+      <c r="P21" s="100" t="s">
         <v>74</v>
       </c>
-      <c r="Q21" s="102" t="s">
+      <c r="Q21" s="101" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="85"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="99" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="89"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="88"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="88"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="87"/>
       <c r="I22" s="48"/>
       <c r="J22" s="49"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="100" t="s">
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="N22" s="89" t="n">
+      <c r="N22" s="88" t="n">
         <v>4</v>
       </c>
-      <c r="O22" s="98" t="n">
+      <c r="O22" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="101" t="s">
+      <c r="P22" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="Q22" s="102" t="s">
+      <c r="Q22" s="101" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="85"/>
-      <c r="B23" s="89" t="s">
+      <c r="A23" s="84"/>
+      <c r="B23" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="87"/>
-      <c r="G23" s="87"/>
-      <c r="H23" s="88"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="87"/>
       <c r="I23" s="48"/>
       <c r="J23" s="49"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="90" t="s">
+      <c r="K23" s="89"/>
+      <c r="L23" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="M23" s="100" t="s">
+      <c r="M23" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="N23" s="89" t="n">
+      <c r="N23" s="88" t="n">
         <v>8</v>
       </c>
-      <c r="O23" s="98" t="n">
+      <c r="O23" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="P23" s="101" t="s">
+      <c r="P23" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="Q23" s="102"/>
+      <c r="Q23" s="101"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A24" s="44"/>
@@ -4630,12 +4626,12 @@
       <c r="I26" s="48"/>
       <c r="J26" s="49"/>
       <c r="K26" s="69"/>
-      <c r="L26" s="103"/>
-      <c r="M26" s="104"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="103"/>
       <c r="N26" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="O26" s="105" t="n">
+      <c r="O26" s="104" t="n">
         <v>4</v>
       </c>
       <c r="P26" s="71" t="s">
@@ -4644,23 +4640,23 @@
       <c r="Q26" s="72"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A27" s="94"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="77"/>
+      <c r="A27" s="93"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="76"/>
       <c r="I27" s="48"/>
       <c r="J27" s="49"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="96"/>
-      <c r="N27" s="80"/>
-      <c r="O27" s="79"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="97"/>
+      <c r="K27" s="80"/>
+      <c r="L27" s="80"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="79"/>
+      <c r="O27" s="78"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="96"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="30" t="s">
@@ -4893,23 +4889,23 @@
       <c r="Q34" s="55"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A35" s="94"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="77"/>
+      <c r="A35" s="93"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="76"/>
       <c r="I35" s="48"/>
       <c r="J35" s="49"/>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="78"/>
-      <c r="O35" s="79"/>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="97"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="80"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="77"/>
+      <c r="O35" s="78"/>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="96"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="30" t="s">
@@ -4972,29 +4968,29 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A37" s="94"/>
-      <c r="B37" s="80"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="95"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="77"/>
+      <c r="A37" s="93"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="76"/>
       <c r="I37" s="48"/>
       <c r="J37" s="49"/>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
-      <c r="M37" s="96"/>
-      <c r="N37" s="78" t="n">
+      <c r="K37" s="80"/>
+      <c r="L37" s="80"/>
+      <c r="M37" s="95"/>
+      <c r="N37" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="O37" s="79" t="n">
+      <c r="O37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="P37" s="83" t="s">
+      <c r="P37" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="Q37" s="97"/>
+      <c r="Q37" s="96"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="30" t="s">
@@ -5068,7 +5064,7 @@
       <c r="I39" s="48"/>
       <c r="J39" s="49"/>
       <c r="K39" s="50"/>
-      <c r="L39" s="106"/>
+      <c r="L39" s="105"/>
       <c r="M39" s="51" t="s">
         <v>97</v>
       </c>
@@ -5155,31 +5151,31 @@
       <c r="Q42" s="63"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A43" s="94"/>
-      <c r="B43" s="78" t="s">
+      <c r="A43" s="93"/>
+      <c r="B43" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="79"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="79"/>
-      <c r="G43" s="79"/>
-      <c r="H43" s="77"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="76"/>
       <c r="I43" s="48"/>
       <c r="J43" s="49"/>
-      <c r="K43" s="81"/>
-      <c r="L43" s="81"/>
-      <c r="M43" s="96" t="s">
+      <c r="K43" s="80"/>
+      <c r="L43" s="80"/>
+      <c r="M43" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="N43" s="80"/>
-      <c r="O43" s="79" t="n">
+      <c r="N43" s="79"/>
+      <c r="O43" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="83" t="s">
+      <c r="P43" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="Q43" s="97"/>
+      <c r="Q43" s="96"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="30" t="s">
@@ -5222,29 +5218,29 @@
       <c r="M44" s="37"/>
       <c r="N44" s="42"/>
       <c r="O44" s="43"/>
-      <c r="P44" s="107"/>
+      <c r="P44" s="106"/>
       <c r="Q44" s="39"/>
       <c r="R44" s="40"/>
       <c r="S44" s="40"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A45" s="94"/>
-      <c r="B45" s="78"/>
-      <c r="C45" s="79"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="80"/>
-      <c r="F45" s="79"/>
-      <c r="G45" s="79"/>
-      <c r="H45" s="77"/>
+      <c r="A45" s="93"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="79"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="76"/>
       <c r="I45" s="48"/>
       <c r="J45" s="49"/>
-      <c r="K45" s="82"/>
-      <c r="L45" s="81"/>
-      <c r="M45" s="96"/>
-      <c r="N45" s="80"/>
-      <c r="O45" s="79"/>
-      <c r="P45" s="108"/>
-      <c r="Q45" s="97"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="80"/>
+      <c r="M45" s="95"/>
+      <c r="N45" s="79"/>
+      <c r="O45" s="78"/>
+      <c r="P45" s="107"/>
+      <c r="Q45" s="96"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="30" t="s">
@@ -5369,23 +5365,23 @@
       <c r="Q50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A51" s="94"/>
-      <c r="B51" s="78"/>
-      <c r="C51" s="79"/>
-      <c r="D51" s="77"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="77"/>
+      <c r="A51" s="93"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="78"/>
+      <c r="H51" s="76"/>
       <c r="I51" s="48"/>
       <c r="J51" s="49"/>
-      <c r="K51" s="81"/>
-      <c r="L51" s="81"/>
-      <c r="M51" s="96"/>
-      <c r="N51" s="80"/>
-      <c r="O51" s="79"/>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="97"/>
+      <c r="K51" s="80"/>
+      <c r="L51" s="80"/>
+      <c r="M51" s="95"/>
+      <c r="N51" s="79"/>
+      <c r="O51" s="78"/>
+      <c r="P51" s="82"/>
+      <c r="Q51" s="96"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="30" t="s">
@@ -5621,31 +5617,31 @@
       <c r="Q59" s="55"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A60" s="94"/>
-      <c r="B60" s="80"/>
-      <c r="C60" s="79"/>
-      <c r="D60" s="95"/>
-      <c r="E60" s="80"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
-      <c r="H60" s="77"/>
+      <c r="A60" s="93"/>
+      <c r="B60" s="79"/>
+      <c r="C60" s="78"/>
+      <c r="D60" s="94"/>
+      <c r="E60" s="79"/>
+      <c r="F60" s="78"/>
+      <c r="G60" s="78"/>
+      <c r="H60" s="76"/>
       <c r="I60" s="48"/>
       <c r="J60" s="49"/>
-      <c r="K60" s="81"/>
-      <c r="L60" s="81" t="s">
+      <c r="K60" s="80"/>
+      <c r="L60" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="M60" s="96"/>
-      <c r="N60" s="78" t="n">
+      <c r="M60" s="95"/>
+      <c r="N60" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="O60" s="79" t="n">
+      <c r="O60" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="P60" s="83" t="s">
+      <c r="P60" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="Q60" s="97"/>
+      <c r="Q60" s="96"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="30" t="s">
@@ -5748,27 +5744,27 @@
       <c r="Q63" s="55"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A64" s="94"/>
-      <c r="B64" s="80"/>
-      <c r="C64" s="79"/>
-      <c r="D64" s="77"/>
-      <c r="E64" s="80"/>
-      <c r="F64" s="79"/>
-      <c r="G64" s="79"/>
-      <c r="H64" s="77"/>
+      <c r="A64" s="93"/>
+      <c r="B64" s="79"/>
+      <c r="C64" s="78"/>
+      <c r="D64" s="76"/>
+      <c r="E64" s="79"/>
+      <c r="F64" s="78"/>
+      <c r="G64" s="78"/>
+      <c r="H64" s="76"/>
       <c r="I64" s="48"/>
       <c r="J64" s="49"/>
-      <c r="K64" s="81"/>
-      <c r="L64" s="81"/>
-      <c r="M64" s="96" t="s">
+      <c r="K64" s="80"/>
+      <c r="L64" s="80"/>
+      <c r="M64" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="N64" s="80"/>
-      <c r="O64" s="79"/>
-      <c r="P64" s="83" t="s">
+      <c r="N64" s="79"/>
+      <c r="O64" s="78"/>
+      <c r="P64" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="Q64" s="97"/>
+      <c r="Q64" s="96"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="30" t="s">
@@ -5842,7 +5838,7 @@
       <c r="I66" s="48"/>
       <c r="J66" s="49"/>
       <c r="K66" s="50"/>
-      <c r="L66" s="106"/>
+      <c r="L66" s="105"/>
       <c r="M66" s="51"/>
       <c r="N66" s="45" t="n">
         <v>4</v>
@@ -6001,28 +5997,28 @@
       <c r="Q72" s="55"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A73" s="94"/>
-      <c r="B73" s="80"/>
-      <c r="C73" s="79"/>
-      <c r="D73" s="77"/>
-      <c r="E73" s="80"/>
-      <c r="F73" s="79"/>
-      <c r="G73" s="79"/>
-      <c r="H73" s="77"/>
+      <c r="A73" s="93"/>
+      <c r="B73" s="79"/>
+      <c r="C73" s="78"/>
+      <c r="D73" s="76"/>
+      <c r="E73" s="79"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="78"/>
+      <c r="H73" s="76"/>
       <c r="I73" s="48"/>
       <c r="J73" s="49"/>
-      <c r="K73" s="81"/>
-      <c r="L73" s="81"/>
-      <c r="M73" s="96"/>
-      <c r="N73" s="78"/>
-      <c r="O73" s="79"/>
-      <c r="P73" s="83"/>
-      <c r="Q73" s="97"/>
+      <c r="K73" s="80"/>
+      <c r="L73" s="80"/>
+      <c r="M73" s="95"/>
+      <c r="N73" s="77"/>
+      <c r="O73" s="78"/>
+      <c r="P73" s="82"/>
+      <c r="Q73" s="96"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-      <c r="J75" s="109"/>
+      <c r="J75" s="108"/>
       <c r="K75" s="3" t="s">
         <v>39</v>
       </c>
@@ -6132,7 +6128,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>136</v>
       </c>
       <c r="C1" s="1"/>
@@ -6148,59 +6144,59 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="110" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111" t="s">
+      <c r="A7" s="110"/>
+      <c r="B7" s="110" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="111"/>
+      <c r="A8" s="110"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="110" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="111" t="s">
+      <c r="B10" s="110" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="111" t="s">
+      <c r="B11" s="110" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="111" t="s">
+      <c r="B12" s="110" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="111"/>
+      <c r="B13" s="110"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="110" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="111" t="s">
+      <c r="B15" s="110" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="111" t="s">
+      <c r="B16" s="110" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="111" t="s">
+      <c r="B17" s="110" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6220,7 +6216,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="109" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="1"/>
@@ -6300,7 +6296,7 @@
   <dimension ref="A1:R1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="112" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="111" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="5" width="3.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="5" width="18.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="15.59"/>
@@ -6312,833 +6308,833 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="113" t="n">
+      <c r="B1" s="112" t="n">
         <v>7</v>
       </c>
-      <c r="C1" s="113" t="n">
+      <c r="C1" s="112" t="n">
         <v>6</v>
       </c>
-      <c r="D1" s="113" t="n">
+      <c r="D1" s="112" t="n">
         <v>5</v>
       </c>
-      <c r="E1" s="113" t="n">
+      <c r="E1" s="112" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="113" t="n">
+      <c r="F1" s="112" t="n">
         <v>3</v>
       </c>
-      <c r="G1" s="113" t="n">
+      <c r="G1" s="112" t="n">
         <v>2</v>
       </c>
-      <c r="H1" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" s="113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1" s="112" t="s">
+      <c r="H1" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="112" t="s">
+      <c r="K1" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="112" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="113" t="s">
+      <c r="L1" s="111" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="112" t="s">
         <v>154</v>
       </c>
-      <c r="N1" s="113" t="s">
+      <c r="N1" s="112" t="s">
         <v>155</v>
       </c>
-      <c r="O1" s="112" t="s">
+      <c r="O1" s="111" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
+      <c r="A2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="116"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="120" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="121"/>
-      <c r="K3" s="122" t="s">
+      <c r="J3" s="120"/>
+      <c r="K3" s="121" t="s">
         <v>157</v>
       </c>
-      <c r="L3" s="122" t="s">
+      <c r="L3" s="121" t="s">
         <v>158</v>
       </c>
-      <c r="M3" s="120" t="s">
+      <c r="M3" s="119" t="s">
         <v>159</v>
       </c>
-      <c r="N3" s="120" t="s">
+      <c r="N3" s="119" t="s">
         <v>160</v>
       </c>
-      <c r="O3" s="123"/>
+      <c r="O3" s="122"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="124"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="125"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="124"/>
       <c r="H4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="128"/>
-      <c r="J4" s="129"/>
-      <c r="K4" s="130" t="s">
+      <c r="I4" s="127"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="129" t="s">
         <v>161</v>
       </c>
-      <c r="L4" s="131"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="132"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="127"/>
+      <c r="N4" s="127"/>
+      <c r="O4" s="131"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="124"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="127"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="126"/>
       <c r="G5" s="12" t="s">
         <v>50</v>
       </c>
       <c r="H5" s="12"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="129" t="s">
+      <c r="I5" s="127"/>
+      <c r="J5" s="128" t="s">
         <v>162</v>
       </c>
-      <c r="K5" s="130" t="s">
+      <c r="K5" s="129" t="s">
         <v>163</v>
       </c>
-      <c r="L5" s="131" t="s">
+      <c r="L5" s="130" t="s">
         <v>164</v>
       </c>
-      <c r="M5" s="128" t="s">
+      <c r="M5" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="N5" s="128" t="s">
+      <c r="N5" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="O5" s="132"/>
+      <c r="O5" s="131"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="133"/>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="136" t="s">
+      <c r="B6" s="132"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="138" t="s">
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="137" t="s">
         <v>162</v>
       </c>
-      <c r="K6" s="139" t="s">
+      <c r="K6" s="138" t="s">
         <v>165</v>
       </c>
-      <c r="L6" s="139" t="s">
+      <c r="L6" s="138" t="s">
         <v>166</v>
       </c>
-      <c r="M6" s="137" t="n">
+      <c r="M6" s="136" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="137" t="s">
+      <c r="N6" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="O6" s="140"/>
+      <c r="O6" s="139"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="114" t="s">
+      <c r="A7" s="113" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="141"/>
-      <c r="C7" s="142"/>
-      <c r="D7" s="142"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="144"/>
-      <c r="G7" s="142"/>
-      <c r="H7" s="142"/>
-      <c r="I7" s="145"/>
-      <c r="J7" s="146" t="s">
+      <c r="B7" s="140"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="141"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145" t="s">
         <v>169</v>
       </c>
-      <c r="K7" s="147"/>
-      <c r="L7" s="147"/>
-      <c r="M7" s="145"/>
-      <c r="N7" s="145"/>
-      <c r="O7" s="148"/>
-      <c r="P7" s="149"/>
-      <c r="Q7" s="149"/>
-      <c r="R7" s="149"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="148"/>
+      <c r="Q7" s="148"/>
+      <c r="R7" s="148"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B8" s="124"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="150" t="s">
+      <c r="B8" s="123"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="149" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="127"/>
-      <c r="G8" s="125"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="124"/>
       <c r="H8" s="12"/>
-      <c r="I8" s="128"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="130" t="s">
+      <c r="I8" s="127"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="129" t="s">
         <v>170</v>
       </c>
-      <c r="L8" s="131"/>
-      <c r="M8" s="128"/>
-      <c r="N8" s="128"/>
-      <c r="O8" s="132"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="127"/>
+      <c r="O8" s="131"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="114" t="s">
+      <c r="A9" s="113" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="151"/>
-      <c r="C9" s="152"/>
-      <c r="D9" s="152"/>
-      <c r="E9" s="153"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="152"/>
-      <c r="H9" s="155"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="157" t="s">
+      <c r="B9" s="150"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="151"/>
+      <c r="H9" s="154"/>
+      <c r="I9" s="155"/>
+      <c r="J9" s="156" t="s">
         <v>171</v>
       </c>
-      <c r="K9" s="158"/>
-      <c r="L9" s="158"/>
-      <c r="M9" s="156"/>
-      <c r="N9" s="156"/>
-      <c r="O9" s="159"/>
-      <c r="P9" s="149"/>
-      <c r="Q9" s="149"/>
-      <c r="R9" s="149"/>
+      <c r="K9" s="157"/>
+      <c r="L9" s="157"/>
+      <c r="M9" s="155"/>
+      <c r="N9" s="155"/>
+      <c r="O9" s="158"/>
+      <c r="P9" s="148"/>
+      <c r="Q9" s="148"/>
+      <c r="R9" s="148"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B10" s="124"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="150"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="125"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="124"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="132"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="137"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="138"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="136"/>
+      <c r="O10" s="131"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A11" s="114" t="s">
+      <c r="A11" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="151"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="153"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="146" t="s">
+      <c r="B11" s="150"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="152"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="151"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="155"/>
+      <c r="J11" s="145" t="s">
         <v>172</v>
       </c>
-      <c r="K11" s="158"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="145"/>
-      <c r="N11" s="145"/>
-      <c r="O11" s="159"/>
-      <c r="P11" s="149"/>
-      <c r="Q11" s="149"/>
-      <c r="R11" s="149"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="144"/>
+      <c r="N11" s="144"/>
+      <c r="O11" s="158"/>
+      <c r="P11" s="148"/>
+      <c r="Q11" s="148"/>
+      <c r="R11" s="148"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B12" s="124"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="125"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="124"/>
       <c r="H12" s="12"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="131" t="s">
+      <c r="I12" s="127"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="130" t="s">
         <v>77</v>
       </c>
-      <c r="M12" s="128" t="n">
+      <c r="M12" s="127" t="n">
         <v>4</v>
       </c>
-      <c r="N12" s="128" t="s">
+      <c r="N12" s="127" t="s">
         <v>167</v>
       </c>
-      <c r="O12" s="132"/>
+      <c r="O12" s="131"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B13" s="124"/>
-      <c r="C13" s="125"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="124"/>
       <c r="D13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="126"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="124"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="131" t="s">
+      <c r="I13" s="127"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="130" t="s">
         <v>173</v>
       </c>
-      <c r="L13" s="131" t="s">
+      <c r="L13" s="130" t="s">
         <v>174</v>
       </c>
-      <c r="M13" s="128" t="n">
+      <c r="M13" s="127" t="n">
         <v>4</v>
       </c>
-      <c r="N13" s="128" t="s">
+      <c r="N13" s="127" t="s">
         <v>175</v>
       </c>
-      <c r="O13" s="132" t="s">
+      <c r="O13" s="131" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B14" s="124"/>
-      <c r="C14" s="125"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="124"/>
       <c r="D14" s="12"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="124"/>
       <c r="H14" s="12"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="129" t="s">
+      <c r="I14" s="127"/>
+      <c r="J14" s="128" t="s">
         <v>173</v>
       </c>
-      <c r="K14" s="131"/>
-      <c r="L14" s="131" t="s">
+      <c r="K14" s="130"/>
+      <c r="L14" s="130" t="s">
         <v>177</v>
       </c>
-      <c r="M14" s="128" t="s">
+      <c r="M14" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="N14" s="128" t="s">
+      <c r="N14" s="127" t="s">
         <v>178</v>
       </c>
-      <c r="O14" s="132"/>
+      <c r="O14" s="131"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B15" s="160"/>
-      <c r="C15" s="134" t="s">
+      <c r="B15" s="159"/>
+      <c r="C15" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="161"/>
-      <c r="E15" s="162"/>
-      <c r="F15" s="163"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="139" t="s">
+      <c r="D15" s="160"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="137"/>
+      <c r="K15" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="L15" s="139" t="s">
+      <c r="L15" s="138" t="s">
         <v>119</v>
       </c>
-      <c r="M15" s="137" t="s">
+      <c r="M15" s="136" t="s">
         <v>159</v>
       </c>
-      <c r="N15" s="137" t="s">
+      <c r="N15" s="136" t="s">
         <v>180</v>
       </c>
-      <c r="O15" s="140"/>
+      <c r="O15" s="139"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="164"/>
-      <c r="C16" s="142"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="166"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="165"/>
-      <c r="H16" s="142"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146" t="s">
+      <c r="A16" s="113" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="163"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="164"/>
+      <c r="E16" s="165"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="164"/>
+      <c r="H16" s="141"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="145" t="s">
         <v>181</v>
       </c>
-      <c r="K16" s="147"/>
-      <c r="L16" s="147"/>
-      <c r="M16" s="145"/>
-      <c r="N16" s="145"/>
-      <c r="O16" s="148"/>
-      <c r="P16" s="149"/>
-      <c r="Q16" s="149"/>
-      <c r="R16" s="149"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="146"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="148"/>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="148"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B17" s="124"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="127"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="130" t="s">
+      <c r="B17" s="123"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="126"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="129" t="s">
         <v>182</v>
       </c>
-      <c r="L17" s="130"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="128"/>
-      <c r="O17" s="132"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="131"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B18" s="124"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="127"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="129"/>
-      <c r="K18" s="130" t="s">
+      <c r="B18" s="123"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="126"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="129" t="s">
         <v>183</v>
       </c>
-      <c r="L18" s="130"/>
-      <c r="M18" s="128"/>
-      <c r="N18" s="128"/>
-      <c r="O18" s="132"/>
+      <c r="L18" s="129"/>
+      <c r="M18" s="127"/>
+      <c r="N18" s="127"/>
+      <c r="O18" s="131"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B19" s="124"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="125" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="127"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="129"/>
-      <c r="K19" s="130" t="s">
+      <c r="B19" s="123"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="126"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="127"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="129" t="s">
         <v>184</v>
       </c>
-      <c r="L19" s="130"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="128"/>
-      <c r="O19" s="132"/>
+      <c r="L19" s="129"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="127"/>
+      <c r="O19" s="131"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="114" t="s">
+      <c r="A20" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="151"/>
-      <c r="C20" s="155"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="154"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="155"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="157" t="s">
+      <c r="B20" s="150"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="151"/>
+      <c r="H20" s="154"/>
+      <c r="I20" s="155"/>
+      <c r="J20" s="156" t="s">
         <v>182</v>
       </c>
-      <c r="K20" s="158"/>
-      <c r="L20" s="158"/>
-      <c r="M20" s="156"/>
-      <c r="N20" s="156"/>
-      <c r="O20" s="159"/>
-      <c r="P20" s="149"/>
-      <c r="Q20" s="149"/>
-      <c r="R20" s="149"/>
+      <c r="K20" s="157"/>
+      <c r="L20" s="157"/>
+      <c r="M20" s="155"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="158"/>
+      <c r="P20" s="148"/>
+      <c r="Q20" s="148"/>
+      <c r="R20" s="148"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B21" s="124"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="129"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="130" t="s">
+      <c r="B21" s="123"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="129" t="s">
         <v>186</v>
       </c>
-      <c r="M21" s="128" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="128" t="s">
+      <c r="M21" s="127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="127" t="s">
         <v>186</v>
       </c>
-      <c r="O21" s="132" t="s">
+      <c r="O21" s="131" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="114" t="s">
+      <c r="A22" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="B22" s="151"/>
-      <c r="C22" s="155"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="154"/>
-      <c r="G22" s="152"/>
-      <c r="H22" s="155"/>
-      <c r="I22" s="156"/>
-      <c r="J22" s="157" t="s">
+      <c r="B22" s="150"/>
+      <c r="C22" s="154"/>
+      <c r="D22" s="151"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="151"/>
+      <c r="H22" s="154"/>
+      <c r="I22" s="155"/>
+      <c r="J22" s="156" t="s">
         <v>189</v>
       </c>
-      <c r="K22" s="158"/>
-      <c r="L22" s="158"/>
-      <c r="M22" s="156"/>
-      <c r="N22" s="156"/>
-      <c r="O22" s="159"/>
-      <c r="P22" s="149"/>
-      <c r="Q22" s="149"/>
-      <c r="R22" s="149"/>
+      <c r="K22" s="157"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="155"/>
+      <c r="N22" s="155"/>
+      <c r="O22" s="158"/>
+      <c r="P22" s="148"/>
+      <c r="Q22" s="148"/>
+      <c r="R22" s="148"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B23" s="124"/>
-      <c r="C23" s="109" t="s">
+      <c r="B23" s="123"/>
+      <c r="C23" s="108" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="125"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="109"/>
-      <c r="I23" s="128"/>
-      <c r="J23" s="129"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="130" t="s">
+      <c r="D23" s="124"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="129" t="s">
         <v>190</v>
       </c>
-      <c r="M23" s="128" t="s">
+      <c r="M23" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="N23" s="128" t="s">
+      <c r="N23" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="O23" s="132" t="s">
+      <c r="O23" s="131" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B24" s="124"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="128"/>
-      <c r="J24" s="129"/>
-      <c r="K24" s="130"/>
-      <c r="L24" s="130" t="s">
+      <c r="B24" s="123"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="127"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="129" t="s">
         <v>186</v>
       </c>
-      <c r="M24" s="128" t="s">
+      <c r="M24" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="N24" s="128" t="s">
+      <c r="N24" s="127" t="s">
         <v>186</v>
       </c>
-      <c r="O24" s="132" t="s">
+      <c r="O24" s="131" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A25" s="114" t="s">
+      <c r="A25" s="113" t="s">
         <v>192</v>
       </c>
-      <c r="B25" s="151"/>
-      <c r="C25" s="155"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="152"/>
-      <c r="H25" s="155"/>
-      <c r="I25" s="156"/>
-      <c r="J25" s="157" t="s">
+      <c r="B25" s="150"/>
+      <c r="C25" s="154"/>
+      <c r="D25" s="151"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="154"/>
+      <c r="I25" s="155"/>
+      <c r="J25" s="156" t="s">
         <v>184</v>
       </c>
-      <c r="K25" s="158"/>
-      <c r="L25" s="158"/>
-      <c r="M25" s="156"/>
-      <c r="N25" s="156"/>
-      <c r="O25" s="159"/>
-      <c r="P25" s="149"/>
-      <c r="Q25" s="149"/>
-      <c r="R25" s="149"/>
+      <c r="K25" s="157"/>
+      <c r="L25" s="157"/>
+      <c r="M25" s="155"/>
+      <c r="N25" s="155"/>
+      <c r="O25" s="158"/>
+      <c r="P25" s="148"/>
+      <c r="Q25" s="148"/>
+      <c r="R25" s="148"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B26" s="124"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="150"/>
-      <c r="F26" s="127"/>
-      <c r="G26" s="125"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="124"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="128"/>
-      <c r="J26" s="129"/>
-      <c r="K26" s="131"/>
-      <c r="L26" s="131" t="s">
+      <c r="I26" s="127"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="130"/>
+      <c r="L26" s="130" t="s">
         <v>193</v>
       </c>
-      <c r="M26" s="128" t="n">
+      <c r="M26" s="127" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="128" t="s">
+      <c r="N26" s="127" t="s">
         <v>167</v>
       </c>
-      <c r="O26" s="169" t="s">
+      <c r="O26" s="168" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B27" s="124"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="150"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="125"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="124"/>
       <c r="H27" s="12"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="129"/>
-      <c r="K27" s="131"/>
-      <c r="L27" s="131" t="s">
+      <c r="I27" s="127"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="130"/>
+      <c r="L27" s="130" t="s">
         <v>195</v>
       </c>
-      <c r="M27" s="128" t="s">
+      <c r="M27" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="N27" s="128" t="s">
+      <c r="N27" s="127" t="s">
         <v>196</v>
       </c>
-      <c r="O27" s="169" t="s">
+      <c r="O27" s="168" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="114" t="s">
+      <c r="A28" s="113" t="s">
         <v>198</v>
       </c>
-      <c r="B28" s="151"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="152"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="152"/>
-      <c r="H28" s="155"/>
-      <c r="I28" s="156"/>
-      <c r="J28" s="157" t="s">
+      <c r="B28" s="150"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="151"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="155"/>
+      <c r="J28" s="156" t="s">
         <v>183</v>
       </c>
-      <c r="K28" s="158"/>
-      <c r="L28" s="158"/>
-      <c r="M28" s="156"/>
-      <c r="N28" s="156"/>
-      <c r="O28" s="159"/>
-      <c r="P28" s="149"/>
-      <c r="Q28" s="149"/>
-      <c r="R28" s="149"/>
+      <c r="K28" s="157"/>
+      <c r="L28" s="157"/>
+      <c r="M28" s="155"/>
+      <c r="N28" s="155"/>
+      <c r="O28" s="158"/>
+      <c r="P28" s="148"/>
+      <c r="Q28" s="148"/>
+      <c r="R28" s="148"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B29" s="124"/>
+      <c r="B29" s="123"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="125"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="125"/>
+      <c r="D29" s="124"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="124"/>
       <c r="H29" s="12"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="129"/>
-      <c r="K29" s="131"/>
-      <c r="L29" s="131" t="s">
+      <c r="I29" s="127"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="130" t="s">
         <v>199</v>
       </c>
-      <c r="M29" s="128" t="n">
+      <c r="M29" s="127" t="n">
         <v>4</v>
       </c>
-      <c r="N29" s="128" t="s">
+      <c r="N29" s="127" t="s">
         <v>167</v>
       </c>
-      <c r="O29" s="169" t="s">
+      <c r="O29" s="168" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B30" s="124"/>
+      <c r="B30" s="123"/>
       <c r="C30" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="125"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="127"/>
-      <c r="G30" s="125"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="126"/>
+      <c r="G30" s="124"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="129"/>
-      <c r="K30" s="131" t="s">
+      <c r="I30" s="127"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="130" t="s">
         <v>201</v>
       </c>
-      <c r="L30" s="131" t="s">
+      <c r="L30" s="130" t="s">
         <v>202</v>
       </c>
-      <c r="M30" s="128" t="s">
+      <c r="M30" s="127" t="s">
         <v>203</v>
       </c>
-      <c r="N30" s="128" t="s">
+      <c r="N30" s="127" t="s">
         <v>204</v>
       </c>
-      <c r="O30" s="169" t="s">
+      <c r="O30" s="168" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B31" s="124"/>
+      <c r="B31" s="123"/>
       <c r="C31" s="12"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="125"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="124"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="128"/>
-      <c r="J31" s="129" t="s">
+      <c r="I31" s="127"/>
+      <c r="J31" s="128" t="s">
         <v>201</v>
       </c>
-      <c r="K31" s="131"/>
-      <c r="L31" s="131" t="s">
+      <c r="K31" s="130"/>
+      <c r="L31" s="130" t="s">
         <v>195</v>
       </c>
-      <c r="M31" s="128" t="s">
+      <c r="M31" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="N31" s="128" t="s">
+      <c r="N31" s="127" t="s">
         <v>196</v>
       </c>
-      <c r="O31" s="169" t="s">
+      <c r="O31" s="168" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B32" s="160"/>
-      <c r="C32" s="134"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="162"/>
-      <c r="F32" s="163"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="137"/>
-      <c r="J32" s="138" t="s">
+      <c r="B32" s="159"/>
+      <c r="C32" s="133"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="133"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="137" t="s">
         <v>207</v>
       </c>
-      <c r="K32" s="139"/>
-      <c r="L32" s="139" t="s">
+      <c r="K32" s="138"/>
+      <c r="L32" s="138" t="s">
         <v>195</v>
       </c>
-      <c r="M32" s="137" t="s">
+      <c r="M32" s="136" t="s">
         <v>159</v>
       </c>
-      <c r="N32" s="137" t="s">
+      <c r="N32" s="136" t="s">
         <v>196</v>
       </c>
-      <c r="O32" s="170" t="s">
+      <c r="O32" s="169" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="124"/>
+      <c r="G33" s="124"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="131"/>
-      <c r="K33" s="131"/>
-      <c r="L33" s="131"/>
-      <c r="M33" s="131"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="130"/>
+      <c r="L33" s="130"/>
+      <c r="M33" s="130"/>
       <c r="N33" s="12"/>
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
-      <c r="Q33" s="131"/>
-      <c r="R33" s="131"/>
+      <c r="Q33" s="130"/>
+      <c r="R33" s="130"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="125"/>
-      <c r="C34" s="125"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="124"/>
+      <c r="G34" s="124"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="171" t="s">
+      <c r="J34" s="170" t="s">
         <v>155</v>
       </c>
-      <c r="K34" s="171"/>
-      <c r="L34" s="171"/>
-      <c r="M34" s="171"/>
-      <c r="N34" s="109"/>
+      <c r="K34" s="170"/>
+      <c r="L34" s="170"/>
+      <c r="M34" s="170"/>
+      <c r="N34" s="108"/>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
       <c r="Q34" s="12"/>
-      <c r="R34" s="131"/>
+      <c r="R34" s="130"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J35" s="5" t="s">
@@ -7151,55 +7147,55 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="172" t="s">
+      <c r="A39" s="171" t="s">
         <v>210</v>
       </c>
-      <c r="B39" s="173"/>
-      <c r="C39" s="173"/>
-      <c r="D39" s="174"/>
-      <c r="E39" s="174"/>
-      <c r="F39" s="173" t="s">
+      <c r="B39" s="172"/>
+      <c r="C39" s="172"/>
+      <c r="D39" s="173"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="172" t="s">
         <v>169</v>
       </c>
-      <c r="G39" s="174" t="s">
+      <c r="G39" s="173" t="s">
         <v>163</v>
       </c>
-      <c r="H39" s="174" t="s">
+      <c r="H39" s="173" t="s">
         <v>161</v>
       </c>
-      <c r="I39" s="174" t="s">
+      <c r="I39" s="173" t="s">
         <v>157</v>
       </c>
-      <c r="J39" s="175" t="s">
+      <c r="J39" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="K39" s="175" t="s">
+      <c r="K39" s="174" t="s">
         <v>211</v>
       </c>
-      <c r="L39" s="176" t="s">
+      <c r="L39" s="175" t="s">
         <v>212</v>
       </c>
-      <c r="M39" s="172" t="s">
+      <c r="M39" s="171" t="s">
         <v>213</v>
       </c>
-      <c r="N39" s="175"/>
-      <c r="O39" s="172"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
-      <c r="R39" s="172"/>
+      <c r="N39" s="174"/>
+      <c r="O39" s="171"/>
+      <c r="P39" s="171"/>
+      <c r="Q39" s="171"/>
+      <c r="R39" s="171"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="177"/>
-      <c r="B40" s="178"/>
-      <c r="C40" s="179"/>
-      <c r="D40" s="179"/>
-      <c r="E40" s="180"/>
-      <c r="F40" s="181"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="179" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="182" t="s">
+      <c r="A40" s="176"/>
+      <c r="B40" s="177"/>
+      <c r="C40" s="178"/>
+      <c r="D40" s="178"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="178"/>
+      <c r="H40" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="181" t="s">
         <v>69</v>
       </c>
       <c r="J40" s="2" t="str">
@@ -7222,14 +7218,14 @@
       <c r="R40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="177"/>
-      <c r="B41" s="183"/>
+      <c r="A41" s="176"/>
+      <c r="B41" s="182"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41" s="150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="184" t="n">
+      <c r="E41" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="183" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="12" t="s">
@@ -7238,7 +7234,7 @@
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="128" t="s">
+      <c r="I41" s="127" t="s">
         <v>69</v>
       </c>
       <c r="J41" s="2" t="str">
@@ -7261,18 +7257,18 @@
       <c r="R41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="177"/>
-      <c r="B42" s="183"/>
+      <c r="A42" s="176"/>
+      <c r="B42" s="182"/>
       <c r="C42" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="184" t="n">
+      <c r="E42" s="149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="183" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="12" t="s">
@@ -7281,7 +7277,7 @@
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="128" t="s">
+      <c r="I42" s="127" t="s">
         <v>69</v>
       </c>
       <c r="J42" s="2" t="str">
@@ -7304,16 +7300,16 @@
       <c r="R42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="177"/>
-      <c r="B43" s="183"/>
+      <c r="A43" s="176"/>
+      <c r="B43" s="182"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="184" t="n">
+      <c r="E43" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="183" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="12" t="s">
@@ -7322,7 +7318,7 @@
       <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="128" t="s">
+      <c r="I43" s="127" t="s">
         <v>69</v>
       </c>
       <c r="J43" s="2" t="str">
@@ -7345,16 +7341,16 @@
       <c r="R43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="177"/>
-      <c r="B44" s="183"/>
+      <c r="A44" s="176"/>
+      <c r="B44" s="182"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="184" t="n">
+      <c r="E44" s="149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="183" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="12" t="s">
@@ -7363,7 +7359,7 @@
       <c r="H44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="128" t="s">
+      <c r="I44" s="127" t="s">
         <v>69</v>
       </c>
       <c r="J44" s="2" t="str">
@@ -7386,16 +7382,16 @@
       <c r="R44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="177"/>
-      <c r="B45" s="183"/>
+      <c r="A45" s="176"/>
+      <c r="B45" s="182"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="184" t="n">
+      <c r="E45" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="183" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="12" t="s">
@@ -7404,7 +7400,7 @@
       <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="128" t="s">
+      <c r="I45" s="127" t="s">
         <v>69</v>
       </c>
       <c r="J45" s="2" t="str">
@@ -7427,27 +7423,27 @@
       <c r="R45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="177"/>
-      <c r="B46" s="185"/>
-      <c r="C46" s="134" t="s">
+      <c r="A46" s="176"/>
+      <c r="B46" s="184"/>
+      <c r="C46" s="133" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="134" t="s">
+      <c r="D46" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="133" t="s">
         <v>69</v>
       </c>
-      <c r="H46" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="137" t="s">
+      <c r="H46" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="136" t="s">
         <v>69</v>
       </c>
       <c r="J46" s="2" t="str">
@@ -7503,7 +7499,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="186"/>
+      <c r="A1" s="185"/>
       <c r="B1" s="16" t="s">
         <v>42</v>
       </c>
@@ -7513,10 +7509,10 @@
       <c r="D1" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="E1" s="187" t="n">
+      <c r="E1" s="186" t="n">
         <v>6</v>
       </c>
-      <c r="F1" s="187" t="n">
+      <c r="F1" s="186" t="n">
         <v>5</v>
       </c>
       <c r="G1" s="25" t="n">
@@ -7525,74 +7521,74 @@
       <c r="H1" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I1" s="187" t="n">
+      <c r="I1" s="186" t="n">
         <v>2</v>
       </c>
-      <c r="J1" s="187" t="n">
+      <c r="J1" s="186" t="n">
         <v>1</v>
       </c>
       <c r="K1" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="L1" s="188" t="s">
+      <c r="L1" s="187" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="189" t="s">
+      <c r="M1" s="188" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="189" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="190" t="s">
+      <c r="N1" s="188" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="189" t="s">
         <v>154</v>
       </c>
-      <c r="P1" s="191" t="s">
+      <c r="P1" s="190" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="191" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="193" t="str">
+      <c r="B2" s="192" t="str">
         <f aca="false">DEC2HEX(C2,2)</f>
         <v>00</v>
       </c>
-      <c r="C2" s="155" t="n">
+      <c r="C2" s="154" t="n">
         <f aca="false">IF(D2=1,128,0)+IF(E2=1,64,0)+IF(F2=1,32,0)+IF(G2=1,16,0)+IF(H2=1,8,0)+IF(I2=1,4,0)+IF(J2=1,2,0)+IF(K2=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="194"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="194" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="195"/>
-      <c r="M2" s="196" t="s">
+      <c r="D2" s="193"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="194"/>
+      <c r="M2" s="195" t="s">
         <v>223</v>
       </c>
-      <c r="N2" s="195"/>
-      <c r="O2" s="197"/>
-      <c r="P2" s="198"/>
+      <c r="N2" s="194"/>
+      <c r="O2" s="196"/>
+      <c r="P2" s="197"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="199"/>
+      <c r="A3" s="198"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="109"/>
+      <c r="C3" s="108"/>
       <c r="D3" s="48"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109" t="s">
+      <c r="E3" s="108"/>
+      <c r="F3" s="108" t="s">
         <v>224</v>
       </c>
       <c r="G3" s="49" t="s">
@@ -7600,124 +7596,124 @@
       </c>
       <c r="H3" s="48"/>
       <c r="I3" s="12"/>
-      <c r="J3" s="109"/>
+      <c r="J3" s="108"/>
       <c r="K3" s="49"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="200"/>
-      <c r="N3" s="200" t="s">
+      <c r="L3" s="129"/>
+      <c r="M3" s="199"/>
+      <c r="N3" s="199" t="s">
         <v>225</v>
       </c>
-      <c r="O3" s="201" t="s">
+      <c r="O3" s="200" t="s">
         <v>226</v>
       </c>
-      <c r="P3" s="202"/>
+      <c r="P3" s="201"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="199"/>
+      <c r="A4" s="198"/>
       <c r="D4" s="48"/>
-      <c r="E4" s="109" t="s">
+      <c r="E4" s="108" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="109"/>
+      <c r="F4" s="108"/>
       <c r="G4" s="49"/>
       <c r="H4" s="48"/>
       <c r="I4" s="12"/>
-      <c r="J4" s="109"/>
+      <c r="J4" s="108"/>
       <c r="K4" s="49"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="200" t="s">
+      <c r="L4" s="129"/>
+      <c r="M4" s="199" t="s">
         <v>228</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
-      <c r="P4" s="203"/>
+      <c r="P4" s="202"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="199"/>
+      <c r="A5" s="198"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="109"/>
+      <c r="C5" s="108"/>
       <c r="D5" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="49"/>
       <c r="H5" s="48"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="109"/>
+      <c r="J5" s="108"/>
       <c r="K5" s="49"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="200" t="s">
+      <c r="L5" s="129"/>
+      <c r="M5" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O5" s="201"/>
-      <c r="P5" s="202"/>
+      <c r="O5" s="200"/>
+      <c r="P5" s="201"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A6" s="199"/>
+      <c r="A6" s="198"/>
       <c r="D6" s="48"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
       <c r="G6" s="49"/>
       <c r="H6" s="48"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="109"/>
+      <c r="J6" s="108"/>
       <c r="K6" s="49"/>
-      <c r="L6" s="130" t="s">
+      <c r="L6" s="129" t="s">
         <v>230</v>
       </c>
-      <c r="M6" s="200"/>
+      <c r="M6" s="199"/>
       <c r="N6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="P6" s="203"/>
+      <c r="P6" s="202"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="192" t="s">
+      <c r="A7" s="191" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="193" t="str">
+      <c r="B7" s="192" t="str">
         <f aca="false">DEC2HEX(C7,2)</f>
         <v>01</v>
       </c>
-      <c r="C7" s="155" t="n">
+      <c r="C7" s="154" t="n">
         <f aca="false">IF(D7=1,128,0)+IF(E7=1,64,0)+IF(F7=1,32,0)+IF(G7=1,16,0)+IF(H7=1,8,0)+IF(I7=1,4,0)+IF(J7=1,2,0)+IF(K7=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="194"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="194" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="156" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="195"/>
-      <c r="M7" s="196" t="s">
+      <c r="D7" s="193"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="194"/>
+      <c r="M7" s="195" t="s">
         <v>233</v>
       </c>
-      <c r="N7" s="195"/>
-      <c r="O7" s="196"/>
-      <c r="P7" s="198"/>
+      <c r="N7" s="194"/>
+      <c r="O7" s="195"/>
+      <c r="P7" s="197"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="199"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="109"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="48"/>
-      <c r="E8" s="109"/>
-      <c r="F8" s="109" t="s">
+      <c r="E8" s="108"/>
+      <c r="F8" s="108" t="s">
         <v>224</v>
       </c>
       <c r="G8" s="49" t="s">
@@ -7725,52 +7721,52 @@
       </c>
       <c r="H8" s="48"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="109"/>
+      <c r="J8" s="108"/>
       <c r="K8" s="49"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="200"/>
+      <c r="L8" s="129"/>
+      <c r="M8" s="199"/>
       <c r="N8" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="O8" s="201" t="s">
+      <c r="O8" s="200" t="s">
         <v>226</v>
       </c>
-      <c r="P8" s="202" t="s">
+      <c r="P8" s="201" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="199"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="16"/>
-      <c r="C9" s="109"/>
+      <c r="C9" s="108"/>
       <c r="D9" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E9" s="109"/>
-      <c r="F9" s="109"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
       <c r="G9" s="49"/>
       <c r="H9" s="48"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="109"/>
+      <c r="J9" s="108"/>
       <c r="K9" s="49"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="200" t="s">
+      <c r="L9" s="129"/>
+      <c r="M9" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O9" s="201"/>
-      <c r="P9" s="202"/>
+      <c r="O9" s="200"/>
+      <c r="P9" s="201"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="199"/>
-      <c r="D10" s="204"/>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
+      <c r="A10" s="198"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="49"/>
-      <c r="H10" s="204"/>
-      <c r="I10" s="109"/>
-      <c r="J10" s="109"/>
+      <c r="H10" s="203"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
       <c r="K10" s="49"/>
-      <c r="L10" s="130" t="s">
+      <c r="L10" s="129" t="s">
         <v>230</v>
       </c>
       <c r="M10" s="10"/>
@@ -7780,51 +7776,51 @@
       <c r="O10" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="P10" s="203"/>
+      <c r="P10" s="202"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="192" t="s">
+      <c r="A11" s="191" t="s">
         <v>235</v>
       </c>
-      <c r="B11" s="193" t="str">
+      <c r="B11" s="192" t="str">
         <f aca="false">DEC2HEX(C11,2)</f>
         <v>02</v>
       </c>
-      <c r="C11" s="155" t="n">
+      <c r="C11" s="154" t="n">
         <f aca="false">IF(D11=1,128,0)+IF(E11=1,64,0)+IF(F11=1,32,0)+IF(G11=1,16,0)+IF(H11=1,8,0)+IF(I11=1,4,0)+IF(J11=1,2,0)+IF(K11=1,1,0)</f>
         <v>2</v>
       </c>
-      <c r="D11" s="194"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="195"/>
-      <c r="M11" s="196" t="s">
+      <c r="D11" s="193"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="194"/>
+      <c r="M11" s="195" t="s">
         <v>236</v>
       </c>
-      <c r="N11" s="195"/>
-      <c r="O11" s="197"/>
-      <c r="P11" s="198"/>
+      <c r="N11" s="194"/>
+      <c r="O11" s="196"/>
+      <c r="P11" s="197"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A12" s="199"/>
+      <c r="A12" s="198"/>
       <c r="B12" s="16"/>
-      <c r="C12" s="109"/>
+      <c r="C12" s="108"/>
       <c r="D12" s="48"/>
-      <c r="E12" s="109"/>
-      <c r="F12" s="109" t="s">
+      <c r="E12" s="108"/>
+      <c r="F12" s="108" t="s">
         <v>224</v>
       </c>
       <c r="G12" s="49" t="s">
@@ -7832,157 +7828,157 @@
       </c>
       <c r="H12" s="48"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="109"/>
+      <c r="J12" s="108"/>
       <c r="K12" s="49"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="200"/>
-      <c r="N12" s="200" t="s">
+      <c r="L12" s="129"/>
+      <c r="M12" s="199"/>
+      <c r="N12" s="199" t="s">
         <v>237</v>
       </c>
-      <c r="O12" s="201" t="s">
+      <c r="O12" s="200" t="s">
         <v>226</v>
       </c>
-      <c r="P12" s="205" t="s">
+      <c r="P12" s="204" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="199"/>
+      <c r="A13" s="198"/>
       <c r="B13" s="16"/>
-      <c r="C13" s="109"/>
+      <c r="C13" s="108"/>
       <c r="D13" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
       <c r="G13" s="49"/>
       <c r="H13" s="48"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="109"/>
+      <c r="J13" s="108"/>
       <c r="K13" s="49"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="200" t="s">
+      <c r="L13" s="129"/>
+      <c r="M13" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O13" s="201"/>
-      <c r="P13" s="202"/>
+      <c r="O13" s="200"/>
+      <c r="P13" s="201"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="199"/>
+      <c r="A14" s="198"/>
       <c r="D14" s="48"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
       <c r="G14" s="49"/>
       <c r="H14" s="48"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="109"/>
+      <c r="J14" s="108"/>
       <c r="K14" s="49"/>
-      <c r="L14" s="130" t="s">
+      <c r="L14" s="129" t="s">
         <v>230</v>
       </c>
-      <c r="M14" s="200"/>
+      <c r="M14" s="199"/>
       <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="P14" s="203" t="s">
+      <c r="P14" s="202" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="192" t="s">
+      <c r="A15" s="191" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="193" t="str">
+      <c r="B15" s="192" t="str">
         <f aca="false">DEC2HEX(C15,2)</f>
         <v>03</v>
       </c>
-      <c r="C15" s="155" t="n">
+      <c r="C15" s="154" t="n">
         <f aca="false">IF(D15=1,128,0)+IF(E15=1,64,0)+IF(F15=1,32,0)+IF(G15=1,16,0)+IF(H15=1,8,0)+IF(I15=1,4,0)+IF(J15=1,2,0)+IF(K15=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="D15" s="194"/>
-      <c r="E15" s="155"/>
-      <c r="F15" s="155"/>
-      <c r="G15" s="156"/>
-      <c r="H15" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="156" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="195"/>
-      <c r="M15" s="196" t="s">
+      <c r="D15" s="193"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="155"/>
+      <c r="H15" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="194"/>
+      <c r="M15" s="195" t="s">
         <v>98</v>
       </c>
-      <c r="N15" s="195"/>
-      <c r="O15" s="196"/>
-      <c r="P15" s="198"/>
+      <c r="N15" s="194"/>
+      <c r="O15" s="195"/>
+      <c r="P15" s="197"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A16" s="199"/>
+      <c r="A16" s="198"/>
       <c r="B16" s="16"/>
-      <c r="C16" s="109"/>
+      <c r="C16" s="108"/>
       <c r="D16" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
       <c r="G16" s="49"/>
       <c r="H16" s="48"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="109"/>
+      <c r="J16" s="108"/>
       <c r="K16" s="49"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="200" t="s">
+      <c r="L16" s="129"/>
+      <c r="M16" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O16" s="201"/>
-      <c r="P16" s="202"/>
+      <c r="O16" s="200"/>
+      <c r="P16" s="201"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A17" s="199"/>
+      <c r="A17" s="198"/>
       <c r="B17" s="16"/>
-      <c r="C17" s="109"/>
+      <c r="C17" s="108"/>
       <c r="D17" s="48"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
       <c r="G17" s="49"/>
       <c r="H17" s="48"/>
       <c r="I17" s="12"/>
-      <c r="J17" s="109"/>
+      <c r="J17" s="108"/>
       <c r="K17" s="49"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="200"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="199"/>
       <c r="N17" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="O17" s="201" t="s">
+      <c r="O17" s="200" t="s">
         <v>242</v>
       </c>
-      <c r="P17" s="202" t="s">
+      <c r="P17" s="201" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="199"/>
-      <c r="D18" s="204"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
+      <c r="A18" s="198"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
       <c r="G18" s="49"/>
-      <c r="H18" s="204"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
+      <c r="H18" s="203"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="108"/>
       <c r="K18" s="49"/>
-      <c r="L18" s="130" t="s">
+      <c r="L18" s="129" t="s">
         <v>230</v>
       </c>
       <c r="M18" s="10"/>
@@ -7992,61 +7988,61 @@
       <c r="O18" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="P18" s="206" t="s">
+      <c r="P18" s="205" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="192" t="s">
+      <c r="A19" s="191" t="s">
         <v>246</v>
       </c>
-      <c r="B19" s="193" t="str">
+      <c r="B19" s="192" t="str">
         <f aca="false">DEC2HEX(C19,2)</f>
         <v>04</v>
       </c>
-      <c r="C19" s="155" t="n">
+      <c r="C19" s="154" t="n">
         <f aca="false">IF(D19=1,128,0)+IF(E19=1,64,0)+IF(F19=1,32,0)+IF(G19=1,16,0)+IF(H19=1,8,0)+IF(I19=1,4,0)+IF(J19=1,2,0)+IF(K19=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="D19" s="194"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="156"/>
-      <c r="H19" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="195"/>
-      <c r="M19" s="196" t="s">
+      <c r="D19" s="193"/>
+      <c r="E19" s="154"/>
+      <c r="F19" s="154"/>
+      <c r="G19" s="155"/>
+      <c r="H19" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="194"/>
+      <c r="M19" s="195" t="s">
         <v>247</v>
       </c>
-      <c r="N19" s="195"/>
-      <c r="O19" s="196"/>
-      <c r="P19" s="198"/>
+      <c r="N19" s="194"/>
+      <c r="O19" s="195"/>
+      <c r="P19" s="197"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="199"/>
-      <c r="D20" s="204"/>
-      <c r="E20" s="109"/>
-      <c r="F20" s="109" t="s">
+      <c r="A20" s="198"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="108" t="s">
         <v>224</v>
       </c>
       <c r="G20" s="49" t="s">
         <v>224</v>
       </c>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
       <c r="K20" s="49"/>
-      <c r="L20" s="130"/>
+      <c r="L20" s="129"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
         <v>225</v>
@@ -8054,82 +8050,82 @@
       <c r="O20" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="P20" s="202"/>
+      <c r="P20" s="201"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="199"/>
-      <c r="D21" s="204"/>
-      <c r="E21" s="109" t="s">
+      <c r="A21" s="198"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="108" t="s">
         <v>227</v>
       </c>
-      <c r="F21" s="109"/>
+      <c r="F21" s="108"/>
       <c r="G21" s="49"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
       <c r="K21" s="49"/>
-      <c r="L21" s="131"/>
+      <c r="L21" s="130"/>
       <c r="M21" s="10" t="s">
         <v>248</v>
       </c>
       <c r="N21" s="10"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="202" t="s">
+      <c r="O21" s="130"/>
+      <c r="P21" s="201" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="199"/>
-      <c r="D22" s="204"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
+      <c r="A22" s="198"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="108"/>
       <c r="G22" s="49"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="108"/>
       <c r="K22" s="49"/>
-      <c r="L22" s="131"/>
+      <c r="L22" s="130"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="O22" s="131" t="s">
+      <c r="O22" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="P22" s="202"/>
+      <c r="P22" s="201"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="199"/>
+      <c r="A23" s="198"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="109"/>
+      <c r="C23" s="108"/>
       <c r="D23" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
       <c r="G23" s="49"/>
       <c r="H23" s="48"/>
       <c r="I23" s="12"/>
-      <c r="J23" s="109"/>
+      <c r="J23" s="108"/>
       <c r="K23" s="49"/>
-      <c r="L23" s="130"/>
-      <c r="M23" s="200" t="s">
+      <c r="L23" s="129"/>
+      <c r="M23" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O23" s="201"/>
-      <c r="P23" s="202"/>
+      <c r="O23" s="200"/>
+      <c r="P23" s="201"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="199"/>
-      <c r="D24" s="204"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
+      <c r="A24" s="198"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="108"/>
       <c r="G24" s="49"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="109"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="108"/>
       <c r="K24" s="49"/>
-      <c r="L24" s="130" t="s">
+      <c r="L24" s="129" t="s">
         <v>230</v>
       </c>
       <c r="M24" s="10"/>
@@ -8137,120 +8133,120 @@
       <c r="O24" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="P24" s="202" t="s">
+      <c r="P24" s="201" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="192" t="s">
+      <c r="A25" s="191" t="s">
         <v>253</v>
       </c>
-      <c r="B25" s="193" t="str">
+      <c r="B25" s="192" t="str">
         <f aca="false">DEC2HEX(C25,2)</f>
         <v>05</v>
       </c>
-      <c r="C25" s="155" t="n">
+      <c r="C25" s="154" t="n">
         <f aca="false">IF(D25=1,128,0)+IF(E25=1,64,0)+IF(F25=1,32,0)+IF(G25=1,16,0)+IF(H25=1,8,0)+IF(I25=1,4,0)+IF(J25=1,2,0)+IF(K25=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="D25" s="194"/>
-      <c r="E25" s="155"/>
-      <c r="F25" s="155"/>
-      <c r="G25" s="156"/>
-      <c r="H25" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="156" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="195"/>
-      <c r="M25" s="196" t="s">
+      <c r="D25" s="193"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="194"/>
+      <c r="M25" s="195" t="s">
         <v>254</v>
       </c>
-      <c r="N25" s="195"/>
-      <c r="O25" s="196"/>
-      <c r="P25" s="198"/>
+      <c r="N25" s="194"/>
+      <c r="O25" s="195"/>
+      <c r="P25" s="197"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="199"/>
-      <c r="D26" s="204"/>
-      <c r="E26" s="109" t="s">
+      <c r="A26" s="198"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="108" t="s">
         <v>227</v>
       </c>
-      <c r="F26" s="109"/>
+      <c r="F26" s="108"/>
       <c r="G26" s="49"/>
-      <c r="H26" s="109"/>
-      <c r="I26" s="109"/>
-      <c r="J26" s="109"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="108"/>
+      <c r="J26" s="108"/>
       <c r="K26" s="49"/>
-      <c r="L26" s="131"/>
+      <c r="L26" s="130"/>
       <c r="M26" s="10" t="s">
         <v>248</v>
       </c>
       <c r="N26" s="10"/>
-      <c r="O26" s="131"/>
-      <c r="P26" s="202" t="s">
+      <c r="O26" s="130"/>
+      <c r="P26" s="201" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="199"/>
-      <c r="D27" s="204"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="109"/>
+      <c r="A27" s="198"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
       <c r="G27" s="49"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="109"/>
-      <c r="J27" s="109"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="108"/>
       <c r="K27" s="49"/>
-      <c r="L27" s="131"/>
+      <c r="L27" s="130"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="O27" s="131" t="s">
+      <c r="O27" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="P27" s="202"/>
+      <c r="P27" s="201"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="199"/>
+      <c r="A28" s="198"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="109"/>
+      <c r="C28" s="108"/>
       <c r="D28" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
       <c r="G28" s="49"/>
       <c r="H28" s="48"/>
       <c r="I28" s="12"/>
-      <c r="J28" s="109"/>
+      <c r="J28" s="108"/>
       <c r="K28" s="49"/>
-      <c r="L28" s="130"/>
-      <c r="M28" s="200" t="s">
+      <c r="L28" s="129"/>
+      <c r="M28" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O28" s="201"/>
-      <c r="P28" s="202"/>
+      <c r="O28" s="200"/>
+      <c r="P28" s="201"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="199"/>
-      <c r="D29" s="204"/>
-      <c r="E29" s="109"/>
-      <c r="F29" s="109"/>
+      <c r="A29" s="198"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
       <c r="G29" s="49"/>
-      <c r="H29" s="204"/>
-      <c r="I29" s="109"/>
-      <c r="J29" s="109"/>
+      <c r="H29" s="203"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
       <c r="K29" s="49"/>
-      <c r="L29" s="130" t="s">
+      <c r="L29" s="129" t="s">
         <v>230</v>
       </c>
       <c r="M29" s="10"/>
@@ -8260,777 +8256,777 @@
       <c r="O29" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="P29" s="206" t="s">
+      <c r="P29" s="205" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="192" t="s">
+      <c r="A30" s="191" t="s">
         <v>257</v>
       </c>
-      <c r="B30" s="193" t="str">
+      <c r="B30" s="192" t="str">
         <f aca="false">DEC2HEX(C30,2)</f>
         <v>06</v>
       </c>
-      <c r="C30" s="155" t="n">
+      <c r="C30" s="154" t="n">
         <f aca="false">IF(D30=1,128,0)+IF(E30=1,64,0)+IF(F30=1,32,0)+IF(G30=1,16,0)+IF(H30=1,8,0)+IF(I30=1,4,0)+IF(J30=1,2,0)+IF(K30=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="D30" s="194"/>
-      <c r="E30" s="155"/>
-      <c r="F30" s="155"/>
-      <c r="G30" s="156"/>
-      <c r="H30" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="195"/>
-      <c r="M30" s="196" t="s">
+      <c r="D30" s="193"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="155"/>
+      <c r="H30" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="194"/>
+      <c r="M30" s="195" t="s">
         <v>258</v>
       </c>
-      <c r="N30" s="195"/>
-      <c r="O30" s="196"/>
-      <c r="P30" s="207" t="s">
+      <c r="N30" s="194"/>
+      <c r="O30" s="195"/>
+      <c r="P30" s="206" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A31" s="199"/>
-      <c r="D31" s="204"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="109" t="n">
+      <c r="A31" s="198"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="109"/>
-      <c r="I31" s="109"/>
-      <c r="J31" s="109"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="108"/>
       <c r="K31" s="49"/>
-      <c r="M31" s="131" t="s">
+      <c r="M31" s="130" t="s">
         <v>260</v>
       </c>
-      <c r="P31" s="202"/>
+      <c r="P31" s="201"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A32" s="199"/>
-      <c r="D32" s="204"/>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109" t="n">
+      <c r="A32" s="198"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="109"/>
-      <c r="I32" s="109"/>
-      <c r="J32" s="109"/>
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
       <c r="K32" s="49"/>
-      <c r="M32" s="200" t="s">
+      <c r="M32" s="199" t="s">
         <v>261</v>
       </c>
-      <c r="P32" s="202"/>
+      <c r="P32" s="201"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="199"/>
-      <c r="D33" s="204"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109" t="n">
+      <c r="A33" s="198"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="109"/>
-      <c r="I33" s="109"/>
-      <c r="J33" s="109"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="108"/>
       <c r="K33" s="49"/>
-      <c r="M33" s="200" t="s">
+      <c r="M33" s="199" t="s">
         <v>262</v>
       </c>
-      <c r="P33" s="202"/>
+      <c r="P33" s="201"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="199"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109" t="n">
+      <c r="A34" s="198"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
       <c r="K34" s="49"/>
       <c r="M34" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="P34" s="202"/>
+      <c r="P34" s="201"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="199"/>
-      <c r="D35" s="204"/>
-      <c r="E35" s="109" t="s">
+      <c r="A35" s="198"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="108" t="s">
         <v>264</v>
       </c>
-      <c r="F35" s="109"/>
+      <c r="F35" s="108"/>
       <c r="G35" s="49"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="109"/>
-      <c r="J35" s="109"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
       <c r="K35" s="49"/>
-      <c r="M35" s="131" t="s">
+      <c r="M35" s="130" t="s">
         <v>265</v>
       </c>
-      <c r="P35" s="202" t="s">
+      <c r="P35" s="201" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="199"/>
+      <c r="A36" s="198"/>
       <c r="B36" s="16"/>
-      <c r="C36" s="109"/>
+      <c r="C36" s="108"/>
       <c r="D36" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E36" s="109"/>
-      <c r="F36" s="109"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
       <c r="G36" s="49"/>
       <c r="H36" s="48"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="109"/>
+      <c r="J36" s="108"/>
       <c r="K36" s="49"/>
-      <c r="L36" s="130"/>
-      <c r="M36" s="200" t="s">
+      <c r="L36" s="129"/>
+      <c r="M36" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O36" s="201"/>
-      <c r="P36" s="202"/>
+      <c r="O36" s="200"/>
+      <c r="P36" s="201"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="199"/>
-      <c r="D37" s="204"/>
-      <c r="E37" s="109"/>
-      <c r="F37" s="109"/>
+      <c r="A37" s="198"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
       <c r="G37" s="49"/>
-      <c r="H37" s="109"/>
-      <c r="I37" s="109"/>
-      <c r="J37" s="109"/>
+      <c r="H37" s="108"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="108"/>
       <c r="K37" s="49"/>
-      <c r="L37" s="130" t="s">
+      <c r="L37" s="129" t="s">
         <v>230</v>
       </c>
-      <c r="M37" s="131"/>
+      <c r="M37" s="130"/>
       <c r="O37" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="P37" s="202" t="s">
+      <c r="P37" s="201" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="192" t="s">
+      <c r="A38" s="191" t="s">
         <v>269</v>
       </c>
-      <c r="B38" s="193" t="str">
+      <c r="B38" s="192" t="str">
         <f aca="false">DEC2HEX(C38,2)</f>
         <v>07</v>
       </c>
-      <c r="C38" s="155" t="n">
+      <c r="C38" s="154" t="n">
         <f aca="false">IF(D38=1,128,0)+IF(E38=1,64,0)+IF(F38=1,32,0)+IF(G38=1,16,0)+IF(H38=1,8,0)+IF(I38=1,4,0)+IF(J38=1,2,0)+IF(K38=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="D38" s="194"/>
-      <c r="E38" s="155"/>
-      <c r="F38" s="155"/>
-      <c r="G38" s="156"/>
-      <c r="H38" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="156" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="195"/>
-      <c r="M38" s="196" t="s">
+      <c r="D38" s="193"/>
+      <c r="E38" s="154"/>
+      <c r="F38" s="154"/>
+      <c r="G38" s="155"/>
+      <c r="H38" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="194"/>
+      <c r="M38" s="195" t="s">
         <v>270</v>
       </c>
-      <c r="N38" s="195"/>
-      <c r="O38" s="196"/>
-      <c r="P38" s="198"/>
+      <c r="N38" s="194"/>
+      <c r="O38" s="195"/>
+      <c r="P38" s="197"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A39" s="199"/>
-      <c r="D39" s="204"/>
-      <c r="E39" s="109"/>
-      <c r="F39" s="109" t="n">
+      <c r="A39" s="198"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="109"/>
-      <c r="I39" s="109"/>
-      <c r="J39" s="109"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
       <c r="K39" s="49"/>
-      <c r="M39" s="131" t="s">
+      <c r="M39" s="130" t="s">
         <v>271</v>
       </c>
-      <c r="P39" s="205" t="s">
+      <c r="P39" s="204" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="199"/>
-      <c r="D40" s="204"/>
-      <c r="E40" s="109"/>
-      <c r="F40" s="109" t="n">
+      <c r="A40" s="198"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="109"/>
-      <c r="I40" s="109"/>
-      <c r="J40" s="109"/>
+      <c r="H40" s="108"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
       <c r="K40" s="49"/>
-      <c r="M40" s="200" t="s">
+      <c r="M40" s="199" t="s">
         <v>261</v>
       </c>
-      <c r="P40" s="205" t="s">
+      <c r="P40" s="204" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="199"/>
-      <c r="D41" s="204"/>
-      <c r="E41" s="109"/>
-      <c r="F41" s="109" t="n">
+      <c r="A41" s="198"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="108" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="109"/>
-      <c r="I41" s="109"/>
-      <c r="J41" s="109"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="108"/>
+      <c r="J41" s="108"/>
       <c r="K41" s="49"/>
-      <c r="M41" s="200" t="s">
+      <c r="M41" s="199" t="s">
         <v>262</v>
       </c>
-      <c r="P41" s="205" t="s">
+      <c r="P41" s="204" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="199"/>
-      <c r="D42" s="204"/>
-      <c r="E42" s="109"/>
-      <c r="F42" s="109" t="n">
+      <c r="A42" s="198"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="109"/>
-      <c r="I42" s="109"/>
-      <c r="J42" s="109"/>
+      <c r="H42" s="108"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="108"/>
       <c r="K42" s="49"/>
       <c r="M42" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="P42" s="205" t="s">
+      <c r="P42" s="204" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="199"/>
-      <c r="D43" s="204"/>
-      <c r="E43" s="109"/>
-      <c r="F43" s="109"/>
+      <c r="A43" s="198"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
       <c r="G43" s="49"/>
-      <c r="H43" s="109"/>
-      <c r="I43" s="109"/>
-      <c r="J43" s="109"/>
+      <c r="H43" s="108"/>
+      <c r="I43" s="108"/>
+      <c r="J43" s="108"/>
       <c r="K43" s="49"/>
       <c r="M43" s="10"/>
       <c r="O43" s="1"/>
-      <c r="P43" s="208" t="s">
+      <c r="P43" s="207" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="199"/>
-      <c r="D44" s="204"/>
-      <c r="E44" s="109"/>
-      <c r="F44" s="109"/>
+      <c r="A44" s="198"/>
+      <c r="D44" s="203"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
       <c r="G44" s="49"/>
-      <c r="H44" s="109"/>
-      <c r="I44" s="109"/>
-      <c r="J44" s="109"/>
+      <c r="H44" s="108"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="108"/>
       <c r="K44" s="49"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="208" t="s">
+      <c r="P44" s="207" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A45" s="199"/>
-      <c r="D45" s="204"/>
-      <c r="E45" s="109"/>
-      <c r="F45" s="109"/>
+      <c r="A45" s="198"/>
+      <c r="D45" s="203"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="108"/>
       <c r="G45" s="49"/>
-      <c r="H45" s="109"/>
-      <c r="I45" s="109"/>
-      <c r="J45" s="109"/>
+      <c r="H45" s="108"/>
+      <c r="I45" s="108"/>
+      <c r="J45" s="108"/>
       <c r="K45" s="49"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="208" t="s">
+      <c r="P45" s="207" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A46" s="199"/>
+      <c r="A46" s="198"/>
       <c r="B46" s="16"/>
-      <c r="C46" s="109"/>
+      <c r="C46" s="108"/>
       <c r="D46" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E46" s="109"/>
-      <c r="F46" s="109"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
       <c r="G46" s="49"/>
       <c r="H46" s="48"/>
       <c r="I46" s="12"/>
-      <c r="J46" s="109"/>
+      <c r="J46" s="108"/>
       <c r="K46" s="49"/>
-      <c r="L46" s="130"/>
-      <c r="M46" s="200" t="s">
+      <c r="L46" s="129"/>
+      <c r="M46" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O46" s="201"/>
-      <c r="P46" s="202"/>
+      <c r="O46" s="200"/>
+      <c r="P46" s="201"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="199"/>
+      <c r="A47" s="198"/>
       <c r="B47" s="16"/>
-      <c r="C47" s="109"/>
+      <c r="C47" s="108"/>
       <c r="D47" s="48"/>
-      <c r="E47" s="109"/>
-      <c r="F47" s="109"/>
+      <c r="E47" s="108"/>
+      <c r="F47" s="108"/>
       <c r="G47" s="49"/>
       <c r="H47" s="48"/>
       <c r="I47" s="12"/>
-      <c r="J47" s="109"/>
+      <c r="J47" s="108"/>
       <c r="K47" s="49"/>
-      <c r="L47" s="200" t="s">
+      <c r="L47" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="M47" s="200"/>
+      <c r="M47" s="199"/>
       <c r="N47" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="O47" s="201" t="s">
+      <c r="O47" s="200" t="s">
         <v>280</v>
       </c>
-      <c r="P47" s="202"/>
+      <c r="P47" s="201"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="209"/>
-      <c r="B48" s="210"/>
-      <c r="C48" s="134"/>
-      <c r="D48" s="133"/>
-      <c r="E48" s="134"/>
-      <c r="F48" s="134"/>
-      <c r="G48" s="137"/>
-      <c r="H48" s="134"/>
-      <c r="I48" s="134"/>
-      <c r="J48" s="134"/>
-      <c r="K48" s="137"/>
-      <c r="L48" s="200" t="s">
+      <c r="A48" s="208"/>
+      <c r="B48" s="209"/>
+      <c r="C48" s="133"/>
+      <c r="D48" s="132"/>
+      <c r="E48" s="133"/>
+      <c r="F48" s="133"/>
+      <c r="G48" s="136"/>
+      <c r="H48" s="133"/>
+      <c r="I48" s="133"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="136"/>
+      <c r="L48" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="M48" s="211"/>
+      <c r="M48" s="210"/>
       <c r="N48" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="P48" s="206" t="s">
+      <c r="P48" s="205" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="192" t="s">
+      <c r="A49" s="191" t="s">
         <v>281</v>
       </c>
-      <c r="B49" s="193" t="str">
+      <c r="B49" s="192" t="str">
         <f aca="false">DEC2HEX(C49,2)</f>
         <v>0A</v>
       </c>
-      <c r="C49" s="155" t="n">
+      <c r="C49" s="154" t="n">
         <f aca="false">IF(D49=1,128,0)+IF(E49=1,64,0)+IF(F49=1,32,0)+IF(G49=1,16,0)+IF(H49=1,8,0)+IF(I49=1,4,0)+IF(J49=1,2,0)+IF(K49=1,1,0)</f>
         <v>10</v>
       </c>
-      <c r="D49" s="194"/>
-      <c r="E49" s="155"/>
-      <c r="F49" s="155"/>
-      <c r="G49" s="156"/>
-      <c r="H49" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="195"/>
-      <c r="M49" s="196" t="s">
+      <c r="D49" s="193"/>
+      <c r="E49" s="154"/>
+      <c r="F49" s="154"/>
+      <c r="G49" s="155"/>
+      <c r="H49" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="194"/>
+      <c r="M49" s="195" t="s">
         <v>282</v>
       </c>
-      <c r="N49" s="195"/>
-      <c r="O49" s="196"/>
-      <c r="P49" s="198"/>
+      <c r="N49" s="194"/>
+      <c r="O49" s="195"/>
+      <c r="P49" s="197"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A50" s="199"/>
+      <c r="A50" s="198"/>
       <c r="B50" s="16"/>
-      <c r="C50" s="109"/>
+      <c r="C50" s="108"/>
       <c r="D50" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="E50" s="109"/>
-      <c r="F50" s="109"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
       <c r="G50" s="49"/>
       <c r="H50" s="48"/>
       <c r="I50" s="12"/>
-      <c r="J50" s="109"/>
+      <c r="J50" s="108"/>
       <c r="K50" s="49"/>
-      <c r="L50" s="130"/>
-      <c r="M50" s="200" t="s">
+      <c r="L50" s="129"/>
+      <c r="M50" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="O50" s="201"/>
-      <c r="P50" s="202"/>
+      <c r="O50" s="200"/>
+      <c r="P50" s="201"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="199"/>
-      <c r="D51" s="204"/>
-      <c r="E51" s="109"/>
-      <c r="F51" s="109"/>
+      <c r="A51" s="198"/>
+      <c r="D51" s="203"/>
+      <c r="E51" s="108"/>
+      <c r="F51" s="108"/>
       <c r="G51" s="49"/>
-      <c r="H51" s="109"/>
-      <c r="I51" s="109"/>
-      <c r="J51" s="109"/>
+      <c r="H51" s="108"/>
+      <c r="I51" s="108"/>
+      <c r="J51" s="108"/>
       <c r="K51" s="49"/>
-      <c r="L51" s="200" t="s">
+      <c r="L51" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="M51" s="131"/>
+      <c r="M51" s="130"/>
       <c r="N51" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O51" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="P51" s="202" t="s">
+      <c r="P51" s="201" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="192" t="s">
+      <c r="A52" s="191" t="s">
         <v>285</v>
       </c>
-      <c r="B52" s="193" t="str">
+      <c r="B52" s="192" t="str">
         <f aca="false">DEC2HEX(C52,2)</f>
         <v>0C</v>
       </c>
-      <c r="C52" s="155" t="n">
+      <c r="C52" s="154" t="n">
         <f aca="false">IF(D52=1,128,0)+IF(E52=1,64,0)+IF(F52=1,32,0)+IF(G52=1,16,0)+IF(H52=1,8,0)+IF(I52=1,4,0)+IF(J52=1,2,0)+IF(K52=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="D52" s="194"/>
-      <c r="E52" s="155"/>
-      <c r="F52" s="155"/>
-      <c r="G52" s="156"/>
-      <c r="H52" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="195"/>
-      <c r="M52" s="195" t="s">
+      <c r="D52" s="193"/>
+      <c r="E52" s="154"/>
+      <c r="F52" s="154"/>
+      <c r="G52" s="155"/>
+      <c r="H52" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="194"/>
+      <c r="M52" s="194" t="s">
         <v>286</v>
       </c>
-      <c r="N52" s="195"/>
-      <c r="O52" s="196"/>
-      <c r="P52" s="198"/>
+      <c r="N52" s="194"/>
+      <c r="O52" s="195"/>
+      <c r="P52" s="197"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="199"/>
-      <c r="D53" s="204" t="s">
+      <c r="A53" s="198"/>
+      <c r="D53" s="203" t="s">
         <v>229</v>
       </c>
-      <c r="E53" s="109"/>
-      <c r="F53" s="109"/>
+      <c r="E53" s="108"/>
+      <c r="F53" s="108"/>
       <c r="G53" s="49"/>
-      <c r="H53" s="109"/>
-      <c r="I53" s="109"/>
-      <c r="J53" s="109"/>
+      <c r="H53" s="108"/>
+      <c r="I53" s="108"/>
+      <c r="J53" s="108"/>
       <c r="K53" s="49"/>
-      <c r="M53" s="200" t="s">
+      <c r="M53" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="N53" s="200"/>
-      <c r="O53" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="202"/>
+      <c r="N53" s="199"/>
+      <c r="O53" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="201"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A54" s="199"/>
-      <c r="D54" s="204"/>
-      <c r="E54" s="109"/>
-      <c r="F54" s="109"/>
+      <c r="A54" s="198"/>
+      <c r="D54" s="203"/>
+      <c r="E54" s="108"/>
+      <c r="F54" s="108"/>
       <c r="G54" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="109"/>
-      <c r="I54" s="109"/>
-      <c r="J54" s="109"/>
+      <c r="H54" s="108"/>
+      <c r="I54" s="108"/>
+      <c r="J54" s="108"/>
       <c r="K54" s="49"/>
-      <c r="L54" s="200" t="s">
+      <c r="L54" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="M54" s="200" t="s">
+      <c r="M54" s="199" t="s">
         <v>287</v>
       </c>
-      <c r="N54" s="200"/>
-      <c r="O54" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="202" t="s">
+      <c r="N54" s="199"/>
+      <c r="O54" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="201" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="199"/>
-      <c r="D55" s="204"/>
-      <c r="E55" s="109"/>
-      <c r="F55" s="109"/>
+      <c r="A55" s="198"/>
+      <c r="D55" s="203"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="108"/>
       <c r="G55" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="109"/>
-      <c r="I55" s="109"/>
-      <c r="J55" s="109"/>
+      <c r="H55" s="108"/>
+      <c r="I55" s="108"/>
+      <c r="J55" s="108"/>
       <c r="K55" s="49"/>
-      <c r="L55" s="200" t="s">
+      <c r="L55" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="M55" s="200" t="s">
+      <c r="M55" s="199" t="s">
         <v>289</v>
       </c>
-      <c r="N55" s="200"/>
-      <c r="O55" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="202" t="s">
+      <c r="N55" s="199"/>
+      <c r="O55" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="201" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="192"/>
-      <c r="B56" s="193" t="str">
+      <c r="A56" s="191"/>
+      <c r="B56" s="192" t="str">
         <f aca="false">DEC2HEX(C56,2)</f>
         <v>00</v>
       </c>
-      <c r="C56" s="155" t="n">
+      <c r="C56" s="154" t="n">
         <f aca="false">IF(D56=1,128,0)+IF(E56=1,64,0)+IF(F56=1,32,0)+IF(G56=1,16,0)+IF(H56=1,8,0)+IF(I56=1,4,0)+IF(J56=1,2,0)+IF(K56=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="194"/>
-      <c r="E56" s="155"/>
-      <c r="F56" s="155"/>
-      <c r="G56" s="156"/>
-      <c r="H56" s="155"/>
-      <c r="I56" s="155"/>
-      <c r="J56" s="155"/>
-      <c r="K56" s="156"/>
-      <c r="L56" s="195"/>
-      <c r="M56" s="195"/>
-      <c r="N56" s="195"/>
-      <c r="O56" s="196"/>
-      <c r="P56" s="198"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="154"/>
+      <c r="F56" s="154"/>
+      <c r="G56" s="155"/>
+      <c r="H56" s="154"/>
+      <c r="I56" s="154"/>
+      <c r="J56" s="154"/>
+      <c r="K56" s="155"/>
+      <c r="L56" s="194"/>
+      <c r="M56" s="194"/>
+      <c r="N56" s="194"/>
+      <c r="O56" s="195"/>
+      <c r="P56" s="197"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A57" s="199"/>
-      <c r="D57" s="204"/>
-      <c r="E57" s="109"/>
-      <c r="F57" s="109"/>
+      <c r="A57" s="198"/>
+      <c r="D57" s="203"/>
+      <c r="E57" s="108"/>
+      <c r="F57" s="108"/>
       <c r="G57" s="49"/>
-      <c r="H57" s="109"/>
-      <c r="I57" s="109"/>
-      <c r="J57" s="109"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="108"/>
+      <c r="J57" s="108"/>
       <c r="K57" s="49"/>
-      <c r="M57" s="200"/>
-      <c r="N57" s="200"/>
-      <c r="O57" s="130"/>
-      <c r="P57" s="202"/>
+      <c r="M57" s="199"/>
+      <c r="N57" s="199"/>
+      <c r="O57" s="129"/>
+      <c r="P57" s="201"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="199"/>
-      <c r="D58" s="204"/>
-      <c r="E58" s="109"/>
-      <c r="F58" s="109"/>
+      <c r="A58" s="198"/>
+      <c r="D58" s="203"/>
+      <c r="E58" s="108"/>
+      <c r="F58" s="108"/>
       <c r="G58" s="49"/>
-      <c r="H58" s="109"/>
-      <c r="I58" s="109"/>
-      <c r="J58" s="109"/>
+      <c r="H58" s="108"/>
+      <c r="I58" s="108"/>
+      <c r="J58" s="108"/>
       <c r="K58" s="49"/>
-      <c r="M58" s="200"/>
-      <c r="N58" s="200"/>
-      <c r="O58" s="130"/>
-      <c r="P58" s="202"/>
+      <c r="M58" s="199"/>
+      <c r="N58" s="199"/>
+      <c r="O58" s="129"/>
+      <c r="P58" s="201"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A59" s="199"/>
-      <c r="D59" s="204"/>
-      <c r="E59" s="109"/>
-      <c r="F59" s="109"/>
+      <c r="A59" s="198"/>
+      <c r="D59" s="203"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="108"/>
       <c r="G59" s="49"/>
-      <c r="H59" s="109"/>
-      <c r="I59" s="109"/>
-      <c r="J59" s="109"/>
+      <c r="H59" s="108"/>
+      <c r="I59" s="108"/>
+      <c r="J59" s="108"/>
       <c r="K59" s="49"/>
-      <c r="M59" s="200"/>
-      <c r="N59" s="200"/>
-      <c r="O59" s="130"/>
-      <c r="P59" s="202"/>
+      <c r="M59" s="199"/>
+      <c r="N59" s="199"/>
+      <c r="O59" s="129"/>
+      <c r="P59" s="201"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A60" s="199"/>
-      <c r="D60" s="204"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
+      <c r="A60" s="198"/>
+      <c r="D60" s="203"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
       <c r="G60" s="49"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
       <c r="K60" s="49"/>
-      <c r="M60" s="200"/>
-      <c r="N60" s="200"/>
-      <c r="O60" s="130"/>
-      <c r="P60" s="202"/>
+      <c r="M60" s="199"/>
+      <c r="N60" s="199"/>
+      <c r="O60" s="129"/>
+      <c r="P60" s="201"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="199"/>
-      <c r="D61" s="204"/>
-      <c r="E61" s="109"/>
-      <c r="F61" s="109"/>
+      <c r="A61" s="198"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="108"/>
+      <c r="F61" s="108"/>
       <c r="G61" s="49"/>
-      <c r="H61" s="109"/>
-      <c r="I61" s="109"/>
-      <c r="J61" s="109"/>
+      <c r="H61" s="108"/>
+      <c r="I61" s="108"/>
+      <c r="J61" s="108"/>
       <c r="K61" s="49"/>
-      <c r="M61" s="200"/>
-      <c r="N61" s="200"/>
-      <c r="O61" s="130"/>
-      <c r="P61" s="202"/>
+      <c r="M61" s="199"/>
+      <c r="N61" s="199"/>
+      <c r="O61" s="129"/>
+      <c r="P61" s="201"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="192" t="s">
+      <c r="A62" s="191" t="s">
         <v>210</v>
       </c>
-      <c r="B62" s="193"/>
-      <c r="C62" s="155"/>
-      <c r="D62" s="194"/>
-      <c r="E62" s="155"/>
-      <c r="F62" s="155"/>
-      <c r="G62" s="156"/>
-      <c r="H62" s="194"/>
-      <c r="I62" s="155"/>
-      <c r="J62" s="155"/>
-      <c r="K62" s="156"/>
-      <c r="L62" s="196"/>
-      <c r="M62" s="195"/>
-      <c r="N62" s="195"/>
-      <c r="O62" s="196"/>
-      <c r="P62" s="198"/>
+      <c r="B62" s="192"/>
+      <c r="C62" s="154"/>
+      <c r="D62" s="193"/>
+      <c r="E62" s="154"/>
+      <c r="F62" s="154"/>
+      <c r="G62" s="155"/>
+      <c r="H62" s="193"/>
+      <c r="I62" s="154"/>
+      <c r="J62" s="154"/>
+      <c r="K62" s="155"/>
+      <c r="L62" s="195"/>
+      <c r="M62" s="194"/>
+      <c r="N62" s="194"/>
+      <c r="O62" s="195"/>
+      <c r="P62" s="197"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A63" s="212" t="s">
+      <c r="A63" s="211" t="s">
         <v>291</v>
       </c>
-      <c r="B63" s="187" t="str">
+      <c r="B63" s="186" t="str">
         <f aca="false">DEC2HEX(C63,2)</f>
         <v>00</v>
       </c>
-      <c r="C63" s="213" t="n">
+      <c r="C63" s="212" t="n">
         <f aca="false">IF(D63=1,128,0)+IF(E63=1,64,0)+IF(F63=1,32,0)+IF(G63=1,16,0)+IF(H63=1,8,0)+IF(I63=1,4,0)+IF(J63=1,2,0)+IF(K63=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="216"/>
-      <c r="M63" s="217"/>
-      <c r="N63" s="217"/>
-      <c r="O63" s="216"/>
-      <c r="P63" s="218"/>
+      <c r="D63" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="215"/>
+      <c r="M63" s="216"/>
+      <c r="N63" s="216"/>
+      <c r="O63" s="215"/>
+      <c r="P63" s="217"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="199" t="s">
+      <c r="A64" s="198" t="s">
         <v>292</v>
       </c>
       <c r="B64" s="20" t="str">
@@ -9044,10 +9040,10 @@
       <c r="D64" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="109" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="109" t="n">
+      <c r="E64" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="49" t="n">
@@ -9056,23 +9052,23 @@
       <c r="H64" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="I64" s="109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="109" t="n">
+      <c r="I64" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="L64" s="130"/>
-      <c r="M64" s="200"/>
-      <c r="N64" s="200"/>
-      <c r="O64" s="130"/>
-      <c r="P64" s="202"/>
+      <c r="L64" s="129"/>
+      <c r="M64" s="199"/>
+      <c r="N64" s="199"/>
+      <c r="O64" s="129"/>
+      <c r="P64" s="201"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A65" s="199" t="s">
+      <c r="A65" s="198" t="s">
         <v>293</v>
       </c>
       <c r="B65" s="20" t="str">
@@ -9086,10 +9082,10 @@
       <c r="D65" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="109" t="n">
+      <c r="E65" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="49" t="n">
@@ -9098,107 +9094,107 @@
       <c r="H65" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="I65" s="109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="109" t="n">
+      <c r="I65" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="130"/>
-      <c r="M65" s="200"/>
-      <c r="N65" s="200"/>
-      <c r="O65" s="130"/>
-      <c r="P65" s="202"/>
+      <c r="L65" s="129"/>
+      <c r="M65" s="199"/>
+      <c r="N65" s="199"/>
+      <c r="O65" s="129"/>
+      <c r="P65" s="201"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A66" s="209" t="s">
+      <c r="A66" s="208" t="s">
         <v>294</v>
       </c>
-      <c r="B66" s="210" t="str">
+      <c r="B66" s="209" t="str">
         <f aca="false">DEC2HEX(C66,2)</f>
         <v>C0</v>
       </c>
-      <c r="C66" s="134" t="n">
+      <c r="C66" s="133" t="n">
         <f aca="false">IF(D66=1,128,0)+IF(E66=1,64,0)+IF(F66=1,32,0)+IF(G66=1,16,0)+IF(H66=1,8,0)+IF(I66=1,4,0)+IF(J66=1,2,0)+IF(K66=1,1,0)</f>
         <v>192</v>
       </c>
-      <c r="D66" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="219"/>
-      <c r="M66" s="220"/>
-      <c r="N66" s="220"/>
-      <c r="O66" s="211"/>
-      <c r="P66" s="221"/>
+      <c r="D66" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="218"/>
+      <c r="M66" s="219"/>
+      <c r="N66" s="219"/>
+      <c r="O66" s="210"/>
+      <c r="P66" s="220"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A67" s="212" t="s">
+      <c r="A67" s="211" t="s">
         <v>295</v>
       </c>
-      <c r="B67" s="187" t="str">
+      <c r="B67" s="186" t="str">
         <f aca="false">DEC2HEX(C67,2)</f>
         <v>01</v>
       </c>
-      <c r="C67" s="213" t="n">
+      <c r="C67" s="212" t="n">
         <f aca="false">IF(D67=1,128,0)+IF(E67=1,64,0)+IF(F67=1,32,0)+IF(G67=1,16,0)+IF(H67=1,8,0)+IF(I67=1,4,0)+IF(J67=1,2,0)+IF(K67=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="D67" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="215" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="222"/>
-      <c r="M67" s="217"/>
-      <c r="N67" s="217"/>
-      <c r="O67" s="216"/>
-      <c r="P67" s="218"/>
+      <c r="D67" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="214" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="221"/>
+      <c r="M67" s="216"/>
+      <c r="N67" s="216"/>
+      <c r="O67" s="215"/>
+      <c r="P67" s="217"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A68" s="199" t="s">
+      <c r="A68" s="198" t="s">
         <v>296</v>
       </c>
       <c r="B68" s="20" t="str">
@@ -9209,7 +9205,7 @@
         <f aca="false">IF(D68=1,128,0)+IF(E68=1,64,0)+IF(F68=1,32,0)+IF(G68=1,16,0)+IF(H68=1,8,0)+IF(I68=1,4,0)+IF(J68=1,2,0)+IF(K68=1,1,0)</f>
         <v>65</v>
       </c>
-      <c r="D68" s="204" t="n">
+      <c r="D68" s="203" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="n">
@@ -9233,11 +9229,11 @@
       <c r="K68" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="L68" s="223"/>
-      <c r="P68" s="202"/>
+      <c r="L68" s="222"/>
+      <c r="P68" s="201"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A69" s="199" t="s">
+      <c r="A69" s="198" t="s">
         <v>297</v>
       </c>
       <c r="B69" s="20" t="str">
@@ -9248,13 +9244,13 @@
         <f aca="false">IF(D69=1,128,0)+IF(E69=1,64,0)+IF(F69=1,32,0)+IF(G69=1,16,0)+IF(H69=1,8,0)+IF(I69=1,4,0)+IF(J69=1,2,0)+IF(K69=1,1,0)</f>
         <v>193</v>
       </c>
-      <c r="D69" s="204" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="109" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="109" t="n">
+      <c r="D69" s="203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="49" t="n">
@@ -9272,100 +9268,100 @@
       <c r="K69" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="L69" s="223"/>
+      <c r="L69" s="222"/>
       <c r="M69" s="10"/>
       <c r="N69" s="10"/>
-      <c r="O69" s="130"/>
-      <c r="P69" s="202"/>
+      <c r="O69" s="129"/>
+      <c r="P69" s="201"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A70" s="209" t="s">
+      <c r="A70" s="208" t="s">
         <v>298</v>
       </c>
-      <c r="B70" s="210" t="str">
+      <c r="B70" s="209" t="str">
         <f aca="false">DEC2HEX(C70,2)</f>
         <v>03</v>
       </c>
-      <c r="C70" s="134" t="n">
+      <c r="C70" s="133" t="n">
         <f aca="false">IF(D70=1,128,0)+IF(E70=1,64,0)+IF(F70=1,32,0)+IF(G70=1,16,0)+IF(H70=1,8,0)+IF(I70=1,4,0)+IF(J70=1,2,0)+IF(K70=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="D70" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="211"/>
-      <c r="M70" s="220"/>
-      <c r="N70" s="220"/>
-      <c r="O70" s="211"/>
-      <c r="P70" s="221"/>
+      <c r="D70" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="210"/>
+      <c r="M70" s="219"/>
+      <c r="N70" s="219"/>
+      <c r="O70" s="210"/>
+      <c r="P70" s="220"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="212" t="s">
+      <c r="A71" s="211" t="s">
         <v>299</v>
       </c>
-      <c r="B71" s="187" t="str">
+      <c r="B71" s="186" t="str">
         <f aca="false">DEC2HEX(C71,2)</f>
         <v>04</v>
       </c>
-      <c r="C71" s="213" t="n">
+      <c r="C71" s="212" t="n">
         <f aca="false">IF(D71=1,128,0)+IF(E71=1,64,0)+IF(F71=1,32,0)+IF(G71=1,16,0)+IF(H71=1,8,0)+IF(I71=1,4,0)+IF(J71=1,2,0)+IF(K71=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="D71" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="179" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="216"/>
-      <c r="M71" s="217"/>
-      <c r="N71" s="217"/>
-      <c r="O71" s="216"/>
-      <c r="P71" s="218" t="s">
+      <c r="D71" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="215"/>
+      <c r="M71" s="216"/>
+      <c r="N71" s="216"/>
+      <c r="O71" s="215"/>
+      <c r="P71" s="217" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="199" t="s">
+      <c r="A72" s="198" t="s">
         <v>301</v>
       </c>
       <c r="B72" s="20" t="str">
@@ -9379,10 +9375,10 @@
       <c r="D72" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="109" t="n">
+      <c r="E72" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="49" t="n">
@@ -9391,216 +9387,216 @@
       <c r="H72" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="I72" s="109" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="109" t="n">
+      <c r="I72" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="108" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="130"/>
-      <c r="M72" s="200"/>
-      <c r="N72" s="200"/>
-      <c r="O72" s="130"/>
-      <c r="P72" s="202" t="s">
+      <c r="L72" s="129"/>
+      <c r="M72" s="199"/>
+      <c r="N72" s="199"/>
+      <c r="O72" s="129"/>
+      <c r="P72" s="201" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="209" t="s">
+      <c r="A73" s="208" t="s">
         <v>303</v>
       </c>
-      <c r="B73" s="210" t="str">
+      <c r="B73" s="209" t="str">
         <f aca="false">DEC2HEX(C73,2)</f>
         <v>54</v>
       </c>
-      <c r="C73" s="134" t="n">
+      <c r="C73" s="133" t="n">
         <f aca="false">IF(D73=1,128,0)+IF(E73=1,64,0)+IF(F73=1,32,0)+IF(G73=1,16,0)+IF(H73=1,8,0)+IF(I73=1,4,0)+IF(J73=1,2,0)+IF(K73=1,1,0)</f>
         <v>84</v>
       </c>
-      <c r="D73" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="211"/>
-      <c r="M73" s="220"/>
-      <c r="N73" s="220"/>
-      <c r="O73" s="211"/>
-      <c r="P73" s="221" t="s">
+      <c r="D73" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="210"/>
+      <c r="M73" s="219"/>
+      <c r="N73" s="219"/>
+      <c r="O73" s="210"/>
+      <c r="P73" s="220" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="212" t="s">
+      <c r="A74" s="211" t="s">
         <v>305</v>
       </c>
-      <c r="B74" s="187" t="str">
+      <c r="B74" s="186" t="str">
         <f aca="false">DEC2HEX(C74,2)</f>
         <v>05</v>
       </c>
-      <c r="C74" s="213" t="n">
+      <c r="C74" s="212" t="n">
         <f aca="false">IF(D74=1,128,0)+IF(E74=1,64,0)+IF(F74=1,32,0)+IF(G74=1,16,0)+IF(H74=1,8,0)+IF(I74=1,4,0)+IF(J74=1,2,0)+IF(K74=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="D74" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="179" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="215" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="216"/>
-      <c r="M74" s="217"/>
-      <c r="N74" s="217"/>
-      <c r="O74" s="216"/>
-      <c r="P74" s="218" t="s">
+      <c r="D74" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="214" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="215"/>
+      <c r="M74" s="216"/>
+      <c r="N74" s="216"/>
+      <c r="O74" s="215"/>
+      <c r="P74" s="217" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="209" t="s">
+      <c r="A75" s="208" t="s">
         <v>307</v>
       </c>
-      <c r="B75" s="210" t="str">
+      <c r="B75" s="209" t="str">
         <f aca="false">DEC2HEX(C75,2)</f>
         <v>15</v>
       </c>
-      <c r="C75" s="134" t="n">
+      <c r="C75" s="133" t="n">
         <f aca="false">IF(D75=1,128,0)+IF(E75=1,64,0)+IF(F75=1,32,0)+IF(G75=1,16,0)+IF(H75=1,8,0)+IF(I75=1,4,0)+IF(J75=1,2,0)+IF(K75=1,1,0)</f>
         <v>21</v>
       </c>
-      <c r="D75" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="211"/>
-      <c r="M75" s="220"/>
-      <c r="N75" s="220"/>
-      <c r="O75" s="211"/>
-      <c r="P75" s="221" t="s">
+      <c r="D75" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="210"/>
+      <c r="M75" s="219"/>
+      <c r="N75" s="219"/>
+      <c r="O75" s="210"/>
+      <c r="P75" s="220" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="212" t="s">
+      <c r="A76" s="211" t="s">
         <v>309</v>
       </c>
-      <c r="B76" s="187" t="str">
+      <c r="B76" s="186" t="str">
         <f aca="false">DEC2HEX(C76,2)</f>
         <v>46</v>
       </c>
-      <c r="C76" s="213" t="n">
+      <c r="C76" s="212" t="n">
         <f aca="false">IF(D76=1,128,0)+IF(E76=1,64,0)+IF(F76=1,32,0)+IF(G76=1,16,0)+IF(H76=1,8,0)+IF(I76=1,4,0)+IF(J76=1,2,0)+IF(K76=1,1,0)</f>
         <v>70</v>
       </c>
-      <c r="D76" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="179" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="179" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="179" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="216"/>
-      <c r="M76" s="217"/>
-      <c r="N76" s="217"/>
-      <c r="O76" s="216"/>
-      <c r="P76" s="218"/>
+      <c r="D76" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="215"/>
+      <c r="M76" s="216"/>
+      <c r="N76" s="216"/>
+      <c r="O76" s="215"/>
+      <c r="P76" s="217"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="199" t="s">
+      <c r="A77" s="198" t="s">
         <v>310</v>
       </c>
       <c r="B77" s="16" t="str">
         <f aca="false">DEC2HEX(C77,2)</f>
         <v>56</v>
       </c>
-      <c r="C77" s="109" t="n">
+      <c r="C77" s="108" t="n">
         <f aca="false">IF(D77=1,128,0)+IF(E77=1,64,0)+IF(F77=1,32,0)+IF(G77=1,16,0)+IF(H77=1,8,0)+IF(I77=1,4,0)+IF(J77=1,2,0)+IF(K77=1,1,0)</f>
         <v>86</v>
       </c>
       <c r="D77" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="109" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="109" t="n">
+      <c r="E77" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="49" t="n">
@@ -9609,40 +9605,40 @@
       <c r="H77" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="109" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="109" t="n">
+      <c r="I77" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K77" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="L77" s="130"/>
-      <c r="M77" s="200"/>
-      <c r="N77" s="200"/>
-      <c r="O77" s="130"/>
-      <c r="P77" s="202"/>
+      <c r="L77" s="129"/>
+      <c r="M77" s="199"/>
+      <c r="N77" s="199"/>
+      <c r="O77" s="129"/>
+      <c r="P77" s="201"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="199" t="s">
+      <c r="A78" s="198" t="s">
         <v>311</v>
       </c>
       <c r="B78" s="16" t="str">
         <f aca="false">DEC2HEX(C78,2)</f>
         <v>C7</v>
       </c>
-      <c r="C78" s="109" t="n">
+      <c r="C78" s="108" t="n">
         <f aca="false">IF(D78=1,128,0)+IF(E78=1,64,0)+IF(F78=1,32,0)+IF(G78=1,16,0)+IF(H78=1,8,0)+IF(I78=1,4,0)+IF(J78=1,2,0)+IF(K78=1,1,0)</f>
         <v>199</v>
       </c>
       <c r="D78" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="109" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="109" t="n">
+      <c r="E78" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="108" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="49" t="n">
@@ -9651,197 +9647,197 @@
       <c r="H78" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="109" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="109" t="n">
+      <c r="I78" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="108" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="L78" s="130"/>
-      <c r="M78" s="200"/>
-      <c r="N78" s="200"/>
-      <c r="O78" s="130"/>
-      <c r="P78" s="202"/>
+      <c r="L78" s="129"/>
+      <c r="M78" s="199"/>
+      <c r="N78" s="199"/>
+      <c r="O78" s="129"/>
+      <c r="P78" s="201"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="209" t="s">
+      <c r="A79" s="208" t="s">
         <v>312</v>
       </c>
-      <c r="B79" s="210" t="str">
+      <c r="B79" s="209" t="str">
         <f aca="false">DEC2HEX(C79,2)</f>
         <v>D7</v>
       </c>
-      <c r="C79" s="134" t="n">
+      <c r="C79" s="133" t="n">
         <f aca="false">IF(D79=1,128,0)+IF(E79=1,64,0)+IF(F79=1,32,0)+IF(G79=1,16,0)+IF(H79=1,8,0)+IF(I79=1,4,0)+IF(J79=1,2,0)+IF(K79=1,1,0)</f>
         <v>215</v>
       </c>
-      <c r="D79" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="211"/>
-      <c r="M79" s="220"/>
-      <c r="N79" s="220"/>
-      <c r="O79" s="211"/>
-      <c r="P79" s="221"/>
+      <c r="D79" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="210"/>
+      <c r="M79" s="219"/>
+      <c r="N79" s="219"/>
+      <c r="O79" s="210"/>
+      <c r="P79" s="220"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="212" t="s">
+      <c r="A80" s="211" t="s">
         <v>313</v>
       </c>
-      <c r="B80" s="187" t="str">
+      <c r="B80" s="186" t="str">
         <f aca="false">DEC2HEX(C80,2)</f>
         <v>0C</v>
       </c>
-      <c r="C80" s="213" t="n">
+      <c r="C80" s="212" t="n">
         <f aca="false">IF(D80=1,128,0)+IF(E80=1,64,0)+IF(F80=1,32,0)+IF(G80=1,16,0)+IF(H80=1,8,0)+IF(I80=1,4,0)+IF(J80=1,2,0)+IF(K80=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="D80" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="214" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" s="179" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="215" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="216"/>
-      <c r="M80" s="217"/>
-      <c r="N80" s="217"/>
-      <c r="O80" s="216"/>
-      <c r="P80" s="218"/>
+      <c r="D80" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="215"/>
+      <c r="M80" s="216"/>
+      <c r="N80" s="216"/>
+      <c r="O80" s="215"/>
+      <c r="P80" s="217"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="209" t="s">
+      <c r="A81" s="208" t="s">
         <v>314</v>
       </c>
-      <c r="B81" s="210" t="str">
+      <c r="B81" s="209" t="str">
         <f aca="false">DEC2HEX(C81,2)</f>
         <v>8C</v>
       </c>
-      <c r="C81" s="134" t="n">
+      <c r="C81" s="133" t="n">
         <f aca="false">IF(D81=1,128,0)+IF(E81=1,64,0)+IF(F81=1,32,0)+IF(G81=1,16,0)+IF(H81=1,8,0)+IF(I81=1,4,0)+IF(J81=1,2,0)+IF(K81=1,1,0)</f>
         <v>140</v>
       </c>
-      <c r="D81" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="211"/>
-      <c r="M81" s="220"/>
-      <c r="N81" s="220"/>
-      <c r="O81" s="211"/>
-      <c r="P81" s="221"/>
+      <c r="D81" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="210"/>
+      <c r="M81" s="219"/>
+      <c r="N81" s="219"/>
+      <c r="O81" s="210"/>
+      <c r="P81" s="220"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="199"/>
+      <c r="A82" s="198"/>
       <c r="B82" s="16" t="str">
         <f aca="false">DEC2HEX(C82,2)</f>
         <v>00</v>
       </c>
-      <c r="C82" s="109" t="n">
+      <c r="C82" s="108" t="n">
         <f aca="false">IF(D82=1,128,0)+IF(E82=1,64,0)+IF(F82=1,32,0)+IF(G82=1,16,0)+IF(H82=1,8,0)+IF(I82=1,4,0)+IF(J82=1,2,0)+IF(K82=1,1,0)</f>
         <v>0</v>
       </c>
       <c r="D82" s="48"/>
-      <c r="E82" s="109"/>
-      <c r="F82" s="109"/>
+      <c r="E82" s="108"/>
+      <c r="F82" s="108"/>
       <c r="G82" s="49"/>
       <c r="H82" s="48"/>
-      <c r="I82" s="109"/>
-      <c r="J82" s="109"/>
+      <c r="I82" s="108"/>
+      <c r="J82" s="108"/>
       <c r="K82" s="49"/>
-      <c r="L82" s="130"/>
-      <c r="M82" s="200"/>
-      <c r="N82" s="200"/>
-      <c r="O82" s="130"/>
-      <c r="P82" s="202"/>
+      <c r="L82" s="129"/>
+      <c r="M82" s="199"/>
+      <c r="N82" s="199"/>
+      <c r="O82" s="129"/>
+      <c r="P82" s="201"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="209"/>
-      <c r="B83" s="210" t="str">
+      <c r="A83" s="208"/>
+      <c r="B83" s="209" t="str">
         <f aca="false">DEC2HEX(C83,2)</f>
         <v>00</v>
       </c>
-      <c r="C83" s="134" t="n">
+      <c r="C83" s="133" t="n">
         <f aca="false">IF(D83=1,128,0)+IF(E83=1,64,0)+IF(F83=1,32,0)+IF(G83=1,16,0)+IF(H83=1,8,0)+IF(I83=1,4,0)+IF(J83=1,2,0)+IF(K83=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D83" s="133"/>
-      <c r="E83" s="134"/>
-      <c r="F83" s="134"/>
-      <c r="G83" s="137"/>
-      <c r="H83" s="133"/>
-      <c r="I83" s="134"/>
-      <c r="J83" s="134"/>
-      <c r="K83" s="137"/>
-      <c r="L83" s="211"/>
-      <c r="M83" s="220"/>
-      <c r="N83" s="220"/>
-      <c r="O83" s="211"/>
-      <c r="P83" s="221"/>
+      <c r="D83" s="132"/>
+      <c r="E83" s="133"/>
+      <c r="F83" s="133"/>
+      <c r="G83" s="136"/>
+      <c r="H83" s="132"/>
+      <c r="I83" s="133"/>
+      <c r="J83" s="133"/>
+      <c r="K83" s="136"/>
+      <c r="L83" s="210"/>
+      <c r="M83" s="219"/>
+      <c r="N83" s="219"/>
+      <c r="O83" s="210"/>
+      <c r="P83" s="220"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L84" s="131"/>
+      <c r="L84" s="130"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
@@ -9860,7 +9856,7 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="224"/>
+      <c r="O85" s="223"/>
       <c r="P85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9918,12 +9914,12 @@
       <c r="F1" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="G1" s="225" t="s">
+      <c r="G1" s="224" t="s">
         <v>318</v>
       </c>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225" t="s">
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224" t="s">
         <v>319</v>
       </c>
     </row>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Connection" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="L6" authorId="0">
+    <comment ref="M6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,7 +52,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L15" authorId="0">
+    <comment ref="M15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -74,7 +74,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M13" authorId="0">
+    <comment ref="N13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -86,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="0">
+    <comment ref="N14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M15" authorId="0">
+    <comment ref="N15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="345">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -1075,9 +1075,15 @@
     <t xml:space="preserve">IsStream</t>
   </si>
   <si>
+    <t xml:space="preserve">04</t>
+  </si>
+  <si>
     <t xml:space="preserve">IsServlet</t>
   </si>
   <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
     <t xml:space="preserve">HasDevicePath</t>
   </si>
   <si>
@@ -1117,25 +1123,91 @@
     <t xml:space="preserve">Simple</t>
   </si>
   <si>
+    <t xml:space="preserve">00</t>
+  </si>
+  <si>
     <t xml:space="preserve">SimpleType</t>
   </si>
   <si>
     <t xml:space="preserve">See SimpleType tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsCustomType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CustomTypeName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer's proprietary type.</t>
+    <t xml:space="preserve">Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayElemCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Number of </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">elements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> in the array, not number of bytes that make up the data.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">IsArrayElemType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayElemType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1..2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ValueType (+SimpleType)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specifies the type of all elements in the array.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every value is of the type specified by ArrayElemType.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not IsArrayElemType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each value begins with its own ValueType.</t>
   </si>
   <si>
     <t xml:space="preserve">Struct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
   </si>
   <si>
     <t xml:space="preserve">StructElemCount</t>
@@ -1174,73 +1246,16 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each value begins with its own ValueType.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArrayElemCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Number of </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">elements</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> in the array, not number of bytes that make up the data.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">IsArrayElemType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArrayElemType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1..2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ValueType (+SimpleType)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specifies the type of all elements in the array.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every value is of the type specified by ArrayElemType.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not IsArrayElemType</t>
+    <t xml:space="preserve">Custom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsCustomType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CustomTypeName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer's proprietary type.</t>
   </si>
   <si>
     <t xml:space="preserve">String: 2 bytes representing byte count of the string, followed by UTF-8 characters</t>
@@ -1276,13 +1291,13 @@
     <t xml:space="preserve">(ValueName), (TypeName), SimpleType</t>
   </si>
   <si>
+    <t xml:space="preserve">(ValueName), (TypeName), ArrayElemCount, (ArrayElemType), Values</t>
+  </si>
+  <si>
     <t xml:space="preserve">(ValueName), (TypeName), StructElemCount, Values</t>
   </si>
   <si>
     <t xml:space="preserve">(ValueName), (TypeName), (CustomTypeName), SimpleType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(ValueName), (TypeName), ArrayElemCount, (ArrayElemType), Values</t>
   </si>
   <si>
     <t xml:space="preserve">Integer</t>
@@ -1823,7 +1838,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1877,12 +1892,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2423,11 +2432,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="236">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2836,7 +2845,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2864,23 +2873,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2888,19 +2909,23 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="43" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2920,19 +2945,23 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2956,6 +2985,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2988,6 +3021,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3028,11 +3065,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3040,7 +3081,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3060,59 +3101,83 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3124,15 +3189,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3152,7 +3217,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3160,7 +3225,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3240,7 +3305,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6119,7 +6184,7 @@
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="109"/>
     </row>
-    <row r="9" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="109" t="s">
         <v>140</v>
       </c>
@@ -6129,12 +6194,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="109" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="109" t="s">
         <v>143</v>
       </c>
@@ -6142,17 +6207,17 @@
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="109"/>
     </row>
-    <row r="14" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="109" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="109" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="109" t="s">
         <v>146</v>
       </c>
@@ -6255,1179 +6320,1239 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:S1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="110" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="5" width="3.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="15.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="24.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="27.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="5" width="76.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="5" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="5" width="71.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="111" width="3.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="5" width="3.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="15.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="5" width="24.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="27.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="5" width="76.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="5" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="5" width="71.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="111" t="n">
+      <c r="C1" s="112" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="113" t="n">
         <v>7</v>
       </c>
-      <c r="D1" s="111" t="n">
+      <c r="E1" s="113" t="n">
         <v>6</v>
       </c>
-      <c r="E1" s="111" t="n">
+      <c r="F1" s="113" t="n">
         <v>5</v>
       </c>
-      <c r="F1" s="111" t="n">
+      <c r="G1" s="113" t="n">
         <v>4</v>
       </c>
-      <c r="G1" s="111" t="n">
+      <c r="H1" s="113" t="n">
         <v>3</v>
       </c>
-      <c r="H1" s="111" t="n">
+      <c r="I1" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="I1" s="111" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1" s="110" t="s">
+      <c r="J1" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="111" t="s">
+      <c r="M1" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="113" t="s">
         <v>153</v>
       </c>
-      <c r="N1" s="111" t="s">
+      <c r="O1" s="113" t="s">
         <v>154</v>
       </c>
-      <c r="O1" s="110" t="s">
+      <c r="P1" s="110" t="s">
         <v>155</v>
       </c>
-      <c r="P1" s="110"/>
       <c r="Q1" s="110"/>
       <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="112"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="114"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="119" t="s">
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="120" t="s">
+      <c r="L3" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="L3" s="120" t="s">
+      <c r="M3" s="124" t="s">
         <v>157</v>
       </c>
-      <c r="M3" s="119" t="s">
+      <c r="N3" s="123" t="s">
         <v>158</v>
       </c>
-      <c r="N3" s="119" t="s">
+      <c r="O3" s="123" t="s">
         <v>159</v>
       </c>
-      <c r="O3" s="121"/>
+      <c r="P3" s="125"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="122"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="13" t="s">
+      <c r="B4" s="126"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="127"/>
-      <c r="K4" s="128" t="s">
+      <c r="K4" s="132"/>
+      <c r="L4" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="L4" s="129"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="130"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="135"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="122" t="s">
+      <c r="B5" s="126" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="13" t="s">
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="128" t="s">
+      <c r="J5" s="13"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="133" t="s">
         <v>162</v>
       </c>
-      <c r="L5" s="129" t="s">
+      <c r="M5" s="134" t="s">
         <v>163</v>
       </c>
-      <c r="M5" s="127" t="s">
+      <c r="N5" s="132" t="s">
         <v>158</v>
       </c>
-      <c r="N5" s="127" t="s">
+      <c r="O5" s="132" t="s">
         <v>159</v>
       </c>
-      <c r="O5" s="130"/>
+      <c r="P5" s="135"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="131" t="s">
+      <c r="B6" s="136" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="135" t="s">
+      <c r="C6" s="137"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="137" t="s">
+      <c r="I6" s="139"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="143" t="s">
         <v>164</v>
       </c>
-      <c r="L6" s="137" t="s">
+      <c r="M6" s="143" t="s">
         <v>165</v>
       </c>
-      <c r="M6" s="136" t="n">
+      <c r="N6" s="142" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="136" t="s">
+      <c r="O6" s="142" t="s">
         <v>166</v>
       </c>
-      <c r="O6" s="138"/>
+      <c r="P6" s="144"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="112" t="s">
+      <c r="A7" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="145" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="140"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="144"/>
-      <c r="K7" s="145"/>
-      <c r="L7" s="145"/>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="147"/>
-      <c r="Q7" s="147"/>
-      <c r="R7" s="147"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="149"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="151"/>
+      <c r="L7" s="152"/>
+      <c r="M7" s="152"/>
+      <c r="N7" s="151"/>
+      <c r="O7" s="151"/>
+      <c r="P7" s="153"/>
+      <c r="Q7" s="154"/>
+      <c r="R7" s="154"/>
+      <c r="S7" s="154"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B8" s="122"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="148" t="s">
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+      <c r="G8" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="126"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="127"/>
-      <c r="K8" s="128" t="s">
+      <c r="H8" s="131"/>
+      <c r="I8" s="129"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="133" t="s">
         <v>169</v>
       </c>
-      <c r="L8" s="129"/>
-      <c r="M8" s="127"/>
-      <c r="N8" s="127"/>
-      <c r="O8" s="130"/>
+      <c r="M8" s="134"/>
+      <c r="N8" s="132"/>
+      <c r="O8" s="132"/>
+      <c r="P8" s="135"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="112" t="s">
+      <c r="A9" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="149" t="s">
+      <c r="B9" s="156" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="153"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="154"/>
-      <c r="J9" s="155"/>
-      <c r="K9" s="156"/>
-      <c r="L9" s="156"/>
-      <c r="M9" s="155"/>
-      <c r="N9" s="155"/>
-      <c r="O9" s="157"/>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="147"/>
-      <c r="R9" s="147"/>
+      <c r="C9" s="157" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="158"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="161"/>
+      <c r="I9" s="159"/>
+      <c r="J9" s="162"/>
+      <c r="K9" s="163"/>
+      <c r="L9" s="164"/>
+      <c r="M9" s="164"/>
+      <c r="N9" s="163"/>
+      <c r="O9" s="163"/>
+      <c r="P9" s="165"/>
+      <c r="Q9" s="154"/>
+      <c r="R9" s="154"/>
+      <c r="S9" s="154"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B10" s="131"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="148"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="136"/>
-      <c r="O10" s="130"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="155"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="132"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="143"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="135"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A11" s="112" t="s">
+      <c r="A11" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="139" t="s">
-        <v>171</v>
-      </c>
-      <c r="C11" s="150"/>
-      <c r="D11" s="151"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="152"/>
-      <c r="G11" s="153"/>
-      <c r="H11" s="151"/>
-      <c r="I11" s="154"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="156"/>
-      <c r="L11" s="145"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="147"/>
+      <c r="B11" s="145" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="146" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="158"/>
+      <c r="E11" s="159"/>
+      <c r="F11" s="159"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="159"/>
+      <c r="J11" s="162"/>
+      <c r="K11" s="163"/>
+      <c r="L11" s="164"/>
+      <c r="M11" s="152"/>
+      <c r="N11" s="151"/>
+      <c r="O11" s="151"/>
+      <c r="P11" s="165"/>
+      <c r="Q11" s="154"/>
+      <c r="R11" s="154"/>
+      <c r="S11" s="154"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B12" s="122"/>
-      <c r="C12" s="123"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="148"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="129" t="s">
+      <c r="B12" s="126"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="127" t="n">
+      <c r="N12" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="N12" s="127" t="s">
+      <c r="O12" s="132" t="s">
         <v>166</v>
       </c>
-      <c r="O12" s="130"/>
+      <c r="P12" s="135"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B13" s="122"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="13" t="s">
+      <c r="B13" s="126"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="125"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="129" t="s">
-        <v>172</v>
-      </c>
-      <c r="L13" s="129" t="s">
-        <v>173</v>
-      </c>
-      <c r="M13" s="127" t="n">
+      <c r="G13" s="130"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="134" t="s">
+        <v>174</v>
+      </c>
+      <c r="M13" s="134" t="s">
+        <v>175</v>
+      </c>
+      <c r="N13" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="N13" s="127" t="s">
+      <c r="O13" s="132" t="s">
+        <v>176</v>
+      </c>
+      <c r="P13" s="135" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B14" s="126" t="s">
         <v>174</v>
       </c>
-      <c r="O13" s="130" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B14" s="122" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" s="123"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129" t="s">
-        <v>176</v>
-      </c>
-      <c r="M14" s="127" t="s">
+      <c r="C14" s="127"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134" t="s">
+        <v>178</v>
+      </c>
+      <c r="N14" s="132" t="s">
         <v>158</v>
       </c>
-      <c r="N14" s="127" t="s">
-        <v>177</v>
-      </c>
-      <c r="O14" s="130"/>
+      <c r="O14" s="132" t="s">
+        <v>179</v>
+      </c>
+      <c r="P14" s="135"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B15" s="131"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="133" t="s">
+      <c r="B15" s="136"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="166"/>
+      <c r="E15" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="159"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="159"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="137" t="s">
-        <v>178</v>
-      </c>
-      <c r="L15" s="137" t="s">
+      <c r="F15" s="167"/>
+      <c r="G15" s="168"/>
+      <c r="H15" s="169"/>
+      <c r="I15" s="167"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="143" t="s">
+        <v>180</v>
+      </c>
+      <c r="M15" s="143" t="s">
         <v>118</v>
       </c>
-      <c r="M15" s="136" t="s">
+      <c r="N15" s="142" t="s">
         <v>158</v>
       </c>
-      <c r="N15" s="136" t="s">
-        <v>179</v>
-      </c>
-      <c r="O15" s="138"/>
+      <c r="O15" s="142" t="s">
+        <v>181</v>
+      </c>
+      <c r="P15" s="144"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="112" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="139" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="162"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="163"/>
-      <c r="F16" s="164"/>
-      <c r="G16" s="165"/>
-      <c r="H16" s="163"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="145"/>
-      <c r="L16" s="145"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="146"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
+      <c r="A16" s="114" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="145" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="146"/>
+      <c r="D16" s="170"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="172"/>
+      <c r="H16" s="173"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="151"/>
+      <c r="L16" s="152"/>
+      <c r="M16" s="152"/>
+      <c r="N16" s="151"/>
+      <c r="O16" s="151"/>
+      <c r="P16" s="153"/>
+      <c r="Q16" s="154"/>
+      <c r="R16" s="154"/>
+      <c r="S16" s="154"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B17" s="122"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="126"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="128" t="s">
-        <v>181</v>
-      </c>
-      <c r="L17" s="128"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="130"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="131"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="M17" s="133"/>
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
+      <c r="P17" s="135"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B18" s="122"/>
-      <c r="C18" s="123"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="125" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="126"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="128" t="s">
-        <v>182</v>
-      </c>
-      <c r="L18" s="128"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="127"/>
-      <c r="O18" s="130"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="128"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="131"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="133" t="s">
+        <v>184</v>
+      </c>
+      <c r="M18" s="133"/>
+      <c r="N18" s="132"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="135"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B19" s="122"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="124" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="126"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="128" t="s">
+      <c r="B19" s="126"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="131"/>
+      <c r="I19" s="129"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="133" t="s">
+        <v>185</v>
+      </c>
+      <c r="M19" s="133"/>
+      <c r="N19" s="132"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="135"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A20" s="114" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="156" t="s">
         <v>183</v>
       </c>
-      <c r="L19" s="128"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="127"/>
-      <c r="O19" s="130"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="112" t="s">
+      <c r="C20" s="157" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" s="158"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="159"/>
+      <c r="J20" s="162"/>
+      <c r="K20" s="163"/>
+      <c r="L20" s="164"/>
+      <c r="M20" s="164"/>
+      <c r="N20" s="163"/>
+      <c r="O20" s="163"/>
+      <c r="P20" s="165"/>
+      <c r="Q20" s="154"/>
+      <c r="R20" s="154"/>
+      <c r="S20" s="154"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B21" s="126"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133" t="s">
+        <v>188</v>
+      </c>
+      <c r="N21" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="132" t="s">
+        <v>188</v>
+      </c>
+      <c r="P21" s="135" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A22" s="114" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="156" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="149" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="150"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="166"/>
-      <c r="G20" s="153"/>
-      <c r="H20" s="151"/>
-      <c r="I20" s="154"/>
-      <c r="J20" s="155"/>
-      <c r="K20" s="156"/>
-      <c r="L20" s="156"/>
-      <c r="M20" s="155"/>
-      <c r="N20" s="155"/>
-      <c r="O20" s="157"/>
-      <c r="P20" s="147"/>
-      <c r="Q20" s="147"/>
-      <c r="R20" s="147"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B21" s="122"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="125"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="124"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="128" t="s">
+      <c r="C22" s="157" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="158"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="159"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="159"/>
+      <c r="J22" s="162"/>
+      <c r="K22" s="163"/>
+      <c r="L22" s="164"/>
+      <c r="M22" s="164"/>
+      <c r="N22" s="163"/>
+      <c r="O22" s="163"/>
+      <c r="P22" s="165"/>
+      <c r="Q22" s="154"/>
+      <c r="R22" s="154"/>
+      <c r="S22" s="154"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B23" s="126"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="134" t="s">
+        <v>192</v>
+      </c>
+      <c r="N23" s="132" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" s="132" t="s">
+        <v>166</v>
+      </c>
+      <c r="P23" s="175" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B24" s="126"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="129"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="134" t="s">
+        <v>194</v>
+      </c>
+      <c r="M24" s="134" t="s">
+        <v>195</v>
+      </c>
+      <c r="N24" s="132" t="s">
+        <v>196</v>
+      </c>
+      <c r="O24" s="132" t="s">
+        <v>197</v>
+      </c>
+      <c r="P24" s="175" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B25" s="126" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="129"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="134" t="s">
+        <v>199</v>
+      </c>
+      <c r="N25" s="132" t="s">
+        <v>158</v>
+      </c>
+      <c r="O25" s="132" t="s">
+        <v>200</v>
+      </c>
+      <c r="P25" s="175" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B26" s="136" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="137"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="168"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="167"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="143"/>
+      <c r="M26" s="143" t="s">
+        <v>199</v>
+      </c>
+      <c r="N26" s="142" t="s">
+        <v>158</v>
+      </c>
+      <c r="O26" s="142" t="s">
+        <v>200</v>
+      </c>
+      <c r="P26" s="176" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A27" s="114" t="s">
+        <v>204</v>
+      </c>
+      <c r="B27" s="156" t="s">
         <v>185</v>
       </c>
-      <c r="M21" s="127" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="127" t="s">
-        <v>185</v>
-      </c>
-      <c r="O21" s="130" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="112" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="149" t="s">
+      <c r="C27" s="157" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="158"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="159"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="159"/>
+      <c r="J27" s="162"/>
+      <c r="K27" s="163"/>
+      <c r="L27" s="164"/>
+      <c r="M27" s="164"/>
+      <c r="N27" s="163"/>
+      <c r="O27" s="163"/>
+      <c r="P27" s="165"/>
+      <c r="Q27" s="154"/>
+      <c r="R27" s="154"/>
+      <c r="S27" s="154"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B28" s="126"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="155"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="129"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="134"/>
+      <c r="M28" s="134" t="s">
+        <v>206</v>
+      </c>
+      <c r="N28" s="132" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" s="132" t="s">
+        <v>166</v>
+      </c>
+      <c r="P28" s="175" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B29" s="126"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="129"/>
+      <c r="F29" s="129"/>
+      <c r="G29" s="155"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="129"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="134" t="s">
+        <v>199</v>
+      </c>
+      <c r="N29" s="132" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="132" t="s">
+        <v>200</v>
+      </c>
+      <c r="P29" s="175" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A30" s="114" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" s="156" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="158"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="159"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="159"/>
+      <c r="J30" s="162"/>
+      <c r="K30" s="163"/>
+      <c r="L30" s="164"/>
+      <c r="M30" s="164"/>
+      <c r="N30" s="163"/>
+      <c r="O30" s="163"/>
+      <c r="P30" s="165"/>
+      <c r="Q30" s="154"/>
+      <c r="R30" s="154"/>
+      <c r="S30" s="154"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B31" s="126"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="128"/>
+      <c r="E31" s="107" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="129"/>
+      <c r="G31" s="130"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="133" t="s">
+        <v>210</v>
+      </c>
+      <c r="N31" s="132" t="s">
+        <v>158</v>
+      </c>
+      <c r="O31" s="132" t="s">
+        <v>159</v>
+      </c>
+      <c r="P31" s="135" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B32" s="177"/>
+      <c r="C32" s="178"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="167"/>
+      <c r="G32" s="168"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="167"/>
+      <c r="J32" s="139"/>
+      <c r="K32" s="142"/>
+      <c r="L32" s="143"/>
+      <c r="M32" s="143" t="s">
         <v>188</v>
       </c>
-      <c r="C22" s="150"/>
-      <c r="D22" s="154"/>
-      <c r="E22" s="151"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="151"/>
-      <c r="I22" s="154"/>
-      <c r="J22" s="155"/>
-      <c r="K22" s="156"/>
-      <c r="L22" s="156"/>
-      <c r="M22" s="155"/>
-      <c r="N22" s="155"/>
-      <c r="O22" s="157"/>
-      <c r="P22" s="147"/>
-      <c r="Q22" s="147"/>
-      <c r="R22" s="147"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B23" s="122"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="107" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="124"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="128"/>
-      <c r="L23" s="128" t="s">
+      <c r="N32" s="142" t="s">
+        <v>158</v>
+      </c>
+      <c r="O32" s="142" t="s">
+        <v>188</v>
+      </c>
+      <c r="P32" s="179" t="s">
         <v>189</v>
       </c>
-      <c r="M23" s="127" t="s">
-        <v>158</v>
-      </c>
-      <c r="N23" s="127" t="s">
-        <v>159</v>
-      </c>
-      <c r="O23" s="130" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B24" s="122"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="127"/>
-      <c r="K24" s="128"/>
-      <c r="L24" s="128" t="s">
-        <v>185</v>
-      </c>
-      <c r="M24" s="127" t="s">
-        <v>158</v>
-      </c>
-      <c r="N24" s="127" t="s">
-        <v>185</v>
-      </c>
-      <c r="O24" s="130" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A25" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="B25" s="149" t="s">
-        <v>183</v>
-      </c>
-      <c r="C25" s="150"/>
-      <c r="D25" s="154"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="166"/>
-      <c r="G25" s="153"/>
-      <c r="H25" s="151"/>
-      <c r="I25" s="154"/>
-      <c r="J25" s="155"/>
-      <c r="K25" s="156"/>
-      <c r="L25" s="156"/>
-      <c r="M25" s="155"/>
-      <c r="N25" s="155"/>
-      <c r="O25" s="157"/>
-      <c r="P25" s="147"/>
-      <c r="Q25" s="147"/>
-      <c r="R25" s="147"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B26" s="122"/>
-      <c r="C26" s="123"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="124"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="127"/>
-      <c r="K26" s="129"/>
-      <c r="L26" s="129" t="s">
-        <v>192</v>
-      </c>
-      <c r="M26" s="127" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" s="127" t="s">
-        <v>166</v>
-      </c>
-      <c r="O26" s="167" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B27" s="122"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="124"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="127"/>
-      <c r="K27" s="129"/>
-      <c r="L27" s="129" t="s">
-        <v>194</v>
-      </c>
-      <c r="M27" s="127" t="s">
-        <v>158</v>
-      </c>
-      <c r="N27" s="127" t="s">
-        <v>195</v>
-      </c>
-      <c r="O27" s="167" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="112" t="s">
-        <v>197</v>
-      </c>
-      <c r="B28" s="149" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" s="150"/>
-      <c r="D28" s="154"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="166"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="151"/>
-      <c r="I28" s="154"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="156"/>
-      <c r="L28" s="156"/>
-      <c r="M28" s="155"/>
-      <c r="N28" s="155"/>
-      <c r="O28" s="157"/>
-      <c r="P28" s="147"/>
-      <c r="Q28" s="147"/>
-      <c r="R28" s="147"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B29" s="122"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="124"/>
-      <c r="F29" s="125"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="124"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="129" t="s">
-        <v>198</v>
-      </c>
-      <c r="M29" s="127" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" s="127" t="s">
-        <v>166</v>
-      </c>
-      <c r="O29" s="167" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B30" s="122"/>
-      <c r="C30" s="123"/>
-      <c r="D30" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="124"/>
-      <c r="F30" s="125"/>
-      <c r="G30" s="126"/>
-      <c r="H30" s="124"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="129" t="s">
-        <v>200</v>
-      </c>
-      <c r="L30" s="129" t="s">
-        <v>201</v>
-      </c>
-      <c r="M30" s="127" t="s">
-        <v>202</v>
-      </c>
-      <c r="N30" s="127" t="s">
-        <v>203</v>
-      </c>
-      <c r="O30" s="167" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B31" s="122" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="123"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="125"/>
-      <c r="G31" s="126"/>
-      <c r="H31" s="124"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="127"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="129" t="s">
-        <v>194</v>
-      </c>
-      <c r="M31" s="127" t="s">
-        <v>158</v>
-      </c>
-      <c r="N31" s="127" t="s">
-        <v>195</v>
-      </c>
-      <c r="O31" s="167" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B32" s="131" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="158"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="159"/>
-      <c r="F32" s="160"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="159"/>
-      <c r="I32" s="133"/>
-      <c r="J32" s="136"/>
-      <c r="K32" s="137"/>
-      <c r="L32" s="137" t="s">
-        <v>194</v>
-      </c>
-      <c r="M32" s="136" t="s">
-        <v>158</v>
-      </c>
-      <c r="N32" s="136" t="s">
-        <v>195</v>
-      </c>
-      <c r="O32" s="168" t="s">
-        <v>196</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="129"/>
-      <c r="C33" s="13"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="180"/>
       <c r="D33" s="13"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="124"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="124"/>
-      <c r="I33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="129"/>
+      <c r="G33" s="129"/>
+      <c r="H33" s="129"/>
+      <c r="I33" s="129"/>
       <c r="J33" s="13"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="129"/>
-      <c r="M33" s="129"/>
-      <c r="N33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="134"/>
+      <c r="M33" s="134"/>
+      <c r="N33" s="134"/>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
-      <c r="Q33" s="129"/>
-      <c r="R33" s="129"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="134"/>
+      <c r="S33" s="134"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="169" t="s">
+      <c r="B34" s="181" t="s">
         <v>154</v>
       </c>
-      <c r="C34" s="124"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="124"/>
-      <c r="I34" s="13"/>
+      <c r="C34" s="182"/>
+      <c r="D34" s="129"/>
+      <c r="E34" s="129"/>
+      <c r="F34" s="129"/>
+      <c r="G34" s="129"/>
+      <c r="H34" s="129"/>
+      <c r="I34" s="129"/>
       <c r="J34" s="13"/>
-      <c r="K34" s="169"/>
-      <c r="L34" s="169"/>
-      <c r="M34" s="169"/>
-      <c r="N34" s="107"/>
-      <c r="O34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="181"/>
+      <c r="M34" s="181"/>
+      <c r="N34" s="181"/>
+      <c r="O34" s="107"/>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
-      <c r="R34" s="129"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="134"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="170" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="171" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="183" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" s="184" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="172"/>
-      <c r="D39" s="172"/>
-      <c r="E39" s="173"/>
-      <c r="F39" s="173"/>
-      <c r="G39" s="172" t="s">
+      <c r="C39" s="185"/>
+      <c r="D39" s="186"/>
+      <c r="E39" s="186"/>
+      <c r="F39" s="187"/>
+      <c r="G39" s="187"/>
+      <c r="H39" s="186" t="s">
         <v>168</v>
       </c>
-      <c r="H39" s="173" t="s">
+      <c r="I39" s="187" t="s">
         <v>162</v>
       </c>
-      <c r="I39" s="173" t="s">
+      <c r="J39" s="187" t="s">
         <v>160</v>
       </c>
-      <c r="J39" s="173" t="s">
+      <c r="K39" s="187" t="s">
         <v>156</v>
       </c>
-      <c r="K39" s="171" t="s">
-        <v>210</v>
-      </c>
-      <c r="L39" s="174" t="s">
-        <v>211</v>
-      </c>
-      <c r="M39" s="170" t="s">
-        <v>212</v>
-      </c>
-      <c r="N39" s="171"/>
-      <c r="O39" s="170"/>
-      <c r="P39" s="170"/>
-      <c r="Q39" s="170"/>
-      <c r="R39" s="170"/>
+      <c r="L39" s="184" t="s">
+        <v>215</v>
+      </c>
+      <c r="M39" s="188" t="s">
+        <v>216</v>
+      </c>
+      <c r="N39" s="183" t="s">
+        <v>217</v>
+      </c>
+      <c r="O39" s="184"/>
+      <c r="P39" s="183"/>
+      <c r="Q39" s="183"/>
+      <c r="R39" s="183"/>
+      <c r="S39" s="183"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="175"/>
+      <c r="A40" s="189"/>
       <c r="B40" s="2" t="str">
-        <f aca="false">DEC2HEX(C40,2)</f>
-        <v>00</v>
-      </c>
-      <c r="C40" s="176"/>
-      <c r="D40" s="177"/>
-      <c r="E40" s="177"/>
-      <c r="F40" s="178"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="177"/>
-      <c r="I40" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="180" t="s">
+        <f aca="false">DEC2HEX(L40,2)</f>
+        <v>02</v>
+      </c>
+      <c r="D40" s="190"/>
+      <c r="E40" s="191"/>
+      <c r="F40" s="191"/>
+      <c r="G40" s="192"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="191"/>
+      <c r="J40" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="194" t="s">
         <v>68</v>
       </c>
-      <c r="K40" s="2" t="n">
-        <f aca="false">IF(C40=1,128,0)+IF(D40=1,64,0)+IF(E40=1,32,0)+IF(F40=1,16,0)+IF(G40=1,8,0)+IF(H40=1,4,0)+IF(I40=1,2,0)+IF(J40=1,1,0)</f>
+      <c r="L40" s="2" t="n">
+        <f aca="false">IF(D40=1,128,0)+IF(E40=1,64,0)+IF(F40=1,32,0)+IF(G40=1,16,0)+IF(H40=1,8,0)+IF(I40=1,4,0)+IF(J40=1,2,0)+IF(K40=1,1,0)</f>
         <v>2</v>
       </c>
-      <c r="L40" s="10" t="s">
+      <c r="M40" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="M40" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="O40" s="11"/>
+      <c r="N40" s="11" t="s">
+        <v>218</v>
+      </c>
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="175"/>
+      <c r="A41" s="189"/>
       <c r="B41" s="2" t="str">
-        <f aca="false">DEC2HEX(C41,2)</f>
-        <v>00</v>
-      </c>
-      <c r="C41" s="181"/>
-      <c r="D41" s="13"/>
+        <f aca="false">DEC2HEX(L41,2)</f>
+        <v>08</v>
+      </c>
+      <c r="D41" s="195"/>
       <c r="E41" s="13"/>
-      <c r="F41" s="148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="182" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="13" t="s">
+      <c r="F41" s="13"/>
+      <c r="G41" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="196" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="127" t="s">
+      <c r="J41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="K41" s="2" t="n">
-        <f aca="false">IF(C41=1,128,0)+IF(D41=1,64,0)+IF(E41=1,32,0)+IF(F41=1,16,0)+IF(G41=1,8,0)+IF(H41=1,4,0)+IF(I41=1,2,0)+IF(J41=1,1,0)</f>
+      <c r="L41" s="2" t="n">
+        <f aca="false">IF(D41=1,128,0)+IF(E41=1,64,0)+IF(F41=1,32,0)+IF(G41=1,16,0)+IF(H41=1,8,0)+IF(I41=1,4,0)+IF(J41=1,2,0)+IF(K41=1,1,0)</f>
         <v>8</v>
       </c>
-      <c r="L41" s="10" t="s">
+      <c r="M41" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="M41" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="O41" s="11"/>
+      <c r="N41" s="11" t="s">
+        <v>219</v>
+      </c>
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="175"/>
+      <c r="A42" s="189"/>
       <c r="B42" s="2" t="str">
-        <f aca="false">DEC2HEX(C42,2)</f>
-        <v>00</v>
-      </c>
-      <c r="C42" s="181"/>
-      <c r="D42" s="13" t="s">
-        <v>68</v>
-      </c>
+        <f aca="false">DEC2HEX(L42,2)</f>
+        <v>18</v>
+      </c>
+      <c r="D42" s="195"/>
       <c r="E42" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F42" s="148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="182" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="13" t="s">
+      <c r="F42" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="127" t="s">
+      <c r="G42" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="196" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="K42" s="2" t="n">
-        <f aca="false">IF(C42=1,128,0)+IF(D42=1,64,0)+IF(E42=1,32,0)+IF(F42=1,16,0)+IF(G42=1,8,0)+IF(H42=1,4,0)+IF(I42=1,2,0)+IF(J42=1,1,0)</f>
+      <c r="J42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="132" t="s">
+        <v>68</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <f aca="false">IF(D42=1,128,0)+IF(E42=1,64,0)+IF(F42=1,32,0)+IF(G42=1,16,0)+IF(H42=1,8,0)+IF(I42=1,4,0)+IF(J42=1,2,0)+IF(K42=1,1,0)</f>
         <v>24</v>
       </c>
-      <c r="L42" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="M42" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="O42" s="11"/>
+      <c r="M42" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="N42" s="11" t="s">
+        <v>220</v>
+      </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="175"/>
+      <c r="A43" s="189"/>
       <c r="B43" s="2" t="str">
-        <f aca="false">DEC2HEX(C43,2)</f>
+        <f aca="false">DEC2HEX(L43,2)</f>
         <v>00</v>
       </c>
-      <c r="C43" s="181"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="182" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="13" t="s">
+      <c r="D43" s="195"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="127" t="s">
+      <c r="J43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="K43" s="2" t="n">
-        <f aca="false">IF(C43=1,128,0)+IF(D43=1,64,0)+IF(E43=1,32,0)+IF(F43=1,16,0)+IF(G43=1,8,0)+IF(H43=1,4,0)+IF(I43=1,2,0)+IF(J43=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="M43" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="O43" s="11"/>
+      <c r="L43" s="2" t="n">
+        <f aca="false">IF(D43=1,128,0)+IF(E43=1,64,0)+IF(F43=1,32,0)+IF(G43=1,16,0)+IF(H43=1,8,0)+IF(I43=1,4,0)+IF(J43=1,2,0)+IF(K43=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="N43" s="11" t="s">
+        <v>222</v>
+      </c>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="175"/>
+      <c r="A44" s="189"/>
       <c r="B44" s="2" t="str">
-        <f aca="false">DEC2HEX(C44,2)</f>
-        <v>00</v>
-      </c>
-      <c r="C44" s="181"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="182" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="13" t="s">
+        <f aca="false">DEC2HEX(L44,2)</f>
+        <v>10</v>
+      </c>
+      <c r="D44" s="195"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="127" t="s">
+      <c r="J44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="K44" s="2" t="n">
-        <f aca="false">IF(C44=1,128,0)+IF(D44=1,64,0)+IF(E44=1,32,0)+IF(F44=1,16,0)+IF(G44=1,8,0)+IF(H44=1,4,0)+IF(I44=1,2,0)+IF(J44=1,1,0)</f>
+      <c r="L44" s="2" t="n">
+        <f aca="false">IF(D44=1,128,0)+IF(E44=1,64,0)+IF(F44=1,32,0)+IF(G44=1,16,0)+IF(H44=1,8,0)+IF(I44=1,4,0)+IF(J44=1,2,0)+IF(K44=1,1,0)</f>
         <v>16</v>
       </c>
-      <c r="L44" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="M44" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="O44" s="11"/>
+      <c r="M44" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="N44" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="O44" s="0"/>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="175"/>
+      <c r="A45" s="189"/>
       <c r="B45" s="2" t="str">
-        <f aca="false">DEC2HEX(C45,2)</f>
-        <v>00</v>
-      </c>
-      <c r="C45" s="181"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="182" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="13" t="s">
+        <f aca="false">DEC2HEX(L45,2)</f>
+        <v>20</v>
+      </c>
+      <c r="D45" s="195"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="127" t="s">
+      <c r="J45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="K45" s="2" t="n">
-        <f aca="false">IF(C45=1,128,0)+IF(D45=1,64,0)+IF(E45=1,32,0)+IF(F45=1,16,0)+IF(G45=1,8,0)+IF(H45=1,4,0)+IF(I45=1,2,0)+IF(J45=1,1,0)</f>
+      <c r="L45" s="2" t="n">
+        <f aca="false">IF(D45=1,128,0)+IF(E45=1,64,0)+IF(F45=1,32,0)+IF(G45=1,16,0)+IF(H45=1,8,0)+IF(I45=1,4,0)+IF(J45=1,2,0)+IF(K45=1,1,0)</f>
         <v>32</v>
       </c>
-      <c r="L45" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="M45" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="O45" s="11"/>
+      <c r="M45" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="N45" s="11" t="s">
+        <v>224</v>
+      </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="175"/>
+      <c r="A46" s="189"/>
       <c r="B46" s="2" t="str">
-        <f aca="false">DEC2HEX(C46,2)</f>
+        <f aca="false">DEC2HEX(L46,2)</f>
         <v>00</v>
       </c>
-      <c r="C46" s="183"/>
-      <c r="D46" s="133" t="s">
+      <c r="D46" s="197"/>
+      <c r="E46" s="139" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="133" t="s">
+      <c r="F46" s="139" t="s">
         <v>68</v>
       </c>
-      <c r="I46" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="136" t="s">
+      <c r="G46" s="140" t="s">
         <v>68</v>
       </c>
-      <c r="K46" s="2" t="n">
-        <f aca="false">IF(C46=1,128,0)+IF(D46=1,64,0)+IF(E46=1,32,0)+IF(F46=1,16,0)+IF(G46=1,8,0)+IF(H46=1,4,0)+IF(I46=1,2,0)+IF(J46=1,1,0)</f>
-        <v>48</v>
-      </c>
-      <c r="L46" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="O46" s="11"/>
+      <c r="H46" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="139" t="s">
+        <v>68</v>
+      </c>
+      <c r="J46" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="142" t="s">
+        <v>68</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <f aca="false">IF(D46=1,128,0)+IF(E46=1,64,0)+IF(F46=1,32,0)+IF(G46=1,16,0)+IF(H46=1,8,0)+IF(I46=1,4,0)+IF(J46=1,2,0)+IF(K46=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>225</v>
+      </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
-    </row>
+      <c r="S46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M47" s="0"/>
+      <c r="N47" s="0"/>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7460,8 +7585,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="184"/>
-      <c r="B1" s="185" t="s">
+      <c r="A1" s="198"/>
+      <c r="B1" s="199" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="17" t="s">
@@ -7473,10 +7598,10 @@
       <c r="E1" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="186" t="n">
+      <c r="F1" s="200" t="n">
         <v>6</v>
       </c>
-      <c r="G1" s="186" t="n">
+      <c r="G1" s="200" t="n">
         <v>5</v>
       </c>
       <c r="H1" s="27" t="n">
@@ -7485,96 +7610,96 @@
       <c r="I1" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J1" s="186" t="n">
+      <c r="J1" s="200" t="n">
         <v>2</v>
       </c>
-      <c r="K1" s="186" t="n">
+      <c r="K1" s="200" t="n">
         <v>1</v>
       </c>
       <c r="L1" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M1" s="187" t="s">
+      <c r="M1" s="201" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="187" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="188" t="s">
+      <c r="N1" s="201" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="202" t="s">
         <v>153</v>
       </c>
-      <c r="P1" s="189" t="s">
+      <c r="P1" s="203" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="190" t="s">
-        <v>221</v>
-      </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="192" t="str">
+      <c r="A2" s="204" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="205"/>
+      <c r="C2" s="206" t="str">
         <f aca="false">DEC2HEX(D2,2)</f>
         <v>00</v>
       </c>
-      <c r="D2" s="154" t="n">
+      <c r="D2" s="162" t="n">
         <f aca="false">IF(E2=1,128,0)+IF(F2=1,64,0)+IF(G2=1,32,0)+IF(H2=1,16,0)+IF(I2=1,8,0)+IF(J2=1,4,0)+IF(K2=1,2,0)+IF(L2=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E2" s="193"/>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="193" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="194" t="s">
-        <v>222</v>
-      </c>
-      <c r="N2" s="191"/>
-      <c r="O2" s="195"/>
-      <c r="P2" s="196"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="208" t="s">
+        <v>227</v>
+      </c>
+      <c r="N2" s="205"/>
+      <c r="O2" s="209"/>
+      <c r="P2" s="210"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="197"/>
-      <c r="B3" s="128"/>
+      <c r="A3" s="211"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="17"/>
       <c r="D3" s="107"/>
       <c r="E3" s="49"/>
       <c r="F3" s="107"/>
       <c r="G3" s="107" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="13"/>
       <c r="K3" s="107"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198" t="s">
-        <v>224</v>
-      </c>
-      <c r="O3" s="199" t="s">
-        <v>225</v>
-      </c>
-      <c r="P3" s="200"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="212" t="s">
+        <v>229</v>
+      </c>
+      <c r="O3" s="213" t="s">
+        <v>230</v>
+      </c>
+      <c r="P3" s="214"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="197"/>
-      <c r="B4" s="128"/>
+      <c r="A4" s="211"/>
+      <c r="B4" s="133"/>
       <c r="E4" s="49"/>
       <c r="F4" s="107" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G4" s="107"/>
       <c r="H4" s="50"/>
@@ -7582,20 +7707,20 @@
       <c r="J4" s="13"/>
       <c r="K4" s="107"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="198" t="s">
-        <v>227</v>
+      <c r="M4" s="212" t="s">
+        <v>232</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
-      <c r="P4" s="201"/>
+      <c r="P4" s="215"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="197"/>
-      <c r="B5" s="128"/>
+      <c r="A5" s="211"/>
+      <c r="B5" s="133"/>
       <c r="C5" s="17"/>
       <c r="D5" s="107"/>
       <c r="E5" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F5" s="107"/>
       <c r="G5" s="107"/>
@@ -7604,16 +7729,16 @@
       <c r="J5" s="13"/>
       <c r="K5" s="107"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O5" s="199"/>
-      <c r="P5" s="200"/>
+      <c r="M5" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O5" s="213"/>
+      <c r="P5" s="214"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A6" s="197"/>
-      <c r="B6" s="128" t="s">
-        <v>229</v>
+      <c r="A6" s="211"/>
+      <c r="B6" s="133" t="s">
+        <v>234</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="107"/>
@@ -7623,86 +7748,86 @@
       <c r="J6" s="13"/>
       <c r="K6" s="107"/>
       <c r="L6" s="50"/>
-      <c r="M6" s="198"/>
+      <c r="M6" s="212"/>
       <c r="N6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="P6" s="201"/>
+        <v>235</v>
+      </c>
+      <c r="P6" s="215"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="190" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="191"/>
-      <c r="C7" s="192" t="str">
+      <c r="A7" s="204" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="205"/>
+      <c r="C7" s="206" t="str">
         <f aca="false">DEC2HEX(D7,2)</f>
         <v>01</v>
       </c>
-      <c r="D7" s="154" t="n">
+      <c r="D7" s="162" t="n">
         <f aca="false">IF(E7=1,128,0)+IF(F7=1,64,0)+IF(G7=1,32,0)+IF(H7=1,16,0)+IF(I7=1,8,0)+IF(J7=1,4,0)+IF(K7=1,2,0)+IF(L7=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="193"/>
-      <c r="F7" s="154"/>
-      <c r="G7" s="154"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="193" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="194" t="s">
-        <v>232</v>
-      </c>
-      <c r="N7" s="191"/>
-      <c r="O7" s="194"/>
-      <c r="P7" s="196"/>
+      <c r="E7" s="207"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="163"/>
+      <c r="I7" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="208" t="s">
+        <v>237</v>
+      </c>
+      <c r="N7" s="205"/>
+      <c r="O7" s="208"/>
+      <c r="P7" s="210"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="197"/>
-      <c r="B8" s="128"/>
+      <c r="A8" s="211"/>
+      <c r="B8" s="133"/>
       <c r="C8" s="17"/>
       <c r="D8" s="107"/>
       <c r="E8" s="49"/>
       <c r="F8" s="107"/>
       <c r="G8" s="107" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I8" s="49"/>
       <c r="J8" s="13"/>
       <c r="K8" s="107"/>
       <c r="L8" s="50"/>
-      <c r="M8" s="198"/>
+      <c r="M8" s="212"/>
       <c r="N8" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O8" s="199" t="s">
-        <v>225</v>
-      </c>
-      <c r="P8" s="200" t="s">
-        <v>233</v>
+        <v>229</v>
+      </c>
+      <c r="O8" s="213" t="s">
+        <v>230</v>
+      </c>
+      <c r="P8" s="214" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="197"/>
-      <c r="B9" s="128"/>
+      <c r="A9" s="211"/>
+      <c r="B9" s="133"/>
       <c r="C9" s="17"/>
       <c r="D9" s="107"/>
       <c r="E9" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F9" s="107"/>
       <c r="G9" s="107"/>
@@ -7711,22 +7836,22 @@
       <c r="J9" s="13"/>
       <c r="K9" s="107"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O9" s="199"/>
-      <c r="P9" s="200"/>
+      <c r="M9" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O9" s="213"/>
+      <c r="P9" s="214"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="197"/>
-      <c r="B10" s="128" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="202"/>
+      <c r="A10" s="211"/>
+      <c r="B10" s="133" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="216"/>
       <c r="F10" s="107"/>
       <c r="G10" s="107"/>
       <c r="H10" s="50"/>
-      <c r="I10" s="202"/>
+      <c r="I10" s="216"/>
       <c r="J10" s="107"/>
       <c r="K10" s="107"/>
       <c r="L10" s="50"/>
@@ -7735,81 +7860,81 @@
         <v>1</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="P10" s="201"/>
+        <v>235</v>
+      </c>
+      <c r="P10" s="215"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="190" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="191"/>
-      <c r="C11" s="192" t="str">
+      <c r="A11" s="204" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="205"/>
+      <c r="C11" s="206" t="str">
         <f aca="false">DEC2HEX(D11,2)</f>
         <v>02</v>
       </c>
-      <c r="D11" s="154" t="n">
+      <c r="D11" s="162" t="n">
         <f aca="false">IF(E11=1,128,0)+IF(F11=1,64,0)+IF(G11=1,32,0)+IF(H11=1,16,0)+IF(I11=1,8,0)+IF(J11=1,4,0)+IF(K11=1,2,0)+IF(L11=1,1,0)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="193"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="194" t="s">
-        <v>235</v>
-      </c>
-      <c r="N11" s="191"/>
-      <c r="O11" s="195"/>
-      <c r="P11" s="196"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="163"/>
+      <c r="I11" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="208" t="s">
+        <v>240</v>
+      </c>
+      <c r="N11" s="205"/>
+      <c r="O11" s="209"/>
+      <c r="P11" s="210"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A12" s="197"/>
-      <c r="B12" s="128"/>
+      <c r="A12" s="211"/>
+      <c r="B12" s="133"/>
       <c r="C12" s="17"/>
       <c r="D12" s="107"/>
       <c r="E12" s="49"/>
       <c r="F12" s="107"/>
       <c r="G12" s="107" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I12" s="49"/>
       <c r="J12" s="13"/>
       <c r="K12" s="107"/>
       <c r="L12" s="50"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="198" t="s">
-        <v>236</v>
-      </c>
-      <c r="O12" s="199" t="s">
-        <v>225</v>
-      </c>
-      <c r="P12" s="203" t="s">
-        <v>237</v>
+      <c r="M12" s="212"/>
+      <c r="N12" s="212" t="s">
+        <v>241</v>
+      </c>
+      <c r="O12" s="213" t="s">
+        <v>230</v>
+      </c>
+      <c r="P12" s="217" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="197"/>
-      <c r="B13" s="128"/>
+      <c r="A13" s="211"/>
+      <c r="B13" s="133"/>
       <c r="C13" s="17"/>
       <c r="D13" s="107"/>
       <c r="E13" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F13" s="107"/>
       <c r="G13" s="107"/>
@@ -7818,16 +7943,16 @@
       <c r="J13" s="13"/>
       <c r="K13" s="107"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O13" s="199"/>
-      <c r="P13" s="200"/>
+      <c r="M13" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O13" s="213"/>
+      <c r="P13" s="214"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="197"/>
-      <c r="B14" s="128" t="s">
-        <v>229</v>
+      <c r="A14" s="211"/>
+      <c r="B14" s="133" t="s">
+        <v>234</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="107"/>
@@ -7837,60 +7962,60 @@
       <c r="J14" s="13"/>
       <c r="K14" s="107"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="198"/>
+      <c r="M14" s="212"/>
       <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="P14" s="201" t="s">
-        <v>239</v>
+        <v>243</v>
+      </c>
+      <c r="P14" s="215" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="190" t="s">
+      <c r="A15" s="204" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="191"/>
-      <c r="C15" s="192" t="str">
+      <c r="B15" s="205"/>
+      <c r="C15" s="206" t="str">
         <f aca="false">DEC2HEX(D15,2)</f>
         <v>03</v>
       </c>
-      <c r="D15" s="154" t="n">
+      <c r="D15" s="162" t="n">
         <f aca="false">IF(E15=1,128,0)+IF(F15=1,64,0)+IF(G15=1,32,0)+IF(H15=1,16,0)+IF(I15=1,8,0)+IF(J15=1,4,0)+IF(K15=1,2,0)+IF(L15=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="E15" s="193"/>
-      <c r="F15" s="154"/>
-      <c r="G15" s="154"/>
-      <c r="H15" s="155"/>
-      <c r="I15" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="194" t="s">
+      <c r="E15" s="207"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="163"/>
+      <c r="I15" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="208" t="s">
         <v>97</v>
       </c>
-      <c r="N15" s="191"/>
-      <c r="O15" s="194"/>
-      <c r="P15" s="196"/>
+      <c r="N15" s="205"/>
+      <c r="O15" s="208"/>
+      <c r="P15" s="210"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A16" s="197"/>
-      <c r="B16" s="128"/>
+      <c r="A16" s="211"/>
+      <c r="B16" s="133"/>
       <c r="C16" s="17"/>
       <c r="D16" s="107"/>
       <c r="E16" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F16" s="107"/>
       <c r="G16" s="107"/>
@@ -7899,15 +8024,15 @@
       <c r="J16" s="13"/>
       <c r="K16" s="107"/>
       <c r="L16" s="50"/>
-      <c r="M16" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O16" s="199"/>
-      <c r="P16" s="200"/>
+      <c r="M16" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O16" s="213"/>
+      <c r="P16" s="214"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A17" s="197"/>
-      <c r="B17" s="128"/>
+      <c r="A17" s="211"/>
+      <c r="B17" s="133"/>
       <c r="C17" s="17"/>
       <c r="D17" s="107"/>
       <c r="E17" s="49"/>
@@ -7918,27 +8043,27 @@
       <c r="J17" s="13"/>
       <c r="K17" s="107"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="198"/>
+      <c r="M17" s="212"/>
       <c r="N17" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="O17" s="199" t="s">
-        <v>241</v>
-      </c>
-      <c r="P17" s="200" t="s">
-        <v>242</v>
+        <v>245</v>
+      </c>
+      <c r="O17" s="213" t="s">
+        <v>246</v>
+      </c>
+      <c r="P17" s="214" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="197"/>
-      <c r="B18" s="128" t="s">
-        <v>229</v>
-      </c>
-      <c r="E18" s="202"/>
+      <c r="A18" s="211"/>
+      <c r="B18" s="133" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18" s="216"/>
       <c r="F18" s="107"/>
       <c r="G18" s="107"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="202"/>
+      <c r="I18" s="216"/>
       <c r="J18" s="107"/>
       <c r="K18" s="107"/>
       <c r="L18" s="50"/>
@@ -7947,58 +8072,58 @@
         <v>1</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="P18" s="204" t="s">
-        <v>244</v>
+        <v>248</v>
+      </c>
+      <c r="P18" s="218" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="190" t="s">
-        <v>245</v>
-      </c>
-      <c r="B19" s="191"/>
-      <c r="C19" s="192" t="str">
+      <c r="A19" s="204" t="s">
+        <v>250</v>
+      </c>
+      <c r="B19" s="205"/>
+      <c r="C19" s="206" t="str">
         <f aca="false">DEC2HEX(D19,2)</f>
         <v>04</v>
       </c>
-      <c r="D19" s="154" t="n">
+      <c r="D19" s="162" t="n">
         <f aca="false">IF(E19=1,128,0)+IF(F19=1,64,0)+IF(G19=1,32,0)+IF(H19=1,16,0)+IF(I19=1,8,0)+IF(J19=1,4,0)+IF(K19=1,2,0)+IF(L19=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E19" s="193"/>
-      <c r="F19" s="154"/>
-      <c r="G19" s="154"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="194" t="s">
-        <v>246</v>
-      </c>
-      <c r="N19" s="191"/>
-      <c r="O19" s="194"/>
-      <c r="P19" s="196"/>
+      <c r="E19" s="207"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="163"/>
+      <c r="I19" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="208" t="s">
+        <v>251</v>
+      </c>
+      <c r="N19" s="205"/>
+      <c r="O19" s="208"/>
+      <c r="P19" s="210"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="197"/>
-      <c r="B20" s="128"/>
-      <c r="E20" s="202"/>
+      <c r="A20" s="211"/>
+      <c r="B20" s="133"/>
+      <c r="E20" s="216"/>
       <c r="F20" s="107"/>
       <c r="G20" s="107" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I20" s="107"/>
       <c r="J20" s="107"/>
@@ -8006,19 +8131,19 @@
       <c r="L20" s="50"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="P20" s="200"/>
+        <v>230</v>
+      </c>
+      <c r="P20" s="214"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="197"/>
-      <c r="B21" s="129"/>
-      <c r="E21" s="202"/>
+      <c r="A21" s="211"/>
+      <c r="B21" s="134"/>
+      <c r="E21" s="216"/>
       <c r="F21" s="107" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G21" s="107"/>
       <c r="H21" s="50"/>
@@ -8027,18 +8152,18 @@
       <c r="K21" s="107"/>
       <c r="L21" s="50"/>
       <c r="M21" s="10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N21" s="10"/>
-      <c r="O21" s="129"/>
-      <c r="P21" s="200" t="s">
-        <v>248</v>
+      <c r="O21" s="134"/>
+      <c r="P21" s="214" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="197"/>
-      <c r="B22" s="129"/>
-      <c r="E22" s="202"/>
+      <c r="A22" s="211"/>
+      <c r="B22" s="134"/>
+      <c r="E22" s="216"/>
       <c r="F22" s="107"/>
       <c r="G22" s="107"/>
       <c r="H22" s="50"/>
@@ -8048,20 +8173,20 @@
       <c r="L22" s="50"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="O22" s="129" t="s">
+        <v>254</v>
+      </c>
+      <c r="O22" s="134" t="s">
         <v>72</v>
       </c>
-      <c r="P22" s="200"/>
+      <c r="P22" s="214"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="197"/>
-      <c r="B23" s="128"/>
+      <c r="A23" s="211"/>
+      <c r="B23" s="133"/>
       <c r="C23" s="17"/>
       <c r="D23" s="107"/>
       <c r="E23" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F23" s="107"/>
       <c r="G23" s="107"/>
@@ -8070,18 +8195,18 @@
       <c r="J23" s="13"/>
       <c r="K23" s="107"/>
       <c r="L23" s="50"/>
-      <c r="M23" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O23" s="199"/>
-      <c r="P23" s="200"/>
+      <c r="M23" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O23" s="213"/>
+      <c r="P23" s="214"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="197"/>
-      <c r="B24" s="128" t="s">
-        <v>229</v>
-      </c>
-      <c r="E24" s="202"/>
+      <c r="A24" s="211"/>
+      <c r="B24" s="133" t="s">
+        <v>234</v>
+      </c>
+      <c r="E24" s="216"/>
       <c r="F24" s="107"/>
       <c r="G24" s="107"/>
       <c r="H24" s="50"/>
@@ -8092,54 +8217,54 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="P24" s="200" t="s">
-        <v>251</v>
+        <v>255</v>
+      </c>
+      <c r="P24" s="214" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="190" t="s">
-        <v>252</v>
-      </c>
-      <c r="B25" s="191"/>
-      <c r="C25" s="192" t="str">
+      <c r="A25" s="204" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" s="205"/>
+      <c r="C25" s="206" t="str">
         <f aca="false">DEC2HEX(D25,2)</f>
         <v>05</v>
       </c>
-      <c r="D25" s="154" t="n">
+      <c r="D25" s="162" t="n">
         <f aca="false">IF(E25=1,128,0)+IF(F25=1,64,0)+IF(G25=1,32,0)+IF(H25=1,16,0)+IF(I25=1,8,0)+IF(J25=1,4,0)+IF(K25=1,2,0)+IF(L25=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E25" s="193"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="154"/>
-      <c r="H25" s="155"/>
-      <c r="I25" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="194" t="s">
-        <v>253</v>
-      </c>
-      <c r="N25" s="191"/>
-      <c r="O25" s="194"/>
-      <c r="P25" s="196"/>
+      <c r="E25" s="207"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="163"/>
+      <c r="I25" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="208" t="s">
+        <v>258</v>
+      </c>
+      <c r="N25" s="205"/>
+      <c r="O25" s="208"/>
+      <c r="P25" s="210"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="197"/>
-      <c r="B26" s="129"/>
-      <c r="E26" s="202"/>
+      <c r="A26" s="211"/>
+      <c r="B26" s="134"/>
+      <c r="E26" s="216"/>
       <c r="F26" s="107" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G26" s="107"/>
       <c r="H26" s="50"/>
@@ -8148,18 +8273,18 @@
       <c r="K26" s="107"/>
       <c r="L26" s="50"/>
       <c r="M26" s="10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N26" s="10"/>
-      <c r="O26" s="129"/>
-      <c r="P26" s="200" t="s">
-        <v>254</v>
+      <c r="O26" s="134"/>
+      <c r="P26" s="214" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="197"/>
-      <c r="B27" s="129"/>
-      <c r="E27" s="202"/>
+      <c r="A27" s="211"/>
+      <c r="B27" s="134"/>
+      <c r="E27" s="216"/>
       <c r="F27" s="107"/>
       <c r="G27" s="107"/>
       <c r="H27" s="50"/>
@@ -8169,20 +8294,20 @@
       <c r="L27" s="50"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="O27" s="129" t="s">
+        <v>254</v>
+      </c>
+      <c r="O27" s="134" t="s">
         <v>72</v>
       </c>
-      <c r="P27" s="200"/>
+      <c r="P27" s="214"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="197"/>
-      <c r="B28" s="128"/>
+      <c r="A28" s="211"/>
+      <c r="B28" s="133"/>
       <c r="C28" s="17"/>
       <c r="D28" s="107"/>
       <c r="E28" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F28" s="107"/>
       <c r="G28" s="107"/>
@@ -8191,22 +8316,22 @@
       <c r="J28" s="13"/>
       <c r="K28" s="107"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O28" s="199"/>
-      <c r="P28" s="200"/>
+      <c r="M28" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O28" s="213"/>
+      <c r="P28" s="214"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="197"/>
-      <c r="B29" s="128" t="s">
-        <v>229</v>
-      </c>
-      <c r="E29" s="202"/>
+      <c r="A29" s="211"/>
+      <c r="B29" s="133" t="s">
+        <v>234</v>
+      </c>
+      <c r="E29" s="216"/>
       <c r="F29" s="107"/>
       <c r="G29" s="107"/>
       <c r="H29" s="50"/>
-      <c r="I29" s="202"/>
+      <c r="I29" s="216"/>
       <c r="J29" s="107"/>
       <c r="K29" s="107"/>
       <c r="L29" s="50"/>
@@ -8215,53 +8340,53 @@
         <v>1</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="P29" s="204" t="s">
-        <v>244</v>
+        <v>260</v>
+      </c>
+      <c r="P29" s="218" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="190" t="s">
-        <v>256</v>
-      </c>
-      <c r="B30" s="191"/>
-      <c r="C30" s="192" t="str">
+      <c r="A30" s="204" t="s">
+        <v>261</v>
+      </c>
+      <c r="B30" s="205"/>
+      <c r="C30" s="206" t="str">
         <f aca="false">DEC2HEX(D30,2)</f>
         <v>06</v>
       </c>
-      <c r="D30" s="154" t="n">
+      <c r="D30" s="162" t="n">
         <f aca="false">IF(E30=1,128,0)+IF(F30=1,64,0)+IF(G30=1,32,0)+IF(H30=1,16,0)+IF(I30=1,8,0)+IF(J30=1,4,0)+IF(K30=1,2,0)+IF(L30=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="E30" s="193"/>
-      <c r="F30" s="154"/>
-      <c r="G30" s="154"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="194" t="s">
-        <v>257</v>
-      </c>
-      <c r="N30" s="191"/>
-      <c r="O30" s="194"/>
-      <c r="P30" s="205" t="s">
-        <v>258</v>
+      <c r="E30" s="207"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="163"/>
+      <c r="I30" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="208" t="s">
+        <v>262</v>
+      </c>
+      <c r="N30" s="205"/>
+      <c r="O30" s="208"/>
+      <c r="P30" s="219" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A31" s="197"/>
-      <c r="E31" s="202"/>
+      <c r="A31" s="211"/>
+      <c r="E31" s="216"/>
       <c r="F31" s="107"/>
       <c r="G31" s="107" t="n">
         <v>0</v>
@@ -8273,14 +8398,14 @@
       <c r="J31" s="107"/>
       <c r="K31" s="107"/>
       <c r="L31" s="50"/>
-      <c r="M31" s="129" t="s">
-        <v>259</v>
-      </c>
-      <c r="P31" s="200"/>
+      <c r="M31" s="134" t="s">
+        <v>264</v>
+      </c>
+      <c r="P31" s="214"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A32" s="197"/>
-      <c r="E32" s="202"/>
+      <c r="A32" s="211"/>
+      <c r="E32" s="216"/>
       <c r="F32" s="107"/>
       <c r="G32" s="107" t="n">
         <v>0</v>
@@ -8292,14 +8417,14 @@
       <c r="J32" s="107"/>
       <c r="K32" s="107"/>
       <c r="L32" s="50"/>
-      <c r="M32" s="198" t="s">
-        <v>260</v>
-      </c>
-      <c r="P32" s="200"/>
+      <c r="M32" s="212" t="s">
+        <v>265</v>
+      </c>
+      <c r="P32" s="214"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="197"/>
-      <c r="E33" s="202"/>
+      <c r="A33" s="211"/>
+      <c r="E33" s="216"/>
       <c r="F33" s="107"/>
       <c r="G33" s="107" t="n">
         <v>1</v>
@@ -8311,14 +8436,14 @@
       <c r="J33" s="107"/>
       <c r="K33" s="107"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="198" t="s">
-        <v>261</v>
-      </c>
-      <c r="P33" s="200"/>
+      <c r="M33" s="212" t="s">
+        <v>266</v>
+      </c>
+      <c r="P33" s="214"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="197"/>
-      <c r="E34" s="202"/>
+      <c r="A34" s="211"/>
+      <c r="E34" s="216"/>
       <c r="F34" s="107"/>
       <c r="G34" s="107" t="n">
         <v>1</v>
@@ -8331,15 +8456,15 @@
       <c r="K34" s="107"/>
       <c r="L34" s="50"/>
       <c r="M34" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="P34" s="200"/>
+        <v>267</v>
+      </c>
+      <c r="P34" s="214"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="197"/>
-      <c r="E35" s="202"/>
+      <c r="A35" s="211"/>
+      <c r="E35" s="216"/>
       <c r="F35" s="107" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G35" s="107"/>
       <c r="H35" s="50"/>
@@ -8347,20 +8472,20 @@
       <c r="J35" s="107"/>
       <c r="K35" s="107"/>
       <c r="L35" s="50"/>
-      <c r="M35" s="129" t="s">
-        <v>264</v>
-      </c>
-      <c r="P35" s="200" t="s">
-        <v>265</v>
+      <c r="M35" s="134" t="s">
+        <v>269</v>
+      </c>
+      <c r="P35" s="214" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="197"/>
-      <c r="B36" s="128"/>
+      <c r="A36" s="211"/>
+      <c r="B36" s="133"/>
       <c r="C36" s="17"/>
       <c r="D36" s="107"/>
       <c r="E36" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F36" s="107"/>
       <c r="G36" s="107"/>
@@ -8369,18 +8494,18 @@
       <c r="J36" s="13"/>
       <c r="K36" s="107"/>
       <c r="L36" s="50"/>
-      <c r="M36" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O36" s="199"/>
-      <c r="P36" s="200"/>
+      <c r="M36" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O36" s="213"/>
+      <c r="P36" s="214"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="197"/>
-      <c r="B37" s="128" t="s">
-        <v>229</v>
-      </c>
-      <c r="E37" s="202"/>
+      <c r="A37" s="211"/>
+      <c r="B37" s="133" t="s">
+        <v>234</v>
+      </c>
+      <c r="E37" s="216"/>
       <c r="F37" s="107"/>
       <c r="G37" s="107"/>
       <c r="H37" s="50"/>
@@ -8388,53 +8513,53 @@
       <c r="J37" s="107"/>
       <c r="K37" s="107"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="129"/>
+      <c r="M37" s="134"/>
       <c r="O37" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="P37" s="200" t="s">
-        <v>267</v>
+        <v>271</v>
+      </c>
+      <c r="P37" s="214" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="190" t="s">
-        <v>268</v>
-      </c>
-      <c r="B38" s="191"/>
-      <c r="C38" s="192" t="str">
+      <c r="A38" s="204" t="s">
+        <v>273</v>
+      </c>
+      <c r="B38" s="205"/>
+      <c r="C38" s="206" t="str">
         <f aca="false">DEC2HEX(D38,2)</f>
         <v>07</v>
       </c>
-      <c r="D38" s="154" t="n">
+      <c r="D38" s="162" t="n">
         <f aca="false">IF(E38=1,128,0)+IF(F38=1,64,0)+IF(G38=1,32,0)+IF(H38=1,16,0)+IF(I38=1,8,0)+IF(J38=1,4,0)+IF(K38=1,2,0)+IF(L38=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="E38" s="193"/>
-      <c r="F38" s="154"/>
-      <c r="G38" s="154"/>
-      <c r="H38" s="155"/>
-      <c r="I38" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" s="194" t="s">
-        <v>269</v>
-      </c>
-      <c r="N38" s="191"/>
-      <c r="O38" s="194"/>
-      <c r="P38" s="196"/>
+      <c r="E38" s="207"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="163"/>
+      <c r="I38" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="208" t="s">
+        <v>274</v>
+      </c>
+      <c r="N38" s="205"/>
+      <c r="O38" s="208"/>
+      <c r="P38" s="210"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A39" s="197"/>
-      <c r="E39" s="202"/>
+      <c r="A39" s="211"/>
+      <c r="E39" s="216"/>
       <c r="F39" s="107"/>
       <c r="G39" s="107" t="n">
         <v>0</v>
@@ -8446,16 +8571,16 @@
       <c r="J39" s="107"/>
       <c r="K39" s="107"/>
       <c r="L39" s="50"/>
-      <c r="M39" s="129" t="s">
-        <v>270</v>
-      </c>
-      <c r="P39" s="203" t="s">
-        <v>271</v>
+      <c r="M39" s="134" t="s">
+        <v>275</v>
+      </c>
+      <c r="P39" s="217" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="197"/>
-      <c r="E40" s="202"/>
+      <c r="A40" s="211"/>
+      <c r="E40" s="216"/>
       <c r="F40" s="107"/>
       <c r="G40" s="107" t="n">
         <v>0</v>
@@ -8467,16 +8592,16 @@
       <c r="J40" s="107"/>
       <c r="K40" s="107"/>
       <c r="L40" s="50"/>
-      <c r="M40" s="198" t="s">
-        <v>260</v>
-      </c>
-      <c r="P40" s="203" t="s">
-        <v>272</v>
+      <c r="M40" s="212" t="s">
+        <v>265</v>
+      </c>
+      <c r="P40" s="217" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="197"/>
-      <c r="E41" s="202"/>
+      <c r="A41" s="211"/>
+      <c r="E41" s="216"/>
       <c r="F41" s="107"/>
       <c r="G41" s="107" t="n">
         <v>1</v>
@@ -8488,16 +8613,16 @@
       <c r="J41" s="107"/>
       <c r="K41" s="107"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="198" t="s">
-        <v>261</v>
-      </c>
-      <c r="P41" s="203" t="s">
-        <v>273</v>
+      <c r="M41" s="212" t="s">
+        <v>266</v>
+      </c>
+      <c r="P41" s="217" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="197"/>
-      <c r="E42" s="202"/>
+      <c r="A42" s="211"/>
+      <c r="E42" s="216"/>
       <c r="F42" s="107"/>
       <c r="G42" s="107" t="n">
         <v>1</v>
@@ -8510,15 +8635,15 @@
       <c r="K42" s="107"/>
       <c r="L42" s="50"/>
       <c r="M42" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="P42" s="203" t="s">
-        <v>274</v>
+        <v>267</v>
+      </c>
+      <c r="P42" s="217" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="197"/>
-      <c r="E43" s="202"/>
+      <c r="A43" s="211"/>
+      <c r="E43" s="216"/>
       <c r="F43" s="107"/>
       <c r="G43" s="107"/>
       <c r="H43" s="50"/>
@@ -8528,13 +8653,13 @@
       <c r="L43" s="50"/>
       <c r="M43" s="10"/>
       <c r="O43" s="1"/>
-      <c r="P43" s="206" t="s">
-        <v>275</v>
+      <c r="P43" s="220" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="197"/>
-      <c r="E44" s="202"/>
+      <c r="A44" s="211"/>
+      <c r="E44" s="216"/>
       <c r="F44" s="107"/>
       <c r="G44" s="107"/>
       <c r="H44" s="50"/>
@@ -8544,13 +8669,13 @@
       <c r="L44" s="50"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="206" t="s">
-        <v>276</v>
+      <c r="P44" s="220" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A45" s="197"/>
-      <c r="E45" s="202"/>
+      <c r="A45" s="211"/>
+      <c r="E45" s="216"/>
       <c r="F45" s="107"/>
       <c r="G45" s="107"/>
       <c r="H45" s="50"/>
@@ -8560,17 +8685,17 @@
       <c r="L45" s="50"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="206" t="s">
-        <v>277</v>
+      <c r="P45" s="220" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A46" s="197"/>
-      <c r="B46" s="128"/>
+      <c r="A46" s="211"/>
+      <c r="B46" s="133"/>
       <c r="C46" s="17"/>
       <c r="D46" s="107"/>
       <c r="E46" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F46" s="107"/>
       <c r="G46" s="107"/>
@@ -8579,16 +8704,16 @@
       <c r="J46" s="13"/>
       <c r="K46" s="107"/>
       <c r="L46" s="50"/>
-      <c r="M46" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O46" s="199"/>
-      <c r="P46" s="200"/>
+      <c r="M46" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O46" s="213"/>
+      <c r="P46" s="214"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="197"/>
-      <c r="B47" s="198" t="s">
-        <v>229</v>
+      <c r="A47" s="211"/>
+      <c r="B47" s="212" t="s">
+        <v>234</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="107"/>
@@ -8600,84 +8725,84 @@
       <c r="J47" s="13"/>
       <c r="K47" s="107"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="198"/>
+      <c r="M47" s="212"/>
       <c r="N47" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="O47" s="199" t="s">
-        <v>279</v>
-      </c>
-      <c r="P47" s="200"/>
+        <v>283</v>
+      </c>
+      <c r="O47" s="213" t="s">
+        <v>284</v>
+      </c>
+      <c r="P47" s="214"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="207"/>
-      <c r="B48" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="C48" s="208"/>
-      <c r="D48" s="133"/>
-      <c r="E48" s="132"/>
-      <c r="F48" s="133"/>
-      <c r="G48" s="133"/>
-      <c r="H48" s="136"/>
-      <c r="I48" s="133"/>
-      <c r="J48" s="133"/>
-      <c r="K48" s="133"/>
-      <c r="L48" s="136"/>
-      <c r="M48" s="209"/>
+      <c r="A48" s="221"/>
+      <c r="B48" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="C48" s="222"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="138"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="139"/>
+      <c r="H48" s="142"/>
+      <c r="I48" s="139"/>
+      <c r="J48" s="139"/>
+      <c r="K48" s="139"/>
+      <c r="L48" s="142"/>
+      <c r="M48" s="223"/>
       <c r="N48" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="P48" s="204" t="s">
-        <v>244</v>
+        <v>283</v>
+      </c>
+      <c r="P48" s="218" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="190" t="s">
-        <v>280</v>
-      </c>
-      <c r="B49" s="191"/>
-      <c r="C49" s="192" t="str">
+      <c r="A49" s="204" t="s">
+        <v>285</v>
+      </c>
+      <c r="B49" s="205"/>
+      <c r="C49" s="206" t="str">
         <f aca="false">DEC2HEX(D49,2)</f>
         <v>0A</v>
       </c>
-      <c r="D49" s="154" t="n">
+      <c r="D49" s="162" t="n">
         <f aca="false">IF(E49=1,128,0)+IF(F49=1,64,0)+IF(G49=1,32,0)+IF(H49=1,16,0)+IF(I49=1,8,0)+IF(J49=1,4,0)+IF(K49=1,2,0)+IF(L49=1,1,0)</f>
         <v>10</v>
       </c>
-      <c r="E49" s="193"/>
-      <c r="F49" s="154"/>
-      <c r="G49" s="154"/>
-      <c r="H49" s="155"/>
-      <c r="I49" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="194" t="s">
-        <v>281</v>
-      </c>
-      <c r="N49" s="191"/>
-      <c r="O49" s="194"/>
-      <c r="P49" s="196"/>
+      <c r="E49" s="207"/>
+      <c r="F49" s="162"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="163"/>
+      <c r="I49" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="208" t="s">
+        <v>286</v>
+      </c>
+      <c r="N49" s="205"/>
+      <c r="O49" s="208"/>
+      <c r="P49" s="210"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A50" s="197"/>
-      <c r="B50" s="128"/>
+      <c r="A50" s="211"/>
+      <c r="B50" s="133"/>
       <c r="C50" s="17"/>
       <c r="D50" s="107"/>
       <c r="E50" s="49" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F50" s="107"/>
       <c r="G50" s="107"/>
@@ -8686,18 +8811,18 @@
       <c r="J50" s="13"/>
       <c r="K50" s="107"/>
       <c r="L50" s="50"/>
-      <c r="M50" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="O50" s="199"/>
-      <c r="P50" s="200"/>
+      <c r="M50" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="O50" s="213"/>
+      <c r="P50" s="214"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="197"/>
-      <c r="B51" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="E51" s="202"/>
+      <c r="A51" s="211"/>
+      <c r="B51" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="E51" s="216"/>
       <c r="F51" s="107"/>
       <c r="G51" s="107"/>
       <c r="H51" s="50"/>
@@ -8705,57 +8830,57 @@
       <c r="J51" s="107"/>
       <c r="K51" s="107"/>
       <c r="L51" s="50"/>
-      <c r="M51" s="129"/>
+      <c r="M51" s="134"/>
       <c r="N51" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O51" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="P51" s="200" t="s">
-        <v>283</v>
+        <v>287</v>
+      </c>
+      <c r="P51" s="214" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="190" t="s">
-        <v>284</v>
-      </c>
-      <c r="B52" s="191"/>
-      <c r="C52" s="192" t="str">
+      <c r="A52" s="204" t="s">
+        <v>289</v>
+      </c>
+      <c r="B52" s="205"/>
+      <c r="C52" s="206" t="str">
         <f aca="false">DEC2HEX(D52,2)</f>
         <v>0C</v>
       </c>
-      <c r="D52" s="154" t="n">
+      <c r="D52" s="162" t="n">
         <f aca="false">IF(E52=1,128,0)+IF(F52=1,64,0)+IF(G52=1,32,0)+IF(H52=1,16,0)+IF(I52=1,8,0)+IF(J52=1,4,0)+IF(K52=1,2,0)+IF(L52=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="E52" s="193"/>
-      <c r="F52" s="154"/>
-      <c r="G52" s="154"/>
-      <c r="H52" s="155"/>
-      <c r="I52" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="191" t="s">
-        <v>285</v>
-      </c>
-      <c r="N52" s="191"/>
-      <c r="O52" s="194"/>
-      <c r="P52" s="196"/>
+      <c r="E52" s="207"/>
+      <c r="F52" s="162"/>
+      <c r="G52" s="162"/>
+      <c r="H52" s="163"/>
+      <c r="I52" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="205" t="s">
+        <v>290</v>
+      </c>
+      <c r="N52" s="205"/>
+      <c r="O52" s="208"/>
+      <c r="P52" s="210"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="197"/>
-      <c r="E53" s="202" t="s">
-        <v>228</v>
+      <c r="A53" s="211"/>
+      <c r="E53" s="216" t="s">
+        <v>233</v>
       </c>
       <c r="F53" s="107"/>
       <c r="G53" s="107"/>
@@ -8764,21 +8889,21 @@
       <c r="J53" s="107"/>
       <c r="K53" s="107"/>
       <c r="L53" s="50"/>
-      <c r="M53" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="N53" s="198"/>
-      <c r="O53" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="200"/>
+      <c r="M53" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="N53" s="212"/>
+      <c r="O53" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="214"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A54" s="197"/>
-      <c r="B54" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="E54" s="202"/>
+      <c r="A54" s="211"/>
+      <c r="B54" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="E54" s="216"/>
       <c r="F54" s="107"/>
       <c r="G54" s="107"/>
       <c r="H54" s="50" t="n">
@@ -8788,23 +8913,23 @@
       <c r="J54" s="107"/>
       <c r="K54" s="107"/>
       <c r="L54" s="50"/>
-      <c r="M54" s="198" t="s">
-        <v>286</v>
-      </c>
-      <c r="N54" s="198"/>
-      <c r="O54" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="200" t="s">
-        <v>287</v>
+      <c r="M54" s="212" t="s">
+        <v>291</v>
+      </c>
+      <c r="N54" s="212"/>
+      <c r="O54" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="214" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="197"/>
-      <c r="B55" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="E55" s="202"/>
+      <c r="A55" s="211"/>
+      <c r="B55" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="E55" s="216"/>
       <c r="F55" s="107"/>
       <c r="G55" s="107"/>
       <c r="H55" s="50" t="n">
@@ -8814,44 +8939,44 @@
       <c r="J55" s="107"/>
       <c r="K55" s="107"/>
       <c r="L55" s="50"/>
-      <c r="M55" s="198" t="s">
-        <v>288</v>
-      </c>
-      <c r="N55" s="198"/>
-      <c r="O55" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="200" t="s">
-        <v>289</v>
+      <c r="M55" s="212" t="s">
+        <v>293</v>
+      </c>
+      <c r="N55" s="212"/>
+      <c r="O55" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="214" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="190"/>
-      <c r="B56" s="191"/>
-      <c r="C56" s="192" t="str">
+      <c r="A56" s="204"/>
+      <c r="B56" s="205"/>
+      <c r="C56" s="206" t="str">
         <f aca="false">DEC2HEX(D56,2)</f>
         <v>00</v>
       </c>
-      <c r="D56" s="154" t="n">
+      <c r="D56" s="162" t="n">
         <f aca="false">IF(E56=1,128,0)+IF(F56=1,64,0)+IF(G56=1,32,0)+IF(H56=1,16,0)+IF(I56=1,8,0)+IF(J56=1,4,0)+IF(K56=1,2,0)+IF(L56=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E56" s="193"/>
-      <c r="F56" s="154"/>
-      <c r="G56" s="154"/>
-      <c r="H56" s="155"/>
-      <c r="I56" s="154"/>
-      <c r="J56" s="154"/>
-      <c r="K56" s="154"/>
-      <c r="L56" s="155"/>
-      <c r="M56" s="191"/>
-      <c r="N56" s="191"/>
-      <c r="O56" s="194"/>
-      <c r="P56" s="196"/>
+      <c r="E56" s="207"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="163"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="162"/>
+      <c r="K56" s="162"/>
+      <c r="L56" s="163"/>
+      <c r="M56" s="205"/>
+      <c r="N56" s="205"/>
+      <c r="O56" s="208"/>
+      <c r="P56" s="210"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A57" s="197"/>
-      <c r="E57" s="202"/>
+      <c r="A57" s="211"/>
+      <c r="E57" s="216"/>
       <c r="F57" s="107"/>
       <c r="G57" s="107"/>
       <c r="H57" s="50"/>
@@ -8859,14 +8984,14 @@
       <c r="J57" s="107"/>
       <c r="K57" s="107"/>
       <c r="L57" s="50"/>
-      <c r="M57" s="198"/>
-      <c r="N57" s="198"/>
-      <c r="O57" s="128"/>
-      <c r="P57" s="200"/>
+      <c r="M57" s="212"/>
+      <c r="N57" s="212"/>
+      <c r="O57" s="133"/>
+      <c r="P57" s="214"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="197"/>
-      <c r="E58" s="202"/>
+      <c r="A58" s="211"/>
+      <c r="E58" s="216"/>
       <c r="F58" s="107"/>
       <c r="G58" s="107"/>
       <c r="H58" s="50"/>
@@ -8874,14 +8999,14 @@
       <c r="J58" s="107"/>
       <c r="K58" s="107"/>
       <c r="L58" s="50"/>
-      <c r="M58" s="198"/>
-      <c r="N58" s="198"/>
-      <c r="O58" s="128"/>
-      <c r="P58" s="200"/>
+      <c r="M58" s="212"/>
+      <c r="N58" s="212"/>
+      <c r="O58" s="133"/>
+      <c r="P58" s="214"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A59" s="197"/>
-      <c r="E59" s="202"/>
+      <c r="A59" s="211"/>
+      <c r="E59" s="216"/>
       <c r="F59" s="107"/>
       <c r="G59" s="107"/>
       <c r="H59" s="50"/>
@@ -8889,14 +9014,14 @@
       <c r="J59" s="107"/>
       <c r="K59" s="107"/>
       <c r="L59" s="50"/>
-      <c r="M59" s="198"/>
-      <c r="N59" s="198"/>
-      <c r="O59" s="128"/>
-      <c r="P59" s="200"/>
+      <c r="M59" s="212"/>
+      <c r="N59" s="212"/>
+      <c r="O59" s="133"/>
+      <c r="P59" s="214"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A60" s="197"/>
-      <c r="E60" s="202"/>
+      <c r="A60" s="211"/>
+      <c r="E60" s="216"/>
       <c r="F60" s="107"/>
       <c r="G60" s="107"/>
       <c r="H60" s="50"/>
@@ -8904,14 +9029,14 @@
       <c r="J60" s="107"/>
       <c r="K60" s="107"/>
       <c r="L60" s="50"/>
-      <c r="M60" s="198"/>
-      <c r="N60" s="198"/>
-      <c r="O60" s="128"/>
-      <c r="P60" s="200"/>
+      <c r="M60" s="212"/>
+      <c r="N60" s="212"/>
+      <c r="O60" s="133"/>
+      <c r="P60" s="214"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="197"/>
-      <c r="E61" s="202"/>
+      <c r="A61" s="211"/>
+      <c r="E61" s="216"/>
       <c r="F61" s="107"/>
       <c r="G61" s="107"/>
       <c r="H61" s="50"/>
@@ -8919,78 +9044,78 @@
       <c r="J61" s="107"/>
       <c r="K61" s="107"/>
       <c r="L61" s="50"/>
-      <c r="M61" s="198"/>
-      <c r="N61" s="198"/>
-      <c r="O61" s="128"/>
-      <c r="P61" s="200"/>
+      <c r="M61" s="212"/>
+      <c r="N61" s="212"/>
+      <c r="O61" s="133"/>
+      <c r="P61" s="214"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="190" t="s">
-        <v>209</v>
-      </c>
-      <c r="B62" s="194"/>
-      <c r="C62" s="192"/>
-      <c r="D62" s="154"/>
-      <c r="E62" s="193"/>
-      <c r="F62" s="154"/>
-      <c r="G62" s="154"/>
-      <c r="H62" s="155"/>
-      <c r="I62" s="193"/>
-      <c r="J62" s="154"/>
-      <c r="K62" s="154"/>
-      <c r="L62" s="155"/>
-      <c r="M62" s="191"/>
-      <c r="N62" s="191"/>
-      <c r="O62" s="194"/>
-      <c r="P62" s="196"/>
+      <c r="A62" s="204" t="s">
+        <v>214</v>
+      </c>
+      <c r="B62" s="208"/>
+      <c r="C62" s="206"/>
+      <c r="D62" s="162"/>
+      <c r="E62" s="207"/>
+      <c r="F62" s="162"/>
+      <c r="G62" s="162"/>
+      <c r="H62" s="163"/>
+      <c r="I62" s="207"/>
+      <c r="J62" s="162"/>
+      <c r="K62" s="162"/>
+      <c r="L62" s="163"/>
+      <c r="M62" s="205"/>
+      <c r="N62" s="205"/>
+      <c r="O62" s="208"/>
+      <c r="P62" s="210"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A63" s="210" t="s">
-        <v>290</v>
-      </c>
-      <c r="B63" s="211"/>
-      <c r="C63" s="186" t="str">
+      <c r="A63" s="224" t="s">
+        <v>295</v>
+      </c>
+      <c r="B63" s="225"/>
+      <c r="C63" s="200" t="str">
         <f aca="false">DEC2HEX(D63,2)</f>
         <v>00</v>
       </c>
-      <c r="D63" s="212" t="n">
+      <c r="D63" s="226" t="n">
         <f aca="false">IF(E63=1,128,0)+IF(F63=1,64,0)+IF(G63=1,32,0)+IF(H63=1,16,0)+IF(I63=1,8,0)+IF(J63=1,4,0)+IF(K63=1,2,0)+IF(L63=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="215"/>
-      <c r="N63" s="215"/>
-      <c r="O63" s="211"/>
-      <c r="P63" s="216"/>
+      <c r="E63" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="229"/>
+      <c r="N63" s="229"/>
+      <c r="O63" s="225"/>
+      <c r="P63" s="230"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="197" t="s">
-        <v>291</v>
-      </c>
-      <c r="B64" s="128"/>
+      <c r="A64" s="211" t="s">
+        <v>296</v>
+      </c>
+      <c r="B64" s="133"/>
       <c r="C64" s="20" t="str">
         <f aca="false">DEC2HEX(D64,2)</f>
         <v>40</v>
@@ -9023,16 +9148,16 @@
       <c r="L64" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M64" s="198"/>
-      <c r="N64" s="198"/>
-      <c r="O64" s="128"/>
-      <c r="P64" s="200"/>
+      <c r="M64" s="212"/>
+      <c r="N64" s="212"/>
+      <c r="O64" s="133"/>
+      <c r="P64" s="214"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A65" s="197" t="s">
-        <v>292</v>
-      </c>
-      <c r="B65" s="128"/>
+      <c r="A65" s="211" t="s">
+        <v>297</v>
+      </c>
+      <c r="B65" s="133"/>
       <c r="C65" s="20" t="str">
         <f aca="false">DEC2HEX(D65,2)</f>
         <v>80</v>
@@ -9065,100 +9190,100 @@
       <c r="L65" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M65" s="198"/>
-      <c r="N65" s="198"/>
-      <c r="O65" s="128"/>
-      <c r="P65" s="200"/>
+      <c r="M65" s="212"/>
+      <c r="N65" s="212"/>
+      <c r="O65" s="133"/>
+      <c r="P65" s="214"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A66" s="207" t="s">
-        <v>293</v>
-      </c>
-      <c r="B66" s="209"/>
-      <c r="C66" s="208" t="str">
+      <c r="A66" s="221" t="s">
+        <v>298</v>
+      </c>
+      <c r="B66" s="223"/>
+      <c r="C66" s="222" t="str">
         <f aca="false">DEC2HEX(D66,2)</f>
         <v>C0</v>
       </c>
-      <c r="D66" s="133" t="n">
+      <c r="D66" s="139" t="n">
         <f aca="false">IF(E66=1,128,0)+IF(F66=1,64,0)+IF(G66=1,32,0)+IF(H66=1,16,0)+IF(I66=1,8,0)+IF(J66=1,4,0)+IF(K66=1,2,0)+IF(L66=1,1,0)</f>
         <v>192</v>
       </c>
-      <c r="E66" s="132" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="217"/>
-      <c r="N66" s="217"/>
-      <c r="O66" s="209"/>
-      <c r="P66" s="218"/>
+      <c r="E66" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="231"/>
+      <c r="N66" s="231"/>
+      <c r="O66" s="223"/>
+      <c r="P66" s="232"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A67" s="210" t="s">
-        <v>294</v>
-      </c>
-      <c r="B67" s="219"/>
-      <c r="C67" s="186" t="str">
+      <c r="A67" s="224" t="s">
+        <v>299</v>
+      </c>
+      <c r="B67" s="233"/>
+      <c r="C67" s="200" t="str">
         <f aca="false">DEC2HEX(D67,2)</f>
         <v>01</v>
       </c>
-      <c r="D67" s="212" t="n">
+      <c r="D67" s="226" t="n">
         <f aca="false">IF(E67=1,128,0)+IF(F67=1,64,0)+IF(G67=1,32,0)+IF(H67=1,16,0)+IF(I67=1,8,0)+IF(J67=1,4,0)+IF(K67=1,2,0)+IF(L67=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E67" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="214" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" s="215"/>
-      <c r="N67" s="215"/>
-      <c r="O67" s="211"/>
-      <c r="P67" s="216"/>
+      <c r="E67" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="229"/>
+      <c r="N67" s="229"/>
+      <c r="O67" s="225"/>
+      <c r="P67" s="230"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A68" s="197" t="s">
-        <v>295</v>
-      </c>
-      <c r="B68" s="128"/>
+      <c r="A68" s="211" t="s">
+        <v>300</v>
+      </c>
+      <c r="B68" s="133"/>
       <c r="C68" s="20" t="str">
         <f aca="false">DEC2HEX(D68,2)</f>
         <v>41</v>
@@ -9167,7 +9292,7 @@
         <f aca="false">IF(E68=1,128,0)+IF(F68=1,64,0)+IF(G68=1,32,0)+IF(H68=1,16,0)+IF(I68=1,8,0)+IF(J68=1,4,0)+IF(K68=1,2,0)+IF(L68=1,1,0)</f>
         <v>65</v>
       </c>
-      <c r="E68" s="202" t="n">
+      <c r="E68" s="216" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="2" t="n">
@@ -9191,13 +9316,13 @@
       <c r="L68" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="P68" s="200"/>
+      <c r="P68" s="214"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A69" s="197" t="s">
-        <v>296</v>
-      </c>
-      <c r="B69" s="128"/>
+      <c r="A69" s="211" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="133"/>
       <c r="C69" s="20" t="str">
         <f aca="false">DEC2HEX(D69,2)</f>
         <v>C1</v>
@@ -9206,7 +9331,7 @@
         <f aca="false">IF(E69=1,128,0)+IF(F69=1,64,0)+IF(G69=1,32,0)+IF(H69=1,16,0)+IF(I69=1,8,0)+IF(J69=1,4,0)+IF(K69=1,2,0)+IF(L69=1,1,0)</f>
         <v>193</v>
       </c>
-      <c r="E69" s="202" t="n">
+      <c r="E69" s="216" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="107" t="n">
@@ -9232,100 +9357,100 @@
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10"/>
-      <c r="O69" s="128"/>
-      <c r="P69" s="200"/>
+      <c r="O69" s="133"/>
+      <c r="P69" s="214"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A70" s="207" t="s">
-        <v>297</v>
-      </c>
-      <c r="B70" s="209"/>
-      <c r="C70" s="208" t="str">
+      <c r="A70" s="221" t="s">
+        <v>302</v>
+      </c>
+      <c r="B70" s="223"/>
+      <c r="C70" s="222" t="str">
         <f aca="false">DEC2HEX(D70,2)</f>
         <v>03</v>
       </c>
-      <c r="D70" s="133" t="n">
+      <c r="D70" s="139" t="n">
         <f aca="false">IF(E70=1,128,0)+IF(F70=1,64,0)+IF(G70=1,32,0)+IF(H70=1,16,0)+IF(I70=1,8,0)+IF(J70=1,4,0)+IF(K70=1,2,0)+IF(L70=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="E70" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" s="217"/>
-      <c r="N70" s="217"/>
-      <c r="O70" s="209"/>
-      <c r="P70" s="218"/>
+      <c r="E70" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="231"/>
+      <c r="N70" s="231"/>
+      <c r="O70" s="223"/>
+      <c r="P70" s="232"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="210" t="s">
-        <v>298</v>
-      </c>
-      <c r="B71" s="211"/>
-      <c r="C71" s="186" t="str">
+      <c r="A71" s="224" t="s">
+        <v>303</v>
+      </c>
+      <c r="B71" s="225"/>
+      <c r="C71" s="200" t="str">
         <f aca="false">DEC2HEX(D71,2)</f>
         <v>04</v>
       </c>
-      <c r="D71" s="212" t="n">
+      <c r="D71" s="226" t="n">
         <f aca="false">IF(E71=1,128,0)+IF(F71=1,64,0)+IF(G71=1,32,0)+IF(H71=1,16,0)+IF(I71=1,8,0)+IF(J71=1,4,0)+IF(K71=1,2,0)+IF(L71=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E71" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="215"/>
-      <c r="N71" s="215"/>
-      <c r="O71" s="211"/>
-      <c r="P71" s="216" t="s">
-        <v>299</v>
+      <c r="E71" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="229"/>
+      <c r="N71" s="229"/>
+      <c r="O71" s="225"/>
+      <c r="P71" s="230" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="197" t="s">
-        <v>300</v>
-      </c>
-      <c r="B72" s="128"/>
+      <c r="A72" s="211" t="s">
+        <v>305</v>
+      </c>
+      <c r="B72" s="133"/>
       <c r="C72" s="20" t="str">
         <f aca="false">DEC2HEX(D72,2)</f>
         <v>14</v>
@@ -9358,192 +9483,192 @@
       <c r="L72" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="198"/>
-      <c r="N72" s="198"/>
-      <c r="O72" s="128"/>
-      <c r="P72" s="200" t="s">
-        <v>301</v>
+      <c r="M72" s="212"/>
+      <c r="N72" s="212"/>
+      <c r="O72" s="133"/>
+      <c r="P72" s="214" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="207" t="s">
-        <v>302</v>
-      </c>
-      <c r="B73" s="209"/>
-      <c r="C73" s="208" t="str">
+      <c r="A73" s="221" t="s">
+        <v>307</v>
+      </c>
+      <c r="B73" s="223"/>
+      <c r="C73" s="222" t="str">
         <f aca="false">DEC2HEX(D73,2)</f>
         <v>54</v>
       </c>
-      <c r="D73" s="133" t="n">
+      <c r="D73" s="139" t="n">
         <f aca="false">IF(E73=1,128,0)+IF(F73=1,64,0)+IF(G73=1,32,0)+IF(H73=1,16,0)+IF(I73=1,8,0)+IF(J73=1,4,0)+IF(K73=1,2,0)+IF(L73=1,1,0)</f>
         <v>84</v>
       </c>
-      <c r="E73" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="217"/>
-      <c r="N73" s="217"/>
-      <c r="O73" s="209"/>
-      <c r="P73" s="218" t="s">
-        <v>303</v>
+      <c r="E73" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="231"/>
+      <c r="N73" s="231"/>
+      <c r="O73" s="223"/>
+      <c r="P73" s="232" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="210" t="s">
-        <v>304</v>
-      </c>
-      <c r="B74" s="211"/>
-      <c r="C74" s="186" t="str">
+      <c r="A74" s="224" t="s">
+        <v>309</v>
+      </c>
+      <c r="B74" s="225"/>
+      <c r="C74" s="200" t="str">
         <f aca="false">DEC2HEX(D74,2)</f>
         <v>05</v>
       </c>
-      <c r="D74" s="212" t="n">
+      <c r="D74" s="226" t="n">
         <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E74" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="214" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" s="215"/>
-      <c r="N74" s="215"/>
-      <c r="O74" s="211"/>
-      <c r="P74" s="216" t="s">
-        <v>305</v>
+      <c r="E74" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" s="229"/>
+      <c r="N74" s="229"/>
+      <c r="O74" s="225"/>
+      <c r="P74" s="230" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="207" t="s">
-        <v>306</v>
-      </c>
-      <c r="B75" s="209"/>
-      <c r="C75" s="208" t="str">
+      <c r="A75" s="221" t="s">
+        <v>311</v>
+      </c>
+      <c r="B75" s="223"/>
+      <c r="C75" s="222" t="str">
         <f aca="false">DEC2HEX(D75,2)</f>
         <v>15</v>
       </c>
-      <c r="D75" s="133" t="n">
+      <c r="D75" s="139" t="n">
         <f aca="false">IF(E75=1,128,0)+IF(F75=1,64,0)+IF(G75=1,32,0)+IF(H75=1,16,0)+IF(I75=1,8,0)+IF(J75=1,4,0)+IF(K75=1,2,0)+IF(L75=1,1,0)</f>
         <v>21</v>
       </c>
-      <c r="E75" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="M75" s="217"/>
-      <c r="N75" s="217"/>
-      <c r="O75" s="209"/>
-      <c r="P75" s="218" t="s">
-        <v>307</v>
+      <c r="E75" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" s="231"/>
+      <c r="N75" s="231"/>
+      <c r="O75" s="223"/>
+      <c r="P75" s="232" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="210" t="s">
-        <v>308</v>
-      </c>
-      <c r="B76" s="211"/>
-      <c r="C76" s="186" t="str">
+      <c r="A76" s="224" t="s">
+        <v>313</v>
+      </c>
+      <c r="B76" s="225"/>
+      <c r="C76" s="200" t="str">
         <f aca="false">DEC2HEX(D76,2)</f>
         <v>46</v>
       </c>
-      <c r="D76" s="212" t="n">
+      <c r="D76" s="226" t="n">
         <f aca="false">IF(E76=1,128,0)+IF(F76=1,64,0)+IF(G76=1,32,0)+IF(H76=1,16,0)+IF(I76=1,8,0)+IF(J76=1,4,0)+IF(K76=1,2,0)+IF(L76=1,1,0)</f>
         <v>70</v>
       </c>
-      <c r="E76" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="215"/>
-      <c r="N76" s="215"/>
-      <c r="O76" s="211"/>
-      <c r="P76" s="216"/>
+      <c r="E76" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="229"/>
+      <c r="N76" s="229"/>
+      <c r="O76" s="225"/>
+      <c r="P76" s="230"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="197" t="s">
-        <v>309</v>
-      </c>
-      <c r="B77" s="128"/>
+      <c r="A77" s="211" t="s">
+        <v>314</v>
+      </c>
+      <c r="B77" s="133"/>
       <c r="C77" s="17" t="str">
         <f aca="false">DEC2HEX(D77,2)</f>
         <v>56</v>
@@ -9576,16 +9701,16 @@
       <c r="L77" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="198"/>
-      <c r="N77" s="198"/>
-      <c r="O77" s="128"/>
-      <c r="P77" s="200"/>
+      <c r="M77" s="212"/>
+      <c r="N77" s="212"/>
+      <c r="O77" s="133"/>
+      <c r="P77" s="214"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="197" t="s">
-        <v>310</v>
-      </c>
-      <c r="B78" s="128"/>
+      <c r="A78" s="211" t="s">
+        <v>315</v>
+      </c>
+      <c r="B78" s="133"/>
       <c r="C78" s="17" t="str">
         <f aca="false">DEC2HEX(D78,2)</f>
         <v>C7</v>
@@ -9618,140 +9743,140 @@
       <c r="L78" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M78" s="198"/>
-      <c r="N78" s="198"/>
-      <c r="O78" s="128"/>
-      <c r="P78" s="200"/>
+      <c r="M78" s="212"/>
+      <c r="N78" s="212"/>
+      <c r="O78" s="133"/>
+      <c r="P78" s="214"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="207" t="s">
-        <v>311</v>
-      </c>
-      <c r="B79" s="209"/>
-      <c r="C79" s="208" t="str">
+      <c r="A79" s="221" t="s">
+        <v>316</v>
+      </c>
+      <c r="B79" s="223"/>
+      <c r="C79" s="222" t="str">
         <f aca="false">DEC2HEX(D79,2)</f>
         <v>D7</v>
       </c>
-      <c r="D79" s="133" t="n">
+      <c r="D79" s="139" t="n">
         <f aca="false">IF(E79=1,128,0)+IF(F79=1,64,0)+IF(G79=1,32,0)+IF(H79=1,16,0)+IF(I79=1,8,0)+IF(J79=1,4,0)+IF(K79=1,2,0)+IF(L79=1,1,0)</f>
         <v>215</v>
       </c>
-      <c r="E79" s="132" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="217"/>
-      <c r="N79" s="217"/>
-      <c r="O79" s="209"/>
-      <c r="P79" s="218"/>
+      <c r="E79" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="231"/>
+      <c r="N79" s="231"/>
+      <c r="O79" s="223"/>
+      <c r="P79" s="232"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="210" t="s">
-        <v>312</v>
-      </c>
-      <c r="B80" s="211"/>
-      <c r="C80" s="186" t="str">
+      <c r="A80" s="224" t="s">
+        <v>317</v>
+      </c>
+      <c r="B80" s="225"/>
+      <c r="C80" s="200" t="str">
         <f aca="false">DEC2HEX(D80,2)</f>
         <v>0C</v>
       </c>
-      <c r="D80" s="212" t="n">
+      <c r="D80" s="226" t="n">
         <f aca="false">IF(E80=1,128,0)+IF(F80=1,64,0)+IF(G80=1,32,0)+IF(H80=1,16,0)+IF(I80=1,8,0)+IF(J80=1,4,0)+IF(K80=1,2,0)+IF(L80=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="E80" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="215"/>
-      <c r="N80" s="215"/>
-      <c r="O80" s="211"/>
-      <c r="P80" s="216"/>
+      <c r="E80" s="227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="227" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="229"/>
+      <c r="N80" s="229"/>
+      <c r="O80" s="225"/>
+      <c r="P80" s="230"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="207" t="s">
-        <v>313</v>
-      </c>
-      <c r="B81" s="209"/>
-      <c r="C81" s="208" t="str">
+      <c r="A81" s="221" t="s">
+        <v>318</v>
+      </c>
+      <c r="B81" s="223"/>
+      <c r="C81" s="222" t="str">
         <f aca="false">DEC2HEX(D81,2)</f>
         <v>8C</v>
       </c>
-      <c r="D81" s="133" t="n">
+      <c r="D81" s="139" t="n">
         <f aca="false">IF(E81=1,128,0)+IF(F81=1,64,0)+IF(G81=1,32,0)+IF(H81=1,16,0)+IF(I81=1,8,0)+IF(J81=1,4,0)+IF(K81=1,2,0)+IF(L81=1,1,0)</f>
         <v>140</v>
       </c>
-      <c r="E81" s="132" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="132" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="133" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="217"/>
-      <c r="N81" s="217"/>
-      <c r="O81" s="209"/>
-      <c r="P81" s="218"/>
+      <c r="E81" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="231"/>
+      <c r="N81" s="231"/>
+      <c r="O81" s="223"/>
+      <c r="P81" s="232"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="197"/>
-      <c r="B82" s="128"/>
+      <c r="A82" s="211"/>
+      <c r="B82" s="133"/>
       <c r="C82" s="17" t="str">
         <f aca="false">DEC2HEX(D82,2)</f>
         <v>00</v>
@@ -9768,41 +9893,41 @@
       <c r="J82" s="107"/>
       <c r="K82" s="107"/>
       <c r="L82" s="50"/>
-      <c r="M82" s="198"/>
-      <c r="N82" s="198"/>
-      <c r="O82" s="128"/>
-      <c r="P82" s="200"/>
+      <c r="M82" s="212"/>
+      <c r="N82" s="212"/>
+      <c r="O82" s="133"/>
+      <c r="P82" s="214"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="207"/>
-      <c r="B83" s="209"/>
-      <c r="C83" s="208" t="str">
+      <c r="A83" s="221"/>
+      <c r="B83" s="223"/>
+      <c r="C83" s="222" t="str">
         <f aca="false">DEC2HEX(D83,2)</f>
         <v>00</v>
       </c>
-      <c r="D83" s="133" t="n">
+      <c r="D83" s="139" t="n">
         <f aca="false">IF(E83=1,128,0)+IF(F83=1,64,0)+IF(G83=1,32,0)+IF(H83=1,16,0)+IF(I83=1,8,0)+IF(J83=1,4,0)+IF(K83=1,2,0)+IF(L83=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E83" s="132"/>
-      <c r="F83" s="133"/>
-      <c r="G83" s="133"/>
-      <c r="H83" s="136"/>
-      <c r="I83" s="132"/>
-      <c r="J83" s="133"/>
-      <c r="K83" s="133"/>
-      <c r="L83" s="136"/>
-      <c r="M83" s="217"/>
-      <c r="N83" s="217"/>
-      <c r="O83" s="209"/>
-      <c r="P83" s="218"/>
+      <c r="E83" s="138"/>
+      <c r="F83" s="139"/>
+      <c r="G83" s="139"/>
+      <c r="H83" s="142"/>
+      <c r="I83" s="138"/>
+      <c r="J83" s="139"/>
+      <c r="K83" s="139"/>
+      <c r="L83" s="142"/>
+      <c r="M83" s="231"/>
+      <c r="N83" s="231"/>
+      <c r="O83" s="223"/>
+      <c r="P83" s="232"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="129"/>
+      <c r="B84" s="134"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -9817,12 +9942,12 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="220"/>
+      <c r="O85" s="234"/>
       <c r="P85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -9858,10 +9983,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>50</v>
@@ -9875,13 +10000,13 @@
       <c r="F1" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="G1" s="221" t="s">
-        <v>317</v>
-      </c>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221" t="s">
-        <v>318</v>
+      <c r="G1" s="235" t="s">
+        <v>322</v>
+      </c>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9895,26 +10020,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>118</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9928,13 +10053,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>118</v>
@@ -9944,10 +10069,10 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9964,25 +10089,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9999,25 +10124,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10031,28 +10156,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10066,28 +10191,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10101,26 +10226,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>118</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10134,13 +10259,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>118</v>
@@ -10150,10 +10275,10 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10167,28 +10292,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10202,28 +10327,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10237,28 +10362,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10272,28 +10397,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -30,29 +30,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="M6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Note:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">ReferenceID can be ServletID or StreamID.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M15" authorId="0">
+    <comment ref="M34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -74,7 +52,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N13" authorId="0">
+    <comment ref="N32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -86,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="0">
+    <comment ref="N33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -98,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N15" authorId="0">
+    <comment ref="N34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="344">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -613,14 +591,29 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> link.</t>
+      <t xml:space="preserve"> link within the context of </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">If the Data link contains neither of the flags HasParameters nor HasSpecial, then it contains simply a byte array.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the Data link contains either of the flags HasParameters or HasSpecial, then the following rules apply:</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LinkType: Member</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -652,7 +645,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Parameters count </t>
+      <t xml:space="preserve">ParamCount </t>
     </r>
     <r>
       <rPr>
@@ -694,7 +687,28 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">This does not include the Special (if there even is a Special).</t>
+      <t xml:space="preserve">This </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">does</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> include the Special (when there is a Special).</t>
     </r>
   </si>
   <si>
@@ -833,7 +847,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Property parameters when setting an array property.</t>
+      <t xml:space="preserve">Property parameters when accessing an array property.</t>
     </r>
   </si>
   <si>
@@ -866,7 +880,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Special Value</t>
+      <t xml:space="preserve">Special </t>
     </r>
     <r>
       <rPr>
@@ -876,7 +890,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> - These should be used for:</t>
+      <t xml:space="preserve">- This is an additional parameter that should be used for:</t>
     </r>
   </si>
   <si>
@@ -976,49 +990,241 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">If Parameter Count = 0 and there is no Special, then the whole Data link can be dropped.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Note that a parameter/special can have a value of null, which is not the same as the value not existing.</t>
   </si>
   <si>
     <t xml:space="preserve">There is no difference in encoding between Parameters and a Special Value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Special value must always be last parameter (when there is one).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thus, the Special (if there is one) is always the last parameter in the parameter list.</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Each value begins with a </t>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> part of a </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ValueType</t>
+      <t xml:space="preserve">LinkType: Data</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> byte.  That ValueType specifies what else needs to be read and in what order.</t>
+      <t xml:space="preserve"> begins with </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">The Special Value must always be last (when there is one).</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ParamCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (4 bytes) that specifies the total number of parameters, followed by the parameters.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Thus, a </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LinkType: Data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">link</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> contains: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DataSize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (4 bytes) + </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ParamCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (4 bytes) + the </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">parameters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (? bytes)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">If the parameter count is 0 (ie. no parameters and no special) then the </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LinkType: Data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> can be omitted entirely.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Size (bytes)</t>
@@ -1030,84 +1236,39 @@
     <t xml:space="preserve">Comments</t>
   </si>
   <si>
+    <t xml:space="preserve">HasTypeName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TypeName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String</t>
+  </si>
+  <si>
     <t xml:space="preserve">HasValueName</t>
   </si>
   <si>
     <t xml:space="preserve">ValueName</t>
   </si>
   <si>
-    <t xml:space="preserve">+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String</t>
+    <t xml:space="preserve">IsValue/IsReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ReferenceID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsReference</t>
   </si>
   <si>
     <t xml:space="preserve">IsNull</t>
   </si>
   <si>
-    <t xml:space="preserve">IsNull=False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HasTypeName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TypeName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsValue/IsReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReferenceID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsStream/IsServlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsStream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsServlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HasDevicePath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevicePathSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevicesLength</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of bytes that Devices consists of.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevicePath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morph links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HasArrayIndex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ValueType</t>
-  </si>
-  <si>
     <t xml:space="preserve">IsValue</t>
   </si>
   <si>
@@ -1120,10 +1281,13 @@
     <t xml:space="preserve">IsStruct</t>
   </si>
   <si>
+    <t xml:space="preserve">IsCustomType</t>
+  </si>
+  <si>
     <t xml:space="preserve">Simple</t>
   </si>
   <si>
-    <t xml:space="preserve">00</t>
+    <t xml:space="preserve">IsValue and IsSimpleType</t>
   </si>
   <si>
     <t xml:space="preserve">SimpleType</t>
@@ -1135,7 +1299,22 @@
     <t xml:space="preserve">Array</t>
   </si>
   <si>
-    <t xml:space="preserve">10</t>
+    <t xml:space="preserve">IsValue and IsArray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsArrayElemType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayElemType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1..2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ValueType (+SimpleType)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specifies the type of all elements in the array.</t>
   </si>
   <si>
     <t xml:space="preserve">ArrayElemCount</t>
@@ -1174,21 +1353,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">IsArrayElemType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArrayElemType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1..2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ValueType (+SimpleType)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specifies the type of all elements in the array.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Values</t>
   </si>
   <si>
@@ -1207,7 +1371,7 @@
     <t xml:space="preserve">Struct</t>
   </si>
   <si>
-    <t xml:space="preserve">20</t>
+    <t xml:space="preserve">IsValue and IsStruct</t>
   </si>
   <si>
     <t xml:space="preserve">StructElemCount</t>
@@ -1249,13 +1413,46 @@
     <t xml:space="preserve">Custom</t>
   </si>
   <si>
-    <t xml:space="preserve">IsCustomType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CustomTypeName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer's proprietary type.</t>
+    <t xml:space="preserve">IsValue and IsCustomType and HasTypeName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsNullable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsStream/IsServlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsReference and IsStream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsReference and IsServlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HasDevicePath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevicePathSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevicesLength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of bytes that Devices consists of.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevicePath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morph links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HasArrayIndex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ValueType</t>
   </si>
   <si>
     <t xml:space="preserve">String: 2 bytes representing byte count of the string, followed by UTF-8 characters</t>
@@ -1279,9 +1476,15 @@
     <t xml:space="preserve">(ValueName), </t>
   </si>
   <si>
+    <t xml:space="preserve">IsStream</t>
+  </si>
+  <si>
     <t xml:space="preserve">(ValueName), (TypeName), ReferenceID</t>
   </si>
   <si>
+    <t xml:space="preserve">IsServlet</t>
+  </si>
+  <si>
     <t xml:space="preserve">(ValueName), (TypeName), ReferenceID, ApartmentID, (DevicePath), (Index)</t>
   </si>
   <si>
@@ -1319,9 +1522,6 @@
   </si>
   <si>
     <t xml:space="preserve">IsUnsigned/IsSigned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v</t>
   </si>
   <si>
     <t xml:space="preserve">HasValue</t>
@@ -1438,6 +1638,15 @@
     <t xml:space="preserve">Enum type name</t>
   </si>
   <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsBool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The full byte value for boolean is 0x84.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1, 2, 4, 8</t>
   </si>
   <si>
@@ -1451,9 +1660,6 @@
   </si>
   <si>
     <t xml:space="preserve">Values are comma delimited, without spaces. Ending comma is ignored.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4+</t>
   </si>
   <si>
     <t xml:space="preserve">Date/Time (numeric)</t>
@@ -1621,94 +1827,94 @@
     <t xml:space="preserve">https://learn.microsoft.com/en-us/office/vba/language/reference/user-interface-help/currency-data-type</t>
   </si>
   <si>
+    <t xml:space="preserve">Loose reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More complexity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size indicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composite type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric vs. character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UInt8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UInt16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UInt32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UInt64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Char (UTF-8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Char (UTF-16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Char (UTF-32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Char (ASCII)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reasonable enum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An enumerated type in ordinal (numeric) form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set (small enum)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A set of an enumerated type with a maximum of 8 values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set (medium enum)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A set of an enumerated type with a maximum of 16 values.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Boolean</t>
   </si>
   <si>
-    <t xml:space="preserve">IsBool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsFalse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean value False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsTrue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean value True</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Char (UTF-8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Char (UTF-16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Char (ASCII)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String (Unicode)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reasonable enum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An enumerated value in ordinal (numeric) form.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set (small enum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A set of an enumerated type with a maximum of 8 values.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set (medium enum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A set of an enumerated type with a maximum of 16 values.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Enum as string</t>
   </si>
   <si>
-    <t xml:space="preserve">An enumerated value in string form.</t>
+    <t xml:space="preserve">An enumerated type in string form.</t>
   </si>
   <si>
     <t xml:space="preserve">Enum set as string</t>
   </si>
   <si>
-    <t xml:space="preserve">A set of an enumerated type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UTC time (numeric)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local time (numeric)</t>
+    <t xml:space="preserve">An enumerated set type in string form.</t>
   </si>
   <si>
     <t xml:space="preserve">UTC date/time (string)</t>
   </si>
   <si>
     <t xml:space="preserve">Local date/time (string)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean True</t>
   </si>
   <si>
     <r>
@@ -1753,8 +1959,30 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> It is not expected that all platforms support all data-types.</t>
+      <t xml:space="preserve"> It is </t>
     </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> expected that all platforms support all data-types.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">y</t>
@@ -1764,9 +1992,6 @@
   </si>
   <si>
     <t xml:space="preserve">Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -1838,7 +2063,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1908,6 +2133,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -1920,6 +2153,14 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1964,8 +2205,17 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1975,7 +2225,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.15"/>
-        <bgColor rgb="FFC0C0C0"/>
+        <bgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -2432,11 +2688,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="251">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2877,7 +3133,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2885,23 +3141,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2913,19 +3157,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2949,19 +3193,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2973,14 +3217,30 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="49" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2989,7 +3249,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3017,6 +3277,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3025,7 +3289,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3033,11 +3297,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="49" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="50" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3057,10 +3325,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3069,23 +3333,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3101,48 +3365,32 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3157,76 +3405,104 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="59" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="59" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="59" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="50" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="50" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3265,10 +3541,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3301,11 +3573,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3313,6 +3581,50 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3329,22 +3641,22 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3370,6 +3682,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3394,7 +3710,7 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
@@ -3779,7 +4095,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="12" width="6.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="12" width="13.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="11" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="74.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="46.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="12" width="6.85"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="22" style="11" width="9.14"/>
   </cols>
@@ -3987,7 +4303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A5" s="44"/>
       <c r="B5" s="44"/>
       <c r="C5" s="45"/>
@@ -4014,7 +4330,7 @@
       </c>
       <c r="Q5" s="55"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A6" s="56"/>
       <c r="B6" s="56"/>
       <c r="C6" s="57"/>
@@ -4037,7 +4353,7 @@
       <c r="P6" s="63"/>
       <c r="Q6" s="64"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A7" s="56"/>
       <c r="B7" s="56"/>
       <c r="C7" s="57"/>
@@ -4062,7 +4378,7 @@
       </c>
       <c r="Q7" s="64"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A8" s="56"/>
       <c r="B8" s="56"/>
       <c r="C8" s="57"/>
@@ -4091,7 +4407,7 @@
       <c r="R8" s="13"/>
       <c r="S8" s="13"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A9" s="56"/>
       <c r="B9" s="56"/>
       <c r="C9" s="57"/>
@@ -4118,7 +4434,7 @@
       <c r="R9" s="13"/>
       <c r="S9" s="13"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A10" s="56"/>
       <c r="B10" s="56" t="s">
         <v>58</v>
@@ -4201,7 +4517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A12" s="66"/>
       <c r="B12" s="66"/>
       <c r="C12" s="67"/>
@@ -4226,7 +4542,7 @@
       </c>
       <c r="Q12" s="73"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A13" s="44"/>
       <c r="B13" s="44"/>
       <c r="C13" s="45"/>
@@ -4253,7 +4569,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A14" s="66"/>
       <c r="B14" s="66"/>
       <c r="C14" s="70"/>
@@ -4723,7 +5039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A27" s="66"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
@@ -4748,7 +5064,7 @@
       </c>
       <c r="Q27" s="73"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A28" s="66"/>
       <c r="B28" s="44"/>
       <c r="C28" s="67"/>
@@ -4775,7 +5091,7 @@
       <c r="P28" s="54"/>
       <c r="Q28" s="73"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A29" s="66"/>
       <c r="B29" s="102" t="s">
         <v>88</v>
@@ -4800,7 +5116,7 @@
       <c r="P29" s="54"/>
       <c r="Q29" s="73"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A30" s="44"/>
       <c r="B30" s="102" t="s">
         <v>88</v>
@@ -6161,112 +6477,115 @@
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="109" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="109"/>
+      <c r="B4" s="109" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="109"/>
+    </row>
+    <row r="6" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="109" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="109"/>
       <c r="B7" s="109" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="109"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="109" t="s">
+    <row r="8" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="109" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="109" t="s">
+    <row r="9" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="109" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="109" t="s">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="109"/>
+    </row>
+    <row r="11" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="109" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="109" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="109"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="109" t="s">
+    <row r="13" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="109" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="109" t="s">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="109" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="109" t="s">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="109" t="s">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="C19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>149</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="108" t="s">
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1"/>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6275,21 +6594,15 @@
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C31" s="1"/>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C35" s="1"/>
-    </row>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6325,7 +6638,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="110" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="111" width="3.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="111" width="3.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="5" width="3.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="18.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="15.59"/>
@@ -6387,990 +6700,924 @@
       <c r="S1" s="110"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="114"/>
       <c r="B2" s="114"/>
       <c r="C2" s="115"/>
       <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="114"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="121" t="s">
+        <v>156</v>
+      </c>
+      <c r="M2" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="N2" s="120" t="s">
+        <v>158</v>
+      </c>
+      <c r="O2" s="120" t="s">
+        <v>159</v>
+      </c>
+      <c r="P2" s="122"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="117"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="123" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="124" t="s">
+      <c r="K3" s="129"/>
+      <c r="L3" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="M3" s="130" t="s">
+        <v>161</v>
+      </c>
+      <c r="N3" s="129" t="s">
+        <v>158</v>
+      </c>
+      <c r="O3" s="129" t="s">
+        <v>159</v>
+      </c>
+      <c r="P3" s="131"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="132"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="107" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="107"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="130" t="s">
+        <v>162</v>
+      </c>
+      <c r="M4" s="130" t="s">
+        <v>163</v>
+      </c>
+      <c r="N4" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="129" t="s">
+        <v>164</v>
+      </c>
+      <c r="P4" s="131"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="137" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="138"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="142" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="144" t="s">
+        <v>166</v>
+      </c>
+      <c r="M5" s="144"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="145"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="148"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="150"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="152"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="154"/>
+      <c r="L6" s="155"/>
+      <c r="M6" s="155"/>
+      <c r="N6" s="154"/>
+      <c r="O6" s="154"/>
+      <c r="P6" s="156"/>
+      <c r="Q6" s="157"/>
+      <c r="R6" s="157"/>
+      <c r="S6" s="157"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B7" s="123"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="128"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="130" t="s">
+        <v>168</v>
+      </c>
+      <c r="M7" s="130"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="131"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B8" s="123"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="128"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="M8" s="130"/>
+      <c r="N8" s="129"/>
+      <c r="O8" s="129"/>
+      <c r="P8" s="131"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B9" s="123"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="128"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="130" t="s">
+        <v>170</v>
+      </c>
+      <c r="M9" s="130"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="129"/>
+      <c r="P9" s="131"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B10" s="123"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="128"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="130" t="s">
+        <v>171</v>
+      </c>
+      <c r="M10" s="130"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="129"/>
+      <c r="P10" s="131"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="146" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="158" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="159"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="161"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="164"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="161"/>
+      <c r="K11" s="165"/>
+      <c r="L11" s="166"/>
+      <c r="M11" s="166"/>
+      <c r="N11" s="165"/>
+      <c r="O11" s="165"/>
+      <c r="P11" s="167"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B12" s="123"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="107"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="130"/>
+      <c r="M12" s="130" t="s">
+        <v>174</v>
+      </c>
+      <c r="N12" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="129" t="s">
+        <v>174</v>
+      </c>
+      <c r="P12" s="131" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B13" s="123"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="131"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="146" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="158" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="159"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="163"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="161"/>
+      <c r="K14" s="165"/>
+      <c r="L14" s="166"/>
+      <c r="M14" s="166"/>
+      <c r="N14" s="165"/>
+      <c r="O14" s="165"/>
+      <c r="P14" s="167"/>
+      <c r="Q14" s="157"/>
+      <c r="R14" s="157"/>
+      <c r="S14" s="157"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="126"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="129"/>
+      <c r="L15" s="130" t="s">
+        <v>178</v>
+      </c>
+      <c r="M15" s="130" t="s">
+        <v>179</v>
+      </c>
+      <c r="N15" s="129" t="s">
+        <v>180</v>
+      </c>
+      <c r="O15" s="129" t="s">
+        <v>181</v>
+      </c>
+      <c r="P15" s="168" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B16" s="123"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="130"/>
+      <c r="M16" s="130" t="s">
+        <v>183</v>
+      </c>
+      <c r="N16" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="129" t="s">
+        <v>164</v>
+      </c>
+      <c r="P16" s="168" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B17" s="123" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="124"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="130" t="s">
+        <v>185</v>
+      </c>
+      <c r="N17" s="129" t="s">
+        <v>158</v>
+      </c>
+      <c r="O17" s="129" t="s">
+        <v>186</v>
+      </c>
+      <c r="P17" s="168" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B18" s="137" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="138"/>
+      <c r="D18" s="169"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="170"/>
+      <c r="G18" s="171"/>
+      <c r="H18" s="172"/>
+      <c r="I18" s="170"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="143"/>
+      <c r="L18" s="144"/>
+      <c r="M18" s="144" t="s">
+        <v>185</v>
+      </c>
+      <c r="N18" s="143" t="s">
+        <v>158</v>
+      </c>
+      <c r="O18" s="143" t="s">
+        <v>186</v>
+      </c>
+      <c r="P18" s="173" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="146" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="158" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="159"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="161"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="164"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="161"/>
+      <c r="K19" s="165"/>
+      <c r="L19" s="166"/>
+      <c r="M19" s="166"/>
+      <c r="N19" s="165"/>
+      <c r="O19" s="165"/>
+      <c r="P19" s="167"/>
+      <c r="Q19" s="157"/>
+      <c r="R19" s="157"/>
+      <c r="S19" s="157"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B20" s="123"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="130"/>
+      <c r="M20" s="130" t="s">
+        <v>192</v>
+      </c>
+      <c r="N20" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" s="129" t="s">
+        <v>164</v>
+      </c>
+      <c r="P20" s="168" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B21" s="123"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="125"/>
+      <c r="E21" s="126"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="130"/>
+      <c r="M21" s="130" t="s">
+        <v>185</v>
+      </c>
+      <c r="N21" s="129" t="s">
+        <v>158</v>
+      </c>
+      <c r="O21" s="129" t="s">
+        <v>186</v>
+      </c>
+      <c r="P21" s="168" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="146" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="158" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" s="159"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="163"/>
+      <c r="H22" s="164"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="165"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="166"/>
+      <c r="N22" s="165"/>
+      <c r="O22" s="165"/>
+      <c r="P22" s="167"/>
+      <c r="Q22" s="157"/>
+      <c r="R22" s="157"/>
+      <c r="S22" s="157"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="107" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="126"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="107"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="130" t="s">
+        <v>196</v>
+      </c>
+      <c r="M23" s="130"/>
+      <c r="N23" s="129"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="131"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B24" s="175"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="169"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="170"/>
+      <c r="G24" s="171"/>
+      <c r="H24" s="172"/>
+      <c r="I24" s="170"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="143"/>
+      <c r="L24" s="144"/>
+      <c r="M24" s="144" t="s">
+        <v>174</v>
+      </c>
+      <c r="N24" s="143" t="s">
+        <v>158</v>
+      </c>
+      <c r="O24" s="143" t="s">
+        <v>174</v>
+      </c>
+      <c r="P24" s="177" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="146" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="158" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="159"/>
+      <c r="D25" s="178"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="179"/>
+      <c r="H25" s="180"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="161"/>
+      <c r="K25" s="165"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="166"/>
+      <c r="N25" s="165"/>
+      <c r="O25" s="165"/>
+      <c r="P25" s="167"/>
+      <c r="Q25" s="157"/>
+      <c r="R25" s="157"/>
+      <c r="S25" s="157"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B26" s="123"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="126"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="174" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="128"/>
+      <c r="I26" s="126"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="129"/>
+      <c r="L26" s="130" t="s">
+        <v>198</v>
+      </c>
+      <c r="M26" s="130"/>
+      <c r="N26" s="129"/>
+      <c r="O26" s="129"/>
+      <c r="P26" s="131"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B27" s="123"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="130"/>
+      <c r="M27" s="130"/>
+      <c r="N27" s="129"/>
+      <c r="O27" s="129"/>
+      <c r="P27" s="131"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="146" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="158" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="159"/>
+      <c r="D28" s="160"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="164"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="161"/>
+      <c r="K28" s="165"/>
+      <c r="L28" s="166"/>
+      <c r="M28" s="166"/>
+      <c r="N28" s="165"/>
+      <c r="O28" s="165"/>
+      <c r="P28" s="167"/>
+      <c r="Q28" s="157"/>
+      <c r="R28" s="157"/>
+      <c r="S28" s="157"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B29" s="137"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="126"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="126"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="129"/>
+      <c r="L29" s="130"/>
+      <c r="M29" s="144"/>
+      <c r="N29" s="143"/>
+      <c r="O29" s="143"/>
+      <c r="P29" s="131"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="146" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="158" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="159"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="164"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="165"/>
+      <c r="L30" s="166"/>
+      <c r="M30" s="166"/>
+      <c r="N30" s="165"/>
+      <c r="O30" s="165"/>
+      <c r="P30" s="167"/>
+      <c r="Q30" s="157"/>
+      <c r="R30" s="157"/>
+      <c r="S30" s="157"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B31" s="123"/>
+      <c r="C31" s="124"/>
+      <c r="D31" s="125"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="128"/>
+      <c r="I31" s="126"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="130"/>
+      <c r="M31" s="130" t="s">
+        <v>76</v>
+      </c>
+      <c r="N31" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" s="129" t="s">
+        <v>164</v>
+      </c>
+      <c r="P31" s="131"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B32" s="123"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="127"/>
+      <c r="H32" s="128"/>
+      <c r="I32" s="126"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="129"/>
+      <c r="L32" s="130" t="s">
+        <v>201</v>
+      </c>
+      <c r="M32" s="130" t="s">
+        <v>202</v>
+      </c>
+      <c r="N32" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="129" t="s">
+        <v>203</v>
+      </c>
+      <c r="P32" s="131" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B33" s="123" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="124"/>
+      <c r="D33" s="125"/>
+      <c r="E33" s="126"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="128"/>
+      <c r="I33" s="126"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="130"/>
+      <c r="M33" s="130" t="s">
+        <v>205</v>
+      </c>
+      <c r="N33" s="129" t="s">
+        <v>158</v>
+      </c>
+      <c r="O33" s="129" t="s">
+        <v>206</v>
+      </c>
+      <c r="P33" s="131"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B34" s="137"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="140" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="170"/>
+      <c r="G34" s="171"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="140"/>
+      <c r="K34" s="143"/>
+      <c r="L34" s="144" t="s">
+        <v>207</v>
+      </c>
+      <c r="M34" s="144" t="s">
+        <v>118</v>
+      </c>
+      <c r="N34" s="143" t="s">
+        <v>158</v>
+      </c>
+      <c r="O34" s="143" t="s">
+        <v>208</v>
+      </c>
+      <c r="P34" s="145"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="181"/>
+      <c r="C35" s="182"/>
+      <c r="D35" s="183"/>
+      <c r="E35" s="183"/>
+      <c r="F35" s="184"/>
+      <c r="G35" s="184"/>
+      <c r="H35" s="184"/>
+      <c r="I35" s="184"/>
+      <c r="J35" s="183"/>
+      <c r="K35" s="183"/>
+      <c r="L35" s="181"/>
+      <c r="M35" s="181"/>
+      <c r="N35" s="181"/>
+      <c r="O35" s="183"/>
+      <c r="P35" s="183"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="130"/>
+      <c r="S35" s="130"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="185" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="186"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="126"/>
+      <c r="H36" s="126"/>
+      <c r="I36" s="126"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="185"/>
+      <c r="M36" s="185"/>
+      <c r="N36" s="185"/>
+      <c r="O36" s="107"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="130"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="187" t="s">
+        <v>211</v>
+      </c>
+      <c r="B41" s="188" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="189"/>
+      <c r="D41" s="190"/>
+      <c r="E41" s="190"/>
+      <c r="F41" s="191"/>
+      <c r="G41" s="191"/>
+      <c r="H41" s="190" t="s">
+        <v>165</v>
+      </c>
+      <c r="I41" s="191" t="s">
         <v>156</v>
       </c>
-      <c r="M3" s="124" t="s">
-        <v>157</v>
-      </c>
-      <c r="N3" s="123" t="s">
-        <v>158</v>
-      </c>
-      <c r="O3" s="123" t="s">
-        <v>159</v>
-      </c>
-      <c r="P3" s="125"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="126"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="132"/>
-      <c r="L4" s="133" t="s">
+      <c r="J41" s="191" t="s">
+        <v>166</v>
+      </c>
+      <c r="K41" s="191" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="134"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="135"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="126" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="133" t="s">
-        <v>162</v>
-      </c>
-      <c r="M5" s="134" t="s">
-        <v>163</v>
-      </c>
-      <c r="N5" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="O5" s="132" t="s">
-        <v>159</v>
-      </c>
-      <c r="P5" s="135"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="136" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="137"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="140"/>
-      <c r="H6" s="141" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="139"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="143" t="s">
-        <v>164</v>
-      </c>
-      <c r="M6" s="143" t="s">
-        <v>165</v>
-      </c>
-      <c r="N6" s="142" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" s="142" t="s">
-        <v>166</v>
-      </c>
-      <c r="P6" s="144"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="114" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="145" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="149"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="151"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="151"/>
-      <c r="O7" s="151"/>
-      <c r="P7" s="153"/>
-      <c r="Q7" s="154"/>
-      <c r="R7" s="154"/>
-      <c r="S7" s="154"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B8" s="126"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="155" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="131"/>
-      <c r="I8" s="129"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="133" t="s">
-        <v>169</v>
-      </c>
-      <c r="M8" s="134"/>
-      <c r="N8" s="132"/>
-      <c r="O8" s="132"/>
-      <c r="P8" s="135"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="114" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="156" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="157" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="158"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="159"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="161"/>
-      <c r="I9" s="159"/>
-      <c r="J9" s="162"/>
-      <c r="K9" s="163"/>
-      <c r="L9" s="164"/>
-      <c r="M9" s="164"/>
-      <c r="N9" s="163"/>
-      <c r="O9" s="163"/>
-      <c r="P9" s="165"/>
-      <c r="Q9" s="154"/>
-      <c r="R9" s="154"/>
-      <c r="S9" s="154"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B10" s="136"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="128"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="155"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="132"/>
-      <c r="L10" s="133"/>
-      <c r="M10" s="143"/>
-      <c r="N10" s="142"/>
-      <c r="O10" s="142"/>
-      <c r="P10" s="135"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A11" s="114" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="145" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11" s="146" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="158"/>
-      <c r="E11" s="159"/>
-      <c r="F11" s="159"/>
-      <c r="G11" s="160"/>
-      <c r="H11" s="161"/>
-      <c r="I11" s="159"/>
-      <c r="J11" s="162"/>
-      <c r="K11" s="163"/>
-      <c r="L11" s="164"/>
-      <c r="M11" s="152"/>
-      <c r="N11" s="151"/>
-      <c r="O11" s="151"/>
-      <c r="P11" s="165"/>
-      <c r="Q11" s="154"/>
-      <c r="R11" s="154"/>
-      <c r="S11" s="154"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B12" s="126"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="155"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="133"/>
-      <c r="M12" s="134" t="s">
-        <v>76</v>
-      </c>
-      <c r="N12" s="132" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" s="132" t="s">
-        <v>166</v>
-      </c>
-      <c r="P12" s="135"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B13" s="126"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="130"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="134" t="s">
-        <v>174</v>
-      </c>
-      <c r="M13" s="134" t="s">
-        <v>175</v>
-      </c>
-      <c r="N13" s="132" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" s="132" t="s">
-        <v>176</v>
-      </c>
-      <c r="P13" s="135" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B14" s="126" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="127"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="131"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134" t="s">
-        <v>178</v>
-      </c>
-      <c r="N14" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="O14" s="132" t="s">
-        <v>179</v>
-      </c>
-      <c r="P14" s="135"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B15" s="136"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="166"/>
-      <c r="E15" s="139" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="167"/>
-      <c r="G15" s="168"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="167"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="142"/>
-      <c r="L15" s="143" t="s">
-        <v>180</v>
-      </c>
-      <c r="M15" s="143" t="s">
-        <v>118</v>
-      </c>
-      <c r="N15" s="142" t="s">
-        <v>158</v>
-      </c>
-      <c r="O15" s="142" t="s">
-        <v>181</v>
-      </c>
-      <c r="P15" s="144"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="145" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" s="146"/>
-      <c r="D16" s="170"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="171"/>
-      <c r="G16" s="172"/>
-      <c r="H16" s="173"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="151"/>
-      <c r="L16" s="152"/>
-      <c r="M16" s="152"/>
-      <c r="N16" s="151"/>
-      <c r="O16" s="151"/>
-      <c r="P16" s="153"/>
-      <c r="Q16" s="154"/>
-      <c r="R16" s="154"/>
-      <c r="S16" s="154"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B17" s="126"/>
-      <c r="C17" s="127"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="131"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="132"/>
-      <c r="L17" s="133" t="s">
-        <v>183</v>
-      </c>
-      <c r="M17" s="133"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="132"/>
-      <c r="P17" s="135"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B18" s="126"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="131"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="107"/>
-      <c r="K18" s="132"/>
-      <c r="L18" s="133" t="s">
-        <v>184</v>
-      </c>
-      <c r="M18" s="133"/>
-      <c r="N18" s="132"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="135"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B19" s="126"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="131"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="133" t="s">
-        <v>185</v>
-      </c>
-      <c r="M19" s="133"/>
-      <c r="N19" s="132"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="135"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="114" t="s">
-        <v>186</v>
-      </c>
-      <c r="B20" s="156" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="157" t="s">
-        <v>187</v>
-      </c>
-      <c r="D20" s="158"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="161"/>
-      <c r="I20" s="159"/>
-      <c r="J20" s="162"/>
-      <c r="K20" s="163"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="164"/>
-      <c r="N20" s="163"/>
-      <c r="O20" s="163"/>
-      <c r="P20" s="165"/>
-      <c r="Q20" s="154"/>
-      <c r="R20" s="154"/>
-      <c r="S20" s="154"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B21" s="126"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="133" t="s">
-        <v>188</v>
-      </c>
-      <c r="N21" s="132" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="132" t="s">
-        <v>188</v>
-      </c>
-      <c r="P21" s="135" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="114" t="s">
-        <v>190</v>
-      </c>
-      <c r="B22" s="156" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="157" t="s">
-        <v>191</v>
-      </c>
-      <c r="D22" s="158"/>
-      <c r="E22" s="162"/>
-      <c r="F22" s="159"/>
-      <c r="G22" s="174"/>
-      <c r="H22" s="161"/>
-      <c r="I22" s="159"/>
-      <c r="J22" s="162"/>
-      <c r="K22" s="163"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="164"/>
-      <c r="N22" s="163"/>
-      <c r="O22" s="163"/>
-      <c r="P22" s="165"/>
-      <c r="Q22" s="154"/>
-      <c r="R22" s="154"/>
-      <c r="S22" s="154"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B23" s="126"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="131"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="132"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="134" t="s">
-        <v>192</v>
-      </c>
-      <c r="N23" s="132" t="n">
-        <v>4</v>
-      </c>
-      <c r="O23" s="132" t="s">
-        <v>166</v>
-      </c>
-      <c r="P23" s="175" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B24" s="126"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="129"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="132"/>
-      <c r="L24" s="134" t="s">
-        <v>194</v>
-      </c>
-      <c r="M24" s="134" t="s">
-        <v>195</v>
-      </c>
-      <c r="N24" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="O24" s="132" t="s">
-        <v>197</v>
-      </c>
-      <c r="P24" s="175" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B25" s="126" t="s">
-        <v>194</v>
-      </c>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="130"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="132"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="134" t="s">
-        <v>199</v>
-      </c>
-      <c r="N25" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="O25" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="P25" s="175" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B26" s="136" t="s">
-        <v>202</v>
-      </c>
-      <c r="C26" s="137"/>
-      <c r="D26" s="166"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="167"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="167"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="142"/>
-      <c r="L26" s="143"/>
-      <c r="M26" s="143" t="s">
-        <v>199</v>
-      </c>
-      <c r="N26" s="142" t="s">
-        <v>158</v>
-      </c>
-      <c r="O26" s="142" t="s">
-        <v>200</v>
-      </c>
-      <c r="P26" s="176" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="114" t="s">
-        <v>204</v>
-      </c>
-      <c r="B27" s="156" t="s">
-        <v>185</v>
-      </c>
-      <c r="C27" s="157" t="s">
-        <v>205</v>
-      </c>
-      <c r="D27" s="158"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="174"/>
-      <c r="H27" s="161"/>
-      <c r="I27" s="159"/>
-      <c r="J27" s="162"/>
-      <c r="K27" s="163"/>
-      <c r="L27" s="164"/>
-      <c r="M27" s="164"/>
-      <c r="N27" s="163"/>
-      <c r="O27" s="163"/>
-      <c r="P27" s="165"/>
-      <c r="Q27" s="154"/>
-      <c r="R27" s="154"/>
-      <c r="S27" s="154"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B28" s="126"/>
-      <c r="C28" s="127"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="155"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="132"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="134" t="s">
-        <v>206</v>
-      </c>
-      <c r="N28" s="132" t="n">
-        <v>4</v>
-      </c>
-      <c r="O28" s="132" t="s">
-        <v>166</v>
-      </c>
-      <c r="P28" s="175" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B29" s="126"/>
-      <c r="C29" s="127"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="129"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="132"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="134" t="s">
-        <v>199</v>
-      </c>
-      <c r="N29" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="O29" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="P29" s="175" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A30" s="114" t="s">
-        <v>208</v>
-      </c>
-      <c r="B30" s="156" t="s">
-        <v>209</v>
-      </c>
-      <c r="C30" s="157" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="158"/>
-      <c r="E30" s="162"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="161"/>
-      <c r="I30" s="159"/>
-      <c r="J30" s="162"/>
-      <c r="K30" s="163"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="164"/>
-      <c r="N30" s="163"/>
-      <c r="O30" s="163"/>
-      <c r="P30" s="165"/>
-      <c r="Q30" s="154"/>
-      <c r="R30" s="154"/>
-      <c r="S30" s="154"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B31" s="126"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="107" t="s">
-        <v>50</v>
-      </c>
-      <c r="F31" s="129"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="132"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="133" t="s">
-        <v>210</v>
-      </c>
-      <c r="N31" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="O31" s="132" t="s">
-        <v>159</v>
-      </c>
-      <c r="P31" s="135" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B32" s="177"/>
-      <c r="C32" s="178"/>
-      <c r="D32" s="166"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="167"/>
-      <c r="G32" s="168"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="167"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="143"/>
-      <c r="M32" s="143" t="s">
-        <v>188</v>
-      </c>
-      <c r="N32" s="142" t="s">
-        <v>158</v>
-      </c>
-      <c r="O32" s="142" t="s">
-        <v>188</v>
-      </c>
-      <c r="P32" s="179" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="134"/>
-      <c r="C33" s="180"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="129"/>
-      <c r="G33" s="129"/>
-      <c r="H33" s="129"/>
-      <c r="I33" s="129"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="134"/>
-      <c r="M33" s="134"/>
-      <c r="N33" s="134"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="134"/>
-      <c r="S33" s="134"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="181" t="s">
-        <v>154</v>
-      </c>
-      <c r="C34" s="182"/>
-      <c r="D34" s="129"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="129"/>
-      <c r="G34" s="129"/>
-      <c r="H34" s="129"/>
-      <c r="I34" s="129"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="181"/>
-      <c r="M34" s="181"/>
-      <c r="N34" s="181"/>
-      <c r="O34" s="107"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
-      <c r="S34" s="134"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="s">
+      <c r="L41" s="188" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="5" t="s">
+      <c r="M41" s="192" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="183" t="s">
+      <c r="N41" s="187" t="s">
         <v>214</v>
       </c>
-      <c r="B39" s="184" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" s="185"/>
-      <c r="D39" s="186"/>
-      <c r="E39" s="186"/>
-      <c r="F39" s="187"/>
-      <c r="G39" s="187"/>
-      <c r="H39" s="186" t="s">
-        <v>168</v>
-      </c>
-      <c r="I39" s="187" t="s">
-        <v>162</v>
-      </c>
-      <c r="J39" s="187" t="s">
-        <v>160</v>
-      </c>
-      <c r="K39" s="187" t="s">
-        <v>156</v>
-      </c>
-      <c r="L39" s="184" t="s">
-        <v>215</v>
-      </c>
-      <c r="M39" s="188" t="s">
-        <v>216</v>
-      </c>
-      <c r="N39" s="183" t="s">
-        <v>217</v>
-      </c>
-      <c r="O39" s="184"/>
-      <c r="P39" s="183"/>
-      <c r="Q39" s="183"/>
-      <c r="R39" s="183"/>
-      <c r="S39" s="183"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="189"/>
-      <c r="B40" s="2" t="str">
-        <f aca="false">DEC2HEX(L40,2)</f>
-        <v>02</v>
-      </c>
-      <c r="D40" s="190"/>
-      <c r="E40" s="191"/>
-      <c r="F40" s="191"/>
-      <c r="G40" s="192"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="191"/>
-      <c r="J40" s="191" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="194" t="s">
-        <v>68</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <f aca="false">IF(D40=1,128,0)+IF(E40=1,64,0)+IF(F40=1,32,0)+IF(G40=1,16,0)+IF(H40=1,8,0)+IF(I40=1,4,0)+IF(J40=1,2,0)+IF(K40=1,1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="M40" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="N40" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
-      <c r="S40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="189"/>
-      <c r="B41" s="2" t="str">
-        <f aca="false">DEC2HEX(L41,2)</f>
-        <v>08</v>
-      </c>
-      <c r="D41" s="195"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="196" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="132" t="s">
-        <v>68</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <f aca="false">IF(D41=1,128,0)+IF(E41=1,64,0)+IF(F41=1,32,0)+IF(G41=1,16,0)+IF(H41=1,8,0)+IF(I41=1,4,0)+IF(J41=1,2,0)+IF(K41=1,1,0)</f>
-        <v>8</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="N41" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
+      <c r="O41" s="188"/>
+      <c r="P41" s="187"/>
+      <c r="Q41" s="187"/>
+      <c r="R41" s="187"/>
+      <c r="S41" s="187"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="189"/>
+      <c r="A42" s="193"/>
       <c r="B42" s="2" t="str">
         <f aca="false">DEC2HEX(L42,2)</f>
-        <v>18</v>
-      </c>
-      <c r="D42" s="195"/>
-      <c r="E42" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G42" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="196" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="132" t="s">
+        <v>02</v>
+      </c>
+      <c r="D42" s="194"/>
+      <c r="E42" s="195"/>
+      <c r="F42" s="195"/>
+      <c r="G42" s="196"/>
+      <c r="H42" s="197"/>
+      <c r="I42" s="195"/>
+      <c r="J42" s="195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="198" t="s">
         <v>68</v>
       </c>
       <c r="L42" s="2" t="n">
         <f aca="false">IF(D42=1,128,0)+IF(E42=1,64,0)+IF(F42=1,32,0)+IF(G42=1,16,0)+IF(H42=1,8,0)+IF(I42=1,4,0)+IF(J42=1,2,0)+IF(K42=1,1,0)</f>
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
@@ -7378,21 +7625,19 @@
       <c r="S42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="189"/>
+      <c r="A43" s="193"/>
       <c r="B43" s="2" t="str">
         <f aca="false">DEC2HEX(L43,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D43" s="195"/>
+        <v>08</v>
+      </c>
+      <c r="D43" s="199"/>
       <c r="E43" s="13"/>
-      <c r="F43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="196" t="n">
-        <v>0</v>
+      <c r="F43" s="13"/>
+      <c r="G43" s="174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="200" t="n">
+        <v>1</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>68</v>
@@ -7400,18 +7645,18 @@
       <c r="J43" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="132" t="s">
+      <c r="K43" s="129" t="s">
         <v>68</v>
       </c>
       <c r="L43" s="2" t="n">
         <f aca="false">IF(D43=1,128,0)+IF(E43=1,64,0)+IF(F43=1,32,0)+IF(G43=1,16,0)+IF(H43=1,8,0)+IF(I43=1,4,0)+IF(J43=1,2,0)+IF(K43=1,1,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
@@ -7419,21 +7664,23 @@
       <c r="S43" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="189"/>
+      <c r="A44" s="193"/>
       <c r="B44" s="2" t="str">
         <f aca="false">DEC2HEX(L44,2)</f>
-        <v>10</v>
-      </c>
-      <c r="D44" s="195"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="196" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="D44" s="199"/>
+      <c r="E44" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="200" t="n">
+        <v>1</v>
       </c>
       <c r="I44" s="13" t="s">
         <v>68</v>
@@ -7441,40 +7688,39 @@
       <c r="J44" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="132" t="s">
+      <c r="K44" s="129" t="s">
         <v>68</v>
       </c>
       <c r="L44" s="2" t="n">
         <f aca="false">IF(D44=1,128,0)+IF(E44=1,64,0)+IF(F44=1,32,0)+IF(G44=1,16,0)+IF(H44=1,8,0)+IF(I44=1,4,0)+IF(J44=1,2,0)+IF(K44=1,1,0)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="O44" s="0"/>
+        <v>219</v>
+      </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
       <c r="S44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="189"/>
+      <c r="A45" s="193"/>
       <c r="B45" s="2" t="str">
         <f aca="false">DEC2HEX(L45,2)</f>
-        <v>20</v>
-      </c>
-      <c r="D45" s="195"/>
+        <v>00</v>
+      </c>
+      <c r="D45" s="199"/>
       <c r="E45" s="13"/>
       <c r="F45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="200" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="13" t="s">
@@ -7483,18 +7729,18 @@
       <c r="J45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K45" s="132" t="s">
+      <c r="K45" s="129" t="s">
         <v>68</v>
       </c>
       <c r="L45" s="2" t="n">
         <f aca="false">IF(D45=1,128,0)+IF(E45=1,64,0)+IF(F45=1,32,0)+IF(G45=1,16,0)+IF(H45=1,8,0)+IF(I45=1,4,0)+IF(J45=1,2,0)+IF(K45=1,1,0)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
@@ -7502,52 +7748,137 @@
       <c r="S45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="189"/>
+      <c r="A46" s="193"/>
       <c r="B46" s="2" t="str">
         <f aca="false">DEC2HEX(L46,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D46" s="197"/>
-      <c r="E46" s="139" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="199"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F46" s="139" t="s">
-        <v>68</v>
-      </c>
-      <c r="G46" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="H46" s="141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="139" t="s">
-        <v>68</v>
-      </c>
-      <c r="J46" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="142" t="s">
+      <c r="J46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="129" t="s">
         <v>68</v>
       </c>
       <c r="L46" s="2" t="n">
         <f aca="false">IF(D46=1,128,0)+IF(E46=1,64,0)+IF(F46=1,32,0)+IF(G46=1,16,0)+IF(H46=1,8,0)+IF(I46=1,4,0)+IF(J46=1,2,0)+IF(K46=1,1,0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>225</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O46" s="1"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
       <c r="S46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M47" s="0"/>
-      <c r="N47" s="0"/>
-    </row>
+      <c r="A47" s="193"/>
+      <c r="B47" s="2" t="str">
+        <f aca="false">DEC2HEX(L47,2)</f>
+        <v>20</v>
+      </c>
+      <c r="D47" s="199"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="129" t="s">
+        <v>68</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <f aca="false">IF(D47=1,128,0)+IF(E47=1,64,0)+IF(F47=1,32,0)+IF(G47=1,16,0)+IF(H47=1,8,0)+IF(I47=1,4,0)+IF(J47=1,2,0)+IF(K47=1,1,0)</f>
+        <v>32</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N47" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="193"/>
+      <c r="B48" s="2" t="str">
+        <f aca="false">DEC2HEX(L48,2)</f>
+        <v>00</v>
+      </c>
+      <c r="D48" s="201"/>
+      <c r="E48" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="F48" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="G48" s="202" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="J48" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="143" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <f aca="false">IF(D48=1,128,0)+IF(E48=1,64,0)+IF(F48=1,32,0)+IF(G48=1,16,0)+IF(H48=1,8,0)+IF(I48=1,4,0)+IF(J48=1,2,0)+IF(K48=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="N48" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7570,7 +7901,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P1048576"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="18.74"/>
@@ -7585,8 +7916,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="198"/>
-      <c r="B1" s="199" t="s">
+      <c r="A1" s="203"/>
+      <c r="B1" s="204" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="17" t="s">
@@ -7598,10 +7929,10 @@
       <c r="E1" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="200" t="n">
+      <c r="F1" s="205" t="n">
         <v>6</v>
       </c>
-      <c r="G1" s="200" t="n">
+      <c r="G1" s="205" t="n">
         <v>5</v>
       </c>
       <c r="H1" s="27" t="n">
@@ -7610,96 +7941,96 @@
       <c r="I1" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J1" s="200" t="n">
+      <c r="J1" s="205" t="n">
         <v>2</v>
       </c>
-      <c r="K1" s="200" t="n">
+      <c r="K1" s="205" t="n">
         <v>1</v>
       </c>
       <c r="L1" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M1" s="201" t="s">
+      <c r="M1" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="201" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="202" t="s">
+      <c r="N1" s="206" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="207" t="s">
         <v>153</v>
       </c>
-      <c r="P1" s="203" t="s">
+      <c r="P1" s="208" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="204" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="205"/>
-      <c r="C2" s="206" t="str">
+      <c r="A2" s="209" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="210"/>
+      <c r="C2" s="211" t="str">
         <f aca="false">DEC2HEX(D2,2)</f>
         <v>00</v>
       </c>
-      <c r="D2" s="162" t="n">
+      <c r="D2" s="161" t="n">
         <f aca="false">IF(E2=1,128,0)+IF(F2=1,64,0)+IF(G2=1,32,0)+IF(H2=1,16,0)+IF(I2=1,8,0)+IF(J2=1,4,0)+IF(K2=1,2,0)+IF(L2=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E2" s="207"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="208" t="s">
-        <v>227</v>
-      </c>
-      <c r="N2" s="205"/>
-      <c r="O2" s="209"/>
-      <c r="P2" s="210"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="211"/>
-      <c r="B3" s="133"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="212" t="s">
+        <v>226</v>
+      </c>
+      <c r="N2" s="210"/>
+      <c r="O2" s="213"/>
+      <c r="P2" s="214"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A3" s="215"/>
+      <c r="B3" s="130"/>
       <c r="C3" s="17"/>
       <c r="D3" s="107"/>
       <c r="E3" s="49"/>
       <c r="F3" s="107"/>
       <c r="G3" s="107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="13"/>
       <c r="K3" s="107"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="212" t="s">
+      <c r="M3" s="216"/>
+      <c r="N3" s="216" t="s">
+        <v>228</v>
+      </c>
+      <c r="O3" s="217" t="s">
         <v>229</v>
       </c>
-      <c r="O3" s="213" t="s">
-        <v>230</v>
-      </c>
-      <c r="P3" s="214"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="211"/>
-      <c r="B4" s="133"/>
+      <c r="P3" s="218"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A4" s="215"/>
+      <c r="B4" s="130"/>
       <c r="E4" s="49"/>
       <c r="F4" s="107" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G4" s="107"/>
       <c r="H4" s="50"/>
@@ -7707,21 +8038,19 @@
       <c r="J4" s="13"/>
       <c r="K4" s="107"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="212" t="s">
-        <v>232</v>
+      <c r="M4" s="216" t="s">
+        <v>231</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
-      <c r="P4" s="215"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="211"/>
-      <c r="B5" s="133"/>
+      <c r="P4" s="219"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A5" s="215"/>
+      <c r="B5" s="130"/>
       <c r="C5" s="17"/>
       <c r="D5" s="107"/>
-      <c r="E5" s="49" t="s">
-        <v>233</v>
-      </c>
+      <c r="E5" s="49"/>
       <c r="F5" s="107"/>
       <c r="G5" s="107"/>
       <c r="H5" s="50"/>
@@ -7729,16 +8058,14 @@
       <c r="J5" s="13"/>
       <c r="K5" s="107"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O5" s="213"/>
-      <c r="P5" s="214"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A6" s="211"/>
-      <c r="B6" s="133" t="s">
-        <v>234</v>
+      <c r="M5" s="216"/>
+      <c r="O5" s="217"/>
+      <c r="P5" s="218"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A6" s="215"/>
+      <c r="B6" s="130" t="s">
+        <v>232</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="107"/>
@@ -7748,87 +8075,85 @@
       <c r="J6" s="13"/>
       <c r="K6" s="107"/>
       <c r="L6" s="50"/>
-      <c r="M6" s="212"/>
+      <c r="M6" s="216"/>
       <c r="N6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="P6" s="215"/>
+        <v>233</v>
+      </c>
+      <c r="P6" s="219"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="204" t="s">
-        <v>236</v>
-      </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="206" t="str">
+      <c r="A7" s="209" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="210"/>
+      <c r="C7" s="211" t="str">
         <f aca="false">DEC2HEX(D7,2)</f>
         <v>01</v>
       </c>
-      <c r="D7" s="162" t="n">
+      <c r="D7" s="161" t="n">
         <f aca="false">IF(E7=1,128,0)+IF(F7=1,64,0)+IF(G7=1,32,0)+IF(H7=1,16,0)+IF(I7=1,8,0)+IF(J7=1,4,0)+IF(K7=1,2,0)+IF(L7=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="207"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="163"/>
-      <c r="I7" s="207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="163" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="208" t="s">
-        <v>237</v>
-      </c>
-      <c r="N7" s="205"/>
-      <c r="O7" s="208"/>
-      <c r="P7" s="210"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="211"/>
-      <c r="B8" s="133"/>
+      <c r="E7" s="178"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="161"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="212" t="s">
+        <v>235</v>
+      </c>
+      <c r="N7" s="210"/>
+      <c r="O7" s="212"/>
+      <c r="P7" s="214"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A8" s="215"/>
+      <c r="B8" s="130"/>
       <c r="C8" s="17"/>
       <c r="D8" s="107"/>
       <c r="E8" s="49"/>
       <c r="F8" s="107"/>
       <c r="G8" s="107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I8" s="49"/>
       <c r="J8" s="13"/>
       <c r="K8" s="107"/>
       <c r="L8" s="50"/>
-      <c r="M8" s="212"/>
+      <c r="M8" s="216"/>
       <c r="N8" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="O8" s="217" t="s">
         <v>229</v>
       </c>
-      <c r="O8" s="213" t="s">
-        <v>230</v>
-      </c>
-      <c r="P8" s="214" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="211"/>
-      <c r="B9" s="133"/>
+      <c r="P8" s="218" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A9" s="215"/>
+      <c r="B9" s="130"/>
       <c r="C9" s="17"/>
       <c r="D9" s="107"/>
-      <c r="E9" s="49" t="s">
-        <v>233</v>
-      </c>
+      <c r="E9" s="49"/>
       <c r="F9" s="107"/>
       <c r="G9" s="107"/>
       <c r="H9" s="50"/>
@@ -7836,22 +8161,20 @@
       <c r="J9" s="13"/>
       <c r="K9" s="107"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O9" s="213"/>
-      <c r="P9" s="214"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="211"/>
-      <c r="B10" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="216"/>
+      <c r="M9" s="216"/>
+      <c r="O9" s="217"/>
+      <c r="P9" s="218"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A10" s="215"/>
+      <c r="B10" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="134"/>
       <c r="F10" s="107"/>
       <c r="G10" s="107"/>
       <c r="H10" s="50"/>
-      <c r="I10" s="216"/>
+      <c r="I10" s="134"/>
       <c r="J10" s="107"/>
       <c r="K10" s="107"/>
       <c r="L10" s="50"/>
@@ -7860,82 +8183,80 @@
         <v>1</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="P10" s="215"/>
+        <v>233</v>
+      </c>
+      <c r="P10" s="219"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="204" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="205"/>
-      <c r="C11" s="206" t="str">
+      <c r="A11" s="209" t="s">
+        <v>237</v>
+      </c>
+      <c r="B11" s="210"/>
+      <c r="C11" s="211" t="str">
         <f aca="false">DEC2HEX(D11,2)</f>
         <v>02</v>
       </c>
-      <c r="D11" s="162" t="n">
+      <c r="D11" s="161" t="n">
         <f aca="false">IF(E11=1,128,0)+IF(F11=1,64,0)+IF(G11=1,32,0)+IF(H11=1,16,0)+IF(I11=1,8,0)+IF(J11=1,4,0)+IF(K11=1,2,0)+IF(L11=1,1,0)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="207"/>
-      <c r="F11" s="162"/>
-      <c r="G11" s="162"/>
-      <c r="H11" s="163"/>
-      <c r="I11" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="208" t="s">
-        <v>240</v>
-      </c>
-      <c r="N11" s="205"/>
-      <c r="O11" s="209"/>
-      <c r="P11" s="210"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A12" s="211"/>
-      <c r="B12" s="133"/>
+      <c r="E11" s="178"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="161"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="212" t="s">
+        <v>238</v>
+      </c>
+      <c r="N11" s="210"/>
+      <c r="O11" s="213"/>
+      <c r="P11" s="214"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A12" s="215"/>
+      <c r="B12" s="130"/>
       <c r="C12" s="17"/>
       <c r="D12" s="107"/>
       <c r="E12" s="49"/>
       <c r="F12" s="107"/>
       <c r="G12" s="107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I12" s="49"/>
       <c r="J12" s="13"/>
       <c r="K12" s="107"/>
       <c r="L12" s="50"/>
-      <c r="M12" s="212"/>
-      <c r="N12" s="212" t="s">
-        <v>241</v>
-      </c>
-      <c r="O12" s="213" t="s">
-        <v>230</v>
-      </c>
-      <c r="P12" s="217" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="211"/>
-      <c r="B13" s="133"/>
+      <c r="M12" s="216"/>
+      <c r="N12" s="216" t="s">
+        <v>239</v>
+      </c>
+      <c r="O12" s="217" t="s">
+        <v>229</v>
+      </c>
+      <c r="P12" s="220" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A13" s="215"/>
+      <c r="B13" s="130"/>
       <c r="C13" s="17"/>
       <c r="D13" s="107"/>
-      <c r="E13" s="49" t="s">
-        <v>233</v>
-      </c>
+      <c r="E13" s="49"/>
       <c r="F13" s="107"/>
       <c r="G13" s="107"/>
       <c r="H13" s="50"/>
@@ -7943,16 +8264,14 @@
       <c r="J13" s="13"/>
       <c r="K13" s="107"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O13" s="213"/>
-      <c r="P13" s="214"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="211"/>
-      <c r="B14" s="133" t="s">
-        <v>234</v>
+      <c r="M13" s="216"/>
+      <c r="O13" s="217"/>
+      <c r="P13" s="218"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A14" s="215"/>
+      <c r="B14" s="130" t="s">
+        <v>232</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="107"/>
@@ -7962,61 +8281,59 @@
       <c r="J14" s="13"/>
       <c r="K14" s="107"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="212"/>
+      <c r="M14" s="216"/>
       <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="P14" s="215" t="s">
-        <v>244</v>
+        <v>241</v>
+      </c>
+      <c r="P14" s="219" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="204" t="s">
+      <c r="A15" s="209" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="205"/>
-      <c r="C15" s="206" t="str">
+      <c r="B15" s="210"/>
+      <c r="C15" s="211" t="str">
         <f aca="false">DEC2HEX(D15,2)</f>
         <v>03</v>
       </c>
-      <c r="D15" s="162" t="n">
+      <c r="D15" s="161" t="n">
         <f aca="false">IF(E15=1,128,0)+IF(F15=1,64,0)+IF(G15=1,32,0)+IF(H15=1,16,0)+IF(I15=1,8,0)+IF(J15=1,4,0)+IF(K15=1,2,0)+IF(L15=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="E15" s="207"/>
-      <c r="F15" s="162"/>
-      <c r="G15" s="162"/>
-      <c r="H15" s="163"/>
-      <c r="I15" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="163" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="208" t="s">
+      <c r="E15" s="178"/>
+      <c r="F15" s="161"/>
+      <c r="G15" s="161"/>
+      <c r="H15" s="165"/>
+      <c r="I15" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="212" t="s">
         <v>97</v>
       </c>
-      <c r="N15" s="205"/>
-      <c r="O15" s="208"/>
-      <c r="P15" s="210"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A16" s="211"/>
-      <c r="B16" s="133"/>
+      <c r="N15" s="210"/>
+      <c r="O15" s="212"/>
+      <c r="P15" s="214"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A16" s="215"/>
+      <c r="B16" s="130"/>
       <c r="C16" s="17"/>
       <c r="D16" s="107"/>
-      <c r="E16" s="49" t="s">
-        <v>233</v>
-      </c>
+      <c r="E16" s="49"/>
       <c r="F16" s="107"/>
       <c r="G16" s="107"/>
       <c r="H16" s="50"/>
@@ -8024,15 +8341,15 @@
       <c r="J16" s="13"/>
       <c r="K16" s="107"/>
       <c r="L16" s="50"/>
-      <c r="M16" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O16" s="213"/>
-      <c r="P16" s="214"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A17" s="211"/>
-      <c r="B17" s="133"/>
+      <c r="M16" s="216"/>
+      <c r="O16" s="217"/>
+      <c r="P16" s="218"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A17" s="215"/>
+      <c r="B17" s="130" t="s">
+        <v>232</v>
+      </c>
       <c r="C17" s="17"/>
       <c r="D17" s="107"/>
       <c r="E17" s="49"/>
@@ -8043,27 +8360,27 @@
       <c r="J17" s="13"/>
       <c r="K17" s="107"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="212"/>
+      <c r="M17" s="216"/>
       <c r="N17" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="O17" s="217" t="s">
+        <v>244</v>
+      </c>
+      <c r="P17" s="218" t="s">
         <v>245</v>
       </c>
-      <c r="O17" s="213" t="s">
-        <v>246</v>
-      </c>
-      <c r="P17" s="214" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="211"/>
-      <c r="B18" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="E18" s="216"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A18" s="215"/>
+      <c r="B18" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" s="134"/>
       <c r="F18" s="107"/>
       <c r="G18" s="107"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="216"/>
+      <c r="I18" s="134"/>
       <c r="J18" s="107"/>
       <c r="K18" s="107"/>
       <c r="L18" s="50"/>
@@ -8072,58 +8389,58 @@
         <v>1</v>
       </c>
       <c r="O18" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="P18" s="221" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="209" t="s">
         <v>248</v>
       </c>
-      <c r="P18" s="218" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="204" t="s">
-        <v>250</v>
-      </c>
-      <c r="B19" s="205"/>
-      <c r="C19" s="206" t="str">
+      <c r="B19" s="210"/>
+      <c r="C19" s="211" t="str">
         <f aca="false">DEC2HEX(D19,2)</f>
         <v>04</v>
       </c>
-      <c r="D19" s="162" t="n">
+      <c r="D19" s="161" t="n">
         <f aca="false">IF(E19=1,128,0)+IF(F19=1,64,0)+IF(G19=1,32,0)+IF(H19=1,16,0)+IF(I19=1,8,0)+IF(J19=1,4,0)+IF(K19=1,2,0)+IF(L19=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E19" s="207"/>
-      <c r="F19" s="162"/>
-      <c r="G19" s="162"/>
-      <c r="H19" s="163"/>
-      <c r="I19" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="208" t="s">
-        <v>251</v>
-      </c>
-      <c r="N19" s="205"/>
-      <c r="O19" s="208"/>
-      <c r="P19" s="210"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="211"/>
-      <c r="B20" s="133"/>
-      <c r="E20" s="216"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="161"/>
+      <c r="G19" s="161"/>
+      <c r="H19" s="165"/>
+      <c r="I19" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="212" t="s">
+        <v>249</v>
+      </c>
+      <c r="N19" s="210"/>
+      <c r="O19" s="212"/>
+      <c r="P19" s="214"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A20" s="215"/>
+      <c r="B20" s="130"/>
+      <c r="E20" s="134"/>
       <c r="F20" s="107"/>
       <c r="G20" s="107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I20" s="107"/>
       <c r="J20" s="107"/>
@@ -8131,19 +8448,19 @@
       <c r="L20" s="50"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="O20" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="O20" s="14" t="s">
+      <c r="P20" s="218"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A21" s="215"/>
+      <c r="B21" s="130"/>
+      <c r="E21" s="134"/>
+      <c r="F21" s="107" t="s">
         <v>230</v>
-      </c>
-      <c r="P20" s="214"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="211"/>
-      <c r="B21" s="134"/>
-      <c r="E21" s="216"/>
-      <c r="F21" s="107" t="s">
-        <v>231</v>
       </c>
       <c r="G21" s="107"/>
       <c r="H21" s="50"/>
@@ -8152,18 +8469,20 @@
       <c r="K21" s="107"/>
       <c r="L21" s="50"/>
       <c r="M21" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N21" s="10"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="214" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="211"/>
-      <c r="B22" s="134"/>
-      <c r="E22" s="216"/>
+      <c r="O21" s="130"/>
+      <c r="P21" s="218" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22" s="222" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A22" s="215"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="134"/>
       <c r="F22" s="107"/>
       <c r="G22" s="107"/>
       <c r="H22" s="50"/>
@@ -8173,40 +8492,43 @@
       <c r="L22" s="50"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="O22" s="130" t="s">
+        <v>72</v>
+      </c>
+      <c r="P22" s="218"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A23" s="223"/>
+      <c r="B23" s="224"/>
+      <c r="C23" s="225"/>
+      <c r="D23" s="226"/>
+      <c r="E23" s="227" t="s">
+        <v>253</v>
+      </c>
+      <c r="F23" s="226"/>
+      <c r="G23" s="226"/>
+      <c r="H23" s="228"/>
+      <c r="I23" s="227"/>
+      <c r="J23" s="229"/>
+      <c r="K23" s="226"/>
+      <c r="L23" s="228"/>
+      <c r="M23" s="230" t="s">
         <v>254</v>
       </c>
-      <c r="O22" s="134" t="s">
-        <v>72</v>
-      </c>
-      <c r="P22" s="214"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="211"/>
-      <c r="B23" s="133"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O23" s="213"/>
-      <c r="P23" s="214"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="211"/>
-      <c r="B24" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="E24" s="216"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="231"/>
+      <c r="P23" s="232" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A24" s="215"/>
+      <c r="B24" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="134"/>
       <c r="F24" s="107"/>
       <c r="G24" s="107"/>
       <c r="H24" s="50"/>
@@ -8217,54 +8539,54 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="P24" s="214" t="s">
         <v>256</v>
       </c>
+      <c r="P24" s="218" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="204" t="s">
-        <v>257</v>
-      </c>
-      <c r="B25" s="205"/>
-      <c r="C25" s="206" t="str">
+      <c r="A25" s="209" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="210"/>
+      <c r="C25" s="211" t="str">
         <f aca="false">DEC2HEX(D25,2)</f>
         <v>05</v>
       </c>
-      <c r="D25" s="162" t="n">
+      <c r="D25" s="161" t="n">
         <f aca="false">IF(E25=1,128,0)+IF(F25=1,64,0)+IF(G25=1,32,0)+IF(H25=1,16,0)+IF(I25=1,8,0)+IF(J25=1,4,0)+IF(K25=1,2,0)+IF(L25=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E25" s="207"/>
-      <c r="F25" s="162"/>
-      <c r="G25" s="162"/>
-      <c r="H25" s="163"/>
-      <c r="I25" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="163" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="208" t="s">
-        <v>258</v>
-      </c>
-      <c r="N25" s="205"/>
-      <c r="O25" s="208"/>
-      <c r="P25" s="210"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="211"/>
-      <c r="B26" s="134"/>
-      <c r="E26" s="216"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="161"/>
+      <c r="H25" s="165"/>
+      <c r="I25" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="212" t="s">
+        <v>259</v>
+      </c>
+      <c r="N25" s="210"/>
+      <c r="O25" s="212"/>
+      <c r="P25" s="214"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A26" s="215"/>
+      <c r="B26" s="130"/>
+      <c r="E26" s="134"/>
       <c r="F26" s="107" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G26" s="107"/>
       <c r="H26" s="50"/>
@@ -8273,18 +8595,18 @@
       <c r="K26" s="107"/>
       <c r="L26" s="50"/>
       <c r="M26" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N26" s="10"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="214" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="211"/>
-      <c r="B27" s="134"/>
-      <c r="E27" s="216"/>
+      <c r="O26" s="130"/>
+      <c r="P26" s="218" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A27" s="215"/>
+      <c r="B27" s="130"/>
+      <c r="E27" s="134"/>
       <c r="F27" s="107"/>
       <c r="G27" s="107"/>
       <c r="H27" s="50"/>
@@ -8294,21 +8616,19 @@
       <c r="L27" s="50"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="O27" s="134" t="s">
+        <v>252</v>
+      </c>
+      <c r="O27" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="P27" s="214"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="211"/>
-      <c r="B28" s="133"/>
+      <c r="P27" s="218"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A28" s="215"/>
+      <c r="B28" s="130"/>
       <c r="C28" s="17"/>
       <c r="D28" s="107"/>
-      <c r="E28" s="49" t="s">
-        <v>233</v>
-      </c>
+      <c r="E28" s="49"/>
       <c r="F28" s="107"/>
       <c r="G28" s="107"/>
       <c r="H28" s="50"/>
@@ -8316,350 +8636,353 @@
       <c r="J28" s="13"/>
       <c r="K28" s="107"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O28" s="213"/>
-      <c r="P28" s="214"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="211"/>
-      <c r="B29" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="E29" s="216"/>
+      <c r="M28" s="216"/>
+      <c r="O28" s="217"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A29" s="215"/>
+      <c r="B29" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="C29" s="17"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="49"/>
       <c r="F29" s="107"/>
       <c r="G29" s="107"/>
       <c r="H29" s="50"/>
-      <c r="I29" s="216"/>
-      <c r="J29" s="107"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="13"/>
       <c r="K29" s="107"/>
       <c r="L29" s="50"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O29" s="14" t="s">
-        <v>260</v>
+      <c r="M29" s="216"/>
+      <c r="N29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="O29" s="217" t="s">
+        <v>244</v>
       </c>
       <c r="P29" s="218" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="204" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A30" s="215"/>
+      <c r="B30" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" s="134"/>
+      <c r="F30" s="107"/>
+      <c r="G30" s="107"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="134"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="107"/>
+      <c r="L30" s="50"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O30" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="P30" s="221" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="209" t="s">
         <v>261</v>
       </c>
-      <c r="B30" s="205"/>
-      <c r="C30" s="206" t="str">
-        <f aca="false">DEC2HEX(D30,2)</f>
+      <c r="B31" s="210"/>
+      <c r="C31" s="211" t="str">
+        <f aca="false">DEC2HEX(D31,2)</f>
         <v>06</v>
       </c>
-      <c r="D30" s="162" t="n">
-        <f aca="false">IF(E30=1,128,0)+IF(F30=1,64,0)+IF(G30=1,32,0)+IF(H30=1,16,0)+IF(I30=1,8,0)+IF(J30=1,4,0)+IF(K30=1,2,0)+IF(L30=1,1,0)</f>
+      <c r="D31" s="161" t="n">
+        <f aca="false">IF(E31=1,128,0)+IF(F31=1,64,0)+IF(G31=1,32,0)+IF(H31=1,16,0)+IF(I31=1,8,0)+IF(J31=1,4,0)+IF(K31=1,2,0)+IF(L31=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="E30" s="207"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="162"/>
-      <c r="H30" s="163"/>
-      <c r="I30" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="208" t="s">
+      <c r="E31" s="178"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="165"/>
+      <c r="I31" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="212" t="s">
         <v>262</v>
       </c>
-      <c r="N30" s="205"/>
-      <c r="O30" s="208"/>
-      <c r="P30" s="219" t="s">
+      <c r="N31" s="210"/>
+      <c r="O31" s="212"/>
+      <c r="P31" s="233" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A31" s="211"/>
-      <c r="E31" s="216"/>
-      <c r="F31" s="107"/>
-      <c r="G31" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="134" t="s">
-        <v>264</v>
-      </c>
-      <c r="P31" s="214"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A32" s="211"/>
-      <c r="E32" s="216"/>
+    <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A32" s="215"/>
+      <c r="E32" s="134"/>
       <c r="F32" s="107"/>
       <c r="G32" s="107" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="107"/>
       <c r="J32" s="107"/>
       <c r="K32" s="107"/>
       <c r="L32" s="50"/>
-      <c r="M32" s="212" t="s">
-        <v>265</v>
-      </c>
-      <c r="P32" s="214"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="211"/>
-      <c r="E33" s="216"/>
+      <c r="M32" s="130" t="s">
+        <v>264</v>
+      </c>
+      <c r="P32" s="218"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A33" s="215"/>
+      <c r="E33" s="134"/>
       <c r="F33" s="107"/>
       <c r="G33" s="107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="107"/>
       <c r="J33" s="107"/>
       <c r="K33" s="107"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="212" t="s">
-        <v>266</v>
-      </c>
-      <c r="P33" s="214"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="211"/>
-      <c r="E34" s="216"/>
+      <c r="M33" s="216" t="s">
+        <v>265</v>
+      </c>
+      <c r="P33" s="218"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A34" s="215"/>
+      <c r="E34" s="134"/>
       <c r="F34" s="107"/>
       <c r="G34" s="107" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="107"/>
       <c r="J34" s="107"/>
       <c r="K34" s="107"/>
       <c r="L34" s="50"/>
-      <c r="M34" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="P34" s="214"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="211"/>
-      <c r="E35" s="216"/>
-      <c r="F35" s="107" t="s">
-        <v>268</v>
-      </c>
-      <c r="G35" s="107"/>
-      <c r="H35" s="50"/>
+      <c r="M34" s="216" t="s">
+        <v>266</v>
+      </c>
+      <c r="P34" s="218"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A35" s="215"/>
+      <c r="E35" s="134"/>
+      <c r="F35" s="107"/>
+      <c r="G35" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="50" t="n">
+        <v>1</v>
+      </c>
       <c r="I35" s="107"/>
       <c r="J35" s="107"/>
       <c r="K35" s="107"/>
       <c r="L35" s="50"/>
-      <c r="M35" s="134" t="s">
-        <v>269</v>
-      </c>
-      <c r="P35" s="214" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="211"/>
-      <c r="B36" s="133"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="F36" s="107"/>
+      <c r="M35" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="P35" s="218"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A36" s="215"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="107" t="s">
+        <v>268</v>
+      </c>
       <c r="G36" s="107"/>
       <c r="H36" s="50"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="13"/>
+      <c r="I36" s="107"/>
+      <c r="J36" s="107"/>
       <c r="K36" s="107"/>
       <c r="L36" s="50"/>
-      <c r="M36" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O36" s="213"/>
-      <c r="P36" s="214"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="211"/>
-      <c r="B37" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="E37" s="216"/>
+      <c r="M36" s="130" t="s">
+        <v>269</v>
+      </c>
+      <c r="P36" s="218" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A37" s="215"/>
+      <c r="B37" s="130"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="49"/>
       <c r="F37" s="107"/>
       <c r="G37" s="107"/>
       <c r="H37" s="50"/>
-      <c r="I37" s="107"/>
-      <c r="J37" s="107"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="13"/>
       <c r="K37" s="107"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="134"/>
-      <c r="O37" s="5" t="s">
+      <c r="M37" s="216"/>
+      <c r="O37" s="217"/>
+      <c r="P37" s="218"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A38" s="215"/>
+      <c r="B38" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="E38" s="134"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="50"/>
+      <c r="M38" s="130"/>
+      <c r="O38" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="P37" s="214" t="s">
+      <c r="P38" s="218" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="204" t="s">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="209" t="s">
         <v>273</v>
       </c>
-      <c r="B38" s="205"/>
-      <c r="C38" s="206" t="str">
-        <f aca="false">DEC2HEX(D38,2)</f>
+      <c r="B39" s="210"/>
+      <c r="C39" s="211" t="str">
+        <f aca="false">DEC2HEX(D39,2)</f>
         <v>07</v>
       </c>
-      <c r="D38" s="162" t="n">
-        <f aca="false">IF(E38=1,128,0)+IF(F38=1,64,0)+IF(G38=1,32,0)+IF(H38=1,16,0)+IF(I38=1,8,0)+IF(J38=1,4,0)+IF(K38=1,2,0)+IF(L38=1,1,0)</f>
+      <c r="D39" s="161" t="n">
+        <f aca="false">IF(E39=1,128,0)+IF(F39=1,64,0)+IF(G39=1,32,0)+IF(H39=1,16,0)+IF(I39=1,8,0)+IF(J39=1,4,0)+IF(K39=1,2,0)+IF(L39=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="E38" s="207"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162"/>
-      <c r="H38" s="163"/>
-      <c r="I38" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="163" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" s="208" t="s">
+      <c r="E39" s="178"/>
+      <c r="F39" s="161"/>
+      <c r="G39" s="161"/>
+      <c r="H39" s="165"/>
+      <c r="I39" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="212" t="s">
         <v>274</v>
       </c>
-      <c r="N38" s="205"/>
-      <c r="O38" s="208"/>
-      <c r="P38" s="210"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A39" s="211"/>
-      <c r="E39" s="216"/>
-      <c r="F39" s="107"/>
-      <c r="G39" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="107"/>
-      <c r="J39" s="107"/>
-      <c r="K39" s="107"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="134" t="s">
-        <v>275</v>
-      </c>
-      <c r="P39" s="217" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="211"/>
-      <c r="E40" s="216"/>
+      <c r="N39" s="210"/>
+      <c r="O39" s="212"/>
+      <c r="P39" s="214"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A40" s="215"/>
+      <c r="E40" s="134"/>
       <c r="F40" s="107"/>
       <c r="G40" s="107" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="107"/>
       <c r="J40" s="107"/>
       <c r="K40" s="107"/>
       <c r="L40" s="50"/>
-      <c r="M40" s="212" t="s">
-        <v>265</v>
-      </c>
-      <c r="P40" s="217" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="211"/>
-      <c r="E41" s="216"/>
+      <c r="M40" s="130" t="s">
+        <v>275</v>
+      </c>
+      <c r="P40" s="220" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A41" s="215"/>
+      <c r="E41" s="134"/>
       <c r="F41" s="107"/>
       <c r="G41" s="107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="107"/>
       <c r="J41" s="107"/>
       <c r="K41" s="107"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="212" t="s">
-        <v>266</v>
-      </c>
-      <c r="P41" s="217" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="211"/>
-      <c r="E42" s="216"/>
+      <c r="M41" s="216" t="s">
+        <v>265</v>
+      </c>
+      <c r="P41" s="220" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A42" s="215"/>
+      <c r="E42" s="134"/>
       <c r="F42" s="107"/>
       <c r="G42" s="107" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="107"/>
       <c r="J42" s="107"/>
       <c r="K42" s="107"/>
       <c r="L42" s="50"/>
-      <c r="M42" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="P42" s="217" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="211"/>
-      <c r="E43" s="216"/>
+      <c r="M42" s="216" t="s">
+        <v>266</v>
+      </c>
+      <c r="P42" s="220" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A43" s="215"/>
+      <c r="E43" s="134"/>
       <c r="F43" s="107"/>
-      <c r="G43" s="107"/>
-      <c r="H43" s="50"/>
+      <c r="G43" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="50" t="n">
+        <v>1</v>
+      </c>
       <c r="I43" s="107"/>
       <c r="J43" s="107"/>
       <c r="K43" s="107"/>
       <c r="L43" s="50"/>
-      <c r="M43" s="10"/>
-      <c r="O43" s="1"/>
+      <c r="M43" s="10" t="s">
+        <v>267</v>
+      </c>
       <c r="P43" s="220" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="211"/>
-      <c r="E44" s="216"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A44" s="215"/>
+      <c r="E44" s="134"/>
       <c r="F44" s="107"/>
       <c r="G44" s="107"/>
       <c r="H44" s="50"/>
@@ -8669,13 +8992,13 @@
       <c r="L44" s="50"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="220" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A45" s="211"/>
-      <c r="E45" s="216"/>
+      <c r="P44" s="234" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A45" s="215"/>
+      <c r="E45" s="134"/>
       <c r="F45" s="107"/>
       <c r="G45" s="107"/>
       <c r="H45" s="50"/>
@@ -8685,36 +9008,29 @@
       <c r="L45" s="50"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="220" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A46" s="211"/>
-      <c r="B46" s="133"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="107"/>
-      <c r="E46" s="49" t="s">
-        <v>233</v>
-      </c>
+      <c r="P45" s="234" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A46" s="215"/>
+      <c r="E46" s="134"/>
       <c r="F46" s="107"/>
       <c r="G46" s="107"/>
       <c r="H46" s="50"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="13"/>
+      <c r="I46" s="107"/>
+      <c r="J46" s="107"/>
       <c r="K46" s="107"/>
       <c r="L46" s="50"/>
-      <c r="M46" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O46" s="213"/>
-      <c r="P46" s="214"/>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="211"/>
-      <c r="B47" s="212" t="s">
-        <v>234</v>
-      </c>
+      <c r="M46" s="10"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="234" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A47" s="215"/>
+      <c r="B47" s="130"/>
       <c r="C47" s="17"/>
       <c r="D47" s="107"/>
       <c r="E47" s="49"/>
@@ -8725,303 +9041,319 @@
       <c r="J47" s="13"/>
       <c r="K47" s="107"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="212"/>
-      <c r="N47" s="1" t="s">
+      <c r="M47" s="216"/>
+      <c r="O47" s="217"/>
+      <c r="P47" s="218"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A48" s="215"/>
+      <c r="B48" s="216" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="107"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="107"/>
+      <c r="G48" s="107"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="107"/>
+      <c r="L48" s="50"/>
+      <c r="M48" s="216"/>
+      <c r="N48" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="O47" s="213" t="s">
+      <c r="O48" s="217" t="s">
         <v>284</v>
       </c>
-      <c r="P47" s="214"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="221"/>
-      <c r="B48" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="138"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="139"/>
-      <c r="H48" s="142"/>
-      <c r="I48" s="139"/>
-      <c r="J48" s="139"/>
-      <c r="K48" s="139"/>
-      <c r="L48" s="142"/>
-      <c r="M48" s="223"/>
-      <c r="N48" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O48" s="1" t="s">
+      <c r="P48" s="218"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A49" s="235"/>
+      <c r="B49" s="216" t="s">
+        <v>232</v>
+      </c>
+      <c r="C49" s="236"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="237"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="140"/>
+      <c r="K49" s="140"/>
+      <c r="L49" s="143"/>
+      <c r="M49" s="238"/>
+      <c r="N49" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="P48" s="218" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="204" t="s">
-        <v>285</v>
-      </c>
-      <c r="B49" s="205"/>
-      <c r="C49" s="206" t="str">
-        <f aca="false">DEC2HEX(D49,2)</f>
-        <v>0A</v>
-      </c>
-      <c r="D49" s="162" t="n">
-        <f aca="false">IF(E49=1,128,0)+IF(F49=1,64,0)+IF(G49=1,32,0)+IF(H49=1,16,0)+IF(I49=1,8,0)+IF(J49=1,4,0)+IF(K49=1,2,0)+IF(L49=1,1,0)</f>
-        <v>10</v>
-      </c>
-      <c r="E49" s="207"/>
-      <c r="F49" s="162"/>
-      <c r="G49" s="162"/>
-      <c r="H49" s="163"/>
-      <c r="I49" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="208" t="s">
-        <v>286</v>
-      </c>
-      <c r="N49" s="205"/>
-      <c r="O49" s="208"/>
-      <c r="P49" s="210"/>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A50" s="211"/>
-      <c r="B50" s="133"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="107"/>
-      <c r="E50" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="F50" s="107"/>
-      <c r="G50" s="107"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="107"/>
-      <c r="L50" s="50"/>
-      <c r="M50" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="O50" s="213"/>
+      <c r="P49" s="221" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="209"/>
+      <c r="B50" s="210"/>
+      <c r="C50" s="211" t="str">
+        <f aca="false">DEC2HEX(D50,2)</f>
+        <v>08</v>
+      </c>
+      <c r="D50" s="161" t="n">
+        <f aca="false">IF(E50=1,128,0)+IF(F50=1,64,0)+IF(G50=1,32,0)+IF(H50=1,16,0)+IF(I50=1,8,0)+IF(J50=1,4,0)+IF(K50=1,2,0)+IF(L50=1,1,0)</f>
+        <v>8</v>
+      </c>
+      <c r="E50" s="178"/>
+      <c r="F50" s="161"/>
+      <c r="G50" s="161"/>
+      <c r="H50" s="165"/>
+      <c r="I50" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="212"/>
+      <c r="N50" s="210"/>
+      <c r="O50" s="212"/>
       <c r="P50" s="214"/>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="211"/>
-      <c r="B51" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="E51" s="216"/>
+    <row r="51" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A51" s="215"/>
+      <c r="B51" s="130"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="107"/>
+      <c r="E51" s="49"/>
       <c r="F51" s="107"/>
       <c r="G51" s="107"/>
       <c r="H51" s="50"/>
-      <c r="I51" s="107"/>
-      <c r="J51" s="107"/>
+      <c r="I51" s="49"/>
+      <c r="J51" s="13"/>
       <c r="K51" s="107"/>
       <c r="L51" s="50"/>
-      <c r="M51" s="134"/>
-      <c r="N51" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="O51" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="P51" s="214" t="s">
-        <v>288</v>
-      </c>
+      <c r="M51" s="216"/>
+      <c r="O51" s="217"/>
+      <c r="P51" s="218"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="204" t="s">
-        <v>289</v>
-      </c>
-      <c r="B52" s="205"/>
-      <c r="C52" s="206" t="str">
+      <c r="A52" s="209"/>
+      <c r="B52" s="210"/>
+      <c r="C52" s="211" t="str">
         <f aca="false">DEC2HEX(D52,2)</f>
-        <v>0C</v>
-      </c>
-      <c r="D52" s="162" t="n">
+        <v>09</v>
+      </c>
+      <c r="D52" s="161" t="n">
         <f aca="false">IF(E52=1,128,0)+IF(F52=1,64,0)+IF(G52=1,32,0)+IF(H52=1,16,0)+IF(I52=1,8,0)+IF(J52=1,4,0)+IF(K52=1,2,0)+IF(L52=1,1,0)</f>
-        <v>12</v>
-      </c>
-      <c r="E52" s="207"/>
-      <c r="F52" s="162"/>
-      <c r="G52" s="162"/>
-      <c r="H52" s="163"/>
-      <c r="I52" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="162" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="205" t="s">
-        <v>290</v>
-      </c>
-      <c r="N52" s="205"/>
-      <c r="O52" s="208"/>
-      <c r="P52" s="210"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="211"/>
-      <c r="E53" s="216" t="s">
-        <v>233</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E52" s="178"/>
+      <c r="F52" s="161"/>
+      <c r="G52" s="161"/>
+      <c r="H52" s="165"/>
+      <c r="I52" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="212"/>
+      <c r="N52" s="210"/>
+      <c r="O52" s="212"/>
+      <c r="P52" s="214"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A53" s="215"/>
+      <c r="B53" s="130"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="107"/>
+      <c r="E53" s="49"/>
       <c r="F53" s="107"/>
       <c r="G53" s="107"/>
       <c r="H53" s="50"/>
-      <c r="I53" s="107"/>
-      <c r="J53" s="107"/>
+      <c r="I53" s="49"/>
+      <c r="J53" s="13"/>
       <c r="K53" s="107"/>
       <c r="L53" s="50"/>
-      <c r="M53" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="N53" s="212"/>
-      <c r="O53" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="214"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A54" s="211"/>
-      <c r="B54" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="E54" s="216"/>
-      <c r="F54" s="107"/>
-      <c r="G54" s="107"/>
-      <c r="H54" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="107"/>
-      <c r="J54" s="107"/>
-      <c r="K54" s="107"/>
-      <c r="L54" s="50"/>
+      <c r="M53" s="216"/>
+      <c r="O53" s="217"/>
+      <c r="P53" s="218"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="209" t="s">
+        <v>285</v>
+      </c>
+      <c r="B54" s="210"/>
+      <c r="C54" s="211" t="str">
+        <f aca="false">DEC2HEX(D54,2)</f>
+        <v>0A</v>
+      </c>
+      <c r="D54" s="161" t="n">
+        <f aca="false">IF(E54=1,128,0)+IF(F54=1,64,0)+IF(G54=1,32,0)+IF(H54=1,16,0)+IF(I54=1,8,0)+IF(J54=1,4,0)+IF(K54=1,2,0)+IF(L54=1,1,0)</f>
+        <v>10</v>
+      </c>
+      <c r="E54" s="178"/>
+      <c r="F54" s="161"/>
+      <c r="G54" s="161"/>
+      <c r="H54" s="165"/>
+      <c r="I54" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="165" t="n">
+        <v>0</v>
+      </c>
       <c r="M54" s="212" t="s">
-        <v>291</v>
-      </c>
-      <c r="N54" s="212"/>
-      <c r="O54" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="214" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="211"/>
-      <c r="B55" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="E55" s="216"/>
+        <v>286</v>
+      </c>
+      <c r="N54" s="210"/>
+      <c r="O54" s="212"/>
+      <c r="P54" s="214"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A55" s="215"/>
+      <c r="B55" s="130"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="107"/>
+      <c r="E55" s="49"/>
       <c r="F55" s="107"/>
       <c r="G55" s="107"/>
-      <c r="H55" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="107"/>
-      <c r="J55" s="107"/>
+      <c r="H55" s="50"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="13"/>
       <c r="K55" s="107"/>
       <c r="L55" s="50"/>
-      <c r="M55" s="212" t="s">
-        <v>293</v>
-      </c>
-      <c r="N55" s="212"/>
-      <c r="O55" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="214" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="204"/>
-      <c r="B56" s="205"/>
-      <c r="C56" s="206" t="str">
-        <f aca="false">DEC2HEX(D56,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D56" s="162" t="n">
-        <f aca="false">IF(E56=1,128,0)+IF(F56=1,64,0)+IF(G56=1,32,0)+IF(H56=1,16,0)+IF(I56=1,8,0)+IF(J56=1,4,0)+IF(K56=1,2,0)+IF(L56=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="207"/>
-      <c r="F56" s="162"/>
-      <c r="G56" s="162"/>
-      <c r="H56" s="163"/>
-      <c r="I56" s="162"/>
-      <c r="J56" s="162"/>
-      <c r="K56" s="162"/>
-      <c r="L56" s="163"/>
-      <c r="M56" s="205"/>
-      <c r="N56" s="205"/>
-      <c r="O56" s="208"/>
-      <c r="P56" s="210"/>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A57" s="211"/>
-      <c r="E57" s="216"/>
-      <c r="F57" s="107"/>
-      <c r="G57" s="107"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="107"/>
-      <c r="J57" s="107"/>
-      <c r="K57" s="107"/>
-      <c r="L57" s="50"/>
+      <c r="M55" s="216"/>
+      <c r="O55" s="217"/>
+      <c r="P55" s="218"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A56" s="215"/>
+      <c r="B56" s="216" t="s">
+        <v>232</v>
+      </c>
+      <c r="E56" s="134"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="107"/>
+      <c r="H56" s="50"/>
+      <c r="I56" s="107"/>
+      <c r="J56" s="107"/>
+      <c r="K56" s="107"/>
+      <c r="L56" s="50"/>
+      <c r="M56" s="130"/>
+      <c r="N56" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="P56" s="218" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="209"/>
+      <c r="B57" s="210"/>
+      <c r="C57" s="211" t="str">
+        <f aca="false">DEC2HEX(D57,2)</f>
+        <v>0B</v>
+      </c>
+      <c r="D57" s="161" t="n">
+        <f aca="false">IF(E57=1,128,0)+IF(F57=1,64,0)+IF(G57=1,32,0)+IF(H57=1,16,0)+IF(I57=1,8,0)+IF(J57=1,4,0)+IF(K57=1,2,0)+IF(L57=1,1,0)</f>
+        <v>11</v>
+      </c>
+      <c r="E57" s="178"/>
+      <c r="F57" s="161"/>
+      <c r="G57" s="161"/>
+      <c r="H57" s="165"/>
+      <c r="I57" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="165" t="n">
+        <v>1</v>
+      </c>
       <c r="M57" s="212"/>
-      <c r="N57" s="212"/>
-      <c r="O57" s="133"/>
+      <c r="N57" s="210"/>
+      <c r="O57" s="212"/>
       <c r="P57" s="214"/>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="211"/>
-      <c r="E58" s="216"/>
+    <row r="58" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A58" s="215"/>
+      <c r="B58" s="130"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="107"/>
+      <c r="E58" s="49"/>
       <c r="F58" s="107"/>
       <c r="G58" s="107"/>
       <c r="H58" s="50"/>
-      <c r="I58" s="107"/>
-      <c r="J58" s="107"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="13"/>
       <c r="K58" s="107"/>
       <c r="L58" s="50"/>
-      <c r="M58" s="212"/>
-      <c r="N58" s="212"/>
-      <c r="O58" s="133"/>
-      <c r="P58" s="214"/>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A59" s="211"/>
-      <c r="E59" s="216"/>
-      <c r="F59" s="107"/>
-      <c r="G59" s="107"/>
-      <c r="H59" s="50"/>
-      <c r="I59" s="107"/>
-      <c r="J59" s="107"/>
-      <c r="K59" s="107"/>
-      <c r="L59" s="50"/>
-      <c r="M59" s="212"/>
-      <c r="N59" s="212"/>
-      <c r="O59" s="133"/>
+      <c r="M58" s="216"/>
+      <c r="O58" s="217"/>
+      <c r="P58" s="218"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="209"/>
+      <c r="B59" s="210"/>
+      <c r="C59" s="211" t="str">
+        <f aca="false">DEC2HEX(D59,2)</f>
+        <v>0C</v>
+      </c>
+      <c r="D59" s="161" t="n">
+        <f aca="false">IF(E59=1,128,0)+IF(F59=1,64,0)+IF(G59=1,32,0)+IF(H59=1,16,0)+IF(I59=1,8,0)+IF(J59=1,4,0)+IF(K59=1,2,0)+IF(L59=1,1,0)</f>
+        <v>12</v>
+      </c>
+      <c r="E59" s="178"/>
+      <c r="F59" s="161"/>
+      <c r="G59" s="161"/>
+      <c r="H59" s="165"/>
+      <c r="I59" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="210"/>
+      <c r="N59" s="210"/>
+      <c r="O59" s="212"/>
       <c r="P59" s="214"/>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A60" s="211"/>
-      <c r="E60" s="216"/>
+    <row r="60" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A60" s="215"/>
+      <c r="E60" s="134"/>
       <c r="F60" s="107"/>
       <c r="G60" s="107"/>
       <c r="H60" s="50"/>
@@ -9029,935 +9361,1163 @@
       <c r="J60" s="107"/>
       <c r="K60" s="107"/>
       <c r="L60" s="50"/>
-      <c r="M60" s="212"/>
-      <c r="N60" s="212"/>
-      <c r="O60" s="133"/>
-      <c r="P60" s="214"/>
+      <c r="M60" s="216"/>
+      <c r="N60" s="216"/>
+      <c r="O60" s="130"/>
+      <c r="P60" s="218"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="211"/>
-      <c r="E61" s="216"/>
-      <c r="F61" s="107"/>
-      <c r="G61" s="107"/>
-      <c r="H61" s="50"/>
-      <c r="I61" s="107"/>
-      <c r="J61" s="107"/>
-      <c r="K61" s="107"/>
-      <c r="L61" s="50"/>
-      <c r="M61" s="212"/>
-      <c r="N61" s="212"/>
-      <c r="O61" s="133"/>
+      <c r="A61" s="209"/>
+      <c r="B61" s="210"/>
+      <c r="C61" s="211" t="str">
+        <f aca="false">DEC2HEX(D61,2)</f>
+        <v>0D</v>
+      </c>
+      <c r="D61" s="161" t="n">
+        <f aca="false">IF(E61=1,128,0)+IF(F61=1,64,0)+IF(G61=1,32,0)+IF(H61=1,16,0)+IF(I61=1,8,0)+IF(J61=1,4,0)+IF(K61=1,2,0)+IF(L61=1,1,0)</f>
+        <v>13</v>
+      </c>
+      <c r="E61" s="178"/>
+      <c r="F61" s="161"/>
+      <c r="G61" s="161"/>
+      <c r="H61" s="165"/>
+      <c r="I61" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="210"/>
+      <c r="N61" s="210"/>
+      <c r="O61" s="212"/>
       <c r="P61" s="214"/>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="204" t="s">
-        <v>214</v>
-      </c>
-      <c r="B62" s="208"/>
-      <c r="C62" s="206"/>
-      <c r="D62" s="162"/>
-      <c r="E62" s="207"/>
-      <c r="F62" s="162"/>
-      <c r="G62" s="162"/>
-      <c r="H62" s="163"/>
-      <c r="I62" s="207"/>
-      <c r="J62" s="162"/>
-      <c r="K62" s="162"/>
-      <c r="L62" s="163"/>
-      <c r="M62" s="205"/>
-      <c r="N62" s="205"/>
-      <c r="O62" s="208"/>
-      <c r="P62" s="210"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A63" s="224" t="s">
+    <row r="62" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A62" s="215"/>
+      <c r="E62" s="134"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
+      <c r="H62" s="50"/>
+      <c r="I62" s="107"/>
+      <c r="J62" s="107"/>
+      <c r="K62" s="107"/>
+      <c r="L62" s="50"/>
+      <c r="M62" s="216"/>
+      <c r="N62" s="216"/>
+      <c r="O62" s="130"/>
+      <c r="P62" s="218"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="209"/>
+      <c r="B63" s="210"/>
+      <c r="C63" s="211" t="str">
+        <f aca="false">DEC2HEX(D63,2)</f>
+        <v>0E</v>
+      </c>
+      <c r="D63" s="161" t="n">
+        <f aca="false">IF(E63=1,128,0)+IF(F63=1,64,0)+IF(G63=1,32,0)+IF(H63=1,16,0)+IF(I63=1,8,0)+IF(J63=1,4,0)+IF(K63=1,2,0)+IF(L63=1,1,0)</f>
+        <v>14</v>
+      </c>
+      <c r="E63" s="178"/>
+      <c r="F63" s="161"/>
+      <c r="G63" s="161"/>
+      <c r="H63" s="165"/>
+      <c r="I63" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="210"/>
+      <c r="N63" s="210"/>
+      <c r="O63" s="212"/>
+      <c r="P63" s="214"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A64" s="215"/>
+      <c r="E64" s="134"/>
+      <c r="F64" s="107"/>
+      <c r="G64" s="107"/>
+      <c r="H64" s="50"/>
+      <c r="I64" s="107"/>
+      <c r="J64" s="107"/>
+      <c r="K64" s="107"/>
+      <c r="L64" s="50"/>
+      <c r="M64" s="216"/>
+      <c r="N64" s="216"/>
+      <c r="O64" s="130"/>
+      <c r="P64" s="218"/>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="209"/>
+      <c r="B65" s="210"/>
+      <c r="C65" s="211" t="str">
+        <f aca="false">DEC2HEX(D65,2)</f>
+        <v>0F</v>
+      </c>
+      <c r="D65" s="161" t="n">
+        <f aca="false">IF(E65=1,128,0)+IF(F65=1,64,0)+IF(G65=1,32,0)+IF(H65=1,16,0)+IF(I65=1,8,0)+IF(J65=1,4,0)+IF(K65=1,2,0)+IF(L65=1,1,0)</f>
+        <v>15</v>
+      </c>
+      <c r="E65" s="178"/>
+      <c r="F65" s="161"/>
+      <c r="G65" s="161"/>
+      <c r="H65" s="165"/>
+      <c r="I65" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="210"/>
+      <c r="N65" s="210"/>
+      <c r="O65" s="212"/>
+      <c r="P65" s="214"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A66" s="215"/>
+      <c r="E66" s="134"/>
+      <c r="F66" s="107"/>
+      <c r="G66" s="107"/>
+      <c r="H66" s="50"/>
+      <c r="I66" s="107"/>
+      <c r="J66" s="107"/>
+      <c r="K66" s="107"/>
+      <c r="L66" s="50"/>
+      <c r="M66" s="216"/>
+      <c r="N66" s="216"/>
+      <c r="O66" s="130"/>
+      <c r="P66" s="218"/>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="215"/>
+      <c r="E67" s="134"/>
+      <c r="F67" s="107"/>
+      <c r="G67" s="107"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="107"/>
+      <c r="J67" s="107"/>
+      <c r="K67" s="107"/>
+      <c r="L67" s="50"/>
+      <c r="M67" s="216"/>
+      <c r="N67" s="216"/>
+      <c r="O67" s="130"/>
+      <c r="P67" s="218"/>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="215"/>
+      <c r="E68" s="134"/>
+      <c r="F68" s="107"/>
+      <c r="G68" s="107"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="107"/>
+      <c r="J68" s="107"/>
+      <c r="K68" s="107"/>
+      <c r="L68" s="50"/>
+      <c r="M68" s="216"/>
+      <c r="N68" s="216"/>
+      <c r="O68" s="130"/>
+      <c r="P68" s="218"/>
+    </row>
+    <row r="69" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="239" t="s">
+        <v>289</v>
+      </c>
+      <c r="E69" s="134"/>
+      <c r="F69" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="G69" s="191" t="s">
+        <v>291</v>
+      </c>
+      <c r="H69" s="191" t="s">
+        <v>291</v>
+      </c>
+      <c r="I69" s="191"/>
+      <c r="J69" s="191"/>
+      <c r="K69" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="L69" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="M69" s="216"/>
+      <c r="N69" s="216"/>
+      <c r="O69" s="130"/>
+      <c r="P69" s="218"/>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="209" t="s">
+        <v>211</v>
+      </c>
+      <c r="B70" s="212"/>
+      <c r="C70" s="211"/>
+      <c r="D70" s="161"/>
+      <c r="E70" s="178"/>
+      <c r="F70" s="161"/>
+      <c r="G70" s="161"/>
+      <c r="H70" s="165"/>
+      <c r="I70" s="178"/>
+      <c r="J70" s="161"/>
+      <c r="K70" s="161"/>
+      <c r="L70" s="165"/>
+      <c r="M70" s="210"/>
+      <c r="N70" s="210"/>
+      <c r="O70" s="212"/>
+      <c r="P70" s="214"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A71" s="240" t="s">
+        <v>294</v>
+      </c>
+      <c r="B71" s="181"/>
+      <c r="C71" s="205" t="str">
+        <f aca="false">DEC2HEX(D71,2)</f>
+        <v>00</v>
+      </c>
+      <c r="D71" s="183" t="n">
+        <f aca="false">IF(E71=1,128,0)+IF(F71=1,64,0)+IF(G71=1,32,0)+IF(H71=1,16,0)+IF(I71=1,8,0)+IF(J71=1,4,0)+IF(K71=1,2,0)+IF(L71=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="243"/>
+      <c r="N71" s="243"/>
+      <c r="O71" s="181"/>
+      <c r="P71" s="244"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A72" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="B63" s="225"/>
-      <c r="C63" s="200" t="str">
-        <f aca="false">DEC2HEX(D63,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D63" s="226" t="n">
-        <f aca="false">IF(E63=1,128,0)+IF(F63=1,64,0)+IF(G63=1,32,0)+IF(H63=1,16,0)+IF(I63=1,8,0)+IF(J63=1,4,0)+IF(K63=1,2,0)+IF(L63=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="229"/>
-      <c r="N63" s="229"/>
-      <c r="O63" s="225"/>
-      <c r="P63" s="230"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="211" t="s">
-        <v>296</v>
-      </c>
-      <c r="B64" s="133"/>
-      <c r="C64" s="20" t="str">
-        <f aca="false">DEC2HEX(D64,2)</f>
-        <v>40</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <f aca="false">IF(E64=1,128,0)+IF(F64=1,64,0)+IF(G64=1,32,0)+IF(H64=1,16,0)+IF(I64=1,8,0)+IF(J64=1,4,0)+IF(K64=1,2,0)+IF(L64=1,1,0)</f>
-        <v>64</v>
-      </c>
-      <c r="E64" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="212"/>
-      <c r="N64" s="212"/>
-      <c r="O64" s="133"/>
-      <c r="P64" s="214"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A65" s="211" t="s">
-        <v>297</v>
-      </c>
-      <c r="B65" s="133"/>
-      <c r="C65" s="20" t="str">
-        <f aca="false">DEC2HEX(D65,2)</f>
-        <v>80</v>
-      </c>
-      <c r="D65" s="2" t="n">
-        <f aca="false">IF(E65=1,128,0)+IF(F65=1,64,0)+IF(G65=1,32,0)+IF(H65=1,16,0)+IF(I65=1,8,0)+IF(J65=1,4,0)+IF(K65=1,2,0)+IF(L65=1,1,0)</f>
-        <v>128</v>
-      </c>
-      <c r="E65" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="212"/>
-      <c r="N65" s="212"/>
-      <c r="O65" s="133"/>
-      <c r="P65" s="214"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A66" s="221" t="s">
-        <v>298</v>
-      </c>
-      <c r="B66" s="223"/>
-      <c r="C66" s="222" t="str">
-        <f aca="false">DEC2HEX(D66,2)</f>
-        <v>C0</v>
-      </c>
-      <c r="D66" s="139" t="n">
-        <f aca="false">IF(E66=1,128,0)+IF(F66=1,64,0)+IF(G66=1,32,0)+IF(H66=1,16,0)+IF(I66=1,8,0)+IF(J66=1,4,0)+IF(K66=1,2,0)+IF(L66=1,1,0)</f>
-        <v>192</v>
-      </c>
-      <c r="E66" s="138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="231"/>
-      <c r="N66" s="231"/>
-      <c r="O66" s="223"/>
-      <c r="P66" s="232"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A67" s="224" t="s">
-        <v>299</v>
-      </c>
-      <c r="B67" s="233"/>
-      <c r="C67" s="200" t="str">
-        <f aca="false">DEC2HEX(D67,2)</f>
-        <v>01</v>
-      </c>
-      <c r="D67" s="226" t="n">
-        <f aca="false">IF(E67=1,128,0)+IF(F67=1,64,0)+IF(G67=1,32,0)+IF(H67=1,16,0)+IF(I67=1,8,0)+IF(J67=1,4,0)+IF(K67=1,2,0)+IF(L67=1,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E67" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="226" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="228" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" s="229"/>
-      <c r="N67" s="229"/>
-      <c r="O67" s="225"/>
-      <c r="P67" s="230"/>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A68" s="211" t="s">
-        <v>300</v>
-      </c>
-      <c r="B68" s="133"/>
-      <c r="C68" s="20" t="str">
-        <f aca="false">DEC2HEX(D68,2)</f>
-        <v>41</v>
-      </c>
-      <c r="D68" s="2" t="n">
-        <f aca="false">IF(E68=1,128,0)+IF(F68=1,64,0)+IF(G68=1,32,0)+IF(H68=1,16,0)+IF(I68=1,8,0)+IF(J68=1,4,0)+IF(K68=1,2,0)+IF(L68=1,1,0)</f>
-        <v>65</v>
-      </c>
-      <c r="E68" s="216" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" s="214"/>
-    </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A69" s="211" t="s">
-        <v>301</v>
-      </c>
-      <c r="B69" s="133"/>
-      <c r="C69" s="20" t="str">
-        <f aca="false">DEC2HEX(D69,2)</f>
-        <v>C1</v>
-      </c>
-      <c r="D69" s="2" t="n">
-        <f aca="false">IF(E69=1,128,0)+IF(F69=1,64,0)+IF(G69=1,32,0)+IF(H69=1,16,0)+IF(I69=1,8,0)+IF(J69=1,4,0)+IF(K69=1,2,0)+IF(L69=1,1,0)</f>
-        <v>193</v>
-      </c>
-      <c r="E69" s="216" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-      <c r="O69" s="133"/>
-      <c r="P69" s="214"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A70" s="221" t="s">
-        <v>302</v>
-      </c>
-      <c r="B70" s="223"/>
-      <c r="C70" s="222" t="str">
-        <f aca="false">DEC2HEX(D70,2)</f>
-        <v>03</v>
-      </c>
-      <c r="D70" s="139" t="n">
-        <f aca="false">IF(E70=1,128,0)+IF(F70=1,64,0)+IF(G70=1,32,0)+IF(H70=1,16,0)+IF(I70=1,8,0)+IF(J70=1,4,0)+IF(K70=1,2,0)+IF(L70=1,1,0)</f>
-        <v>3</v>
-      </c>
-      <c r="E70" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="142" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" s="231"/>
-      <c r="N70" s="231"/>
-      <c r="O70" s="223"/>
-      <c r="P70" s="232"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="224" t="s">
-        <v>303</v>
-      </c>
-      <c r="B71" s="225"/>
-      <c r="C71" s="200" t="str">
-        <f aca="false">DEC2HEX(D71,2)</f>
-        <v>04</v>
-      </c>
-      <c r="D71" s="226" t="n">
-        <f aca="false">IF(E71=1,128,0)+IF(F71=1,64,0)+IF(G71=1,32,0)+IF(H71=1,16,0)+IF(I71=1,8,0)+IF(J71=1,4,0)+IF(K71=1,2,0)+IF(L71=1,1,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E71" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="191" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="229"/>
-      <c r="N71" s="229"/>
-      <c r="O71" s="225"/>
-      <c r="P71" s="230" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="211" t="s">
-        <v>305</v>
-      </c>
-      <c r="B72" s="133"/>
+      <c r="B72" s="130"/>
       <c r="C72" s="20" t="str">
         <f aca="false">DEC2HEX(D72,2)</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">IF(E72=1,128,0)+IF(F72=1,64,0)+IF(G72=1,32,0)+IF(H72=1,16,0)+IF(I72=1,8,0)+IF(J72=1,4,0)+IF(K72=1,2,0)+IF(L72=1,1,0)</f>
+        <v>16</v>
+      </c>
+      <c r="E72" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="216"/>
+      <c r="N72" s="216"/>
+      <c r="O72" s="130"/>
+      <c r="P72" s="218"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A73" s="215" t="s">
+        <v>296</v>
+      </c>
+      <c r="B73" s="130"/>
+      <c r="C73" s="20" t="str">
+        <f aca="false">DEC2HEX(D73,2)</f>
         <v>20</v>
       </c>
-      <c r="E72" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="212"/>
-      <c r="N72" s="212"/>
-      <c r="O72" s="133"/>
-      <c r="P72" s="214" t="s">
+      <c r="D73" s="2" t="n">
+        <f aca="false">IF(E73=1,128,0)+IF(F73=1,64,0)+IF(G73=1,32,0)+IF(H73=1,16,0)+IF(I73=1,8,0)+IF(J73=1,4,0)+IF(K73=1,2,0)+IF(L73=1,1,0)</f>
+        <v>32</v>
+      </c>
+      <c r="E73" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="216"/>
+      <c r="N73" s="216"/>
+      <c r="O73" s="130"/>
+      <c r="P73" s="218"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A74" s="235" t="s">
+        <v>297</v>
+      </c>
+      <c r="B74" s="238"/>
+      <c r="C74" s="236" t="str">
+        <f aca="false">DEC2HEX(D74,2)</f>
+        <v>30</v>
+      </c>
+      <c r="D74" s="140" t="n">
+        <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
+        <v>48</v>
+      </c>
+      <c r="E74" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="245"/>
+      <c r="N74" s="245"/>
+      <c r="O74" s="238"/>
+      <c r="P74" s="246"/>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A75" s="240" t="s">
+        <v>298</v>
+      </c>
+      <c r="B75" s="181"/>
+      <c r="C75" s="205" t="str">
+        <f aca="false">DEC2HEX(D75,2)</f>
+        <v>40</v>
+      </c>
+      <c r="D75" s="183" t="n">
+        <f aca="false">IF(E75=1,128,0)+IF(F75=1,64,0)+IF(G75=1,32,0)+IF(H75=1,16,0)+IF(I75=1,8,0)+IF(J75=1,4,0)+IF(K75=1,2,0)+IF(L75=1,1,0)</f>
+        <v>64</v>
+      </c>
+      <c r="E75" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="243"/>
+      <c r="N75" s="243"/>
+      <c r="O75" s="181"/>
+      <c r="P75" s="244"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A76" s="215" t="s">
+        <v>299</v>
+      </c>
+      <c r="B76" s="130"/>
+      <c r="C76" s="20" t="str">
+        <f aca="false">DEC2HEX(D76,2)</f>
+        <v>50</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <f aca="false">IF(E76=1,128,0)+IF(F76=1,64,0)+IF(G76=1,32,0)+IF(H76=1,16,0)+IF(I76=1,8,0)+IF(J76=1,4,0)+IF(K76=1,2,0)+IF(L76=1,1,0)</f>
+        <v>80</v>
+      </c>
+      <c r="E76" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="216"/>
+      <c r="N76" s="216"/>
+      <c r="O76" s="130"/>
+      <c r="P76" s="218"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A77" s="215" t="s">
+        <v>300</v>
+      </c>
+      <c r="B77" s="130"/>
+      <c r="C77" s="20" t="str">
+        <f aca="false">DEC2HEX(D77,2)</f>
+        <v>60</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <f aca="false">IF(E77=1,128,0)+IF(F77=1,64,0)+IF(G77=1,32,0)+IF(H77=1,16,0)+IF(I77=1,8,0)+IF(J77=1,4,0)+IF(K77=1,2,0)+IF(L77=1,1,0)</f>
+        <v>96</v>
+      </c>
+      <c r="E77" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="216"/>
+      <c r="N77" s="216"/>
+      <c r="O77" s="130"/>
+      <c r="P77" s="218"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A78" s="235" t="s">
+        <v>301</v>
+      </c>
+      <c r="B78" s="238"/>
+      <c r="C78" s="236" t="str">
+        <f aca="false">DEC2HEX(D78,2)</f>
+        <v>70</v>
+      </c>
+      <c r="D78" s="140" t="n">
+        <f aca="false">IF(E78=1,128,0)+IF(F78=1,64,0)+IF(G78=1,32,0)+IF(H78=1,16,0)+IF(I78=1,8,0)+IF(J78=1,4,0)+IF(K78=1,2,0)+IF(L78=1,1,0)</f>
+        <v>112</v>
+      </c>
+      <c r="E78" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="245"/>
+      <c r="N78" s="245"/>
+      <c r="O78" s="238"/>
+      <c r="P78" s="246"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A79" s="240" t="s">
+        <v>302</v>
+      </c>
+      <c r="B79" s="247"/>
+      <c r="C79" s="205" t="str">
+        <f aca="false">DEC2HEX(D79,2)</f>
+        <v>01</v>
+      </c>
+      <c r="D79" s="183" t="n">
+        <f aca="false">IF(E79=1,128,0)+IF(F79=1,64,0)+IF(G79=1,32,0)+IF(H79=1,16,0)+IF(I79=1,8,0)+IF(J79=1,4,0)+IF(K79=1,2,0)+IF(L79=1,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E79" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="243"/>
+      <c r="N79" s="243"/>
+      <c r="O79" s="181"/>
+      <c r="P79" s="244"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A80" s="215" t="s">
+        <v>303</v>
+      </c>
+      <c r="B80" s="130"/>
+      <c r="C80" s="20" t="str">
+        <f aca="false">DEC2HEX(D80,2)</f>
+        <v>11</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <f aca="false">IF(E80=1,128,0)+IF(F80=1,64,0)+IF(G80=1,32,0)+IF(H80=1,16,0)+IF(I80=1,8,0)+IF(J80=1,4,0)+IF(K80=1,2,0)+IF(L80=1,1,0)</f>
+        <v>17</v>
+      </c>
+      <c r="E80" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="218"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A81" s="215" t="s">
+        <v>304</v>
+      </c>
+      <c r="B81" s="130"/>
+      <c r="C81" s="20" t="str">
+        <f aca="false">DEC2HEX(D81,2)</f>
+        <v>21</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <f aca="false">IF(E81=1,128,0)+IF(F81=1,64,0)+IF(G81=1,32,0)+IF(H81=1,16,0)+IF(I81=1,8,0)+IF(J81=1,4,0)+IF(K81=1,2,0)+IF(L81=1,1,0)</f>
+        <v>33</v>
+      </c>
+      <c r="E81" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="130"/>
+      <c r="P81" s="218"/>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A82" s="235" t="s">
+        <v>305</v>
+      </c>
+      <c r="B82" s="238"/>
+      <c r="C82" s="236" t="str">
+        <f aca="false">DEC2HEX(D82,2)</f>
+        <v>31</v>
+      </c>
+      <c r="D82" s="140" t="n">
+        <f aca="false">IF(E82=1,128,0)+IF(F82=1,64,0)+IF(G82=1,32,0)+IF(H82=1,16,0)+IF(I82=1,8,0)+IF(J82=1,4,0)+IF(K82=1,2,0)+IF(L82=1,1,0)</f>
+        <v>49</v>
+      </c>
+      <c r="E82" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="245"/>
+      <c r="N82" s="245"/>
+      <c r="O82" s="238"/>
+      <c r="P82" s="246"/>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A83" s="240" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="221" t="s">
+      <c r="B83" s="181"/>
+      <c r="C83" s="205" t="str">
+        <f aca="false">DEC2HEX(D83,2)</f>
+        <v>04</v>
+      </c>
+      <c r="D83" s="183" t="n">
+        <f aca="false">IF(E83=1,128,0)+IF(F83=1,64,0)+IF(G83=1,32,0)+IF(H83=1,16,0)+IF(I83=1,8,0)+IF(J83=1,4,0)+IF(K83=1,2,0)+IF(L83=1,1,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E83" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="243"/>
+      <c r="N83" s="243"/>
+      <c r="O83" s="181"/>
+      <c r="P83" s="244" t="s">
         <v>307</v>
       </c>
-      <c r="B73" s="223"/>
-      <c r="C73" s="222" t="str">
-        <f aca="false">DEC2HEX(D73,2)</f>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A84" s="215" t="s">
+        <v>308</v>
+      </c>
+      <c r="B84" s="130"/>
+      <c r="C84" s="20" t="str">
+        <f aca="false">DEC2HEX(D84,2)</f>
+        <v>44</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <f aca="false">IF(E84=1,128,0)+IF(F84=1,64,0)+IF(G84=1,32,0)+IF(H84=1,16,0)+IF(I84=1,8,0)+IF(J84=1,4,0)+IF(K84=1,2,0)+IF(L84=1,1,0)</f>
+        <v>68</v>
+      </c>
+      <c r="E84" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="216"/>
+      <c r="N84" s="216"/>
+      <c r="O84" s="130"/>
+      <c r="P84" s="218" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A85" s="215" t="s">
+        <v>310</v>
+      </c>
+      <c r="B85" s="248"/>
+      <c r="C85" s="17" t="str">
+        <f aca="false">DEC2HEX(D85,2)</f>
         <v>54</v>
       </c>
-      <c r="D73" s="139" t="n">
-        <f aca="false">IF(E73=1,128,0)+IF(F73=1,64,0)+IF(G73=1,32,0)+IF(H73=1,16,0)+IF(I73=1,8,0)+IF(J73=1,4,0)+IF(K73=1,2,0)+IF(L73=1,1,0)</f>
+      <c r="D85" s="107" t="n">
+        <f aca="false">IF(E85=1,128,0)+IF(F85=1,64,0)+IF(G85=1,32,0)+IF(H85=1,16,0)+IF(I85=1,8,0)+IF(J85=1,4,0)+IF(K85=1,2,0)+IF(L85=1,1,0)</f>
         <v>84</v>
       </c>
-      <c r="E73" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="142" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="231"/>
-      <c r="N73" s="231"/>
-      <c r="O73" s="223"/>
-      <c r="P73" s="232" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="224" t="s">
-        <v>309</v>
-      </c>
-      <c r="B74" s="225"/>
-      <c r="C74" s="200" t="str">
-        <f aca="false">DEC2HEX(D74,2)</f>
+      <c r="E85" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="216"/>
+      <c r="N85" s="216"/>
+      <c r="O85" s="248"/>
+      <c r="P85" s="218" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A86" s="215" t="s">
+        <v>312</v>
+      </c>
+      <c r="B86" s="248"/>
+      <c r="C86" s="17" t="str">
+        <f aca="false">DEC2HEX(D86,2)</f>
+        <v>84</v>
+      </c>
+      <c r="D86" s="13" t="n">
+        <f aca="false">IF(E86=1,128,0)+IF(F86=1,64,0)+IF(G86=1,32,0)+IF(H86=1,16,0)+IF(I86=1,8,0)+IF(J86=1,4,0)+IF(K86=1,2,0)+IF(L86=1,1,0)</f>
+        <v>132</v>
+      </c>
+      <c r="E86" s="134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="216"/>
+      <c r="N86" s="216"/>
+      <c r="O86" s="248"/>
+      <c r="P86" s="218"/>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A87" s="240" t="s">
+        <v>313</v>
+      </c>
+      <c r="B87" s="181"/>
+      <c r="C87" s="205" t="str">
+        <f aca="false">DEC2HEX(D87,2)</f>
         <v>05</v>
       </c>
-      <c r="D74" s="226" t="n">
-        <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
+      <c r="D87" s="183" t="n">
+        <f aca="false">IF(E87=1,128,0)+IF(F87=1,64,0)+IF(G87=1,32,0)+IF(H87=1,16,0)+IF(I87=1,8,0)+IF(J87=1,4,0)+IF(K87=1,2,0)+IF(L87=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E74" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="191" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="228" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" s="229"/>
-      <c r="N74" s="229"/>
-      <c r="O74" s="225"/>
-      <c r="P74" s="230" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="221" t="s">
-        <v>311</v>
-      </c>
-      <c r="B75" s="223"/>
-      <c r="C75" s="222" t="str">
-        <f aca="false">DEC2HEX(D75,2)</f>
-        <v>15</v>
-      </c>
-      <c r="D75" s="139" t="n">
-        <f aca="false">IF(E75=1,128,0)+IF(F75=1,64,0)+IF(G75=1,32,0)+IF(H75=1,16,0)+IF(I75=1,8,0)+IF(J75=1,4,0)+IF(K75=1,2,0)+IF(L75=1,1,0)</f>
-        <v>21</v>
-      </c>
-      <c r="E75" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="142" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="142" t="n">
-        <v>1</v>
-      </c>
-      <c r="M75" s="231"/>
-      <c r="N75" s="231"/>
-      <c r="O75" s="223"/>
-      <c r="P75" s="232" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="224" t="s">
-        <v>313</v>
-      </c>
-      <c r="B76" s="225"/>
-      <c r="C76" s="200" t="str">
-        <f aca="false">DEC2HEX(D76,2)</f>
-        <v>46</v>
-      </c>
-      <c r="D76" s="226" t="n">
-        <f aca="false">IF(E76=1,128,0)+IF(F76=1,64,0)+IF(G76=1,32,0)+IF(H76=1,16,0)+IF(I76=1,8,0)+IF(J76=1,4,0)+IF(K76=1,2,0)+IF(L76=1,1,0)</f>
-        <v>70</v>
-      </c>
-      <c r="E76" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="191" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="191" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" s="191" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="229"/>
-      <c r="N76" s="229"/>
-      <c r="O76" s="225"/>
-      <c r="P76" s="230"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="211" t="s">
+      <c r="E87" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="243"/>
+      <c r="N87" s="243"/>
+      <c r="O87" s="181"/>
+      <c r="P87" s="244" t="s">
         <v>314</v>
       </c>
-      <c r="B77" s="133"/>
-      <c r="C77" s="17" t="str">
-        <f aca="false">DEC2HEX(D77,2)</f>
-        <v>56</v>
-      </c>
-      <c r="D77" s="107" t="n">
-        <f aca="false">IF(E77=1,128,0)+IF(F77=1,64,0)+IF(G77=1,32,0)+IF(H77=1,16,0)+IF(I77=1,8,0)+IF(J77=1,4,0)+IF(K77=1,2,0)+IF(L77=1,1,0)</f>
-        <v>86</v>
-      </c>
-      <c r="E77" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K77" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="212"/>
-      <c r="N77" s="212"/>
-      <c r="O77" s="133"/>
-      <c r="P77" s="214"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="211" t="s">
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A88" s="235" t="s">
         <v>315</v>
       </c>
-      <c r="B78" s="133"/>
-      <c r="C78" s="17" t="str">
-        <f aca="false">DEC2HEX(D78,2)</f>
-        <v>C7</v>
-      </c>
-      <c r="D78" s="107" t="n">
-        <f aca="false">IF(E78=1,128,0)+IF(F78=1,64,0)+IF(G78=1,32,0)+IF(H78=1,16,0)+IF(I78=1,8,0)+IF(J78=1,4,0)+IF(K78=1,2,0)+IF(L78=1,1,0)</f>
-        <v>199</v>
-      </c>
-      <c r="E78" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" s="212"/>
-      <c r="N78" s="212"/>
-      <c r="O78" s="133"/>
-      <c r="P78" s="214"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="221" t="s">
+      <c r="B88" s="238"/>
+      <c r="C88" s="236" t="str">
+        <f aca="false">DEC2HEX(D88,2)</f>
+        <v>45</v>
+      </c>
+      <c r="D88" s="140" t="n">
+        <f aca="false">IF(E88=1,128,0)+IF(F88=1,64,0)+IF(G88=1,32,0)+IF(H88=1,16,0)+IF(I88=1,8,0)+IF(J88=1,4,0)+IF(K88=1,2,0)+IF(L88=1,1,0)</f>
+        <v>69</v>
+      </c>
+      <c r="E88" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="245"/>
+      <c r="N88" s="245"/>
+      <c r="O88" s="238"/>
+      <c r="P88" s="246" t="s">
         <v>316</v>
       </c>
-      <c r="B79" s="223"/>
-      <c r="C79" s="222" t="str">
-        <f aca="false">DEC2HEX(D79,2)</f>
-        <v>D7</v>
-      </c>
-      <c r="D79" s="139" t="n">
-        <f aca="false">IF(E79=1,128,0)+IF(F79=1,64,0)+IF(G79=1,32,0)+IF(H79=1,16,0)+IF(I79=1,8,0)+IF(J79=1,4,0)+IF(K79=1,2,0)+IF(L79=1,1,0)</f>
-        <v>215</v>
-      </c>
-      <c r="E79" s="138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="142" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="142" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="231"/>
-      <c r="N79" s="231"/>
-      <c r="O79" s="223"/>
-      <c r="P79" s="232"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="224" t="s">
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A89" s="215" t="s">
         <v>317</v>
       </c>
-      <c r="B80" s="225"/>
-      <c r="C80" s="200" t="str">
-        <f aca="false">DEC2HEX(D80,2)</f>
-        <v>0C</v>
-      </c>
-      <c r="D80" s="226" t="n">
-        <f aca="false">IF(E80=1,128,0)+IF(F80=1,64,0)+IF(G80=1,32,0)+IF(H80=1,16,0)+IF(I80=1,8,0)+IF(J80=1,4,0)+IF(K80=1,2,0)+IF(L80=1,1,0)</f>
-        <v>12</v>
-      </c>
-      <c r="E80" s="227" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="227" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="191" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" s="191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="228" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="229"/>
-      <c r="N80" s="229"/>
-      <c r="O80" s="225"/>
-      <c r="P80" s="230"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="221" t="s">
+      <c r="B89" s="130"/>
+      <c r="C89" s="17" t="str">
+        <f aca="false">DEC2HEX(D89,2)</f>
+        <v>37</v>
+      </c>
+      <c r="D89" s="107" t="n">
+        <f aca="false">IF(E89=1,128,0)+IF(F89=1,64,0)+IF(G89=1,32,0)+IF(H89=1,16,0)+IF(I89=1,8,0)+IF(J89=1,4,0)+IF(K89=1,2,0)+IF(L89=1,1,0)</f>
+        <v>55</v>
+      </c>
+      <c r="E89" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="216"/>
+      <c r="N89" s="216"/>
+      <c r="O89" s="130"/>
+      <c r="P89" s="218"/>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A90" s="235" t="s">
         <v>318</v>
       </c>
-      <c r="B81" s="223"/>
-      <c r="C81" s="222" t="str">
-        <f aca="false">DEC2HEX(D81,2)</f>
-        <v>8C</v>
-      </c>
-      <c r="D81" s="139" t="n">
-        <f aca="false">IF(E81=1,128,0)+IF(F81=1,64,0)+IF(G81=1,32,0)+IF(H81=1,16,0)+IF(I81=1,8,0)+IF(J81=1,4,0)+IF(K81=1,2,0)+IF(L81=1,1,0)</f>
-        <v>140</v>
-      </c>
-      <c r="E81" s="138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="138" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="231"/>
-      <c r="N81" s="231"/>
-      <c r="O81" s="223"/>
-      <c r="P81" s="232"/>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="211"/>
-      <c r="B82" s="133"/>
-      <c r="C82" s="17" t="str">
-        <f aca="false">DEC2HEX(D82,2)</f>
+      <c r="B90" s="238"/>
+      <c r="C90" s="236" t="str">
+        <f aca="false">DEC2HEX(D90,2)</f>
+        <v>37</v>
+      </c>
+      <c r="D90" s="140" t="n">
+        <f aca="false">IF(E90=1,128,0)+IF(F90=1,64,0)+IF(G90=1,32,0)+IF(H90=1,16,0)+IF(I90=1,8,0)+IF(J90=1,4,0)+IF(K90=1,2,0)+IF(L90=1,1,0)</f>
+        <v>55</v>
+      </c>
+      <c r="E90" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" s="245"/>
+      <c r="N90" s="245"/>
+      <c r="O90" s="238"/>
+      <c r="P90" s="246"/>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A91" s="215"/>
+      <c r="B91" s="130"/>
+      <c r="C91" s="17" t="str">
+        <f aca="false">DEC2HEX(D91,2)</f>
         <v>00</v>
       </c>
-      <c r="D82" s="107" t="n">
-        <f aca="false">IF(E82=1,128,0)+IF(F82=1,64,0)+IF(G82=1,32,0)+IF(H82=1,16,0)+IF(I82=1,8,0)+IF(J82=1,4,0)+IF(K82=1,2,0)+IF(L82=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E82" s="49"/>
-      <c r="F82" s="107"/>
-      <c r="G82" s="107"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="49"/>
-      <c r="J82" s="107"/>
-      <c r="K82" s="107"/>
-      <c r="L82" s="50"/>
-      <c r="M82" s="212"/>
-      <c r="N82" s="212"/>
-      <c r="O82" s="133"/>
-      <c r="P82" s="214"/>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="221"/>
-      <c r="B83" s="223"/>
-      <c r="C83" s="222" t="str">
-        <f aca="false">DEC2HEX(D83,2)</f>
+      <c r="D91" s="107" t="n">
+        <f aca="false">IF(E91=1,128,0)+IF(F91=1,64,0)+IF(G91=1,32,0)+IF(H91=1,16,0)+IF(I91=1,8,0)+IF(J91=1,4,0)+IF(K91=1,2,0)+IF(L91=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E91" s="49"/>
+      <c r="F91" s="107"/>
+      <c r="G91" s="107"/>
+      <c r="H91" s="50"/>
+      <c r="I91" s="49"/>
+      <c r="J91" s="107"/>
+      <c r="K91" s="107"/>
+      <c r="L91" s="50"/>
+      <c r="M91" s="216"/>
+      <c r="N91" s="216"/>
+      <c r="O91" s="130"/>
+      <c r="P91" s="218"/>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A92" s="235"/>
+      <c r="B92" s="238"/>
+      <c r="C92" s="236" t="str">
+        <f aca="false">DEC2HEX(D92,2)</f>
         <v>00</v>
       </c>
-      <c r="D83" s="139" t="n">
-        <f aca="false">IF(E83=1,128,0)+IF(F83=1,64,0)+IF(G83=1,32,0)+IF(H83=1,16,0)+IF(I83=1,8,0)+IF(J83=1,4,0)+IF(K83=1,2,0)+IF(L83=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="138"/>
-      <c r="F83" s="139"/>
-      <c r="G83" s="139"/>
-      <c r="H83" s="142"/>
-      <c r="I83" s="138"/>
-      <c r="J83" s="139"/>
-      <c r="K83" s="139"/>
-      <c r="L83" s="142"/>
-      <c r="M83" s="231"/>
-      <c r="N83" s="231"/>
-      <c r="O83" s="223"/>
-      <c r="P83" s="232"/>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="134"/>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6" t="s">
+      <c r="D92" s="140" t="n">
+        <f aca="false">IF(E92=1,128,0)+IF(F92=1,64,0)+IF(G92=1,32,0)+IF(H92=1,16,0)+IF(I92=1,8,0)+IF(J92=1,4,0)+IF(K92=1,2,0)+IF(L92=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E92" s="237"/>
+      <c r="F92" s="140"/>
+      <c r="G92" s="140"/>
+      <c r="H92" s="143"/>
+      <c r="I92" s="237"/>
+      <c r="J92" s="140"/>
+      <c r="K92" s="140"/>
+      <c r="L92" s="143"/>
+      <c r="M92" s="245"/>
+      <c r="N92" s="245"/>
+      <c r="O92" s="238"/>
+      <c r="P92" s="246"/>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="130"/>
+    </row>
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="3"/>
-      <c r="O85" s="234"/>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="s">
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="249"/>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="s">
         <v>320</v>
       </c>
     </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="P12" r:id="rId1" location="Basic_and_interchange_formats" display="https://en.wikipedia.org/wiki/IEEE_754#Basic_and_interchange_formats"/>
-    <hyperlink ref="P39" r:id="rId2" location="Durations" display="https://en.wikipedia.org/wiki/ISO_8601#Durations"/>
-    <hyperlink ref="P40" r:id="rId3" location="time" display="http://www.w3.org/TR/xmlschema-2/#time"/>
-    <hyperlink ref="P41" r:id="rId4" location="date" display="http://www.w3.org/TR/xmlschema-2/#date"/>
-    <hyperlink ref="P42" r:id="rId5" location="dateTime" display="http://www.w3.org/TR/xmlschema-2/#dateTime"/>
-    <hyperlink ref="P51" r:id="rId6" display="https://learn.microsoft.com/en-us/office/vba/language/reference/user-interface-help/currency-data-type"/>
+    <hyperlink ref="P40" r:id="rId2" location="Durations" display="https://en.wikipedia.org/wiki/ISO_8601#Durations"/>
+    <hyperlink ref="P41" r:id="rId3" location="time" display="http://www.w3.org/TR/xmlschema-2/#time"/>
+    <hyperlink ref="P42" r:id="rId4" location="date" display="http://www.w3.org/TR/xmlschema-2/#date"/>
+    <hyperlink ref="P43" r:id="rId5" location="dateTime" display="http://www.w3.org/TR/xmlschema-2/#dateTime"/>
+    <hyperlink ref="P56" r:id="rId6" display="https://learn.microsoft.com/en-us/office/vba/language/reference/user-interface-help/currency-data-type"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9983,7 +10543,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>321</v>
@@ -10000,12 +10560,12 @@
       <c r="F1" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="G1" s="235" t="s">
+      <c r="G1" s="250" t="s">
         <v>322</v>
       </c>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235" t="s">
+      <c r="H1" s="250"/>
+      <c r="I1" s="250"/>
+      <c r="J1" s="250" t="s">
         <v>323</v>
       </c>
     </row>
@@ -10020,26 +10580,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>118</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10053,13 +10613,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>118</v>
@@ -10069,10 +10629,10 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10089,25 +10649,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="5" t="s">
         <v>335</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10124,25 +10684,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="I5" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>335</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10156,28 +10716,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I6" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="5" t="s">
         <v>335</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10191,28 +10751,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>335</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10226,26 +10786,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>118</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10259,13 +10819,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>118</v>
@@ -10275,10 +10835,10 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10292,28 +10852,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="G10" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10327,28 +10887,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10362,28 +10922,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="G12" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10397,28 +10957,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="G13" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Connection" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Author</author>
   </authors>
@@ -51,6 +51,27 @@
           <t xml:space="preserve">If the servet represents an array, and we're specifying an element in that array, then this value specifies the array, and the following value represent the index.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>26</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="N32" authorId="0">
       <text>
@@ -63,6 +84,27 @@
           <t xml:space="preserve">This consists if Morph links.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>26</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="N33" authorId="0">
       <text>
@@ -75,6 +117,27 @@
           <t xml:space="preserve">This consists if Morph links.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="N34" authorId="0">
       <text>
@@ -87,13 +150,34 @@
           <t xml:space="preserve">This consists of a value (starting with a ValueType).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>26</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="348">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -131,7 +215,7 @@
     <t xml:space="preserve">This amounts to the following set of bytes:</t>
   </si>
   <si>
-    <t xml:space="preserve">0x4D, 0x6F, 0x72, 0x70, 0x68, 0x00, 0x01, 0x01</t>
+    <t xml:space="preserve">0x4D, 0x6F, 0x72, 0x70, 0x68, 0x00, 0x02, 0x01</t>
   </si>
   <si>
     <r>
@@ -187,16 +271,16 @@
     <t xml:space="preserve">Hexadecimal:</t>
   </si>
   <si>
-    <t xml:space="preserve">$E000</t>
+    <t xml:space="preserve">$3000</t>
   </si>
   <si>
     <t xml:space="preserve">Connection port (encrypted)</t>
   </si>
   <si>
-    <t xml:space="preserve">$E055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proper Morph implementations will use a daemon that listens for incoming connections on port $E000.</t>
+    <t xml:space="preserve">$3055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proper Morph implementations will use a daemon that listens for incoming connections on port $3000.</t>
   </si>
   <si>
     <t xml:space="preserve">A Morph daemon will relay all Morph packets, subject to system administrator permissions, such as enforcing the use of encryption and validation when deemed neccessary</t>
@@ -259,6 +343,12 @@
     <t xml:space="preserve">C#</t>
   </si>
   <si>
+    <t xml:space="preserve">C++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delphi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dec</t>
   </si>
   <si>
@@ -310,9 +400,6 @@
     <t xml:space="preserve">ToPath</t>
   </si>
   <si>
-    <t xml:space="preserve">HasPathFrom</t>
-  </si>
-  <si>
     <t xml:space="preserve">FromPath</t>
   </si>
   <si>
@@ -370,7 +457,10 @@
     <t xml:space="preserve">IsApartmentNotShared</t>
   </si>
   <si>
-    <t xml:space="preserve">SessionID+P60</t>
+    <t xml:space="preserve">SessionID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probably will never be needed. Not implemented.</t>
   </si>
   <si>
     <t xml:space="preserve">IsApartmentProxy</t>
@@ -1245,7 +1335,7 @@
     <t xml:space="preserve">+</t>
   </si>
   <si>
-    <t xml:space="preserve">String</t>
+    <t xml:space="preserve">Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">HasValueName</t>
@@ -1314,7 +1404,7 @@
     <t xml:space="preserve">ValueType (+SimpleType)</t>
   </si>
   <si>
-    <t xml:space="preserve">Specifies the type of all elements in the array.</t>
+    <t xml:space="preserve">Specifies the type of all elements in the array. For multi-dimensional arrays, use one array ValueType per dimension.</t>
   </si>
   <si>
     <t xml:space="preserve">ArrayElemCount</t>
@@ -1455,10 +1545,10 @@
     <t xml:space="preserve">ValueType</t>
   </si>
   <si>
-    <t xml:space="preserve">String: 2 bytes representing byte count of the string, followed by UTF-8 characters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SimpleType: See tab SimpleType</t>
+    <t xml:space="preserve">SimpleType:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See tab SimpleType</t>
   </si>
   <si>
     <t xml:space="preserve">Examples</t>
@@ -1473,34 +1563,34 @@
     <t xml:space="preserve">Values obtained</t>
   </si>
   <si>
-    <t xml:space="preserve">(ValueName), </t>
+    <t xml:space="preserve">(TypeName), (ValueName), </t>
   </si>
   <si>
     <t xml:space="preserve">IsStream</t>
   </si>
   <si>
-    <t xml:space="preserve">(ValueName), (TypeName), ReferenceID</t>
+    <t xml:space="preserve">(TypeName), (ValueName), ReferenceID</t>
   </si>
   <si>
     <t xml:space="preserve">IsServlet</t>
   </si>
   <si>
-    <t xml:space="preserve">(ValueName), (TypeName), ReferenceID, ApartmentID, (DevicePath), (Index)</t>
+    <t xml:space="preserve">(TypeName), (ValueName), ReferenceID, ApartmentID, (DevicePath), (Index)</t>
   </si>
   <si>
     <t xml:space="preserve">IsSimple</t>
   </si>
   <si>
-    <t xml:space="preserve">(ValueName), (TypeName), SimpleType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(ValueName), (TypeName), ArrayElemCount, (ArrayElemType), Values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(ValueName), (TypeName), StructElemCount, Values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(ValueName), (TypeName), (CustomTypeName), SimpleType</t>
+    <t xml:space="preserve">(TypeName), (ValueName), SimpleType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(TypeName), (ValueName), (ArrayElemType), ArrayElemCount, Values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(TypeName), (ValueName), StructElemCount, Values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TypeName, (ValueName), SimpleType</t>
   </si>
   <si>
     <t xml:space="preserve">Integer</t>
@@ -1555,6 +1645,9 @@
   </si>
   <si>
     <t xml:space="preserve">binary32, binary64, binary128, binary256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String</t>
   </si>
   <si>
     <t xml:space="preserve">ByteCount</t>
@@ -1815,6 +1908,9 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">This is an exception to the rule that the byte count is 4 bytes for strings or 2 bytes for identifiers.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Currency</t>
   </si>
   <si>
@@ -2021,16 +2117,16 @@
     <t xml:space="preserve">Request</t>
   </si>
   <si>
+    <t xml:space="preserve">Lossy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start - Send</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkSequenceStartSend</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lossless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start - Send</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkSequenceStartSend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lossy</t>
   </si>
   <si>
     <t xml:space="preserve">Confirm</t>
@@ -2063,7 +2159,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2114,6 +2210,13 @@
       <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2688,11 +2791,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="262">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3093,6 +3196,54 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3129,11 +3280,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3141,11 +3292,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3157,19 +3308,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3193,19 +3344,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3277,7 +3428,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3289,7 +3440,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3297,15 +3448,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3333,7 +3484,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3341,15 +3492,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3365,27 +3516,27 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3429,27 +3580,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3461,15 +3608,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3489,7 +3636,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3497,7 +3644,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3573,7 +3720,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3756,7 +3903,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -3778,34 +3925,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -3979,7 +4126,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>57344</v>
+        <v>12288</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4003,7 +4150,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>57429</v>
+        <v>12373</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4084,7 +4231,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S1048576"/>
+  <dimension ref="A1:U1048576"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="15"/>
@@ -4096,7 +4243,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="12" width="13.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="11" width="17.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="46.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="12" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="18" style="12" width="6.85"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="22" style="11" width="9.14"/>
   </cols>
   <sheetData>
@@ -4144,6 +4291,12 @@
       <c r="S1" s="20" t="s">
         <v>40</v>
       </c>
+      <c r="T1" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="20" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="21"/>
@@ -4173,17 +4326,17 @@
         <v>0</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O2" s="28" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P2" s="22"/>
       <c r="Q2" s="29"/>
@@ -4191,14 +4344,22 @@
         <f aca="false">CONCATENATE(ROUND(AVERAGE(R3:R68)*100/3,0),"%")</f>
         <v>81%</v>
       </c>
-      <c r="S2" s="20" t="str">
+      <c r="S2" s="20" t="e">
         <f aca="false">CONCATENATE(ROUND(AVERAGE(S3:S68)*100/4,0),"%")</f>
-        <v>69%</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T2" s="20" t="e">
+        <f aca="false">CONCATENATE(ROUND(AVERAGE(T3:T68)*100/4,0),"%")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U2" s="20" t="e">
+        <f aca="false">CONCATENATE(ROUND(AVERAGE(U3:U68)*100/4,0),"%")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="31"/>
@@ -4234,22 +4395,22 @@
       </c>
       <c r="P3" s="38"/>
       <c r="Q3" s="39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R3" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S3" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" s="32" t="str">
         <f aca="false">IF(COUNTA(D5:D8)&gt;0,"z","")</f>
@@ -4294,14 +4455,14 @@
       </c>
       <c r="P4" s="38"/>
       <c r="Q4" s="39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R4" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S4" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A5" s="44"/>
@@ -4310,7 +4471,7 @@
       <c r="D5" s="46"/>
       <c r="E5" s="47"/>
       <c r="F5" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G5" s="46"/>
       <c r="H5" s="47"/>
@@ -4319,14 +4480,14 @@
       <c r="K5" s="49"/>
       <c r="L5" s="50"/>
       <c r="M5" s="51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N5" s="52"/>
       <c r="O5" s="53" t="n">
         <v>4</v>
       </c>
       <c r="P5" s="54" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q5" s="55"/>
     </row>
@@ -4336,7 +4497,7 @@
       <c r="C6" s="57"/>
       <c r="D6" s="58"/>
       <c r="E6" s="59" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="60"/>
       <c r="G6" s="58"/>
@@ -4346,7 +4507,7 @@
       <c r="K6" s="49"/>
       <c r="L6" s="50"/>
       <c r="M6" s="61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N6" s="62"/>
       <c r="O6" s="59"/>
@@ -4374,7 +4535,7 @@
         <v>4</v>
       </c>
       <c r="P7" s="63" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q7" s="64"/>
     </row>
@@ -4383,7 +4544,7 @@
       <c r="B8" s="56"/>
       <c r="C8" s="57"/>
       <c r="D8" s="58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" s="59"/>
       <c r="F8" s="60"/>
@@ -4394,18 +4555,20 @@
       <c r="K8" s="49"/>
       <c r="L8" s="50"/>
       <c r="M8" s="61" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N8" s="58"/>
       <c r="O8" s="59" t="n">
         <v>4</v>
       </c>
       <c r="P8" s="63" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q8" s="64"/>
       <c r="R8" s="13"/>
       <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A9" s="56"/>
@@ -4425,19 +4588,21 @@
         <v>0</v>
       </c>
       <c r="O9" s="59" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P9" s="63" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q9" s="64"/>
       <c r="R9" s="13"/>
       <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A10" s="56"/>
       <c r="B10" s="56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="62"/>
@@ -4454,20 +4619,20 @@
         <v>0</v>
       </c>
       <c r="O10" s="59" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P10" s="63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="64"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" s="32" t="str">
         <f aca="false">IF(COUNTA(D13:D14)&gt;0,"z","")</f>
@@ -4506,16 +4671,16 @@
         <v>5</v>
       </c>
       <c r="O11" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P11" s="38"/>
       <c r="Q11" s="39"/>
       <c r="R11" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S11" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A12" s="66"/>
@@ -4523,7 +4688,9 @@
       <c r="C12" s="67"/>
       <c r="D12" s="68"/>
       <c r="E12" s="69"/>
-      <c r="F12" s="70"/>
+      <c r="F12" s="70" t="s">
+        <v>52</v>
+      </c>
       <c r="G12" s="68"/>
       <c r="H12" s="69"/>
       <c r="I12" s="69"/>
@@ -4531,14 +4698,14 @@
       <c r="K12" s="49"/>
       <c r="L12" s="50"/>
       <c r="M12" s="71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N12" s="68"/>
       <c r="O12" s="69" t="n">
         <v>4</v>
       </c>
       <c r="P12" s="72" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q12" s="73"/>
     </row>
@@ -4563,10 +4730,10 @@
         <v>4</v>
       </c>
       <c r="P13" s="54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
@@ -4587,20 +4754,20 @@
         <v>0</v>
       </c>
       <c r="O14" s="69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P14" s="72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="32" t="str">
         <f aca="false">IF(COUNTA(D16:D17)&gt;0,"z","")</f>
@@ -4636,21 +4803,21 @@
       </c>
       <c r="M15" s="37"/>
       <c r="N15" s="42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O15" s="43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P15" s="38"/>
       <c r="Q15" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R15" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="40" t="n">
-        <v>0</v>
-      </c>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A16" s="76"/>
@@ -4692,11 +4859,11 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D18" s="32" t="str">
         <f aca="false">IF(COUNTA(D19:D22)&gt;0,"z","")</f>
@@ -4735,16 +4902,16 @@
         <v>5</v>
       </c>
       <c r="O18" s="43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P18" s="38"/>
       <c r="Q18" s="39"/>
       <c r="R18" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S18" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S18" s="40"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A19" s="76"/>
@@ -4764,19 +4931,19 @@
       <c r="K19" s="49"/>
       <c r="L19" s="50"/>
       <c r="M19" s="97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N19" s="81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O19" s="95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P19" s="98" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q19" s="99" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -4797,7 +4964,7 @@
       <c r="K20" s="49"/>
       <c r="L20" s="50"/>
       <c r="M20" s="97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N20" s="81" t="n">
         <v>4</v>
@@ -4806,42 +4973,48 @@
         <v>4</v>
       </c>
       <c r="P20" s="98" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q20" s="99" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" s="111" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A21" s="100"/>
+      <c r="B21" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="Q20" s="99" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="76"/>
-      <c r="B21" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="81" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="95"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="97" t="s">
-        <v>77</v>
-      </c>
-      <c r="N21" s="81" t="n">
+      <c r="C21" s="101"/>
+      <c r="D21" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="103"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="107" t="s">
+        <v>78</v>
+      </c>
+      <c r="N21" s="102" t="n">
         <v>8</v>
       </c>
-      <c r="O21" s="95" t="n">
+      <c r="O21" s="103" t="n">
         <v>8</v>
       </c>
-      <c r="P21" s="98" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q21" s="99"/>
+      <c r="P21" s="108" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q21" s="109" t="s">
+        <v>80</v>
+      </c>
+      <c r="R21" s="110"/>
+      <c r="S21" s="110"/>
+      <c r="T21" s="110"/>
+      <c r="U21" s="110"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A22" s="66"/>
@@ -4861,28 +5034,28 @@
       <c r="K22" s="49"/>
       <c r="L22" s="50"/>
       <c r="M22" s="71" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N22" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="O22" s="100" t="n">
+      <c r="O22" s="112" t="n">
         <v>4</v>
       </c>
       <c r="P22" s="72" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="73" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D23" s="32" t="str">
         <f aca="false">IF(COUNTA(D24:D25)&gt;0,"z","")</f>
@@ -4927,18 +5100,18 @@
       </c>
       <c r="P23" s="38"/>
       <c r="Q23" s="39" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R23" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S23" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S23" s="40"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A24" s="56"/>
-      <c r="B24" s="101"/>
+      <c r="B24" s="113"/>
       <c r="C24" s="57"/>
       <c r="D24" s="58"/>
       <c r="E24" s="59"/>
@@ -4957,7 +5130,7 @@
         <v>4</v>
       </c>
       <c r="P24" s="63" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q24" s="64"/>
     </row>
@@ -4982,11 +5155,11 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D26" s="32" t="str">
         <f aca="false">IF(COUNTA(D27:D30)&gt;0,"z","")</f>
@@ -5022,22 +5195,22 @@
       </c>
       <c r="M26" s="41"/>
       <c r="N26" s="42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O26" s="43" t="str">
         <f aca="false">CONCATENATE(1+SUM(O27:O30)," + str")</f>
-        <v>5 + str</v>
+        <v>1 + str</v>
       </c>
       <c r="P26" s="38"/>
       <c r="Q26" s="39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R26" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S26" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A27" s="66"/>
@@ -5054,13 +5227,13 @@
       <c r="L27" s="50"/>
       <c r="M27" s="71"/>
       <c r="N27" s="68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O27" s="69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P27" s="72" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q27" s="73"/>
     </row>
@@ -5071,7 +5244,7 @@
       <c r="D28" s="68"/>
       <c r="E28" s="69"/>
       <c r="F28" s="70" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G28" s="68"/>
       <c r="H28" s="69"/>
@@ -5080,26 +5253,22 @@
       <c r="K28" s="49"/>
       <c r="L28" s="50"/>
       <c r="M28" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="N28" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="O28" s="47" t="n">
-        <v>4</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="N28" s="46"/>
+      <c r="O28" s="47"/>
       <c r="P28" s="54"/>
       <c r="Q28" s="73"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A29" s="66"/>
-      <c r="B29" s="102" t="s">
-        <v>88</v>
+      <c r="B29" s="114" t="s">
+        <v>90</v>
       </c>
       <c r="C29" s="67"/>
       <c r="D29" s="68"/>
       <c r="E29" s="69" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F29" s="70"/>
       <c r="G29" s="68"/>
@@ -5109,7 +5278,7 @@
       <c r="K29" s="49"/>
       <c r="L29" s="50"/>
       <c r="M29" s="51" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N29" s="46"/>
       <c r="O29" s="47"/>
@@ -5118,12 +5287,12 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A30" s="44"/>
-      <c r="B30" s="102" t="s">
-        <v>88</v>
+      <c r="B30" s="114" t="s">
+        <v>90</v>
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="46" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E30" s="53"/>
       <c r="F30" s="48"/>
@@ -5134,7 +5303,7 @@
       <c r="K30" s="49"/>
       <c r="L30" s="50"/>
       <c r="M30" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N30" s="46"/>
       <c r="O30" s="47"/>
@@ -5145,7 +5314,7 @@
       <c r="A31" s="30"/>
       <c r="B31" s="30"/>
       <c r="C31" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D31" s="32" t="str">
         <f aca="false">IF(COUNTA(D32:D34)&gt;0,"z","")</f>
@@ -5186,6 +5355,8 @@
       <c r="Q31" s="39"/>
       <c r="R31" s="40"/>
       <c r="S31" s="40"/>
+      <c r="T31" s="40"/>
+      <c r="U31" s="40"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A32" s="66"/>
@@ -5202,7 +5373,7 @@
       <c r="L32" s="50"/>
       <c r="M32" s="71"/>
       <c r="N32" s="74"/>
-      <c r="O32" s="100"/>
+      <c r="O32" s="112"/>
       <c r="P32" s="72"/>
       <c r="Q32" s="73"/>
     </row>
@@ -5211,7 +5382,7 @@
       <c r="B33" s="66"/>
       <c r="C33" s="67"/>
       <c r="D33" s="68"/>
-      <c r="E33" s="100"/>
+      <c r="E33" s="112"/>
       <c r="F33" s="70"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
@@ -5221,7 +5392,7 @@
       <c r="L33" s="50"/>
       <c r="M33" s="71"/>
       <c r="N33" s="74"/>
-      <c r="O33" s="100"/>
+      <c r="O33" s="112"/>
       <c r="P33" s="72"/>
       <c r="Q33" s="73"/>
     </row>
@@ -5246,11 +5417,11 @@
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D35" s="32" t="str">
         <f aca="false">IF(COUNTA(D36)&gt;0,"z","")</f>
@@ -5295,14 +5466,14 @@
       </c>
       <c r="P35" s="38"/>
       <c r="Q35" s="39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R35" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S35" s="40" t="n">
-        <v>0</v>
-      </c>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="40"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A36" s="85"/>
@@ -5325,17 +5496,17 @@
         <v>4</v>
       </c>
       <c r="P36" s="93" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q36" s="94"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D37" s="32" t="str">
         <f aca="false">IF(COUNTA(D38:D42)&gt;0,"z","")</f>
@@ -5374,27 +5545,27 @@
         <v>5</v>
       </c>
       <c r="O37" s="43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P37" s="38"/>
       <c r="Q37" s="39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R37" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S37" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S37" s="40"/>
+      <c r="T37" s="40"/>
+      <c r="U37" s="40"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A38" s="66"/>
-      <c r="B38" s="103"/>
+      <c r="B38" s="115"/>
       <c r="C38" s="67"/>
       <c r="D38" s="68"/>
-      <c r="E38" s="100"/>
+      <c r="E38" s="112"/>
       <c r="F38" s="70" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G38" s="68"/>
       <c r="H38" s="69"/>
@@ -5403,10 +5574,10 @@
       <c r="K38" s="49"/>
       <c r="L38" s="50"/>
       <c r="M38" s="71" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N38" s="68"/>
-      <c r="O38" s="100"/>
+      <c r="O38" s="112"/>
       <c r="P38" s="72"/>
       <c r="Q38" s="73"/>
     </row>
@@ -5416,7 +5587,7 @@
       <c r="C39" s="45"/>
       <c r="D39" s="46"/>
       <c r="E39" s="53" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F39" s="48"/>
       <c r="G39" s="46"/>
@@ -5426,21 +5597,21 @@
       <c r="K39" s="49"/>
       <c r="L39" s="50"/>
       <c r="M39" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N39" s="46"/>
       <c r="O39" s="53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P39" s="54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q39" s="55"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A40" s="44"/>
       <c r="B40" s="44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C40" s="45"/>
       <c r="D40" s="46"/>
@@ -5458,14 +5629,14 @@
         <v>4</v>
       </c>
       <c r="P40" s="54" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q40" s="55"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A41" s="44"/>
       <c r="B41" s="44" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C41" s="45"/>
       <c r="D41" s="46"/>
@@ -5483,7 +5654,7 @@
         <v>16</v>
       </c>
       <c r="P41" s="54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q41" s="55"/>
     </row>
@@ -5492,7 +5663,7 @@
       <c r="B42" s="85"/>
       <c r="C42" s="86"/>
       <c r="D42" s="92" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E42" s="88"/>
       <c r="F42" s="89"/>
@@ -5503,14 +5674,14 @@
       <c r="K42" s="49"/>
       <c r="L42" s="50"/>
       <c r="M42" s="91" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N42" s="87"/>
       <c r="O42" s="88" t="n">
         <v>2</v>
       </c>
       <c r="P42" s="93" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q42" s="94"/>
     </row>
@@ -5518,7 +5689,7 @@
       <c r="A43" s="41"/>
       <c r="B43" s="30"/>
       <c r="C43" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D43" s="32" t="str">
         <f aca="false">IF(COUNTA(D44)&gt;0,"z","")</f>
@@ -5555,13 +5726,15 @@
       <c r="M43" s="37"/>
       <c r="N43" s="42"/>
       <c r="O43" s="43"/>
-      <c r="P43" s="104"/>
+      <c r="P43" s="116"/>
       <c r="Q43" s="39"/>
       <c r="R43" s="40"/>
       <c r="S43" s="40"/>
+      <c r="T43" s="40"/>
+      <c r="U43" s="40"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A44" s="105"/>
+      <c r="A44" s="117"/>
       <c r="B44" s="85"/>
       <c r="C44" s="86"/>
       <c r="D44" s="92"/>
@@ -5576,14 +5749,14 @@
       <c r="M44" s="91"/>
       <c r="N44" s="87"/>
       <c r="O44" s="88"/>
-      <c r="P44" s="106"/>
+      <c r="P44" s="118"/>
       <c r="Q44" s="94"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="30"/>
       <c r="B45" s="30"/>
       <c r="C45" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D45" s="32" t="str">
         <f aca="false">IF(COUNTA(D46:D50)&gt;0,"z","")</f>
@@ -5624,6 +5797,8 @@
       <c r="Q45" s="39"/>
       <c r="R45" s="40"/>
       <c r="S45" s="40"/>
+      <c r="T45" s="40"/>
+      <c r="U45" s="40"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A46" s="44"/>
@@ -5722,11 +5897,11 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B51" s="30"/>
       <c r="C51" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D51" s="32" t="str">
         <f aca="false">IF(COUNTA(D52:D59)&gt;0,"z","")</f>
@@ -5769,23 +5944,23 @@
       </c>
       <c r="P51" s="38"/>
       <c r="Q51" s="39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R51" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S51" s="40" t="n">
-        <v>4</v>
-      </c>
+      <c r="S51" s="40"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="40"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A52" s="66"/>
       <c r="B52" s="66"/>
       <c r="C52" s="67"/>
       <c r="D52" s="74"/>
-      <c r="E52" s="100"/>
+      <c r="E52" s="112"/>
       <c r="F52" s="70" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G52" s="68"/>
       <c r="H52" s="69"/>
@@ -5794,7 +5969,7 @@
       <c r="K52" s="49"/>
       <c r="L52" s="50"/>
       <c r="M52" s="71" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N52" s="68"/>
       <c r="O52" s="69"/>
@@ -5806,8 +5981,8 @@
       <c r="B53" s="66"/>
       <c r="C53" s="67"/>
       <c r="D53" s="74"/>
-      <c r="E53" s="100" t="s">
-        <v>50</v>
+      <c r="E53" s="112" t="s">
+        <v>52</v>
       </c>
       <c r="F53" s="70"/>
       <c r="G53" s="68"/>
@@ -5817,7 +5992,7 @@
       <c r="K53" s="49"/>
       <c r="L53" s="50"/>
       <c r="M53" s="71" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N53" s="68"/>
       <c r="O53" s="69"/>
@@ -5827,13 +6002,13 @@
     <row r="54" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A54" s="66"/>
       <c r="B54" s="66" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C54" s="67"/>
       <c r="D54" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="100"/>
+        <v>52</v>
+      </c>
+      <c r="E54" s="112"/>
       <c r="F54" s="70"/>
       <c r="G54" s="68"/>
       <c r="H54" s="69"/>
@@ -5842,7 +6017,7 @@
       <c r="K54" s="49"/>
       <c r="L54" s="50"/>
       <c r="M54" s="71" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N54" s="68"/>
       <c r="O54" s="69"/>
@@ -5852,13 +6027,13 @@
     <row r="55" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A55" s="66"/>
       <c r="B55" s="66" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C55" s="67"/>
       <c r="D55" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="E55" s="100"/>
+        <v>52</v>
+      </c>
+      <c r="E55" s="112"/>
       <c r="F55" s="70"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
@@ -5867,7 +6042,7 @@
       <c r="K55" s="49"/>
       <c r="L55" s="50"/>
       <c r="M55" s="71" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N55" s="68"/>
       <c r="O55" s="69"/>
@@ -5877,13 +6052,13 @@
     <row r="56" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A56" s="66"/>
       <c r="B56" s="66" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C56" s="67"/>
       <c r="D56" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56" s="100"/>
+        <v>52</v>
+      </c>
+      <c r="E56" s="112"/>
       <c r="F56" s="70"/>
       <c r="G56" s="68"/>
       <c r="H56" s="69"/>
@@ -5892,7 +6067,7 @@
       <c r="K56" s="49"/>
       <c r="L56" s="50"/>
       <c r="M56" s="71" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N56" s="68"/>
       <c r="O56" s="69"/>
@@ -5902,7 +6077,7 @@
     <row r="57" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A57" s="66"/>
       <c r="B57" s="66" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C57" s="67"/>
       <c r="D57" s="74"/>
@@ -5922,18 +6097,18 @@
         <v>4</v>
       </c>
       <c r="P57" s="72" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q57" s="73"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A58" s="66"/>
       <c r="B58" s="66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C58" s="67"/>
       <c r="D58" s="74"/>
-      <c r="E58" s="100"/>
+      <c r="E58" s="112"/>
       <c r="F58" s="70"/>
       <c r="G58" s="68"/>
       <c r="H58" s="69"/>
@@ -5949,14 +6124,14 @@
         <v>4</v>
       </c>
       <c r="P58" s="72" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q58" s="73"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A59" s="85"/>
       <c r="B59" s="85" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C59" s="86"/>
       <c r="D59" s="87"/>
@@ -5976,17 +6151,17 @@
         <v>4</v>
       </c>
       <c r="P59" s="93" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q59" s="94"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B60" s="30"/>
       <c r="C60" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D60" s="32" t="str">
         <f aca="false">IF(COUNTA(D61:D63)&gt;0,"z","")</f>
@@ -6022,21 +6197,21 @@
       </c>
       <c r="M60" s="37"/>
       <c r="N60" s="42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O60" s="43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P60" s="38"/>
       <c r="Q60" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R60" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="S60" s="40" t="n">
-        <v>0</v>
-      </c>
+      <c r="S60" s="40"/>
+      <c r="T60" s="40"/>
+      <c r="U60" s="40"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A61" s="66"/>
@@ -6052,7 +6227,7 @@
       <c r="K61" s="49"/>
       <c r="L61" s="50"/>
       <c r="M61" s="71" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N61" s="68"/>
       <c r="O61" s="69"/>
@@ -6073,7 +6248,7 @@
       <c r="K62" s="49"/>
       <c r="L62" s="50"/>
       <c r="M62" s="71" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N62" s="68"/>
       <c r="O62" s="69"/>
@@ -6094,22 +6269,22 @@
       <c r="K63" s="49"/>
       <c r="L63" s="50"/>
       <c r="M63" s="91" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N63" s="87"/>
       <c r="O63" s="88"/>
       <c r="P63" s="93" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q63" s="94"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B64" s="30"/>
       <c r="C64" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D64" s="32" t="str">
         <f aca="false">IF(COUNTA(D65:D67)&gt;0,"z","")</f>
@@ -6154,18 +6329,18 @@
       </c>
       <c r="P64" s="38"/>
       <c r="Q64" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R64" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="S64" s="40" t="n">
-        <v>1</v>
-      </c>
+      <c r="S64" s="40"/>
+      <c r="T64" s="40"/>
+      <c r="U64" s="40"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A65" s="66"/>
-      <c r="B65" s="103"/>
+      <c r="B65" s="115"/>
       <c r="C65" s="67"/>
       <c r="D65" s="68"/>
       <c r="E65" s="69"/>
@@ -6184,7 +6359,7 @@
         <v>4</v>
       </c>
       <c r="P65" s="72" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q65" s="73"/>
     </row>
@@ -6202,7 +6377,7 @@
       <c r="K66" s="49"/>
       <c r="L66" s="50"/>
       <c r="M66" s="71" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N66" s="68"/>
       <c r="O66" s="69"/>
@@ -6214,7 +6389,7 @@
       <c r="B67" s="66"/>
       <c r="C67" s="67"/>
       <c r="D67" s="74"/>
-      <c r="E67" s="100"/>
+      <c r="E67" s="112"/>
       <c r="F67" s="70"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
@@ -6223,7 +6398,7 @@
       <c r="K67" s="49"/>
       <c r="L67" s="50"/>
       <c r="M67" s="71" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N67" s="68"/>
       <c r="O67" s="69"/>
@@ -6234,7 +6409,7 @@
       <c r="A68" s="30"/>
       <c r="B68" s="30"/>
       <c r="C68" s="31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D68" s="32" t="str">
         <f aca="false">IF(COUNTA(D69:D72)&gt;0,"z","")</f>
@@ -6275,6 +6450,8 @@
       <c r="Q68" s="39"/>
       <c r="R68" s="40"/>
       <c r="S68" s="40"/>
+      <c r="T68" s="40"/>
+      <c r="U68" s="40"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A69" s="66"/>
@@ -6356,13 +6533,13 @@
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="L74" s="107"/>
+      <c r="L74" s="119"/>
       <c r="M74" s="3" t="s">
         <v>39</v>
       </c>
       <c r="O74" s="11"/>
       <c r="P74" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6371,13 +6548,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O75" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6386,13 +6563,13 @@
         <v>1</v>
       </c>
       <c r="M76" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>1</v>
       </c>
       <c r="P76" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6401,13 +6578,13 @@
         <v>2</v>
       </c>
       <c r="M77" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>2</v>
       </c>
       <c r="P77" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6416,13 +6593,13 @@
         <v>3</v>
       </c>
       <c r="M78" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>3</v>
       </c>
       <c r="P78" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6431,7 +6608,7 @@
         <v>4</v>
       </c>
       <c r="P79" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6471,76 +6648,76 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="108" t="s">
-        <v>135</v>
+      <c r="A1" s="120" t="s">
+        <v>137</v>
       </c>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="109" t="s">
-        <v>136</v>
+      <c r="A3" s="121" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="109"/>
-      <c r="B4" s="109" t="s">
-        <v>137</v>
+      <c r="A4" s="121"/>
+      <c r="B4" s="121" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="109"/>
+      <c r="A5" s="121"/>
     </row>
     <row r="6" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="109" t="s">
-        <v>138</v>
+      <c r="A6" s="121" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="109" t="s">
-        <v>139</v>
+      <c r="B7" s="121" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="109" t="s">
-        <v>140</v>
+      <c r="B8" s="121" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="109" t="s">
-        <v>141</v>
+      <c r="B9" s="121" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="109"/>
+      <c r="B10" s="121"/>
     </row>
     <row r="11" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="109" t="s">
-        <v>142</v>
+      <c r="A11" s="121" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="109" t="s">
-        <v>143</v>
+      <c r="B12" s="121" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="109" t="s">
-        <v>144</v>
+      <c r="B13" s="121" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="109" t="s">
-        <v>145</v>
+      <c r="B14" s="121" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6548,13 +6725,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C21" s="1"/>
     </row>
@@ -6566,19 +6743,19 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C26" s="1"/>
     </row>
@@ -6636,9 +6813,9 @@
   <dimension ref="A1:S1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="110" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="122" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="111" width="3.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="123" width="3.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="5" width="3.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="18.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="15.59"/>
@@ -6650,974 +6827,991 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="122" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="112" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="113" t="n">
+      <c r="C1" s="124" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="125" t="n">
         <v>7</v>
       </c>
-      <c r="E1" s="113" t="n">
+      <c r="E1" s="125" t="n">
         <v>6</v>
       </c>
-      <c r="F1" s="113" t="n">
+      <c r="F1" s="125" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="113" t="n">
+      <c r="G1" s="125" t="n">
         <v>4</v>
       </c>
-      <c r="H1" s="113" t="n">
+      <c r="H1" s="125" t="n">
         <v>3</v>
       </c>
-      <c r="I1" s="113" t="n">
+      <c r="I1" s="125" t="n">
         <v>2</v>
       </c>
-      <c r="J1" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1" s="113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1" s="110" t="s">
+      <c r="J1" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="113" t="s">
-        <v>153</v>
-      </c>
-      <c r="O1" s="113" t="s">
-        <v>154</v>
-      </c>
-      <c r="P1" s="110" t="s">
+      <c r="M1" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="125" t="s">
         <v>155</v>
       </c>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
+      <c r="O1" s="125" t="s">
+        <v>156</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="114"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="120" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2" s="121" t="s">
+      <c r="B2" s="126"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="132" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="133" t="s">
+        <v>158</v>
+      </c>
+      <c r="M2" s="133" t="s">
+        <v>159</v>
+      </c>
+      <c r="N2" s="132" t="s">
+        <v>160</v>
+      </c>
+      <c r="O2" s="132" t="s">
+        <v>161</v>
+      </c>
+      <c r="P2" s="134"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="141"/>
+      <c r="L3" s="142" t="s">
+        <v>162</v>
+      </c>
+      <c r="M3" s="142" t="s">
+        <v>163</v>
+      </c>
+      <c r="N3" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="O3" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="P3" s="143"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="144"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="119" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="119"/>
+      <c r="K4" s="141"/>
+      <c r="L4" s="142" t="s">
+        <v>164</v>
+      </c>
+      <c r="M4" s="142" t="s">
+        <v>165</v>
+      </c>
+      <c r="N4" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="P4" s="143"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="149" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="150"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="156" t="s">
+        <v>168</v>
+      </c>
+      <c r="M5" s="156"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="157"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="159" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="160"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="163"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="163"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="166"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="166"/>
+      <c r="O6" s="166"/>
+      <c r="P6" s="168"/>
+      <c r="Q6" s="169"/>
+      <c r="R6" s="169"/>
+      <c r="S6" s="169"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="140"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="142" t="s">
+        <v>170</v>
+      </c>
+      <c r="M7" s="142"/>
+      <c r="N7" s="141"/>
+      <c r="O7" s="141"/>
+      <c r="P7" s="143"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="140"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="142" t="s">
+        <v>171</v>
+      </c>
+      <c r="M8" s="142"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="141"/>
+      <c r="P8" s="143"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="140"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="142" t="s">
+        <v>172</v>
+      </c>
+      <c r="M9" s="142"/>
+      <c r="N9" s="141"/>
+      <c r="O9" s="141"/>
+      <c r="P9" s="143"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B10" s="135"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="140"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="142" t="s">
+        <v>173</v>
+      </c>
+      <c r="M10" s="142"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="141"/>
+      <c r="P10" s="143"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="158" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="170" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="171"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="173"/>
+      <c r="K11" s="177"/>
+      <c r="L11" s="178"/>
+      <c r="M11" s="178"/>
+      <c r="N11" s="177"/>
+      <c r="O11" s="177"/>
+      <c r="P11" s="179"/>
+      <c r="Q11" s="169"/>
+      <c r="R11" s="169"/>
+      <c r="S11" s="169"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B12" s="135"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="141"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="142" t="s">
+        <v>176</v>
+      </c>
+      <c r="N12" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="141" t="s">
+        <v>176</v>
+      </c>
+      <c r="P12" s="143" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B13" s="135"/>
+      <c r="C13" s="136"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="141"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="141"/>
+      <c r="O13" s="141"/>
+      <c r="P13" s="143"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="158" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="170" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="171"/>
+      <c r="D14" s="172"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="175"/>
+      <c r="H14" s="176"/>
+      <c r="I14" s="174"/>
+      <c r="J14" s="173"/>
+      <c r="K14" s="177"/>
+      <c r="L14" s="178"/>
+      <c r="M14" s="178"/>
+      <c r="N14" s="177"/>
+      <c r="O14" s="177"/>
+      <c r="P14" s="179"/>
+      <c r="Q14" s="169"/>
+      <c r="R14" s="169"/>
+      <c r="S14" s="169"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B15" s="135"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="138"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="140"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="142" t="s">
+        <v>180</v>
+      </c>
+      <c r="M15" s="142" t="s">
+        <v>181</v>
+      </c>
+      <c r="N15" s="141" t="s">
+        <v>182</v>
+      </c>
+      <c r="O15" s="141" t="s">
+        <v>183</v>
+      </c>
+      <c r="P15" s="180" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B16" s="135"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="142" t="s">
+        <v>185</v>
+      </c>
+      <c r="N16" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="P16" s="180" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B17" s="135" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="136"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="140"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="142"/>
+      <c r="M17" s="142" t="s">
+        <v>187</v>
+      </c>
+      <c r="N17" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="O17" s="141" t="s">
+        <v>188</v>
+      </c>
+      <c r="P17" s="180" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B18" s="149" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="150"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="182"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="184"/>
+      <c r="I18" s="182"/>
+      <c r="J18" s="152"/>
+      <c r="K18" s="155"/>
+      <c r="L18" s="156"/>
+      <c r="M18" s="156" t="s">
+        <v>187</v>
+      </c>
+      <c r="N18" s="155" t="s">
+        <v>160</v>
+      </c>
+      <c r="O18" s="155" t="s">
+        <v>188</v>
+      </c>
+      <c r="P18" s="185" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="158" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="170" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="171"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="176"/>
+      <c r="I19" s="174"/>
+      <c r="J19" s="173"/>
+      <c r="K19" s="177"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="178"/>
+      <c r="N19" s="177"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="169"/>
+      <c r="R19" s="169"/>
+      <c r="S19" s="169"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B20" s="135"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="138"/>
+      <c r="G20" s="186"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="142" t="s">
+        <v>194</v>
+      </c>
+      <c r="N20" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="P20" s="180" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B21" s="135"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="186"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="141"/>
+      <c r="L21" s="142"/>
+      <c r="M21" s="142" t="s">
+        <v>187</v>
+      </c>
+      <c r="N21" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="O21" s="141" t="s">
+        <v>188</v>
+      </c>
+      <c r="P21" s="180" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="158" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="170" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="171"/>
+      <c r="D22" s="172"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="176"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="177"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="178"/>
+      <c r="N22" s="177"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="179"/>
+      <c r="Q22" s="169"/>
+      <c r="R22" s="169"/>
+      <c r="S22" s="169"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B23" s="135"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="119" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="138"/>
+      <c r="G23" s="139"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="141"/>
+      <c r="L23" s="142" t="s">
+        <v>198</v>
+      </c>
+      <c r="M23" s="142"/>
+      <c r="N23" s="141"/>
+      <c r="O23" s="141"/>
+      <c r="P23" s="143"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B24" s="187"/>
+      <c r="C24" s="188"/>
+      <c r="D24" s="181"/>
+      <c r="E24" s="152"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="183"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="152"/>
+      <c r="K24" s="155"/>
+      <c r="L24" s="156"/>
+      <c r="M24" s="156" t="s">
+        <v>176</v>
+      </c>
+      <c r="N24" s="155" t="s">
+        <v>160</v>
+      </c>
+      <c r="O24" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="P24" s="189" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="158" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="170" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="171"/>
+      <c r="D25" s="190"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="173"/>
+      <c r="G25" s="191"/>
+      <c r="H25" s="192"/>
+      <c r="I25" s="173"/>
+      <c r="J25" s="173"/>
+      <c r="K25" s="177"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="178"/>
+      <c r="N25" s="177"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="179"/>
+      <c r="Q25" s="169"/>
+      <c r="R25" s="169"/>
+      <c r="S25" s="169"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B26" s="135"/>
+      <c r="C26" s="136"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="186" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" s="140"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="141"/>
+      <c r="L26" s="142" t="s">
+        <v>200</v>
+      </c>
+      <c r="M26" s="142"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="141"/>
+      <c r="P26" s="143"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B27" s="135"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="186"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="141"/>
+      <c r="L27" s="142"/>
+      <c r="M27" s="142"/>
+      <c r="N27" s="141"/>
+      <c r="O27" s="141"/>
+      <c r="P27" s="143"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="158" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="170" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" s="171"/>
+      <c r="D28" s="172"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="191"/>
+      <c r="H28" s="176"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="177"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="178"/>
+      <c r="N28" s="177"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="169"/>
+      <c r="R28" s="169"/>
+      <c r="S28" s="169"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B29" s="149"/>
+      <c r="C29" s="150"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="186"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="141"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="156"/>
+      <c r="N29" s="155"/>
+      <c r="O29" s="155"/>
+      <c r="P29" s="143"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="158" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="170" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="171"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="174"/>
+      <c r="G30" s="191"/>
+      <c r="H30" s="176"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="173"/>
+      <c r="K30" s="177"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="178"/>
+      <c r="N30" s="177"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="179"/>
+      <c r="Q30" s="169"/>
+      <c r="R30" s="169"/>
+      <c r="S30" s="169"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B31" s="135"/>
+      <c r="C31" s="136"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="186"/>
+      <c r="H31" s="140"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="142"/>
+      <c r="M31" s="142" t="s">
+        <v>77</v>
+      </c>
+      <c r="N31" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="P31" s="143"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B32" s="135"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="139"/>
+      <c r="H32" s="140"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="141"/>
+      <c r="L32" s="142" t="s">
+        <v>203</v>
+      </c>
+      <c r="M32" s="142" t="s">
+        <v>204</v>
+      </c>
+      <c r="N32" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="141" t="s">
+        <v>205</v>
+      </c>
+      <c r="P32" s="143" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B33" s="135" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="136"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="140"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="141"/>
+      <c r="L33" s="142"/>
+      <c r="M33" s="142" t="s">
+        <v>207</v>
+      </c>
+      <c r="N33" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="O33" s="141" t="s">
+        <v>208</v>
+      </c>
+      <c r="P33" s="143"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B34" s="149"/>
+      <c r="C34" s="150"/>
+      <c r="D34" s="181"/>
+      <c r="E34" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="182"/>
+      <c r="G34" s="183"/>
+      <c r="H34" s="184"/>
+      <c r="I34" s="182"/>
+      <c r="J34" s="152"/>
+      <c r="K34" s="155"/>
+      <c r="L34" s="156" t="s">
+        <v>209</v>
+      </c>
+      <c r="M34" s="156" t="s">
+        <v>120</v>
+      </c>
+      <c r="N34" s="155" t="s">
+        <v>160</v>
+      </c>
+      <c r="O34" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="P34" s="157"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="193"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="195"/>
+      <c r="E35" s="195"/>
+      <c r="F35" s="196"/>
+      <c r="G35" s="196"/>
+      <c r="H35" s="196"/>
+      <c r="I35" s="196"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="195"/>
+      <c r="L35" s="193"/>
+      <c r="M35" s="193"/>
+      <c r="N35" s="193"/>
+      <c r="O35" s="195"/>
+      <c r="P35" s="195"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="142"/>
+      <c r="S35" s="142"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="197" t="s">
         <v>156</v>
       </c>
-      <c r="M2" s="121" t="s">
-        <v>157</v>
-      </c>
-      <c r="N2" s="120" t="s">
-        <v>158</v>
-      </c>
-      <c r="O2" s="120" t="s">
-        <v>159</v>
-      </c>
-      <c r="P2" s="122"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="123"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="129"/>
-      <c r="L3" s="130" t="s">
-        <v>160</v>
-      </c>
-      <c r="M3" s="130" t="s">
-        <v>161</v>
-      </c>
-      <c r="N3" s="129" t="s">
-        <v>158</v>
-      </c>
-      <c r="O3" s="129" t="s">
-        <v>159</v>
-      </c>
-      <c r="P3" s="131"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="132"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="107" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="107"/>
-      <c r="K4" s="129"/>
-      <c r="L4" s="130" t="s">
-        <v>162</v>
-      </c>
-      <c r="M4" s="130" t="s">
-        <v>163</v>
-      </c>
-      <c r="N4" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" s="129" t="s">
-        <v>164</v>
-      </c>
-      <c r="P4" s="131"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="137" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="138"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="141"/>
-      <c r="H5" s="142" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="144" t="s">
-        <v>166</v>
-      </c>
-      <c r="M5" s="144"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="145"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="147" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" s="148"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="151"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="154"/>
-      <c r="L6" s="155"/>
-      <c r="M6" s="155"/>
-      <c r="N6" s="154"/>
-      <c r="O6" s="154"/>
-      <c r="P6" s="156"/>
-      <c r="Q6" s="157"/>
-      <c r="R6" s="157"/>
-      <c r="S6" s="157"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B7" s="123"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="128"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="130" t="s">
-        <v>168</v>
-      </c>
-      <c r="M7" s="130"/>
-      <c r="N7" s="129"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="131"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B8" s="123"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="127" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="128"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="107"/>
-      <c r="K8" s="129"/>
-      <c r="L8" s="130" t="s">
-        <v>169</v>
-      </c>
-      <c r="M8" s="130"/>
-      <c r="N8" s="129"/>
-      <c r="O8" s="129"/>
-      <c r="P8" s="131"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B9" s="123"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="128"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="130" t="s">
-        <v>170</v>
-      </c>
-      <c r="M9" s="130"/>
-      <c r="N9" s="129"/>
-      <c r="O9" s="129"/>
-      <c r="P9" s="131"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B10" s="123"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="127" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="128"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="129"/>
-      <c r="L10" s="130" t="s">
-        <v>171</v>
-      </c>
-      <c r="M10" s="130"/>
-      <c r="N10" s="129"/>
-      <c r="O10" s="129"/>
-      <c r="P10" s="131"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="146" t="s">
-        <v>172</v>
-      </c>
-      <c r="B11" s="158" t="s">
-        <v>173</v>
-      </c>
-      <c r="C11" s="159"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="161"/>
-      <c r="F11" s="162"/>
-      <c r="G11" s="163"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="162"/>
-      <c r="J11" s="161"/>
-      <c r="K11" s="165"/>
-      <c r="L11" s="166"/>
-      <c r="M11" s="166"/>
-      <c r="N11" s="165"/>
-      <c r="O11" s="165"/>
-      <c r="P11" s="167"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B12" s="123"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="107"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130" t="s">
-        <v>174</v>
-      </c>
-      <c r="N12" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="129" t="s">
-        <v>174</v>
-      </c>
-      <c r="P12" s="131" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B13" s="123"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="129"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="129"/>
-      <c r="O13" s="129"/>
-      <c r="P13" s="131"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="146" t="s">
-        <v>176</v>
-      </c>
-      <c r="B14" s="158" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="159"/>
-      <c r="D14" s="160"/>
-      <c r="E14" s="161"/>
-      <c r="F14" s="162"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="164"/>
-      <c r="I14" s="162"/>
-      <c r="J14" s="161"/>
-      <c r="K14" s="165"/>
-      <c r="L14" s="166"/>
-      <c r="M14" s="166"/>
-      <c r="N14" s="165"/>
-      <c r="O14" s="165"/>
-      <c r="P14" s="167"/>
-      <c r="Q14" s="157"/>
-      <c r="R14" s="157"/>
-      <c r="S14" s="157"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="126"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="130" t="s">
-        <v>178</v>
-      </c>
-      <c r="M15" s="130" t="s">
-        <v>179</v>
-      </c>
-      <c r="N15" s="129" t="s">
-        <v>180</v>
-      </c>
-      <c r="O15" s="129" t="s">
-        <v>181</v>
-      </c>
-      <c r="P15" s="168" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B16" s="123"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="130" t="s">
-        <v>183</v>
-      </c>
-      <c r="N16" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" s="129" t="s">
-        <v>164</v>
-      </c>
-      <c r="P16" s="168" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B17" s="123" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130" t="s">
-        <v>185</v>
-      </c>
-      <c r="N17" s="129" t="s">
-        <v>158</v>
-      </c>
-      <c r="O17" s="129" t="s">
-        <v>186</v>
-      </c>
-      <c r="P17" s="168" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B18" s="137" t="s">
-        <v>188</v>
-      </c>
-      <c r="C18" s="138"/>
-      <c r="D18" s="169"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="170"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="172"/>
-      <c r="I18" s="170"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="143"/>
-      <c r="L18" s="144"/>
-      <c r="M18" s="144" t="s">
-        <v>185</v>
-      </c>
-      <c r="N18" s="143" t="s">
-        <v>158</v>
-      </c>
-      <c r="O18" s="143" t="s">
-        <v>186</v>
-      </c>
-      <c r="P18" s="173" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="146" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="158" t="s">
-        <v>191</v>
-      </c>
-      <c r="C19" s="159"/>
-      <c r="D19" s="160"/>
-      <c r="E19" s="161"/>
-      <c r="F19" s="162"/>
-      <c r="G19" s="163"/>
-      <c r="H19" s="164"/>
-      <c r="I19" s="162"/>
-      <c r="J19" s="161"/>
-      <c r="K19" s="165"/>
-      <c r="L19" s="166"/>
-      <c r="M19" s="166"/>
-      <c r="N19" s="165"/>
-      <c r="O19" s="165"/>
-      <c r="P19" s="167"/>
-      <c r="Q19" s="157"/>
-      <c r="R19" s="157"/>
-      <c r="S19" s="157"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B20" s="123"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="129"/>
-      <c r="L20" s="130"/>
-      <c r="M20" s="130" t="s">
-        <v>192</v>
-      </c>
-      <c r="N20" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="O20" s="129" t="s">
-        <v>164</v>
-      </c>
-      <c r="P20" s="168" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B21" s="123"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="129"/>
-      <c r="L21" s="130"/>
-      <c r="M21" s="130" t="s">
-        <v>185</v>
-      </c>
-      <c r="N21" s="129" t="s">
-        <v>158</v>
-      </c>
-      <c r="O21" s="129" t="s">
-        <v>186</v>
-      </c>
-      <c r="P21" s="168" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="B22" s="158" t="s">
-        <v>195</v>
-      </c>
-      <c r="C22" s="159"/>
-      <c r="D22" s="160"/>
-      <c r="E22" s="161"/>
-      <c r="F22" s="162"/>
-      <c r="G22" s="163"/>
-      <c r="H22" s="164"/>
-      <c r="I22" s="162"/>
-      <c r="J22" s="161"/>
-      <c r="K22" s="165"/>
-      <c r="L22" s="166"/>
-      <c r="M22" s="166"/>
-      <c r="N22" s="165"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="167"/>
-      <c r="Q22" s="157"/>
-      <c r="R22" s="157"/>
-      <c r="S22" s="157"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="107" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="126"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="129"/>
-      <c r="L23" s="130" t="s">
-        <v>196</v>
-      </c>
-      <c r="M23" s="130"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="131"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B24" s="175"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="169"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="172"/>
-      <c r="I24" s="170"/>
-      <c r="J24" s="140"/>
-      <c r="K24" s="143"/>
-      <c r="L24" s="144"/>
-      <c r="M24" s="144" t="s">
-        <v>174</v>
-      </c>
-      <c r="N24" s="143" t="s">
-        <v>158</v>
-      </c>
-      <c r="O24" s="143" t="s">
-        <v>174</v>
-      </c>
-      <c r="P24" s="177" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="146" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" s="158" t="s">
-        <v>165</v>
-      </c>
-      <c r="C25" s="159"/>
-      <c r="D25" s="178"/>
-      <c r="E25" s="161"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="179"/>
-      <c r="H25" s="180"/>
-      <c r="I25" s="161"/>
-      <c r="J25" s="161"/>
-      <c r="K25" s="165"/>
-      <c r="L25" s="166"/>
-      <c r="M25" s="166"/>
-      <c r="N25" s="165"/>
-      <c r="O25" s="165"/>
-      <c r="P25" s="167"/>
-      <c r="Q25" s="157"/>
-      <c r="R25" s="157"/>
-      <c r="S25" s="157"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B26" s="123"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="174" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="128"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="129"/>
-      <c r="L26" s="130" t="s">
-        <v>198</v>
-      </c>
-      <c r="M26" s="130"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="129"/>
-      <c r="P26" s="131"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B27" s="123"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="174"/>
-      <c r="H27" s="128"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="129"/>
-      <c r="L27" s="130"/>
-      <c r="M27" s="130"/>
-      <c r="N27" s="129"/>
-      <c r="O27" s="129"/>
-      <c r="P27" s="131"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="146" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="158" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="159"/>
-      <c r="D28" s="160"/>
-      <c r="E28" s="162"/>
-      <c r="F28" s="162"/>
-      <c r="G28" s="179"/>
-      <c r="H28" s="164"/>
-      <c r="I28" s="162"/>
-      <c r="J28" s="161"/>
-      <c r="K28" s="165"/>
-      <c r="L28" s="166"/>
-      <c r="M28" s="166"/>
-      <c r="N28" s="165"/>
-      <c r="O28" s="165"/>
-      <c r="P28" s="167"/>
-      <c r="Q28" s="157"/>
-      <c r="R28" s="157"/>
-      <c r="S28" s="157"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B29" s="137"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="125"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="128"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="130"/>
-      <c r="M29" s="144"/>
-      <c r="N29" s="143"/>
-      <c r="O29" s="143"/>
-      <c r="P29" s="131"/>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="146" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="158" t="s">
-        <v>200</v>
-      </c>
-      <c r="C30" s="159"/>
-      <c r="D30" s="160"/>
-      <c r="E30" s="162"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="179"/>
-      <c r="H30" s="164"/>
-      <c r="I30" s="162"/>
-      <c r="J30" s="161"/>
-      <c r="K30" s="165"/>
-      <c r="L30" s="166"/>
-      <c r="M30" s="166"/>
-      <c r="N30" s="165"/>
-      <c r="O30" s="165"/>
-      <c r="P30" s="167"/>
-      <c r="Q30" s="157"/>
-      <c r="R30" s="157"/>
-      <c r="S30" s="157"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B31" s="123"/>
-      <c r="C31" s="124"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="126"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="128"/>
-      <c r="I31" s="126"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="130"/>
-      <c r="M31" s="130" t="s">
-        <v>76</v>
-      </c>
-      <c r="N31" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="O31" s="129" t="s">
-        <v>164</v>
-      </c>
-      <c r="P31" s="131"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B32" s="123"/>
-      <c r="C32" s="124"/>
-      <c r="D32" s="125"/>
-      <c r="E32" s="126"/>
-      <c r="F32" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32" s="127"/>
-      <c r="H32" s="128"/>
-      <c r="I32" s="126"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="129"/>
-      <c r="L32" s="130" t="s">
-        <v>201</v>
-      </c>
-      <c r="M32" s="130" t="s">
-        <v>202</v>
-      </c>
-      <c r="N32" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" s="129" t="s">
-        <v>203</v>
-      </c>
-      <c r="P32" s="131" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B33" s="123" t="s">
-        <v>201</v>
-      </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="126"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="128"/>
-      <c r="I33" s="126"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="130"/>
-      <c r="M33" s="130" t="s">
-        <v>205</v>
-      </c>
-      <c r="N33" s="129" t="s">
-        <v>158</v>
-      </c>
-      <c r="O33" s="129" t="s">
-        <v>206</v>
-      </c>
-      <c r="P33" s="131"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B34" s="137"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="169"/>
-      <c r="E34" s="140" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" s="170"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="172"/>
-      <c r="I34" s="170"/>
-      <c r="J34" s="140"/>
-      <c r="K34" s="143"/>
-      <c r="L34" s="144" t="s">
-        <v>207</v>
-      </c>
-      <c r="M34" s="144" t="s">
-        <v>118</v>
-      </c>
-      <c r="N34" s="143" t="s">
-        <v>158</v>
-      </c>
-      <c r="O34" s="143" t="s">
-        <v>208</v>
-      </c>
-      <c r="P34" s="145"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="181"/>
-      <c r="C35" s="182"/>
-      <c r="D35" s="183"/>
-      <c r="E35" s="183"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="183"/>
-      <c r="K35" s="183"/>
-      <c r="L35" s="181"/>
-      <c r="M35" s="181"/>
-      <c r="N35" s="181"/>
-      <c r="O35" s="183"/>
-      <c r="P35" s="183"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="130"/>
-      <c r="S35" s="130"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="185" t="s">
-        <v>154</v>
-      </c>
-      <c r="C36" s="186"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126"/>
-      <c r="H36" s="126"/>
-      <c r="I36" s="126"/>
+      <c r="C36" s="198"/>
+      <c r="D36" s="138"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="138"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
-      <c r="L36" s="185"/>
-      <c r="M36" s="185"/>
-      <c r="N36" s="185"/>
-      <c r="O36" s="107"/>
+      <c r="L36" s="197"/>
+      <c r="M36" s="197"/>
+      <c r="N36" s="197"/>
+      <c r="O36" s="119"/>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
-      <c r="S36" s="130"/>
+      <c r="S36" s="142"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5" t="s">
-        <v>209</v>
+      <c r="B37" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="142" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5" t="s">
-        <v>210</v>
+      <c r="B38" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="142" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="187" t="s">
-        <v>211</v>
-      </c>
-      <c r="B41" s="188" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="189"/>
-      <c r="D41" s="190"/>
-      <c r="E41" s="190"/>
-      <c r="F41" s="191"/>
-      <c r="G41" s="191"/>
-      <c r="H41" s="190" t="s">
-        <v>165</v>
-      </c>
-      <c r="I41" s="191" t="s">
-        <v>156</v>
-      </c>
-      <c r="J41" s="191" t="s">
-        <v>166</v>
-      </c>
-      <c r="K41" s="191" t="s">
-        <v>160</v>
-      </c>
-      <c r="L41" s="188" t="s">
-        <v>212</v>
-      </c>
-      <c r="M41" s="192" t="s">
+      <c r="A41" s="199" t="s">
         <v>213</v>
       </c>
-      <c r="N41" s="187" t="s">
+      <c r="B41" s="1"/>
+      <c r="C41" s="200" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="201"/>
+      <c r="E41" s="201"/>
+      <c r="F41" s="202"/>
+      <c r="G41" s="202"/>
+      <c r="H41" s="201" t="s">
+        <v>168</v>
+      </c>
+      <c r="I41" s="202" t="s">
+        <v>167</v>
+      </c>
+      <c r="J41" s="202" t="s">
+        <v>162</v>
+      </c>
+      <c r="K41" s="202" t="s">
+        <v>158</v>
+      </c>
+      <c r="L41" s="200" t="s">
         <v>214</v>
       </c>
-      <c r="O41" s="188"/>
-      <c r="P41" s="187"/>
-      <c r="Q41" s="187"/>
-      <c r="R41" s="187"/>
-      <c r="S41" s="187"/>
+      <c r="M41" s="203" t="s">
+        <v>215</v>
+      </c>
+      <c r="N41" s="199" t="s">
+        <v>216</v>
+      </c>
+      <c r="O41" s="200"/>
+      <c r="P41" s="199"/>
+      <c r="Q41" s="199"/>
+      <c r="R41" s="199"/>
+      <c r="S41" s="199"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="193"/>
-      <c r="B42" s="2" t="str">
+      <c r="A42" s="204"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="2" t="str">
         <f aca="false">DEC2HEX(L42,2)</f>
-        <v>02</v>
-      </c>
-      <c r="D42" s="194"/>
-      <c r="E42" s="195"/>
-      <c r="F42" s="195"/>
-      <c r="G42" s="196"/>
-      <c r="H42" s="197"/>
-      <c r="I42" s="195"/>
-      <c r="J42" s="195" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="198" t="s">
-        <v>68</v>
+        <v>08</v>
+      </c>
+      <c r="D42" s="205"/>
+      <c r="E42" s="206"/>
+      <c r="F42" s="206"/>
+      <c r="G42" s="207"/>
+      <c r="H42" s="208" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="206"/>
+      <c r="J42" s="206" t="s">
+        <v>69</v>
+      </c>
+      <c r="K42" s="209" t="s">
+        <v>69</v>
       </c>
       <c r="L42" s="2" t="n">
         <f aca="false">IF(D42=1,128,0)+IF(E42=1,64,0)+IF(F42=1,32,0)+IF(G42=1,16,0)+IF(H42=1,8,0)+IF(I42=1,4,0)+IF(J42=1,2,0)+IF(K42=1,1,0)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
@@ -7625,38 +7819,37 @@
       <c r="S42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="193"/>
-      <c r="B43" s="2" t="str">
+      <c r="A43" s="204"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="2" t="str">
         <f aca="false">DEC2HEX(L43,2)</f>
-        <v>08</v>
-      </c>
-      <c r="D43" s="199"/>
+        <v>04</v>
+      </c>
+      <c r="D43" s="210"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
-      <c r="G43" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="200" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="129" t="s">
-        <v>68</v>
+      <c r="G43" s="186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="211"/>
+      <c r="I43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K43" s="141" t="s">
+        <v>69</v>
       </c>
       <c r="L43" s="2" t="n">
         <f aca="false">IF(D43=1,128,0)+IF(E43=1,64,0)+IF(F43=1,32,0)+IF(G43=1,16,0)+IF(H43=1,8,0)+IF(I43=1,4,0)+IF(J43=1,2,0)+IF(K43=1,1,0)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
@@ -7664,42 +7857,41 @@
       <c r="S43" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="193"/>
-      <c r="B44" s="2" t="str">
+      <c r="A44" s="204"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="2" t="str">
         <f aca="false">DEC2HEX(L44,2)</f>
-        <v>18</v>
-      </c>
-      <c r="D44" s="199"/>
+        <v>14</v>
+      </c>
+      <c r="D44" s="210"/>
       <c r="E44" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G44" s="174" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="200" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="129" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="G44" s="186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="211"/>
+      <c r="I44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K44" s="141" t="s">
+        <v>69</v>
       </c>
       <c r="L44" s="2" t="n">
         <f aca="false">IF(D44=1,128,0)+IF(E44=1,64,0)+IF(F44=1,32,0)+IF(G44=1,16,0)+IF(H44=1,8,0)+IF(I44=1,4,0)+IF(J44=1,2,0)+IF(K44=1,1,0)</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
@@ -7707,40 +7899,39 @@
       <c r="S44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="193"/>
-      <c r="B45" s="2" t="str">
+      <c r="A45" s="204"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="2" t="str">
         <f aca="false">DEC2HEX(L45,2)</f>
         <v>00</v>
       </c>
-      <c r="D45" s="199"/>
+      <c r="D45" s="210"/>
       <c r="E45" s="13"/>
       <c r="F45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="200" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="129" t="s">
-        <v>68</v>
+      <c r="G45" s="186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="211"/>
+      <c r="I45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K45" s="141" t="s">
+        <v>69</v>
       </c>
       <c r="L45" s="2" t="n">
         <f aca="false">IF(D45=1,128,0)+IF(E45=1,64,0)+IF(F45=1,32,0)+IF(G45=1,16,0)+IF(H45=1,8,0)+IF(I45=1,4,0)+IF(J45=1,2,0)+IF(K45=1,1,0)</f>
         <v>0</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
@@ -7748,40 +7939,41 @@
       <c r="S45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="193"/>
-      <c r="B46" s="2" t="str">
+      <c r="A46" s="204"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="2" t="str">
         <f aca="false">DEC2HEX(L46,2)</f>
         <v>10</v>
       </c>
-      <c r="D46" s="199"/>
-      <c r="E46" s="13"/>
+      <c r="D46" s="210"/>
+      <c r="E46" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="F46" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="174" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="200" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="129" t="s">
-        <v>68</v>
+      <c r="G46" s="186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="211"/>
+      <c r="I46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K46" s="141" t="s">
+        <v>69</v>
       </c>
       <c r="L46" s="2" t="n">
         <f aca="false">IF(D46=1,128,0)+IF(E46=1,64,0)+IF(F46=1,32,0)+IF(G46=1,16,0)+IF(H46=1,8,0)+IF(I46=1,4,0)+IF(J46=1,2,0)+IF(K46=1,1,0)</f>
         <v>16</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="11"/>
@@ -7790,40 +7982,39 @@
       <c r="S46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="193"/>
-      <c r="B47" s="2" t="str">
+      <c r="A47" s="204"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="2" t="str">
         <f aca="false">DEC2HEX(L47,2)</f>
         <v>20</v>
       </c>
-      <c r="D47" s="199"/>
+      <c r="D47" s="210"/>
       <c r="E47" s="13"/>
       <c r="F47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="200" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="129" t="s">
-        <v>68</v>
+      <c r="G47" s="186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="211"/>
+      <c r="I47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K47" s="141" t="s">
+        <v>69</v>
       </c>
       <c r="L47" s="2" t="n">
         <f aca="false">IF(D47=1,128,0)+IF(E47=1,64,0)+IF(F47=1,32,0)+IF(G47=1,16,0)+IF(H47=1,8,0)+IF(I47=1,4,0)+IF(J47=1,2,0)+IF(K47=1,1,0)</f>
         <v>32</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
@@ -7831,42 +8022,41 @@
       <c r="S47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="193"/>
-      <c r="B48" s="2" t="str">
+      <c r="A48" s="204"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="2" t="str">
         <f aca="false">DEC2HEX(L48,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D48" s="201"/>
-      <c r="E48" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="F48" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="G48" s="202" t="s">
-        <v>68</v>
-      </c>
-      <c r="H48" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="J48" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="143" t="s">
-        <v>68</v>
+        <v>31</v>
+      </c>
+      <c r="D48" s="212"/>
+      <c r="E48" s="152" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="154"/>
+      <c r="I48" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="152" t="s">
+        <v>69</v>
+      </c>
+      <c r="K48" s="155" t="n">
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <f aca="false">IF(D48=1,128,0)+IF(E48=1,64,0)+IF(F48=1,32,0)+IF(G48=1,16,0)+IF(H48=1,8,0)+IF(I48=1,4,0)+IF(J48=1,2,0)+IF(K48=1,1,0)</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P48" s="11"/>
       <c r="Q48" s="11"/>
@@ -7916,23 +8106,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="203"/>
-      <c r="B1" s="204" t="s">
+      <c r="A1" s="214"/>
+      <c r="B1" s="215" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="205" t="n">
+      <c r="F1" s="216" t="n">
         <v>6</v>
       </c>
-      <c r="G1" s="205" t="n">
+      <c r="G1" s="216" t="n">
         <v>5</v>
       </c>
       <c r="H1" s="27" t="n">
@@ -7941,1696 +8131,1698 @@
       <c r="I1" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J1" s="205" t="n">
+      <c r="J1" s="216" t="n">
         <v>2</v>
       </c>
-      <c r="K1" s="205" t="n">
+      <c r="K1" s="216" t="n">
         <v>1</v>
       </c>
       <c r="L1" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M1" s="206" t="s">
+      <c r="M1" s="217" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="206" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="207" t="s">
-        <v>153</v>
-      </c>
-      <c r="P1" s="208" t="s">
+      <c r="N1" s="217" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="218" t="s">
+        <v>155</v>
+      </c>
+      <c r="P1" s="219" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="209" t="s">
-        <v>225</v>
-      </c>
-      <c r="B2" s="210"/>
-      <c r="C2" s="211" t="str">
+      <c r="A2" s="220" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="221"/>
+      <c r="C2" s="222" t="str">
         <f aca="false">DEC2HEX(D2,2)</f>
         <v>00</v>
       </c>
-      <c r="D2" s="161" t="n">
+      <c r="D2" s="173" t="n">
         <f aca="false">IF(E2=1,128,0)+IF(F2=1,64,0)+IF(G2=1,32,0)+IF(H2=1,16,0)+IF(I2=1,8,0)+IF(J2=1,4,0)+IF(K2=1,2,0)+IF(L2=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E2" s="178"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="178" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="212" t="s">
-        <v>226</v>
-      </c>
-      <c r="N2" s="210"/>
-      <c r="O2" s="213"/>
-      <c r="P2" s="214"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="215"/>
-      <c r="B3" s="130"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="177"/>
+      <c r="I2" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="223" t="s">
+        <v>228</v>
+      </c>
+      <c r="N2" s="221"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="225"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A3" s="226"/>
+      <c r="B3" s="142"/>
       <c r="C3" s="17"/>
-      <c r="D3" s="107"/>
+      <c r="D3" s="119"/>
       <c r="E3" s="49"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107" t="s">
-        <v>227</v>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119" t="s">
+        <v>229</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="13"/>
-      <c r="K3" s="107"/>
+      <c r="K3" s="119"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="216"/>
-      <c r="N3" s="216" t="s">
-        <v>228</v>
-      </c>
-      <c r="O3" s="217" t="s">
-        <v>229</v>
-      </c>
-      <c r="P3" s="218"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="215"/>
-      <c r="B4" s="130"/>
+      <c r="M3" s="227"/>
+      <c r="N3" s="227" t="s">
+        <v>230</v>
+      </c>
+      <c r="O3" s="228" t="s">
+        <v>231</v>
+      </c>
+      <c r="P3" s="229"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A4" s="226"/>
+      <c r="B4" s="142"/>
       <c r="E4" s="49"/>
-      <c r="F4" s="107" t="s">
-        <v>230</v>
-      </c>
-      <c r="G4" s="107"/>
+      <c r="F4" s="119" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="119"/>
       <c r="H4" s="50"/>
       <c r="I4" s="49"/>
       <c r="J4" s="13"/>
-      <c r="K4" s="107"/>
+      <c r="K4" s="119"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="216" t="s">
-        <v>231</v>
+      <c r="M4" s="227" t="s">
+        <v>233</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
-      <c r="P4" s="219"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="215"/>
-      <c r="B5" s="130"/>
+      <c r="P4" s="230"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A5" s="226"/>
+      <c r="B5" s="142"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="107"/>
+      <c r="D5" s="119"/>
       <c r="E5" s="49"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
       <c r="H5" s="50"/>
       <c r="I5" s="49"/>
       <c r="J5" s="13"/>
-      <c r="K5" s="107"/>
+      <c r="K5" s="119"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="216"/>
-      <c r="O5" s="217"/>
-      <c r="P5" s="218"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A6" s="215"/>
-      <c r="B6" s="130" t="s">
-        <v>232</v>
+      <c r="M5" s="227"/>
+      <c r="O5" s="228"/>
+      <c r="P5" s="229"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A6" s="226"/>
+      <c r="B6" s="142" t="s">
+        <v>234</v>
       </c>
       <c r="E6" s="49"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
       <c r="H6" s="50"/>
       <c r="I6" s="49"/>
       <c r="J6" s="13"/>
-      <c r="K6" s="107"/>
+      <c r="K6" s="119"/>
       <c r="L6" s="50"/>
-      <c r="M6" s="216"/>
+      <c r="M6" s="227"/>
       <c r="N6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="P6" s="219"/>
+        <v>235</v>
+      </c>
+      <c r="P6" s="230"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="209" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="210"/>
-      <c r="C7" s="211" t="str">
+      <c r="A7" s="220" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="221"/>
+      <c r="C7" s="222" t="str">
         <f aca="false">DEC2HEX(D7,2)</f>
         <v>01</v>
       </c>
-      <c r="D7" s="161" t="n">
+      <c r="D7" s="173" t="n">
         <f aca="false">IF(E7=1,128,0)+IF(F7=1,64,0)+IF(G7=1,32,0)+IF(H7=1,16,0)+IF(I7=1,8,0)+IF(J7=1,4,0)+IF(K7=1,2,0)+IF(L7=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="178"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="161"/>
-      <c r="H7" s="165"/>
-      <c r="I7" s="178" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="212" t="s">
-        <v>235</v>
-      </c>
-      <c r="N7" s="210"/>
-      <c r="O7" s="212"/>
-      <c r="P7" s="214"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="215"/>
-      <c r="B8" s="130"/>
+      <c r="E7" s="190"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="177"/>
+      <c r="I7" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="223" t="s">
+        <v>237</v>
+      </c>
+      <c r="N7" s="221"/>
+      <c r="O7" s="223"/>
+      <c r="P7" s="225"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A8" s="226"/>
+      <c r="B8" s="142"/>
       <c r="C8" s="17"/>
-      <c r="D8" s="107"/>
+      <c r="D8" s="119"/>
       <c r="E8" s="49"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107" t="s">
-        <v>227</v>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119" t="s">
+        <v>229</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I8" s="49"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="107"/>
+      <c r="K8" s="119"/>
       <c r="L8" s="50"/>
-      <c r="M8" s="216"/>
+      <c r="M8" s="227"/>
       <c r="N8" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O8" s="217" t="s">
-        <v>229</v>
-      </c>
-      <c r="P8" s="218" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="215"/>
-      <c r="B9" s="130"/>
+        <v>230</v>
+      </c>
+      <c r="O8" s="228" t="s">
+        <v>231</v>
+      </c>
+      <c r="P8" s="229" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A9" s="226"/>
+      <c r="B9" s="142"/>
       <c r="C9" s="17"/>
-      <c r="D9" s="107"/>
+      <c r="D9" s="119"/>
       <c r="E9" s="49"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
       <c r="H9" s="50"/>
       <c r="I9" s="49"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="107"/>
+      <c r="K9" s="119"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="216"/>
-      <c r="O9" s="217"/>
-      <c r="P9" s="218"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="215"/>
-      <c r="B10" s="130" t="s">
-        <v>232</v>
-      </c>
-      <c r="E10" s="134"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
+      <c r="M9" s="227"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="229"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A10" s="226"/>
+      <c r="B10" s="142" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="146"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
       <c r="H10" s="50"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="107"/>
+      <c r="I10" s="146"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
       <c r="L10" s="50"/>
       <c r="M10" s="10"/>
       <c r="N10" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="P10" s="219"/>
+        <v>235</v>
+      </c>
+      <c r="P10" s="230"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="209" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="210"/>
-      <c r="C11" s="211" t="str">
+      <c r="A11" s="220" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="221"/>
+      <c r="C11" s="222" t="str">
         <f aca="false">DEC2HEX(D11,2)</f>
         <v>02</v>
       </c>
-      <c r="D11" s="161" t="n">
+      <c r="D11" s="173" t="n">
         <f aca="false">IF(E11=1,128,0)+IF(F11=1,64,0)+IF(G11=1,32,0)+IF(H11=1,16,0)+IF(I11=1,8,0)+IF(J11=1,4,0)+IF(K11=1,2,0)+IF(L11=1,1,0)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="178"/>
-      <c r="F11" s="161"/>
-      <c r="G11" s="161"/>
-      <c r="H11" s="165"/>
-      <c r="I11" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="212" t="s">
-        <v>238</v>
-      </c>
-      <c r="N11" s="210"/>
-      <c r="O11" s="213"/>
-      <c r="P11" s="214"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A12" s="215"/>
-      <c r="B12" s="130"/>
+      <c r="E11" s="190"/>
+      <c r="F11" s="173"/>
+      <c r="G11" s="173"/>
+      <c r="H11" s="177"/>
+      <c r="I11" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="223" t="s">
+        <v>240</v>
+      </c>
+      <c r="N11" s="221"/>
+      <c r="O11" s="224"/>
+      <c r="P11" s="225"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A12" s="226"/>
+      <c r="B12" s="142"/>
       <c r="C12" s="17"/>
-      <c r="D12" s="107"/>
+      <c r="D12" s="119"/>
       <c r="E12" s="49"/>
-      <c r="F12" s="107"/>
-      <c r="G12" s="107" t="s">
-        <v>227</v>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119" t="s">
+        <v>229</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I12" s="49"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="107"/>
+      <c r="K12" s="119"/>
       <c r="L12" s="50"/>
-      <c r="M12" s="216"/>
-      <c r="N12" s="216" t="s">
-        <v>239</v>
-      </c>
-      <c r="O12" s="217" t="s">
-        <v>229</v>
-      </c>
-      <c r="P12" s="220" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="215"/>
-      <c r="B13" s="130"/>
+      <c r="M12" s="227"/>
+      <c r="N12" s="227" t="s">
+        <v>241</v>
+      </c>
+      <c r="O12" s="228" t="s">
+        <v>231</v>
+      </c>
+      <c r="P12" s="231" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A13" s="226"/>
+      <c r="B13" s="142"/>
       <c r="C13" s="17"/>
-      <c r="D13" s="107"/>
+      <c r="D13" s="119"/>
       <c r="E13" s="49"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="119"/>
       <c r="H13" s="50"/>
       <c r="I13" s="49"/>
       <c r="J13" s="13"/>
-      <c r="K13" s="107"/>
+      <c r="K13" s="119"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="216"/>
-      <c r="O13" s="217"/>
-      <c r="P13" s="218"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="215"/>
-      <c r="B14" s="130" t="s">
-        <v>232</v>
+      <c r="M13" s="227"/>
+      <c r="O13" s="228"/>
+      <c r="P13" s="229"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A14" s="226"/>
+      <c r="B14" s="142" t="s">
+        <v>234</v>
       </c>
       <c r="E14" s="49"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="107"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
       <c r="H14" s="50"/>
       <c r="I14" s="49"/>
       <c r="J14" s="13"/>
-      <c r="K14" s="107"/>
+      <c r="K14" s="119"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="216"/>
+      <c r="M14" s="227"/>
       <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="P14" s="219" t="s">
-        <v>242</v>
+        <v>243</v>
+      </c>
+      <c r="P14" s="230" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="209" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="210"/>
-      <c r="C15" s="211" t="str">
+      <c r="A15" s="220" t="s">
+        <v>245</v>
+      </c>
+      <c r="B15" s="221"/>
+      <c r="C15" s="222" t="str">
         <f aca="false">DEC2HEX(D15,2)</f>
         <v>03</v>
       </c>
-      <c r="D15" s="161" t="n">
+      <c r="D15" s="173" t="n">
         <f aca="false">IF(E15=1,128,0)+IF(F15=1,64,0)+IF(G15=1,32,0)+IF(H15=1,16,0)+IF(I15=1,8,0)+IF(J15=1,4,0)+IF(K15=1,2,0)+IF(L15=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="161"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="165"/>
-      <c r="I15" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="212" t="s">
-        <v>97</v>
-      </c>
-      <c r="N15" s="210"/>
-      <c r="O15" s="212"/>
-      <c r="P15" s="214"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A16" s="215"/>
-      <c r="B16" s="130"/>
+      <c r="E15" s="190"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="177"/>
+      <c r="I15" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="223" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="221"/>
+      <c r="O15" s="223"/>
+      <c r="P15" s="225"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A16" s="226"/>
+      <c r="B16" s="142"/>
       <c r="C16" s="17"/>
-      <c r="D16" s="107"/>
+      <c r="D16" s="119"/>
       <c r="E16" s="49"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="107"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
       <c r="H16" s="50"/>
       <c r="I16" s="49"/>
       <c r="J16" s="13"/>
-      <c r="K16" s="107"/>
+      <c r="K16" s="119"/>
       <c r="L16" s="50"/>
-      <c r="M16" s="216"/>
-      <c r="O16" s="217"/>
-      <c r="P16" s="218"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A17" s="215"/>
-      <c r="B17" s="130" t="s">
-        <v>232</v>
+      <c r="M16" s="227"/>
+      <c r="O16" s="228"/>
+      <c r="P16" s="229"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A17" s="226"/>
+      <c r="B17" s="142" t="s">
+        <v>234</v>
       </c>
       <c r="C17" s="17"/>
-      <c r="D17" s="107"/>
+      <c r="D17" s="119"/>
       <c r="E17" s="49"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="107"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
       <c r="H17" s="50"/>
       <c r="I17" s="49"/>
       <c r="J17" s="13"/>
-      <c r="K17" s="107"/>
+      <c r="K17" s="119"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="216"/>
+      <c r="M17" s="227"/>
       <c r="N17" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="O17" s="217" t="s">
-        <v>244</v>
-      </c>
-      <c r="P17" s="218" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="215"/>
-      <c r="B18" s="130" t="s">
-        <v>232</v>
-      </c>
-      <c r="E18" s="134"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="107"/>
+        <v>246</v>
+      </c>
+      <c r="O17" s="228" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="229" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A18" s="226"/>
+      <c r="B18" s="142" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18" s="146"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="107"/>
-      <c r="K18" s="107"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
       <c r="L18" s="50"/>
       <c r="M18" s="10"/>
       <c r="N18" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="P18" s="221" t="s">
-        <v>247</v>
+        <v>249</v>
+      </c>
+      <c r="P18" s="232" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="209" t="s">
-        <v>248</v>
-      </c>
-      <c r="B19" s="210"/>
-      <c r="C19" s="211" t="str">
+      <c r="A19" s="220" t="s">
+        <v>251</v>
+      </c>
+      <c r="B19" s="221"/>
+      <c r="C19" s="222" t="str">
         <f aca="false">DEC2HEX(D19,2)</f>
         <v>04</v>
       </c>
-      <c r="D19" s="161" t="n">
+      <c r="D19" s="173" t="n">
         <f aca="false">IF(E19=1,128,0)+IF(F19=1,64,0)+IF(G19=1,32,0)+IF(H19=1,16,0)+IF(I19=1,8,0)+IF(J19=1,4,0)+IF(K19=1,2,0)+IF(L19=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E19" s="178"/>
-      <c r="F19" s="161"/>
-      <c r="G19" s="161"/>
-      <c r="H19" s="165"/>
-      <c r="I19" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="212" t="s">
-        <v>249</v>
-      </c>
-      <c r="N19" s="210"/>
-      <c r="O19" s="212"/>
-      <c r="P19" s="214"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="215"/>
-      <c r="B20" s="130"/>
-      <c r="E20" s="134"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107" t="s">
-        <v>227</v>
+      <c r="E19" s="190"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="177"/>
+      <c r="I19" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="223" t="s">
+        <v>252</v>
+      </c>
+      <c r="N19" s="221"/>
+      <c r="O19" s="223"/>
+      <c r="P19" s="225"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A20" s="226"/>
+      <c r="B20" s="142"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119" t="s">
+        <v>229</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
+        <v>229</v>
+      </c>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
       <c r="L20" s="50"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="P20" s="218"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="215"/>
-      <c r="B21" s="130"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="107" t="s">
-        <v>230</v>
-      </c>
-      <c r="G21" s="107"/>
+        <v>231</v>
+      </c>
+      <c r="P20" s="229"/>
+    </row>
+    <row r="21" s="233" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A21" s="226"/>
+      <c r="B21" s="142"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="119" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="119"/>
       <c r="H21" s="50"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
       <c r="L21" s="50"/>
       <c r="M21" s="10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N21" s="10"/>
-      <c r="O21" s="130"/>
-      <c r="P21" s="218" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="22" s="222" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="215"/>
-      <c r="B22" s="130"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="229" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A22" s="226"/>
+      <c r="B22" s="142"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
       <c r="H22" s="50"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
       <c r="L22" s="50"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="O22" s="130" t="s">
-        <v>72</v>
-      </c>
-      <c r="P22" s="218"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="223"/>
-      <c r="B23" s="224"/>
-      <c r="C23" s="225"/>
-      <c r="D23" s="226"/>
-      <c r="E23" s="227" t="s">
-        <v>253</v>
-      </c>
-      <c r="F23" s="226"/>
-      <c r="G23" s="226"/>
-      <c r="H23" s="228"/>
-      <c r="I23" s="227"/>
-      <c r="J23" s="229"/>
-      <c r="K23" s="226"/>
-      <c r="L23" s="228"/>
-      <c r="M23" s="230" t="s">
-        <v>254</v>
-      </c>
-      <c r="N23" s="222"/>
-      <c r="O23" s="231"/>
-      <c r="P23" s="232" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="215"/>
-      <c r="B24" s="130" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" s="134"/>
-      <c r="F24" s="107"/>
-      <c r="G24" s="107"/>
+      <c r="O22" s="142" t="s">
+        <v>73</v>
+      </c>
+      <c r="P22" s="229"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A23" s="234"/>
+      <c r="B23" s="235"/>
+      <c r="C23" s="236"/>
+      <c r="D23" s="237"/>
+      <c r="E23" s="238" t="s">
+        <v>256</v>
+      </c>
+      <c r="F23" s="237"/>
+      <c r="G23" s="237"/>
+      <c r="H23" s="239"/>
+      <c r="I23" s="238"/>
+      <c r="J23" s="240"/>
+      <c r="K23" s="237"/>
+      <c r="L23" s="239"/>
+      <c r="M23" s="241" t="s">
+        <v>257</v>
+      </c>
+      <c r="N23" s="233"/>
+      <c r="O23" s="242"/>
+      <c r="P23" s="243" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A24" s="226"/>
+      <c r="B24" s="142" t="s">
+        <v>234</v>
+      </c>
+      <c r="E24" s="146"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
       <c r="H24" s="50"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="107"/>
-      <c r="K24" s="107"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
       <c r="L24" s="50"/>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="P24" s="218" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+      <c r="P24" s="229" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="209" t="s">
-        <v>258</v>
-      </c>
-      <c r="B25" s="210"/>
-      <c r="C25" s="211" t="str">
+      <c r="A25" s="220" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" s="221"/>
+      <c r="C25" s="222" t="str">
         <f aca="false">DEC2HEX(D25,2)</f>
         <v>05</v>
       </c>
-      <c r="D25" s="161" t="n">
+      <c r="D25" s="173" t="n">
         <f aca="false">IF(E25=1,128,0)+IF(F25=1,64,0)+IF(G25=1,32,0)+IF(H25=1,16,0)+IF(I25=1,8,0)+IF(J25=1,4,0)+IF(K25=1,2,0)+IF(L25=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E25" s="178"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="161"/>
-      <c r="H25" s="165"/>
-      <c r="I25" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="212" t="s">
-        <v>259</v>
-      </c>
-      <c r="N25" s="210"/>
-      <c r="O25" s="212"/>
-      <c r="P25" s="214"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="215"/>
-      <c r="B26" s="130"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="107" t="s">
-        <v>230</v>
-      </c>
-      <c r="G26" s="107"/>
+      <c r="E25" s="190"/>
+      <c r="F25" s="173"/>
+      <c r="G25" s="173"/>
+      <c r="H25" s="177"/>
+      <c r="I25" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="223" t="s">
+        <v>262</v>
+      </c>
+      <c r="N25" s="221"/>
+      <c r="O25" s="223"/>
+      <c r="P25" s="225"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A26" s="226"/>
+      <c r="B26" s="142"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="119" t="s">
+        <v>232</v>
+      </c>
+      <c r="G26" s="119"/>
       <c r="H26" s="50"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
       <c r="L26" s="50"/>
       <c r="M26" s="10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N26" s="10"/>
-      <c r="O26" s="130"/>
-      <c r="P26" s="218" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="215"/>
-      <c r="B27" s="130"/>
-      <c r="E27" s="134"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="107"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="229" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A27" s="226"/>
+      <c r="B27" s="142"/>
+      <c r="E27" s="146"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
       <c r="H27" s="50"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="107"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
       <c r="L27" s="50"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="O27" s="130" t="s">
-        <v>72</v>
-      </c>
-      <c r="P27" s="218"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="215"/>
-      <c r="B28" s="130"/>
+        <v>255</v>
+      </c>
+      <c r="O27" s="142" t="s">
+        <v>73</v>
+      </c>
+      <c r="P27" s="229"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A28" s="226"/>
+      <c r="B28" s="142"/>
       <c r="C28" s="17"/>
-      <c r="D28" s="107"/>
+      <c r="D28" s="119"/>
       <c r="E28" s="49"/>
-      <c r="F28" s="107"/>
-      <c r="G28" s="107"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
       <c r="H28" s="50"/>
       <c r="I28" s="49"/>
       <c r="J28" s="13"/>
-      <c r="K28" s="107"/>
+      <c r="K28" s="119"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="216"/>
-      <c r="O28" s="217"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="215"/>
-      <c r="B29" s="130" t="s">
-        <v>232</v>
+      <c r="M28" s="227"/>
+      <c r="O28" s="228"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A29" s="226"/>
+      <c r="B29" s="142" t="s">
+        <v>234</v>
       </c>
       <c r="C29" s="17"/>
-      <c r="D29" s="107"/>
+      <c r="D29" s="119"/>
       <c r="E29" s="49"/>
-      <c r="F29" s="107"/>
-      <c r="G29" s="107"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
       <c r="H29" s="50"/>
       <c r="I29" s="49"/>
       <c r="J29" s="13"/>
-      <c r="K29" s="107"/>
+      <c r="K29" s="119"/>
       <c r="L29" s="50"/>
-      <c r="M29" s="216"/>
+      <c r="M29" s="227"/>
       <c r="N29" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="O29" s="217" t="s">
-        <v>244</v>
-      </c>
-      <c r="P29" s="218" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A30" s="215"/>
-      <c r="B30" s="130" t="s">
-        <v>232</v>
-      </c>
-      <c r="E30" s="134"/>
-      <c r="F30" s="107"/>
-      <c r="G30" s="107"/>
+        <v>246</v>
+      </c>
+      <c r="O29" s="228" t="s">
+        <v>247</v>
+      </c>
+      <c r="P29" s="229" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A30" s="226"/>
+      <c r="B30" s="142" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" s="146"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
       <c r="H30" s="50"/>
-      <c r="I30" s="134"/>
-      <c r="J30" s="107"/>
-      <c r="K30" s="107"/>
+      <c r="I30" s="146"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="119"/>
       <c r="L30" s="50"/>
       <c r="M30" s="10"/>
       <c r="N30" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="P30" s="221" t="s">
-        <v>247</v>
+        <v>249</v>
+      </c>
+      <c r="P30" s="232" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="209" t="s">
-        <v>261</v>
-      </c>
-      <c r="B31" s="210"/>
-      <c r="C31" s="211" t="str">
+      <c r="A31" s="220" t="s">
+        <v>264</v>
+      </c>
+      <c r="B31" s="221"/>
+      <c r="C31" s="222" t="str">
         <f aca="false">DEC2HEX(D31,2)</f>
         <v>06</v>
       </c>
-      <c r="D31" s="161" t="n">
+      <c r="D31" s="173" t="n">
         <f aca="false">IF(E31=1,128,0)+IF(F31=1,64,0)+IF(G31=1,32,0)+IF(H31=1,16,0)+IF(I31=1,8,0)+IF(J31=1,4,0)+IF(K31=1,2,0)+IF(L31=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="E31" s="178"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="165"/>
-      <c r="I31" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="212" t="s">
-        <v>262</v>
-      </c>
-      <c r="N31" s="210"/>
-      <c r="O31" s="212"/>
-      <c r="P31" s="233" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A32" s="215"/>
-      <c r="E32" s="134"/>
-      <c r="F32" s="107"/>
-      <c r="G32" s="107" t="n">
+      <c r="E31" s="190"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="223" t="s">
+        <v>265</v>
+      </c>
+      <c r="N31" s="221"/>
+      <c r="O31" s="223"/>
+      <c r="P31" s="244" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A32" s="226"/>
+      <c r="E32" s="146"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107"/>
-      <c r="K32" s="107"/>
+      <c r="I32" s="119"/>
+      <c r="J32" s="119"/>
+      <c r="K32" s="119"/>
       <c r="L32" s="50"/>
-      <c r="M32" s="130" t="s">
-        <v>264</v>
-      </c>
-      <c r="P32" s="218"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="215"/>
-      <c r="E33" s="134"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="107" t="n">
+      <c r="M32" s="142" t="s">
+        <v>267</v>
+      </c>
+      <c r="P32" s="229"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A33" s="226"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="107"/>
-      <c r="J33" s="107"/>
-      <c r="K33" s="107"/>
+      <c r="I33" s="119"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="119"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="216" t="s">
-        <v>265</v>
-      </c>
-      <c r="P33" s="218"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="215"/>
-      <c r="E34" s="134"/>
-      <c r="F34" s="107"/>
-      <c r="G34" s="107" t="n">
+      <c r="M33" s="227" t="s">
+        <v>268</v>
+      </c>
+      <c r="P33" s="229"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A34" s="226"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="119"/>
+      <c r="G34" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="107"/>
-      <c r="J34" s="107"/>
-      <c r="K34" s="107"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="119"/>
+      <c r="K34" s="119"/>
       <c r="L34" s="50"/>
-      <c r="M34" s="216" t="s">
-        <v>266</v>
-      </c>
-      <c r="P34" s="218"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="215"/>
-      <c r="E35" s="134"/>
-      <c r="F35" s="107"/>
-      <c r="G35" s="107" t="n">
+      <c r="M34" s="227" t="s">
+        <v>269</v>
+      </c>
+      <c r="P34" s="229"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A35" s="226"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="119"/>
+      <c r="G35" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="107"/>
-      <c r="J35" s="107"/>
-      <c r="K35" s="107"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="119"/>
       <c r="L35" s="50"/>
       <c r="M35" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="P35" s="218"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="215"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="107" t="s">
-        <v>268</v>
-      </c>
-      <c r="G36" s="107"/>
+        <v>270</v>
+      </c>
+      <c r="P35" s="229"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A36" s="226"/>
+      <c r="E36" s="146"/>
+      <c r="F36" s="119" t="s">
+        <v>271</v>
+      </c>
+      <c r="G36" s="119"/>
       <c r="H36" s="50"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="107"/>
-      <c r="K36" s="107"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="119"/>
       <c r="L36" s="50"/>
-      <c r="M36" s="130" t="s">
-        <v>269</v>
-      </c>
-      <c r="P36" s="218" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="215"/>
-      <c r="B37" s="130"/>
+      <c r="M36" s="142" t="s">
+        <v>272</v>
+      </c>
+      <c r="P36" s="229" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A37" s="226"/>
+      <c r="B37" s="142"/>
       <c r="C37" s="17"/>
-      <c r="D37" s="107"/>
+      <c r="D37" s="119"/>
       <c r="E37" s="49"/>
-      <c r="F37" s="107"/>
-      <c r="G37" s="107"/>
+      <c r="F37" s="119"/>
+      <c r="G37" s="119"/>
       <c r="H37" s="50"/>
       <c r="I37" s="49"/>
       <c r="J37" s="13"/>
-      <c r="K37" s="107"/>
+      <c r="K37" s="119"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="216"/>
-      <c r="O37" s="217"/>
-      <c r="P37" s="218"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A38" s="215"/>
-      <c r="B38" s="130" t="s">
-        <v>232</v>
-      </c>
-      <c r="E38" s="134"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="107"/>
+      <c r="M37" s="227"/>
+      <c r="O37" s="228"/>
+      <c r="P37" s="229"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A38" s="226"/>
+      <c r="B38" s="142" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="146"/>
+      <c r="F38" s="119"/>
+      <c r="G38" s="119"/>
       <c r="H38" s="50"/>
-      <c r="I38" s="107"/>
-      <c r="J38" s="107"/>
-      <c r="K38" s="107"/>
+      <c r="I38" s="119"/>
+      <c r="J38" s="119"/>
+      <c r="K38" s="119"/>
       <c r="L38" s="50"/>
-      <c r="M38" s="130"/>
+      <c r="M38" s="142"/>
       <c r="O38" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="P38" s="218" t="s">
-        <v>272</v>
+        <v>274</v>
+      </c>
+      <c r="P38" s="229" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="209" t="s">
-        <v>273</v>
-      </c>
-      <c r="B39" s="210"/>
-      <c r="C39" s="211" t="str">
+      <c r="A39" s="220" t="s">
+        <v>276</v>
+      </c>
+      <c r="B39" s="221"/>
+      <c r="C39" s="222" t="str">
         <f aca="false">DEC2HEX(D39,2)</f>
         <v>07</v>
       </c>
-      <c r="D39" s="161" t="n">
+      <c r="D39" s="173" t="n">
         <f aca="false">IF(E39=1,128,0)+IF(F39=1,64,0)+IF(G39=1,32,0)+IF(H39=1,16,0)+IF(I39=1,8,0)+IF(J39=1,4,0)+IF(K39=1,2,0)+IF(L39=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="E39" s="178"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="165"/>
-      <c r="I39" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="212" t="s">
-        <v>274</v>
-      </c>
-      <c r="N39" s="210"/>
-      <c r="O39" s="212"/>
-      <c r="P39" s="214"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="215"/>
-      <c r="E40" s="134"/>
-      <c r="F40" s="107"/>
-      <c r="G40" s="107" t="n">
+      <c r="E39" s="190"/>
+      <c r="F39" s="173"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="177"/>
+      <c r="I39" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="223" t="s">
+        <v>277</v>
+      </c>
+      <c r="N39" s="221"/>
+      <c r="O39" s="223"/>
+      <c r="P39" s="225"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A40" s="226"/>
+      <c r="E40" s="146"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="107"/>
-      <c r="J40" s="107"/>
-      <c r="K40" s="107"/>
+      <c r="I40" s="119"/>
+      <c r="J40" s="119"/>
+      <c r="K40" s="119"/>
       <c r="L40" s="50"/>
-      <c r="M40" s="130" t="s">
-        <v>275</v>
-      </c>
-      <c r="P40" s="220" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="215"/>
-      <c r="E41" s="134"/>
-      <c r="F41" s="107"/>
-      <c r="G41" s="107" t="n">
+      <c r="M40" s="142" t="s">
+        <v>278</v>
+      </c>
+      <c r="P40" s="231" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A41" s="226"/>
+      <c r="E41" s="146"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="107"/>
-      <c r="J41" s="107"/>
-      <c r="K41" s="107"/>
+      <c r="I41" s="119"/>
+      <c r="J41" s="119"/>
+      <c r="K41" s="119"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="216" t="s">
-        <v>265</v>
-      </c>
-      <c r="P41" s="220" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="215"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="107"/>
-      <c r="G42" s="107" t="n">
+      <c r="M41" s="227" t="s">
+        <v>268</v>
+      </c>
+      <c r="P41" s="231" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A42" s="226"/>
+      <c r="E42" s="146"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="107"/>
-      <c r="J42" s="107"/>
-      <c r="K42" s="107"/>
+      <c r="I42" s="119"/>
+      <c r="J42" s="119"/>
+      <c r="K42" s="119"/>
       <c r="L42" s="50"/>
-      <c r="M42" s="216" t="s">
-        <v>266</v>
-      </c>
-      <c r="P42" s="220" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="215"/>
-      <c r="E43" s="134"/>
-      <c r="F43" s="107"/>
-      <c r="G43" s="107" t="n">
+      <c r="M42" s="227" t="s">
+        <v>269</v>
+      </c>
+      <c r="P42" s="231" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A43" s="226"/>
+      <c r="E43" s="146"/>
+      <c r="F43" s="119"/>
+      <c r="G43" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="107"/>
-      <c r="J43" s="107"/>
-      <c r="K43" s="107"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="119"/>
+      <c r="K43" s="119"/>
       <c r="L43" s="50"/>
       <c r="M43" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="P43" s="220" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="215"/>
-      <c r="E44" s="134"/>
-      <c r="F44" s="107"/>
-      <c r="G44" s="107"/>
+        <v>270</v>
+      </c>
+      <c r="P43" s="231" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A44" s="226"/>
+      <c r="E44" s="146"/>
+      <c r="F44" s="119"/>
+      <c r="G44" s="119"/>
       <c r="H44" s="50"/>
-      <c r="I44" s="107"/>
-      <c r="J44" s="107"/>
-      <c r="K44" s="107"/>
+      <c r="I44" s="119"/>
+      <c r="J44" s="119"/>
+      <c r="K44" s="119"/>
       <c r="L44" s="50"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="234" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A45" s="215"/>
-      <c r="E45" s="134"/>
-      <c r="F45" s="107"/>
-      <c r="G45" s="107"/>
+      <c r="P44" s="245" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A45" s="226"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="119"/>
       <c r="H45" s="50"/>
-      <c r="I45" s="107"/>
-      <c r="J45" s="107"/>
-      <c r="K45" s="107"/>
+      <c r="I45" s="119"/>
+      <c r="J45" s="119"/>
+      <c r="K45" s="119"/>
       <c r="L45" s="50"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="234" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A46" s="215"/>
-      <c r="E46" s="134"/>
-      <c r="F46" s="107"/>
-      <c r="G46" s="107"/>
+      <c r="P45" s="245" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A46" s="226"/>
+      <c r="E46" s="146"/>
+      <c r="F46" s="119"/>
+      <c r="G46" s="119"/>
       <c r="H46" s="50"/>
-      <c r="I46" s="107"/>
-      <c r="J46" s="107"/>
-      <c r="K46" s="107"/>
+      <c r="I46" s="119"/>
+      <c r="J46" s="119"/>
+      <c r="K46" s="119"/>
       <c r="L46" s="50"/>
       <c r="M46" s="10"/>
       <c r="O46" s="1"/>
-      <c r="P46" s="234" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="215"/>
-      <c r="B47" s="130"/>
+      <c r="P46" s="245" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A47" s="226"/>
+      <c r="B47" s="142"/>
       <c r="C47" s="17"/>
-      <c r="D47" s="107"/>
+      <c r="D47" s="119"/>
       <c r="E47" s="49"/>
-      <c r="F47" s="107"/>
-      <c r="G47" s="107"/>
+      <c r="F47" s="119"/>
+      <c r="G47" s="119"/>
       <c r="H47" s="50"/>
       <c r="I47" s="49"/>
       <c r="J47" s="13"/>
-      <c r="K47" s="107"/>
+      <c r="K47" s="119"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="216"/>
-      <c r="O47" s="217"/>
-      <c r="P47" s="218"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="215"/>
-      <c r="B48" s="216" t="s">
-        <v>232</v>
+      <c r="M47" s="227"/>
+      <c r="O47" s="228"/>
+      <c r="P47" s="229"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A48" s="226"/>
+      <c r="B48" s="227" t="s">
+        <v>234</v>
       </c>
       <c r="C48" s="17"/>
-      <c r="D48" s="107"/>
+      <c r="D48" s="119"/>
       <c r="E48" s="49"/>
-      <c r="F48" s="107"/>
-      <c r="G48" s="107"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="119"/>
       <c r="H48" s="50"/>
       <c r="I48" s="49"/>
       <c r="J48" s="13"/>
-      <c r="K48" s="107"/>
+      <c r="K48" s="119"/>
       <c r="L48" s="50"/>
-      <c r="M48" s="216"/>
+      <c r="M48" s="227"/>
       <c r="N48" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="O48" s="217" t="s">
-        <v>284</v>
-      </c>
-      <c r="P48" s="218"/>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A49" s="235"/>
-      <c r="B49" s="216" t="s">
-        <v>232</v>
-      </c>
-      <c r="C49" s="236"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="237"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="143"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="140"/>
-      <c r="K49" s="140"/>
-      <c r="L49" s="143"/>
-      <c r="M49" s="238"/>
+        <v>286</v>
+      </c>
+      <c r="O48" s="228" t="s">
+        <v>287</v>
+      </c>
+      <c r="P48" s="229" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A49" s="246"/>
+      <c r="B49" s="227" t="s">
+        <v>234</v>
+      </c>
+      <c r="C49" s="247"/>
+      <c r="D49" s="152"/>
+      <c r="E49" s="248"/>
+      <c r="F49" s="152"/>
+      <c r="G49" s="152"/>
+      <c r="H49" s="155"/>
+      <c r="I49" s="152"/>
+      <c r="J49" s="152"/>
+      <c r="K49" s="152"/>
+      <c r="L49" s="155"/>
+      <c r="M49" s="249"/>
       <c r="N49" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="P49" s="221" t="s">
-        <v>247</v>
+        <v>286</v>
+      </c>
+      <c r="P49" s="232" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="209"/>
-      <c r="B50" s="210"/>
-      <c r="C50" s="211" t="str">
+      <c r="A50" s="220"/>
+      <c r="B50" s="221"/>
+      <c r="C50" s="222" t="str">
         <f aca="false">DEC2HEX(D50,2)</f>
         <v>08</v>
       </c>
-      <c r="D50" s="161" t="n">
+      <c r="D50" s="173" t="n">
         <f aca="false">IF(E50=1,128,0)+IF(F50=1,64,0)+IF(G50=1,32,0)+IF(H50=1,16,0)+IF(I50=1,8,0)+IF(J50=1,4,0)+IF(K50=1,2,0)+IF(L50=1,1,0)</f>
         <v>8</v>
       </c>
-      <c r="E50" s="178"/>
-      <c r="F50" s="161"/>
-      <c r="G50" s="161"/>
-      <c r="H50" s="165"/>
-      <c r="I50" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="212"/>
-      <c r="N50" s="210"/>
-      <c r="O50" s="212"/>
-      <c r="P50" s="214"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="215"/>
-      <c r="B51" s="130"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="173"/>
+      <c r="G50" s="173"/>
+      <c r="H50" s="177"/>
+      <c r="I50" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="223"/>
+      <c r="N50" s="221"/>
+      <c r="O50" s="223"/>
+      <c r="P50" s="225"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A51" s="226"/>
+      <c r="B51" s="142"/>
       <c r="C51" s="17"/>
-      <c r="D51" s="107"/>
+      <c r="D51" s="119"/>
       <c r="E51" s="49"/>
-      <c r="F51" s="107"/>
-      <c r="G51" s="107"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="119"/>
       <c r="H51" s="50"/>
       <c r="I51" s="49"/>
       <c r="J51" s="13"/>
-      <c r="K51" s="107"/>
+      <c r="K51" s="119"/>
       <c r="L51" s="50"/>
-      <c r="M51" s="216"/>
-      <c r="O51" s="217"/>
-      <c r="P51" s="218"/>
+      <c r="M51" s="227"/>
+      <c r="O51" s="228"/>
+      <c r="P51" s="229"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="209"/>
-      <c r="B52" s="210"/>
-      <c r="C52" s="211" t="str">
+      <c r="A52" s="220"/>
+      <c r="B52" s="221"/>
+      <c r="C52" s="222" t="str">
         <f aca="false">DEC2HEX(D52,2)</f>
         <v>09</v>
       </c>
-      <c r="D52" s="161" t="n">
+      <c r="D52" s="173" t="n">
         <f aca="false">IF(E52=1,128,0)+IF(F52=1,64,0)+IF(G52=1,32,0)+IF(H52=1,16,0)+IF(I52=1,8,0)+IF(J52=1,4,0)+IF(K52=1,2,0)+IF(L52=1,1,0)</f>
         <v>9</v>
       </c>
-      <c r="E52" s="178"/>
-      <c r="F52" s="161"/>
-      <c r="G52" s="161"/>
-      <c r="H52" s="165"/>
-      <c r="I52" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" s="212"/>
-      <c r="N52" s="210"/>
-      <c r="O52" s="212"/>
-      <c r="P52" s="214"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="215"/>
-      <c r="B53" s="130"/>
+      <c r="E52" s="190"/>
+      <c r="F52" s="173"/>
+      <c r="G52" s="173"/>
+      <c r="H52" s="177"/>
+      <c r="I52" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="223"/>
+      <c r="N52" s="221"/>
+      <c r="O52" s="223"/>
+      <c r="P52" s="225"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A53" s="226"/>
+      <c r="B53" s="142"/>
       <c r="C53" s="17"/>
-      <c r="D53" s="107"/>
+      <c r="D53" s="119"/>
       <c r="E53" s="49"/>
-      <c r="F53" s="107"/>
-      <c r="G53" s="107"/>
+      <c r="F53" s="119"/>
+      <c r="G53" s="119"/>
       <c r="H53" s="50"/>
       <c r="I53" s="49"/>
       <c r="J53" s="13"/>
-      <c r="K53" s="107"/>
+      <c r="K53" s="119"/>
       <c r="L53" s="50"/>
-      <c r="M53" s="216"/>
-      <c r="O53" s="217"/>
-      <c r="P53" s="218"/>
+      <c r="M53" s="227"/>
+      <c r="O53" s="228"/>
+      <c r="P53" s="229"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="209" t="s">
-        <v>285</v>
-      </c>
-      <c r="B54" s="210"/>
-      <c r="C54" s="211" t="str">
+      <c r="A54" s="220" t="s">
+        <v>289</v>
+      </c>
+      <c r="B54" s="221"/>
+      <c r="C54" s="222" t="str">
         <f aca="false">DEC2HEX(D54,2)</f>
         <v>0A</v>
       </c>
-      <c r="D54" s="161" t="n">
+      <c r="D54" s="173" t="n">
         <f aca="false">IF(E54=1,128,0)+IF(F54=1,64,0)+IF(G54=1,32,0)+IF(H54=1,16,0)+IF(I54=1,8,0)+IF(J54=1,4,0)+IF(K54=1,2,0)+IF(L54=1,1,0)</f>
         <v>10</v>
       </c>
-      <c r="E54" s="178"/>
-      <c r="F54" s="161"/>
-      <c r="G54" s="161"/>
-      <c r="H54" s="165"/>
-      <c r="I54" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="212" t="s">
-        <v>286</v>
-      </c>
-      <c r="N54" s="210"/>
-      <c r="O54" s="212"/>
-      <c r="P54" s="214"/>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="215"/>
-      <c r="B55" s="130"/>
+      <c r="E54" s="190"/>
+      <c r="F54" s="173"/>
+      <c r="G54" s="173"/>
+      <c r="H54" s="177"/>
+      <c r="I54" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="223" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="221"/>
+      <c r="O54" s="223"/>
+      <c r="P54" s="225"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A55" s="226"/>
+      <c r="B55" s="142"/>
       <c r="C55" s="17"/>
-      <c r="D55" s="107"/>
+      <c r="D55" s="119"/>
       <c r="E55" s="49"/>
-      <c r="F55" s="107"/>
-      <c r="G55" s="107"/>
+      <c r="F55" s="119"/>
+      <c r="G55" s="119"/>
       <c r="H55" s="50"/>
       <c r="I55" s="49"/>
       <c r="J55" s="13"/>
-      <c r="K55" s="107"/>
+      <c r="K55" s="119"/>
       <c r="L55" s="50"/>
-      <c r="M55" s="216"/>
-      <c r="O55" s="217"/>
-      <c r="P55" s="218"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A56" s="215"/>
-      <c r="B56" s="216" t="s">
-        <v>232</v>
-      </c>
-      <c r="E56" s="134"/>
-      <c r="F56" s="107"/>
-      <c r="G56" s="107"/>
+      <c r="M55" s="227"/>
+      <c r="O55" s="228"/>
+      <c r="P55" s="229"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A56" s="226"/>
+      <c r="B56" s="227" t="s">
+        <v>234</v>
+      </c>
+      <c r="E56" s="146"/>
+      <c r="F56" s="119"/>
+      <c r="G56" s="119"/>
       <c r="H56" s="50"/>
-      <c r="I56" s="107"/>
-      <c r="J56" s="107"/>
-      <c r="K56" s="107"/>
+      <c r="I56" s="119"/>
+      <c r="J56" s="119"/>
+      <c r="K56" s="119"/>
       <c r="L56" s="50"/>
-      <c r="M56" s="130"/>
+      <c r="M56" s="142"/>
       <c r="N56" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="P56" s="218" t="s">
-        <v>288</v>
+        <v>291</v>
+      </c>
+      <c r="P56" s="229" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="209"/>
-      <c r="B57" s="210"/>
-      <c r="C57" s="211" t="str">
+      <c r="A57" s="220"/>
+      <c r="B57" s="221"/>
+      <c r="C57" s="222" t="str">
         <f aca="false">DEC2HEX(D57,2)</f>
         <v>0B</v>
       </c>
-      <c r="D57" s="161" t="n">
+      <c r="D57" s="173" t="n">
         <f aca="false">IF(E57=1,128,0)+IF(F57=1,64,0)+IF(G57=1,32,0)+IF(H57=1,16,0)+IF(I57=1,8,0)+IF(J57=1,4,0)+IF(K57=1,2,0)+IF(L57=1,1,0)</f>
         <v>11</v>
       </c>
-      <c r="E57" s="178"/>
-      <c r="F57" s="161"/>
-      <c r="G57" s="161"/>
-      <c r="H57" s="165"/>
-      <c r="I57" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="212"/>
-      <c r="N57" s="210"/>
-      <c r="O57" s="212"/>
-      <c r="P57" s="214"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="215"/>
-      <c r="B58" s="130"/>
+      <c r="E57" s="190"/>
+      <c r="F57" s="173"/>
+      <c r="G57" s="173"/>
+      <c r="H57" s="177"/>
+      <c r="I57" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="223"/>
+      <c r="N57" s="221"/>
+      <c r="O57" s="223"/>
+      <c r="P57" s="225"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A58" s="226"/>
+      <c r="B58" s="142"/>
       <c r="C58" s="17"/>
-      <c r="D58" s="107"/>
+      <c r="D58" s="119"/>
       <c r="E58" s="49"/>
-      <c r="F58" s="107"/>
-      <c r="G58" s="107"/>
+      <c r="F58" s="119"/>
+      <c r="G58" s="119"/>
       <c r="H58" s="50"/>
       <c r="I58" s="49"/>
       <c r="J58" s="13"/>
-      <c r="K58" s="107"/>
+      <c r="K58" s="119"/>
       <c r="L58" s="50"/>
-      <c r="M58" s="216"/>
-      <c r="O58" s="217"/>
-      <c r="P58" s="218"/>
+      <c r="M58" s="227"/>
+      <c r="O58" s="228"/>
+      <c r="P58" s="229"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="209"/>
-      <c r="B59" s="210"/>
-      <c r="C59" s="211" t="str">
+      <c r="A59" s="220"/>
+      <c r="B59" s="221"/>
+      <c r="C59" s="222" t="str">
         <f aca="false">DEC2HEX(D59,2)</f>
         <v>0C</v>
       </c>
-      <c r="D59" s="161" t="n">
+      <c r="D59" s="173" t="n">
         <f aca="false">IF(E59=1,128,0)+IF(F59=1,64,0)+IF(G59=1,32,0)+IF(H59=1,16,0)+IF(I59=1,8,0)+IF(J59=1,4,0)+IF(K59=1,2,0)+IF(L59=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="E59" s="178"/>
-      <c r="F59" s="161"/>
-      <c r="G59" s="161"/>
-      <c r="H59" s="165"/>
-      <c r="I59" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="210"/>
-      <c r="N59" s="210"/>
-      <c r="O59" s="212"/>
-      <c r="P59" s="214"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A60" s="215"/>
-      <c r="E60" s="134"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
+      <c r="E59" s="190"/>
+      <c r="F59" s="173"/>
+      <c r="G59" s="173"/>
+      <c r="H59" s="177"/>
+      <c r="I59" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="221"/>
+      <c r="N59" s="221"/>
+      <c r="O59" s="223"/>
+      <c r="P59" s="225"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A60" s="226"/>
+      <c r="E60" s="146"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="119"/>
       <c r="H60" s="50"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="107"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="119"/>
       <c r="L60" s="50"/>
-      <c r="M60" s="216"/>
-      <c r="N60" s="216"/>
-      <c r="O60" s="130"/>
-      <c r="P60" s="218"/>
+      <c r="M60" s="227"/>
+      <c r="N60" s="227"/>
+      <c r="O60" s="142"/>
+      <c r="P60" s="229"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="209"/>
-      <c r="B61" s="210"/>
-      <c r="C61" s="211" t="str">
+      <c r="A61" s="220"/>
+      <c r="B61" s="221"/>
+      <c r="C61" s="222" t="str">
         <f aca="false">DEC2HEX(D61,2)</f>
         <v>0D</v>
       </c>
-      <c r="D61" s="161" t="n">
+      <c r="D61" s="173" t="n">
         <f aca="false">IF(E61=1,128,0)+IF(F61=1,64,0)+IF(G61=1,32,0)+IF(H61=1,16,0)+IF(I61=1,8,0)+IF(J61=1,4,0)+IF(K61=1,2,0)+IF(L61=1,1,0)</f>
         <v>13</v>
       </c>
-      <c r="E61" s="178"/>
-      <c r="F61" s="161"/>
-      <c r="G61" s="161"/>
-      <c r="H61" s="165"/>
-      <c r="I61" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="210"/>
-      <c r="N61" s="210"/>
-      <c r="O61" s="212"/>
-      <c r="P61" s="214"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A62" s="215"/>
-      <c r="E62" s="134"/>
-      <c r="F62" s="107"/>
-      <c r="G62" s="107"/>
+      <c r="E61" s="190"/>
+      <c r="F61" s="173"/>
+      <c r="G61" s="173"/>
+      <c r="H61" s="177"/>
+      <c r="I61" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="221"/>
+      <c r="N61" s="221"/>
+      <c r="O61" s="223"/>
+      <c r="P61" s="225"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A62" s="226"/>
+      <c r="E62" s="146"/>
+      <c r="F62" s="119"/>
+      <c r="G62" s="119"/>
       <c r="H62" s="50"/>
-      <c r="I62" s="107"/>
-      <c r="J62" s="107"/>
-      <c r="K62" s="107"/>
+      <c r="I62" s="119"/>
+      <c r="J62" s="119"/>
+      <c r="K62" s="119"/>
       <c r="L62" s="50"/>
-      <c r="M62" s="216"/>
-      <c r="N62" s="216"/>
-      <c r="O62" s="130"/>
-      <c r="P62" s="218"/>
+      <c r="M62" s="227"/>
+      <c r="N62" s="227"/>
+      <c r="O62" s="142"/>
+      <c r="P62" s="229"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="209"/>
-      <c r="B63" s="210"/>
-      <c r="C63" s="211" t="str">
+      <c r="A63" s="220"/>
+      <c r="B63" s="221"/>
+      <c r="C63" s="222" t="str">
         <f aca="false">DEC2HEX(D63,2)</f>
         <v>0E</v>
       </c>
-      <c r="D63" s="161" t="n">
+      <c r="D63" s="173" t="n">
         <f aca="false">IF(E63=1,128,0)+IF(F63=1,64,0)+IF(G63=1,32,0)+IF(H63=1,16,0)+IF(I63=1,8,0)+IF(J63=1,4,0)+IF(K63=1,2,0)+IF(L63=1,1,0)</f>
         <v>14</v>
       </c>
-      <c r="E63" s="178"/>
-      <c r="F63" s="161"/>
-      <c r="G63" s="161"/>
-      <c r="H63" s="165"/>
-      <c r="I63" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="210"/>
-      <c r="N63" s="210"/>
-      <c r="O63" s="212"/>
-      <c r="P63" s="214"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="215"/>
-      <c r="E64" s="134"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
+      <c r="E63" s="190"/>
+      <c r="F63" s="173"/>
+      <c r="G63" s="173"/>
+      <c r="H63" s="177"/>
+      <c r="I63" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="221"/>
+      <c r="N63" s="221"/>
+      <c r="O63" s="223"/>
+      <c r="P63" s="225"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A64" s="226"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="119"/>
+      <c r="G64" s="119"/>
       <c r="H64" s="50"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="107"/>
+      <c r="I64" s="119"/>
+      <c r="J64" s="119"/>
+      <c r="K64" s="119"/>
       <c r="L64" s="50"/>
-      <c r="M64" s="216"/>
-      <c r="N64" s="216"/>
-      <c r="O64" s="130"/>
-      <c r="P64" s="218"/>
+      <c r="M64" s="227"/>
+      <c r="N64" s="227"/>
+      <c r="O64" s="142"/>
+      <c r="P64" s="229"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="209"/>
-      <c r="B65" s="210"/>
-      <c r="C65" s="211" t="str">
+      <c r="A65" s="220"/>
+      <c r="B65" s="221"/>
+      <c r="C65" s="222" t="str">
         <f aca="false">DEC2HEX(D65,2)</f>
         <v>0F</v>
       </c>
-      <c r="D65" s="161" t="n">
+      <c r="D65" s="173" t="n">
         <f aca="false">IF(E65=1,128,0)+IF(F65=1,64,0)+IF(G65=1,32,0)+IF(H65=1,16,0)+IF(I65=1,8,0)+IF(J65=1,4,0)+IF(K65=1,2,0)+IF(L65=1,1,0)</f>
         <v>15</v>
       </c>
-      <c r="E65" s="178"/>
-      <c r="F65" s="161"/>
-      <c r="G65" s="161"/>
-      <c r="H65" s="165"/>
-      <c r="I65" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="210"/>
-      <c r="N65" s="210"/>
-      <c r="O65" s="212"/>
-      <c r="P65" s="214"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A66" s="215"/>
-      <c r="E66" s="134"/>
-      <c r="F66" s="107"/>
-      <c r="G66" s="107"/>
+      <c r="E65" s="190"/>
+      <c r="F65" s="173"/>
+      <c r="G65" s="173"/>
+      <c r="H65" s="177"/>
+      <c r="I65" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="221"/>
+      <c r="N65" s="221"/>
+      <c r="O65" s="223"/>
+      <c r="P65" s="225"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A66" s="226"/>
+      <c r="E66" s="146"/>
+      <c r="F66" s="119"/>
+      <c r="G66" s="119"/>
       <c r="H66" s="50"/>
-      <c r="I66" s="107"/>
-      <c r="J66" s="107"/>
-      <c r="K66" s="107"/>
+      <c r="I66" s="119"/>
+      <c r="J66" s="119"/>
+      <c r="K66" s="119"/>
       <c r="L66" s="50"/>
-      <c r="M66" s="216"/>
-      <c r="N66" s="216"/>
-      <c r="O66" s="130"/>
-      <c r="P66" s="218"/>
+      <c r="M66" s="227"/>
+      <c r="N66" s="227"/>
+      <c r="O66" s="142"/>
+      <c r="P66" s="229"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="215"/>
-      <c r="E67" s="134"/>
-      <c r="F67" s="107"/>
-      <c r="G67" s="107"/>
+      <c r="A67" s="226"/>
+      <c r="E67" s="146"/>
+      <c r="F67" s="119"/>
+      <c r="G67" s="119"/>
       <c r="H67" s="50"/>
-      <c r="I67" s="107"/>
-      <c r="J67" s="107"/>
-      <c r="K67" s="107"/>
+      <c r="I67" s="119"/>
+      <c r="J67" s="119"/>
+      <c r="K67" s="119"/>
       <c r="L67" s="50"/>
-      <c r="M67" s="216"/>
-      <c r="N67" s="216"/>
-      <c r="O67" s="130"/>
-      <c r="P67" s="218"/>
+      <c r="M67" s="227"/>
+      <c r="N67" s="227"/>
+      <c r="O67" s="142"/>
+      <c r="P67" s="229"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="215"/>
-      <c r="E68" s="134"/>
-      <c r="F68" s="107"/>
-      <c r="G68" s="107"/>
+      <c r="A68" s="226"/>
+      <c r="E68" s="146"/>
+      <c r="F68" s="119"/>
+      <c r="G68" s="119"/>
       <c r="H68" s="50"/>
-      <c r="I68" s="107"/>
-      <c r="J68" s="107"/>
-      <c r="K68" s="107"/>
+      <c r="I68" s="119"/>
+      <c r="J68" s="119"/>
+      <c r="K68" s="119"/>
       <c r="L68" s="50"/>
-      <c r="M68" s="216"/>
-      <c r="N68" s="216"/>
-      <c r="O68" s="130"/>
-      <c r="P68" s="218"/>
+      <c r="M68" s="227"/>
+      <c r="N68" s="227"/>
+      <c r="O68" s="142"/>
+      <c r="P68" s="229"/>
     </row>
     <row r="69" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="239" t="s">
-        <v>289</v>
-      </c>
-      <c r="E69" s="134"/>
-      <c r="F69" s="191" t="s">
-        <v>290</v>
-      </c>
-      <c r="G69" s="191" t="s">
-        <v>291</v>
-      </c>
-      <c r="H69" s="191" t="s">
-        <v>291</v>
-      </c>
-      <c r="I69" s="191"/>
-      <c r="J69" s="191"/>
-      <c r="K69" s="191" t="s">
-        <v>292</v>
-      </c>
-      <c r="L69" s="191" t="s">
+      <c r="A69" s="250" t="s">
         <v>293</v>
       </c>
-      <c r="M69" s="216"/>
-      <c r="N69" s="216"/>
-      <c r="O69" s="130"/>
-      <c r="P69" s="218"/>
+      <c r="E69" s="146"/>
+      <c r="F69" s="202" t="s">
+        <v>294</v>
+      </c>
+      <c r="G69" s="202" t="s">
+        <v>295</v>
+      </c>
+      <c r="H69" s="202" t="s">
+        <v>295</v>
+      </c>
+      <c r="I69" s="202"/>
+      <c r="J69" s="202"/>
+      <c r="K69" s="202" t="s">
+        <v>296</v>
+      </c>
+      <c r="L69" s="202" t="s">
+        <v>297</v>
+      </c>
+      <c r="M69" s="227"/>
+      <c r="N69" s="227"/>
+      <c r="O69" s="142"/>
+      <c r="P69" s="229"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="209" t="s">
-        <v>211</v>
-      </c>
-      <c r="B70" s="212"/>
-      <c r="C70" s="211"/>
-      <c r="D70" s="161"/>
-      <c r="E70" s="178"/>
-      <c r="F70" s="161"/>
-      <c r="G70" s="161"/>
-      <c r="H70" s="165"/>
-      <c r="I70" s="178"/>
-      <c r="J70" s="161"/>
-      <c r="K70" s="161"/>
-      <c r="L70" s="165"/>
-      <c r="M70" s="210"/>
-      <c r="N70" s="210"/>
-      <c r="O70" s="212"/>
-      <c r="P70" s="214"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="240" t="s">
-        <v>294</v>
-      </c>
-      <c r="B71" s="181"/>
-      <c r="C71" s="205" t="str">
+      <c r="A70" s="220" t="s">
+        <v>213</v>
+      </c>
+      <c r="B70" s="223"/>
+      <c r="C70" s="222"/>
+      <c r="D70" s="173"/>
+      <c r="E70" s="190"/>
+      <c r="F70" s="173"/>
+      <c r="G70" s="173"/>
+      <c r="H70" s="177"/>
+      <c r="I70" s="190"/>
+      <c r="J70" s="173"/>
+      <c r="K70" s="173"/>
+      <c r="L70" s="177"/>
+      <c r="M70" s="221"/>
+      <c r="N70" s="221"/>
+      <c r="O70" s="223"/>
+      <c r="P70" s="225"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A71" s="251" t="s">
+        <v>298</v>
+      </c>
+      <c r="B71" s="193"/>
+      <c r="C71" s="216" t="str">
         <f aca="false">DEC2HEX(D71,2)</f>
         <v>00</v>
       </c>
-      <c r="D71" s="183" t="n">
+      <c r="D71" s="195" t="n">
         <f aca="false">IF(E71=1,128,0)+IF(F71=1,64,0)+IF(G71=1,32,0)+IF(H71=1,16,0)+IF(I71=1,8,0)+IF(J71=1,4,0)+IF(K71=1,2,0)+IF(L71=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E71" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="243"/>
-      <c r="N71" s="243"/>
-      <c r="O71" s="181"/>
-      <c r="P71" s="244"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="215" t="s">
-        <v>295</v>
-      </c>
-      <c r="B72" s="130"/>
+      <c r="E71" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="254"/>
+      <c r="N71" s="254"/>
+      <c r="O71" s="193"/>
+      <c r="P71" s="255"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A72" s="226" t="s">
+        <v>299</v>
+      </c>
+      <c r="B72" s="142"/>
       <c r="C72" s="20" t="str">
         <f aca="false">DEC2HEX(D72,2)</f>
         <v>10</v>
@@ -9642,10 +9834,10 @@
       <c r="E72" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="107" t="n">
+      <c r="F72" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="50" t="n">
@@ -9654,25 +9846,25 @@
       <c r="I72" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="107" t="n">
+      <c r="J72" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="119" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="216"/>
-      <c r="N72" s="216"/>
-      <c r="O72" s="130"/>
-      <c r="P72" s="218"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="215" t="s">
-        <v>296</v>
-      </c>
-      <c r="B73" s="130"/>
+      <c r="M72" s="227"/>
+      <c r="N72" s="227"/>
+      <c r="O72" s="142"/>
+      <c r="P72" s="229"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A73" s="226" t="s">
+        <v>300</v>
+      </c>
+      <c r="B73" s="142"/>
       <c r="C73" s="20" t="str">
         <f aca="false">DEC2HEX(D73,2)</f>
         <v>20</v>
@@ -9684,10 +9876,10 @@
       <c r="E73" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="107" t="n">
+      <c r="F73" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="50" t="n">
@@ -9696,109 +9888,109 @@
       <c r="I73" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="107" t="n">
+      <c r="J73" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="119" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="216"/>
-      <c r="N73" s="216"/>
-      <c r="O73" s="130"/>
-      <c r="P73" s="218"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="235" t="s">
-        <v>297</v>
-      </c>
-      <c r="B74" s="238"/>
-      <c r="C74" s="236" t="str">
+      <c r="M73" s="227"/>
+      <c r="N73" s="227"/>
+      <c r="O73" s="142"/>
+      <c r="P73" s="229"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A74" s="246" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="249"/>
+      <c r="C74" s="247" t="str">
         <f aca="false">DEC2HEX(D74,2)</f>
         <v>30</v>
       </c>
-      <c r="D74" s="140" t="n">
+      <c r="D74" s="152" t="n">
         <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
         <v>48</v>
       </c>
-      <c r="E74" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="143" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="245"/>
-      <c r="N74" s="245"/>
-      <c r="O74" s="238"/>
-      <c r="P74" s="246"/>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="240" t="s">
-        <v>298</v>
-      </c>
-      <c r="B75" s="181"/>
-      <c r="C75" s="205" t="str">
+      <c r="E74" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="256"/>
+      <c r="N74" s="256"/>
+      <c r="O74" s="249"/>
+      <c r="P74" s="257"/>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A75" s="251" t="s">
+        <v>302</v>
+      </c>
+      <c r="B75" s="193"/>
+      <c r="C75" s="216" t="str">
         <f aca="false">DEC2HEX(D75,2)</f>
         <v>40</v>
       </c>
-      <c r="D75" s="183" t="n">
+      <c r="D75" s="195" t="n">
         <f aca="false">IF(E75=1,128,0)+IF(F75=1,64,0)+IF(G75=1,32,0)+IF(H75=1,16,0)+IF(I75=1,8,0)+IF(J75=1,4,0)+IF(K75=1,2,0)+IF(L75=1,1,0)</f>
         <v>64</v>
       </c>
-      <c r="E75" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="195" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="243"/>
-      <c r="N75" s="243"/>
-      <c r="O75" s="181"/>
-      <c r="P75" s="244"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="215" t="s">
-        <v>299</v>
-      </c>
-      <c r="B76" s="130"/>
+      <c r="E75" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="254"/>
+      <c r="N75" s="254"/>
+      <c r="O75" s="193"/>
+      <c r="P75" s="255"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A76" s="226" t="s">
+        <v>303</v>
+      </c>
+      <c r="B76" s="142"/>
       <c r="C76" s="20" t="str">
         <f aca="false">DEC2HEX(D76,2)</f>
         <v>50</v>
@@ -9810,10 +10002,10 @@
       <c r="E76" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="107" t="n">
+      <c r="F76" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="50" t="n">
@@ -9822,25 +10014,25 @@
       <c r="I76" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="107" t="n">
+      <c r="J76" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="119" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="216"/>
-      <c r="N76" s="216"/>
-      <c r="O76" s="130"/>
-      <c r="P76" s="218"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="215" t="s">
-        <v>300</v>
-      </c>
-      <c r="B77" s="130"/>
+      <c r="M76" s="227"/>
+      <c r="N76" s="227"/>
+      <c r="O76" s="142"/>
+      <c r="P76" s="229"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A77" s="226" t="s">
+        <v>304</v>
+      </c>
+      <c r="B77" s="142"/>
       <c r="C77" s="20" t="str">
         <f aca="false">DEC2HEX(D77,2)</f>
         <v>60</v>
@@ -9852,10 +10044,10 @@
       <c r="E77" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="107" t="n">
+      <c r="F77" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="50" t="n">
@@ -9864,109 +10056,109 @@
       <c r="I77" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="107" t="n">
+      <c r="J77" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="119" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="216"/>
-      <c r="N77" s="216"/>
-      <c r="O77" s="130"/>
-      <c r="P77" s="218"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="235" t="s">
-        <v>301</v>
-      </c>
-      <c r="B78" s="238"/>
-      <c r="C78" s="236" t="str">
+      <c r="M77" s="227"/>
+      <c r="N77" s="227"/>
+      <c r="O77" s="142"/>
+      <c r="P77" s="229"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A78" s="246" t="s">
+        <v>305</v>
+      </c>
+      <c r="B78" s="249"/>
+      <c r="C78" s="247" t="str">
         <f aca="false">DEC2HEX(D78,2)</f>
         <v>70</v>
       </c>
-      <c r="D78" s="140" t="n">
+      <c r="D78" s="152" t="n">
         <f aca="false">IF(E78=1,128,0)+IF(F78=1,64,0)+IF(G78=1,32,0)+IF(H78=1,16,0)+IF(I78=1,8,0)+IF(J78=1,4,0)+IF(K78=1,2,0)+IF(L78=1,1,0)</f>
         <v>112</v>
       </c>
-      <c r="E78" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="143" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="245"/>
-      <c r="N78" s="245"/>
-      <c r="O78" s="238"/>
-      <c r="P78" s="246"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="240" t="s">
-        <v>302</v>
-      </c>
-      <c r="B79" s="247"/>
-      <c r="C79" s="205" t="str">
+      <c r="E78" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="256"/>
+      <c r="N78" s="256"/>
+      <c r="O78" s="249"/>
+      <c r="P78" s="257"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A79" s="251" t="s">
+        <v>306</v>
+      </c>
+      <c r="B79" s="258"/>
+      <c r="C79" s="216" t="str">
         <f aca="false">DEC2HEX(D79,2)</f>
         <v>01</v>
       </c>
-      <c r="D79" s="183" t="n">
+      <c r="D79" s="195" t="n">
         <f aca="false">IF(E79=1,128,0)+IF(F79=1,64,0)+IF(G79=1,32,0)+IF(H79=1,16,0)+IF(I79=1,8,0)+IF(J79=1,4,0)+IF(K79=1,2,0)+IF(L79=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E79" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="242" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="243"/>
-      <c r="N79" s="243"/>
-      <c r="O79" s="181"/>
-      <c r="P79" s="244"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="215" t="s">
-        <v>303</v>
-      </c>
-      <c r="B80" s="130"/>
+      <c r="E79" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="254"/>
+      <c r="N79" s="254"/>
+      <c r="O79" s="193"/>
+      <c r="P79" s="255"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A80" s="226" t="s">
+        <v>307</v>
+      </c>
+      <c r="B80" s="142"/>
       <c r="C80" s="20" t="str">
         <f aca="false">DEC2HEX(D80,2)</f>
         <v>11</v>
@@ -9975,7 +10167,7 @@
         <f aca="false">IF(E80=1,128,0)+IF(F80=1,64,0)+IF(G80=1,32,0)+IF(H80=1,16,0)+IF(I80=1,8,0)+IF(J80=1,4,0)+IF(K80=1,2,0)+IF(L80=1,1,0)</f>
         <v>17</v>
       </c>
-      <c r="E80" s="134" t="n">
+      <c r="E80" s="146" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="2" t="n">
@@ -9999,13 +10191,13 @@
       <c r="L80" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="P80" s="218"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="215" t="s">
-        <v>304</v>
-      </c>
-      <c r="B81" s="130"/>
+      <c r="P80" s="229"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A81" s="226" t="s">
+        <v>308</v>
+      </c>
+      <c r="B81" s="142"/>
       <c r="C81" s="20" t="str">
         <f aca="false">DEC2HEX(D81,2)</f>
         <v>21</v>
@@ -10014,13 +10206,13 @@
         <f aca="false">IF(E81=1,128,0)+IF(F81=1,64,0)+IF(G81=1,32,0)+IF(H81=1,16,0)+IF(I81=1,8,0)+IF(J81=1,4,0)+IF(K81=1,2,0)+IF(L81=1,1,0)</f>
         <v>33</v>
       </c>
-      <c r="E81" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="107" t="n">
+      <c r="E81" s="146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="50" t="n">
@@ -10040,100 +10232,100 @@
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10"/>
-      <c r="O81" s="130"/>
-      <c r="P81" s="218"/>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="235" t="s">
-        <v>305</v>
-      </c>
-      <c r="B82" s="238"/>
-      <c r="C82" s="236" t="str">
+      <c r="O81" s="142"/>
+      <c r="P81" s="229"/>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A82" s="246" t="s">
+        <v>309</v>
+      </c>
+      <c r="B82" s="249"/>
+      <c r="C82" s="247" t="str">
         <f aca="false">DEC2HEX(D82,2)</f>
         <v>31</v>
       </c>
-      <c r="D82" s="140" t="n">
+      <c r="D82" s="152" t="n">
         <f aca="false">IF(E82=1,128,0)+IF(F82=1,64,0)+IF(G82=1,32,0)+IF(H82=1,16,0)+IF(I82=1,8,0)+IF(J82=1,4,0)+IF(K82=1,2,0)+IF(L82=1,1,0)</f>
         <v>49</v>
       </c>
-      <c r="E82" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="143" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="143" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" s="245"/>
-      <c r="N82" s="245"/>
-      <c r="O82" s="238"/>
-      <c r="P82" s="246"/>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="240" t="s">
-        <v>306</v>
-      </c>
-      <c r="B83" s="181"/>
-      <c r="C83" s="205" t="str">
+      <c r="E82" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="256"/>
+      <c r="N82" s="256"/>
+      <c r="O82" s="249"/>
+      <c r="P82" s="257"/>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A83" s="251" t="s">
+        <v>310</v>
+      </c>
+      <c r="B83" s="193"/>
+      <c r="C83" s="216" t="str">
         <f aca="false">DEC2HEX(D83,2)</f>
         <v>04</v>
       </c>
-      <c r="D83" s="183" t="n">
+      <c r="D83" s="195" t="n">
         <f aca="false">IF(E83=1,128,0)+IF(F83=1,64,0)+IF(G83=1,32,0)+IF(H83=1,16,0)+IF(I83=1,8,0)+IF(J83=1,4,0)+IF(K83=1,2,0)+IF(L83=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E83" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="195" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="243"/>
-      <c r="N83" s="243"/>
-      <c r="O83" s="181"/>
-      <c r="P83" s="244" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A84" s="215" t="s">
-        <v>308</v>
-      </c>
-      <c r="B84" s="130"/>
+      <c r="E83" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="254"/>
+      <c r="N83" s="254"/>
+      <c r="O83" s="193"/>
+      <c r="P83" s="255" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A84" s="226" t="s">
+        <v>312</v>
+      </c>
+      <c r="B84" s="142"/>
       <c r="C84" s="20" t="str">
         <f aca="false">DEC2HEX(D84,2)</f>
         <v>44</v>
@@ -10145,10 +10337,10 @@
       <c r="E84" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="107" t="n">
+      <c r="F84" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="50" t="n">
@@ -10157,71 +10349,71 @@
       <c r="I84" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" s="107" t="n">
+      <c r="J84" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="119" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="216"/>
-      <c r="N84" s="216"/>
-      <c r="O84" s="130"/>
-      <c r="P84" s="218" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A85" s="215" t="s">
-        <v>310</v>
-      </c>
-      <c r="B85" s="248"/>
+      <c r="M84" s="227"/>
+      <c r="N84" s="227"/>
+      <c r="O84" s="142"/>
+      <c r="P84" s="229" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A85" s="226" t="s">
+        <v>314</v>
+      </c>
+      <c r="B85" s="259"/>
       <c r="C85" s="17" t="str">
         <f aca="false">DEC2HEX(D85,2)</f>
         <v>54</v>
       </c>
-      <c r="D85" s="107" t="n">
+      <c r="D85" s="119" t="n">
         <f aca="false">IF(E85=1,128,0)+IF(F85=1,64,0)+IF(G85=1,32,0)+IF(H85=1,16,0)+IF(I85=1,8,0)+IF(J85=1,4,0)+IF(K85=1,2,0)+IF(L85=1,1,0)</f>
         <v>84</v>
       </c>
-      <c r="E85" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="216"/>
-      <c r="N85" s="216"/>
-      <c r="O85" s="248"/>
-      <c r="P85" s="218" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A86" s="215" t="s">
-        <v>312</v>
-      </c>
-      <c r="B86" s="248"/>
+      <c r="E85" s="146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="227"/>
+      <c r="N85" s="227"/>
+      <c r="O85" s="259"/>
+      <c r="P85" s="229" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A86" s="226" t="s">
+        <v>316</v>
+      </c>
+      <c r="B86" s="259"/>
       <c r="C86" s="17" t="str">
         <f aca="false">DEC2HEX(D86,2)</f>
         <v>84</v>
@@ -10230,143 +10422,143 @@
         <f aca="false">IF(E86=1,128,0)+IF(F86=1,64,0)+IF(G86=1,32,0)+IF(H86=1,16,0)+IF(I86=1,8,0)+IF(J86=1,4,0)+IF(K86=1,2,0)+IF(L86=1,1,0)</f>
         <v>132</v>
       </c>
-      <c r="E86" s="134" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="216"/>
-      <c r="N86" s="216"/>
-      <c r="O86" s="248"/>
-      <c r="P86" s="218"/>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A87" s="240" t="s">
-        <v>313</v>
-      </c>
-      <c r="B87" s="181"/>
-      <c r="C87" s="205" t="str">
+      <c r="E86" s="146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="227"/>
+      <c r="N86" s="227"/>
+      <c r="O86" s="259"/>
+      <c r="P86" s="229"/>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A87" s="251" t="s">
+        <v>317</v>
+      </c>
+      <c r="B87" s="193"/>
+      <c r="C87" s="216" t="str">
         <f aca="false">DEC2HEX(D87,2)</f>
         <v>05</v>
       </c>
-      <c r="D87" s="183" t="n">
+      <c r="D87" s="195" t="n">
         <f aca="false">IF(E87=1,128,0)+IF(F87=1,64,0)+IF(G87=1,32,0)+IF(H87=1,16,0)+IF(I87=1,8,0)+IF(J87=1,4,0)+IF(K87=1,2,0)+IF(L87=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E87" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="195" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="242" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="243"/>
-      <c r="N87" s="243"/>
-      <c r="O87" s="181"/>
-      <c r="P87" s="244" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A88" s="235" t="s">
-        <v>315</v>
-      </c>
-      <c r="B88" s="238"/>
-      <c r="C88" s="236" t="str">
+      <c r="E87" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="254"/>
+      <c r="N87" s="254"/>
+      <c r="O87" s="193"/>
+      <c r="P87" s="255" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A88" s="246" t="s">
+        <v>319</v>
+      </c>
+      <c r="B88" s="249"/>
+      <c r="C88" s="247" t="str">
         <f aca="false">DEC2HEX(D88,2)</f>
         <v>45</v>
       </c>
-      <c r="D88" s="140" t="n">
+      <c r="D88" s="152" t="n">
         <f aca="false">IF(E88=1,128,0)+IF(F88=1,64,0)+IF(G88=1,32,0)+IF(H88=1,16,0)+IF(I88=1,8,0)+IF(J88=1,4,0)+IF(K88=1,2,0)+IF(L88=1,1,0)</f>
         <v>69</v>
       </c>
-      <c r="E88" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="143" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" s="245"/>
-      <c r="N88" s="245"/>
-      <c r="O88" s="238"/>
-      <c r="P88" s="246" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A89" s="215" t="s">
-        <v>317</v>
-      </c>
-      <c r="B89" s="130"/>
+      <c r="E88" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="256"/>
+      <c r="N88" s="256"/>
+      <c r="O88" s="249"/>
+      <c r="P88" s="257" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A89" s="226" t="s">
+        <v>321</v>
+      </c>
+      <c r="B89" s="142"/>
       <c r="C89" s="17" t="str">
         <f aca="false">DEC2HEX(D89,2)</f>
         <v>37</v>
       </c>
-      <c r="D89" s="107" t="n">
+      <c r="D89" s="119" t="n">
         <f aca="false">IF(E89=1,128,0)+IF(F89=1,64,0)+IF(G89=1,32,0)+IF(H89=1,16,0)+IF(I89=1,8,0)+IF(J89=1,4,0)+IF(K89=1,2,0)+IF(L89=1,1,0)</f>
         <v>55</v>
       </c>
       <c r="E89" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F89" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="107" t="n">
+      <c r="F89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="119" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="50" t="n">
@@ -10375,116 +10567,116 @@
       <c r="I89" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" s="107" t="n">
+      <c r="J89" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="119" t="n">
         <v>1</v>
       </c>
       <c r="L89" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="216"/>
-      <c r="N89" s="216"/>
-      <c r="O89" s="130"/>
-      <c r="P89" s="218"/>
-    </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A90" s="235" t="s">
-        <v>318</v>
-      </c>
-      <c r="B90" s="238"/>
-      <c r="C90" s="236" t="str">
+      <c r="M89" s="227"/>
+      <c r="N89" s="227"/>
+      <c r="O89" s="142"/>
+      <c r="P89" s="229"/>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A90" s="246" t="s">
+        <v>322</v>
+      </c>
+      <c r="B90" s="249"/>
+      <c r="C90" s="247" t="str">
         <f aca="false">DEC2HEX(D90,2)</f>
         <v>37</v>
       </c>
-      <c r="D90" s="140" t="n">
+      <c r="D90" s="152" t="n">
         <f aca="false">IF(E90=1,128,0)+IF(F90=1,64,0)+IF(G90=1,32,0)+IF(H90=1,16,0)+IF(I90=1,8,0)+IF(J90=1,4,0)+IF(K90=1,2,0)+IF(L90=1,1,0)</f>
         <v>55</v>
       </c>
-      <c r="E90" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="143" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" s="140" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="143" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" s="245"/>
-      <c r="N90" s="245"/>
-      <c r="O90" s="238"/>
-      <c r="P90" s="246"/>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A91" s="215"/>
-      <c r="B91" s="130"/>
+      <c r="E90" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" s="256"/>
+      <c r="N90" s="256"/>
+      <c r="O90" s="249"/>
+      <c r="P90" s="257"/>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A91" s="226"/>
+      <c r="B91" s="142"/>
       <c r="C91" s="17" t="str">
         <f aca="false">DEC2HEX(D91,2)</f>
         <v>00</v>
       </c>
-      <c r="D91" s="107" t="n">
+      <c r="D91" s="119" t="n">
         <f aca="false">IF(E91=1,128,0)+IF(F91=1,64,0)+IF(G91=1,32,0)+IF(H91=1,16,0)+IF(I91=1,8,0)+IF(J91=1,4,0)+IF(K91=1,2,0)+IF(L91=1,1,0)</f>
         <v>0</v>
       </c>
       <c r="E91" s="49"/>
-      <c r="F91" s="107"/>
-      <c r="G91" s="107"/>
+      <c r="F91" s="119"/>
+      <c r="G91" s="119"/>
       <c r="H91" s="50"/>
       <c r="I91" s="49"/>
-      <c r="J91" s="107"/>
-      <c r="K91" s="107"/>
+      <c r="J91" s="119"/>
+      <c r="K91" s="119"/>
       <c r="L91" s="50"/>
-      <c r="M91" s="216"/>
-      <c r="N91" s="216"/>
-      <c r="O91" s="130"/>
-      <c r="P91" s="218"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A92" s="235"/>
-      <c r="B92" s="238"/>
-      <c r="C92" s="236" t="str">
+      <c r="M91" s="227"/>
+      <c r="N91" s="227"/>
+      <c r="O91" s="142"/>
+      <c r="P91" s="229"/>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A92" s="246"/>
+      <c r="B92" s="249"/>
+      <c r="C92" s="247" t="str">
         <f aca="false">DEC2HEX(D92,2)</f>
         <v>00</v>
       </c>
-      <c r="D92" s="140" t="n">
+      <c r="D92" s="152" t="n">
         <f aca="false">IF(E92=1,128,0)+IF(F92=1,64,0)+IF(G92=1,32,0)+IF(H92=1,16,0)+IF(I92=1,8,0)+IF(J92=1,4,0)+IF(K92=1,2,0)+IF(L92=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E92" s="237"/>
-      <c r="F92" s="140"/>
-      <c r="G92" s="140"/>
-      <c r="H92" s="143"/>
-      <c r="I92" s="237"/>
-      <c r="J92" s="140"/>
-      <c r="K92" s="140"/>
-      <c r="L92" s="143"/>
-      <c r="M92" s="245"/>
-      <c r="N92" s="245"/>
-      <c r="O92" s="238"/>
-      <c r="P92" s="246"/>
+      <c r="E92" s="248"/>
+      <c r="F92" s="152"/>
+      <c r="G92" s="152"/>
+      <c r="H92" s="155"/>
+      <c r="I92" s="248"/>
+      <c r="J92" s="152"/>
+      <c r="K92" s="152"/>
+      <c r="L92" s="155"/>
+      <c r="M92" s="256"/>
+      <c r="N92" s="256"/>
+      <c r="O92" s="249"/>
+      <c r="P92" s="257"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="130"/>
+      <c r="B93" s="142"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -10499,12 +10691,12 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="3"/>
-      <c r="O94" s="249"/>
+      <c r="O94" s="260"/>
       <c r="P94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -10543,30 +10735,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="G1" s="250" t="s">
-        <v>322</v>
-      </c>
-      <c r="H1" s="250"/>
-      <c r="I1" s="250"/>
-      <c r="J1" s="250" t="s">
-        <v>323</v>
+        <v>120</v>
+      </c>
+      <c r="G1" s="261" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10580,26 +10772,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10613,26 +10805,26 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10649,25 +10841,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10684,25 +10876,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10716,28 +10908,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10751,28 +10943,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10786,26 +10978,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10819,26 +11011,26 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10852,28 +11044,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10887,28 +11079,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10922,28 +11114,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10957,28 +11149,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Connection" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="M34" authorId="0">
+    <comment ref="M36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -58,14 +58,14 @@
               <xdr:from>
                 <xdr:col>13</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>26</xdr:row>
+                <xdr:row>28</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>14</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>31</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>26</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>15</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -73,7 +73,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="N32" authorId="0">
+    <comment ref="N34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -91,13 +91,13 @@
               <xdr:from>
                 <xdr:col>14</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>24</xdr:row>
+                <xdr:row>26</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>26</xdr:row>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>28</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
@@ -106,7 +106,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="N33" authorId="0">
+    <comment ref="N35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,16 +122,16 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>13</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>31</xdr:row>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>102</xdr:colOff>
+                <xdr:row>33</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>14</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>32</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>159</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -139,7 +139,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="N34" authorId="0">
+    <comment ref="N36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -157,14 +157,14 @@
               <xdr:from>
                 <xdr:col>14</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>26</xdr:row>
+                <xdr:row>28</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>27</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="351">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -1353,12 +1353,6 @@
     <t xml:space="preserve">int</t>
   </si>
   <si>
-    <t xml:space="preserve">IsReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IsNull</t>
-  </si>
-  <si>
     <t xml:space="preserve">IsValue</t>
   </si>
   <si>
@@ -1404,7 +1398,82 @@
     <t xml:space="preserve">ValueType (+SimpleType)</t>
   </si>
   <si>
-    <t xml:space="preserve">Specifies the type of all elements in the array. For multi-dimensional arrays, use one array ValueType per dimension.</t>
+    <t xml:space="preserve">Specifies the type of all elements in the array.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">ArrayElemType</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> specifies an array type, then it’s another dimension in a </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">nested array</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> of </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">fixed length dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ArrayElemCount</t>
@@ -1458,6 +1527,81 @@
     <t xml:space="preserve">Each value begins with its own ValueType.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">ArrayElemType</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> specifies an array type, then it’s another dimension in a </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">nested array</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> of </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">variable length arrays</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Struct</t>
   </si>
   <si>
@@ -1506,13 +1650,22 @@
     <t xml:space="preserve">IsValue and IsCustomType and HasTypeName</t>
   </si>
   <si>
-    <t xml:space="preserve">IsNullable</t>
+    <t xml:space="preserve">IsNull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not IsNull</t>
   </si>
   <si>
     <t xml:space="preserve">Reference</t>
   </si>
   <si>
+    <t xml:space="preserve">IsReference</t>
+  </si>
+  <si>
     <t xml:space="preserve">IsStream/IsServlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If IsNull, then the value is null, and there is not point in encoding/decoding a reference.</t>
   </si>
   <si>
     <t xml:space="preserve">IsReference and IsStream</t>
@@ -2159,7 +2312,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2274,6 +2427,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <i val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2791,7 +2958,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -3196,6 +3363,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3240,10 +3411,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3520,6 +3687,14 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3544,15 +3719,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3584,23 +3755,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3608,7 +3779,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3616,19 +3787,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="59" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3636,19 +3803,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="50" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3720,7 +3883,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3805,6 +3968,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4344,9 +4511,9 @@
         <f aca="false">CONCATENATE(ROUND(AVERAGE(R3:R68)*100/3,0),"%")</f>
         <v>81%</v>
       </c>
-      <c r="S2" s="20" t="e">
+      <c r="S2" s="20" t="str">
         <f aca="false">CONCATENATE(ROUND(AVERAGE(S3:S68)*100/4,0),"%")</f>
-        <v>#DIV/0!</v>
+        <v>67%</v>
       </c>
       <c r="T2" s="20" t="e">
         <f aca="false">CONCATENATE(ROUND(AVERAGE(T3:T68)*100/4,0),"%")</f>
@@ -4400,7 +4567,9 @@
       <c r="R3" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S3" s="40"/>
+      <c r="S3" s="40" t="n">
+        <v>4</v>
+      </c>
       <c r="T3" s="40"/>
       <c r="U3" s="40"/>
     </row>
@@ -4460,7 +4629,9 @@
       <c r="R4" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S4" s="40"/>
+      <c r="S4" s="40" t="n">
+        <v>4</v>
+      </c>
       <c r="T4" s="40"/>
       <c r="U4" s="40"/>
     </row>
@@ -4678,7 +4849,9 @@
       <c r="R11" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S11" s="40"/>
+      <c r="S11" s="40" t="n">
+        <v>4</v>
+      </c>
       <c r="T11" s="40"/>
       <c r="U11" s="40"/>
     </row>
@@ -4815,7 +4988,9 @@
       <c r="R15" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="40"/>
+      <c r="S15" s="40" t="n">
+        <v>1</v>
+      </c>
       <c r="T15" s="40"/>
       <c r="U15" s="40"/>
     </row>
@@ -4909,7 +5084,9 @@
       <c r="R18" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S18" s="40"/>
+      <c r="S18" s="40" t="n">
+        <v>4</v>
+      </c>
       <c r="T18" s="40"/>
       <c r="U18" s="40"/>
     </row>
@@ -4946,7 +5123,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="20" s="100" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A20" s="76"/>
       <c r="B20" s="76"/>
       <c r="C20" s="77"/>
@@ -4978,43 +5155,47 @@
       <c r="Q20" s="99" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="21" s="111" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="100"/>
-      <c r="B21" s="100" t="s">
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A21" s="101"/>
+      <c r="B21" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="101"/>
-      <c r="D21" s="102" t="s">
+      <c r="C21" s="102"/>
+      <c r="D21" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="103"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="107" t="s">
+      <c r="E21" s="104"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="N21" s="102" t="n">
+      <c r="N21" s="103" t="n">
         <v>8</v>
       </c>
-      <c r="O21" s="103" t="n">
+      <c r="O21" s="104" t="n">
         <v>8</v>
       </c>
-      <c r="P21" s="108" t="s">
+      <c r="P21" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="Q21" s="109" t="s">
+      <c r="Q21" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="R21" s="110"/>
-      <c r="S21" s="110"/>
-      <c r="T21" s="110"/>
-      <c r="U21" s="110"/>
+      <c r="R21" s="111"/>
+      <c r="S21" s="111"/>
+      <c r="T21" s="111"/>
+      <c r="U21" s="111"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A22" s="66"/>
@@ -5105,7 +5286,9 @@
       <c r="R23" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S23" s="40"/>
+      <c r="S23" s="40" t="n">
+        <v>4</v>
+      </c>
       <c r="T23" s="40"/>
       <c r="U23" s="40"/>
     </row>
@@ -5208,7 +5391,9 @@
       <c r="R26" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S26" s="40"/>
+      <c r="S26" s="40" t="n">
+        <v>4</v>
+      </c>
       <c r="T26" s="40"/>
       <c r="U26" s="40"/>
     </row>
@@ -5471,7 +5656,9 @@
       <c r="R35" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S35" s="40"/>
+      <c r="S35" s="40" t="n">
+        <v>0</v>
+      </c>
       <c r="T35" s="40"/>
       <c r="U35" s="40"/>
     </row>
@@ -5554,7 +5741,9 @@
       <c r="R37" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S37" s="40"/>
+      <c r="S37" s="40" t="n">
+        <v>4</v>
+      </c>
       <c r="T37" s="40"/>
       <c r="U37" s="40"/>
     </row>
@@ -5949,7 +6138,9 @@
       <c r="R51" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="S51" s="40"/>
+      <c r="S51" s="40" t="n">
+        <v>3</v>
+      </c>
       <c r="T51" s="40"/>
       <c r="U51" s="40"/>
     </row>
@@ -6209,7 +6400,9 @@
       <c r="R60" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="S60" s="40"/>
+      <c r="S60" s="40" t="n">
+        <v>0</v>
+      </c>
       <c r="T60" s="40"/>
       <c r="U60" s="40"/>
     </row>
@@ -6334,7 +6527,9 @@
       <c r="R64" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="S64" s="40"/>
+      <c r="S64" s="40" t="n">
+        <v>0</v>
+      </c>
       <c r="T64" s="40"/>
       <c r="U64" s="40"/>
     </row>
@@ -6813,15 +7008,14 @@
   <dimension ref="A1:S1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="122" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="122" width="9.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="18.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="123" width="3.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="5" width="3.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="15.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="5" width="24.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="27.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="5" width="76.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="5" width="17.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="5" width="21.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="21.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="5" width="92.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="5" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="5" width="71.29"/>
   </cols>
@@ -6958,23 +7152,17 @@
       <c r="P4" s="143"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="149" t="s">
-        <v>167</v>
-      </c>
+      <c r="B5" s="149"/>
       <c r="C5" s="150"/>
       <c r="D5" s="151"/>
       <c r="E5" s="152"/>
       <c r="F5" s="152"/>
       <c r="G5" s="153"/>
-      <c r="H5" s="154" t="s">
-        <v>52</v>
-      </c>
+      <c r="H5" s="154"/>
       <c r="I5" s="152"/>
       <c r="J5" s="152"/>
       <c r="K5" s="155"/>
-      <c r="L5" s="156" t="s">
-        <v>168</v>
-      </c>
+      <c r="L5" s="156"/>
       <c r="M5" s="156"/>
       <c r="N5" s="155"/>
       <c r="O5" s="155"/>
@@ -6985,7 +7173,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="159" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C6" s="160"/>
       <c r="D6" s="161"/>
@@ -7021,7 +7209,7 @@
       <c r="J7" s="119"/>
       <c r="K7" s="141"/>
       <c r="L7" s="142" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M7" s="142"/>
       <c r="N7" s="141"/>
@@ -7044,7 +7232,7 @@
       <c r="J8" s="119"/>
       <c r="K8" s="141"/>
       <c r="L8" s="142" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M8" s="142"/>
       <c r="N8" s="141"/>
@@ -7067,7 +7255,7 @@
       <c r="J9" s="119"/>
       <c r="K9" s="141"/>
       <c r="L9" s="142" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M9" s="142"/>
       <c r="N9" s="141"/>
@@ -7090,7 +7278,7 @@
       <c r="J10" s="119"/>
       <c r="K10" s="141"/>
       <c r="L10" s="142" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M10" s="142"/>
       <c r="N10" s="141"/>
@@ -7099,10 +7287,10 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="158" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B11" s="170" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C11" s="171"/>
       <c r="D11" s="172"/>
@@ -7135,16 +7323,16 @@
       <c r="K12" s="141"/>
       <c r="L12" s="142"/>
       <c r="M12" s="142" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N12" s="141" t="n">
         <v>1</v>
       </c>
       <c r="O12" s="141" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P12" s="143" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -7166,10 +7354,10 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="158" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C14" s="171"/>
       <c r="D14" s="172"/>
@@ -7203,23 +7391,25 @@
       <c r="J15" s="13"/>
       <c r="K15" s="141"/>
       <c r="L15" s="142" t="s">
+        <v>178</v>
+      </c>
+      <c r="M15" s="142" t="s">
+        <v>179</v>
+      </c>
+      <c r="N15" s="141" t="s">
         <v>180</v>
       </c>
-      <c r="M15" s="142" t="s">
+      <c r="O15" s="141" t="s">
         <v>181</v>
       </c>
-      <c r="N15" s="141" t="s">
+      <c r="P15" s="180" t="s">
         <v>182</v>
       </c>
-      <c r="O15" s="141" t="s">
-        <v>183</v>
-      </c>
-      <c r="P15" s="180" t="s">
-        <v>184</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B16" s="135"/>
+      <c r="B16" s="181" t="s">
+        <v>178</v>
+      </c>
       <c r="C16" s="136"/>
       <c r="D16" s="137"/>
       <c r="E16" s="13"/>
@@ -7230,23 +7420,15 @@
       <c r="J16" s="13"/>
       <c r="K16" s="141"/>
       <c r="L16" s="142"/>
-      <c r="M16" s="142" t="s">
-        <v>185</v>
-      </c>
-      <c r="N16" s="141" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" s="141" t="s">
-        <v>166</v>
-      </c>
+      <c r="M16" s="142"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="141"/>
       <c r="P16" s="180" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B17" s="135" t="s">
-        <v>180</v>
-      </c>
+      <c r="B17" s="135"/>
       <c r="C17" s="136"/>
       <c r="D17" s="137"/>
       <c r="E17" s="13"/>
@@ -7258,308 +7440,324 @@
       <c r="K17" s="141"/>
       <c r="L17" s="142"/>
       <c r="M17" s="142" t="s">
+        <v>184</v>
+      </c>
+      <c r="N17" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="P17" s="180" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B18" s="135" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="136"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="141"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="142" t="s">
+        <v>186</v>
+      </c>
+      <c r="N18" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="O18" s="141" t="s">
         <v>187</v>
       </c>
-      <c r="N17" s="141" t="s">
+      <c r="P18" s="180" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B19" s="144" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="145"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="141"/>
+      <c r="L19" s="142"/>
+      <c r="M19" s="142" t="s">
+        <v>186</v>
+      </c>
+      <c r="N19" s="141" t="s">
         <v>160</v>
       </c>
-      <c r="O17" s="141" t="s">
-        <v>188</v>
-      </c>
-      <c r="P17" s="180" t="s">
+      <c r="O19" s="141" t="s">
+        <v>187</v>
+      </c>
+      <c r="P19" s="180" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B20" s="182" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B18" s="149" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="150"/>
-      <c r="D18" s="181"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="182"/>
-      <c r="G18" s="183"/>
-      <c r="H18" s="184"/>
-      <c r="I18" s="182"/>
-      <c r="J18" s="152"/>
-      <c r="K18" s="155"/>
-      <c r="L18" s="156"/>
-      <c r="M18" s="156" t="s">
-        <v>187</v>
-      </c>
-      <c r="N18" s="155" t="s">
-        <v>160</v>
-      </c>
-      <c r="O18" s="155" t="s">
-        <v>188</v>
-      </c>
-      <c r="P18" s="185" t="s">
+      <c r="C20" s="150"/>
+      <c r="D20" s="183"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="186"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="152"/>
+      <c r="K20" s="155"/>
+      <c r="L20" s="156"/>
+      <c r="M20" s="156"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="155"/>
+      <c r="P20" s="187" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="158" t="s">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="158" t="s">
         <v>192</v>
       </c>
-      <c r="B19" s="170" t="s">
+      <c r="B21" s="170" t="s">
         <v>193</v>
       </c>
-      <c r="C19" s="171"/>
-      <c r="D19" s="172"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="174"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="173"/>
-      <c r="K19" s="177"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="178"/>
-      <c r="N19" s="177"/>
-      <c r="O19" s="177"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="169"/>
-      <c r="R19" s="169"/>
-      <c r="S19" s="169"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B20" s="135"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="186"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="142"/>
-      <c r="M20" s="142" t="s">
+      <c r="C21" s="171"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="173"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="176"/>
+      <c r="I21" s="174"/>
+      <c r="J21" s="173"/>
+      <c r="K21" s="177"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="178"/>
+      <c r="N21" s="177"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="179"/>
+      <c r="Q21" s="169"/>
+      <c r="R21" s="169"/>
+      <c r="S21" s="169"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B22" s="135"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="188"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="141"/>
+      <c r="L22" s="142"/>
+      <c r="M22" s="142" t="s">
         <v>194</v>
       </c>
-      <c r="N20" s="141" t="n">
+      <c r="N22" s="141" t="n">
         <v>4</v>
       </c>
-      <c r="O20" s="141" t="s">
+      <c r="O22" s="141" t="s">
         <v>166</v>
       </c>
-      <c r="P20" s="180" t="s">
+      <c r="P22" s="180" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B21" s="135"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="186"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="141"/>
-      <c r="L21" s="142"/>
-      <c r="M21" s="142" t="s">
-        <v>187</v>
-      </c>
-      <c r="N21" s="141" t="s">
-        <v>160</v>
-      </c>
-      <c r="O21" s="141" t="s">
-        <v>188</v>
-      </c>
-      <c r="P21" s="180" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="158" t="s">
-        <v>196</v>
-      </c>
-      <c r="B22" s="170" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="171"/>
-      <c r="D22" s="172"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="174"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="174"/>
-      <c r="J22" s="173"/>
-      <c r="K22" s="177"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="178"/>
-      <c r="N22" s="177"/>
-      <c r="O22" s="177"/>
-      <c r="P22" s="179"/>
-      <c r="Q22" s="169"/>
-      <c r="R22" s="169"/>
-      <c r="S22" s="169"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B23" s="135"/>
       <c r="C23" s="136"/>
       <c r="D23" s="137"/>
-      <c r="E23" s="119" t="s">
-        <v>52</v>
-      </c>
+      <c r="E23" s="138"/>
       <c r="F23" s="138"/>
-      <c r="G23" s="139"/>
+      <c r="G23" s="188"/>
       <c r="H23" s="140"/>
       <c r="I23" s="138"/>
-      <c r="J23" s="119"/>
+      <c r="J23" s="13"/>
       <c r="K23" s="141"/>
-      <c r="L23" s="142" t="s">
+      <c r="L23" s="142"/>
+      <c r="M23" s="142" t="s">
+        <v>186</v>
+      </c>
+      <c r="N23" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="O23" s="141" t="s">
+        <v>187</v>
+      </c>
+      <c r="P23" s="180" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="158" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="170" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="171"/>
+      <c r="D24" s="172"/>
+      <c r="E24" s="173"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="176"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="173"/>
+      <c r="K24" s="177"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="178"/>
+      <c r="N24" s="177"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="179"/>
+      <c r="Q24" s="169"/>
+      <c r="R24" s="169"/>
+      <c r="S24" s="169"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B25" s="135"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="137" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="119"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="141"/>
+      <c r="L25" s="189" t="s">
         <v>198</v>
       </c>
-      <c r="M23" s="142"/>
-      <c r="N23" s="141"/>
-      <c r="O23" s="141"/>
-      <c r="P23" s="143"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B24" s="187"/>
-      <c r="C24" s="188"/>
-      <c r="D24" s="181"/>
-      <c r="E24" s="152"/>
-      <c r="F24" s="182"/>
-      <c r="G24" s="183"/>
-      <c r="H24" s="184"/>
-      <c r="I24" s="182"/>
-      <c r="J24" s="152"/>
-      <c r="K24" s="155"/>
-      <c r="L24" s="156"/>
-      <c r="M24" s="156" t="s">
-        <v>176</v>
-      </c>
-      <c r="N24" s="155" t="s">
-        <v>160</v>
-      </c>
-      <c r="O24" s="155" t="s">
-        <v>176</v>
-      </c>
-      <c r="P24" s="189" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="158" t="s">
+      <c r="M25" s="142"/>
+      <c r="N25" s="141"/>
+      <c r="O25" s="141"/>
+      <c r="P25" s="143"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B26" s="135" t="s">
         <v>199</v>
       </c>
-      <c r="B25" s="170" t="s">
-        <v>167</v>
-      </c>
-      <c r="C25" s="171"/>
-      <c r="D25" s="190"/>
-      <c r="E25" s="173"/>
-      <c r="F25" s="173"/>
-      <c r="G25" s="191"/>
-      <c r="H25" s="192"/>
-      <c r="I25" s="173"/>
-      <c r="J25" s="173"/>
-      <c r="K25" s="177"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="178"/>
-      <c r="N25" s="177"/>
-      <c r="O25" s="177"/>
-      <c r="P25" s="179"/>
-      <c r="Q25" s="169"/>
-      <c r="R25" s="169"/>
-      <c r="S25" s="169"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B26" s="135"/>
       <c r="C26" s="136"/>
       <c r="D26" s="137"/>
-      <c r="E26" s="138"/>
+      <c r="E26" s="119"/>
       <c r="F26" s="138"/>
-      <c r="G26" s="186" t="s">
-        <v>52</v>
-      </c>
+      <c r="G26" s="139"/>
       <c r="H26" s="140"/>
       <c r="I26" s="138"/>
-      <c r="J26" s="13"/>
+      <c r="J26" s="119"/>
       <c r="K26" s="141"/>
-      <c r="L26" s="142" t="s">
+      <c r="L26" s="142"/>
+      <c r="M26" s="142" t="s">
+        <v>174</v>
+      </c>
+      <c r="N26" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="O26" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="P26" s="190" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="158" t="s">
         <v>200</v>
       </c>
-      <c r="M26" s="142"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="141"/>
-      <c r="P26" s="143"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B27" s="135"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="138"/>
-      <c r="F27" s="138"/>
-      <c r="G27" s="186"/>
-      <c r="H27" s="140"/>
-      <c r="I27" s="138"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="142"/>
-      <c r="M27" s="142"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="141"/>
-      <c r="P27" s="143"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="158" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="170" t="s">
+      <c r="B27" s="170" t="s">
         <v>201</v>
       </c>
-      <c r="C28" s="171"/>
-      <c r="D28" s="172"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="174"/>
-      <c r="G28" s="191"/>
-      <c r="H28" s="176"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="173"/>
-      <c r="K28" s="177"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="178"/>
-      <c r="N28" s="177"/>
-      <c r="O28" s="177"/>
-      <c r="P28" s="179"/>
-      <c r="Q28" s="169"/>
-      <c r="R28" s="169"/>
-      <c r="S28" s="169"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="191"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="192"/>
+      <c r="H27" s="193"/>
+      <c r="I27" s="173"/>
+      <c r="J27" s="173"/>
+      <c r="K27" s="177"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="178"/>
+      <c r="N27" s="177"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="169"/>
+      <c r="R27" s="169"/>
+      <c r="S27" s="169"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B28" s="135"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="137" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="119"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="189" t="s">
+        <v>198</v>
+      </c>
+      <c r="M28" s="142"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="141"/>
+      <c r="P28" s="143"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B29" s="149"/>
-      <c r="C29" s="150"/>
+      <c r="B29" s="135" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="136"/>
       <c r="D29" s="137"/>
       <c r="E29" s="138"/>
       <c r="F29" s="138"/>
-      <c r="G29" s="186"/>
+      <c r="G29" s="188" t="s">
+        <v>52</v>
+      </c>
       <c r="H29" s="140"/>
       <c r="I29" s="138"/>
       <c r="J29" s="13"/>
       <c r="K29" s="141"/>
-      <c r="L29" s="142"/>
-      <c r="M29" s="156"/>
-      <c r="N29" s="155"/>
-      <c r="O29" s="155"/>
-      <c r="P29" s="143"/>
+      <c r="L29" s="142" t="s">
+        <v>202</v>
+      </c>
+      <c r="M29" s="142"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="141"/>
+      <c r="P29" s="143" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="158" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="B30" s="170" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C30" s="171"/>
       <c r="D30" s="172"/>
       <c r="E30" s="174"/>
       <c r="F30" s="174"/>
-      <c r="G30" s="191"/>
+      <c r="G30" s="192"/>
       <c r="H30" s="176"/>
       <c r="I30" s="174"/>
       <c r="J30" s="173"/>
@@ -7574,324 +7772,288 @@
       <c r="S30" s="169"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B31" s="135"/>
-      <c r="C31" s="136"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="150"/>
       <c r="D31" s="137"/>
       <c r="E31" s="138"/>
       <c r="F31" s="138"/>
-      <c r="G31" s="186"/>
+      <c r="G31" s="188"/>
       <c r="H31" s="140"/>
       <c r="I31" s="138"/>
       <c r="J31" s="13"/>
       <c r="K31" s="141"/>
       <c r="L31" s="142"/>
-      <c r="M31" s="142" t="s">
-        <v>77</v>
-      </c>
-      <c r="N31" s="141" t="n">
-        <v>4</v>
-      </c>
-      <c r="O31" s="141" t="s">
-        <v>166</v>
-      </c>
+      <c r="M31" s="156"/>
+      <c r="N31" s="155"/>
+      <c r="O31" s="155"/>
       <c r="P31" s="143"/>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B32" s="135"/>
-      <c r="C32" s="136"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" s="139"/>
-      <c r="H32" s="140"/>
-      <c r="I32" s="138"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="141"/>
-      <c r="L32" s="142" t="s">
-        <v>203</v>
-      </c>
-      <c r="M32" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="N32" s="141" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" s="141" t="s">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="158" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="170" t="s">
         <v>205</v>
       </c>
-      <c r="P32" s="143" t="s">
-        <v>206</v>
-      </c>
+      <c r="C32" s="171"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="174"/>
+      <c r="G32" s="192"/>
+      <c r="H32" s="176"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="173"/>
+      <c r="K32" s="177"/>
+      <c r="L32" s="178"/>
+      <c r="M32" s="178"/>
+      <c r="N32" s="177"/>
+      <c r="O32" s="177"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="169"/>
+      <c r="R32" s="169"/>
+      <c r="S32" s="169"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B33" s="135" t="s">
-        <v>203</v>
-      </c>
+      <c r="B33" s="135"/>
       <c r="C33" s="136"/>
       <c r="D33" s="137"/>
       <c r="E33" s="138"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="139"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="188"/>
       <c r="H33" s="140"/>
       <c r="I33" s="138"/>
       <c r="J33" s="13"/>
       <c r="K33" s="141"/>
       <c r="L33" s="142"/>
       <c r="M33" s="142" t="s">
+        <v>77</v>
+      </c>
+      <c r="N33" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="P33" s="143"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B34" s="135"/>
+      <c r="C34" s="136"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="139"/>
+      <c r="H34" s="140"/>
+      <c r="I34" s="138"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="141"/>
+      <c r="L34" s="142" t="s">
+        <v>206</v>
+      </c>
+      <c r="M34" s="142" t="s">
         <v>207</v>
       </c>
-      <c r="N33" s="141" t="s">
+      <c r="N34" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" s="141" t="s">
+        <v>208</v>
+      </c>
+      <c r="P34" s="143" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B35" s="135" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="136"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="139"/>
+      <c r="H35" s="140"/>
+      <c r="I35" s="138"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="141"/>
+      <c r="L35" s="142"/>
+      <c r="M35" s="142" t="s">
+        <v>210</v>
+      </c>
+      <c r="N35" s="141" t="s">
         <v>160</v>
       </c>
-      <c r="O33" s="141" t="s">
-        <v>208</v>
-      </c>
-      <c r="P33" s="143"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B34" s="149"/>
-      <c r="C34" s="150"/>
-      <c r="D34" s="181"/>
-      <c r="E34" s="152" t="s">
+      <c r="O35" s="141" t="s">
+        <v>211</v>
+      </c>
+      <c r="P35" s="143"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="B36" s="149"/>
+      <c r="C36" s="150"/>
+      <c r="D36" s="183"/>
+      <c r="E36" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="182"/>
-      <c r="G34" s="183"/>
-      <c r="H34" s="184"/>
-      <c r="I34" s="182"/>
-      <c r="J34" s="152"/>
-      <c r="K34" s="155"/>
-      <c r="L34" s="156" t="s">
-        <v>209</v>
-      </c>
-      <c r="M34" s="156" t="s">
+      <c r="F36" s="184"/>
+      <c r="G36" s="185"/>
+      <c r="H36" s="186"/>
+      <c r="I36" s="184"/>
+      <c r="J36" s="152"/>
+      <c r="K36" s="155"/>
+      <c r="L36" s="156" t="s">
+        <v>212</v>
+      </c>
+      <c r="M36" s="156" t="s">
         <v>120</v>
       </c>
-      <c r="N34" s="155" t="s">
+      <c r="N36" s="155" t="s">
         <v>160</v>
       </c>
-      <c r="O34" s="155" t="s">
-        <v>210</v>
-      </c>
-      <c r="P34" s="157"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="193"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="195"/>
-      <c r="E35" s="195"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="196"/>
-      <c r="I35" s="196"/>
-      <c r="J35" s="195"/>
-      <c r="K35" s="195"/>
-      <c r="L35" s="193"/>
-      <c r="M35" s="193"/>
-      <c r="N35" s="193"/>
-      <c r="O35" s="195"/>
-      <c r="P35" s="195"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="142"/>
-      <c r="S35" s="142"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="197" t="s">
+      <c r="O36" s="155" t="s">
+        <v>213</v>
+      </c>
+      <c r="P36" s="157"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="194"/>
+      <c r="C37" s="195"/>
+      <c r="D37" s="196"/>
+      <c r="E37" s="196"/>
+      <c r="F37" s="197"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="197"/>
+      <c r="I37" s="197"/>
+      <c r="J37" s="196"/>
+      <c r="K37" s="196"/>
+      <c r="L37" s="194"/>
+      <c r="M37" s="194"/>
+      <c r="N37" s="194"/>
+      <c r="O37" s="196"/>
+      <c r="P37" s="196"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="142"/>
+      <c r="S37" s="142"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="198" t="s">
         <v>156</v>
       </c>
-      <c r="C36" s="198"/>
-      <c r="D36" s="138"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="197"/>
-      <c r="M36" s="197"/>
-      <c r="N36" s="197"/>
-      <c r="O36" s="119"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
-      <c r="S36" s="142"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="142" t="s">
+      <c r="C38" s="199"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="198"/>
+      <c r="M38" s="198"/>
+      <c r="N38" s="198"/>
+      <c r="O38" s="119"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="142"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="142" t="s">
+      <c r="C39" s="142" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="142" t="s">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="142" t="s">
+      <c r="C40" s="142" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="199" t="s">
-        <v>213</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="200" t="s">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="201" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="201"/>
-      <c r="E41" s="201"/>
-      <c r="F41" s="202"/>
-      <c r="G41" s="202"/>
-      <c r="H41" s="201" t="s">
-        <v>168</v>
-      </c>
-      <c r="I41" s="202" t="s">
-        <v>167</v>
-      </c>
-      <c r="J41" s="202" t="s">
+      <c r="D43" s="202" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="202"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
+      <c r="H43" s="202"/>
+      <c r="I43" s="203" t="s">
+        <v>201</v>
+      </c>
+      <c r="J43" s="203" t="s">
         <v>162</v>
       </c>
-      <c r="K41" s="202" t="s">
+      <c r="K43" s="203" t="s">
         <v>158</v>
       </c>
-      <c r="L41" s="200" t="s">
-        <v>214</v>
-      </c>
-      <c r="M41" s="203" t="s">
-        <v>215</v>
-      </c>
-      <c r="N41" s="199" t="s">
-        <v>216</v>
-      </c>
-      <c r="O41" s="200"/>
-      <c r="P41" s="199"/>
-      <c r="Q41" s="199"/>
-      <c r="R41" s="199"/>
-      <c r="S41" s="199"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="204"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="2" t="str">
-        <f aca="false">DEC2HEX(L42,2)</f>
-        <v>08</v>
-      </c>
-      <c r="D42" s="205"/>
-      <c r="E42" s="206"/>
-      <c r="F42" s="206"/>
-      <c r="G42" s="207"/>
-      <c r="H42" s="208" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="206"/>
-      <c r="J42" s="206" t="s">
-        <v>69</v>
-      </c>
-      <c r="K42" s="209" t="s">
-        <v>69</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <f aca="false">IF(D42=1,128,0)+IF(E42=1,64,0)+IF(F42=1,32,0)+IF(G42=1,16,0)+IF(H42=1,8,0)+IF(I42=1,4,0)+IF(J42=1,2,0)+IF(K42=1,1,0)</f>
-        <v>8</v>
-      </c>
-      <c r="M42" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="N42" s="11" t="s">
+      <c r="L43" s="201" t="s">
         <v>217</v>
       </c>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="11"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="204"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="2" t="str">
-        <f aca="false">DEC2HEX(L43,2)</f>
-        <v>04</v>
-      </c>
-      <c r="D43" s="210"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="186" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="211"/>
-      <c r="I43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="K43" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <f aca="false">IF(D43=1,128,0)+IF(E43=1,64,0)+IF(F43=1,32,0)+IF(G43=1,16,0)+IF(H43=1,8,0)+IF(I43=1,4,0)+IF(J43=1,2,0)+IF(K43=1,1,0)</f>
-        <v>4</v>
-      </c>
-      <c r="M43" s="10" t="s">
+      <c r="M43" s="204" t="s">
         <v>218</v>
       </c>
-      <c r="N43" s="11" t="s">
+      <c r="N43" s="200" t="s">
         <v>219</v>
       </c>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
+      <c r="O43" s="201"/>
+      <c r="P43" s="200"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="200"/>
+      <c r="S43" s="200"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="204"/>
+      <c r="A44" s="205"/>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="str">
         <f aca="false">DEC2HEX(L44,2)</f>
-        <v>14</v>
-      </c>
-      <c r="D44" s="210"/>
-      <c r="E44" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="196"/>
+      <c r="F44" s="196"/>
+      <c r="G44" s="207"/>
+      <c r="H44" s="208"/>
+      <c r="I44" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="J44" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="G44" s="186" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="211"/>
-      <c r="I44" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="13" t="s">
+      <c r="K44" s="209" t="s">
         <v>69</v>
       </c>
-      <c r="K44" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="L44" s="2" t="n">
+      <c r="L44" s="12" t="n">
         <f aca="false">IF(D44=1,128,0)+IF(E44=1,64,0)+IF(F44=1,32,0)+IF(G44=1,16,0)+IF(H44=1,8,0)+IF(I44=1,4,0)+IF(J44=1,2,0)+IF(K44=1,1,0)</f>
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="M44" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="N44" s="11" t="s">
         <v>220</v>
-      </c>
-      <c r="N44" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
@@ -7899,39 +8061,39 @@
       <c r="S44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="204"/>
+      <c r="A45" s="205"/>
       <c r="B45" s="1"/>
       <c r="C45" s="2" t="str">
         <f aca="false">DEC2HEX(L45,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D45" s="210"/>
+        <v>04</v>
+      </c>
+      <c r="D45" s="137" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="13"/>
-      <c r="F45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="186" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="211"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="148"/>
       <c r="I45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K45" s="141" t="s">
+      <c r="K45" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="L45" s="2" t="n">
+      <c r="L45" s="12" t="n">
         <f aca="false">IF(D45=1,128,0)+IF(E45=1,64,0)+IF(F45=1,32,0)+IF(G45=1,16,0)+IF(H45=1,8,0)+IF(I45=1,4,0)+IF(J45=1,2,0)+IF(K45=1,1,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M45" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="N45" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="N45" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
@@ -7939,82 +8101,83 @@
       <c r="S45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="204"/>
+      <c r="A46" s="205"/>
       <c r="B46" s="1"/>
       <c r="C46" s="2" t="str">
         <f aca="false">DEC2HEX(L46,2)</f>
-        <v>10</v>
-      </c>
-      <c r="D46" s="210"/>
+        <v>14</v>
+      </c>
+      <c r="D46" s="137" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="186" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="211"/>
+      <c r="F46" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="148"/>
       <c r="I46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K46" s="141" t="s">
+      <c r="K46" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="L46" s="2" t="n">
+      <c r="L46" s="12" t="n">
         <f aca="false">IF(D46=1,128,0)+IF(E46=1,64,0)+IF(F46=1,32,0)+IF(G46=1,16,0)+IF(H46=1,8,0)+IF(I46=1,4,0)+IF(J46=1,2,0)+IF(K46=1,1,0)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="N46" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="O46" s="1"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
       <c r="S46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="204"/>
+      <c r="A47" s="205"/>
       <c r="B47" s="1"/>
       <c r="C47" s="2" t="str">
         <f aca="false">DEC2HEX(L47,2)</f>
-        <v>20</v>
-      </c>
-      <c r="D47" s="210"/>
+        <v>00</v>
+      </c>
+      <c r="D47" s="137"/>
       <c r="E47" s="13"/>
       <c r="F47" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="186" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="211"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="148"/>
       <c r="I47" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K47" s="141" t="s">
+      <c r="K47" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="L47" s="2" t="n">
+      <c r="L47" s="12" t="n">
         <f aca="false">IF(D47=1,128,0)+IF(E47=1,64,0)+IF(F47=1,32,0)+IF(G47=1,16,0)+IF(H47=1,8,0)+IF(I47=1,4,0)+IF(J47=1,2,0)+IF(K47=1,1,0)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
@@ -8022,53 +8185,136 @@
       <c r="S47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="204"/>
+      <c r="A48" s="205"/>
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="str">
         <f aca="false">DEC2HEX(L48,2)</f>
-        <v>31</v>
-      </c>
-      <c r="D48" s="212"/>
-      <c r="E48" s="152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="137"/>
+      <c r="E48" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F48" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="154"/>
-      <c r="I48" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="152" t="s">
+      <c r="F48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="148"/>
+      <c r="I48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K48" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="2" t="n">
+      <c r="K48" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="L48" s="12" t="n">
         <f aca="false">IF(D48=1,128,0)+IF(E48=1,64,0)+IF(F48=1,32,0)+IF(G48=1,16,0)+IF(H48=1,8,0)+IF(I48=1,4,0)+IF(J48=1,2,0)+IF(K48=1,1,0)</f>
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>226</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O48" s="1"/>
       <c r="P48" s="11"/>
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
       <c r="S48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A49" s="205"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="2" t="str">
+        <f aca="false">DEC2HEX(L49,2)</f>
+        <v>20</v>
+      </c>
+      <c r="D49" s="137"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="148"/>
+      <c r="I49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K49" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <f aca="false">IF(D49=1,128,0)+IF(E49=1,64,0)+IF(F49=1,32,0)+IF(G49=1,16,0)+IF(H49=1,8,0)+IF(I49=1,4,0)+IF(J49=1,2,0)+IF(K49=1,1,0)</f>
+        <v>32</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N49" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="205"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="2" t="str">
+        <f aca="false">DEC2HEX(L50,2)</f>
+        <v>31</v>
+      </c>
+      <c r="D50" s="183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="210" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="154"/>
+      <c r="I50" s="210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="210" t="s">
+        <v>69</v>
+      </c>
+      <c r="K50" s="212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <f aca="false">IF(D50=1,128,0)+IF(E50=1,64,0)+IF(F50=1,32,0)+IF(G50=1,16,0)+IF(H50=1,8,0)+IF(I50=1,4,0)+IF(J50=1,2,0)+IF(K50=1,1,0)</f>
+        <v>49</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+    </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -8106,8 +8352,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="214"/>
-      <c r="B1" s="215" t="s">
+      <c r="A1" s="213"/>
+      <c r="B1" s="214" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="17" t="s">
@@ -8119,10 +8365,10 @@
       <c r="E1" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="216" t="n">
+      <c r="F1" s="215" t="n">
         <v>6</v>
       </c>
-      <c r="G1" s="216" t="n">
+      <c r="G1" s="215" t="n">
         <v>5</v>
       </c>
       <c r="H1" s="27" t="n">
@@ -8131,34 +8377,34 @@
       <c r="I1" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J1" s="216" t="n">
+      <c r="J1" s="215" t="n">
         <v>2</v>
       </c>
-      <c r="K1" s="216" t="n">
+      <c r="K1" s="215" t="n">
         <v>1</v>
       </c>
       <c r="L1" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M1" s="217" t="s">
+      <c r="M1" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="217" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="218" t="s">
+      <c r="N1" s="216" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="217" t="s">
         <v>155</v>
       </c>
-      <c r="P1" s="219" t="s">
+      <c r="P1" s="218" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="220" t="s">
-        <v>227</v>
-      </c>
-      <c r="B2" s="221"/>
-      <c r="C2" s="222" t="str">
+      <c r="A2" s="219" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="220"/>
+      <c r="C2" s="221" t="str">
         <f aca="false">DEC2HEX(D2,2)</f>
         <v>00</v>
       </c>
@@ -8166,11 +8412,11 @@
         <f aca="false">IF(E2=1,128,0)+IF(F2=1,64,0)+IF(G2=1,32,0)+IF(H2=1,16,0)+IF(I2=1,8,0)+IF(J2=1,4,0)+IF(K2=1,2,0)+IF(L2=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E2" s="190"/>
+      <c r="E2" s="191"/>
       <c r="F2" s="173"/>
       <c r="G2" s="173"/>
       <c r="H2" s="177"/>
-      <c r="I2" s="190" t="n">
+      <c r="I2" s="191" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="173" t="n">
@@ -8182,45 +8428,45 @@
       <c r="L2" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="223" t="s">
-        <v>228</v>
-      </c>
-      <c r="N2" s="221"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="225"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="226"/>
+      <c r="M2" s="222" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" s="220"/>
+      <c r="O2" s="223"/>
+      <c r="P2" s="224"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A3" s="225"/>
       <c r="B3" s="142"/>
       <c r="C3" s="17"/>
       <c r="D3" s="119"/>
       <c r="E3" s="49"/>
       <c r="F3" s="119"/>
       <c r="G3" s="119" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="13"/>
       <c r="K3" s="119"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="227"/>
-      <c r="N3" s="227" t="s">
-        <v>230</v>
-      </c>
-      <c r="O3" s="228" t="s">
-        <v>231</v>
-      </c>
-      <c r="P3" s="229"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="226" t="s">
+        <v>233</v>
+      </c>
+      <c r="O3" s="227" t="s">
+        <v>234</v>
+      </c>
+      <c r="P3" s="228"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A4" s="225"/>
       <c r="B4" s="142"/>
       <c r="E4" s="49"/>
       <c r="F4" s="119" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G4" s="119"/>
       <c r="H4" s="50"/>
@@ -8228,15 +8474,15 @@
       <c r="J4" s="13"/>
       <c r="K4" s="119"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="227" t="s">
-        <v>233</v>
+      <c r="M4" s="226" t="s">
+        <v>236</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
-      <c r="P4" s="230"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="226"/>
+      <c r="P4" s="229"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A5" s="225"/>
       <c r="B5" s="142"/>
       <c r="C5" s="17"/>
       <c r="D5" s="119"/>
@@ -8248,14 +8494,14 @@
       <c r="J5" s="13"/>
       <c r="K5" s="119"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="227"/>
-      <c r="O5" s="228"/>
-      <c r="P5" s="229"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A6" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="O5" s="227"/>
+      <c r="P5" s="228"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A6" s="225"/>
       <c r="B6" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="119"/>
@@ -8265,21 +8511,21 @@
       <c r="J6" s="13"/>
       <c r="K6" s="119"/>
       <c r="L6" s="50"/>
-      <c r="M6" s="227"/>
+      <c r="M6" s="226"/>
       <c r="N6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="P6" s="230"/>
+        <v>238</v>
+      </c>
+      <c r="P6" s="229"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="220" t="s">
-        <v>236</v>
-      </c>
-      <c r="B7" s="221"/>
-      <c r="C7" s="222" t="str">
+      <c r="A7" s="219" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="220"/>
+      <c r="C7" s="221" t="str">
         <f aca="false">DEC2HEX(D7,2)</f>
         <v>01</v>
       </c>
@@ -8287,11 +8533,11 @@
         <f aca="false">IF(E7=1,128,0)+IF(F7=1,64,0)+IF(G7=1,32,0)+IF(H7=1,16,0)+IF(I7=1,8,0)+IF(J7=1,4,0)+IF(K7=1,2,0)+IF(L7=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="190"/>
+      <c r="E7" s="191"/>
       <c r="F7" s="173"/>
       <c r="G7" s="173"/>
       <c r="H7" s="177"/>
-      <c r="I7" s="190" t="n">
+      <c r="I7" s="191" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="173" t="n">
@@ -8303,43 +8549,43 @@
       <c r="L7" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="223" t="s">
-        <v>237</v>
-      </c>
-      <c r="N7" s="221"/>
-      <c r="O7" s="223"/>
-      <c r="P7" s="225"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="226"/>
+      <c r="M7" s="222" t="s">
+        <v>240</v>
+      </c>
+      <c r="N7" s="220"/>
+      <c r="O7" s="222"/>
+      <c r="P7" s="224"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A8" s="225"/>
       <c r="B8" s="142"/>
       <c r="C8" s="17"/>
       <c r="D8" s="119"/>
       <c r="E8" s="49"/>
       <c r="F8" s="119"/>
       <c r="G8" s="119" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I8" s="49"/>
       <c r="J8" s="13"/>
       <c r="K8" s="119"/>
       <c r="L8" s="50"/>
-      <c r="M8" s="227"/>
+      <c r="M8" s="226"/>
       <c r="N8" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O8" s="228" t="s">
-        <v>231</v>
-      </c>
-      <c r="P8" s="229" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="226"/>
+        <v>233</v>
+      </c>
+      <c r="O8" s="227" t="s">
+        <v>234</v>
+      </c>
+      <c r="P8" s="228" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A9" s="225"/>
       <c r="B9" s="142"/>
       <c r="C9" s="17"/>
       <c r="D9" s="119"/>
@@ -8351,14 +8597,14 @@
       <c r="J9" s="13"/>
       <c r="K9" s="119"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="227"/>
-      <c r="O9" s="228"/>
-      <c r="P9" s="229"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="O9" s="227"/>
+      <c r="P9" s="228"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A10" s="225"/>
       <c r="B10" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E10" s="146"/>
       <c r="F10" s="119"/>
@@ -8373,16 +8619,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="P10" s="230"/>
+        <v>238</v>
+      </c>
+      <c r="P10" s="229"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="220" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="221"/>
-      <c r="C11" s="222" t="str">
+      <c r="A11" s="219" t="s">
+        <v>242</v>
+      </c>
+      <c r="B11" s="220"/>
+      <c r="C11" s="221" t="str">
         <f aca="false">DEC2HEX(D11,2)</f>
         <v>02</v>
       </c>
@@ -8390,7 +8636,7 @@
         <f aca="false">IF(E11=1,128,0)+IF(F11=1,64,0)+IF(G11=1,32,0)+IF(H11=1,16,0)+IF(I11=1,8,0)+IF(J11=1,4,0)+IF(K11=1,2,0)+IF(L11=1,1,0)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="190"/>
+      <c r="E11" s="191"/>
       <c r="F11" s="173"/>
       <c r="G11" s="173"/>
       <c r="H11" s="177"/>
@@ -8406,43 +8652,43 @@
       <c r="L11" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="223" t="s">
-        <v>240</v>
-      </c>
-      <c r="N11" s="221"/>
-      <c r="O11" s="224"/>
-      <c r="P11" s="225"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A12" s="226"/>
+      <c r="M11" s="222" t="s">
+        <v>243</v>
+      </c>
+      <c r="N11" s="220"/>
+      <c r="O11" s="223"/>
+      <c r="P11" s="224"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A12" s="225"/>
       <c r="B12" s="142"/>
       <c r="C12" s="17"/>
       <c r="D12" s="119"/>
       <c r="E12" s="49"/>
       <c r="F12" s="119"/>
       <c r="G12" s="119" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I12" s="49"/>
       <c r="J12" s="13"/>
       <c r="K12" s="119"/>
       <c r="L12" s="50"/>
-      <c r="M12" s="227"/>
-      <c r="N12" s="227" t="s">
-        <v>241</v>
-      </c>
-      <c r="O12" s="228" t="s">
-        <v>231</v>
-      </c>
-      <c r="P12" s="231" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="226" t="s">
+        <v>244</v>
+      </c>
+      <c r="O12" s="227" t="s">
+        <v>234</v>
+      </c>
+      <c r="P12" s="230" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A13" s="225"/>
       <c r="B13" s="142"/>
       <c r="C13" s="17"/>
       <c r="D13" s="119"/>
@@ -8454,14 +8700,14 @@
       <c r="J13" s="13"/>
       <c r="K13" s="119"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="227"/>
-      <c r="O13" s="228"/>
-      <c r="P13" s="229"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="226"/>
+      <c r="M13" s="226"/>
+      <c r="O13" s="227"/>
+      <c r="P13" s="228"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A14" s="225"/>
       <c r="B14" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="119"/>
@@ -8471,23 +8717,23 @@
       <c r="J14" s="13"/>
       <c r="K14" s="119"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="227"/>
+      <c r="M14" s="226"/>
       <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="P14" s="230" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="P14" s="229" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="220" t="s">
-        <v>245</v>
-      </c>
-      <c r="B15" s="221"/>
-      <c r="C15" s="222" t="str">
+      <c r="A15" s="219" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" s="220"/>
+      <c r="C15" s="221" t="str">
         <f aca="false">DEC2HEX(D15,2)</f>
         <v>03</v>
       </c>
@@ -8495,7 +8741,7 @@
         <f aca="false">IF(E15=1,128,0)+IF(F15=1,64,0)+IF(G15=1,32,0)+IF(H15=1,16,0)+IF(I15=1,8,0)+IF(J15=1,4,0)+IF(K15=1,2,0)+IF(L15=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="E15" s="190"/>
+      <c r="E15" s="191"/>
       <c r="F15" s="173"/>
       <c r="G15" s="173"/>
       <c r="H15" s="177"/>
@@ -8511,15 +8757,15 @@
       <c r="L15" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="223" t="s">
+      <c r="M15" s="222" t="s">
         <v>99</v>
       </c>
-      <c r="N15" s="221"/>
-      <c r="O15" s="223"/>
-      <c r="P15" s="225"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A16" s="226"/>
+      <c r="N15" s="220"/>
+      <c r="O15" s="222"/>
+      <c r="P15" s="224"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A16" s="225"/>
       <c r="B16" s="142"/>
       <c r="C16" s="17"/>
       <c r="D16" s="119"/>
@@ -8531,14 +8777,14 @@
       <c r="J16" s="13"/>
       <c r="K16" s="119"/>
       <c r="L16" s="50"/>
-      <c r="M16" s="227"/>
-      <c r="O16" s="228"/>
-      <c r="P16" s="229"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A17" s="226"/>
+      <c r="M16" s="226"/>
+      <c r="O16" s="227"/>
+      <c r="P16" s="228"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A17" s="225"/>
       <c r="B17" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="119"/>
@@ -8550,21 +8796,21 @@
       <c r="J17" s="13"/>
       <c r="K17" s="119"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="227"/>
+      <c r="M17" s="226"/>
       <c r="N17" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="O17" s="228" t="s">
-        <v>247</v>
-      </c>
-      <c r="P17" s="229" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="226"/>
+        <v>249</v>
+      </c>
+      <c r="O17" s="227" t="s">
+        <v>250</v>
+      </c>
+      <c r="P17" s="228" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A18" s="225"/>
       <c r="B18" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E18" s="146"/>
       <c r="F18" s="119"/>
@@ -8579,18 +8825,18 @@
         <v>1</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="P18" s="232" t="s">
-        <v>250</v>
+        <v>252</v>
+      </c>
+      <c r="P18" s="231" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="220" t="s">
-        <v>251</v>
-      </c>
-      <c r="B19" s="221"/>
-      <c r="C19" s="222" t="str">
+      <c r="A19" s="219" t="s">
+        <v>254</v>
+      </c>
+      <c r="B19" s="220"/>
+      <c r="C19" s="221" t="str">
         <f aca="false">DEC2HEX(D19,2)</f>
         <v>04</v>
       </c>
@@ -8598,7 +8844,7 @@
         <f aca="false">IF(E19=1,128,0)+IF(F19=1,64,0)+IF(G19=1,32,0)+IF(H19=1,16,0)+IF(I19=1,8,0)+IF(J19=1,4,0)+IF(K19=1,2,0)+IF(L19=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E19" s="190"/>
+      <c r="E19" s="191"/>
       <c r="F19" s="173"/>
       <c r="G19" s="173"/>
       <c r="H19" s="177"/>
@@ -8614,23 +8860,25 @@
       <c r="L19" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="223" t="s">
-        <v>252</v>
-      </c>
-      <c r="N19" s="221"/>
-      <c r="O19" s="223"/>
-      <c r="P19" s="225"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="226"/>
+      <c r="M19" s="222" t="s">
+        <v>255</v>
+      </c>
+      <c r="N19" s="220"/>
+      <c r="O19" s="222"/>
+      <c r="P19" s="224"/>
+    </row>
+    <row r="20" s="232" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A20" s="225"/>
       <c r="B20" s="142"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="2"/>
       <c r="E20" s="146"/>
       <c r="F20" s="119"/>
       <c r="G20" s="119" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I20" s="119"/>
       <c r="J20" s="119"/>
@@ -8638,21 +8886,19 @@
       <c r="L20" s="50"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="P20" s="229"/>
-    </row>
-    <row r="21" s="233" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="226"/>
+        <v>234</v>
+      </c>
+      <c r="P20" s="228"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A21" s="225"/>
       <c r="B21" s="142"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="2"/>
       <c r="E21" s="146"/>
       <c r="F21" s="119" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G21" s="119"/>
       <c r="H21" s="50"/>
@@ -8661,16 +8907,16 @@
       <c r="K21" s="119"/>
       <c r="L21" s="50"/>
       <c r="M21" s="10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="142"/>
-      <c r="P21" s="229" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="226"/>
+      <c r="P21" s="228" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A22" s="225"/>
       <c r="B22" s="142"/>
       <c r="E22" s="146"/>
       <c r="F22" s="119"/>
@@ -8682,41 +8928,41 @@
       <c r="L22" s="50"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O22" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="P22" s="229"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="234"/>
-      <c r="B23" s="235"/>
-      <c r="C23" s="236"/>
-      <c r="D23" s="237"/>
-      <c r="E23" s="238" t="s">
-        <v>256</v>
-      </c>
-      <c r="F23" s="237"/>
-      <c r="G23" s="237"/>
-      <c r="H23" s="239"/>
-      <c r="I23" s="238"/>
-      <c r="J23" s="240"/>
-      <c r="K23" s="237"/>
-      <c r="L23" s="239"/>
-      <c r="M23" s="241" t="s">
-        <v>257</v>
-      </c>
-      <c r="N23" s="233"/>
-      <c r="O23" s="242"/>
-      <c r="P23" s="243" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="226"/>
+      <c r="P22" s="228"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A23" s="233"/>
+      <c r="B23" s="234"/>
+      <c r="C23" s="235"/>
+      <c r="D23" s="236"/>
+      <c r="E23" s="237" t="s">
+        <v>259</v>
+      </c>
+      <c r="F23" s="236"/>
+      <c r="G23" s="236"/>
+      <c r="H23" s="238"/>
+      <c r="I23" s="237"/>
+      <c r="J23" s="239"/>
+      <c r="K23" s="236"/>
+      <c r="L23" s="238"/>
+      <c r="M23" s="240" t="s">
+        <v>260</v>
+      </c>
+      <c r="N23" s="232"/>
+      <c r="O23" s="241"/>
+      <c r="P23" s="242" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A24" s="225"/>
       <c r="B24" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E24" s="146"/>
       <c r="F24" s="119"/>
@@ -8729,18 +8975,18 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="P24" s="229" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="P24" s="228" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="220" t="s">
-        <v>261</v>
-      </c>
-      <c r="B25" s="221"/>
-      <c r="C25" s="222" t="str">
+      <c r="A25" s="219" t="s">
+        <v>264</v>
+      </c>
+      <c r="B25" s="220"/>
+      <c r="C25" s="221" t="str">
         <f aca="false">DEC2HEX(D25,2)</f>
         <v>05</v>
       </c>
@@ -8748,7 +8994,7 @@
         <f aca="false">IF(E25=1,128,0)+IF(F25=1,64,0)+IF(G25=1,32,0)+IF(H25=1,16,0)+IF(I25=1,8,0)+IF(J25=1,4,0)+IF(K25=1,2,0)+IF(L25=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E25" s="190"/>
+      <c r="E25" s="191"/>
       <c r="F25" s="173"/>
       <c r="G25" s="173"/>
       <c r="H25" s="177"/>
@@ -8764,19 +9010,19 @@
       <c r="L25" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M25" s="223" t="s">
-        <v>262</v>
-      </c>
-      <c r="N25" s="221"/>
-      <c r="O25" s="223"/>
-      <c r="P25" s="225"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="226"/>
+      <c r="M25" s="222" t="s">
+        <v>265</v>
+      </c>
+      <c r="N25" s="220"/>
+      <c r="O25" s="222"/>
+      <c r="P25" s="224"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A26" s="225"/>
       <c r="B26" s="142"/>
       <c r="E26" s="146"/>
       <c r="F26" s="119" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G26" s="119"/>
       <c r="H26" s="50"/>
@@ -8785,16 +9031,16 @@
       <c r="K26" s="119"/>
       <c r="L26" s="50"/>
       <c r="M26" s="10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="142"/>
-      <c r="P26" s="229" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="226"/>
+      <c r="P26" s="228" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A27" s="225"/>
       <c r="B27" s="142"/>
       <c r="E27" s="146"/>
       <c r="F27" s="119"/>
@@ -8806,15 +9052,15 @@
       <c r="L27" s="50"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O27" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="P27" s="229"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="226"/>
+      <c r="P27" s="228"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A28" s="225"/>
       <c r="B28" s="142"/>
       <c r="C28" s="17"/>
       <c r="D28" s="119"/>
@@ -8826,13 +9072,13 @@
       <c r="J28" s="13"/>
       <c r="K28" s="119"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="227"/>
-      <c r="O28" s="228"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="226"/>
+      <c r="M28" s="226"/>
+      <c r="O28" s="227"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A29" s="225"/>
       <c r="B29" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="119"/>
@@ -8844,21 +9090,21 @@
       <c r="J29" s="13"/>
       <c r="K29" s="119"/>
       <c r="L29" s="50"/>
-      <c r="M29" s="227"/>
+      <c r="M29" s="226"/>
       <c r="N29" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="O29" s="228" t="s">
-        <v>247</v>
-      </c>
-      <c r="P29" s="229" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A30" s="226"/>
+        <v>249</v>
+      </c>
+      <c r="O29" s="227" t="s">
+        <v>250</v>
+      </c>
+      <c r="P29" s="228" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A30" s="225"/>
       <c r="B30" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E30" s="146"/>
       <c r="F30" s="119"/>
@@ -8873,18 +9119,18 @@
         <v>1</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="P30" s="232" t="s">
-        <v>250</v>
+        <v>252</v>
+      </c>
+      <c r="P30" s="231" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="220" t="s">
-        <v>264</v>
-      </c>
-      <c r="B31" s="221"/>
-      <c r="C31" s="222" t="str">
+      <c r="A31" s="219" t="s">
+        <v>267</v>
+      </c>
+      <c r="B31" s="220"/>
+      <c r="C31" s="221" t="str">
         <f aca="false">DEC2HEX(D31,2)</f>
         <v>06</v>
       </c>
@@ -8892,7 +9138,7 @@
         <f aca="false">IF(E31=1,128,0)+IF(F31=1,64,0)+IF(G31=1,32,0)+IF(H31=1,16,0)+IF(I31=1,8,0)+IF(J31=1,4,0)+IF(K31=1,2,0)+IF(L31=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="E31" s="190"/>
+      <c r="E31" s="191"/>
       <c r="F31" s="173"/>
       <c r="G31" s="173"/>
       <c r="H31" s="177"/>
@@ -8908,17 +9154,17 @@
       <c r="L31" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="223" t="s">
-        <v>265</v>
-      </c>
-      <c r="N31" s="221"/>
-      <c r="O31" s="223"/>
-      <c r="P31" s="244" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A32" s="226"/>
+      <c r="M31" s="222" t="s">
+        <v>268</v>
+      </c>
+      <c r="N31" s="220"/>
+      <c r="O31" s="222"/>
+      <c r="P31" s="243" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A32" s="225"/>
       <c r="E32" s="146"/>
       <c r="F32" s="119"/>
       <c r="G32" s="119" t="n">
@@ -8932,12 +9178,12 @@
       <c r="K32" s="119"/>
       <c r="L32" s="50"/>
       <c r="M32" s="142" t="s">
-        <v>267</v>
-      </c>
-      <c r="P32" s="229"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="226"/>
+        <v>270</v>
+      </c>
+      <c r="P32" s="228"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A33" s="225"/>
       <c r="E33" s="146"/>
       <c r="F33" s="119"/>
       <c r="G33" s="119" t="n">
@@ -8950,13 +9196,13 @@
       <c r="J33" s="119"/>
       <c r="K33" s="119"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="227" t="s">
-        <v>268</v>
-      </c>
-      <c r="P33" s="229"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="226"/>
+      <c r="M33" s="226" t="s">
+        <v>271</v>
+      </c>
+      <c r="P33" s="228"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A34" s="225"/>
       <c r="E34" s="146"/>
       <c r="F34" s="119"/>
       <c r="G34" s="119" t="n">
@@ -8969,13 +9215,13 @@
       <c r="J34" s="119"/>
       <c r="K34" s="119"/>
       <c r="L34" s="50"/>
-      <c r="M34" s="227" t="s">
-        <v>269</v>
-      </c>
-      <c r="P34" s="229"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="226"/>
+      <c r="M34" s="226" t="s">
+        <v>272</v>
+      </c>
+      <c r="P34" s="228"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A35" s="225"/>
       <c r="E35" s="146"/>
       <c r="F35" s="119"/>
       <c r="G35" s="119" t="n">
@@ -8989,15 +9235,15 @@
       <c r="K35" s="119"/>
       <c r="L35" s="50"/>
       <c r="M35" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="P35" s="229"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="226"/>
+        <v>273</v>
+      </c>
+      <c r="P35" s="228"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A36" s="225"/>
       <c r="E36" s="146"/>
       <c r="F36" s="119" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G36" s="119"/>
       <c r="H36" s="50"/>
@@ -9006,14 +9252,14 @@
       <c r="K36" s="119"/>
       <c r="L36" s="50"/>
       <c r="M36" s="142" t="s">
-        <v>272</v>
-      </c>
-      <c r="P36" s="229" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="226"/>
+        <v>275</v>
+      </c>
+      <c r="P36" s="228" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A37" s="225"/>
       <c r="B37" s="142"/>
       <c r="C37" s="17"/>
       <c r="D37" s="119"/>
@@ -9025,14 +9271,14 @@
       <c r="J37" s="13"/>
       <c r="K37" s="119"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="227"/>
-      <c r="O37" s="228"/>
-      <c r="P37" s="229"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A38" s="226"/>
+      <c r="M37" s="226"/>
+      <c r="O37" s="227"/>
+      <c r="P37" s="228"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A38" s="225"/>
       <c r="B38" s="142" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E38" s="146"/>
       <c r="F38" s="119"/>
@@ -9044,18 +9290,18 @@
       <c r="L38" s="50"/>
       <c r="M38" s="142"/>
       <c r="O38" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="P38" s="229" t="s">
-        <v>275</v>
+        <v>277</v>
+      </c>
+      <c r="P38" s="228" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="220" t="s">
-        <v>276</v>
-      </c>
-      <c r="B39" s="221"/>
-      <c r="C39" s="222" t="str">
+      <c r="A39" s="219" t="s">
+        <v>279</v>
+      </c>
+      <c r="B39" s="220"/>
+      <c r="C39" s="221" t="str">
         <f aca="false">DEC2HEX(D39,2)</f>
         <v>07</v>
       </c>
@@ -9063,7 +9309,7 @@
         <f aca="false">IF(E39=1,128,0)+IF(F39=1,64,0)+IF(G39=1,32,0)+IF(H39=1,16,0)+IF(I39=1,8,0)+IF(J39=1,4,0)+IF(K39=1,2,0)+IF(L39=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="E39" s="190"/>
+      <c r="E39" s="191"/>
       <c r="F39" s="173"/>
       <c r="G39" s="173"/>
       <c r="H39" s="177"/>
@@ -9079,15 +9325,15 @@
       <c r="L39" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M39" s="223" t="s">
-        <v>277</v>
-      </c>
-      <c r="N39" s="221"/>
-      <c r="O39" s="223"/>
-      <c r="P39" s="225"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="226"/>
+      <c r="M39" s="222" t="s">
+        <v>280</v>
+      </c>
+      <c r="N39" s="220"/>
+      <c r="O39" s="222"/>
+      <c r="P39" s="224"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A40" s="225"/>
       <c r="E40" s="146"/>
       <c r="F40" s="119"/>
       <c r="G40" s="119" t="n">
@@ -9101,14 +9347,14 @@
       <c r="K40" s="119"/>
       <c r="L40" s="50"/>
       <c r="M40" s="142" t="s">
-        <v>278</v>
-      </c>
-      <c r="P40" s="231" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="226"/>
+        <v>281</v>
+      </c>
+      <c r="P40" s="230" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A41" s="225"/>
       <c r="E41" s="146"/>
       <c r="F41" s="119"/>
       <c r="G41" s="119" t="n">
@@ -9121,15 +9367,15 @@
       <c r="J41" s="119"/>
       <c r="K41" s="119"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="227" t="s">
-        <v>268</v>
-      </c>
-      <c r="P41" s="231" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="226"/>
+      <c r="M41" s="226" t="s">
+        <v>271</v>
+      </c>
+      <c r="P41" s="230" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A42" s="225"/>
       <c r="E42" s="146"/>
       <c r="F42" s="119"/>
       <c r="G42" s="119" t="n">
@@ -9142,15 +9388,15 @@
       <c r="J42" s="119"/>
       <c r="K42" s="119"/>
       <c r="L42" s="50"/>
-      <c r="M42" s="227" t="s">
-        <v>269</v>
-      </c>
-      <c r="P42" s="231" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="226"/>
+      <c r="M42" s="226" t="s">
+        <v>272</v>
+      </c>
+      <c r="P42" s="230" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A43" s="225"/>
       <c r="E43" s="146"/>
       <c r="F43" s="119"/>
       <c r="G43" s="119" t="n">
@@ -9164,14 +9410,14 @@
       <c r="K43" s="119"/>
       <c r="L43" s="50"/>
       <c r="M43" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="P43" s="231" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="226"/>
+        <v>273</v>
+      </c>
+      <c r="P43" s="230" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A44" s="225"/>
       <c r="E44" s="146"/>
       <c r="F44" s="119"/>
       <c r="G44" s="119"/>
@@ -9182,12 +9428,12 @@
       <c r="L44" s="50"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="245" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A45" s="226"/>
+      <c r="P44" s="244" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A45" s="225"/>
       <c r="E45" s="146"/>
       <c r="F45" s="119"/>
       <c r="G45" s="119"/>
@@ -9198,12 +9444,12 @@
       <c r="L45" s="50"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="245" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A46" s="226"/>
+      <c r="P45" s="244" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A46" s="225"/>
       <c r="E46" s="146"/>
       <c r="F46" s="119"/>
       <c r="G46" s="119"/>
@@ -9214,12 +9460,12 @@
       <c r="L46" s="50"/>
       <c r="M46" s="10"/>
       <c r="O46" s="1"/>
-      <c r="P46" s="245" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="226"/>
+      <c r="P46" s="244" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A47" s="225"/>
       <c r="B47" s="142"/>
       <c r="C47" s="17"/>
       <c r="D47" s="119"/>
@@ -9231,14 +9477,14 @@
       <c r="J47" s="13"/>
       <c r="K47" s="119"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="227"/>
-      <c r="O47" s="228"/>
-      <c r="P47" s="229"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="226"/>
-      <c r="B48" s="227" t="s">
-        <v>234</v>
+      <c r="M47" s="226"/>
+      <c r="O47" s="227"/>
+      <c r="P47" s="228"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A48" s="225"/>
+      <c r="B48" s="226" t="s">
+        <v>237</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="119"/>
@@ -9250,25 +9496,25 @@
       <c r="J48" s="13"/>
       <c r="K48" s="119"/>
       <c r="L48" s="50"/>
-      <c r="M48" s="227"/>
+      <c r="M48" s="226"/>
       <c r="N48" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="O48" s="228" t="s">
-        <v>287</v>
-      </c>
-      <c r="P48" s="229" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A49" s="246"/>
-      <c r="B49" s="227" t="s">
-        <v>234</v>
-      </c>
-      <c r="C49" s="247"/>
+        <v>289</v>
+      </c>
+      <c r="O48" s="227" t="s">
+        <v>290</v>
+      </c>
+      <c r="P48" s="228" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A49" s="245"/>
+      <c r="B49" s="226" t="s">
+        <v>237</v>
+      </c>
+      <c r="C49" s="246"/>
       <c r="D49" s="152"/>
-      <c r="E49" s="248"/>
+      <c r="E49" s="247"/>
       <c r="F49" s="152"/>
       <c r="G49" s="152"/>
       <c r="H49" s="155"/>
@@ -9276,21 +9522,21 @@
       <c r="J49" s="152"/>
       <c r="K49" s="152"/>
       <c r="L49" s="155"/>
-      <c r="M49" s="249"/>
+      <c r="M49" s="248"/>
       <c r="N49" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="P49" s="232" t="s">
-        <v>250</v>
+        <v>289</v>
+      </c>
+      <c r="P49" s="231" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="220"/>
-      <c r="B50" s="221"/>
-      <c r="C50" s="222" t="str">
+      <c r="A50" s="219"/>
+      <c r="B50" s="220"/>
+      <c r="C50" s="221" t="str">
         <f aca="false">DEC2HEX(D50,2)</f>
         <v>08</v>
       </c>
@@ -9298,7 +9544,7 @@
         <f aca="false">IF(E50=1,128,0)+IF(F50=1,64,0)+IF(G50=1,32,0)+IF(H50=1,16,0)+IF(I50=1,8,0)+IF(J50=1,4,0)+IF(K50=1,2,0)+IF(L50=1,1,0)</f>
         <v>8</v>
       </c>
-      <c r="E50" s="190"/>
+      <c r="E50" s="191"/>
       <c r="F50" s="173"/>
       <c r="G50" s="173"/>
       <c r="H50" s="177"/>
@@ -9314,13 +9560,13 @@
       <c r="L50" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="223"/>
-      <c r="N50" s="221"/>
-      <c r="O50" s="223"/>
-      <c r="P50" s="225"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="226"/>
+      <c r="M50" s="222"/>
+      <c r="N50" s="220"/>
+      <c r="O50" s="222"/>
+      <c r="P50" s="224"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A51" s="225"/>
       <c r="B51" s="142"/>
       <c r="C51" s="17"/>
       <c r="D51" s="119"/>
@@ -9332,14 +9578,14 @@
       <c r="J51" s="13"/>
       <c r="K51" s="119"/>
       <c r="L51" s="50"/>
-      <c r="M51" s="227"/>
-      <c r="O51" s="228"/>
-      <c r="P51" s="229"/>
+      <c r="M51" s="226"/>
+      <c r="O51" s="227"/>
+      <c r="P51" s="228"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="220"/>
-      <c r="B52" s="221"/>
-      <c r="C52" s="222" t="str">
+      <c r="A52" s="219"/>
+      <c r="B52" s="220"/>
+      <c r="C52" s="221" t="str">
         <f aca="false">DEC2HEX(D52,2)</f>
         <v>09</v>
       </c>
@@ -9347,7 +9593,7 @@
         <f aca="false">IF(E52=1,128,0)+IF(F52=1,64,0)+IF(G52=1,32,0)+IF(H52=1,16,0)+IF(I52=1,8,0)+IF(J52=1,4,0)+IF(K52=1,2,0)+IF(L52=1,1,0)</f>
         <v>9</v>
       </c>
-      <c r="E52" s="190"/>
+      <c r="E52" s="191"/>
       <c r="F52" s="173"/>
       <c r="G52" s="173"/>
       <c r="H52" s="177"/>
@@ -9363,13 +9609,13 @@
       <c r="L52" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M52" s="223"/>
-      <c r="N52" s="221"/>
-      <c r="O52" s="223"/>
-      <c r="P52" s="225"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="226"/>
+      <c r="M52" s="222"/>
+      <c r="N52" s="220"/>
+      <c r="O52" s="222"/>
+      <c r="P52" s="224"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A53" s="225"/>
       <c r="B53" s="142"/>
       <c r="C53" s="17"/>
       <c r="D53" s="119"/>
@@ -9381,16 +9627,16 @@
       <c r="J53" s="13"/>
       <c r="K53" s="119"/>
       <c r="L53" s="50"/>
-      <c r="M53" s="227"/>
-      <c r="O53" s="228"/>
-      <c r="P53" s="229"/>
+      <c r="M53" s="226"/>
+      <c r="O53" s="227"/>
+      <c r="P53" s="228"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="220" t="s">
-        <v>289</v>
-      </c>
-      <c r="B54" s="221"/>
-      <c r="C54" s="222" t="str">
+      <c r="A54" s="219" t="s">
+        <v>292</v>
+      </c>
+      <c r="B54" s="220"/>
+      <c r="C54" s="221" t="str">
         <f aca="false">DEC2HEX(D54,2)</f>
         <v>0A</v>
       </c>
@@ -9398,7 +9644,7 @@
         <f aca="false">IF(E54=1,128,0)+IF(F54=1,64,0)+IF(G54=1,32,0)+IF(H54=1,16,0)+IF(I54=1,8,0)+IF(J54=1,4,0)+IF(K54=1,2,0)+IF(L54=1,1,0)</f>
         <v>10</v>
       </c>
-      <c r="E54" s="190"/>
+      <c r="E54" s="191"/>
       <c r="F54" s="173"/>
       <c r="G54" s="173"/>
       <c r="H54" s="177"/>
@@ -9414,15 +9660,15 @@
       <c r="L54" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="223" t="s">
-        <v>290</v>
-      </c>
-      <c r="N54" s="221"/>
-      <c r="O54" s="223"/>
-      <c r="P54" s="225"/>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="226"/>
+      <c r="M54" s="222" t="s">
+        <v>293</v>
+      </c>
+      <c r="N54" s="220"/>
+      <c r="O54" s="222"/>
+      <c r="P54" s="224"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A55" s="225"/>
       <c r="B55" s="142"/>
       <c r="C55" s="17"/>
       <c r="D55" s="119"/>
@@ -9434,14 +9680,14 @@
       <c r="J55" s="13"/>
       <c r="K55" s="119"/>
       <c r="L55" s="50"/>
-      <c r="M55" s="227"/>
-      <c r="O55" s="228"/>
-      <c r="P55" s="229"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A56" s="226"/>
-      <c r="B56" s="227" t="s">
-        <v>234</v>
+      <c r="M55" s="226"/>
+      <c r="O55" s="227"/>
+      <c r="P55" s="228"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A56" s="225"/>
+      <c r="B56" s="226" t="s">
+        <v>237</v>
       </c>
       <c r="E56" s="146"/>
       <c r="F56" s="119"/>
@@ -9456,16 +9702,16 @@
         <v>1</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="P56" s="229" t="s">
-        <v>292</v>
+        <v>294</v>
+      </c>
+      <c r="P56" s="228" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="220"/>
-      <c r="B57" s="221"/>
-      <c r="C57" s="222" t="str">
+      <c r="A57" s="219"/>
+      <c r="B57" s="220"/>
+      <c r="C57" s="221" t="str">
         <f aca="false">DEC2HEX(D57,2)</f>
         <v>0B</v>
       </c>
@@ -9473,7 +9719,7 @@
         <f aca="false">IF(E57=1,128,0)+IF(F57=1,64,0)+IF(G57=1,32,0)+IF(H57=1,16,0)+IF(I57=1,8,0)+IF(J57=1,4,0)+IF(K57=1,2,0)+IF(L57=1,1,0)</f>
         <v>11</v>
       </c>
-      <c r="E57" s="190"/>
+      <c r="E57" s="191"/>
       <c r="F57" s="173"/>
       <c r="G57" s="173"/>
       <c r="H57" s="177"/>
@@ -9489,13 +9735,13 @@
       <c r="L57" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M57" s="223"/>
-      <c r="N57" s="221"/>
-      <c r="O57" s="223"/>
-      <c r="P57" s="225"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="226"/>
+      <c r="M57" s="222"/>
+      <c r="N57" s="220"/>
+      <c r="O57" s="222"/>
+      <c r="P57" s="224"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A58" s="225"/>
       <c r="B58" s="142"/>
       <c r="C58" s="17"/>
       <c r="D58" s="119"/>
@@ -9507,14 +9753,14 @@
       <c r="J58" s="13"/>
       <c r="K58" s="119"/>
       <c r="L58" s="50"/>
-      <c r="M58" s="227"/>
-      <c r="O58" s="228"/>
-      <c r="P58" s="229"/>
+      <c r="M58" s="226"/>
+      <c r="O58" s="227"/>
+      <c r="P58" s="228"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="220"/>
-      <c r="B59" s="221"/>
-      <c r="C59" s="222" t="str">
+      <c r="A59" s="219"/>
+      <c r="B59" s="220"/>
+      <c r="C59" s="221" t="str">
         <f aca="false">DEC2HEX(D59,2)</f>
         <v>0C</v>
       </c>
@@ -9522,7 +9768,7 @@
         <f aca="false">IF(E59=1,128,0)+IF(F59=1,64,0)+IF(G59=1,32,0)+IF(H59=1,16,0)+IF(I59=1,8,0)+IF(J59=1,4,0)+IF(K59=1,2,0)+IF(L59=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="E59" s="190"/>
+      <c r="E59" s="191"/>
       <c r="F59" s="173"/>
       <c r="G59" s="173"/>
       <c r="H59" s="177"/>
@@ -9538,13 +9784,13 @@
       <c r="L59" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M59" s="221"/>
-      <c r="N59" s="221"/>
-      <c r="O59" s="223"/>
-      <c r="P59" s="225"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A60" s="226"/>
+      <c r="M59" s="220"/>
+      <c r="N59" s="220"/>
+      <c r="O59" s="222"/>
+      <c r="P59" s="224"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A60" s="225"/>
       <c r="E60" s="146"/>
       <c r="F60" s="119"/>
       <c r="G60" s="119"/>
@@ -9553,15 +9799,15 @@
       <c r="J60" s="119"/>
       <c r="K60" s="119"/>
       <c r="L60" s="50"/>
-      <c r="M60" s="227"/>
-      <c r="N60" s="227"/>
+      <c r="M60" s="226"/>
+      <c r="N60" s="226"/>
       <c r="O60" s="142"/>
-      <c r="P60" s="229"/>
+      <c r="P60" s="228"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="220"/>
-      <c r="B61" s="221"/>
-      <c r="C61" s="222" t="str">
+      <c r="A61" s="219"/>
+      <c r="B61" s="220"/>
+      <c r="C61" s="221" t="str">
         <f aca="false">DEC2HEX(D61,2)</f>
         <v>0D</v>
       </c>
@@ -9569,7 +9815,7 @@
         <f aca="false">IF(E61=1,128,0)+IF(F61=1,64,0)+IF(G61=1,32,0)+IF(H61=1,16,0)+IF(I61=1,8,0)+IF(J61=1,4,0)+IF(K61=1,2,0)+IF(L61=1,1,0)</f>
         <v>13</v>
       </c>
-      <c r="E61" s="190"/>
+      <c r="E61" s="191"/>
       <c r="F61" s="173"/>
       <c r="G61" s="173"/>
       <c r="H61" s="177"/>
@@ -9585,13 +9831,13 @@
       <c r="L61" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M61" s="221"/>
-      <c r="N61" s="221"/>
-      <c r="O61" s="223"/>
-      <c r="P61" s="225"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A62" s="226"/>
+      <c r="M61" s="220"/>
+      <c r="N61" s="220"/>
+      <c r="O61" s="222"/>
+      <c r="P61" s="224"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A62" s="225"/>
       <c r="E62" s="146"/>
       <c r="F62" s="119"/>
       <c r="G62" s="119"/>
@@ -9600,15 +9846,15 @@
       <c r="J62" s="119"/>
       <c r="K62" s="119"/>
       <c r="L62" s="50"/>
-      <c r="M62" s="227"/>
-      <c r="N62" s="227"/>
+      <c r="M62" s="226"/>
+      <c r="N62" s="226"/>
       <c r="O62" s="142"/>
-      <c r="P62" s="229"/>
+      <c r="P62" s="228"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="220"/>
-      <c r="B63" s="221"/>
-      <c r="C63" s="222" t="str">
+      <c r="A63" s="219"/>
+      <c r="B63" s="220"/>
+      <c r="C63" s="221" t="str">
         <f aca="false">DEC2HEX(D63,2)</f>
         <v>0E</v>
       </c>
@@ -9616,7 +9862,7 @@
         <f aca="false">IF(E63=1,128,0)+IF(F63=1,64,0)+IF(G63=1,32,0)+IF(H63=1,16,0)+IF(I63=1,8,0)+IF(J63=1,4,0)+IF(K63=1,2,0)+IF(L63=1,1,0)</f>
         <v>14</v>
       </c>
-      <c r="E63" s="190"/>
+      <c r="E63" s="191"/>
       <c r="F63" s="173"/>
       <c r="G63" s="173"/>
       <c r="H63" s="177"/>
@@ -9632,13 +9878,13 @@
       <c r="L63" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M63" s="221"/>
-      <c r="N63" s="221"/>
-      <c r="O63" s="223"/>
-      <c r="P63" s="225"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="226"/>
+      <c r="M63" s="220"/>
+      <c r="N63" s="220"/>
+      <c r="O63" s="222"/>
+      <c r="P63" s="224"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A64" s="225"/>
       <c r="E64" s="146"/>
       <c r="F64" s="119"/>
       <c r="G64" s="119"/>
@@ -9647,15 +9893,15 @@
       <c r="J64" s="119"/>
       <c r="K64" s="119"/>
       <c r="L64" s="50"/>
-      <c r="M64" s="227"/>
-      <c r="N64" s="227"/>
+      <c r="M64" s="226"/>
+      <c r="N64" s="226"/>
       <c r="O64" s="142"/>
-      <c r="P64" s="229"/>
+      <c r="P64" s="228"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="220"/>
-      <c r="B65" s="221"/>
-      <c r="C65" s="222" t="str">
+      <c r="A65" s="219"/>
+      <c r="B65" s="220"/>
+      <c r="C65" s="221" t="str">
         <f aca="false">DEC2HEX(D65,2)</f>
         <v>0F</v>
       </c>
@@ -9663,7 +9909,7 @@
         <f aca="false">IF(E65=1,128,0)+IF(F65=1,64,0)+IF(G65=1,32,0)+IF(H65=1,16,0)+IF(I65=1,8,0)+IF(J65=1,4,0)+IF(K65=1,2,0)+IF(L65=1,1,0)</f>
         <v>15</v>
       </c>
-      <c r="E65" s="190"/>
+      <c r="E65" s="191"/>
       <c r="F65" s="173"/>
       <c r="G65" s="173"/>
       <c r="H65" s="177"/>
@@ -9679,13 +9925,13 @@
       <c r="L65" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M65" s="221"/>
-      <c r="N65" s="221"/>
-      <c r="O65" s="223"/>
-      <c r="P65" s="225"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A66" s="226"/>
+      <c r="M65" s="220"/>
+      <c r="N65" s="220"/>
+      <c r="O65" s="222"/>
+      <c r="P65" s="224"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A66" s="225"/>
       <c r="E66" s="146"/>
       <c r="F66" s="119"/>
       <c r="G66" s="119"/>
@@ -9694,13 +9940,13 @@
       <c r="J66" s="119"/>
       <c r="K66" s="119"/>
       <c r="L66" s="50"/>
-      <c r="M66" s="227"/>
-      <c r="N66" s="227"/>
+      <c r="M66" s="226"/>
+      <c r="N66" s="226"/>
       <c r="O66" s="142"/>
-      <c r="P66" s="229"/>
+      <c r="P66" s="228"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="226"/>
+      <c r="A67" s="225"/>
       <c r="E67" s="146"/>
       <c r="F67" s="119"/>
       <c r="G67" s="119"/>
@@ -9709,13 +9955,13 @@
       <c r="J67" s="119"/>
       <c r="K67" s="119"/>
       <c r="L67" s="50"/>
-      <c r="M67" s="227"/>
-      <c r="N67" s="227"/>
+      <c r="M67" s="226"/>
+      <c r="N67" s="226"/>
       <c r="O67" s="142"/>
-      <c r="P67" s="229"/>
+      <c r="P67" s="228"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="226"/>
+      <c r="A68" s="225"/>
       <c r="E68" s="146"/>
       <c r="F68" s="119"/>
       <c r="G68" s="119"/>
@@ -9724,90 +9970,90 @@
       <c r="J68" s="119"/>
       <c r="K68" s="119"/>
       <c r="L68" s="50"/>
-      <c r="M68" s="227"/>
-      <c r="N68" s="227"/>
+      <c r="M68" s="226"/>
+      <c r="N68" s="226"/>
       <c r="O68" s="142"/>
-      <c r="P68" s="229"/>
+      <c r="P68" s="228"/>
     </row>
     <row r="69" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="250" t="s">
-        <v>293</v>
+      <c r="A69" s="249" t="s">
+        <v>296</v>
       </c>
       <c r="E69" s="146"/>
-      <c r="F69" s="202" t="s">
-        <v>294</v>
-      </c>
-      <c r="G69" s="202" t="s">
-        <v>295</v>
-      </c>
-      <c r="H69" s="202" t="s">
-        <v>295</v>
-      </c>
-      <c r="I69" s="202"/>
-      <c r="J69" s="202"/>
-      <c r="K69" s="202" t="s">
-        <v>296</v>
-      </c>
-      <c r="L69" s="202" t="s">
+      <c r="F69" s="203" t="s">
         <v>297</v>
       </c>
-      <c r="M69" s="227"/>
-      <c r="N69" s="227"/>
+      <c r="G69" s="203" t="s">
+        <v>298</v>
+      </c>
+      <c r="H69" s="203" t="s">
+        <v>298</v>
+      </c>
+      <c r="I69" s="203"/>
+      <c r="J69" s="203"/>
+      <c r="K69" s="203" t="s">
+        <v>299</v>
+      </c>
+      <c r="L69" s="203" t="s">
+        <v>300</v>
+      </c>
+      <c r="M69" s="226"/>
+      <c r="N69" s="226"/>
       <c r="O69" s="142"/>
-      <c r="P69" s="229"/>
+      <c r="P69" s="228"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="220" t="s">
-        <v>213</v>
-      </c>
-      <c r="B70" s="223"/>
-      <c r="C70" s="222"/>
+      <c r="A70" s="219" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" s="222"/>
+      <c r="C70" s="221"/>
       <c r="D70" s="173"/>
-      <c r="E70" s="190"/>
+      <c r="E70" s="191"/>
       <c r="F70" s="173"/>
       <c r="G70" s="173"/>
       <c r="H70" s="177"/>
-      <c r="I70" s="190"/>
+      <c r="I70" s="191"/>
       <c r="J70" s="173"/>
       <c r="K70" s="173"/>
       <c r="L70" s="177"/>
-      <c r="M70" s="221"/>
-      <c r="N70" s="221"/>
-      <c r="O70" s="223"/>
-      <c r="P70" s="225"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="251" t="s">
-        <v>298</v>
-      </c>
-      <c r="B71" s="193"/>
-      <c r="C71" s="216" t="str">
+      <c r="M70" s="220"/>
+      <c r="N70" s="220"/>
+      <c r="O70" s="222"/>
+      <c r="P70" s="224"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A71" s="250" t="s">
+        <v>301</v>
+      </c>
+      <c r="B71" s="194"/>
+      <c r="C71" s="215" t="str">
         <f aca="false">DEC2HEX(D71,2)</f>
         <v>00</v>
       </c>
-      <c r="D71" s="195" t="n">
+      <c r="D71" s="196" t="n">
         <f aca="false">IF(E71=1,128,0)+IF(F71=1,64,0)+IF(G71=1,32,0)+IF(H71=1,16,0)+IF(I71=1,8,0)+IF(J71=1,4,0)+IF(K71=1,2,0)+IF(L71=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E71" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="206" t="n">
+      <c r="E71" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="252" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="206" t="n">
+      <c r="I71" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="252" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="253" t="n">
@@ -9815,12 +10061,12 @@
       </c>
       <c r="M71" s="254"/>
       <c r="N71" s="254"/>
-      <c r="O71" s="193"/>
+      <c r="O71" s="194"/>
       <c r="P71" s="255"/>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="226" t="s">
-        <v>299</v>
+    <row r="72" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A72" s="225" t="s">
+        <v>302</v>
       </c>
       <c r="B72" s="142"/>
       <c r="C72" s="20" t="str">
@@ -9855,14 +10101,14 @@
       <c r="L72" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="227"/>
-      <c r="N72" s="227"/>
+      <c r="M72" s="226"/>
+      <c r="N72" s="226"/>
       <c r="O72" s="142"/>
-      <c r="P72" s="229"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="226" t="s">
-        <v>300</v>
+      <c r="P72" s="228"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A73" s="225" t="s">
+        <v>303</v>
       </c>
       <c r="B73" s="142"/>
       <c r="C73" s="20" t="str">
@@ -9897,17 +10143,17 @@
       <c r="L73" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="227"/>
-      <c r="N73" s="227"/>
+      <c r="M73" s="226"/>
+      <c r="N73" s="226"/>
       <c r="O73" s="142"/>
-      <c r="P73" s="229"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="246" t="s">
-        <v>301</v>
-      </c>
-      <c r="B74" s="249"/>
-      <c r="C74" s="247" t="str">
+      <c r="P73" s="228"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A74" s="245" t="s">
+        <v>304</v>
+      </c>
+      <c r="B74" s="248"/>
+      <c r="C74" s="246" t="str">
         <f aca="false">DEC2HEX(D74,2)</f>
         <v>30</v>
       </c>
@@ -9915,7 +10161,7 @@
         <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
         <v>48</v>
       </c>
-      <c r="E74" s="248" t="n">
+      <c r="E74" s="247" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="152" t="n">
@@ -9927,7 +10173,7 @@
       <c r="H74" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="248" t="n">
+      <c r="I74" s="247" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="152" t="n">
@@ -9941,41 +10187,41 @@
       </c>
       <c r="M74" s="256"/>
       <c r="N74" s="256"/>
-      <c r="O74" s="249"/>
+      <c r="O74" s="248"/>
       <c r="P74" s="257"/>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="251" t="s">
-        <v>302</v>
-      </c>
-      <c r="B75" s="193"/>
-      <c r="C75" s="216" t="str">
+    <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A75" s="250" t="s">
+        <v>305</v>
+      </c>
+      <c r="B75" s="194"/>
+      <c r="C75" s="215" t="str">
         <f aca="false">DEC2HEX(D75,2)</f>
         <v>40</v>
       </c>
-      <c r="D75" s="195" t="n">
+      <c r="D75" s="196" t="n">
         <f aca="false">IF(E75=1,128,0)+IF(F75=1,64,0)+IF(G75=1,32,0)+IF(H75=1,16,0)+IF(I75=1,8,0)+IF(J75=1,4,0)+IF(K75=1,2,0)+IF(L75=1,1,0)</f>
         <v>64</v>
       </c>
-      <c r="E75" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="206" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="206" t="n">
+      <c r="E75" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="252" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="252" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="I75" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="206" t="n">
+      <c r="I75" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="252" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="253" t="n">
@@ -9983,12 +10229,12 @@
       </c>
       <c r="M75" s="254"/>
       <c r="N75" s="254"/>
-      <c r="O75" s="193"/>
+      <c r="O75" s="194"/>
       <c r="P75" s="255"/>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="226" t="s">
-        <v>303</v>
+    <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A76" s="225" t="s">
+        <v>306</v>
       </c>
       <c r="B76" s="142"/>
       <c r="C76" s="20" t="str">
@@ -10023,14 +10269,14 @@
       <c r="L76" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="227"/>
-      <c r="N76" s="227"/>
+      <c r="M76" s="226"/>
+      <c r="N76" s="226"/>
       <c r="O76" s="142"/>
-      <c r="P76" s="229"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="226" t="s">
-        <v>304</v>
+      <c r="P76" s="228"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A77" s="225" t="s">
+        <v>307</v>
       </c>
       <c r="B77" s="142"/>
       <c r="C77" s="20" t="str">
@@ -10065,17 +10311,17 @@
       <c r="L77" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="227"/>
-      <c r="N77" s="227"/>
+      <c r="M77" s="226"/>
+      <c r="N77" s="226"/>
       <c r="O77" s="142"/>
-      <c r="P77" s="229"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="246" t="s">
-        <v>305</v>
-      </c>
-      <c r="B78" s="249"/>
-      <c r="C78" s="247" t="str">
+      <c r="P77" s="228"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A78" s="245" t="s">
+        <v>308</v>
+      </c>
+      <c r="B78" s="248"/>
+      <c r="C78" s="246" t="str">
         <f aca="false">DEC2HEX(D78,2)</f>
         <v>70</v>
       </c>
@@ -10083,7 +10329,7 @@
         <f aca="false">IF(E78=1,128,0)+IF(F78=1,64,0)+IF(G78=1,32,0)+IF(H78=1,16,0)+IF(I78=1,8,0)+IF(J78=1,4,0)+IF(K78=1,2,0)+IF(L78=1,1,0)</f>
         <v>112</v>
       </c>
-      <c r="E78" s="248" t="n">
+      <c r="E78" s="247" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="152" t="n">
@@ -10095,7 +10341,7 @@
       <c r="H78" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I78" s="248" t="n">
+      <c r="I78" s="247" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="152" t="n">
@@ -10109,41 +10355,41 @@
       </c>
       <c r="M78" s="256"/>
       <c r="N78" s="256"/>
-      <c r="O78" s="249"/>
+      <c r="O78" s="248"/>
       <c r="P78" s="257"/>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="251" t="s">
-        <v>306</v>
+    <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A79" s="250" t="s">
+        <v>309</v>
       </c>
       <c r="B79" s="258"/>
-      <c r="C79" s="216" t="str">
+      <c r="C79" s="215" t="str">
         <f aca="false">DEC2HEX(D79,2)</f>
         <v>01</v>
       </c>
-      <c r="D79" s="195" t="n">
+      <c r="D79" s="196" t="n">
         <f aca="false">IF(E79=1,128,0)+IF(F79=1,64,0)+IF(G79=1,32,0)+IF(H79=1,16,0)+IF(I79=1,8,0)+IF(J79=1,4,0)+IF(K79=1,2,0)+IF(L79=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E79" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="206" t="n">
+      <c r="E79" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="252" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="195" t="n">
+      <c r="I79" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="196" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="253" t="n">
@@ -10151,12 +10397,12 @@
       </c>
       <c r="M79" s="254"/>
       <c r="N79" s="254"/>
-      <c r="O79" s="193"/>
+      <c r="O79" s="194"/>
       <c r="P79" s="255"/>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="226" t="s">
-        <v>307</v>
+    <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A80" s="225" t="s">
+        <v>310</v>
       </c>
       <c r="B80" s="142"/>
       <c r="C80" s="20" t="str">
@@ -10191,11 +10437,11 @@
       <c r="L80" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="P80" s="229"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="226" t="s">
-        <v>308</v>
+      <c r="P80" s="228"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A81" s="225" t="s">
+        <v>311</v>
       </c>
       <c r="B81" s="142"/>
       <c r="C81" s="20" t="str">
@@ -10233,14 +10479,14 @@
       <c r="M81" s="10"/>
       <c r="N81" s="10"/>
       <c r="O81" s="142"/>
-      <c r="P81" s="229"/>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="246" t="s">
-        <v>309</v>
-      </c>
-      <c r="B82" s="249"/>
-      <c r="C82" s="247" t="str">
+      <c r="P81" s="228"/>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A82" s="245" t="s">
+        <v>312</v>
+      </c>
+      <c r="B82" s="248"/>
+      <c r="C82" s="246" t="str">
         <f aca="false">DEC2HEX(D82,2)</f>
         <v>31</v>
       </c>
@@ -10248,7 +10494,7 @@
         <f aca="false">IF(E82=1,128,0)+IF(F82=1,64,0)+IF(G82=1,32,0)+IF(H82=1,16,0)+IF(I82=1,8,0)+IF(J82=1,4,0)+IF(K82=1,2,0)+IF(L82=1,1,0)</f>
         <v>49</v>
       </c>
-      <c r="E82" s="248" t="n">
+      <c r="E82" s="247" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="152" t="n">
@@ -10260,7 +10506,7 @@
       <c r="H82" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I82" s="248" t="n">
+      <c r="I82" s="247" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="152" t="n">
@@ -10274,41 +10520,41 @@
       </c>
       <c r="M82" s="256"/>
       <c r="N82" s="256"/>
-      <c r="O82" s="249"/>
+      <c r="O82" s="248"/>
       <c r="P82" s="257"/>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="251" t="s">
-        <v>310</v>
-      </c>
-      <c r="B83" s="193"/>
-      <c r="C83" s="216" t="str">
+    <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A83" s="250" t="s">
+        <v>313</v>
+      </c>
+      <c r="B83" s="194"/>
+      <c r="C83" s="215" t="str">
         <f aca="false">DEC2HEX(D83,2)</f>
         <v>04</v>
       </c>
-      <c r="D83" s="195" t="n">
+      <c r="D83" s="196" t="n">
         <f aca="false">IF(E83=1,128,0)+IF(F83=1,64,0)+IF(G83=1,32,0)+IF(H83=1,16,0)+IF(I83=1,8,0)+IF(J83=1,4,0)+IF(K83=1,2,0)+IF(L83=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E83" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="206" t="n">
+      <c r="E83" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="252" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="206" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="206" t="n">
+      <c r="I83" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="252" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="253" t="n">
@@ -10316,14 +10562,14 @@
       </c>
       <c r="M83" s="254"/>
       <c r="N83" s="254"/>
-      <c r="O83" s="193"/>
+      <c r="O83" s="194"/>
       <c r="P83" s="255" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A84" s="226" t="s">
-        <v>312</v>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A84" s="225" t="s">
+        <v>315</v>
       </c>
       <c r="B84" s="142"/>
       <c r="C84" s="20" t="str">
@@ -10358,16 +10604,16 @@
       <c r="L84" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="227"/>
-      <c r="N84" s="227"/>
+      <c r="M84" s="226"/>
+      <c r="N84" s="226"/>
       <c r="O84" s="142"/>
-      <c r="P84" s="229" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A85" s="226" t="s">
-        <v>314</v>
+      <c r="P84" s="228" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A85" s="225" t="s">
+        <v>317</v>
       </c>
       <c r="B85" s="259"/>
       <c r="C85" s="17" t="str">
@@ -10402,16 +10648,16 @@
       <c r="L85" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="227"/>
-      <c r="N85" s="227"/>
+      <c r="M85" s="226"/>
+      <c r="N85" s="226"/>
       <c r="O85" s="259"/>
-      <c r="P85" s="229" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A86" s="226" t="s">
-        <v>316</v>
+      <c r="P85" s="228" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A86" s="225" t="s">
+        <v>319</v>
       </c>
       <c r="B86" s="259"/>
       <c r="C86" s="17" t="str">
@@ -10446,43 +10692,43 @@
       <c r="L86" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="M86" s="227"/>
-      <c r="N86" s="227"/>
+      <c r="M86" s="226"/>
+      <c r="N86" s="226"/>
       <c r="O86" s="259"/>
-      <c r="P86" s="229"/>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A87" s="251" t="s">
-        <v>317</v>
-      </c>
-      <c r="B87" s="193"/>
-      <c r="C87" s="216" t="str">
+      <c r="P86" s="228"/>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A87" s="250" t="s">
+        <v>320</v>
+      </c>
+      <c r="B87" s="194"/>
+      <c r="C87" s="215" t="str">
         <f aca="false">DEC2HEX(D87,2)</f>
         <v>05</v>
       </c>
-      <c r="D87" s="195" t="n">
+      <c r="D87" s="196" t="n">
         <f aca="false">IF(E87=1,128,0)+IF(F87=1,64,0)+IF(G87=1,32,0)+IF(H87=1,16,0)+IF(I87=1,8,0)+IF(J87=1,4,0)+IF(K87=1,2,0)+IF(L87=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E87" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="206" t="n">
+      <c r="E87" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="252" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="206" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="206" t="n">
+      <c r="I87" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="252" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="253" t="n">
@@ -10490,17 +10736,17 @@
       </c>
       <c r="M87" s="254"/>
       <c r="N87" s="254"/>
-      <c r="O87" s="193"/>
+      <c r="O87" s="194"/>
       <c r="P87" s="255" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A88" s="246" t="s">
-        <v>319</v>
-      </c>
-      <c r="B88" s="249"/>
-      <c r="C88" s="247" t="str">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A88" s="245" t="s">
+        <v>322</v>
+      </c>
+      <c r="B88" s="248"/>
+      <c r="C88" s="246" t="str">
         <f aca="false">DEC2HEX(D88,2)</f>
         <v>45</v>
       </c>
@@ -10508,7 +10754,7 @@
         <f aca="false">IF(E88=1,128,0)+IF(F88=1,64,0)+IF(G88=1,32,0)+IF(H88=1,16,0)+IF(I88=1,8,0)+IF(J88=1,4,0)+IF(K88=1,2,0)+IF(L88=1,1,0)</f>
         <v>69</v>
       </c>
-      <c r="E88" s="248" t="n">
+      <c r="E88" s="247" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="152" t="n">
@@ -10520,7 +10766,7 @@
       <c r="H88" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="248" t="n">
+      <c r="I88" s="247" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="152" t="n">
@@ -10534,14 +10780,14 @@
       </c>
       <c r="M88" s="256"/>
       <c r="N88" s="256"/>
-      <c r="O88" s="249"/>
+      <c r="O88" s="248"/>
       <c r="P88" s="257" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A89" s="226" t="s">
-        <v>321</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A89" s="225" t="s">
+        <v>324</v>
       </c>
       <c r="B89" s="142"/>
       <c r="C89" s="17" t="str">
@@ -10576,17 +10822,17 @@
       <c r="L89" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="227"/>
-      <c r="N89" s="227"/>
+      <c r="M89" s="226"/>
+      <c r="N89" s="226"/>
       <c r="O89" s="142"/>
-      <c r="P89" s="229"/>
-    </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A90" s="246" t="s">
-        <v>322</v>
-      </c>
-      <c r="B90" s="249"/>
-      <c r="C90" s="247" t="str">
+      <c r="P89" s="228"/>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A90" s="245" t="s">
+        <v>325</v>
+      </c>
+      <c r="B90" s="248"/>
+      <c r="C90" s="246" t="str">
         <f aca="false">DEC2HEX(D90,2)</f>
         <v>37</v>
       </c>
@@ -10594,7 +10840,7 @@
         <f aca="false">IF(E90=1,128,0)+IF(F90=1,64,0)+IF(G90=1,32,0)+IF(H90=1,16,0)+IF(I90=1,8,0)+IF(J90=1,4,0)+IF(K90=1,2,0)+IF(L90=1,1,0)</f>
         <v>55</v>
       </c>
-      <c r="E90" s="248" t="n">
+      <c r="E90" s="247" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="152" t="n">
@@ -10606,7 +10852,7 @@
       <c r="H90" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I90" s="248" t="n">
+      <c r="I90" s="247" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="152" t="n">
@@ -10620,11 +10866,11 @@
       </c>
       <c r="M90" s="256"/>
       <c r="N90" s="256"/>
-      <c r="O90" s="249"/>
+      <c r="O90" s="248"/>
       <c r="P90" s="257"/>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A91" s="226"/>
+    <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A91" s="225"/>
       <c r="B91" s="142"/>
       <c r="C91" s="17" t="str">
         <f aca="false">DEC2HEX(D91,2)</f>
@@ -10642,15 +10888,15 @@
       <c r="J91" s="119"/>
       <c r="K91" s="119"/>
       <c r="L91" s="50"/>
-      <c r="M91" s="227"/>
-      <c r="N91" s="227"/>
+      <c r="M91" s="226"/>
+      <c r="N91" s="226"/>
       <c r="O91" s="142"/>
-      <c r="P91" s="229"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A92" s="246"/>
-      <c r="B92" s="249"/>
-      <c r="C92" s="247" t="str">
+      <c r="P91" s="228"/>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A92" s="245"/>
+      <c r="B92" s="248"/>
+      <c r="C92" s="246" t="str">
         <f aca="false">DEC2HEX(D92,2)</f>
         <v>00</v>
       </c>
@@ -10658,17 +10904,17 @@
         <f aca="false">IF(E92=1,128,0)+IF(F92=1,64,0)+IF(G92=1,32,0)+IF(H92=1,16,0)+IF(I92=1,8,0)+IF(J92=1,4,0)+IF(K92=1,2,0)+IF(L92=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E92" s="248"/>
+      <c r="E92" s="247"/>
       <c r="F92" s="152"/>
       <c r="G92" s="152"/>
       <c r="H92" s="155"/>
-      <c r="I92" s="248"/>
+      <c r="I92" s="247"/>
       <c r="J92" s="152"/>
       <c r="K92" s="152"/>
       <c r="L92" s="155"/>
       <c r="M92" s="256"/>
       <c r="N92" s="256"/>
-      <c r="O92" s="249"/>
+      <c r="O92" s="248"/>
       <c r="P92" s="257"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10676,7 +10922,7 @@
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -10696,7 +10942,7 @@
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -10735,10 +10981,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>52</v>
@@ -10753,12 +10999,12 @@
         <v>120</v>
       </c>
       <c r="G1" s="261" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H1" s="261"/>
       <c r="I1" s="261"/>
       <c r="J1" s="261" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10772,26 +11018,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>120</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10805,13 +11051,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>120</v>
@@ -10821,10 +11067,10 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10841,25 +11087,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10876,25 +11122,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10908,28 +11154,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="K6" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10943,28 +11189,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="K7" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10978,26 +11224,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>120</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11011,13 +11257,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>120</v>
@@ -11027,10 +11273,10 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11044,28 +11290,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11079,28 +11325,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11114,28 +11360,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11149,28 +11395,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -63,9 +63,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>14</xdr:col>
-                <xdr:colOff>26</xdr:colOff>
+                <xdr:colOff>17</xdr:colOff>
                 <xdr:row>33</xdr:row>
-                <xdr:rowOff>15</xdr:rowOff>
+                <xdr:rowOff>10</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -96,7 +96,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
+                <xdr:colOff>31</xdr:colOff>
                 <xdr:row>28</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -123,15 +123,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>12</xdr:col>
-                <xdr:colOff>102</xdr:colOff>
+                <xdr:colOff>68</xdr:colOff>
                 <xdr:row>33</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>13</xdr:col>
-                <xdr:colOff>159</xdr:colOff>
+                <xdr:colOff>106</xdr:colOff>
                 <xdr:row>34</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -162,9 +162,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
+                <xdr:colOff>31</xdr:colOff>
                 <xdr:row>29</xdr:row>
-                <xdr:rowOff>18</xdr:rowOff>
+                <xdr:rowOff>12</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="353">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -1707,6 +1707,12 @@
     <t xml:space="preserve">Examples</t>
   </si>
   <si>
+    <t xml:space="preserve">Array info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data-type type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Decimal</t>
   </si>
   <si>
@@ -2312,7 +2318,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2432,12 +2438,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <i val="true"/>
@@ -2958,11 +2958,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="259">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3687,14 +3687,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3719,10 +3711,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3755,19 +3743,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3775,11 +3763,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3883,7 +3871,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7407,7 +7395,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B16" s="181" t="s">
+      <c r="B16" s="144" t="s">
         <v>178</v>
       </c>
       <c r="C16" s="136"/>
@@ -7507,23 +7495,23 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="B20" s="182" t="s">
+      <c r="B20" s="149" t="s">
         <v>189</v>
       </c>
       <c r="C20" s="150"/>
-      <c r="D20" s="183"/>
+      <c r="D20" s="181"/>
       <c r="E20" s="152"/>
-      <c r="F20" s="184"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="186"/>
-      <c r="I20" s="184"/>
+      <c r="F20" s="182"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="182"/>
       <c r="J20" s="152"/>
       <c r="K20" s="155"/>
       <c r="L20" s="156"/>
       <c r="M20" s="156"/>
       <c r="N20" s="155"/>
       <c r="O20" s="155"/>
-      <c r="P20" s="187" t="s">
+      <c r="P20" s="185" t="s">
         <v>191</v>
       </c>
     </row>
@@ -7558,7 +7546,7 @@
       <c r="D22" s="137"/>
       <c r="E22" s="138"/>
       <c r="F22" s="138"/>
-      <c r="G22" s="188"/>
+      <c r="G22" s="186"/>
       <c r="H22" s="140"/>
       <c r="I22" s="138"/>
       <c r="J22" s="13"/>
@@ -7583,7 +7571,7 @@
       <c r="D23" s="137"/>
       <c r="E23" s="138"/>
       <c r="F23" s="138"/>
-      <c r="G23" s="188"/>
+      <c r="G23" s="186"/>
       <c r="H23" s="140"/>
       <c r="I23" s="138"/>
       <c r="J23" s="13"/>
@@ -7640,7 +7628,7 @@
       <c r="I25" s="138"/>
       <c r="J25" s="119"/>
       <c r="K25" s="141"/>
-      <c r="L25" s="189" t="s">
+      <c r="L25" s="142" t="s">
         <v>198</v>
       </c>
       <c r="M25" s="142"/>
@@ -7671,7 +7659,7 @@
       <c r="O26" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="P26" s="190" t="s">
+      <c r="P26" s="187" t="s">
         <v>175</v>
       </c>
     </row>
@@ -7683,11 +7671,11 @@
         <v>201</v>
       </c>
       <c r="C27" s="171"/>
-      <c r="D27" s="191"/>
+      <c r="D27" s="188"/>
       <c r="E27" s="173"/>
       <c r="F27" s="173"/>
-      <c r="G27" s="192"/>
-      <c r="H27" s="193"/>
+      <c r="G27" s="189"/>
+      <c r="H27" s="190"/>
       <c r="I27" s="173"/>
       <c r="J27" s="173"/>
       <c r="K27" s="177"/>
@@ -7713,7 +7701,7 @@
       <c r="I28" s="138"/>
       <c r="J28" s="119"/>
       <c r="K28" s="141"/>
-      <c r="L28" s="189" t="s">
+      <c r="L28" s="142" t="s">
         <v>198</v>
       </c>
       <c r="M28" s="142"/>
@@ -7729,7 +7717,7 @@
       <c r="D29" s="137"/>
       <c r="E29" s="138"/>
       <c r="F29" s="138"/>
-      <c r="G29" s="188" t="s">
+      <c r="G29" s="186" t="s">
         <v>52</v>
       </c>
       <c r="H29" s="140"/>
@@ -7757,7 +7745,7 @@
       <c r="D30" s="172"/>
       <c r="E30" s="174"/>
       <c r="F30" s="174"/>
-      <c r="G30" s="192"/>
+      <c r="G30" s="189"/>
       <c r="H30" s="176"/>
       <c r="I30" s="174"/>
       <c r="J30" s="173"/>
@@ -7777,7 +7765,7 @@
       <c r="D31" s="137"/>
       <c r="E31" s="138"/>
       <c r="F31" s="138"/>
-      <c r="G31" s="188"/>
+      <c r="G31" s="186"/>
       <c r="H31" s="140"/>
       <c r="I31" s="138"/>
       <c r="J31" s="13"/>
@@ -7799,7 +7787,7 @@
       <c r="D32" s="172"/>
       <c r="E32" s="174"/>
       <c r="F32" s="174"/>
-      <c r="G32" s="192"/>
+      <c r="G32" s="189"/>
       <c r="H32" s="176"/>
       <c r="I32" s="174"/>
       <c r="J32" s="173"/>
@@ -7819,7 +7807,7 @@
       <c r="D33" s="137"/>
       <c r="E33" s="138"/>
       <c r="F33" s="138"/>
-      <c r="G33" s="188"/>
+      <c r="G33" s="186"/>
       <c r="H33" s="140"/>
       <c r="I33" s="138"/>
       <c r="J33" s="13"/>
@@ -7893,14 +7881,14 @@
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B36" s="149"/>
       <c r="C36" s="150"/>
-      <c r="D36" s="183"/>
+      <c r="D36" s="181"/>
       <c r="E36" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="F36" s="184"/>
-      <c r="G36" s="185"/>
-      <c r="H36" s="186"/>
-      <c r="I36" s="184"/>
+      <c r="F36" s="182"/>
+      <c r="G36" s="183"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="182"/>
       <c r="J36" s="152"/>
       <c r="K36" s="155"/>
       <c r="L36" s="156" t="s">
@@ -7918,30 +7906,30 @@
       <c r="P36" s="157"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="194"/>
-      <c r="C37" s="195"/>
-      <c r="D37" s="196"/>
-      <c r="E37" s="196"/>
-      <c r="F37" s="197"/>
-      <c r="G37" s="197"/>
-      <c r="H37" s="197"/>
-      <c r="I37" s="197"/>
-      <c r="J37" s="196"/>
-      <c r="K37" s="196"/>
-      <c r="L37" s="194"/>
-      <c r="M37" s="194"/>
-      <c r="N37" s="194"/>
-      <c r="O37" s="196"/>
-      <c r="P37" s="196"/>
+      <c r="B37" s="191"/>
+      <c r="C37" s="192"/>
+      <c r="D37" s="193"/>
+      <c r="E37" s="193"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="193"/>
+      <c r="K37" s="193"/>
+      <c r="L37" s="191"/>
+      <c r="M37" s="191"/>
+      <c r="N37" s="191"/>
+      <c r="O37" s="193"/>
+      <c r="P37" s="193"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="142"/>
       <c r="S37" s="142"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="198" t="s">
+      <c r="B38" s="195" t="s">
         <v>156</v>
       </c>
-      <c r="C38" s="199"/>
+      <c r="C38" s="196"/>
       <c r="D38" s="138"/>
       <c r="E38" s="138"/>
       <c r="F38" s="138"/>
@@ -7950,9 +7938,9 @@
       <c r="I38" s="138"/>
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
-      <c r="L38" s="198"/>
-      <c r="M38" s="198"/>
-      <c r="N38" s="198"/>
+      <c r="L38" s="195"/>
+      <c r="M38" s="195"/>
+      <c r="N38" s="195"/>
       <c r="O38" s="119"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
@@ -7984,65 +7972,71 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="200" t="s">
+      <c r="A43" s="197" t="s">
         <v>216</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="201" t="s">
+      <c r="C43" s="198" t="s">
         <v>44</v>
       </c>
-      <c r="D43" s="202" t="s">
+      <c r="D43" s="199" t="s">
         <v>198</v>
       </c>
-      <c r="E43" s="202"/>
-      <c r="F43" s="203"/>
-      <c r="G43" s="203"/>
-      <c r="H43" s="202"/>
-      <c r="I43" s="203" t="s">
+      <c r="E43" s="200" t="s">
+        <v>217</v>
+      </c>
+      <c r="F43" s="200" t="s">
+        <v>218</v>
+      </c>
+      <c r="G43" s="200" t="s">
+        <v>218</v>
+      </c>
+      <c r="H43" s="199"/>
+      <c r="I43" s="200" t="s">
         <v>201</v>
       </c>
-      <c r="J43" s="203" t="s">
+      <c r="J43" s="200" t="s">
         <v>162</v>
       </c>
-      <c r="K43" s="203" t="s">
+      <c r="K43" s="200" t="s">
         <v>158</v>
       </c>
-      <c r="L43" s="201" t="s">
-        <v>217</v>
-      </c>
-      <c r="M43" s="204" t="s">
-        <v>218</v>
-      </c>
-      <c r="N43" s="200" t="s">
+      <c r="L43" s="198" t="s">
         <v>219</v>
       </c>
-      <c r="O43" s="201"/>
-      <c r="P43" s="200"/>
-      <c r="Q43" s="200"/>
-      <c r="R43" s="200"/>
-      <c r="S43" s="200"/>
+      <c r="M43" s="201" t="s">
+        <v>220</v>
+      </c>
+      <c r="N43" s="197" t="s">
+        <v>221</v>
+      </c>
+      <c r="O43" s="198"/>
+      <c r="P43" s="197"/>
+      <c r="Q43" s="197"/>
+      <c r="R43" s="197"/>
+      <c r="S43" s="197"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="205"/>
+      <c r="A44" s="202"/>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="str">
         <f aca="false">DEC2HEX(L44,2)</f>
         <v>80</v>
       </c>
-      <c r="D44" s="206" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="196"/>
-      <c r="F44" s="196"/>
-      <c r="G44" s="207"/>
-      <c r="H44" s="208"/>
-      <c r="I44" s="196" t="s">
+      <c r="D44" s="203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="193"/>
+      <c r="F44" s="193"/>
+      <c r="G44" s="204"/>
+      <c r="H44" s="205"/>
+      <c r="I44" s="193" t="s">
         <v>69</v>
       </c>
-      <c r="J44" s="196" t="s">
+      <c r="J44" s="193" t="s">
         <v>69</v>
       </c>
-      <c r="K44" s="209" t="s">
+      <c r="K44" s="206" t="s">
         <v>69</v>
       </c>
       <c r="L44" s="12" t="n">
@@ -8053,7 +8047,7 @@
         <v>198</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
@@ -8061,7 +8055,7 @@
       <c r="S44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="205"/>
+      <c r="A45" s="202"/>
       <c r="B45" s="1"/>
       <c r="C45" s="2" t="str">
         <f aca="false">DEC2HEX(L45,2)</f>
@@ -8072,7 +8066,7 @@
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
-      <c r="G45" s="188" t="n">
+      <c r="G45" s="186" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="148"/>
@@ -8090,10 +8084,10 @@
         <v>4</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
@@ -8101,7 +8095,7 @@
       <c r="S45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="205"/>
+      <c r="A46" s="202"/>
       <c r="B46" s="1"/>
       <c r="C46" s="2" t="str">
         <f aca="false">DEC2HEX(L46,2)</f>
@@ -8116,7 +8110,7 @@
       <c r="F46" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="188" t="n">
+      <c r="G46" s="186" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="148"/>
@@ -8134,10 +8128,10 @@
         <v>20</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
@@ -8145,7 +8139,7 @@
       <c r="S46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="205"/>
+      <c r="A47" s="202"/>
       <c r="B47" s="1"/>
       <c r="C47" s="2" t="str">
         <f aca="false">DEC2HEX(L47,2)</f>
@@ -8156,7 +8150,7 @@
       <c r="F47" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="188" t="n">
+      <c r="G47" s="186" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="148"/>
@@ -8174,10 +8168,10 @@
         <v>0</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
@@ -8185,7 +8179,7 @@
       <c r="S47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="205"/>
+      <c r="A48" s="202"/>
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="str">
         <f aca="false">DEC2HEX(L48,2)</f>
@@ -8198,7 +8192,7 @@
       <c r="F48" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="188" t="n">
+      <c r="G48" s="186" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="148"/>
@@ -8219,7 +8213,7 @@
         <v>169</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="11"/>
@@ -8228,7 +8222,7 @@
       <c r="S48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="205"/>
+      <c r="A49" s="202"/>
       <c r="B49" s="1"/>
       <c r="C49" s="2" t="str">
         <f aca="false">DEC2HEX(L49,2)</f>
@@ -8239,7 +8233,7 @@
       <c r="F49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="188" t="n">
+      <c r="G49" s="186" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="148"/>
@@ -8260,7 +8254,7 @@
         <v>170</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P49" s="11"/>
       <c r="Q49" s="11"/>
@@ -8268,32 +8262,32 @@
       <c r="S49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="205"/>
+      <c r="A50" s="202"/>
       <c r="B50" s="1"/>
       <c r="C50" s="2" t="str">
         <f aca="false">DEC2HEX(L50,2)</f>
         <v>31</v>
       </c>
-      <c r="D50" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="210" t="s">
+      <c r="D50" s="181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="207" t="s">
         <v>69</v>
       </c>
-      <c r="F50" s="210" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="211" t="n">
+      <c r="F50" s="207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="208" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="154"/>
-      <c r="I50" s="210" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="210" t="s">
+      <c r="I50" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="207" t="s">
         <v>69</v>
       </c>
-      <c r="K50" s="212" t="n">
+      <c r="K50" s="209" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="12" t="n">
@@ -8304,7 +8298,7 @@
         <v>171</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P50" s="11"/>
       <c r="Q50" s="11"/>
@@ -8352,8 +8346,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="213"/>
-      <c r="B1" s="214" t="s">
+      <c r="A1" s="210"/>
+      <c r="B1" s="211" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="17" t="s">
@@ -8365,10 +8359,10 @@
       <c r="E1" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="215" t="n">
+      <c r="F1" s="212" t="n">
         <v>6</v>
       </c>
-      <c r="G1" s="215" t="n">
+      <c r="G1" s="212" t="n">
         <v>5</v>
       </c>
       <c r="H1" s="27" t="n">
@@ -8377,34 +8371,34 @@
       <c r="I1" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J1" s="215" t="n">
+      <c r="J1" s="212" t="n">
         <v>2</v>
       </c>
-      <c r="K1" s="215" t="n">
+      <c r="K1" s="212" t="n">
         <v>1</v>
       </c>
       <c r="L1" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M1" s="216" t="s">
+      <c r="M1" s="213" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="216" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="217" t="s">
+      <c r="N1" s="213" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="214" t="s">
         <v>155</v>
       </c>
-      <c r="P1" s="218" t="s">
+      <c r="P1" s="215" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="219" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" s="220"/>
-      <c r="C2" s="221" t="str">
+      <c r="A2" s="216" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="217"/>
+      <c r="C2" s="218" t="str">
         <f aca="false">DEC2HEX(D2,2)</f>
         <v>00</v>
       </c>
@@ -8412,11 +8406,11 @@
         <f aca="false">IF(E2=1,128,0)+IF(F2=1,64,0)+IF(G2=1,32,0)+IF(H2=1,16,0)+IF(I2=1,8,0)+IF(J2=1,4,0)+IF(K2=1,2,0)+IF(L2=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E2" s="191"/>
+      <c r="E2" s="188"/>
       <c r="F2" s="173"/>
       <c r="G2" s="173"/>
       <c r="H2" s="177"/>
-      <c r="I2" s="191" t="n">
+      <c r="I2" s="188" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="173" t="n">
@@ -8428,45 +8422,45 @@
       <c r="L2" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="222" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="220"/>
-      <c r="O2" s="223"/>
-      <c r="P2" s="224"/>
+      <c r="M2" s="219" t="s">
+        <v>233</v>
+      </c>
+      <c r="N2" s="217"/>
+      <c r="O2" s="220"/>
+      <c r="P2" s="221"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="225"/>
+      <c r="A3" s="222"/>
       <c r="B3" s="142"/>
       <c r="C3" s="17"/>
       <c r="D3" s="119"/>
       <c r="E3" s="49"/>
       <c r="F3" s="119"/>
       <c r="G3" s="119" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="13"/>
       <c r="K3" s="119"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="226"/>
-      <c r="N3" s="226" t="s">
-        <v>233</v>
-      </c>
-      <c r="O3" s="227" t="s">
-        <v>234</v>
-      </c>
-      <c r="P3" s="228"/>
+      <c r="M3" s="223"/>
+      <c r="N3" s="223" t="s">
+        <v>235</v>
+      </c>
+      <c r="O3" s="224" t="s">
+        <v>236</v>
+      </c>
+      <c r="P3" s="225"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="225"/>
+      <c r="A4" s="222"/>
       <c r="B4" s="142"/>
       <c r="E4" s="49"/>
       <c r="F4" s="119" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G4" s="119"/>
       <c r="H4" s="50"/>
@@ -8474,15 +8468,15 @@
       <c r="J4" s="13"/>
       <c r="K4" s="119"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="226" t="s">
-        <v>236</v>
+      <c r="M4" s="223" t="s">
+        <v>238</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
-      <c r="P4" s="229"/>
+      <c r="P4" s="226"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="225"/>
+      <c r="A5" s="222"/>
       <c r="B5" s="142"/>
       <c r="C5" s="17"/>
       <c r="D5" s="119"/>
@@ -8494,14 +8488,14 @@
       <c r="J5" s="13"/>
       <c r="K5" s="119"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="226"/>
-      <c r="O5" s="227"/>
-      <c r="P5" s="228"/>
+      <c r="M5" s="223"/>
+      <c r="O5" s="224"/>
+      <c r="P5" s="225"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A6" s="225"/>
+      <c r="A6" s="222"/>
       <c r="B6" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="119"/>
@@ -8511,21 +8505,21 @@
       <c r="J6" s="13"/>
       <c r="K6" s="119"/>
       <c r="L6" s="50"/>
-      <c r="M6" s="226"/>
+      <c r="M6" s="223"/>
       <c r="N6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="P6" s="229"/>
+        <v>240</v>
+      </c>
+      <c r="P6" s="226"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="219" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="220"/>
-      <c r="C7" s="221" t="str">
+      <c r="A7" s="216" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="217"/>
+      <c r="C7" s="218" t="str">
         <f aca="false">DEC2HEX(D7,2)</f>
         <v>01</v>
       </c>
@@ -8533,11 +8527,11 @@
         <f aca="false">IF(E7=1,128,0)+IF(F7=1,64,0)+IF(G7=1,32,0)+IF(H7=1,16,0)+IF(I7=1,8,0)+IF(J7=1,4,0)+IF(K7=1,2,0)+IF(L7=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="191"/>
+      <c r="E7" s="188"/>
       <c r="F7" s="173"/>
       <c r="G7" s="173"/>
       <c r="H7" s="177"/>
-      <c r="I7" s="191" t="n">
+      <c r="I7" s="188" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="173" t="n">
@@ -8549,43 +8543,43 @@
       <c r="L7" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="222" t="s">
-        <v>240</v>
-      </c>
-      <c r="N7" s="220"/>
-      <c r="O7" s="222"/>
-      <c r="P7" s="224"/>
+      <c r="M7" s="219" t="s">
+        <v>242</v>
+      </c>
+      <c r="N7" s="217"/>
+      <c r="O7" s="219"/>
+      <c r="P7" s="221"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="225"/>
+      <c r="A8" s="222"/>
       <c r="B8" s="142"/>
       <c r="C8" s="17"/>
       <c r="D8" s="119"/>
       <c r="E8" s="49"/>
       <c r="F8" s="119"/>
       <c r="G8" s="119" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I8" s="49"/>
       <c r="J8" s="13"/>
       <c r="K8" s="119"/>
       <c r="L8" s="50"/>
-      <c r="M8" s="226"/>
+      <c r="M8" s="223"/>
       <c r="N8" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O8" s="227" t="s">
-        <v>234</v>
-      </c>
-      <c r="P8" s="228" t="s">
-        <v>241</v>
+        <v>235</v>
+      </c>
+      <c r="O8" s="224" t="s">
+        <v>236</v>
+      </c>
+      <c r="P8" s="225" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="225"/>
+      <c r="A9" s="222"/>
       <c r="B9" s="142"/>
       <c r="C9" s="17"/>
       <c r="D9" s="119"/>
@@ -8597,14 +8591,14 @@
       <c r="J9" s="13"/>
       <c r="K9" s="119"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="226"/>
-      <c r="O9" s="227"/>
-      <c r="P9" s="228"/>
+      <c r="M9" s="223"/>
+      <c r="O9" s="224"/>
+      <c r="P9" s="225"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="225"/>
+      <c r="A10" s="222"/>
       <c r="B10" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E10" s="146"/>
       <c r="F10" s="119"/>
@@ -8619,16 +8613,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="P10" s="229"/>
+        <v>240</v>
+      </c>
+      <c r="P10" s="226"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="219" t="s">
-        <v>242</v>
-      </c>
-      <c r="B11" s="220"/>
-      <c r="C11" s="221" t="str">
+      <c r="A11" s="216" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="217"/>
+      <c r="C11" s="218" t="str">
         <f aca="false">DEC2HEX(D11,2)</f>
         <v>02</v>
       </c>
@@ -8636,7 +8630,7 @@
         <f aca="false">IF(E11=1,128,0)+IF(F11=1,64,0)+IF(G11=1,32,0)+IF(H11=1,16,0)+IF(I11=1,8,0)+IF(J11=1,4,0)+IF(K11=1,2,0)+IF(L11=1,1,0)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="191"/>
+      <c r="E11" s="188"/>
       <c r="F11" s="173"/>
       <c r="G11" s="173"/>
       <c r="H11" s="177"/>
@@ -8652,43 +8646,43 @@
       <c r="L11" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="222" t="s">
-        <v>243</v>
-      </c>
-      <c r="N11" s="220"/>
-      <c r="O11" s="223"/>
-      <c r="P11" s="224"/>
+      <c r="M11" s="219" t="s">
+        <v>245</v>
+      </c>
+      <c r="N11" s="217"/>
+      <c r="O11" s="220"/>
+      <c r="P11" s="221"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A12" s="225"/>
+      <c r="A12" s="222"/>
       <c r="B12" s="142"/>
       <c r="C12" s="17"/>
       <c r="D12" s="119"/>
       <c r="E12" s="49"/>
       <c r="F12" s="119"/>
       <c r="G12" s="119" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I12" s="49"/>
       <c r="J12" s="13"/>
       <c r="K12" s="119"/>
       <c r="L12" s="50"/>
-      <c r="M12" s="226"/>
-      <c r="N12" s="226" t="s">
-        <v>244</v>
-      </c>
-      <c r="O12" s="227" t="s">
-        <v>234</v>
-      </c>
-      <c r="P12" s="230" t="s">
-        <v>245</v>
+      <c r="M12" s="223"/>
+      <c r="N12" s="223" t="s">
+        <v>246</v>
+      </c>
+      <c r="O12" s="224" t="s">
+        <v>236</v>
+      </c>
+      <c r="P12" s="227" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="225"/>
+      <c r="A13" s="222"/>
       <c r="B13" s="142"/>
       <c r="C13" s="17"/>
       <c r="D13" s="119"/>
@@ -8700,14 +8694,14 @@
       <c r="J13" s="13"/>
       <c r="K13" s="119"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="226"/>
-      <c r="O13" s="227"/>
-      <c r="P13" s="228"/>
+      <c r="M13" s="223"/>
+      <c r="O13" s="224"/>
+      <c r="P13" s="225"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="225"/>
+      <c r="A14" s="222"/>
       <c r="B14" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="119"/>
@@ -8717,23 +8711,23 @@
       <c r="J14" s="13"/>
       <c r="K14" s="119"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="226"/>
+      <c r="M14" s="223"/>
       <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="P14" s="229" t="s">
-        <v>247</v>
+        <v>248</v>
+      </c>
+      <c r="P14" s="226" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="219" t="s">
-        <v>248</v>
-      </c>
-      <c r="B15" s="220"/>
-      <c r="C15" s="221" t="str">
+      <c r="A15" s="216" t="s">
+        <v>250</v>
+      </c>
+      <c r="B15" s="217"/>
+      <c r="C15" s="218" t="str">
         <f aca="false">DEC2HEX(D15,2)</f>
         <v>03</v>
       </c>
@@ -8741,7 +8735,7 @@
         <f aca="false">IF(E15=1,128,0)+IF(F15=1,64,0)+IF(G15=1,32,0)+IF(H15=1,16,0)+IF(I15=1,8,0)+IF(J15=1,4,0)+IF(K15=1,2,0)+IF(L15=1,1,0)</f>
         <v>3</v>
       </c>
-      <c r="E15" s="191"/>
+      <c r="E15" s="188"/>
       <c r="F15" s="173"/>
       <c r="G15" s="173"/>
       <c r="H15" s="177"/>
@@ -8757,15 +8751,15 @@
       <c r="L15" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="222" t="s">
+      <c r="M15" s="219" t="s">
         <v>99</v>
       </c>
-      <c r="N15" s="220"/>
-      <c r="O15" s="222"/>
-      <c r="P15" s="224"/>
+      <c r="N15" s="217"/>
+      <c r="O15" s="219"/>
+      <c r="P15" s="221"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A16" s="225"/>
+      <c r="A16" s="222"/>
       <c r="B16" s="142"/>
       <c r="C16" s="17"/>
       <c r="D16" s="119"/>
@@ -8777,14 +8771,14 @@
       <c r="J16" s="13"/>
       <c r="K16" s="119"/>
       <c r="L16" s="50"/>
-      <c r="M16" s="226"/>
-      <c r="O16" s="227"/>
-      <c r="P16" s="228"/>
+      <c r="M16" s="223"/>
+      <c r="O16" s="224"/>
+      <c r="P16" s="225"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A17" s="225"/>
+      <c r="A17" s="222"/>
       <c r="B17" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="119"/>
@@ -8796,21 +8790,21 @@
       <c r="J17" s="13"/>
       <c r="K17" s="119"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="226"/>
+      <c r="M17" s="223"/>
       <c r="N17" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="O17" s="227" t="s">
-        <v>250</v>
-      </c>
-      <c r="P17" s="228" t="s">
         <v>251</v>
       </c>
+      <c r="O17" s="224" t="s">
+        <v>252</v>
+      </c>
+      <c r="P17" s="225" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="225"/>
+      <c r="A18" s="222"/>
       <c r="B18" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E18" s="146"/>
       <c r="F18" s="119"/>
@@ -8825,18 +8819,18 @@
         <v>1</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="P18" s="231" t="s">
-        <v>253</v>
+        <v>254</v>
+      </c>
+      <c r="P18" s="228" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="219" t="s">
-        <v>254</v>
-      </c>
-      <c r="B19" s="220"/>
-      <c r="C19" s="221" t="str">
+      <c r="A19" s="216" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="217"/>
+      <c r="C19" s="218" t="str">
         <f aca="false">DEC2HEX(D19,2)</f>
         <v>04</v>
       </c>
@@ -8844,7 +8838,7 @@
         <f aca="false">IF(E19=1,128,0)+IF(F19=1,64,0)+IF(G19=1,32,0)+IF(H19=1,16,0)+IF(I19=1,8,0)+IF(J19=1,4,0)+IF(K19=1,2,0)+IF(L19=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E19" s="191"/>
+      <c r="E19" s="188"/>
       <c r="F19" s="173"/>
       <c r="G19" s="173"/>
       <c r="H19" s="177"/>
@@ -8860,25 +8854,25 @@
       <c r="L19" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="222" t="s">
-        <v>255</v>
-      </c>
-      <c r="N19" s="220"/>
-      <c r="O19" s="222"/>
-      <c r="P19" s="224"/>
-    </row>
-    <row r="20" s="232" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="225"/>
+      <c r="M19" s="219" t="s">
+        <v>257</v>
+      </c>
+      <c r="N19" s="217"/>
+      <c r="O19" s="219"/>
+      <c r="P19" s="221"/>
+    </row>
+    <row r="20" s="229" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A20" s="222"/>
       <c r="B20" s="142"/>
       <c r="C20" s="20"/>
       <c r="D20" s="2"/>
       <c r="E20" s="146"/>
       <c r="F20" s="119"/>
       <c r="G20" s="119" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I20" s="119"/>
       <c r="J20" s="119"/>
@@ -8886,19 +8880,19 @@
       <c r="L20" s="50"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="P20" s="228"/>
+        <v>236</v>
+      </c>
+      <c r="P20" s="225"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="225"/>
+      <c r="A21" s="222"/>
       <c r="B21" s="142"/>
       <c r="E21" s="146"/>
       <c r="F21" s="119" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G21" s="119"/>
       <c r="H21" s="50"/>
@@ -8907,16 +8901,16 @@
       <c r="K21" s="119"/>
       <c r="L21" s="50"/>
       <c r="M21" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="142"/>
-      <c r="P21" s="228" t="s">
-        <v>257</v>
+      <c r="P21" s="225" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="225"/>
+      <c r="A22" s="222"/>
       <c r="B22" s="142"/>
       <c r="E22" s="146"/>
       <c r="F22" s="119"/>
@@ -8928,41 +8922,41 @@
       <c r="L22" s="50"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O22" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="P22" s="228"/>
+      <c r="P22" s="225"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="233"/>
-      <c r="B23" s="234"/>
-      <c r="C23" s="235"/>
-      <c r="D23" s="236"/>
-      <c r="E23" s="237" t="s">
-        <v>259</v>
-      </c>
-      <c r="F23" s="236"/>
-      <c r="G23" s="236"/>
-      <c r="H23" s="238"/>
-      <c r="I23" s="237"/>
-      <c r="J23" s="239"/>
-      <c r="K23" s="236"/>
-      <c r="L23" s="238"/>
-      <c r="M23" s="240" t="s">
-        <v>260</v>
-      </c>
-      <c r="N23" s="232"/>
-      <c r="O23" s="241"/>
-      <c r="P23" s="242" t="s">
+      <c r="A23" s="230"/>
+      <c r="B23" s="231"/>
+      <c r="C23" s="232"/>
+      <c r="D23" s="233"/>
+      <c r="E23" s="234" t="s">
         <v>261</v>
       </c>
+      <c r="F23" s="233"/>
+      <c r="G23" s="233"/>
+      <c r="H23" s="235"/>
+      <c r="I23" s="234"/>
+      <c r="J23" s="236"/>
+      <c r="K23" s="233"/>
+      <c r="L23" s="235"/>
+      <c r="M23" s="237" t="s">
+        <v>262</v>
+      </c>
+      <c r="N23" s="229"/>
+      <c r="O23" s="238"/>
+      <c r="P23" s="239" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="225"/>
+      <c r="A24" s="222"/>
       <c r="B24" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E24" s="146"/>
       <c r="F24" s="119"/>
@@ -8975,18 +8969,18 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="P24" s="228" t="s">
-        <v>263</v>
+        <v>264</v>
+      </c>
+      <c r="P24" s="225" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="219" t="s">
-        <v>264</v>
-      </c>
-      <c r="B25" s="220"/>
-      <c r="C25" s="221" t="str">
+      <c r="A25" s="216" t="s">
+        <v>266</v>
+      </c>
+      <c r="B25" s="217"/>
+      <c r="C25" s="218" t="str">
         <f aca="false">DEC2HEX(D25,2)</f>
         <v>05</v>
       </c>
@@ -8994,7 +8988,7 @@
         <f aca="false">IF(E25=1,128,0)+IF(F25=1,64,0)+IF(G25=1,32,0)+IF(H25=1,16,0)+IF(I25=1,8,0)+IF(J25=1,4,0)+IF(K25=1,2,0)+IF(L25=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E25" s="191"/>
+      <c r="E25" s="188"/>
       <c r="F25" s="173"/>
       <c r="G25" s="173"/>
       <c r="H25" s="177"/>
@@ -9010,19 +9004,19 @@
       <c r="L25" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M25" s="222" t="s">
-        <v>265</v>
-      </c>
-      <c r="N25" s="220"/>
-      <c r="O25" s="222"/>
-      <c r="P25" s="224"/>
+      <c r="M25" s="219" t="s">
+        <v>267</v>
+      </c>
+      <c r="N25" s="217"/>
+      <c r="O25" s="219"/>
+      <c r="P25" s="221"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="225"/>
+      <c r="A26" s="222"/>
       <c r="B26" s="142"/>
       <c r="E26" s="146"/>
       <c r="F26" s="119" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G26" s="119"/>
       <c r="H26" s="50"/>
@@ -9031,16 +9025,16 @@
       <c r="K26" s="119"/>
       <c r="L26" s="50"/>
       <c r="M26" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="142"/>
-      <c r="P26" s="228" t="s">
-        <v>266</v>
+      <c r="P26" s="225" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="225"/>
+      <c r="A27" s="222"/>
       <c r="B27" s="142"/>
       <c r="E27" s="146"/>
       <c r="F27" s="119"/>
@@ -9052,15 +9046,15 @@
       <c r="L27" s="50"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O27" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="P27" s="228"/>
+      <c r="P27" s="225"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="225"/>
+      <c r="A28" s="222"/>
       <c r="B28" s="142"/>
       <c r="C28" s="17"/>
       <c r="D28" s="119"/>
@@ -9072,13 +9066,13 @@
       <c r="J28" s="13"/>
       <c r="K28" s="119"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="226"/>
-      <c r="O28" s="227"/>
+      <c r="M28" s="223"/>
+      <c r="O28" s="224"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="225"/>
+      <c r="A29" s="222"/>
       <c r="B29" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="119"/>
@@ -9090,21 +9084,21 @@
       <c r="J29" s="13"/>
       <c r="K29" s="119"/>
       <c r="L29" s="50"/>
-      <c r="M29" s="226"/>
+      <c r="M29" s="223"/>
       <c r="N29" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="O29" s="227" t="s">
-        <v>250</v>
-      </c>
-      <c r="P29" s="228" t="s">
         <v>251</v>
       </c>
+      <c r="O29" s="224" t="s">
+        <v>252</v>
+      </c>
+      <c r="P29" s="225" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A30" s="225"/>
+      <c r="A30" s="222"/>
       <c r="B30" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E30" s="146"/>
       <c r="F30" s="119"/>
@@ -9119,18 +9113,18 @@
         <v>1</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="P30" s="231" t="s">
-        <v>253</v>
+        <v>254</v>
+      </c>
+      <c r="P30" s="228" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="219" t="s">
-        <v>267</v>
-      </c>
-      <c r="B31" s="220"/>
-      <c r="C31" s="221" t="str">
+      <c r="A31" s="216" t="s">
+        <v>269</v>
+      </c>
+      <c r="B31" s="217"/>
+      <c r="C31" s="218" t="str">
         <f aca="false">DEC2HEX(D31,2)</f>
         <v>06</v>
       </c>
@@ -9138,7 +9132,7 @@
         <f aca="false">IF(E31=1,128,0)+IF(F31=1,64,0)+IF(G31=1,32,0)+IF(H31=1,16,0)+IF(I31=1,8,0)+IF(J31=1,4,0)+IF(K31=1,2,0)+IF(L31=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="E31" s="191"/>
+      <c r="E31" s="188"/>
       <c r="F31" s="173"/>
       <c r="G31" s="173"/>
       <c r="H31" s="177"/>
@@ -9154,17 +9148,17 @@
       <c r="L31" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="222" t="s">
-        <v>268</v>
-      </c>
-      <c r="N31" s="220"/>
-      <c r="O31" s="222"/>
-      <c r="P31" s="243" t="s">
-        <v>269</v>
+      <c r="M31" s="219" t="s">
+        <v>270</v>
+      </c>
+      <c r="N31" s="217"/>
+      <c r="O31" s="219"/>
+      <c r="P31" s="240" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A32" s="225"/>
+      <c r="A32" s="222"/>
       <c r="E32" s="146"/>
       <c r="F32" s="119"/>
       <c r="G32" s="119" t="n">
@@ -9178,12 +9172,12 @@
       <c r="K32" s="119"/>
       <c r="L32" s="50"/>
       <c r="M32" s="142" t="s">
-        <v>270</v>
-      </c>
-      <c r="P32" s="228"/>
+        <v>272</v>
+      </c>
+      <c r="P32" s="225"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="225"/>
+      <c r="A33" s="222"/>
       <c r="E33" s="146"/>
       <c r="F33" s="119"/>
       <c r="G33" s="119" t="n">
@@ -9196,13 +9190,13 @@
       <c r="J33" s="119"/>
       <c r="K33" s="119"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="226" t="s">
-        <v>271</v>
-      </c>
-      <c r="P33" s="228"/>
+      <c r="M33" s="223" t="s">
+        <v>273</v>
+      </c>
+      <c r="P33" s="225"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="225"/>
+      <c r="A34" s="222"/>
       <c r="E34" s="146"/>
       <c r="F34" s="119"/>
       <c r="G34" s="119" t="n">
@@ -9215,13 +9209,13 @@
       <c r="J34" s="119"/>
       <c r="K34" s="119"/>
       <c r="L34" s="50"/>
-      <c r="M34" s="226" t="s">
-        <v>272</v>
-      </c>
-      <c r="P34" s="228"/>
+      <c r="M34" s="223" t="s">
+        <v>274</v>
+      </c>
+      <c r="P34" s="225"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="225"/>
+      <c r="A35" s="222"/>
       <c r="E35" s="146"/>
       <c r="F35" s="119"/>
       <c r="G35" s="119" t="n">
@@ -9235,15 +9229,15 @@
       <c r="K35" s="119"/>
       <c r="L35" s="50"/>
       <c r="M35" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="P35" s="228"/>
+        <v>275</v>
+      </c>
+      <c r="P35" s="225"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="225"/>
+      <c r="A36" s="222"/>
       <c r="E36" s="146"/>
       <c r="F36" s="119" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G36" s="119"/>
       <c r="H36" s="50"/>
@@ -9252,14 +9246,14 @@
       <c r="K36" s="119"/>
       <c r="L36" s="50"/>
       <c r="M36" s="142" t="s">
-        <v>275</v>
-      </c>
-      <c r="P36" s="228" t="s">
-        <v>276</v>
+        <v>277</v>
+      </c>
+      <c r="P36" s="225" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="225"/>
+      <c r="A37" s="222"/>
       <c r="B37" s="142"/>
       <c r="C37" s="17"/>
       <c r="D37" s="119"/>
@@ -9271,14 +9265,14 @@
       <c r="J37" s="13"/>
       <c r="K37" s="119"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="226"/>
-      <c r="O37" s="227"/>
-      <c r="P37" s="228"/>
+      <c r="M37" s="223"/>
+      <c r="O37" s="224"/>
+      <c r="P37" s="225"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A38" s="225"/>
+      <c r="A38" s="222"/>
       <c r="B38" s="142" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E38" s="146"/>
       <c r="F38" s="119"/>
@@ -9290,18 +9284,18 @@
       <c r="L38" s="50"/>
       <c r="M38" s="142"/>
       <c r="O38" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="P38" s="228" t="s">
-        <v>278</v>
+        <v>279</v>
+      </c>
+      <c r="P38" s="225" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="219" t="s">
-        <v>279</v>
-      </c>
-      <c r="B39" s="220"/>
-      <c r="C39" s="221" t="str">
+      <c r="A39" s="216" t="s">
+        <v>281</v>
+      </c>
+      <c r="B39" s="217"/>
+      <c r="C39" s="218" t="str">
         <f aca="false">DEC2HEX(D39,2)</f>
         <v>07</v>
       </c>
@@ -9309,7 +9303,7 @@
         <f aca="false">IF(E39=1,128,0)+IF(F39=1,64,0)+IF(G39=1,32,0)+IF(H39=1,16,0)+IF(I39=1,8,0)+IF(J39=1,4,0)+IF(K39=1,2,0)+IF(L39=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="E39" s="191"/>
+      <c r="E39" s="188"/>
       <c r="F39" s="173"/>
       <c r="G39" s="173"/>
       <c r="H39" s="177"/>
@@ -9325,15 +9319,15 @@
       <c r="L39" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M39" s="222" t="s">
-        <v>280</v>
-      </c>
-      <c r="N39" s="220"/>
-      <c r="O39" s="222"/>
-      <c r="P39" s="224"/>
+      <c r="M39" s="219" t="s">
+        <v>282</v>
+      </c>
+      <c r="N39" s="217"/>
+      <c r="O39" s="219"/>
+      <c r="P39" s="221"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="225"/>
+      <c r="A40" s="222"/>
       <c r="E40" s="146"/>
       <c r="F40" s="119"/>
       <c r="G40" s="119" t="n">
@@ -9347,14 +9341,14 @@
       <c r="K40" s="119"/>
       <c r="L40" s="50"/>
       <c r="M40" s="142" t="s">
-        <v>281</v>
-      </c>
-      <c r="P40" s="230" t="s">
-        <v>282</v>
+        <v>283</v>
+      </c>
+      <c r="P40" s="227" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="225"/>
+      <c r="A41" s="222"/>
       <c r="E41" s="146"/>
       <c r="F41" s="119"/>
       <c r="G41" s="119" t="n">
@@ -9367,15 +9361,15 @@
       <c r="J41" s="119"/>
       <c r="K41" s="119"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="226" t="s">
-        <v>271</v>
-      </c>
-      <c r="P41" s="230" t="s">
-        <v>283</v>
+      <c r="M41" s="223" t="s">
+        <v>273</v>
+      </c>
+      <c r="P41" s="227" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="225"/>
+      <c r="A42" s="222"/>
       <c r="E42" s="146"/>
       <c r="F42" s="119"/>
       <c r="G42" s="119" t="n">
@@ -9388,15 +9382,15 @@
       <c r="J42" s="119"/>
       <c r="K42" s="119"/>
       <c r="L42" s="50"/>
-      <c r="M42" s="226" t="s">
-        <v>272</v>
-      </c>
-      <c r="P42" s="230" t="s">
-        <v>284</v>
+      <c r="M42" s="223" t="s">
+        <v>274</v>
+      </c>
+      <c r="P42" s="227" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="225"/>
+      <c r="A43" s="222"/>
       <c r="E43" s="146"/>
       <c r="F43" s="119"/>
       <c r="G43" s="119" t="n">
@@ -9410,14 +9404,14 @@
       <c r="K43" s="119"/>
       <c r="L43" s="50"/>
       <c r="M43" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="P43" s="230" t="s">
-        <v>285</v>
+        <v>275</v>
+      </c>
+      <c r="P43" s="227" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="225"/>
+      <c r="A44" s="222"/>
       <c r="E44" s="146"/>
       <c r="F44" s="119"/>
       <c r="G44" s="119"/>
@@ -9428,12 +9422,12 @@
       <c r="L44" s="50"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="244" t="s">
-        <v>286</v>
+      <c r="P44" s="241" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A45" s="225"/>
+      <c r="A45" s="222"/>
       <c r="E45" s="146"/>
       <c r="F45" s="119"/>
       <c r="G45" s="119"/>
@@ -9444,12 +9438,12 @@
       <c r="L45" s="50"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="244" t="s">
-        <v>287</v>
+      <c r="P45" s="241" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A46" s="225"/>
+      <c r="A46" s="222"/>
       <c r="E46" s="146"/>
       <c r="F46" s="119"/>
       <c r="G46" s="119"/>
@@ -9460,12 +9454,12 @@
       <c r="L46" s="50"/>
       <c r="M46" s="10"/>
       <c r="O46" s="1"/>
-      <c r="P46" s="244" t="s">
-        <v>288</v>
+      <c r="P46" s="241" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="225"/>
+      <c r="A47" s="222"/>
       <c r="B47" s="142"/>
       <c r="C47" s="17"/>
       <c r="D47" s="119"/>
@@ -9477,14 +9471,14 @@
       <c r="J47" s="13"/>
       <c r="K47" s="119"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="226"/>
-      <c r="O47" s="227"/>
-      <c r="P47" s="228"/>
+      <c r="M47" s="223"/>
+      <c r="O47" s="224"/>
+      <c r="P47" s="225"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="225"/>
-      <c r="B48" s="226" t="s">
-        <v>237</v>
+      <c r="A48" s="222"/>
+      <c r="B48" s="223" t="s">
+        <v>239</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="119"/>
@@ -9496,25 +9490,25 @@
       <c r="J48" s="13"/>
       <c r="K48" s="119"/>
       <c r="L48" s="50"/>
-      <c r="M48" s="226"/>
+      <c r="M48" s="223"/>
       <c r="N48" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="O48" s="227" t="s">
-        <v>290</v>
-      </c>
-      <c r="P48" s="228" t="s">
         <v>291</v>
       </c>
+      <c r="O48" s="224" t="s">
+        <v>292</v>
+      </c>
+      <c r="P48" s="225" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A49" s="245"/>
-      <c r="B49" s="226" t="s">
-        <v>237</v>
-      </c>
-      <c r="C49" s="246"/>
+      <c r="A49" s="242"/>
+      <c r="B49" s="223" t="s">
+        <v>239</v>
+      </c>
+      <c r="C49" s="243"/>
       <c r="D49" s="152"/>
-      <c r="E49" s="247"/>
+      <c r="E49" s="244"/>
       <c r="F49" s="152"/>
       <c r="G49" s="152"/>
       <c r="H49" s="155"/>
@@ -9522,21 +9516,21 @@
       <c r="J49" s="152"/>
       <c r="K49" s="152"/>
       <c r="L49" s="155"/>
-      <c r="M49" s="248"/>
+      <c r="M49" s="245"/>
       <c r="N49" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="P49" s="231" t="s">
-        <v>253</v>
+        <v>291</v>
+      </c>
+      <c r="P49" s="228" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="219"/>
-      <c r="B50" s="220"/>
-      <c r="C50" s="221" t="str">
+      <c r="A50" s="216"/>
+      <c r="B50" s="217"/>
+      <c r="C50" s="218" t="str">
         <f aca="false">DEC2HEX(D50,2)</f>
         <v>08</v>
       </c>
@@ -9544,7 +9538,7 @@
         <f aca="false">IF(E50=1,128,0)+IF(F50=1,64,0)+IF(G50=1,32,0)+IF(H50=1,16,0)+IF(I50=1,8,0)+IF(J50=1,4,0)+IF(K50=1,2,0)+IF(L50=1,1,0)</f>
         <v>8</v>
       </c>
-      <c r="E50" s="191"/>
+      <c r="E50" s="188"/>
       <c r="F50" s="173"/>
       <c r="G50" s="173"/>
       <c r="H50" s="177"/>
@@ -9560,13 +9554,13 @@
       <c r="L50" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="222"/>
-      <c r="N50" s="220"/>
-      <c r="O50" s="222"/>
-      <c r="P50" s="224"/>
+      <c r="M50" s="219"/>
+      <c r="N50" s="217"/>
+      <c r="O50" s="219"/>
+      <c r="P50" s="221"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="225"/>
+      <c r="A51" s="222"/>
       <c r="B51" s="142"/>
       <c r="C51" s="17"/>
       <c r="D51" s="119"/>
@@ -9578,14 +9572,14 @@
       <c r="J51" s="13"/>
       <c r="K51" s="119"/>
       <c r="L51" s="50"/>
-      <c r="M51" s="226"/>
-      <c r="O51" s="227"/>
-      <c r="P51" s="228"/>
+      <c r="M51" s="223"/>
+      <c r="O51" s="224"/>
+      <c r="P51" s="225"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="219"/>
-      <c r="B52" s="220"/>
-      <c r="C52" s="221" t="str">
+      <c r="A52" s="216"/>
+      <c r="B52" s="217"/>
+      <c r="C52" s="218" t="str">
         <f aca="false">DEC2HEX(D52,2)</f>
         <v>09</v>
       </c>
@@ -9593,7 +9587,7 @@
         <f aca="false">IF(E52=1,128,0)+IF(F52=1,64,0)+IF(G52=1,32,0)+IF(H52=1,16,0)+IF(I52=1,8,0)+IF(J52=1,4,0)+IF(K52=1,2,0)+IF(L52=1,1,0)</f>
         <v>9</v>
       </c>
-      <c r="E52" s="191"/>
+      <c r="E52" s="188"/>
       <c r="F52" s="173"/>
       <c r="G52" s="173"/>
       <c r="H52" s="177"/>
@@ -9609,13 +9603,13 @@
       <c r="L52" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M52" s="222"/>
-      <c r="N52" s="220"/>
-      <c r="O52" s="222"/>
-      <c r="P52" s="224"/>
+      <c r="M52" s="219"/>
+      <c r="N52" s="217"/>
+      <c r="O52" s="219"/>
+      <c r="P52" s="221"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="225"/>
+      <c r="A53" s="222"/>
       <c r="B53" s="142"/>
       <c r="C53" s="17"/>
       <c r="D53" s="119"/>
@@ -9627,16 +9621,16 @@
       <c r="J53" s="13"/>
       <c r="K53" s="119"/>
       <c r="L53" s="50"/>
-      <c r="M53" s="226"/>
-      <c r="O53" s="227"/>
-      <c r="P53" s="228"/>
+      <c r="M53" s="223"/>
+      <c r="O53" s="224"/>
+      <c r="P53" s="225"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="219" t="s">
-        <v>292</v>
-      </c>
-      <c r="B54" s="220"/>
-      <c r="C54" s="221" t="str">
+      <c r="A54" s="216" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" s="217"/>
+      <c r="C54" s="218" t="str">
         <f aca="false">DEC2HEX(D54,2)</f>
         <v>0A</v>
       </c>
@@ -9644,7 +9638,7 @@
         <f aca="false">IF(E54=1,128,0)+IF(F54=1,64,0)+IF(G54=1,32,0)+IF(H54=1,16,0)+IF(I54=1,8,0)+IF(J54=1,4,0)+IF(K54=1,2,0)+IF(L54=1,1,0)</f>
         <v>10</v>
       </c>
-      <c r="E54" s="191"/>
+      <c r="E54" s="188"/>
       <c r="F54" s="173"/>
       <c r="G54" s="173"/>
       <c r="H54" s="177"/>
@@ -9660,15 +9654,15 @@
       <c r="L54" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="222" t="s">
-        <v>293</v>
-      </c>
-      <c r="N54" s="220"/>
-      <c r="O54" s="222"/>
-      <c r="P54" s="224"/>
+      <c r="M54" s="219" t="s">
+        <v>295</v>
+      </c>
+      <c r="N54" s="217"/>
+      <c r="O54" s="219"/>
+      <c r="P54" s="221"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="225"/>
+      <c r="A55" s="222"/>
       <c r="B55" s="142"/>
       <c r="C55" s="17"/>
       <c r="D55" s="119"/>
@@ -9680,14 +9674,14 @@
       <c r="J55" s="13"/>
       <c r="K55" s="119"/>
       <c r="L55" s="50"/>
-      <c r="M55" s="226"/>
-      <c r="O55" s="227"/>
-      <c r="P55" s="228"/>
+      <c r="M55" s="223"/>
+      <c r="O55" s="224"/>
+      <c r="P55" s="225"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A56" s="225"/>
-      <c r="B56" s="226" t="s">
-        <v>237</v>
+      <c r="A56" s="222"/>
+      <c r="B56" s="223" t="s">
+        <v>239</v>
       </c>
       <c r="E56" s="146"/>
       <c r="F56" s="119"/>
@@ -9702,16 +9696,16 @@
         <v>1</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="P56" s="228" t="s">
-        <v>295</v>
+        <v>296</v>
+      </c>
+      <c r="P56" s="225" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="219"/>
-      <c r="B57" s="220"/>
-      <c r="C57" s="221" t="str">
+      <c r="A57" s="216"/>
+      <c r="B57" s="217"/>
+      <c r="C57" s="218" t="str">
         <f aca="false">DEC2HEX(D57,2)</f>
         <v>0B</v>
       </c>
@@ -9719,7 +9713,7 @@
         <f aca="false">IF(E57=1,128,0)+IF(F57=1,64,0)+IF(G57=1,32,0)+IF(H57=1,16,0)+IF(I57=1,8,0)+IF(J57=1,4,0)+IF(K57=1,2,0)+IF(L57=1,1,0)</f>
         <v>11</v>
       </c>
-      <c r="E57" s="191"/>
+      <c r="E57" s="188"/>
       <c r="F57" s="173"/>
       <c r="G57" s="173"/>
       <c r="H57" s="177"/>
@@ -9735,13 +9729,13 @@
       <c r="L57" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M57" s="222"/>
-      <c r="N57" s="220"/>
-      <c r="O57" s="222"/>
-      <c r="P57" s="224"/>
+      <c r="M57" s="219"/>
+      <c r="N57" s="217"/>
+      <c r="O57" s="219"/>
+      <c r="P57" s="221"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="225"/>
+      <c r="A58" s="222"/>
       <c r="B58" s="142"/>
       <c r="C58" s="17"/>
       <c r="D58" s="119"/>
@@ -9753,14 +9747,14 @@
       <c r="J58" s="13"/>
       <c r="K58" s="119"/>
       <c r="L58" s="50"/>
-      <c r="M58" s="226"/>
-      <c r="O58" s="227"/>
-      <c r="P58" s="228"/>
+      <c r="M58" s="223"/>
+      <c r="O58" s="224"/>
+      <c r="P58" s="225"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="219"/>
-      <c r="B59" s="220"/>
-      <c r="C59" s="221" t="str">
+      <c r="A59" s="216"/>
+      <c r="B59" s="217"/>
+      <c r="C59" s="218" t="str">
         <f aca="false">DEC2HEX(D59,2)</f>
         <v>0C</v>
       </c>
@@ -9768,7 +9762,7 @@
         <f aca="false">IF(E59=1,128,0)+IF(F59=1,64,0)+IF(G59=1,32,0)+IF(H59=1,16,0)+IF(I59=1,8,0)+IF(J59=1,4,0)+IF(K59=1,2,0)+IF(L59=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="E59" s="191"/>
+      <c r="E59" s="188"/>
       <c r="F59" s="173"/>
       <c r="G59" s="173"/>
       <c r="H59" s="177"/>
@@ -9784,13 +9778,13 @@
       <c r="L59" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M59" s="220"/>
-      <c r="N59" s="220"/>
-      <c r="O59" s="222"/>
-      <c r="P59" s="224"/>
+      <c r="M59" s="217"/>
+      <c r="N59" s="217"/>
+      <c r="O59" s="219"/>
+      <c r="P59" s="221"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A60" s="225"/>
+      <c r="A60" s="222"/>
       <c r="E60" s="146"/>
       <c r="F60" s="119"/>
       <c r="G60" s="119"/>
@@ -9799,15 +9793,15 @@
       <c r="J60" s="119"/>
       <c r="K60" s="119"/>
       <c r="L60" s="50"/>
-      <c r="M60" s="226"/>
-      <c r="N60" s="226"/>
+      <c r="M60" s="223"/>
+      <c r="N60" s="223"/>
       <c r="O60" s="142"/>
-      <c r="P60" s="228"/>
+      <c r="P60" s="225"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="219"/>
-      <c r="B61" s="220"/>
-      <c r="C61" s="221" t="str">
+      <c r="A61" s="216"/>
+      <c r="B61" s="217"/>
+      <c r="C61" s="218" t="str">
         <f aca="false">DEC2HEX(D61,2)</f>
         <v>0D</v>
       </c>
@@ -9815,7 +9809,7 @@
         <f aca="false">IF(E61=1,128,0)+IF(F61=1,64,0)+IF(G61=1,32,0)+IF(H61=1,16,0)+IF(I61=1,8,0)+IF(J61=1,4,0)+IF(K61=1,2,0)+IF(L61=1,1,0)</f>
         <v>13</v>
       </c>
-      <c r="E61" s="191"/>
+      <c r="E61" s="188"/>
       <c r="F61" s="173"/>
       <c r="G61" s="173"/>
       <c r="H61" s="177"/>
@@ -9831,13 +9825,13 @@
       <c r="L61" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M61" s="220"/>
-      <c r="N61" s="220"/>
-      <c r="O61" s="222"/>
-      <c r="P61" s="224"/>
+      <c r="M61" s="217"/>
+      <c r="N61" s="217"/>
+      <c r="O61" s="219"/>
+      <c r="P61" s="221"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A62" s="225"/>
+      <c r="A62" s="222"/>
       <c r="E62" s="146"/>
       <c r="F62" s="119"/>
       <c r="G62" s="119"/>
@@ -9846,15 +9840,15 @@
       <c r="J62" s="119"/>
       <c r="K62" s="119"/>
       <c r="L62" s="50"/>
-      <c r="M62" s="226"/>
-      <c r="N62" s="226"/>
+      <c r="M62" s="223"/>
+      <c r="N62" s="223"/>
       <c r="O62" s="142"/>
-      <c r="P62" s="228"/>
+      <c r="P62" s="225"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="219"/>
-      <c r="B63" s="220"/>
-      <c r="C63" s="221" t="str">
+      <c r="A63" s="216"/>
+      <c r="B63" s="217"/>
+      <c r="C63" s="218" t="str">
         <f aca="false">DEC2HEX(D63,2)</f>
         <v>0E</v>
       </c>
@@ -9862,7 +9856,7 @@
         <f aca="false">IF(E63=1,128,0)+IF(F63=1,64,0)+IF(G63=1,32,0)+IF(H63=1,16,0)+IF(I63=1,8,0)+IF(J63=1,4,0)+IF(K63=1,2,0)+IF(L63=1,1,0)</f>
         <v>14</v>
       </c>
-      <c r="E63" s="191"/>
+      <c r="E63" s="188"/>
       <c r="F63" s="173"/>
       <c r="G63" s="173"/>
       <c r="H63" s="177"/>
@@ -9878,13 +9872,13 @@
       <c r="L63" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M63" s="220"/>
-      <c r="N63" s="220"/>
-      <c r="O63" s="222"/>
-      <c r="P63" s="224"/>
+      <c r="M63" s="217"/>
+      <c r="N63" s="217"/>
+      <c r="O63" s="219"/>
+      <c r="P63" s="221"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="225"/>
+      <c r="A64" s="222"/>
       <c r="E64" s="146"/>
       <c r="F64" s="119"/>
       <c r="G64" s="119"/>
@@ -9893,15 +9887,15 @@
       <c r="J64" s="119"/>
       <c r="K64" s="119"/>
       <c r="L64" s="50"/>
-      <c r="M64" s="226"/>
-      <c r="N64" s="226"/>
+      <c r="M64" s="223"/>
+      <c r="N64" s="223"/>
       <c r="O64" s="142"/>
-      <c r="P64" s="228"/>
+      <c r="P64" s="225"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="219"/>
-      <c r="B65" s="220"/>
-      <c r="C65" s="221" t="str">
+      <c r="A65" s="216"/>
+      <c r="B65" s="217"/>
+      <c r="C65" s="218" t="str">
         <f aca="false">DEC2HEX(D65,2)</f>
         <v>0F</v>
       </c>
@@ -9909,7 +9903,7 @@
         <f aca="false">IF(E65=1,128,0)+IF(F65=1,64,0)+IF(G65=1,32,0)+IF(H65=1,16,0)+IF(I65=1,8,0)+IF(J65=1,4,0)+IF(K65=1,2,0)+IF(L65=1,1,0)</f>
         <v>15</v>
       </c>
-      <c r="E65" s="191"/>
+      <c r="E65" s="188"/>
       <c r="F65" s="173"/>
       <c r="G65" s="173"/>
       <c r="H65" s="177"/>
@@ -9925,13 +9919,13 @@
       <c r="L65" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M65" s="220"/>
-      <c r="N65" s="220"/>
-      <c r="O65" s="222"/>
-      <c r="P65" s="224"/>
+      <c r="M65" s="217"/>
+      <c r="N65" s="217"/>
+      <c r="O65" s="219"/>
+      <c r="P65" s="221"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A66" s="225"/>
+      <c r="A66" s="222"/>
       <c r="E66" s="146"/>
       <c r="F66" s="119"/>
       <c r="G66" s="119"/>
@@ -9940,13 +9934,13 @@
       <c r="J66" s="119"/>
       <c r="K66" s="119"/>
       <c r="L66" s="50"/>
-      <c r="M66" s="226"/>
-      <c r="N66" s="226"/>
+      <c r="M66" s="223"/>
+      <c r="N66" s="223"/>
       <c r="O66" s="142"/>
-      <c r="P66" s="228"/>
+      <c r="P66" s="225"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="225"/>
+      <c r="A67" s="222"/>
       <c r="E67" s="146"/>
       <c r="F67" s="119"/>
       <c r="G67" s="119"/>
@@ -9955,13 +9949,13 @@
       <c r="J67" s="119"/>
       <c r="K67" s="119"/>
       <c r="L67" s="50"/>
-      <c r="M67" s="226"/>
-      <c r="N67" s="226"/>
+      <c r="M67" s="223"/>
+      <c r="N67" s="223"/>
       <c r="O67" s="142"/>
-      <c r="P67" s="228"/>
+      <c r="P67" s="225"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="225"/>
+      <c r="A68" s="222"/>
       <c r="E68" s="146"/>
       <c r="F68" s="119"/>
       <c r="G68" s="119"/>
@@ -9970,103 +9964,103 @@
       <c r="J68" s="119"/>
       <c r="K68" s="119"/>
       <c r="L68" s="50"/>
-      <c r="M68" s="226"/>
-      <c r="N68" s="226"/>
+      <c r="M68" s="223"/>
+      <c r="N68" s="223"/>
       <c r="O68" s="142"/>
-      <c r="P68" s="228"/>
+      <c r="P68" s="225"/>
     </row>
     <row r="69" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="249" t="s">
-        <v>296</v>
+      <c r="A69" s="246" t="s">
+        <v>298</v>
       </c>
       <c r="E69" s="146"/>
-      <c r="F69" s="203" t="s">
-        <v>297</v>
-      </c>
-      <c r="G69" s="203" t="s">
-        <v>298</v>
-      </c>
-      <c r="H69" s="203" t="s">
-        <v>298</v>
-      </c>
-      <c r="I69" s="203"/>
-      <c r="J69" s="203"/>
-      <c r="K69" s="203" t="s">
+      <c r="F69" s="200" t="s">
         <v>299</v>
       </c>
-      <c r="L69" s="203" t="s">
+      <c r="G69" s="200" t="s">
         <v>300</v>
       </c>
-      <c r="M69" s="226"/>
-      <c r="N69" s="226"/>
+      <c r="H69" s="200" t="s">
+        <v>300</v>
+      </c>
+      <c r="I69" s="200"/>
+      <c r="J69" s="200"/>
+      <c r="K69" s="200" t="s">
+        <v>301</v>
+      </c>
+      <c r="L69" s="200" t="s">
+        <v>302</v>
+      </c>
+      <c r="M69" s="223"/>
+      <c r="N69" s="223"/>
       <c r="O69" s="142"/>
-      <c r="P69" s="228"/>
+      <c r="P69" s="225"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="219" t="s">
+      <c r="A70" s="216" t="s">
         <v>216</v>
       </c>
-      <c r="B70" s="222"/>
-      <c r="C70" s="221"/>
+      <c r="B70" s="219"/>
+      <c r="C70" s="218"/>
       <c r="D70" s="173"/>
-      <c r="E70" s="191"/>
+      <c r="E70" s="188"/>
       <c r="F70" s="173"/>
       <c r="G70" s="173"/>
       <c r="H70" s="177"/>
-      <c r="I70" s="191"/>
+      <c r="I70" s="188"/>
       <c r="J70" s="173"/>
       <c r="K70" s="173"/>
       <c r="L70" s="177"/>
-      <c r="M70" s="220"/>
-      <c r="N70" s="220"/>
-      <c r="O70" s="222"/>
-      <c r="P70" s="224"/>
+      <c r="M70" s="217"/>
+      <c r="N70" s="217"/>
+      <c r="O70" s="219"/>
+      <c r="P70" s="221"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="250" t="s">
-        <v>301</v>
-      </c>
-      <c r="B71" s="194"/>
-      <c r="C71" s="215" t="str">
+      <c r="A71" s="247" t="s">
+        <v>303</v>
+      </c>
+      <c r="B71" s="191"/>
+      <c r="C71" s="212" t="str">
         <f aca="false">DEC2HEX(D71,2)</f>
         <v>00</v>
       </c>
-      <c r="D71" s="196" t="n">
+      <c r="D71" s="193" t="n">
         <f aca="false">IF(E71=1,128,0)+IF(F71=1,64,0)+IF(G71=1,32,0)+IF(H71=1,16,0)+IF(I71=1,8,0)+IF(J71=1,4,0)+IF(K71=1,2,0)+IF(L71=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E71" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="254"/>
-      <c r="N71" s="254"/>
-      <c r="O71" s="194"/>
-      <c r="P71" s="255"/>
+      <c r="E71" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="251"/>
+      <c r="N71" s="251"/>
+      <c r="O71" s="191"/>
+      <c r="P71" s="252"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="225" t="s">
-        <v>302</v>
+      <c r="A72" s="222" t="s">
+        <v>304</v>
       </c>
       <c r="B72" s="142"/>
       <c r="C72" s="20" t="str">
@@ -10101,14 +10095,14 @@
       <c r="L72" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="226"/>
-      <c r="N72" s="226"/>
+      <c r="M72" s="223"/>
+      <c r="N72" s="223"/>
       <c r="O72" s="142"/>
-      <c r="P72" s="228"/>
+      <c r="P72" s="225"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="225" t="s">
-        <v>303</v>
+      <c r="A73" s="222" t="s">
+        <v>305</v>
       </c>
       <c r="B73" s="142"/>
       <c r="C73" s="20" t="str">
@@ -10143,17 +10137,17 @@
       <c r="L73" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="226"/>
-      <c r="N73" s="226"/>
+      <c r="M73" s="223"/>
+      <c r="N73" s="223"/>
       <c r="O73" s="142"/>
-      <c r="P73" s="228"/>
+      <c r="P73" s="225"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="245" t="s">
-        <v>304</v>
-      </c>
-      <c r="B74" s="248"/>
-      <c r="C74" s="246" t="str">
+      <c r="A74" s="242" t="s">
+        <v>306</v>
+      </c>
+      <c r="B74" s="245"/>
+      <c r="C74" s="243" t="str">
         <f aca="false">DEC2HEX(D74,2)</f>
         <v>30</v>
       </c>
@@ -10161,7 +10155,7 @@
         <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
         <v>48</v>
       </c>
-      <c r="E74" s="247" t="n">
+      <c r="E74" s="244" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="152" t="n">
@@ -10173,7 +10167,7 @@
       <c r="H74" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="247" t="n">
+      <c r="I74" s="244" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="152" t="n">
@@ -10185,56 +10179,56 @@
       <c r="L74" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="M74" s="256"/>
-      <c r="N74" s="256"/>
-      <c r="O74" s="248"/>
-      <c r="P74" s="257"/>
+      <c r="M74" s="253"/>
+      <c r="N74" s="253"/>
+      <c r="O74" s="245"/>
+      <c r="P74" s="254"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="250" t="s">
-        <v>305</v>
-      </c>
-      <c r="B75" s="194"/>
-      <c r="C75" s="215" t="str">
+      <c r="A75" s="247" t="s">
+        <v>307</v>
+      </c>
+      <c r="B75" s="191"/>
+      <c r="C75" s="212" t="str">
         <f aca="false">DEC2HEX(D75,2)</f>
         <v>40</v>
       </c>
-      <c r="D75" s="196" t="n">
+      <c r="D75" s="193" t="n">
         <f aca="false">IF(E75=1,128,0)+IF(F75=1,64,0)+IF(G75=1,32,0)+IF(H75=1,16,0)+IF(I75=1,8,0)+IF(J75=1,4,0)+IF(K75=1,2,0)+IF(L75=1,1,0)</f>
         <v>64</v>
       </c>
-      <c r="E75" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="252" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="254"/>
-      <c r="N75" s="254"/>
-      <c r="O75" s="194"/>
-      <c r="P75" s="255"/>
+      <c r="E75" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="249" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="251"/>
+      <c r="N75" s="251"/>
+      <c r="O75" s="191"/>
+      <c r="P75" s="252"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="225" t="s">
-        <v>306</v>
+      <c r="A76" s="222" t="s">
+        <v>308</v>
       </c>
       <c r="B76" s="142"/>
       <c r="C76" s="20" t="str">
@@ -10269,14 +10263,14 @@
       <c r="L76" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="226"/>
-      <c r="N76" s="226"/>
+      <c r="M76" s="223"/>
+      <c r="N76" s="223"/>
       <c r="O76" s="142"/>
-      <c r="P76" s="228"/>
+      <c r="P76" s="225"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="225" t="s">
-        <v>307</v>
+      <c r="A77" s="222" t="s">
+        <v>309</v>
       </c>
       <c r="B77" s="142"/>
       <c r="C77" s="20" t="str">
@@ -10311,17 +10305,17 @@
       <c r="L77" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="226"/>
-      <c r="N77" s="226"/>
+      <c r="M77" s="223"/>
+      <c r="N77" s="223"/>
       <c r="O77" s="142"/>
-      <c r="P77" s="228"/>
+      <c r="P77" s="225"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="245" t="s">
-        <v>308</v>
-      </c>
-      <c r="B78" s="248"/>
-      <c r="C78" s="246" t="str">
+      <c r="A78" s="242" t="s">
+        <v>310</v>
+      </c>
+      <c r="B78" s="245"/>
+      <c r="C78" s="243" t="str">
         <f aca="false">DEC2HEX(D78,2)</f>
         <v>70</v>
       </c>
@@ -10329,7 +10323,7 @@
         <f aca="false">IF(E78=1,128,0)+IF(F78=1,64,0)+IF(G78=1,32,0)+IF(H78=1,16,0)+IF(I78=1,8,0)+IF(J78=1,4,0)+IF(K78=1,2,0)+IF(L78=1,1,0)</f>
         <v>112</v>
       </c>
-      <c r="E78" s="247" t="n">
+      <c r="E78" s="244" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="152" t="n">
@@ -10341,7 +10335,7 @@
       <c r="H78" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I78" s="247" t="n">
+      <c r="I78" s="244" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="152" t="n">
@@ -10353,56 +10347,56 @@
       <c r="L78" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="M78" s="256"/>
-      <c r="N78" s="256"/>
-      <c r="O78" s="248"/>
-      <c r="P78" s="257"/>
+      <c r="M78" s="253"/>
+      <c r="N78" s="253"/>
+      <c r="O78" s="245"/>
+      <c r="P78" s="254"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="250" t="s">
-        <v>309</v>
-      </c>
-      <c r="B79" s="258"/>
-      <c r="C79" s="215" t="str">
+      <c r="A79" s="247" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" s="255"/>
+      <c r="C79" s="212" t="str">
         <f aca="false">DEC2HEX(D79,2)</f>
         <v>01</v>
       </c>
-      <c r="D79" s="196" t="n">
+      <c r="D79" s="193" t="n">
         <f aca="false">IF(E79=1,128,0)+IF(F79=1,64,0)+IF(G79=1,32,0)+IF(H79=1,16,0)+IF(I79=1,8,0)+IF(J79=1,4,0)+IF(K79=1,2,0)+IF(L79=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E79" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="196" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="253" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="254"/>
-      <c r="N79" s="254"/>
-      <c r="O79" s="194"/>
-      <c r="P79" s="255"/>
+      <c r="E79" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="251"/>
+      <c r="N79" s="251"/>
+      <c r="O79" s="191"/>
+      <c r="P79" s="252"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="225" t="s">
-        <v>310</v>
+      <c r="A80" s="222" t="s">
+        <v>312</v>
       </c>
       <c r="B80" s="142"/>
       <c r="C80" s="20" t="str">
@@ -10437,11 +10431,11 @@
       <c r="L80" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="P80" s="228"/>
+      <c r="P80" s="225"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="225" t="s">
-        <v>311</v>
+      <c r="A81" s="222" t="s">
+        <v>313</v>
       </c>
       <c r="B81" s="142"/>
       <c r="C81" s="20" t="str">
@@ -10479,14 +10473,14 @@
       <c r="M81" s="10"/>
       <c r="N81" s="10"/>
       <c r="O81" s="142"/>
-      <c r="P81" s="228"/>
+      <c r="P81" s="225"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="245" t="s">
-        <v>312</v>
-      </c>
-      <c r="B82" s="248"/>
-      <c r="C82" s="246" t="str">
+      <c r="A82" s="242" t="s">
+        <v>314</v>
+      </c>
+      <c r="B82" s="245"/>
+      <c r="C82" s="243" t="str">
         <f aca="false">DEC2HEX(D82,2)</f>
         <v>31</v>
       </c>
@@ -10494,7 +10488,7 @@
         <f aca="false">IF(E82=1,128,0)+IF(F82=1,64,0)+IF(G82=1,32,0)+IF(H82=1,16,0)+IF(I82=1,8,0)+IF(J82=1,4,0)+IF(K82=1,2,0)+IF(L82=1,1,0)</f>
         <v>49</v>
       </c>
-      <c r="E82" s="247" t="n">
+      <c r="E82" s="244" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="152" t="n">
@@ -10506,7 +10500,7 @@
       <c r="H82" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I82" s="247" t="n">
+      <c r="I82" s="244" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="152" t="n">
@@ -10518,58 +10512,58 @@
       <c r="L82" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="M82" s="256"/>
-      <c r="N82" s="256"/>
-      <c r="O82" s="248"/>
-      <c r="P82" s="257"/>
+      <c r="M82" s="253"/>
+      <c r="N82" s="253"/>
+      <c r="O82" s="245"/>
+      <c r="P82" s="254"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="250" t="s">
-        <v>313</v>
-      </c>
-      <c r="B83" s="194"/>
-      <c r="C83" s="215" t="str">
+      <c r="A83" s="247" t="s">
+        <v>315</v>
+      </c>
+      <c r="B83" s="191"/>
+      <c r="C83" s="212" t="str">
         <f aca="false">DEC2HEX(D83,2)</f>
         <v>04</v>
       </c>
-      <c r="D83" s="196" t="n">
+      <c r="D83" s="193" t="n">
         <f aca="false">IF(E83=1,128,0)+IF(F83=1,64,0)+IF(G83=1,32,0)+IF(H83=1,16,0)+IF(I83=1,8,0)+IF(J83=1,4,0)+IF(K83=1,2,0)+IF(L83=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E83" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="252" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="254"/>
-      <c r="N83" s="254"/>
-      <c r="O83" s="194"/>
-      <c r="P83" s="255" t="s">
-        <v>314</v>
+      <c r="E83" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="249" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="251"/>
+      <c r="N83" s="251"/>
+      <c r="O83" s="191"/>
+      <c r="P83" s="252" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A84" s="225" t="s">
-        <v>315</v>
+      <c r="A84" s="222" t="s">
+        <v>317</v>
       </c>
       <c r="B84" s="142"/>
       <c r="C84" s="20" t="str">
@@ -10604,18 +10598,18 @@
       <c r="L84" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="226"/>
-      <c r="N84" s="226"/>
+      <c r="M84" s="223"/>
+      <c r="N84" s="223"/>
       <c r="O84" s="142"/>
-      <c r="P84" s="228" t="s">
-        <v>316</v>
+      <c r="P84" s="225" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A85" s="225" t="s">
-        <v>317</v>
-      </c>
-      <c r="B85" s="259"/>
+      <c r="A85" s="222" t="s">
+        <v>319</v>
+      </c>
+      <c r="B85" s="256"/>
       <c r="C85" s="17" t="str">
         <f aca="false">DEC2HEX(D85,2)</f>
         <v>54</v>
@@ -10648,18 +10642,18 @@
       <c r="L85" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="226"/>
-      <c r="N85" s="226"/>
-      <c r="O85" s="259"/>
-      <c r="P85" s="228" t="s">
-        <v>318</v>
+      <c r="M85" s="223"/>
+      <c r="N85" s="223"/>
+      <c r="O85" s="256"/>
+      <c r="P85" s="225" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A86" s="225" t="s">
-        <v>319</v>
-      </c>
-      <c r="B86" s="259"/>
+      <c r="A86" s="222" t="s">
+        <v>321</v>
+      </c>
+      <c r="B86" s="256"/>
       <c r="C86" s="17" t="str">
         <f aca="false">DEC2HEX(D86,2)</f>
         <v>84</v>
@@ -10692,61 +10686,61 @@
       <c r="L86" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="M86" s="226"/>
-      <c r="N86" s="226"/>
-      <c r="O86" s="259"/>
-      <c r="P86" s="228"/>
+      <c r="M86" s="223"/>
+      <c r="N86" s="223"/>
+      <c r="O86" s="256"/>
+      <c r="P86" s="225"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A87" s="250" t="s">
-        <v>320</v>
-      </c>
-      <c r="B87" s="194"/>
-      <c r="C87" s="215" t="str">
+      <c r="A87" s="247" t="s">
+        <v>322</v>
+      </c>
+      <c r="B87" s="191"/>
+      <c r="C87" s="212" t="str">
         <f aca="false">DEC2HEX(D87,2)</f>
         <v>05</v>
       </c>
-      <c r="D87" s="196" t="n">
+      <c r="D87" s="193" t="n">
         <f aca="false">IF(E87=1,128,0)+IF(F87=1,64,0)+IF(G87=1,32,0)+IF(H87=1,16,0)+IF(I87=1,8,0)+IF(J87=1,4,0)+IF(K87=1,2,0)+IF(L87=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E87" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="252" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="253" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="254"/>
-      <c r="N87" s="254"/>
-      <c r="O87" s="194"/>
-      <c r="P87" s="255" t="s">
-        <v>321</v>
+      <c r="E87" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="249" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="251"/>
+      <c r="N87" s="251"/>
+      <c r="O87" s="191"/>
+      <c r="P87" s="252" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A88" s="245" t="s">
-        <v>322</v>
-      </c>
-      <c r="B88" s="248"/>
-      <c r="C88" s="246" t="str">
+      <c r="A88" s="242" t="s">
+        <v>324</v>
+      </c>
+      <c r="B88" s="245"/>
+      <c r="C88" s="243" t="str">
         <f aca="false">DEC2HEX(D88,2)</f>
         <v>45</v>
       </c>
@@ -10754,7 +10748,7 @@
         <f aca="false">IF(E88=1,128,0)+IF(F88=1,64,0)+IF(G88=1,32,0)+IF(H88=1,16,0)+IF(I88=1,8,0)+IF(J88=1,4,0)+IF(K88=1,2,0)+IF(L88=1,1,0)</f>
         <v>69</v>
       </c>
-      <c r="E88" s="247" t="n">
+      <c r="E88" s="244" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="152" t="n">
@@ -10766,7 +10760,7 @@
       <c r="H88" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="247" t="n">
+      <c r="I88" s="244" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="152" t="n">
@@ -10778,16 +10772,16 @@
       <c r="L88" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="M88" s="256"/>
-      <c r="N88" s="256"/>
-      <c r="O88" s="248"/>
-      <c r="P88" s="257" t="s">
-        <v>323</v>
+      <c r="M88" s="253"/>
+      <c r="N88" s="253"/>
+      <c r="O88" s="245"/>
+      <c r="P88" s="254" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A89" s="225" t="s">
-        <v>324</v>
+      <c r="A89" s="222" t="s">
+        <v>326</v>
       </c>
       <c r="B89" s="142"/>
       <c r="C89" s="17" t="str">
@@ -10822,17 +10816,17 @@
       <c r="L89" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="226"/>
-      <c r="N89" s="226"/>
+      <c r="M89" s="223"/>
+      <c r="N89" s="223"/>
       <c r="O89" s="142"/>
-      <c r="P89" s="228"/>
+      <c r="P89" s="225"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A90" s="245" t="s">
-        <v>325</v>
-      </c>
-      <c r="B90" s="248"/>
-      <c r="C90" s="246" t="str">
+      <c r="A90" s="242" t="s">
+        <v>327</v>
+      </c>
+      <c r="B90" s="245"/>
+      <c r="C90" s="243" t="str">
         <f aca="false">DEC2HEX(D90,2)</f>
         <v>37</v>
       </c>
@@ -10840,7 +10834,7 @@
         <f aca="false">IF(E90=1,128,0)+IF(F90=1,64,0)+IF(G90=1,32,0)+IF(H90=1,16,0)+IF(I90=1,8,0)+IF(J90=1,4,0)+IF(K90=1,2,0)+IF(L90=1,1,0)</f>
         <v>55</v>
       </c>
-      <c r="E90" s="247" t="n">
+      <c r="E90" s="244" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="152" t="n">
@@ -10852,7 +10846,7 @@
       <c r="H90" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I90" s="247" t="n">
+      <c r="I90" s="244" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="152" t="n">
@@ -10864,13 +10858,13 @@
       <c r="L90" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="M90" s="256"/>
-      <c r="N90" s="256"/>
-      <c r="O90" s="248"/>
-      <c r="P90" s="257"/>
+      <c r="M90" s="253"/>
+      <c r="N90" s="253"/>
+      <c r="O90" s="245"/>
+      <c r="P90" s="254"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A91" s="225"/>
+      <c r="A91" s="222"/>
       <c r="B91" s="142"/>
       <c r="C91" s="17" t="str">
         <f aca="false">DEC2HEX(D91,2)</f>
@@ -10888,15 +10882,15 @@
       <c r="J91" s="119"/>
       <c r="K91" s="119"/>
       <c r="L91" s="50"/>
-      <c r="M91" s="226"/>
-      <c r="N91" s="226"/>
+      <c r="M91" s="223"/>
+      <c r="N91" s="223"/>
       <c r="O91" s="142"/>
-      <c r="P91" s="228"/>
+      <c r="P91" s="225"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A92" s="245"/>
-      <c r="B92" s="248"/>
-      <c r="C92" s="246" t="str">
+      <c r="A92" s="242"/>
+      <c r="B92" s="245"/>
+      <c r="C92" s="243" t="str">
         <f aca="false">DEC2HEX(D92,2)</f>
         <v>00</v>
       </c>
@@ -10904,25 +10898,25 @@
         <f aca="false">IF(E92=1,128,0)+IF(F92=1,64,0)+IF(G92=1,32,0)+IF(H92=1,16,0)+IF(I92=1,8,0)+IF(J92=1,4,0)+IF(K92=1,2,0)+IF(L92=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E92" s="247"/>
+      <c r="E92" s="244"/>
       <c r="F92" s="152"/>
       <c r="G92" s="152"/>
       <c r="H92" s="155"/>
-      <c r="I92" s="247"/>
+      <c r="I92" s="244"/>
       <c r="J92" s="152"/>
       <c r="K92" s="152"/>
       <c r="L92" s="155"/>
-      <c r="M92" s="256"/>
-      <c r="N92" s="256"/>
-      <c r="O92" s="248"/>
-      <c r="P92" s="257"/>
+      <c r="M92" s="253"/>
+      <c r="N92" s="253"/>
+      <c r="O92" s="245"/>
+      <c r="P92" s="254"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="142"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -10937,12 +10931,12 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="3"/>
-      <c r="O94" s="260"/>
+      <c r="O94" s="257"/>
       <c r="P94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -10981,10 +10975,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>52</v>
@@ -10998,13 +10992,13 @@
       <c r="F1" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="261" t="s">
-        <v>329</v>
-      </c>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261" t="s">
-        <v>330</v>
+      <c r="G1" s="258" t="s">
+        <v>331</v>
+      </c>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11018,26 +11012,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>120</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11051,13 +11045,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>120</v>
@@ -11067,10 +11061,10 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11087,25 +11081,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11122,25 +11116,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="K5" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11154,28 +11148,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11189,28 +11183,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11224,26 +11218,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>120</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11257,13 +11251,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>120</v>
@@ -11273,10 +11267,10 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11290,28 +11284,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11325,28 +11319,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11360,28 +11354,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11395,28 +11389,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Connection" sheetId="1" state="visible" r:id="rId3"/>
@@ -63,9 +63,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>14</xdr:col>
-                <xdr:colOff>17</xdr:colOff>
+                <xdr:colOff>11</xdr:colOff>
                 <xdr:row>33</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
+                <xdr:rowOff>7</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -96,7 +96,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>31</xdr:colOff>
+                <xdr:colOff>21</xdr:colOff>
                 <xdr:row>28</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -123,15 +123,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>12</xdr:col>
-                <xdr:colOff>68</xdr:colOff>
+                <xdr:colOff>45</xdr:colOff>
                 <xdr:row>33</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>13</xdr:col>
-                <xdr:colOff>106</xdr:colOff>
+                <xdr:colOff>71</xdr:colOff>
                 <xdr:row>34</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -162,9 +162,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>31</xdr:colOff>
+                <xdr:colOff>21</xdr:colOff>
                 <xdr:row>29</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:rowOff>8</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="356">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -301,15 +301,24 @@
     <t xml:space="preserve">String types:</t>
   </si>
   <si>
+    <t xml:space="preserve">Abbreviation:</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identifier:</t>
   </si>
   <si>
+    <t xml:space="preserve">idn</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 bytes for string length (in bytes) followed by bytes for string encoded in UTF-8.</t>
   </si>
   <si>
     <t xml:space="preserve">String: </t>
   </si>
   <si>
+    <t xml:space="preserve">str</t>
+  </si>
+  <si>
     <t xml:space="preserve">4 bytes for string length (in bytes) followed by bytes for string encoded in UTF-8.</t>
   </si>
   <si>
@@ -433,15 +442,12 @@
     <t xml:space="preserve">Service</t>
   </si>
   <si>
-    <t xml:space="preserve">1 + str</t>
+    <t xml:space="preserve">1 + idn</t>
   </si>
   <si>
     <t xml:space="preserve">IsService</t>
   </si>
   <si>
-    <t xml:space="preserve">str</t>
-  </si>
-  <si>
     <t xml:space="preserve">ServiceName</t>
   </si>
   <si>
@@ -511,7 +517,7 @@
     <t xml:space="preserve">Internet</t>
   </si>
   <si>
-    <t xml:space="preserve">3 + str</t>
+    <t xml:space="preserve">3 + idn</t>
   </si>
   <si>
     <t xml:space="preserve">IPv4/IPv6</t>
@@ -1914,6 +1920,55 @@
     <t xml:space="preserve">Values are comma delimited, without spaces. Ending comma is ignored.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Strings are </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">always</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> encoded in </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">UTF-8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Date/Time (numeric)</t>
   </si>
   <si>
@@ -2318,7 +2373,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2474,6 +2529,19 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -2962,7 +3030,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="262">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3920,6 +3988,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4353,21 +4433,30 @@
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="B27" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="10" t="s">
         <v>28</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4404,21 +4493,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H1" s="17"/>
       <c r="I1" s="17"/>
@@ -4428,29 +4517,29 @@
       </c>
       <c r="L1" s="17"/>
       <c r="M1" s="15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O1" s="18"/>
       <c r="P1" s="15" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S1" s="20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="T1" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="U1" s="20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4481,17 +4570,17 @@
         <v>0</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O2" s="28" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P2" s="22"/>
       <c r="Q2" s="29"/>
@@ -4514,7 +4603,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="31"/>
@@ -4550,7 +4639,7 @@
       </c>
       <c r="P3" s="38"/>
       <c r="Q3" s="39" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="R3" s="40" t="n">
         <v>3</v>
@@ -4563,11 +4652,11 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" s="32" t="str">
         <f aca="false">IF(COUNTA(D5:D8)&gt;0,"z","")</f>
@@ -4612,7 +4701,7 @@
       </c>
       <c r="P4" s="38"/>
       <c r="Q4" s="39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R4" s="40" t="n">
         <v>3</v>
@@ -4630,7 +4719,7 @@
       <c r="D5" s="46"/>
       <c r="E5" s="47"/>
       <c r="F5" s="48" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G5" s="46"/>
       <c r="H5" s="47"/>
@@ -4639,14 +4728,14 @@
       <c r="K5" s="49"/>
       <c r="L5" s="50"/>
       <c r="M5" s="51" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N5" s="52"/>
       <c r="O5" s="53" t="n">
         <v>4</v>
       </c>
       <c r="P5" s="54" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="55"/>
     </row>
@@ -4656,7 +4745,7 @@
       <c r="C6" s="57"/>
       <c r="D6" s="58"/>
       <c r="E6" s="59" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F6" s="60"/>
       <c r="G6" s="58"/>
@@ -4666,7 +4755,7 @@
       <c r="K6" s="49"/>
       <c r="L6" s="50"/>
       <c r="M6" s="61" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N6" s="62"/>
       <c r="O6" s="59"/>
@@ -4694,7 +4783,7 @@
         <v>4</v>
       </c>
       <c r="P7" s="63" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="64"/>
     </row>
@@ -4703,7 +4792,7 @@
       <c r="B8" s="56"/>
       <c r="C8" s="57"/>
       <c r="D8" s="58" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E8" s="59"/>
       <c r="F8" s="60"/>
@@ -4714,14 +4803,14 @@
       <c r="K8" s="49"/>
       <c r="L8" s="50"/>
       <c r="M8" s="61" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N8" s="58"/>
       <c r="O8" s="59" t="n">
         <v>4</v>
       </c>
       <c r="P8" s="63" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q8" s="64"/>
       <c r="R8" s="13"/>
@@ -4747,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="59" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P9" s="63" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q9" s="64"/>
       <c r="R9" s="13"/>
@@ -4761,7 +4850,7 @@
     <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A10" s="56"/>
       <c r="B10" s="56" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="62"/>
@@ -4778,20 +4867,20 @@
         <v>0</v>
       </c>
       <c r="O10" s="59" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P10" s="63" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q10" s="64"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D11" s="32" t="str">
         <f aca="false">IF(COUNTA(D13:D14)&gt;0,"z","")</f>
@@ -4830,7 +4919,7 @@
         <v>5</v>
       </c>
       <c r="O11" s="43" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P11" s="38"/>
       <c r="Q11" s="39"/>
@@ -4850,7 +4939,7 @@
       <c r="D12" s="68"/>
       <c r="E12" s="69"/>
       <c r="F12" s="70" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G12" s="68"/>
       <c r="H12" s="69"/>
@@ -4859,14 +4948,14 @@
       <c r="K12" s="49"/>
       <c r="L12" s="50"/>
       <c r="M12" s="71" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N12" s="68"/>
       <c r="O12" s="69" t="n">
         <v>4</v>
       </c>
       <c r="P12" s="72" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q12" s="73"/>
     </row>
@@ -4891,10 +4980,10 @@
         <v>4</v>
       </c>
       <c r="P13" s="54" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Q13" s="55" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
@@ -4915,20 +5004,20 @@
         <v>0</v>
       </c>
       <c r="O14" s="69" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P14" s="72" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="41" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" s="32" t="str">
         <f aca="false">IF(COUNTA(D16:D17)&gt;0,"z","")</f>
@@ -4964,14 +5053,14 @@
       </c>
       <c r="M15" s="37"/>
       <c r="N15" s="42" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O15" s="43" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P15" s="38"/>
       <c r="Q15" s="39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R15" s="40" t="n">
         <v>0</v>
@@ -5022,11 +5111,11 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D18" s="32" t="str">
         <f aca="false">IF(COUNTA(D19:D22)&gt;0,"z","")</f>
@@ -5065,7 +5154,7 @@
         <v>5</v>
       </c>
       <c r="O18" s="43" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P18" s="38"/>
       <c r="Q18" s="39"/>
@@ -5096,19 +5185,19 @@
       <c r="K19" s="49"/>
       <c r="L19" s="50"/>
       <c r="M19" s="97" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N19" s="81" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="O19" s="95" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P19" s="98" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="99" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" s="100" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -5129,7 +5218,7 @@
       <c r="K20" s="49"/>
       <c r="L20" s="50"/>
       <c r="M20" s="97" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N20" s="81" t="n">
         <v>4</v>
@@ -5138,10 +5227,10 @@
         <v>4</v>
       </c>
       <c r="P20" s="98" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q20" s="99" t="s">
         <v>77</v>
-      </c>
-      <c r="Q20" s="99" t="s">
-        <v>75</v>
       </c>
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
@@ -5151,11 +5240,11 @@
     <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A21" s="101"/>
       <c r="B21" s="101" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C21" s="102"/>
       <c r="D21" s="103" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E21" s="104"/>
       <c r="F21" s="105"/>
@@ -5166,7 +5255,7 @@
       <c r="K21" s="106"/>
       <c r="L21" s="107"/>
       <c r="M21" s="108" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N21" s="103" t="n">
         <v>8</v>
@@ -5175,10 +5264,10 @@
         <v>8</v>
       </c>
       <c r="P21" s="109" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q21" s="110" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R21" s="111"/>
       <c r="S21" s="111"/>
@@ -5203,7 +5292,7 @@
       <c r="K22" s="49"/>
       <c r="L22" s="50"/>
       <c r="M22" s="71" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N22" s="74" t="n">
         <v>4</v>
@@ -5212,19 +5301,19 @@
         <v>4</v>
       </c>
       <c r="P22" s="72" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="73" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D23" s="32" t="str">
         <f aca="false">IF(COUNTA(D24:D25)&gt;0,"z","")</f>
@@ -5269,7 +5358,7 @@
       </c>
       <c r="P23" s="38"/>
       <c r="Q23" s="39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R23" s="40" t="n">
         <v>3</v>
@@ -5301,7 +5390,7 @@
         <v>4</v>
       </c>
       <c r="P24" s="63" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q24" s="64"/>
     </row>
@@ -5326,11 +5415,11 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D26" s="32" t="str">
         <f aca="false">IF(COUNTA(D27:D30)&gt;0,"z","")</f>
@@ -5366,15 +5455,15 @@
       </c>
       <c r="M26" s="41"/>
       <c r="N26" s="42" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O26" s="43" t="str">
-        <f aca="false">CONCATENATE(1+SUM(O27:O30)," + str")</f>
-        <v>1 + str</v>
+        <f aca="false">CONCATENATE(1+SUM(O27:O30)," + idn")</f>
+        <v>1 + idn</v>
       </c>
       <c r="P26" s="38"/>
       <c r="Q26" s="39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R26" s="40" t="n">
         <v>3</v>
@@ -5400,13 +5489,13 @@
       <c r="L27" s="50"/>
       <c r="M27" s="71"/>
       <c r="N27" s="68" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="O27" s="69" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P27" s="72" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q27" s="73"/>
     </row>
@@ -5417,7 +5506,7 @@
       <c r="D28" s="68"/>
       <c r="E28" s="69"/>
       <c r="F28" s="70" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G28" s="68"/>
       <c r="H28" s="69"/>
@@ -5426,7 +5515,7 @@
       <c r="K28" s="49"/>
       <c r="L28" s="50"/>
       <c r="M28" s="51" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N28" s="46"/>
       <c r="O28" s="47"/>
@@ -5436,12 +5525,12 @@
     <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A29" s="66"/>
       <c r="B29" s="114" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29" s="67"/>
       <c r="D29" s="68"/>
       <c r="E29" s="69" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F29" s="70"/>
       <c r="G29" s="68"/>
@@ -5451,7 +5540,7 @@
       <c r="K29" s="49"/>
       <c r="L29" s="50"/>
       <c r="M29" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N29" s="46"/>
       <c r="O29" s="47"/>
@@ -5461,11 +5550,11 @@
     <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A30" s="44"/>
       <c r="B30" s="114" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="46" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E30" s="53"/>
       <c r="F30" s="48"/>
@@ -5476,7 +5565,7 @@
       <c r="K30" s="49"/>
       <c r="L30" s="50"/>
       <c r="M30" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N30" s="46"/>
       <c r="O30" s="47"/>
@@ -5487,7 +5576,7 @@
       <c r="A31" s="30"/>
       <c r="B31" s="30"/>
       <c r="C31" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D31" s="32" t="str">
         <f aca="false">IF(COUNTA(D32:D34)&gt;0,"z","")</f>
@@ -5590,11 +5679,11 @@
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D35" s="32" t="str">
         <f aca="false">IF(COUNTA(D36)&gt;0,"z","")</f>
@@ -5639,7 +5728,7 @@
       </c>
       <c r="P35" s="38"/>
       <c r="Q35" s="39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="R35" s="40" t="n">
         <v>3</v>
@@ -5671,17 +5760,17 @@
         <v>4</v>
       </c>
       <c r="P36" s="93" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q36" s="94"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D37" s="32" t="str">
         <f aca="false">IF(COUNTA(D38:D42)&gt;0,"z","")</f>
@@ -5720,11 +5809,11 @@
         <v>5</v>
       </c>
       <c r="O37" s="43" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P37" s="38"/>
       <c r="Q37" s="39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="R37" s="40" t="n">
         <v>3</v>
@@ -5742,7 +5831,7 @@
       <c r="D38" s="68"/>
       <c r="E38" s="112"/>
       <c r="F38" s="70" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G38" s="68"/>
       <c r="H38" s="69"/>
@@ -5751,7 +5840,7 @@
       <c r="K38" s="49"/>
       <c r="L38" s="50"/>
       <c r="M38" s="71" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N38" s="68"/>
       <c r="O38" s="112"/>
@@ -5764,7 +5853,7 @@
       <c r="C39" s="45"/>
       <c r="D39" s="46"/>
       <c r="E39" s="53" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F39" s="48"/>
       <c r="G39" s="46"/>
@@ -5774,21 +5863,21 @@
       <c r="K39" s="49"/>
       <c r="L39" s="50"/>
       <c r="M39" s="51" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N39" s="46"/>
       <c r="O39" s="53" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P39" s="54" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q39" s="55"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A40" s="44"/>
       <c r="B40" s="44" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C40" s="45"/>
       <c r="D40" s="46"/>
@@ -5806,14 +5895,14 @@
         <v>4</v>
       </c>
       <c r="P40" s="54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q40" s="55"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A41" s="44"/>
       <c r="B41" s="44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C41" s="45"/>
       <c r="D41" s="46"/>
@@ -5831,7 +5920,7 @@
         <v>16</v>
       </c>
       <c r="P41" s="54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q41" s="55"/>
     </row>
@@ -5840,7 +5929,7 @@
       <c r="B42" s="85"/>
       <c r="C42" s="86"/>
       <c r="D42" s="92" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E42" s="88"/>
       <c r="F42" s="89"/>
@@ -5851,14 +5940,14 @@
       <c r="K42" s="49"/>
       <c r="L42" s="50"/>
       <c r="M42" s="91" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N42" s="87"/>
       <c r="O42" s="88" t="n">
         <v>2</v>
       </c>
       <c r="P42" s="93" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q42" s="94"/>
     </row>
@@ -5866,7 +5955,7 @@
       <c r="A43" s="41"/>
       <c r="B43" s="30"/>
       <c r="C43" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D43" s="32" t="str">
         <f aca="false">IF(COUNTA(D44)&gt;0,"z","")</f>
@@ -5933,7 +6022,7 @@
       <c r="A45" s="30"/>
       <c r="B45" s="30"/>
       <c r="C45" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D45" s="32" t="str">
         <f aca="false">IF(COUNTA(D46:D50)&gt;0,"z","")</f>
@@ -6074,11 +6163,11 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B51" s="30"/>
       <c r="C51" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D51" s="32" t="str">
         <f aca="false">IF(COUNTA(D52:D59)&gt;0,"z","")</f>
@@ -6121,7 +6210,7 @@
       </c>
       <c r="P51" s="38"/>
       <c r="Q51" s="39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R51" s="40" t="n">
         <v>3</v>
@@ -6139,7 +6228,7 @@
       <c r="D52" s="74"/>
       <c r="E52" s="112"/>
       <c r="F52" s="70" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G52" s="68"/>
       <c r="H52" s="69"/>
@@ -6148,7 +6237,7 @@
       <c r="K52" s="49"/>
       <c r="L52" s="50"/>
       <c r="M52" s="71" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N52" s="68"/>
       <c r="O52" s="69"/>
@@ -6161,7 +6250,7 @@
       <c r="C53" s="67"/>
       <c r="D53" s="74"/>
       <c r="E53" s="112" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F53" s="70"/>
       <c r="G53" s="68"/>
@@ -6171,7 +6260,7 @@
       <c r="K53" s="49"/>
       <c r="L53" s="50"/>
       <c r="M53" s="71" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N53" s="68"/>
       <c r="O53" s="69"/>
@@ -6181,11 +6270,11 @@
     <row r="54" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A54" s="66"/>
       <c r="B54" s="66" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C54" s="67"/>
       <c r="D54" s="74" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E54" s="112"/>
       <c r="F54" s="70"/>
@@ -6196,7 +6285,7 @@
       <c r="K54" s="49"/>
       <c r="L54" s="50"/>
       <c r="M54" s="71" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N54" s="68"/>
       <c r="O54" s="69"/>
@@ -6206,11 +6295,11 @@
     <row r="55" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A55" s="66"/>
       <c r="B55" s="66" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C55" s="67"/>
       <c r="D55" s="74" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E55" s="112"/>
       <c r="F55" s="70"/>
@@ -6221,7 +6310,7 @@
       <c r="K55" s="49"/>
       <c r="L55" s="50"/>
       <c r="M55" s="71" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N55" s="68"/>
       <c r="O55" s="69"/>
@@ -6231,11 +6320,11 @@
     <row r="56" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A56" s="66"/>
       <c r="B56" s="66" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C56" s="67"/>
       <c r="D56" s="74" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E56" s="112"/>
       <c r="F56" s="70"/>
@@ -6246,7 +6335,7 @@
       <c r="K56" s="49"/>
       <c r="L56" s="50"/>
       <c r="M56" s="71" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N56" s="68"/>
       <c r="O56" s="69"/>
@@ -6256,7 +6345,7 @@
     <row r="57" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A57" s="66"/>
       <c r="B57" s="66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C57" s="67"/>
       <c r="D57" s="74"/>
@@ -6276,14 +6365,14 @@
         <v>4</v>
       </c>
       <c r="P57" s="72" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q57" s="73"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A58" s="66"/>
       <c r="B58" s="66" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C58" s="67"/>
       <c r="D58" s="74"/>
@@ -6303,14 +6392,14 @@
         <v>4</v>
       </c>
       <c r="P58" s="72" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q58" s="73"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A59" s="85"/>
       <c r="B59" s="85" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C59" s="86"/>
       <c r="D59" s="87"/>
@@ -6330,17 +6419,17 @@
         <v>4</v>
       </c>
       <c r="P59" s="93" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q59" s="94"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B60" s="30"/>
       <c r="C60" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D60" s="32" t="str">
         <f aca="false">IF(COUNTA(D61:D63)&gt;0,"z","")</f>
@@ -6376,14 +6465,14 @@
       </c>
       <c r="M60" s="37"/>
       <c r="N60" s="42" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O60" s="43" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P60" s="38"/>
       <c r="Q60" s="39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R60" s="40" t="n">
         <v>1</v>
@@ -6408,7 +6497,7 @@
       <c r="K61" s="49"/>
       <c r="L61" s="50"/>
       <c r="M61" s="71" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N61" s="68"/>
       <c r="O61" s="69"/>
@@ -6429,7 +6518,7 @@
       <c r="K62" s="49"/>
       <c r="L62" s="50"/>
       <c r="M62" s="71" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N62" s="68"/>
       <c r="O62" s="69"/>
@@ -6450,22 +6539,22 @@
       <c r="K63" s="49"/>
       <c r="L63" s="50"/>
       <c r="M63" s="91" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N63" s="87"/>
       <c r="O63" s="88"/>
       <c r="P63" s="93" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q63" s="94"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B64" s="30"/>
       <c r="C64" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D64" s="32" t="str">
         <f aca="false">IF(COUNTA(D65:D67)&gt;0,"z","")</f>
@@ -6510,7 +6599,7 @@
       </c>
       <c r="P64" s="38"/>
       <c r="Q64" s="39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R64" s="40" t="n">
         <v>1</v>
@@ -6542,7 +6631,7 @@
         <v>4</v>
       </c>
       <c r="P65" s="72" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q65" s="73"/>
     </row>
@@ -6560,7 +6649,7 @@
       <c r="K66" s="49"/>
       <c r="L66" s="50"/>
       <c r="M66" s="71" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N66" s="68"/>
       <c r="O66" s="69"/>
@@ -6581,7 +6670,7 @@
       <c r="K67" s="49"/>
       <c r="L67" s="50"/>
       <c r="M67" s="71" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N67" s="68"/>
       <c r="O67" s="69"/>
@@ -6592,7 +6681,7 @@
       <c r="A68" s="30"/>
       <c r="B68" s="30"/>
       <c r="C68" s="31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D68" s="32" t="str">
         <f aca="false">IF(COUNTA(D69:D72)&gt;0,"z","")</f>
@@ -6718,11 +6807,11 @@
       <c r="E74" s="2"/>
       <c r="L74" s="119"/>
       <c r="M74" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O74" s="11"/>
       <c r="P74" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6731,13 +6820,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O75" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6746,13 +6835,13 @@
         <v>1</v>
       </c>
       <c r="M76" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>1</v>
       </c>
       <c r="P76" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6761,13 +6850,13 @@
         <v>2</v>
       </c>
       <c r="M77" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>2</v>
       </c>
       <c r="P77" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6776,13 +6865,13 @@
         <v>3</v>
       </c>
       <c r="M78" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>3</v>
       </c>
       <c r="P78" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6791,7 +6880,7 @@
         <v>4</v>
       </c>
       <c r="P79" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6832,19 +6921,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="120" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="121" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="121"/>
       <c r="B4" s="121" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6852,22 +6941,22 @@
     </row>
     <row r="6" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="121" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="121" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="121" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="121" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6875,32 +6964,32 @@
     </row>
     <row r="11" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="121" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="121" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="121" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="121" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6908,13 +6997,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C21" s="1"/>
     </row>
@@ -6926,19 +7015,19 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C26" s="1"/>
     </row>
@@ -7010,10 +7099,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="122" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C1" s="124" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D1" s="125" t="n">
         <v>7</v>
@@ -7040,19 +7129,19 @@
         <v>0</v>
       </c>
       <c r="L1" s="122" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M1" s="122" t="s">
         <v>1</v>
       </c>
       <c r="N1" s="125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O1" s="125" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P1" s="122" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q1" s="122"/>
       <c r="R1" s="122"/>
@@ -7069,19 +7158,19 @@
       <c r="I2" s="129"/>
       <c r="J2" s="129"/>
       <c r="K2" s="132" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L2" s="133" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M2" s="133" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N2" s="132" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O2" s="132" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P2" s="134"/>
     </row>
@@ -7095,20 +7184,20 @@
       <c r="H3" s="140"/>
       <c r="I3" s="138"/>
       <c r="J3" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K3" s="141"/>
       <c r="L3" s="142" t="s">
+        <v>164</v>
+      </c>
+      <c r="M3" s="142" t="s">
+        <v>165</v>
+      </c>
+      <c r="N3" s="141" t="s">
         <v>162</v>
       </c>
-      <c r="M3" s="142" t="s">
+      <c r="O3" s="50" t="s">
         <v>163</v>
-      </c>
-      <c r="N3" s="141" t="s">
-        <v>160</v>
-      </c>
-      <c r="O3" s="50" t="s">
-        <v>161</v>
       </c>
       <c r="P3" s="143"/>
     </row>
@@ -7121,21 +7210,21 @@
       <c r="G4" s="147"/>
       <c r="H4" s="148"/>
       <c r="I4" s="119" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J4" s="119"/>
       <c r="K4" s="141"/>
       <c r="L4" s="142" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M4" s="142" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N4" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O4" s="141" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P4" s="143"/>
     </row>
@@ -7161,7 +7250,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="159" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C6" s="160"/>
       <c r="D6" s="161"/>
@@ -7197,7 +7286,7 @@
       <c r="J7" s="119"/>
       <c r="K7" s="141"/>
       <c r="L7" s="142" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M7" s="142"/>
       <c r="N7" s="141"/>
@@ -7220,7 +7309,7 @@
       <c r="J8" s="119"/>
       <c r="K8" s="141"/>
       <c r="L8" s="142" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M8" s="142"/>
       <c r="N8" s="141"/>
@@ -7243,7 +7332,7 @@
       <c r="J9" s="119"/>
       <c r="K9" s="141"/>
       <c r="L9" s="142" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M9" s="142"/>
       <c r="N9" s="141"/>
@@ -7266,7 +7355,7 @@
       <c r="J10" s="119"/>
       <c r="K10" s="141"/>
       <c r="L10" s="142" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M10" s="142"/>
       <c r="N10" s="141"/>
@@ -7275,10 +7364,10 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="158" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B11" s="170" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C11" s="171"/>
       <c r="D11" s="172"/>
@@ -7311,16 +7400,16 @@
       <c r="K12" s="141"/>
       <c r="L12" s="142"/>
       <c r="M12" s="142" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N12" s="141" t="n">
         <v>1</v>
       </c>
       <c r="O12" s="141" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P12" s="143" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -7342,10 +7431,10 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="158" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C14" s="171"/>
       <c r="D14" s="172"/>
@@ -7370,7 +7459,7 @@
       <c r="C15" s="136"/>
       <c r="D15" s="137"/>
       <c r="E15" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F15" s="138"/>
       <c r="G15" s="139"/>
@@ -7379,24 +7468,24 @@
       <c r="J15" s="13"/>
       <c r="K15" s="141"/>
       <c r="L15" s="142" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M15" s="142" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N15" s="141" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O15" s="141" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P15" s="180" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B16" s="144" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C16" s="136"/>
       <c r="D16" s="137"/>
@@ -7412,7 +7501,7 @@
       <c r="N16" s="141"/>
       <c r="O16" s="141"/>
       <c r="P16" s="180" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -7428,21 +7517,21 @@
       <c r="K17" s="141"/>
       <c r="L17" s="142"/>
       <c r="M17" s="142" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N17" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O17" s="141" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P17" s="180" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B18" s="135" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C18" s="136"/>
       <c r="D18" s="137"/>
@@ -7455,21 +7544,21 @@
       <c r="K18" s="141"/>
       <c r="L18" s="142"/>
       <c r="M18" s="142" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N18" s="141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O18" s="141" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P18" s="180" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B19" s="144" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="145"/>
       <c r="D19" s="137"/>
@@ -7482,21 +7571,21 @@
       <c r="K19" s="141"/>
       <c r="L19" s="142"/>
       <c r="M19" s="142" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N19" s="141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O19" s="141" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P19" s="180" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B20" s="149" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C20" s="150"/>
       <c r="D20" s="181"/>
@@ -7512,15 +7601,15 @@
       <c r="N20" s="155"/>
       <c r="O20" s="155"/>
       <c r="P20" s="185" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="158" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B21" s="170" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C21" s="171"/>
       <c r="D21" s="172"/>
@@ -7553,16 +7642,16 @@
       <c r="K22" s="141"/>
       <c r="L22" s="142"/>
       <c r="M22" s="142" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N22" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O22" s="141" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P22" s="180" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -7578,24 +7667,24 @@
       <c r="K23" s="141"/>
       <c r="L23" s="142"/>
       <c r="M23" s="142" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N23" s="141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O23" s="141" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P23" s="180" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="158" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B24" s="170" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C24" s="171"/>
       <c r="D24" s="172"/>
@@ -7619,7 +7708,7 @@
       <c r="B25" s="135"/>
       <c r="C25" s="136"/>
       <c r="D25" s="137" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E25" s="119"/>
       <c r="F25" s="138"/>
@@ -7629,7 +7718,7 @@
       <c r="J25" s="119"/>
       <c r="K25" s="141"/>
       <c r="L25" s="142" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M25" s="142"/>
       <c r="N25" s="141"/>
@@ -7638,7 +7727,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B26" s="135" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="136"/>
       <c r="D26" s="137"/>
@@ -7651,24 +7740,24 @@
       <c r="K26" s="141"/>
       <c r="L26" s="142"/>
       <c r="M26" s="142" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N26" s="141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O26" s="141" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P26" s="187" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="158" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B27" s="170" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C27" s="171"/>
       <c r="D27" s="188"/>
@@ -7692,7 +7781,7 @@
       <c r="B28" s="135"/>
       <c r="C28" s="136"/>
       <c r="D28" s="137" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E28" s="119"/>
       <c r="F28" s="138"/>
@@ -7702,7 +7791,7 @@
       <c r="J28" s="119"/>
       <c r="K28" s="141"/>
       <c r="L28" s="142" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M28" s="142"/>
       <c r="N28" s="141"/>
@@ -7711,35 +7800,35 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B29" s="135" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C29" s="136"/>
       <c r="D29" s="137"/>
       <c r="E29" s="138"/>
       <c r="F29" s="138"/>
       <c r="G29" s="186" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H29" s="140"/>
       <c r="I29" s="138"/>
       <c r="J29" s="13"/>
       <c r="K29" s="141"/>
       <c r="L29" s="142" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M29" s="142"/>
       <c r="N29" s="141"/>
       <c r="O29" s="141"/>
       <c r="P29" s="143" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="158" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B30" s="170" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C30" s="171"/>
       <c r="D30" s="172"/>
@@ -7778,10 +7867,10 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="158" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32" s="170" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C32" s="171"/>
       <c r="D32" s="172"/>
@@ -7814,13 +7903,13 @@
       <c r="K33" s="141"/>
       <c r="L33" s="142"/>
       <c r="M33" s="142" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N33" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O33" s="141" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P33" s="143"/>
     </row>
@@ -7830,7 +7919,7 @@
       <c r="D34" s="137"/>
       <c r="E34" s="138"/>
       <c r="F34" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G34" s="139"/>
       <c r="H34" s="140"/>
@@ -7838,24 +7927,24 @@
       <c r="J34" s="13"/>
       <c r="K34" s="141"/>
       <c r="L34" s="142" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M34" s="142" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N34" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O34" s="141" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P34" s="143" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B35" s="135" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C35" s="136"/>
       <c r="D35" s="137"/>
@@ -7868,13 +7957,13 @@
       <c r="K35" s="141"/>
       <c r="L35" s="142"/>
       <c r="M35" s="142" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N35" s="141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O35" s="141" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P35" s="143"/>
     </row>
@@ -7883,7 +7972,7 @@
       <c r="C36" s="150"/>
       <c r="D36" s="181"/>
       <c r="E36" s="152" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F36" s="182"/>
       <c r="G36" s="183"/>
@@ -7892,16 +7981,16 @@
       <c r="J36" s="152"/>
       <c r="K36" s="155"/>
       <c r="L36" s="156" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M36" s="156" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N36" s="155" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O36" s="155" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P36" s="157"/>
     </row>
@@ -7927,7 +8016,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="195" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C38" s="196"/>
       <c r="D38" s="138"/>
@@ -7949,66 +8038,66 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="142" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C39" s="142" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="142" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C40" s="142" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="197" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="198" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D43" s="199" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E43" s="200" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F43" s="200" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G43" s="200" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H43" s="199"/>
       <c r="I43" s="200" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J43" s="200" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K43" s="200" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L43" s="198" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M43" s="201" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N43" s="197" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O43" s="198"/>
       <c r="P43" s="197"/>
@@ -8031,23 +8120,23 @@
       <c r="G44" s="204"/>
       <c r="H44" s="205"/>
       <c r="I44" s="193" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J44" s="193" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K44" s="206" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L44" s="12" t="n">
         <f aca="false">IF(D44=1,128,0)+IF(E44=1,64,0)+IF(F44=1,32,0)+IF(G44=1,16,0)+IF(H44=1,8,0)+IF(I44=1,4,0)+IF(J44=1,2,0)+IF(K44=1,1,0)</f>
         <v>128</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
@@ -8074,20 +8163,20 @@
         <v>1</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L45" s="12" t="n">
         <f aca="false">IF(D45=1,128,0)+IF(E45=1,64,0)+IF(F45=1,32,0)+IF(G45=1,16,0)+IF(H45=1,8,0)+IF(I45=1,4,0)+IF(J45=1,2,0)+IF(K45=1,1,0)</f>
         <v>4</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
@@ -8105,10 +8194,10 @@
         <v>0</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G46" s="186" t="n">
         <v>1</v>
@@ -8118,20 +8207,20 @@
         <v>1</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L46" s="12" t="n">
         <f aca="false">IF(D46=1,128,0)+IF(E46=1,64,0)+IF(F46=1,32,0)+IF(G46=1,16,0)+IF(H46=1,8,0)+IF(I46=1,4,0)+IF(J46=1,2,0)+IF(K46=1,1,0)</f>
         <v>20</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
@@ -8158,20 +8247,20 @@
         <v>0</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L47" s="12" t="n">
         <f aca="false">IF(D47=1,128,0)+IF(E47=1,64,0)+IF(F47=1,32,0)+IF(G47=1,16,0)+IF(H47=1,8,0)+IF(I47=1,4,0)+IF(J47=1,2,0)+IF(K47=1,1,0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
@@ -8187,7 +8276,7 @@
       </c>
       <c r="D48" s="137"/>
       <c r="E48" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F48" s="13" t="n">
         <v>0</v>
@@ -8200,20 +8289,20 @@
         <v>0</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L48" s="12" t="n">
         <f aca="false">IF(D48=1,128,0)+IF(E48=1,64,0)+IF(F48=1,32,0)+IF(G48=1,16,0)+IF(H48=1,8,0)+IF(I48=1,4,0)+IF(J48=1,2,0)+IF(K48=1,1,0)</f>
         <v>16</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="11"/>
@@ -8241,20 +8330,20 @@
         <v>0</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L49" s="12" t="n">
         <f aca="false">IF(D49=1,128,0)+IF(E49=1,64,0)+IF(F49=1,32,0)+IF(G49=1,16,0)+IF(H49=1,8,0)+IF(I49=1,4,0)+IF(J49=1,2,0)+IF(K49=1,1,0)</f>
         <v>32</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P49" s="11"/>
       <c r="Q49" s="11"/>
@@ -8272,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="207" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F50" s="207" t="n">
         <v>1</v>
@@ -8285,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="207" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K50" s="209" t="n">
         <v>1</v>
@@ -8295,10 +8384,10 @@
         <v>49</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P50" s="11"/>
       <c r="Q50" s="11"/>
@@ -8348,13 +8437,13 @@
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="210"/>
       <c r="B1" s="211" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E1" s="26" t="n">
         <v>7</v>
@@ -8381,13 +8470,13 @@
         <v>0</v>
       </c>
       <c r="M1" s="213" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N1" s="213" t="s">
         <v>1</v>
       </c>
       <c r="O1" s="214" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P1" s="215" t="s">
         <v>3</v>
@@ -8395,7 +8484,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="216" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B2" s="217"/>
       <c r="C2" s="218" t="str">
@@ -8423,13 +8512,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="219" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N2" s="217"/>
       <c r="O2" s="220"/>
       <c r="P2" s="221"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A3" s="222"/>
       <c r="B3" s="142"/>
       <c r="C3" s="17"/>
@@ -8437,10 +8526,10 @@
       <c r="E3" s="49"/>
       <c r="F3" s="119"/>
       <c r="G3" s="119" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="13"/>
@@ -8448,19 +8537,19 @@
       <c r="L3" s="50"/>
       <c r="M3" s="223"/>
       <c r="N3" s="223" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O3" s="224" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P3" s="225"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A4" s="222"/>
       <c r="B4" s="142"/>
       <c r="E4" s="49"/>
       <c r="F4" s="119" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G4" s="119"/>
       <c r="H4" s="50"/>
@@ -8469,13 +8558,13 @@
       <c r="K4" s="119"/>
       <c r="L4" s="50"/>
       <c r="M4" s="223" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
       <c r="P4" s="226"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A5" s="222"/>
       <c r="B5" s="142"/>
       <c r="C5" s="17"/>
@@ -8492,10 +8581,10 @@
       <c r="O5" s="224"/>
       <c r="P5" s="225"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A6" s="222"/>
       <c r="B6" s="142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="119"/>
@@ -8510,13 +8599,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P6" s="226"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="216" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B7" s="217"/>
       <c r="C7" s="218" t="str">
@@ -8544,13 +8633,13 @@
         <v>1</v>
       </c>
       <c r="M7" s="219" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N7" s="217"/>
       <c r="O7" s="219"/>
       <c r="P7" s="221"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A8" s="222"/>
       <c r="B8" s="142"/>
       <c r="C8" s="17"/>
@@ -8558,10 +8647,10 @@
       <c r="E8" s="49"/>
       <c r="F8" s="119"/>
       <c r="G8" s="119" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I8" s="49"/>
       <c r="J8" s="13"/>
@@ -8569,16 +8658,16 @@
       <c r="L8" s="50"/>
       <c r="M8" s="223"/>
       <c r="N8" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O8" s="224" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P8" s="225" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A9" s="222"/>
       <c r="B9" s="142"/>
       <c r="C9" s="17"/>
@@ -8595,10 +8684,10 @@
       <c r="O9" s="224"/>
       <c r="P9" s="225"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A10" s="222"/>
       <c r="B10" s="142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E10" s="146"/>
       <c r="F10" s="119"/>
@@ -8613,13 +8702,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P10" s="226"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="216" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B11" s="217"/>
       <c r="C11" s="218" t="str">
@@ -8647,13 +8736,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="219" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N11" s="217"/>
       <c r="O11" s="220"/>
       <c r="P11" s="221"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A12" s="222"/>
       <c r="B12" s="142"/>
       <c r="C12" s="17"/>
@@ -8661,10 +8750,10 @@
       <c r="E12" s="49"/>
       <c r="F12" s="119"/>
       <c r="G12" s="119" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I12" s="49"/>
       <c r="J12" s="13"/>
@@ -8672,16 +8761,16 @@
       <c r="L12" s="50"/>
       <c r="M12" s="223"/>
       <c r="N12" s="223" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O12" s="224" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P12" s="227" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A13" s="222"/>
       <c r="B13" s="142"/>
       <c r="C13" s="17"/>
@@ -8698,10 +8787,10 @@
       <c r="O13" s="224"/>
       <c r="P13" s="225"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A14" s="222"/>
       <c r="B14" s="142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="119"/>
@@ -8716,15 +8805,15 @@
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P14" s="226" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="216" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B15" s="217"/>
       <c r="C15" s="218" t="str">
@@ -8752,13 +8841,13 @@
         <v>1</v>
       </c>
       <c r="M15" s="219" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N15" s="217"/>
       <c r="O15" s="219"/>
       <c r="P15" s="221"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A16" s="222"/>
       <c r="B16" s="142"/>
       <c r="C16" s="17"/>
@@ -8775,10 +8864,10 @@
       <c r="O16" s="224"/>
       <c r="P16" s="225"/>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A17" s="222"/>
       <c r="B17" s="142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="119"/>
@@ -8792,19 +8881,19 @@
       <c r="L17" s="50"/>
       <c r="M17" s="223"/>
       <c r="N17" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O17" s="224" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P17" s="225" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A18" s="222"/>
       <c r="B18" s="142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E18" s="146"/>
       <c r="F18" s="119"/>
@@ -8819,15 +8908,15 @@
         <v>1</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P18" s="228" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="216" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B19" s="217"/>
       <c r="C19" s="218" t="str">
@@ -8855,13 +8944,13 @@
         <v>0</v>
       </c>
       <c r="M19" s="219" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N19" s="217"/>
       <c r="O19" s="219"/>
       <c r="P19" s="221"/>
     </row>
-    <row r="20" s="229" customFormat="true" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="20" s="229" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A20" s="222"/>
       <c r="B20" s="142"/>
       <c r="C20" s="20"/>
@@ -8869,10 +8958,10 @@
       <c r="E20" s="146"/>
       <c r="F20" s="119"/>
       <c r="G20" s="119" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I20" s="119"/>
       <c r="J20" s="119"/>
@@ -8880,19 +8969,19 @@
       <c r="L20" s="50"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P20" s="225"/>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A21" s="222"/>
       <c r="B21" s="142"/>
       <c r="E21" s="146"/>
       <c r="F21" s="119" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G21" s="119"/>
       <c r="H21" s="50"/>
@@ -8901,15 +8990,15 @@
       <c r="K21" s="119"/>
       <c r="L21" s="50"/>
       <c r="M21" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="142"/>
       <c r="P21" s="225" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A22" s="222"/>
       <c r="B22" s="142"/>
       <c r="E22" s="146"/>
@@ -8922,20 +9011,20 @@
       <c r="L22" s="50"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O22" s="142" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P22" s="225"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A23" s="230"/>
       <c r="B23" s="231"/>
       <c r="C23" s="232"/>
       <c r="D23" s="233"/>
       <c r="E23" s="234" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F23" s="233"/>
       <c r="G23" s="233"/>
@@ -8945,18 +9034,18 @@
       <c r="K23" s="233"/>
       <c r="L23" s="235"/>
       <c r="M23" s="237" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N23" s="229"/>
       <c r="O23" s="238"/>
       <c r="P23" s="239" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A24" s="222"/>
       <c r="B24" s="142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E24" s="146"/>
       <c r="F24" s="119"/>
@@ -8969,15 +9058,15 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P24" s="225" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="216" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B25" s="217"/>
       <c r="C25" s="218" t="str">
@@ -9005,18 +9094,18 @@
         <v>1</v>
       </c>
       <c r="M25" s="219" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N25" s="217"/>
       <c r="O25" s="219"/>
       <c r="P25" s="221"/>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A26" s="222"/>
       <c r="B26" s="142"/>
       <c r="E26" s="146"/>
       <c r="F26" s="119" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G26" s="119"/>
       <c r="H26" s="50"/>
@@ -9025,15 +9114,15 @@
       <c r="K26" s="119"/>
       <c r="L26" s="50"/>
       <c r="M26" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="142"/>
       <c r="P26" s="225" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A27" s="222"/>
       <c r="B27" s="142"/>
       <c r="E27" s="146"/>
@@ -9046,14 +9135,14 @@
       <c r="L27" s="50"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O27" s="142" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P27" s="225"/>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A28" s="222"/>
       <c r="B28" s="142"/>
       <c r="C28" s="17"/>
@@ -9069,10 +9158,10 @@
       <c r="M28" s="223"/>
       <c r="O28" s="224"/>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A29" s="222"/>
       <c r="B29" s="142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="119"/>
@@ -9085,79 +9174,74 @@
       <c r="K29" s="119"/>
       <c r="L29" s="50"/>
       <c r="M29" s="223"/>
-      <c r="N29" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="O29" s="224" t="s">
-        <v>252</v>
-      </c>
-      <c r="P29" s="225" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A30" s="222"/>
-      <c r="B30" s="142" t="s">
-        <v>239</v>
-      </c>
-      <c r="E30" s="146"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="146"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O30" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="P30" s="228" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="216" t="s">
-        <v>269</v>
-      </c>
-      <c r="B31" s="217"/>
-      <c r="C31" s="218" t="str">
-        <f aca="false">DEC2HEX(D31,2)</f>
+      <c r="N29" s="240" t="s">
+        <v>1</v>
+      </c>
+      <c r="O29" s="241" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" s="242" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="216" t="s">
+        <v>272</v>
+      </c>
+      <c r="B30" s="217"/>
+      <c r="C30" s="218" t="str">
+        <f aca="false">DEC2HEX(D30,2)</f>
         <v>06</v>
       </c>
-      <c r="D31" s="173" t="n">
-        <f aca="false">IF(E31=1,128,0)+IF(F31=1,64,0)+IF(G31=1,32,0)+IF(H31=1,16,0)+IF(I31=1,8,0)+IF(J31=1,4,0)+IF(K31=1,2,0)+IF(L31=1,1,0)</f>
+      <c r="D30" s="173" t="n">
+        <f aca="false">IF(E30=1,128,0)+IF(F30=1,64,0)+IF(G30=1,32,0)+IF(H30=1,16,0)+IF(I30=1,8,0)+IF(J30=1,4,0)+IF(K30=1,2,0)+IF(L30=1,1,0)</f>
         <v>6</v>
       </c>
-      <c r="E31" s="188"/>
-      <c r="F31" s="173"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="219" t="s">
-        <v>270</v>
-      </c>
-      <c r="N31" s="217"/>
-      <c r="O31" s="219"/>
-      <c r="P31" s="240" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="E30" s="188"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="177"/>
+      <c r="I30" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="219" t="s">
+        <v>273</v>
+      </c>
+      <c r="N30" s="217"/>
+      <c r="O30" s="219"/>
+      <c r="P30" s="243" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A31" s="222"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="119"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="142" t="s">
+        <v>275</v>
+      </c>
+      <c r="P31" s="225"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A32" s="222"/>
       <c r="E32" s="146"/>
       <c r="F32" s="119"/>
@@ -9165,37 +9249,37 @@
         <v>0</v>
       </c>
       <c r="H32" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="119"/>
       <c r="J32" s="119"/>
       <c r="K32" s="119"/>
       <c r="L32" s="50"/>
-      <c r="M32" s="142" t="s">
-        <v>272</v>
+      <c r="M32" s="223" t="s">
+        <v>276</v>
       </c>
       <c r="P32" s="225"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A33" s="222"/>
       <c r="E33" s="146"/>
       <c r="F33" s="119"/>
       <c r="G33" s="119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="119"/>
       <c r="J33" s="119"/>
       <c r="K33" s="119"/>
       <c r="L33" s="50"/>
       <c r="M33" s="223" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P33" s="225"/>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A34" s="222"/>
       <c r="E34" s="146"/>
       <c r="F34" s="119"/>
@@ -9203,130 +9287,132 @@
         <v>1</v>
       </c>
       <c r="H34" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="119"/>
       <c r="J34" s="119"/>
       <c r="K34" s="119"/>
       <c r="L34" s="50"/>
-      <c r="M34" s="223" t="s">
-        <v>274</v>
+      <c r="M34" s="10" t="s">
+        <v>278</v>
       </c>
       <c r="P34" s="225"/>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A35" s="222"/>
       <c r="E35" s="146"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="50" t="n">
-        <v>1</v>
-      </c>
+      <c r="F35" s="119" t="s">
+        <v>279</v>
+      </c>
+      <c r="G35" s="119"/>
+      <c r="H35" s="50"/>
       <c r="I35" s="119"/>
       <c r="J35" s="119"/>
       <c r="K35" s="119"/>
       <c r="L35" s="50"/>
-      <c r="M35" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="P35" s="225"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M35" s="142" t="s">
+        <v>280</v>
+      </c>
+      <c r="P35" s="225" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A36" s="222"/>
-      <c r="E36" s="146"/>
-      <c r="F36" s="119" t="s">
-        <v>276</v>
-      </c>
+      <c r="B36" s="142"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="119"/>
       <c r="H36" s="50"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="13"/>
       <c r="K36" s="119"/>
       <c r="L36" s="50"/>
-      <c r="M36" s="142" t="s">
-        <v>277</v>
-      </c>
-      <c r="P36" s="225" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M36" s="223"/>
+      <c r="O36" s="224"/>
+      <c r="P36" s="225"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A37" s="222"/>
-      <c r="B37" s="142"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="49"/>
+      <c r="B37" s="142" t="s">
+        <v>241</v>
+      </c>
+      <c r="E37" s="146"/>
       <c r="F37" s="119"/>
       <c r="G37" s="119"/>
       <c r="H37" s="50"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="13"/>
+      <c r="I37" s="119"/>
+      <c r="J37" s="119"/>
       <c r="K37" s="119"/>
       <c r="L37" s="50"/>
-      <c r="M37" s="223"/>
-      <c r="O37" s="224"/>
-      <c r="P37" s="225"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A38" s="222"/>
-      <c r="B38" s="142" t="s">
-        <v>239</v>
-      </c>
-      <c r="E38" s="146"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="119"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="119"/>
-      <c r="J38" s="119"/>
-      <c r="K38" s="119"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="142"/>
-      <c r="O38" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="P38" s="225" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="216" t="s">
-        <v>281</v>
-      </c>
-      <c r="B39" s="217"/>
-      <c r="C39" s="218" t="str">
-        <f aca="false">DEC2HEX(D39,2)</f>
+      <c r="M37" s="142"/>
+      <c r="O37" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="P37" s="225" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="216" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="217"/>
+      <c r="C38" s="218" t="str">
+        <f aca="false">DEC2HEX(D38,2)</f>
         <v>07</v>
       </c>
-      <c r="D39" s="173" t="n">
-        <f aca="false">IF(E39=1,128,0)+IF(F39=1,64,0)+IF(G39=1,32,0)+IF(H39=1,16,0)+IF(I39=1,8,0)+IF(J39=1,4,0)+IF(K39=1,2,0)+IF(L39=1,1,0)</f>
+      <c r="D38" s="173" t="n">
+        <f aca="false">IF(E38=1,128,0)+IF(F38=1,64,0)+IF(G38=1,32,0)+IF(H38=1,16,0)+IF(I38=1,8,0)+IF(J38=1,4,0)+IF(K38=1,2,0)+IF(L38=1,1,0)</f>
         <v>7</v>
       </c>
-      <c r="E39" s="188"/>
-      <c r="F39" s="173"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="177"/>
-      <c r="I39" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="219" t="s">
-        <v>282</v>
-      </c>
-      <c r="N39" s="217"/>
-      <c r="O39" s="219"/>
-      <c r="P39" s="221"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="E38" s="188"/>
+      <c r="F38" s="173"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="177"/>
+      <c r="I38" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="219" t="s">
+        <v>285</v>
+      </c>
+      <c r="N38" s="217"/>
+      <c r="O38" s="219"/>
+      <c r="P38" s="221"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A39" s="222"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="119"/>
+      <c r="J39" s="119"/>
+      <c r="K39" s="119"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="142" t="s">
+        <v>286</v>
+      </c>
+      <c r="P39" s="227" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A40" s="222"/>
       <c r="E40" s="146"/>
       <c r="F40" s="119"/>
@@ -9334,41 +9420,41 @@
         <v>0</v>
       </c>
       <c r="H40" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="119"/>
       <c r="J40" s="119"/>
       <c r="K40" s="119"/>
       <c r="L40" s="50"/>
-      <c r="M40" s="142" t="s">
-        <v>283</v>
+      <c r="M40" s="223" t="s">
+        <v>276</v>
       </c>
       <c r="P40" s="227" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A41" s="222"/>
       <c r="E41" s="146"/>
       <c r="F41" s="119"/>
       <c r="G41" s="119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="119"/>
       <c r="J41" s="119"/>
       <c r="K41" s="119"/>
       <c r="L41" s="50"/>
       <c r="M41" s="223" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P41" s="227" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A42" s="222"/>
       <c r="E42" s="146"/>
       <c r="F42" s="119"/>
@@ -9376,41 +9462,36 @@
         <v>1</v>
       </c>
       <c r="H42" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="119"/>
       <c r="J42" s="119"/>
       <c r="K42" s="119"/>
       <c r="L42" s="50"/>
-      <c r="M42" s="223" t="s">
-        <v>274</v>
+      <c r="M42" s="10" t="s">
+        <v>278</v>
       </c>
       <c r="P42" s="227" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A43" s="222"/>
       <c r="E43" s="146"/>
       <c r="F43" s="119"/>
-      <c r="G43" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="50" t="n">
-        <v>1</v>
-      </c>
+      <c r="G43" s="119"/>
+      <c r="H43" s="50"/>
       <c r="I43" s="119"/>
       <c r="J43" s="119"/>
       <c r="K43" s="119"/>
       <c r="L43" s="50"/>
-      <c r="M43" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="P43" s="227" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M43" s="10"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="244" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A44" s="222"/>
       <c r="E44" s="146"/>
       <c r="F44" s="119"/>
@@ -9422,11 +9503,11 @@
       <c r="L44" s="50"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="241" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="P44" s="244" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A45" s="222"/>
       <c r="E45" s="146"/>
       <c r="F45" s="119"/>
@@ -9438,29 +9519,32 @@
       <c r="L45" s="50"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="241" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="P45" s="244" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A46" s="222"/>
-      <c r="E46" s="146"/>
+      <c r="B46" s="142"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="49"/>
       <c r="F46" s="119"/>
       <c r="G46" s="119"/>
       <c r="H46" s="50"/>
-      <c r="I46" s="119"/>
-      <c r="J46" s="119"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="13"/>
       <c r="K46" s="119"/>
       <c r="L46" s="50"/>
-      <c r="M46" s="10"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="241" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M46" s="223"/>
+      <c r="O46" s="224"/>
+      <c r="P46" s="225"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A47" s="222"/>
-      <c r="B47" s="142"/>
+      <c r="B47" s="223" t="s">
+        <v>241</v>
+      </c>
       <c r="C47" s="17"/>
       <c r="D47" s="119"/>
       <c r="E47" s="49"/>
@@ -9472,459 +9556,455 @@
       <c r="K47" s="119"/>
       <c r="L47" s="50"/>
       <c r="M47" s="223"/>
-      <c r="O47" s="224"/>
-      <c r="P47" s="225"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="222"/>
+      <c r="N47" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="O47" s="224" t="s">
+        <v>295</v>
+      </c>
+      <c r="P47" s="225" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A48" s="245"/>
       <c r="B48" s="223" t="s">
-        <v>239</v>
-      </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="119"/>
-      <c r="G48" s="119"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="119"/>
-      <c r="L48" s="50"/>
-      <c r="M48" s="223"/>
-      <c r="N48" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="O48" s="224" t="s">
-        <v>292</v>
-      </c>
-      <c r="P48" s="225" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A49" s="242"/>
-      <c r="B49" s="223" t="s">
-        <v>239</v>
-      </c>
-      <c r="C49" s="243"/>
-      <c r="D49" s="152"/>
-      <c r="E49" s="244"/>
-      <c r="F49" s="152"/>
-      <c r="G49" s="152"/>
-      <c r="H49" s="155"/>
-      <c r="I49" s="152"/>
-      <c r="J49" s="152"/>
-      <c r="K49" s="152"/>
-      <c r="L49" s="155"/>
-      <c r="M49" s="245"/>
-      <c r="N49" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="P49" s="228" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="216"/>
-      <c r="B50" s="217"/>
-      <c r="C50" s="218" t="str">
-        <f aca="false">DEC2HEX(D50,2)</f>
+        <v>241</v>
+      </c>
+      <c r="C48" s="246"/>
+      <c r="D48" s="152"/>
+      <c r="E48" s="247"/>
+      <c r="F48" s="152"/>
+      <c r="G48" s="152"/>
+      <c r="H48" s="155"/>
+      <c r="I48" s="152"/>
+      <c r="J48" s="152"/>
+      <c r="K48" s="152"/>
+      <c r="L48" s="155"/>
+      <c r="M48" s="248"/>
+      <c r="N48" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="P48" s="228" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="216"/>
+      <c r="B49" s="217"/>
+      <c r="C49" s="218" t="str">
+        <f aca="false">DEC2HEX(D49,2)</f>
         <v>08</v>
       </c>
-      <c r="D50" s="173" t="n">
-        <f aca="false">IF(E50=1,128,0)+IF(F50=1,64,0)+IF(G50=1,32,0)+IF(H50=1,16,0)+IF(I50=1,8,0)+IF(J50=1,4,0)+IF(K50=1,2,0)+IF(L50=1,1,0)</f>
+      <c r="D49" s="173" t="n">
+        <f aca="false">IF(E49=1,128,0)+IF(F49=1,64,0)+IF(G49=1,32,0)+IF(H49=1,16,0)+IF(I49=1,8,0)+IF(J49=1,4,0)+IF(K49=1,2,0)+IF(L49=1,1,0)</f>
         <v>8</v>
       </c>
-      <c r="E50" s="188"/>
-      <c r="F50" s="173"/>
-      <c r="G50" s="173"/>
-      <c r="H50" s="177"/>
-      <c r="I50" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="219"/>
-      <c r="N50" s="217"/>
-      <c r="O50" s="219"/>
-      <c r="P50" s="221"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A51" s="222"/>
-      <c r="B51" s="142"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="119"/>
-      <c r="H51" s="50"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="119"/>
-      <c r="L51" s="50"/>
-      <c r="M51" s="223"/>
-      <c r="O51" s="224"/>
-      <c r="P51" s="225"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="216"/>
-      <c r="B52" s="217"/>
-      <c r="C52" s="218" t="str">
-        <f aca="false">DEC2HEX(D52,2)</f>
+      <c r="E49" s="188"/>
+      <c r="F49" s="173"/>
+      <c r="G49" s="173"/>
+      <c r="H49" s="177"/>
+      <c r="I49" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="219"/>
+      <c r="N49" s="217"/>
+      <c r="O49" s="219"/>
+      <c r="P49" s="221"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A50" s="222"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="119"/>
+      <c r="G50" s="119"/>
+      <c r="H50" s="50"/>
+      <c r="I50" s="49"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="119"/>
+      <c r="L50" s="50"/>
+      <c r="M50" s="223"/>
+      <c r="O50" s="224"/>
+      <c r="P50" s="225"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="216"/>
+      <c r="B51" s="217"/>
+      <c r="C51" s="218" t="str">
+        <f aca="false">DEC2HEX(D51,2)</f>
         <v>09</v>
       </c>
-      <c r="D52" s="173" t="n">
-        <f aca="false">IF(E52=1,128,0)+IF(F52=1,64,0)+IF(G52=1,32,0)+IF(H52=1,16,0)+IF(I52=1,8,0)+IF(J52=1,4,0)+IF(K52=1,2,0)+IF(L52=1,1,0)</f>
+      <c r="D51" s="173" t="n">
+        <f aca="false">IF(E51=1,128,0)+IF(F51=1,64,0)+IF(G51=1,32,0)+IF(H51=1,16,0)+IF(I51=1,8,0)+IF(J51=1,4,0)+IF(K51=1,2,0)+IF(L51=1,1,0)</f>
         <v>9</v>
       </c>
-      <c r="E52" s="188"/>
-      <c r="F52" s="173"/>
-      <c r="G52" s="173"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" s="219"/>
-      <c r="N52" s="217"/>
-      <c r="O52" s="219"/>
-      <c r="P52" s="221"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A53" s="222"/>
-      <c r="B53" s="142"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="119"/>
-      <c r="H53" s="50"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="119"/>
-      <c r="L53" s="50"/>
-      <c r="M53" s="223"/>
-      <c r="O53" s="224"/>
-      <c r="P53" s="225"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="216" t="s">
-        <v>294</v>
-      </c>
-      <c r="B54" s="217"/>
-      <c r="C54" s="218" t="str">
-        <f aca="false">DEC2HEX(D54,2)</f>
+      <c r="E51" s="188"/>
+      <c r="F51" s="173"/>
+      <c r="G51" s="173"/>
+      <c r="H51" s="177"/>
+      <c r="I51" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="219"/>
+      <c r="N51" s="217"/>
+      <c r="O51" s="219"/>
+      <c r="P51" s="221"/>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A52" s="222"/>
+      <c r="B52" s="142"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="50"/>
+      <c r="I52" s="49"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="119"/>
+      <c r="L52" s="50"/>
+      <c r="M52" s="223"/>
+      <c r="O52" s="224"/>
+      <c r="P52" s="225"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="216" t="s">
+        <v>297</v>
+      </c>
+      <c r="B53" s="217"/>
+      <c r="C53" s="218" t="str">
+        <f aca="false">DEC2HEX(D53,2)</f>
         <v>0A</v>
       </c>
-      <c r="D54" s="173" t="n">
-        <f aca="false">IF(E54=1,128,0)+IF(F54=1,64,0)+IF(G54=1,32,0)+IF(H54=1,16,0)+IF(I54=1,8,0)+IF(J54=1,4,0)+IF(K54=1,2,0)+IF(L54=1,1,0)</f>
+      <c r="D53" s="173" t="n">
+        <f aca="false">IF(E53=1,128,0)+IF(F53=1,64,0)+IF(G53=1,32,0)+IF(H53=1,16,0)+IF(I53=1,8,0)+IF(J53=1,4,0)+IF(K53=1,2,0)+IF(L53=1,1,0)</f>
         <v>10</v>
       </c>
-      <c r="E54" s="188"/>
-      <c r="F54" s="173"/>
-      <c r="G54" s="173"/>
-      <c r="H54" s="177"/>
-      <c r="I54" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="219" t="s">
-        <v>295</v>
-      </c>
-      <c r="N54" s="217"/>
-      <c r="O54" s="219"/>
-      <c r="P54" s="221"/>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="E53" s="188"/>
+      <c r="F53" s="173"/>
+      <c r="G53" s="173"/>
+      <c r="H53" s="177"/>
+      <c r="I53" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="219" t="s">
+        <v>298</v>
+      </c>
+      <c r="N53" s="217"/>
+      <c r="O53" s="219"/>
+      <c r="P53" s="221"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A54" s="222"/>
+      <c r="B54" s="142"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="119"/>
+      <c r="G54" s="119"/>
+      <c r="H54" s="50"/>
+      <c r="I54" s="49"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="119"/>
+      <c r="L54" s="50"/>
+      <c r="M54" s="223"/>
+      <c r="O54" s="224"/>
+      <c r="P54" s="225"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A55" s="222"/>
-      <c r="B55" s="142"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="119"/>
-      <c r="E55" s="49"/>
+      <c r="B55" s="223" t="s">
+        <v>241</v>
+      </c>
+      <c r="E55" s="146"/>
       <c r="F55" s="119"/>
       <c r="G55" s="119"/>
       <c r="H55" s="50"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="13"/>
+      <c r="I55" s="119"/>
+      <c r="J55" s="119"/>
       <c r="K55" s="119"/>
       <c r="L55" s="50"/>
-      <c r="M55" s="223"/>
-      <c r="O55" s="224"/>
-      <c r="P55" s="225"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A56" s="222"/>
-      <c r="B56" s="223" t="s">
-        <v>239</v>
-      </c>
-      <c r="E56" s="146"/>
-      <c r="F56" s="119"/>
-      <c r="G56" s="119"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="119"/>
-      <c r="J56" s="119"/>
-      <c r="K56" s="119"/>
-      <c r="L56" s="50"/>
-      <c r="M56" s="142"/>
-      <c r="N56" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="O56" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="P56" s="225" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="216"/>
-      <c r="B57" s="217"/>
-      <c r="C57" s="218" t="str">
-        <f aca="false">DEC2HEX(D57,2)</f>
+      <c r="M55" s="142"/>
+      <c r="N55" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="O55" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="P55" s="225" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="216"/>
+      <c r="B56" s="217"/>
+      <c r="C56" s="218" t="str">
+        <f aca="false">DEC2HEX(D56,2)</f>
         <v>0B</v>
       </c>
-      <c r="D57" s="173" t="n">
-        <f aca="false">IF(E57=1,128,0)+IF(F57=1,64,0)+IF(G57=1,32,0)+IF(H57=1,16,0)+IF(I57=1,8,0)+IF(J57=1,4,0)+IF(K57=1,2,0)+IF(L57=1,1,0)</f>
+      <c r="D56" s="173" t="n">
+        <f aca="false">IF(E56=1,128,0)+IF(F56=1,64,0)+IF(G56=1,32,0)+IF(H56=1,16,0)+IF(I56=1,8,0)+IF(J56=1,4,0)+IF(K56=1,2,0)+IF(L56=1,1,0)</f>
         <v>11</v>
       </c>
-      <c r="E57" s="188"/>
-      <c r="F57" s="173"/>
-      <c r="G57" s="173"/>
-      <c r="H57" s="177"/>
-      <c r="I57" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="219"/>
-      <c r="N57" s="217"/>
-      <c r="O57" s="219"/>
-      <c r="P57" s="221"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="222"/>
-      <c r="B58" s="142"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="119"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="119"/>
-      <c r="G58" s="119"/>
-      <c r="H58" s="50"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="119"/>
-      <c r="L58" s="50"/>
-      <c r="M58" s="223"/>
-      <c r="O58" s="224"/>
-      <c r="P58" s="225"/>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="216"/>
-      <c r="B59" s="217"/>
-      <c r="C59" s="218" t="str">
-        <f aca="false">DEC2HEX(D59,2)</f>
+      <c r="E56" s="188"/>
+      <c r="F56" s="173"/>
+      <c r="G56" s="173"/>
+      <c r="H56" s="177"/>
+      <c r="I56" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="219"/>
+      <c r="N56" s="217"/>
+      <c r="O56" s="219"/>
+      <c r="P56" s="221"/>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A57" s="222"/>
+      <c r="B57" s="142"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="119"/>
+      <c r="G57" s="119"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="119"/>
+      <c r="L57" s="50"/>
+      <c r="M57" s="223"/>
+      <c r="O57" s="224"/>
+      <c r="P57" s="225"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="216"/>
+      <c r="B58" s="217"/>
+      <c r="C58" s="218" t="str">
+        <f aca="false">DEC2HEX(D58,2)</f>
         <v>0C</v>
       </c>
-      <c r="D59" s="173" t="n">
-        <f aca="false">IF(E59=1,128,0)+IF(F59=1,64,0)+IF(G59=1,32,0)+IF(H59=1,16,0)+IF(I59=1,8,0)+IF(J59=1,4,0)+IF(K59=1,2,0)+IF(L59=1,1,0)</f>
+      <c r="D58" s="173" t="n">
+        <f aca="false">IF(E58=1,128,0)+IF(F58=1,64,0)+IF(G58=1,32,0)+IF(H58=1,16,0)+IF(I58=1,8,0)+IF(J58=1,4,0)+IF(K58=1,2,0)+IF(L58=1,1,0)</f>
         <v>12</v>
       </c>
-      <c r="E59" s="188"/>
-      <c r="F59" s="173"/>
-      <c r="G59" s="173"/>
-      <c r="H59" s="177"/>
-      <c r="I59" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="217"/>
-      <c r="N59" s="217"/>
-      <c r="O59" s="219"/>
-      <c r="P59" s="221"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A60" s="222"/>
-      <c r="E60" s="146"/>
-      <c r="F60" s="119"/>
-      <c r="G60" s="119"/>
-      <c r="H60" s="50"/>
-      <c r="I60" s="119"/>
-      <c r="J60" s="119"/>
-      <c r="K60" s="119"/>
-      <c r="L60" s="50"/>
-      <c r="M60" s="223"/>
-      <c r="N60" s="223"/>
-      <c r="O60" s="142"/>
-      <c r="P60" s="225"/>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="216"/>
-      <c r="B61" s="217"/>
-      <c r="C61" s="218" t="str">
-        <f aca="false">DEC2HEX(D61,2)</f>
+      <c r="E58" s="188"/>
+      <c r="F58" s="173"/>
+      <c r="G58" s="173"/>
+      <c r="H58" s="177"/>
+      <c r="I58" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="217"/>
+      <c r="N58" s="217"/>
+      <c r="O58" s="219"/>
+      <c r="P58" s="221"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A59" s="222"/>
+      <c r="E59" s="146"/>
+      <c r="F59" s="119"/>
+      <c r="G59" s="119"/>
+      <c r="H59" s="50"/>
+      <c r="I59" s="119"/>
+      <c r="J59" s="119"/>
+      <c r="K59" s="119"/>
+      <c r="L59" s="50"/>
+      <c r="M59" s="223"/>
+      <c r="N59" s="223"/>
+      <c r="O59" s="142"/>
+      <c r="P59" s="225"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="216"/>
+      <c r="B60" s="217"/>
+      <c r="C60" s="218" t="str">
+        <f aca="false">DEC2HEX(D60,2)</f>
         <v>0D</v>
       </c>
-      <c r="D61" s="173" t="n">
-        <f aca="false">IF(E61=1,128,0)+IF(F61=1,64,0)+IF(G61=1,32,0)+IF(H61=1,16,0)+IF(I61=1,8,0)+IF(J61=1,4,0)+IF(K61=1,2,0)+IF(L61=1,1,0)</f>
+      <c r="D60" s="173" t="n">
+        <f aca="false">IF(E60=1,128,0)+IF(F60=1,64,0)+IF(G60=1,32,0)+IF(H60=1,16,0)+IF(I60=1,8,0)+IF(J60=1,4,0)+IF(K60=1,2,0)+IF(L60=1,1,0)</f>
         <v>13</v>
       </c>
-      <c r="E61" s="188"/>
-      <c r="F61" s="173"/>
-      <c r="G61" s="173"/>
-      <c r="H61" s="177"/>
-      <c r="I61" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="217"/>
-      <c r="N61" s="217"/>
-      <c r="O61" s="219"/>
-      <c r="P61" s="221"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A62" s="222"/>
-      <c r="E62" s="146"/>
-      <c r="F62" s="119"/>
-      <c r="G62" s="119"/>
-      <c r="H62" s="50"/>
-      <c r="I62" s="119"/>
-      <c r="J62" s="119"/>
-      <c r="K62" s="119"/>
-      <c r="L62" s="50"/>
-      <c r="M62" s="223"/>
-      <c r="N62" s="223"/>
-      <c r="O62" s="142"/>
-      <c r="P62" s="225"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="216"/>
-      <c r="B63" s="217"/>
-      <c r="C63" s="218" t="str">
-        <f aca="false">DEC2HEX(D63,2)</f>
+      <c r="E60" s="188"/>
+      <c r="F60" s="173"/>
+      <c r="G60" s="173"/>
+      <c r="H60" s="177"/>
+      <c r="I60" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="217"/>
+      <c r="N60" s="217"/>
+      <c r="O60" s="219"/>
+      <c r="P60" s="221"/>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A61" s="222"/>
+      <c r="E61" s="146"/>
+      <c r="F61" s="119"/>
+      <c r="G61" s="119"/>
+      <c r="H61" s="50"/>
+      <c r="I61" s="119"/>
+      <c r="J61" s="119"/>
+      <c r="K61" s="119"/>
+      <c r="L61" s="50"/>
+      <c r="M61" s="223"/>
+      <c r="N61" s="223"/>
+      <c r="O61" s="142"/>
+      <c r="P61" s="225"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="216"/>
+      <c r="B62" s="217"/>
+      <c r="C62" s="218" t="str">
+        <f aca="false">DEC2HEX(D62,2)</f>
         <v>0E</v>
       </c>
-      <c r="D63" s="173" t="n">
-        <f aca="false">IF(E63=1,128,0)+IF(F63=1,64,0)+IF(G63=1,32,0)+IF(H63=1,16,0)+IF(I63=1,8,0)+IF(J63=1,4,0)+IF(K63=1,2,0)+IF(L63=1,1,0)</f>
+      <c r="D62" s="173" t="n">
+        <f aca="false">IF(E62=1,128,0)+IF(F62=1,64,0)+IF(G62=1,32,0)+IF(H62=1,16,0)+IF(I62=1,8,0)+IF(J62=1,4,0)+IF(K62=1,2,0)+IF(L62=1,1,0)</f>
         <v>14</v>
       </c>
-      <c r="E63" s="188"/>
-      <c r="F63" s="173"/>
-      <c r="G63" s="173"/>
-      <c r="H63" s="177"/>
-      <c r="I63" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="217"/>
-      <c r="N63" s="217"/>
-      <c r="O63" s="219"/>
-      <c r="P63" s="221"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A64" s="222"/>
-      <c r="E64" s="146"/>
-      <c r="F64" s="119"/>
-      <c r="G64" s="119"/>
-      <c r="H64" s="50"/>
-      <c r="I64" s="119"/>
-      <c r="J64" s="119"/>
-      <c r="K64" s="119"/>
-      <c r="L64" s="50"/>
-      <c r="M64" s="223"/>
-      <c r="N64" s="223"/>
-      <c r="O64" s="142"/>
-      <c r="P64" s="225"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="216"/>
-      <c r="B65" s="217"/>
-      <c r="C65" s="218" t="str">
-        <f aca="false">DEC2HEX(D65,2)</f>
+      <c r="E62" s="188"/>
+      <c r="F62" s="173"/>
+      <c r="G62" s="173"/>
+      <c r="H62" s="177"/>
+      <c r="I62" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="217"/>
+      <c r="N62" s="217"/>
+      <c r="O62" s="219"/>
+      <c r="P62" s="221"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A63" s="222"/>
+      <c r="E63" s="146"/>
+      <c r="F63" s="119"/>
+      <c r="G63" s="119"/>
+      <c r="H63" s="50"/>
+      <c r="I63" s="119"/>
+      <c r="J63" s="119"/>
+      <c r="K63" s="119"/>
+      <c r="L63" s="50"/>
+      <c r="M63" s="223"/>
+      <c r="N63" s="223"/>
+      <c r="O63" s="142"/>
+      <c r="P63" s="225"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="216"/>
+      <c r="B64" s="217"/>
+      <c r="C64" s="218" t="str">
+        <f aca="false">DEC2HEX(D64,2)</f>
         <v>0F</v>
       </c>
-      <c r="D65" s="173" t="n">
-        <f aca="false">IF(E65=1,128,0)+IF(F65=1,64,0)+IF(G65=1,32,0)+IF(H65=1,16,0)+IF(I65=1,8,0)+IF(J65=1,4,0)+IF(K65=1,2,0)+IF(L65=1,1,0)</f>
+      <c r="D64" s="173" t="n">
+        <f aca="false">IF(E64=1,128,0)+IF(F64=1,64,0)+IF(G64=1,32,0)+IF(H64=1,16,0)+IF(I64=1,8,0)+IF(J64=1,4,0)+IF(K64=1,2,0)+IF(L64=1,1,0)</f>
         <v>15</v>
       </c>
-      <c r="E65" s="188"/>
-      <c r="F65" s="173"/>
-      <c r="G65" s="173"/>
-      <c r="H65" s="177"/>
-      <c r="I65" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="217"/>
-      <c r="N65" s="217"/>
-      <c r="O65" s="219"/>
-      <c r="P65" s="221"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="E64" s="188"/>
+      <c r="F64" s="173"/>
+      <c r="G64" s="173"/>
+      <c r="H64" s="177"/>
+      <c r="I64" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="217"/>
+      <c r="N64" s="217"/>
+      <c r="O64" s="219"/>
+      <c r="P64" s="221"/>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A65" s="222"/>
+      <c r="E65" s="146"/>
+      <c r="F65" s="119"/>
+      <c r="G65" s="119"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="119"/>
+      <c r="J65" s="119"/>
+      <c r="K65" s="119"/>
+      <c r="L65" s="50"/>
+      <c r="M65" s="223"/>
+      <c r="N65" s="223"/>
+      <c r="O65" s="142"/>
+      <c r="P65" s="225"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="222"/>
       <c r="E66" s="146"/>
       <c r="F66" s="119"/>
@@ -9954,122 +10034,149 @@
       <c r="O67" s="142"/>
       <c r="P67" s="225"/>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="222"/>
+    <row r="68" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="249" t="s">
+        <v>301</v>
+      </c>
       <c r="E68" s="146"/>
-      <c r="F68" s="119"/>
-      <c r="G68" s="119"/>
-      <c r="H68" s="50"/>
-      <c r="I68" s="119"/>
-      <c r="J68" s="119"/>
-      <c r="K68" s="119"/>
-      <c r="L68" s="50"/>
+      <c r="F68" s="200" t="s">
+        <v>302</v>
+      </c>
+      <c r="G68" s="200" t="s">
+        <v>303</v>
+      </c>
+      <c r="H68" s="200" t="s">
+        <v>303</v>
+      </c>
+      <c r="I68" s="200"/>
+      <c r="J68" s="200"/>
+      <c r="K68" s="200" t="s">
+        <v>304</v>
+      </c>
+      <c r="L68" s="200" t="s">
+        <v>305</v>
+      </c>
       <c r="M68" s="223"/>
       <c r="N68" s="223"/>
       <c r="O68" s="142"/>
       <c r="P68" s="225"/>
     </row>
-    <row r="69" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="246" t="s">
-        <v>298</v>
-      </c>
-      <c r="E69" s="146"/>
-      <c r="F69" s="200" t="s">
-        <v>299</v>
-      </c>
-      <c r="G69" s="200" t="s">
-        <v>300</v>
-      </c>
-      <c r="H69" s="200" t="s">
-        <v>300</v>
-      </c>
-      <c r="I69" s="200"/>
-      <c r="J69" s="200"/>
-      <c r="K69" s="200" t="s">
-        <v>301</v>
-      </c>
-      <c r="L69" s="200" t="s">
-        <v>302</v>
-      </c>
-      <c r="M69" s="223"/>
-      <c r="N69" s="223"/>
-      <c r="O69" s="142"/>
-      <c r="P69" s="225"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="216" t="s">
-        <v>216</v>
-      </c>
-      <c r="B70" s="219"/>
-      <c r="C70" s="218"/>
-      <c r="D70" s="173"/>
-      <c r="E70" s="188"/>
-      <c r="F70" s="173"/>
-      <c r="G70" s="173"/>
-      <c r="H70" s="177"/>
-      <c r="I70" s="188"/>
-      <c r="J70" s="173"/>
-      <c r="K70" s="173"/>
-      <c r="L70" s="177"/>
-      <c r="M70" s="217"/>
-      <c r="N70" s="217"/>
-      <c r="O70" s="219"/>
-      <c r="P70" s="221"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="247" t="s">
-        <v>303</v>
-      </c>
-      <c r="B71" s="191"/>
-      <c r="C71" s="212" t="str">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="216" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" s="219"/>
+      <c r="C69" s="218"/>
+      <c r="D69" s="173"/>
+      <c r="E69" s="188"/>
+      <c r="F69" s="173"/>
+      <c r="G69" s="173"/>
+      <c r="H69" s="177"/>
+      <c r="I69" s="188"/>
+      <c r="J69" s="173"/>
+      <c r="K69" s="173"/>
+      <c r="L69" s="177"/>
+      <c r="M69" s="217"/>
+      <c r="N69" s="217"/>
+      <c r="O69" s="219"/>
+      <c r="P69" s="221"/>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A70" s="250" t="s">
+        <v>306</v>
+      </c>
+      <c r="B70" s="191"/>
+      <c r="C70" s="212" t="str">
+        <f aca="false">DEC2HEX(D70,2)</f>
+        <v>00</v>
+      </c>
+      <c r="D70" s="193" t="n">
+        <f aca="false">IF(E70=1,128,0)+IF(F70=1,64,0)+IF(G70=1,32,0)+IF(H70=1,16,0)+IF(I70=1,8,0)+IF(J70=1,4,0)+IF(K70=1,2,0)+IF(L70=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="254"/>
+      <c r="N70" s="254"/>
+      <c r="O70" s="191"/>
+      <c r="P70" s="255"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A71" s="222" t="s">
+        <v>307</v>
+      </c>
+      <c r="B71" s="142"/>
+      <c r="C71" s="20" t="str">
         <f aca="false">DEC2HEX(D71,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D71" s="193" t="n">
+        <v>10</v>
+      </c>
+      <c r="D71" s="2" t="n">
         <f aca="false">IF(E71=1,128,0)+IF(F71=1,64,0)+IF(G71=1,32,0)+IF(H71=1,16,0)+IF(I71=1,8,0)+IF(J71=1,4,0)+IF(K71=1,2,0)+IF(L71=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="251"/>
-      <c r="N71" s="251"/>
-      <c r="O71" s="191"/>
-      <c r="P71" s="252"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>16</v>
+      </c>
+      <c r="E71" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="223"/>
+      <c r="N71" s="223"/>
+      <c r="O71" s="142"/>
+      <c r="P71" s="225"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A72" s="222" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B72" s="142"/>
       <c r="C72" s="20" t="str">
         <f aca="false">DEC2HEX(D72,2)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">IF(E72=1,128,0)+IF(F72=1,64,0)+IF(G72=1,32,0)+IF(H72=1,16,0)+IF(I72=1,8,0)+IF(J72=1,4,0)+IF(K72=1,2,0)+IF(L72=1,1,0)</f>
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E72" s="49" t="n">
         <v>0</v>
@@ -10078,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="G72" s="119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="49" t="n">
         <v>0</v>
@@ -10100,144 +10207,144 @@
       <c r="O72" s="142"/>
       <c r="P72" s="225"/>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="222" t="s">
-        <v>305</v>
-      </c>
-      <c r="B73" s="142"/>
-      <c r="C73" s="20" t="str">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A73" s="245" t="s">
+        <v>309</v>
+      </c>
+      <c r="B73" s="248"/>
+      <c r="C73" s="246" t="str">
         <f aca="false">DEC2HEX(D73,2)</f>
-        <v>20</v>
-      </c>
-      <c r="D73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D73" s="152" t="n">
         <f aca="false">IF(E73=1,128,0)+IF(F73=1,64,0)+IF(G73=1,32,0)+IF(H73=1,16,0)+IF(I73=1,8,0)+IF(J73=1,4,0)+IF(K73=1,2,0)+IF(L73=1,1,0)</f>
-        <v>32</v>
-      </c>
-      <c r="E73" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="223"/>
-      <c r="N73" s="223"/>
-      <c r="O73" s="142"/>
-      <c r="P73" s="225"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="242" t="s">
-        <v>306</v>
-      </c>
-      <c r="B74" s="245"/>
-      <c r="C74" s="243" t="str">
+        <v>48</v>
+      </c>
+      <c r="E73" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="256"/>
+      <c r="N73" s="256"/>
+      <c r="O73" s="248"/>
+      <c r="P73" s="257"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A74" s="250" t="s">
+        <v>310</v>
+      </c>
+      <c r="B74" s="191"/>
+      <c r="C74" s="212" t="str">
         <f aca="false">DEC2HEX(D74,2)</f>
-        <v>30</v>
-      </c>
-      <c r="D74" s="152" t="n">
+        <v>40</v>
+      </c>
+      <c r="D74" s="193" t="n">
         <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
-        <v>48</v>
-      </c>
-      <c r="E74" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="253"/>
-      <c r="N74" s="253"/>
-      <c r="O74" s="245"/>
-      <c r="P74" s="254"/>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="247" t="s">
-        <v>307</v>
-      </c>
-      <c r="B75" s="191"/>
-      <c r="C75" s="212" t="str">
+        <v>64</v>
+      </c>
+      <c r="E74" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="252" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="254"/>
+      <c r="N74" s="254"/>
+      <c r="O74" s="191"/>
+      <c r="P74" s="255"/>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A75" s="222" t="s">
+        <v>311</v>
+      </c>
+      <c r="B75" s="142"/>
+      <c r="C75" s="20" t="str">
         <f aca="false">DEC2HEX(D75,2)</f>
-        <v>40</v>
-      </c>
-      <c r="D75" s="193" t="n">
+        <v>50</v>
+      </c>
+      <c r="D75" s="2" t="n">
         <f aca="false">IF(E75=1,128,0)+IF(F75=1,64,0)+IF(G75=1,32,0)+IF(H75=1,16,0)+IF(I75=1,8,0)+IF(J75=1,4,0)+IF(K75=1,2,0)+IF(L75=1,1,0)</f>
-        <v>64</v>
-      </c>
-      <c r="E75" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="249" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="251"/>
-      <c r="N75" s="251"/>
-      <c r="O75" s="191"/>
-      <c r="P75" s="252"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>80</v>
+      </c>
+      <c r="E75" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="223"/>
+      <c r="N75" s="223"/>
+      <c r="O75" s="142"/>
+      <c r="P75" s="225"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A76" s="222" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B76" s="142"/>
       <c r="C76" s="20" t="str">
         <f aca="false">DEC2HEX(D76,2)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">IF(E76=1,128,0)+IF(F76=1,64,0)+IF(G76=1,32,0)+IF(H76=1,16,0)+IF(I76=1,8,0)+IF(J76=1,4,0)+IF(K76=1,2,0)+IF(L76=1,1,0)</f>
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E76" s="49" t="n">
         <v>0</v>
@@ -10246,10 +10353,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="49" t="n">
         <v>0</v>
@@ -10268,156 +10375,153 @@
       <c r="O76" s="142"/>
       <c r="P76" s="225"/>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="222" t="s">
-        <v>309</v>
-      </c>
-      <c r="B77" s="142"/>
-      <c r="C77" s="20" t="str">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A77" s="245" t="s">
+        <v>313</v>
+      </c>
+      <c r="B77" s="248"/>
+      <c r="C77" s="246" t="str">
         <f aca="false">DEC2HEX(D77,2)</f>
-        <v>60</v>
-      </c>
-      <c r="D77" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D77" s="152" t="n">
         <f aca="false">IF(E77=1,128,0)+IF(F77=1,64,0)+IF(G77=1,32,0)+IF(H77=1,16,0)+IF(I77=1,8,0)+IF(J77=1,4,0)+IF(K77=1,2,0)+IF(L77=1,1,0)</f>
-        <v>96</v>
-      </c>
-      <c r="E77" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="223"/>
-      <c r="N77" s="223"/>
-      <c r="O77" s="142"/>
-      <c r="P77" s="225"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="242" t="s">
-        <v>310</v>
-      </c>
-      <c r="B78" s="245"/>
-      <c r="C78" s="243" t="str">
+        <v>112</v>
+      </c>
+      <c r="E77" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="256"/>
+      <c r="N77" s="256"/>
+      <c r="O77" s="248"/>
+      <c r="P77" s="257"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A78" s="250" t="s">
+        <v>314</v>
+      </c>
+      <c r="B78" s="258"/>
+      <c r="C78" s="212" t="str">
         <f aca="false">DEC2HEX(D78,2)</f>
-        <v>70</v>
-      </c>
-      <c r="D78" s="152" t="n">
+        <v>01</v>
+      </c>
+      <c r="D78" s="193" t="n">
         <f aca="false">IF(E78=1,128,0)+IF(F78=1,64,0)+IF(G78=1,32,0)+IF(H78=1,16,0)+IF(I78=1,8,0)+IF(J78=1,4,0)+IF(K78=1,2,0)+IF(L78=1,1,0)</f>
-        <v>112</v>
-      </c>
-      <c r="E78" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="253"/>
-      <c r="N78" s="253"/>
-      <c r="O78" s="245"/>
-      <c r="P78" s="254"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="247" t="s">
-        <v>311</v>
-      </c>
-      <c r="B79" s="255"/>
-      <c r="C79" s="212" t="str">
+        <v>1</v>
+      </c>
+      <c r="E78" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="254"/>
+      <c r="N78" s="254"/>
+      <c r="O78" s="191"/>
+      <c r="P78" s="255"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A79" s="222" t="s">
+        <v>315</v>
+      </c>
+      <c r="B79" s="142"/>
+      <c r="C79" s="20" t="str">
         <f aca="false">DEC2HEX(D79,2)</f>
-        <v>01</v>
-      </c>
-      <c r="D79" s="193" t="n">
+        <v>11</v>
+      </c>
+      <c r="D79" s="2" t="n">
         <f aca="false">IF(E79=1,128,0)+IF(F79=1,64,0)+IF(G79=1,32,0)+IF(H79=1,16,0)+IF(I79=1,8,0)+IF(J79=1,4,0)+IF(K79=1,2,0)+IF(L79=1,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E79" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="193" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="250" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="251"/>
-      <c r="N79" s="251"/>
-      <c r="O79" s="191"/>
-      <c r="P79" s="252"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="E79" s="146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="225"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A80" s="222" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B80" s="142"/>
       <c r="C80" s="20" t="str">
         <f aca="false">DEC2HEX(D80,2)</f>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">IF(E80=1,128,0)+IF(F80=1,64,0)+IF(G80=1,32,0)+IF(H80=1,16,0)+IF(I80=1,8,0)+IF(J80=1,4,0)+IF(K80=1,2,0)+IF(L80=1,1,0)</f>
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E80" s="146" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>0</v>
+      <c r="F80" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="119" t="n">
+        <v>1</v>
       </c>
       <c r="H80" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="49" t="n">
         <v>0</v>
@@ -10431,150 +10535,155 @@
       <c r="L80" s="50" t="n">
         <v>1</v>
       </c>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="142"/>
       <c r="P80" s="225"/>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="222" t="s">
-        <v>313</v>
-      </c>
-      <c r="B81" s="142"/>
-      <c r="C81" s="20" t="str">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A81" s="245" t="s">
+        <v>317</v>
+      </c>
+      <c r="B81" s="248"/>
+      <c r="C81" s="246" t="str">
         <f aca="false">DEC2HEX(D81,2)</f>
-        <v>21</v>
-      </c>
-      <c r="D81" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D81" s="152" t="n">
         <f aca="false">IF(E81=1,128,0)+IF(F81=1,64,0)+IF(G81=1,32,0)+IF(H81=1,16,0)+IF(I81=1,8,0)+IF(J81=1,4,0)+IF(K81=1,2,0)+IF(L81=1,1,0)</f>
-        <v>33</v>
-      </c>
-      <c r="E81" s="146" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" s="10"/>
-      <c r="N81" s="10"/>
-      <c r="O81" s="142"/>
-      <c r="P81" s="225"/>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="242" t="s">
-        <v>314</v>
-      </c>
-      <c r="B82" s="245"/>
-      <c r="C82" s="243" t="str">
+        <v>49</v>
+      </c>
+      <c r="E81" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="256"/>
+      <c r="N81" s="256"/>
+      <c r="O81" s="248"/>
+      <c r="P81" s="257"/>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A82" s="250" t="s">
+        <v>318</v>
+      </c>
+      <c r="B82" s="191"/>
+      <c r="C82" s="212" t="str">
         <f aca="false">DEC2HEX(D82,2)</f>
-        <v>31</v>
-      </c>
-      <c r="D82" s="152" t="n">
+        <v>04</v>
+      </c>
+      <c r="D82" s="193" t="n">
         <f aca="false">IF(E82=1,128,0)+IF(F82=1,64,0)+IF(G82=1,32,0)+IF(H82=1,16,0)+IF(I82=1,8,0)+IF(J82=1,4,0)+IF(K82=1,2,0)+IF(L82=1,1,0)</f>
-        <v>49</v>
-      </c>
-      <c r="E82" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" s="253"/>
-      <c r="N82" s="253"/>
-      <c r="O82" s="245"/>
-      <c r="P82" s="254"/>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="247" t="s">
-        <v>315</v>
-      </c>
-      <c r="B83" s="191"/>
-      <c r="C83" s="212" t="str">
+        <v>4</v>
+      </c>
+      <c r="E82" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="254"/>
+      <c r="N82" s="254"/>
+      <c r="O82" s="191"/>
+      <c r="P82" s="255" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A83" s="222" t="s">
+        <v>320</v>
+      </c>
+      <c r="B83" s="142"/>
+      <c r="C83" s="20" t="str">
         <f aca="false">DEC2HEX(D83,2)</f>
-        <v>04</v>
-      </c>
-      <c r="D83" s="193" t="n">
+        <v>44</v>
+      </c>
+      <c r="D83" s="2" t="n">
         <f aca="false">IF(E83=1,128,0)+IF(F83=1,64,0)+IF(G83=1,32,0)+IF(H83=1,16,0)+IF(I83=1,8,0)+IF(J83=1,4,0)+IF(K83=1,2,0)+IF(L83=1,1,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E83" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="249" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="251"/>
-      <c r="N83" s="251"/>
-      <c r="O83" s="191"/>
-      <c r="P83" s="252" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>68</v>
+      </c>
+      <c r="E83" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="223"/>
+      <c r="N83" s="223"/>
+      <c r="O83" s="142"/>
+      <c r="P83" s="225" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A84" s="222" t="s">
-        <v>317</v>
-      </c>
-      <c r="B84" s="142"/>
-      <c r="C84" s="20" t="str">
+        <v>322</v>
+      </c>
+      <c r="B84" s="259"/>
+      <c r="C84" s="17" t="str">
         <f aca="false">DEC2HEX(D84,2)</f>
-        <v>44</v>
-      </c>
-      <c r="D84" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="D84" s="119" t="n">
         <f aca="false">IF(E84=1,128,0)+IF(F84=1,64,0)+IF(G84=1,32,0)+IF(H84=1,16,0)+IF(I84=1,8,0)+IF(J84=1,4,0)+IF(K84=1,2,0)+IF(L84=1,1,0)</f>
-        <v>68</v>
-      </c>
-      <c r="E84" s="49" t="n">
+        <v>84</v>
+      </c>
+      <c r="E84" s="146" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="119" t="n">
@@ -10583,10 +10692,10 @@
       <c r="G84" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="49" t="n">
+      <c r="H84" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="146" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="119" t="n">
@@ -10595,40 +10704,40 @@
       <c r="K84" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="L84" s="50" t="n">
+      <c r="L84" s="141" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="223"/>
       <c r="N84" s="223"/>
-      <c r="O84" s="142"/>
+      <c r="O84" s="259"/>
       <c r="P84" s="225" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A85" s="222" t="s">
-        <v>319</v>
-      </c>
-      <c r="B85" s="256"/>
+        <v>324</v>
+      </c>
+      <c r="B85" s="259"/>
       <c r="C85" s="17" t="str">
         <f aca="false">DEC2HEX(D85,2)</f>
-        <v>54</v>
-      </c>
-      <c r="D85" s="119" t="n">
+        <v>84</v>
+      </c>
+      <c r="D85" s="13" t="n">
         <f aca="false">IF(E85=1,128,0)+IF(F85=1,64,0)+IF(G85=1,32,0)+IF(H85=1,16,0)+IF(I85=1,8,0)+IF(J85=1,4,0)+IF(K85=1,2,0)+IF(L85=1,1,0)</f>
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="E85" s="146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="119" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" s="146" t="n">
         <v>0</v>
@@ -10644,312 +10753,269 @@
       </c>
       <c r="M85" s="223"/>
       <c r="N85" s="223"/>
-      <c r="O85" s="256"/>
-      <c r="P85" s="225" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A86" s="222" t="s">
-        <v>321</v>
-      </c>
-      <c r="B86" s="256"/>
-      <c r="C86" s="17" t="str">
+      <c r="O85" s="259"/>
+      <c r="P85" s="225"/>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A86" s="250" t="s">
+        <v>325</v>
+      </c>
+      <c r="B86" s="191"/>
+      <c r="C86" s="212" t="str">
         <f aca="false">DEC2HEX(D86,2)</f>
-        <v>84</v>
-      </c>
-      <c r="D86" s="13" t="n">
+        <v>05</v>
+      </c>
+      <c r="D86" s="193" t="n">
         <f aca="false">IF(E86=1,128,0)+IF(F86=1,64,0)+IF(G86=1,32,0)+IF(H86=1,16,0)+IF(I86=1,8,0)+IF(J86=1,4,0)+IF(K86=1,2,0)+IF(L86=1,1,0)</f>
-        <v>132</v>
-      </c>
-      <c r="E86" s="146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="223"/>
-      <c r="N86" s="223"/>
-      <c r="O86" s="256"/>
-      <c r="P86" s="225"/>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A87" s="247" t="s">
-        <v>322</v>
-      </c>
-      <c r="B87" s="191"/>
-      <c r="C87" s="212" t="str">
+        <v>5</v>
+      </c>
+      <c r="E86" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="254"/>
+      <c r="N86" s="254"/>
+      <c r="O86" s="191"/>
+      <c r="P86" s="255" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A87" s="245" t="s">
+        <v>327</v>
+      </c>
+      <c r="B87" s="248"/>
+      <c r="C87" s="246" t="str">
         <f aca="false">DEC2HEX(D87,2)</f>
-        <v>05</v>
-      </c>
-      <c r="D87" s="193" t="n">
+        <v>45</v>
+      </c>
+      <c r="D87" s="152" t="n">
         <f aca="false">IF(E87=1,128,0)+IF(F87=1,64,0)+IF(G87=1,32,0)+IF(H87=1,16,0)+IF(I87=1,8,0)+IF(J87=1,4,0)+IF(K87=1,2,0)+IF(L87=1,1,0)</f>
-        <v>5</v>
-      </c>
-      <c r="E87" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="248" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="249" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="249" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="250" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="251"/>
-      <c r="N87" s="251"/>
-      <c r="O87" s="191"/>
-      <c r="P87" s="252" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A88" s="242" t="s">
-        <v>324</v>
-      </c>
-      <c r="B88" s="245"/>
-      <c r="C88" s="243" t="str">
+        <v>69</v>
+      </c>
+      <c r="E87" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="256"/>
+      <c r="N87" s="256"/>
+      <c r="O87" s="248"/>
+      <c r="P87" s="257" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A88" s="222" t="s">
+        <v>329</v>
+      </c>
+      <c r="B88" s="142"/>
+      <c r="C88" s="17" t="str">
         <f aca="false">DEC2HEX(D88,2)</f>
-        <v>45</v>
-      </c>
-      <c r="D88" s="152" t="n">
+        <v>37</v>
+      </c>
+      <c r="D88" s="119" t="n">
         <f aca="false">IF(E88=1,128,0)+IF(F88=1,64,0)+IF(G88=1,32,0)+IF(H88=1,16,0)+IF(I88=1,8,0)+IF(J88=1,4,0)+IF(K88=1,2,0)+IF(L88=1,1,0)</f>
-        <v>69</v>
-      </c>
-      <c r="E88" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" s="253"/>
-      <c r="N88" s="253"/>
-      <c r="O88" s="245"/>
-      <c r="P88" s="254" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A89" s="222" t="s">
-        <v>326</v>
-      </c>
-      <c r="B89" s="142"/>
-      <c r="C89" s="17" t="str">
+        <v>55</v>
+      </c>
+      <c r="E88" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="223"/>
+      <c r="N88" s="223"/>
+      <c r="O88" s="142"/>
+      <c r="P88" s="225"/>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A89" s="245" t="s">
+        <v>330</v>
+      </c>
+      <c r="B89" s="248"/>
+      <c r="C89" s="246" t="str">
         <f aca="false">DEC2HEX(D89,2)</f>
         <v>37</v>
       </c>
-      <c r="D89" s="119" t="n">
+      <c r="D89" s="152" t="n">
         <f aca="false">IF(E89=1,128,0)+IF(F89=1,64,0)+IF(G89=1,32,0)+IF(H89=1,16,0)+IF(I89=1,8,0)+IF(J89=1,4,0)+IF(K89=1,2,0)+IF(L89=1,1,0)</f>
         <v>55</v>
       </c>
-      <c r="E89" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" s="119" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M89" s="223"/>
-      <c r="N89" s="223"/>
-      <c r="O89" s="142"/>
-      <c r="P89" s="225"/>
-    </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A90" s="242" t="s">
-        <v>327</v>
-      </c>
-      <c r="B90" s="245"/>
-      <c r="C90" s="243" t="str">
+      <c r="E89" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="256"/>
+      <c r="N89" s="256"/>
+      <c r="O89" s="248"/>
+      <c r="P89" s="257"/>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A90" s="222"/>
+      <c r="B90" s="142"/>
+      <c r="C90" s="17" t="str">
         <f aca="false">DEC2HEX(D90,2)</f>
-        <v>37</v>
-      </c>
-      <c r="D90" s="152" t="n">
+        <v>00</v>
+      </c>
+      <c r="D90" s="119" t="n">
         <f aca="false">IF(E90=1,128,0)+IF(F90=1,64,0)+IF(G90=1,32,0)+IF(H90=1,16,0)+IF(I90=1,8,0)+IF(J90=1,4,0)+IF(K90=1,2,0)+IF(L90=1,1,0)</f>
-        <v>55</v>
-      </c>
-      <c r="E90" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" s="244" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" s="152" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" s="253"/>
-      <c r="N90" s="253"/>
-      <c r="O90" s="245"/>
-      <c r="P90" s="254"/>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A91" s="222"/>
-      <c r="B91" s="142"/>
-      <c r="C91" s="17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E90" s="49"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="119"/>
+      <c r="H90" s="50"/>
+      <c r="I90" s="49"/>
+      <c r="J90" s="119"/>
+      <c r="K90" s="119"/>
+      <c r="L90" s="50"/>
+      <c r="M90" s="223"/>
+      <c r="N90" s="223"/>
+      <c r="O90" s="142"/>
+      <c r="P90" s="225"/>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A91" s="245"/>
+      <c r="B91" s="248"/>
+      <c r="C91" s="246" t="str">
         <f aca="false">DEC2HEX(D91,2)</f>
         <v>00</v>
       </c>
-      <c r="D91" s="119" t="n">
+      <c r="D91" s="152" t="n">
         <f aca="false">IF(E91=1,128,0)+IF(F91=1,64,0)+IF(G91=1,32,0)+IF(H91=1,16,0)+IF(I91=1,8,0)+IF(J91=1,4,0)+IF(K91=1,2,0)+IF(L91=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E91" s="49"/>
-      <c r="F91" s="119"/>
-      <c r="G91" s="119"/>
-      <c r="H91" s="50"/>
-      <c r="I91" s="49"/>
-      <c r="J91" s="119"/>
-      <c r="K91" s="119"/>
-      <c r="L91" s="50"/>
-      <c r="M91" s="223"/>
-      <c r="N91" s="223"/>
-      <c r="O91" s="142"/>
-      <c r="P91" s="225"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A92" s="242"/>
-      <c r="B92" s="245"/>
-      <c r="C92" s="243" t="str">
-        <f aca="false">DEC2HEX(D92,2)</f>
-        <v>00</v>
-      </c>
-      <c r="D92" s="152" t="n">
-        <f aca="false">IF(E92=1,128,0)+IF(F92=1,64,0)+IF(G92=1,32,0)+IF(H92=1,16,0)+IF(I92=1,8,0)+IF(J92=1,4,0)+IF(K92=1,2,0)+IF(L92=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E92" s="244"/>
-      <c r="F92" s="152"/>
-      <c r="G92" s="152"/>
-      <c r="H92" s="155"/>
-      <c r="I92" s="244"/>
-      <c r="J92" s="152"/>
-      <c r="K92" s="152"/>
-      <c r="L92" s="155"/>
-      <c r="M92" s="253"/>
-      <c r="N92" s="253"/>
-      <c r="O92" s="245"/>
-      <c r="P92" s="254"/>
+      <c r="E91" s="247"/>
+      <c r="F91" s="152"/>
+      <c r="G91" s="152"/>
+      <c r="H91" s="155"/>
+      <c r="I91" s="247"/>
+      <c r="J91" s="152"/>
+      <c r="K91" s="152"/>
+      <c r="L91" s="155"/>
+      <c r="M91" s="256"/>
+      <c r="N91" s="256"/>
+      <c r="O91" s="248"/>
+      <c r="P91" s="257"/>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="142"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="142"/>
+      <c r="A93" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="260"/>
+      <c r="P93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="3"/>
-      <c r="O94" s="257"/>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="s">
-        <v>329</v>
-      </c>
-    </row>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="P12" r:id="rId1" location="Basic_and_interchange_formats" display="https://en.wikipedia.org/wiki/IEEE_754#Basic_and_interchange_formats"/>
-    <hyperlink ref="P40" r:id="rId2" location="Durations" display="https://en.wikipedia.org/wiki/ISO_8601#Durations"/>
-    <hyperlink ref="P41" r:id="rId3" location="time" display="http://www.w3.org/TR/xmlschema-2/#time"/>
-    <hyperlink ref="P42" r:id="rId4" location="date" display="http://www.w3.org/TR/xmlschema-2/#date"/>
-    <hyperlink ref="P43" r:id="rId5" location="dateTime" display="http://www.w3.org/TR/xmlschema-2/#dateTime"/>
-    <hyperlink ref="P56" r:id="rId6" display="https://learn.microsoft.com/en-us/office/vba/language/reference/user-interface-help/currency-data-type"/>
+    <hyperlink ref="P39" r:id="rId2" location="Durations" display="https://en.wikipedia.org/wiki/ISO_8601#Durations"/>
+    <hyperlink ref="P40" r:id="rId3" location="time" display="http://www.w3.org/TR/xmlschema-2/#time"/>
+    <hyperlink ref="P41" r:id="rId4" location="date" display="http://www.w3.org/TR/xmlschema-2/#date"/>
+    <hyperlink ref="P42" r:id="rId5" location="dateTime" display="http://www.w3.org/TR/xmlschema-2/#dateTime"/>
+    <hyperlink ref="P55" r:id="rId6" display="https://learn.microsoft.com/en-us/office/vba/language/reference/user-interface-help/currency-data-type"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10975,30 +11041,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="258" t="s">
-        <v>331</v>
-      </c>
-      <c r="H1" s="258"/>
-      <c r="I1" s="258"/>
-      <c r="J1" s="258" t="s">
-        <v>332</v>
+        <v>122</v>
+      </c>
+      <c r="G1" s="261" t="s">
+        <v>334</v>
+      </c>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11012,26 +11078,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11045,26 +11111,26 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11081,25 +11147,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11116,25 +11182,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11148,28 +11214,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="K6" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11183,28 +11249,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="K7" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11218,26 +11284,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11251,26 +11317,26 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11284,28 +11350,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11319,28 +11385,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11354,28 +11420,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11389,28 +11455,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/Protocol/Morph Protocol.xlsx
+++ b/Protocol/Morph Protocol.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Connection" sheetId="1" state="visible" r:id="rId3"/>
@@ -63,9 +63,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>14</xdr:col>
-                <xdr:colOff>11</xdr:colOff>
+                <xdr:colOff>5</xdr:colOff>
                 <xdr:row>33</xdr:row>
-                <xdr:rowOff>7</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -96,7 +96,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>21</xdr:colOff>
+                <xdr:colOff>9</xdr:colOff>
                 <xdr:row>28</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -123,15 +123,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>12</xdr:col>
-                <xdr:colOff>45</xdr:colOff>
+                <xdr:colOff>20</xdr:colOff>
                 <xdr:row>33</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>13</xdr:col>
-                <xdr:colOff>71</xdr:colOff>
+                <xdr:colOff>31</xdr:colOff>
                 <xdr:row>34</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -162,9 +162,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>15</xdr:col>
-                <xdr:colOff>21</xdr:colOff>
+                <xdr:colOff>9</xdr:colOff>
                 <xdr:row>29</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="358">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -1350,6 +1350,12 @@
     <t xml:space="preserve">ValueName</t>
   </si>
   <si>
+    <t xml:space="preserve">IsTypeDefinition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not not be used. If set, then this is only the type information, no value data.</t>
+  </si>
+  <si>
     <t xml:space="preserve">IsValue/IsReference</t>
   </si>
   <si>
@@ -1926,6 +1932,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Strings are </t>
     </r>
@@ -1936,6 +1943,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">always</t>
     </r>
@@ -1945,6 +1953,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> encoded in </t>
     </r>
@@ -1955,6 +1964,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">UTF-8</t>
     </r>
@@ -1964,6 +1974,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -2373,7 +2384,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2512,6 +2523,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2529,19 +2546,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -3026,11 +3030,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="260">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3835,6 +3839,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="74" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3939,7 +3947,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3988,18 +3996,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4441,7 +4437,7 @@
       <c r="A28" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -4452,7 +4448,7 @@
       <c r="A29" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -7217,16 +7213,12 @@
       <c r="L4" s="142" t="s">
         <v>166</v>
       </c>
-      <c r="M4" s="142" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="141"/>
+      <c r="O4" s="141"/>
+      <c r="P4" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="N4" s="141" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" s="141" t="s">
-        <v>168</v>
-      </c>
-      <c r="P4" s="143"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="149"/>
@@ -7235,14 +7227,24 @@
       <c r="E5" s="152"/>
       <c r="F5" s="152"/>
       <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
+      <c r="H5" s="154" t="s">
+        <v>55</v>
+      </c>
       <c r="I5" s="152"/>
       <c r="J5" s="152"/>
       <c r="K5" s="155"/>
-      <c r="L5" s="156"/>
-      <c r="M5" s="156"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
+      <c r="L5" s="156" t="s">
+        <v>168</v>
+      </c>
+      <c r="M5" s="156" t="s">
+        <v>169</v>
+      </c>
+      <c r="N5" s="155" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" s="155" t="s">
+        <v>170</v>
+      </c>
       <c r="P5" s="157"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7250,7 +7252,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="159" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C6" s="160"/>
       <c r="D6" s="161"/>
@@ -7286,7 +7288,7 @@
       <c r="J7" s="119"/>
       <c r="K7" s="141"/>
       <c r="L7" s="142" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M7" s="142"/>
       <c r="N7" s="141"/>
@@ -7309,7 +7311,7 @@
       <c r="J8" s="119"/>
       <c r="K8" s="141"/>
       <c r="L8" s="142" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M8" s="142"/>
       <c r="N8" s="141"/>
@@ -7332,7 +7334,7 @@
       <c r="J9" s="119"/>
       <c r="K9" s="141"/>
       <c r="L9" s="142" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M9" s="142"/>
       <c r="N9" s="141"/>
@@ -7355,7 +7357,7 @@
       <c r="J10" s="119"/>
       <c r="K10" s="141"/>
       <c r="L10" s="142" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M10" s="142"/>
       <c r="N10" s="141"/>
@@ -7364,10 +7366,10 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="158" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" s="170" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C11" s="171"/>
       <c r="D11" s="172"/>
@@ -7400,16 +7402,16 @@
       <c r="K12" s="141"/>
       <c r="L12" s="142"/>
       <c r="M12" s="142" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N12" s="141" t="n">
         <v>1</v>
       </c>
       <c r="O12" s="141" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P12" s="143" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -7431,10 +7433,10 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="158" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C14" s="171"/>
       <c r="D14" s="172"/>
@@ -7468,24 +7470,24 @@
       <c r="J15" s="13"/>
       <c r="K15" s="141"/>
       <c r="L15" s="142" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M15" s="142" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N15" s="141" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O15" s="141" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P15" s="180" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B16" s="144" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C16" s="136"/>
       <c r="D16" s="137"/>
@@ -7501,7 +7503,7 @@
       <c r="N16" s="141"/>
       <c r="O16" s="141"/>
       <c r="P16" s="180" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -7517,21 +7519,21 @@
       <c r="K17" s="141"/>
       <c r="L17" s="142"/>
       <c r="M17" s="142" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N17" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O17" s="141" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P17" s="180" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B18" s="135" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C18" s="136"/>
       <c r="D18" s="137"/>
@@ -7544,21 +7546,21 @@
       <c r="K18" s="141"/>
       <c r="L18" s="142"/>
       <c r="M18" s="142" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N18" s="141" t="s">
         <v>162</v>
       </c>
       <c r="O18" s="141" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P18" s="180" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B19" s="144" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C19" s="145"/>
       <c r="D19" s="137"/>
@@ -7571,21 +7573,21 @@
       <c r="K19" s="141"/>
       <c r="L19" s="142"/>
       <c r="M19" s="142" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N19" s="141" t="s">
         <v>162</v>
       </c>
       <c r="O19" s="141" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P19" s="180" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B20" s="149" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C20" s="150"/>
       <c r="D20" s="181"/>
@@ -7601,15 +7603,15 @@
       <c r="N20" s="155"/>
       <c r="O20" s="155"/>
       <c r="P20" s="185" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="158" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B21" s="170" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C21" s="171"/>
       <c r="D21" s="172"/>
@@ -7642,16 +7644,16 @@
       <c r="K22" s="141"/>
       <c r="L22" s="142"/>
       <c r="M22" s="142" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N22" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O22" s="141" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P22" s="180" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
@@ -7667,24 +7669,24 @@
       <c r="K23" s="141"/>
       <c r="L23" s="142"/>
       <c r="M23" s="142" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N23" s="141" t="s">
         <v>162</v>
       </c>
       <c r="O23" s="141" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P23" s="180" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="158" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B24" s="170" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C24" s="171"/>
       <c r="D24" s="172"/>
@@ -7718,7 +7720,7 @@
       <c r="J25" s="119"/>
       <c r="K25" s="141"/>
       <c r="L25" s="142" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M25" s="142"/>
       <c r="N25" s="141"/>
@@ -7727,7 +7729,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B26" s="135" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C26" s="136"/>
       <c r="D26" s="137"/>
@@ -7740,24 +7742,24 @@
       <c r="K26" s="141"/>
       <c r="L26" s="142"/>
       <c r="M26" s="142" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N26" s="141" t="s">
         <v>162</v>
       </c>
       <c r="O26" s="141" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P26" s="187" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="158" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B27" s="170" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C27" s="171"/>
       <c r="D27" s="188"/>
@@ -7791,7 +7793,7 @@
       <c r="J28" s="119"/>
       <c r="K28" s="141"/>
       <c r="L28" s="142" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M28" s="142"/>
       <c r="N28" s="141"/>
@@ -7800,7 +7802,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B29" s="135" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C29" s="136"/>
       <c r="D29" s="137"/>
@@ -7814,13 +7816,13 @@
       <c r="J29" s="13"/>
       <c r="K29" s="141"/>
       <c r="L29" s="142" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M29" s="142"/>
       <c r="N29" s="141"/>
       <c r="O29" s="141"/>
       <c r="P29" s="143" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7828,7 +7830,7 @@
         <v>128</v>
       </c>
       <c r="B30" s="170" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C30" s="171"/>
       <c r="D30" s="172"/>
@@ -7870,7 +7872,7 @@
         <v>85</v>
       </c>
       <c r="B32" s="170" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C32" s="171"/>
       <c r="D32" s="172"/>
@@ -7909,7 +7911,7 @@
         <v>4</v>
       </c>
       <c r="O33" s="141" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P33" s="143"/>
     </row>
@@ -7927,24 +7929,24 @@
       <c r="J34" s="13"/>
       <c r="K34" s="141"/>
       <c r="L34" s="142" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M34" s="142" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N34" s="141" t="n">
         <v>4</v>
       </c>
       <c r="O34" s="141" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P34" s="143" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="B35" s="135" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C35" s="136"/>
       <c r="D35" s="137"/>
@@ -7957,13 +7959,13 @@
       <c r="K35" s="141"/>
       <c r="L35" s="142"/>
       <c r="M35" s="142" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N35" s="141" t="s">
         <v>162</v>
       </c>
       <c r="O35" s="141" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P35" s="143"/>
     </row>
@@ -7981,7 +7983,7 @@
       <c r="J36" s="152"/>
       <c r="K36" s="155"/>
       <c r="L36" s="156" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M36" s="156" t="s">
         <v>122</v>
@@ -7990,7 +7992,7 @@
         <v>162</v>
       </c>
       <c r="O36" s="155" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P36" s="157"/>
     </row>
@@ -8054,35 +8056,37 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="71.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="76.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="197" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="198" t="s">
         <v>47</v>
       </c>
       <c r="D43" s="199" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E43" s="200" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F43" s="200" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G43" s="200" t="s">
-        <v>220</v>
-      </c>
-      <c r="H43" s="199"/>
-      <c r="I43" s="200" t="s">
-        <v>203</v>
+        <v>222</v>
+      </c>
+      <c r="H43" s="200" t="s">
+        <v>205</v>
+      </c>
+      <c r="I43" s="201" t="s">
+        <v>166</v>
       </c>
       <c r="J43" s="200" t="s">
         <v>164</v>
@@ -8091,13 +8095,13 @@
         <v>160</v>
       </c>
       <c r="L43" s="198" t="s">
-        <v>221</v>
-      </c>
-      <c r="M43" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
+      </c>
+      <c r="M43" s="202" t="s">
+        <v>224</v>
       </c>
       <c r="N43" s="197" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O43" s="198"/>
       <c r="P43" s="197"/>
@@ -8106,26 +8110,26 @@
       <c r="S43" s="197"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="202"/>
+      <c r="A44" s="203"/>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="str">
         <f aca="false">DEC2HEX(L44,2)</f>
         <v>80</v>
       </c>
-      <c r="D44" s="203" t="n">
+      <c r="D44" s="204" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="193"/>
       <c r="F44" s="193"/>
-      <c r="G44" s="204"/>
-      <c r="H44" s="205"/>
-      <c r="I44" s="193" t="s">
+      <c r="G44" s="205"/>
+      <c r="H44" s="206" t="s">
         <v>72</v>
       </c>
+      <c r="I44" s="193"/>
       <c r="J44" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="K44" s="206" t="s">
+      <c r="K44" s="207" t="s">
         <v>72</v>
       </c>
       <c r="L44" s="12" t="n">
@@ -8133,10 +8137,10 @@
         <v>128</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
@@ -8144,11 +8148,11 @@
       <c r="S44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="202"/>
+      <c r="A45" s="203"/>
       <c r="B45" s="1"/>
       <c r="C45" s="2" t="str">
         <f aca="false">DEC2HEX(L45,2)</f>
-        <v>04</v>
+        <v>08</v>
       </c>
       <c r="D45" s="137" t="n">
         <v>0</v>
@@ -8158,10 +8162,10 @@
       <c r="G45" s="186" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="148"/>
-      <c r="I45" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="H45" s="148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="13"/>
       <c r="J45" s="13" t="s">
         <v>72</v>
       </c>
@@ -8170,13 +8174,13 @@
       </c>
       <c r="L45" s="12" t="n">
         <f aca="false">IF(D45=1,128,0)+IF(E45=1,64,0)+IF(F45=1,32,0)+IF(G45=1,16,0)+IF(H45=1,8,0)+IF(I45=1,4,0)+IF(J45=1,2,0)+IF(K45=1,1,0)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
@@ -8184,11 +8188,11 @@
       <c r="S45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="202"/>
+      <c r="A46" s="203"/>
       <c r="B46" s="1"/>
       <c r="C46" s="2" t="str">
         <f aca="false">DEC2HEX(L46,2)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D46" s="137" t="n">
         <v>0</v>
@@ -8202,10 +8206,10 @@
       <c r="G46" s="186" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="148"/>
-      <c r="I46" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="H46" s="148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="13"/>
       <c r="J46" s="13" t="s">
         <v>72</v>
       </c>
@@ -8214,13 +8218,13 @@
       </c>
       <c r="L46" s="12" t="n">
         <f aca="false">IF(D46=1,128,0)+IF(E46=1,64,0)+IF(F46=1,32,0)+IF(G46=1,16,0)+IF(H46=1,8,0)+IF(I46=1,4,0)+IF(J46=1,2,0)+IF(K46=1,1,0)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
@@ -8228,7 +8232,7 @@
       <c r="S46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="202"/>
+      <c r="A47" s="203"/>
       <c r="B47" s="1"/>
       <c r="C47" s="2" t="str">
         <f aca="false">DEC2HEX(L47,2)</f>
@@ -8242,10 +8246,10 @@
       <c r="G47" s="186" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="148"/>
-      <c r="I47" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="H47" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13"/>
       <c r="J47" s="13" t="s">
         <v>72</v>
       </c>
@@ -8257,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
@@ -8268,7 +8272,7 @@
       <c r="S47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="202"/>
+      <c r="A48" s="203"/>
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="str">
         <f aca="false">DEC2HEX(L48,2)</f>
@@ -8284,10 +8288,10 @@
       <c r="G48" s="186" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="148"/>
-      <c r="I48" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="H48" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13"/>
       <c r="J48" s="13" t="s">
         <v>72</v>
       </c>
@@ -8299,10 +8303,10 @@
         <v>16</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="11"/>
@@ -8311,7 +8315,7 @@
       <c r="S48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="202"/>
+      <c r="A49" s="203"/>
       <c r="B49" s="1"/>
       <c r="C49" s="2" t="str">
         <f aca="false">DEC2HEX(L49,2)</f>
@@ -8325,10 +8329,10 @@
       <c r="G49" s="186" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="148"/>
-      <c r="I49" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="H49" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="13"/>
       <c r="J49" s="13" t="s">
         <v>72</v>
       </c>
@@ -8340,10 +8344,10 @@
         <v>32</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P49" s="11"/>
       <c r="Q49" s="11"/>
@@ -8351,7 +8355,7 @@
       <c r="S49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="202"/>
+      <c r="A50" s="203"/>
       <c r="B50" s="1"/>
       <c r="C50" s="2" t="str">
         <f aca="false">DEC2HEX(L50,2)</f>
@@ -8360,23 +8364,23 @@
       <c r="D50" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="207" t="s">
+      <c r="E50" s="208" t="s">
         <v>72</v>
       </c>
-      <c r="F50" s="207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="208" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="154"/>
-      <c r="I50" s="207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="207" t="s">
+      <c r="F50" s="208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="209" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="208"/>
+      <c r="J50" s="208" t="s">
         <v>72</v>
       </c>
-      <c r="K50" s="209" t="n">
+      <c r="K50" s="210" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="12" t="n">
@@ -8384,10 +8388,10 @@
         <v>49</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P50" s="11"/>
       <c r="Q50" s="11"/>
@@ -8435,8 +8439,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="210"/>
-      <c r="B1" s="211" t="s">
+      <c r="A1" s="211"/>
+      <c r="B1" s="212" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="17" t="s">
@@ -8448,10 +8452,10 @@
       <c r="E1" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="F1" s="212" t="n">
+      <c r="F1" s="213" t="n">
         <v>6</v>
       </c>
-      <c r="G1" s="212" t="n">
+      <c r="G1" s="213" t="n">
         <v>5</v>
       </c>
       <c r="H1" s="27" t="n">
@@ -8460,34 +8464,34 @@
       <c r="I1" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J1" s="212" t="n">
+      <c r="J1" s="213" t="n">
         <v>2</v>
       </c>
-      <c r="K1" s="212" t="n">
+      <c r="K1" s="213" t="n">
         <v>1</v>
       </c>
       <c r="L1" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M1" s="213" t="s">
+      <c r="M1" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="213" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="214" t="s">
+      <c r="N1" s="214" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="215" t="s">
         <v>157</v>
       </c>
-      <c r="P1" s="215" t="s">
+      <c r="P1" s="216" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="216" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="217"/>
-      <c r="C2" s="218" t="str">
+      <c r="A2" s="217" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" s="218"/>
+      <c r="C2" s="219" t="str">
         <f aca="false">DEC2HEX(D2,2)</f>
         <v>00</v>
       </c>
@@ -8511,45 +8515,45 @@
       <c r="L2" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="219" t="s">
-        <v>235</v>
-      </c>
-      <c r="N2" s="217"/>
-      <c r="O2" s="220"/>
-      <c r="P2" s="221"/>
+      <c r="M2" s="220" t="s">
+        <v>237</v>
+      </c>
+      <c r="N2" s="218"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="222"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A3" s="222"/>
+      <c r="A3" s="223"/>
       <c r="B3" s="142"/>
       <c r="C3" s="17"/>
       <c r="D3" s="119"/>
       <c r="E3" s="49"/>
       <c r="F3" s="119"/>
       <c r="G3" s="119" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="13"/>
       <c r="K3" s="119"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="223"/>
-      <c r="N3" s="223" t="s">
-        <v>237</v>
-      </c>
-      <c r="O3" s="224" t="s">
-        <v>238</v>
-      </c>
-      <c r="P3" s="225"/>
+      <c r="M3" s="224"/>
+      <c r="N3" s="224" t="s">
+        <v>239</v>
+      </c>
+      <c r="O3" s="225" t="s">
+        <v>240</v>
+      </c>
+      <c r="P3" s="226"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A4" s="222"/>
+      <c r="A4" s="223"/>
       <c r="B4" s="142"/>
       <c r="E4" s="49"/>
       <c r="F4" s="119" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G4" s="119"/>
       <c r="H4" s="50"/>
@@ -8557,15 +8561,15 @@
       <c r="J4" s="13"/>
       <c r="K4" s="119"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="223" t="s">
-        <v>240</v>
+      <c r="M4" s="224" t="s">
+        <v>242</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="14"/>
-      <c r="P4" s="226"/>
+      <c r="P4" s="227"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A5" s="222"/>
+      <c r="A5" s="223"/>
       <c r="B5" s="142"/>
       <c r="C5" s="17"/>
       <c r="D5" s="119"/>
@@ -8577,14 +8581,14 @@
       <c r="J5" s="13"/>
       <c r="K5" s="119"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="223"/>
-      <c r="O5" s="224"/>
-      <c r="P5" s="225"/>
+      <c r="M5" s="224"/>
+      <c r="O5" s="225"/>
+      <c r="P5" s="226"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A6" s="222"/>
+      <c r="A6" s="223"/>
       <c r="B6" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="119"/>
@@ -8594,21 +8598,21 @@
       <c r="J6" s="13"/>
       <c r="K6" s="119"/>
       <c r="L6" s="50"/>
-      <c r="M6" s="223"/>
+      <c r="M6" s="224"/>
       <c r="N6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="P6" s="226"/>
+        <v>244</v>
+      </c>
+      <c r="P6" s="227"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="216" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="217"/>
-      <c r="C7" s="218" t="str">
+      <c r="A7" s="217" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="218"/>
+      <c r="C7" s="219" t="str">
         <f aca="false">DEC2HEX(D7,2)</f>
         <v>01</v>
       </c>
@@ -8632,43 +8636,43 @@
       <c r="L7" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="219" t="s">
-        <v>244</v>
-      </c>
-      <c r="N7" s="217"/>
-      <c r="O7" s="219"/>
-      <c r="P7" s="221"/>
+      <c r="M7" s="220" t="s">
+        <v>246</v>
+      </c>
+      <c r="N7" s="218"/>
+      <c r="O7" s="220"/>
+      <c r="P7" s="222"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A8" s="222"/>
+      <c r="A8" s="223"/>
       <c r="B8" s="142"/>
       <c r="C8" s="17"/>
       <c r="D8" s="119"/>
       <c r="E8" s="49"/>
       <c r="F8" s="119"/>
       <c r="G8" s="119" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I8" s="49"/>
       <c r="J8" s="13"/>
       <c r="K8" s="119"/>
       <c r="L8" s="50"/>
-      <c r="M8" s="223"/>
+      <c r="M8" s="224"/>
       <c r="N8" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O8" s="224" t="s">
-        <v>238</v>
-      </c>
-      <c r="P8" s="225" t="s">
-        <v>245</v>
+        <v>239</v>
+      </c>
+      <c r="O8" s="225" t="s">
+        <v>240</v>
+      </c>
+      <c r="P8" s="226" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A9" s="222"/>
+      <c r="A9" s="223"/>
       <c r="B9" s="142"/>
       <c r="C9" s="17"/>
       <c r="D9" s="119"/>
@@ -8680,14 +8684,14 @@
       <c r="J9" s="13"/>
       <c r="K9" s="119"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="223"/>
-      <c r="O9" s="224"/>
-      <c r="P9" s="225"/>
+      <c r="M9" s="224"/>
+      <c r="O9" s="225"/>
+      <c r="P9" s="226"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="222"/>
+      <c r="A10" s="223"/>
       <c r="B10" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E10" s="146"/>
       <c r="F10" s="119"/>
@@ -8702,16 +8706,16 @@
         <v>1</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="P10" s="226"/>
+        <v>244</v>
+      </c>
+      <c r="P10" s="227"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="216" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="217"/>
-      <c r="C11" s="218" t="str">
+      <c r="A11" s="217" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="218"/>
+      <c r="C11" s="219" t="str">
         <f aca="false">DEC2HEX(D11,2)</f>
         <v>02</v>
       </c>
@@ -8735,43 +8739,43 @@
       <c r="L11" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="219" t="s">
-        <v>247</v>
-      </c>
-      <c r="N11" s="217"/>
-      <c r="O11" s="220"/>
-      <c r="P11" s="221"/>
+      <c r="M11" s="220" t="s">
+        <v>249</v>
+      </c>
+      <c r="N11" s="218"/>
+      <c r="O11" s="221"/>
+      <c r="P11" s="222"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A12" s="222"/>
+      <c r="A12" s="223"/>
       <c r="B12" s="142"/>
       <c r="C12" s="17"/>
       <c r="D12" s="119"/>
       <c r="E12" s="49"/>
       <c r="F12" s="119"/>
       <c r="G12" s="119" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I12" s="49"/>
       <c r="J12" s="13"/>
       <c r="K12" s="119"/>
       <c r="L12" s="50"/>
-      <c r="M12" s="223"/>
-      <c r="N12" s="223" t="s">
-        <v>248</v>
-      </c>
-      <c r="O12" s="224" t="s">
-        <v>238</v>
-      </c>
-      <c r="P12" s="227" t="s">
-        <v>249</v>
+      <c r="M12" s="224"/>
+      <c r="N12" s="224" t="s">
+        <v>250</v>
+      </c>
+      <c r="O12" s="225" t="s">
+        <v>240</v>
+      </c>
+      <c r="P12" s="228" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A13" s="222"/>
+      <c r="A13" s="223"/>
       <c r="B13" s="142"/>
       <c r="C13" s="17"/>
       <c r="D13" s="119"/>
@@ -8783,14 +8787,14 @@
       <c r="J13" s="13"/>
       <c r="K13" s="119"/>
       <c r="L13" s="50"/>
-      <c r="M13" s="223"/>
-      <c r="O13" s="224"/>
-      <c r="P13" s="225"/>
+      <c r="M13" s="224"/>
+      <c r="O13" s="225"/>
+      <c r="P13" s="226"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A14" s="222"/>
+      <c r="A14" s="223"/>
       <c r="B14" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="119"/>
@@ -8800,23 +8804,23 @@
       <c r="J14" s="13"/>
       <c r="K14" s="119"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="223"/>
+      <c r="M14" s="224"/>
       <c r="N14" s="10" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="P14" s="226" t="s">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="P14" s="227" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="216" t="s">
-        <v>252</v>
-      </c>
-      <c r="B15" s="217"/>
-      <c r="C15" s="218" t="str">
+      <c r="A15" s="217" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="218"/>
+      <c r="C15" s="219" t="str">
         <f aca="false">DEC2HEX(D15,2)</f>
         <v>03</v>
       </c>
@@ -8840,15 +8844,15 @@
       <c r="L15" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="219" t="s">
+      <c r="M15" s="220" t="s">
         <v>101</v>
       </c>
-      <c r="N15" s="217"/>
-      <c r="O15" s="219"/>
-      <c r="P15" s="221"/>
+      <c r="N15" s="218"/>
+      <c r="O15" s="220"/>
+      <c r="P15" s="222"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A16" s="222"/>
+      <c r="A16" s="223"/>
       <c r="B16" s="142"/>
       <c r="C16" s="17"/>
       <c r="D16" s="119"/>
@@ -8860,14 +8864,14 @@
       <c r="J16" s="13"/>
       <c r="K16" s="119"/>
       <c r="L16" s="50"/>
-      <c r="M16" s="223"/>
-      <c r="O16" s="224"/>
-      <c r="P16" s="225"/>
+      <c r="M16" s="224"/>
+      <c r="O16" s="225"/>
+      <c r="P16" s="226"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A17" s="222"/>
+      <c r="A17" s="223"/>
       <c r="B17" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="119"/>
@@ -8879,21 +8883,21 @@
       <c r="J17" s="13"/>
       <c r="K17" s="119"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="223"/>
+      <c r="M17" s="224"/>
       <c r="N17" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="O17" s="224" t="s">
-        <v>254</v>
-      </c>
-      <c r="P17" s="225" t="s">
         <v>255</v>
       </c>
+      <c r="O17" s="225" t="s">
+        <v>256</v>
+      </c>
+      <c r="P17" s="226" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A18" s="222"/>
+      <c r="A18" s="223"/>
       <c r="B18" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E18" s="146"/>
       <c r="F18" s="119"/>
@@ -8908,18 +8912,18 @@
         <v>1</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="P18" s="228" t="s">
-        <v>257</v>
+        <v>258</v>
+      </c>
+      <c r="P18" s="229" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="216" t="s">
-        <v>258</v>
-      </c>
-      <c r="B19" s="217"/>
-      <c r="C19" s="218" t="str">
+      <c r="A19" s="217" t="s">
+        <v>260</v>
+      </c>
+      <c r="B19" s="218"/>
+      <c r="C19" s="219" t="str">
         <f aca="false">DEC2HEX(D19,2)</f>
         <v>04</v>
       </c>
@@ -8943,25 +8947,25 @@
       <c r="L19" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="219" t="s">
-        <v>259</v>
-      </c>
-      <c r="N19" s="217"/>
-      <c r="O19" s="219"/>
-      <c r="P19" s="221"/>
-    </row>
-    <row r="20" s="229" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A20" s="222"/>
+      <c r="M19" s="220" t="s">
+        <v>261</v>
+      </c>
+      <c r="N19" s="218"/>
+      <c r="O19" s="220"/>
+      <c r="P19" s="222"/>
+    </row>
+    <row r="20" s="230" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A20" s="223"/>
       <c r="B20" s="142"/>
       <c r="C20" s="20"/>
       <c r="D20" s="2"/>
       <c r="E20" s="146"/>
       <c r="F20" s="119"/>
       <c r="G20" s="119" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I20" s="119"/>
       <c r="J20" s="119"/>
@@ -8969,19 +8973,19 @@
       <c r="L20" s="50"/>
       <c r="M20" s="10"/>
       <c r="N20" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="P20" s="225"/>
+        <v>240</v>
+      </c>
+      <c r="P20" s="226"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A21" s="222"/>
+      <c r="A21" s="223"/>
       <c r="B21" s="142"/>
       <c r="E21" s="146"/>
       <c r="F21" s="119" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G21" s="119"/>
       <c r="H21" s="50"/>
@@ -8990,16 +8994,16 @@
       <c r="K21" s="119"/>
       <c r="L21" s="50"/>
       <c r="M21" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="142"/>
-      <c r="P21" s="225" t="s">
-        <v>261</v>
+      <c r="P21" s="226" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A22" s="222"/>
+      <c r="A22" s="223"/>
       <c r="B22" s="142"/>
       <c r="E22" s="146"/>
       <c r="F22" s="119"/>
@@ -9011,41 +9015,41 @@
       <c r="L22" s="50"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O22" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="P22" s="225"/>
+      <c r="P22" s="226"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A23" s="230"/>
-      <c r="B23" s="231"/>
-      <c r="C23" s="232"/>
-      <c r="D23" s="233"/>
-      <c r="E23" s="234" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" s="233"/>
-      <c r="G23" s="233"/>
-      <c r="H23" s="235"/>
-      <c r="I23" s="234"/>
-      <c r="J23" s="236"/>
-      <c r="K23" s="233"/>
-      <c r="L23" s="235"/>
-      <c r="M23" s="237" t="s">
-        <v>264</v>
-      </c>
-      <c r="N23" s="229"/>
-      <c r="O23" s="238"/>
-      <c r="P23" s="239" t="s">
+      <c r="A23" s="231"/>
+      <c r="B23" s="232"/>
+      <c r="C23" s="233"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="235" t="s">
         <v>265</v>
       </c>
+      <c r="F23" s="234"/>
+      <c r="G23" s="234"/>
+      <c r="H23" s="236"/>
+      <c r="I23" s="235"/>
+      <c r="J23" s="237"/>
+      <c r="K23" s="234"/>
+      <c r="L23" s="236"/>
+      <c r="M23" s="238" t="s">
+        <v>266</v>
+      </c>
+      <c r="N23" s="230"/>
+      <c r="O23" s="239"/>
+      <c r="P23" s="240" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A24" s="222"/>
+      <c r="A24" s="223"/>
       <c r="B24" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E24" s="146"/>
       <c r="F24" s="119"/>
@@ -9058,18 +9062,18 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="P24" s="225" t="s">
-        <v>267</v>
+        <v>268</v>
+      </c>
+      <c r="P24" s="226" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="216" t="s">
-        <v>268</v>
-      </c>
-      <c r="B25" s="217"/>
-      <c r="C25" s="218" t="str">
+      <c r="A25" s="217" t="s">
+        <v>270</v>
+      </c>
+      <c r="B25" s="218"/>
+      <c r="C25" s="219" t="str">
         <f aca="false">DEC2HEX(D25,2)</f>
         <v>05</v>
       </c>
@@ -9093,19 +9097,19 @@
       <c r="L25" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M25" s="219" t="s">
-        <v>269</v>
-      </c>
-      <c r="N25" s="217"/>
-      <c r="O25" s="219"/>
-      <c r="P25" s="221"/>
+      <c r="M25" s="220" t="s">
+        <v>271</v>
+      </c>
+      <c r="N25" s="218"/>
+      <c r="O25" s="220"/>
+      <c r="P25" s="222"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A26" s="222"/>
+      <c r="A26" s="223"/>
       <c r="B26" s="142"/>
       <c r="E26" s="146"/>
       <c r="F26" s="119" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G26" s="119"/>
       <c r="H26" s="50"/>
@@ -9114,16 +9118,16 @@
       <c r="K26" s="119"/>
       <c r="L26" s="50"/>
       <c r="M26" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="142"/>
-      <c r="P26" s="225" t="s">
-        <v>270</v>
+      <c r="P26" s="226" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A27" s="222"/>
+      <c r="A27" s="223"/>
       <c r="B27" s="142"/>
       <c r="E27" s="146"/>
       <c r="F27" s="119"/>
@@ -9135,15 +9139,15 @@
       <c r="L27" s="50"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O27" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="P27" s="225"/>
+      <c r="P27" s="226"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A28" s="222"/>
+      <c r="A28" s="223"/>
       <c r="B28" s="142"/>
       <c r="C28" s="17"/>
       <c r="D28" s="119"/>
@@ -9155,13 +9159,13 @@
       <c r="J28" s="13"/>
       <c r="K28" s="119"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="223"/>
-      <c r="O28" s="224"/>
+      <c r="M28" s="224"/>
+      <c r="O28" s="225"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A29" s="222"/>
+      <c r="A29" s="223"/>
       <c r="B29" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="119"/>
@@ -9173,23 +9177,23 @@
       <c r="J29" s="13"/>
       <c r="K29" s="119"/>
       <c r="L29" s="50"/>
-      <c r="M29" s="223"/>
-      <c r="N29" s="240" t="s">
-        <v>1</v>
-      </c>
-      <c r="O29" s="241" t="s">
+      <c r="M29" s="224"/>
+      <c r="N29" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="O29" s="225" t="s">
         <v>32</v>
       </c>
-      <c r="P29" s="242" t="s">
-        <v>271</v>
+      <c r="P29" s="227" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="216" t="s">
-        <v>272</v>
-      </c>
-      <c r="B30" s="217"/>
-      <c r="C30" s="218" t="str">
+      <c r="A30" s="217" t="s">
+        <v>274</v>
+      </c>
+      <c r="B30" s="218"/>
+      <c r="C30" s="219" t="str">
         <f aca="false">DEC2HEX(D30,2)</f>
         <v>06</v>
       </c>
@@ -9213,17 +9217,17 @@
       <c r="L30" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="219" t="s">
-        <v>273</v>
-      </c>
-      <c r="N30" s="217"/>
-      <c r="O30" s="219"/>
-      <c r="P30" s="243" t="s">
-        <v>274</v>
+      <c r="M30" s="220" t="s">
+        <v>275</v>
+      </c>
+      <c r="N30" s="218"/>
+      <c r="O30" s="220"/>
+      <c r="P30" s="241" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A31" s="222"/>
+      <c r="A31" s="223"/>
       <c r="E31" s="146"/>
       <c r="F31" s="119"/>
       <c r="G31" s="119" t="n">
@@ -9237,12 +9241,12 @@
       <c r="K31" s="119"/>
       <c r="L31" s="50"/>
       <c r="M31" s="142" t="s">
-        <v>275</v>
-      </c>
-      <c r="P31" s="225"/>
+        <v>277</v>
+      </c>
+      <c r="P31" s="226"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A32" s="222"/>
+      <c r="A32" s="223"/>
       <c r="E32" s="146"/>
       <c r="F32" s="119"/>
       <c r="G32" s="119" t="n">
@@ -9255,13 +9259,13 @@
       <c r="J32" s="119"/>
       <c r="K32" s="119"/>
       <c r="L32" s="50"/>
-      <c r="M32" s="223" t="s">
-        <v>276</v>
-      </c>
-      <c r="P32" s="225"/>
+      <c r="M32" s="224" t="s">
+        <v>278</v>
+      </c>
+      <c r="P32" s="226"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A33" s="222"/>
+      <c r="A33" s="223"/>
       <c r="E33" s="146"/>
       <c r="F33" s="119"/>
       <c r="G33" s="119" t="n">
@@ -9274,13 +9278,13 @@
       <c r="J33" s="119"/>
       <c r="K33" s="119"/>
       <c r="L33" s="50"/>
-      <c r="M33" s="223" t="s">
-        <v>277</v>
-      </c>
-      <c r="P33" s="225"/>
+      <c r="M33" s="224" t="s">
+        <v>279</v>
+      </c>
+      <c r="P33" s="226"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A34" s="222"/>
+      <c r="A34" s="223"/>
       <c r="E34" s="146"/>
       <c r="F34" s="119"/>
       <c r="G34" s="119" t="n">
@@ -9294,15 +9298,15 @@
       <c r="K34" s="119"/>
       <c r="L34" s="50"/>
       <c r="M34" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="P34" s="225"/>
+        <v>280</v>
+      </c>
+      <c r="P34" s="226"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="222"/>
+      <c r="A35" s="223"/>
       <c r="E35" s="146"/>
       <c r="F35" s="119" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G35" s="119"/>
       <c r="H35" s="50"/>
@@ -9311,14 +9315,14 @@
       <c r="K35" s="119"/>
       <c r="L35" s="50"/>
       <c r="M35" s="142" t="s">
-        <v>280</v>
-      </c>
-      <c r="P35" s="225" t="s">
-        <v>281</v>
+        <v>282</v>
+      </c>
+      <c r="P35" s="226" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="222"/>
+      <c r="A36" s="223"/>
       <c r="B36" s="142"/>
       <c r="C36" s="17"/>
       <c r="D36" s="119"/>
@@ -9330,14 +9334,14 @@
       <c r="J36" s="13"/>
       <c r="K36" s="119"/>
       <c r="L36" s="50"/>
-      <c r="M36" s="223"/>
-      <c r="O36" s="224"/>
-      <c r="P36" s="225"/>
+      <c r="M36" s="224"/>
+      <c r="O36" s="225"/>
+      <c r="P36" s="226"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="222"/>
+      <c r="A37" s="223"/>
       <c r="B37" s="142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E37" s="146"/>
       <c r="F37" s="119"/>
@@ -9349,18 +9353,18 @@
       <c r="L37" s="50"/>
       <c r="M37" s="142"/>
       <c r="O37" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="P37" s="225" t="s">
-        <v>283</v>
+        <v>284</v>
+      </c>
+      <c r="P37" s="226" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="216" t="s">
-        <v>284</v>
-      </c>
-      <c r="B38" s="217"/>
-      <c r="C38" s="218" t="str">
+      <c r="A38" s="217" t="s">
+        <v>286</v>
+      </c>
+      <c r="B38" s="218"/>
+      <c r="C38" s="219" t="str">
         <f aca="false">DEC2HEX(D38,2)</f>
         <v>07</v>
       </c>
@@ -9384,15 +9388,15 @@
       <c r="L38" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M38" s="219" t="s">
-        <v>285</v>
-      </c>
-      <c r="N38" s="217"/>
-      <c r="O38" s="219"/>
-      <c r="P38" s="221"/>
+      <c r="M38" s="220" t="s">
+        <v>287</v>
+      </c>
+      <c r="N38" s="218"/>
+      <c r="O38" s="220"/>
+      <c r="P38" s="222"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A39" s="222"/>
+      <c r="A39" s="223"/>
       <c r="E39" s="146"/>
       <c r="F39" s="119"/>
       <c r="G39" s="119" t="n">
@@ -9406,14 +9410,14 @@
       <c r="K39" s="119"/>
       <c r="L39" s="50"/>
       <c r="M39" s="142" t="s">
-        <v>286</v>
-      </c>
-      <c r="P39" s="227" t="s">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="P39" s="228" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="222"/>
+      <c r="A40" s="223"/>
       <c r="E40" s="146"/>
       <c r="F40" s="119"/>
       <c r="G40" s="119" t="n">
@@ -9426,15 +9430,15 @@
       <c r="J40" s="119"/>
       <c r="K40" s="119"/>
       <c r="L40" s="50"/>
-      <c r="M40" s="223" t="s">
-        <v>276</v>
-      </c>
-      <c r="P40" s="227" t="s">
-        <v>288</v>
+      <c r="M40" s="224" t="s">
+        <v>278</v>
+      </c>
+      <c r="P40" s="228" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A41" s="222"/>
+      <c r="A41" s="223"/>
       <c r="E41" s="146"/>
       <c r="F41" s="119"/>
       <c r="G41" s="119" t="n">
@@ -9447,15 +9451,15 @@
       <c r="J41" s="119"/>
       <c r="K41" s="119"/>
       <c r="L41" s="50"/>
-      <c r="M41" s="223" t="s">
-        <v>277</v>
-      </c>
-      <c r="P41" s="227" t="s">
-        <v>289</v>
+      <c r="M41" s="224" t="s">
+        <v>279</v>
+      </c>
+      <c r="P41" s="228" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A42" s="222"/>
+      <c r="A42" s="223"/>
       <c r="E42" s="146"/>
       <c r="F42" s="119"/>
       <c r="G42" s="119" t="n">
@@ -9469,14 +9473,14 @@
       <c r="K42" s="119"/>
       <c r="L42" s="50"/>
       <c r="M42" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="P42" s="227" t="s">
-        <v>290</v>
+        <v>280</v>
+      </c>
+      <c r="P42" s="228" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A43" s="222"/>
+      <c r="A43" s="223"/>
       <c r="E43" s="146"/>
       <c r="F43" s="119"/>
       <c r="G43" s="119"/>
@@ -9487,12 +9491,12 @@
       <c r="L43" s="50"/>
       <c r="M43" s="10"/>
       <c r="O43" s="1"/>
-      <c r="P43" s="244" t="s">
-        <v>291</v>
+      <c r="P43" s="242" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A44" s="222"/>
+      <c r="A44" s="223"/>
       <c r="E44" s="146"/>
       <c r="F44" s="119"/>
       <c r="G44" s="119"/>
@@ -9503,12 +9507,12 @@
       <c r="L44" s="50"/>
       <c r="M44" s="10"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="244" t="s">
-        <v>292</v>
+      <c r="P44" s="242" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A45" s="222"/>
+      <c r="A45" s="223"/>
       <c r="E45" s="146"/>
       <c r="F45" s="119"/>
       <c r="G45" s="119"/>
@@ -9519,12 +9523,12 @@
       <c r="L45" s="50"/>
       <c r="M45" s="10"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="244" t="s">
-        <v>293</v>
+      <c r="P45" s="242" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A46" s="222"/>
+      <c r="A46" s="223"/>
       <c r="B46" s="142"/>
       <c r="C46" s="17"/>
       <c r="D46" s="119"/>
@@ -9536,14 +9540,14 @@
       <c r="J46" s="13"/>
       <c r="K46" s="119"/>
       <c r="L46" s="50"/>
-      <c r="M46" s="223"/>
-      <c r="O46" s="224"/>
-      <c r="P46" s="225"/>
+      <c r="M46" s="224"/>
+      <c r="O46" s="225"/>
+      <c r="P46" s="226"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A47" s="222"/>
-      <c r="B47" s="223" t="s">
-        <v>241</v>
+      <c r="A47" s="223"/>
+      <c r="B47" s="224" t="s">
+        <v>243</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="119"/>
@@ -9555,25 +9559,25 @@
       <c r="J47" s="13"/>
       <c r="K47" s="119"/>
       <c r="L47" s="50"/>
-      <c r="M47" s="223"/>
+      <c r="M47" s="224"/>
       <c r="N47" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="O47" s="224" t="s">
-        <v>295</v>
-      </c>
-      <c r="P47" s="225" t="s">
         <v>296</v>
       </c>
+      <c r="O47" s="225" t="s">
+        <v>297</v>
+      </c>
+      <c r="P47" s="226" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A48" s="245"/>
-      <c r="B48" s="223" t="s">
-        <v>241</v>
-      </c>
-      <c r="C48" s="246"/>
+      <c r="A48" s="243"/>
+      <c r="B48" s="224" t="s">
+        <v>243</v>
+      </c>
+      <c r="C48" s="244"/>
       <c r="D48" s="152"/>
-      <c r="E48" s="247"/>
+      <c r="E48" s="245"/>
       <c r="F48" s="152"/>
       <c r="G48" s="152"/>
       <c r="H48" s="155"/>
@@ -9581,21 +9585,21 @@
       <c r="J48" s="152"/>
       <c r="K48" s="152"/>
       <c r="L48" s="155"/>
-      <c r="M48" s="248"/>
+      <c r="M48" s="246"/>
       <c r="N48" s="14" t="s">
         <v>1</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="P48" s="228" t="s">
-        <v>257</v>
+        <v>296</v>
+      </c>
+      <c r="P48" s="229" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="216"/>
-      <c r="B49" s="217"/>
-      <c r="C49" s="218" t="str">
+      <c r="A49" s="217"/>
+      <c r="B49" s="218"/>
+      <c r="C49" s="219" t="str">
         <f aca="false">DEC2HEX(D49,2)</f>
         <v>08</v>
       </c>
@@ -9619,13 +9623,13 @@
       <c r="L49" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="219"/>
-      <c r="N49" s="217"/>
-      <c r="O49" s="219"/>
-      <c r="P49" s="221"/>
+      <c r="M49" s="220"/>
+      <c r="N49" s="218"/>
+      <c r="O49" s="220"/>
+      <c r="P49" s="222"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A50" s="222"/>
+      <c r="A50" s="223"/>
       <c r="B50" s="142"/>
       <c r="C50" s="17"/>
       <c r="D50" s="119"/>
@@ -9637,14 +9641,14 @@
       <c r="J50" s="13"/>
       <c r="K50" s="119"/>
       <c r="L50" s="50"/>
-      <c r="M50" s="223"/>
-      <c r="O50" s="224"/>
-      <c r="P50" s="225"/>
+      <c r="M50" s="224"/>
+      <c r="O50" s="225"/>
+      <c r="P50" s="226"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="216"/>
-      <c r="B51" s="217"/>
-      <c r="C51" s="218" t="str">
+      <c r="A51" s="217"/>
+      <c r="B51" s="218"/>
+      <c r="C51" s="219" t="str">
         <f aca="false">DEC2HEX(D51,2)</f>
         <v>09</v>
       </c>
@@ -9668,13 +9672,13 @@
       <c r="L51" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M51" s="219"/>
-      <c r="N51" s="217"/>
-      <c r="O51" s="219"/>
-      <c r="P51" s="221"/>
+      <c r="M51" s="220"/>
+      <c r="N51" s="218"/>
+      <c r="O51" s="220"/>
+      <c r="P51" s="222"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A52" s="222"/>
+      <c r="A52" s="223"/>
       <c r="B52" s="142"/>
       <c r="C52" s="17"/>
       <c r="D52" s="119"/>
@@ -9686,16 +9690,16 @@
       <c r="J52" s="13"/>
       <c r="K52" s="119"/>
       <c r="L52" s="50"/>
-      <c r="M52" s="223"/>
-      <c r="O52" s="224"/>
-      <c r="P52" s="225"/>
+      <c r="M52" s="224"/>
+      <c r="O52" s="225"/>
+      <c r="P52" s="226"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="216" t="s">
-        <v>297</v>
-      </c>
-      <c r="B53" s="217"/>
-      <c r="C53" s="218" t="str">
+      <c r="A53" s="217" t="s">
+        <v>299</v>
+      </c>
+      <c r="B53" s="218"/>
+      <c r="C53" s="219" t="str">
         <f aca="false">DEC2HEX(D53,2)</f>
         <v>0A</v>
       </c>
@@ -9719,15 +9723,15 @@
       <c r="L53" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="219" t="s">
-        <v>298</v>
-      </c>
-      <c r="N53" s="217"/>
-      <c r="O53" s="219"/>
-      <c r="P53" s="221"/>
+      <c r="M53" s="220" t="s">
+        <v>300</v>
+      </c>
+      <c r="N53" s="218"/>
+      <c r="O53" s="220"/>
+      <c r="P53" s="222"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A54" s="222"/>
+      <c r="A54" s="223"/>
       <c r="B54" s="142"/>
       <c r="C54" s="17"/>
       <c r="D54" s="119"/>
@@ -9739,14 +9743,14 @@
       <c r="J54" s="13"/>
       <c r="K54" s="119"/>
       <c r="L54" s="50"/>
-      <c r="M54" s="223"/>
-      <c r="O54" s="224"/>
-      <c r="P54" s="225"/>
+      <c r="M54" s="224"/>
+      <c r="O54" s="225"/>
+      <c r="P54" s="226"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A55" s="222"/>
-      <c r="B55" s="223" t="s">
-        <v>241</v>
+      <c r="A55" s="223"/>
+      <c r="B55" s="224" t="s">
+        <v>243</v>
       </c>
       <c r="E55" s="146"/>
       <c r="F55" s="119"/>
@@ -9761,16 +9765,16 @@
         <v>1</v>
       </c>
       <c r="O55" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="P55" s="225" t="s">
-        <v>300</v>
+        <v>301</v>
+      </c>
+      <c r="P55" s="226" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="216"/>
-      <c r="B56" s="217"/>
-      <c r="C56" s="218" t="str">
+      <c r="A56" s="217"/>
+      <c r="B56" s="218"/>
+      <c r="C56" s="219" t="str">
         <f aca="false">DEC2HEX(D56,2)</f>
         <v>0B</v>
       </c>
@@ -9794,13 +9798,13 @@
       <c r="L56" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M56" s="219"/>
-      <c r="N56" s="217"/>
-      <c r="O56" s="219"/>
-      <c r="P56" s="221"/>
+      <c r="M56" s="220"/>
+      <c r="N56" s="218"/>
+      <c r="O56" s="220"/>
+      <c r="P56" s="222"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A57" s="222"/>
+      <c r="A57" s="223"/>
       <c r="B57" s="142"/>
       <c r="C57" s="17"/>
       <c r="D57" s="119"/>
@@ -9812,14 +9816,14 @@
       <c r="J57" s="13"/>
       <c r="K57" s="119"/>
       <c r="L57" s="50"/>
-      <c r="M57" s="223"/>
-      <c r="O57" s="224"/>
-      <c r="P57" s="225"/>
+      <c r="M57" s="224"/>
+      <c r="O57" s="225"/>
+      <c r="P57" s="226"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="216"/>
-      <c r="B58" s="217"/>
-      <c r="C58" s="218" t="str">
+      <c r="A58" s="217"/>
+      <c r="B58" s="218"/>
+      <c r="C58" s="219" t="str">
         <f aca="false">DEC2HEX(D58,2)</f>
         <v>0C</v>
       </c>
@@ -9843,13 +9847,13 @@
       <c r="L58" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M58" s="217"/>
-      <c r="N58" s="217"/>
-      <c r="O58" s="219"/>
-      <c r="P58" s="221"/>
+      <c r="M58" s="218"/>
+      <c r="N58" s="218"/>
+      <c r="O58" s="220"/>
+      <c r="P58" s="222"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A59" s="222"/>
+      <c r="A59" s="223"/>
       <c r="E59" s="146"/>
       <c r="F59" s="119"/>
       <c r="G59" s="119"/>
@@ -9858,15 +9862,15 @@
       <c r="J59" s="119"/>
       <c r="K59" s="119"/>
       <c r="L59" s="50"/>
-      <c r="M59" s="223"/>
-      <c r="N59" s="223"/>
+      <c r="M59" s="224"/>
+      <c r="N59" s="224"/>
       <c r="O59" s="142"/>
-      <c r="P59" s="225"/>
+      <c r="P59" s="226"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="216"/>
-      <c r="B60" s="217"/>
-      <c r="C60" s="218" t="str">
+      <c r="A60" s="217"/>
+      <c r="B60" s="218"/>
+      <c r="C60" s="219" t="str">
         <f aca="false">DEC2HEX(D60,2)</f>
         <v>0D</v>
       </c>
@@ -9890,13 +9894,13 @@
       <c r="L60" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M60" s="217"/>
-      <c r="N60" s="217"/>
-      <c r="O60" s="219"/>
-      <c r="P60" s="221"/>
+      <c r="M60" s="218"/>
+      <c r="N60" s="218"/>
+      <c r="O60" s="220"/>
+      <c r="P60" s="222"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A61" s="222"/>
+      <c r="A61" s="223"/>
       <c r="E61" s="146"/>
       <c r="F61" s="119"/>
       <c r="G61" s="119"/>
@@ -9905,15 +9909,15 @@
       <c r="J61" s="119"/>
       <c r="K61" s="119"/>
       <c r="L61" s="50"/>
-      <c r="M61" s="223"/>
-      <c r="N61" s="223"/>
+      <c r="M61" s="224"/>
+      <c r="N61" s="224"/>
       <c r="O61" s="142"/>
-      <c r="P61" s="225"/>
+      <c r="P61" s="226"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="216"/>
-      <c r="B62" s="217"/>
-      <c r="C62" s="218" t="str">
+      <c r="A62" s="217"/>
+      <c r="B62" s="218"/>
+      <c r="C62" s="219" t="str">
         <f aca="false">DEC2HEX(D62,2)</f>
         <v>0E</v>
       </c>
@@ -9937,13 +9941,13 @@
       <c r="L62" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="M62" s="217"/>
-      <c r="N62" s="217"/>
-      <c r="O62" s="219"/>
-      <c r="P62" s="221"/>
+      <c r="M62" s="218"/>
+      <c r="N62" s="218"/>
+      <c r="O62" s="220"/>
+      <c r="P62" s="222"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A63" s="222"/>
+      <c r="A63" s="223"/>
       <c r="E63" s="146"/>
       <c r="F63" s="119"/>
       <c r="G63" s="119"/>
@@ -9952,15 +9956,15 @@
       <c r="J63" s="119"/>
       <c r="K63" s="119"/>
       <c r="L63" s="50"/>
-      <c r="M63" s="223"/>
-      <c r="N63" s="223"/>
+      <c r="M63" s="224"/>
+      <c r="N63" s="224"/>
       <c r="O63" s="142"/>
-      <c r="P63" s="225"/>
+      <c r="P63" s="226"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="216"/>
-      <c r="B64" s="217"/>
-      <c r="C64" s="218" t="str">
+      <c r="A64" s="217"/>
+      <c r="B64" s="218"/>
+      <c r="C64" s="219" t="str">
         <f aca="false">DEC2HEX(D64,2)</f>
         <v>0F</v>
       </c>
@@ -9984,13 +9988,13 @@
       <c r="L64" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="M64" s="217"/>
-      <c r="N64" s="217"/>
-      <c r="O64" s="219"/>
-      <c r="P64" s="221"/>
+      <c r="M64" s="218"/>
+      <c r="N64" s="218"/>
+      <c r="O64" s="220"/>
+      <c r="P64" s="222"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A65" s="222"/>
+      <c r="A65" s="223"/>
       <c r="E65" s="146"/>
       <c r="F65" s="119"/>
       <c r="G65" s="119"/>
@@ -9999,13 +10003,13 @@
       <c r="J65" s="119"/>
       <c r="K65" s="119"/>
       <c r="L65" s="50"/>
-      <c r="M65" s="223"/>
-      <c r="N65" s="223"/>
+      <c r="M65" s="224"/>
+      <c r="N65" s="224"/>
       <c r="O65" s="142"/>
-      <c r="P65" s="225"/>
+      <c r="P65" s="226"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="222"/>
+      <c r="A66" s="223"/>
       <c r="E66" s="146"/>
       <c r="F66" s="119"/>
       <c r="G66" s="119"/>
@@ -10014,13 +10018,13 @@
       <c r="J66" s="119"/>
       <c r="K66" s="119"/>
       <c r="L66" s="50"/>
-      <c r="M66" s="223"/>
-      <c r="N66" s="223"/>
+      <c r="M66" s="224"/>
+      <c r="N66" s="224"/>
       <c r="O66" s="142"/>
-      <c r="P66" s="225"/>
+      <c r="P66" s="226"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="222"/>
+      <c r="A67" s="223"/>
       <c r="E67" s="146"/>
       <c r="F67" s="119"/>
       <c r="G67" s="119"/>
@@ -10029,44 +10033,44 @@
       <c r="J67" s="119"/>
       <c r="K67" s="119"/>
       <c r="L67" s="50"/>
-      <c r="M67" s="223"/>
-      <c r="N67" s="223"/>
+      <c r="M67" s="224"/>
+      <c r="N67" s="224"/>
       <c r="O67" s="142"/>
-      <c r="P67" s="225"/>
+      <c r="P67" s="226"/>
     </row>
     <row r="68" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="249" t="s">
-        <v>301</v>
+      <c r="A68" s="247" t="s">
+        <v>303</v>
       </c>
       <c r="E68" s="146"/>
       <c r="F68" s="200" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G68" s="200" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H68" s="200" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I68" s="200"/>
       <c r="J68" s="200"/>
       <c r="K68" s="200" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L68" s="200" t="s">
-        <v>305</v>
-      </c>
-      <c r="M68" s="223"/>
-      <c r="N68" s="223"/>
+        <v>307</v>
+      </c>
+      <c r="M68" s="224"/>
+      <c r="N68" s="224"/>
       <c r="O68" s="142"/>
-      <c r="P68" s="225"/>
+      <c r="P68" s="226"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="216" t="s">
-        <v>218</v>
-      </c>
-      <c r="B69" s="219"/>
-      <c r="C69" s="218"/>
+      <c r="A69" s="217" t="s">
+        <v>220</v>
+      </c>
+      <c r="B69" s="220"/>
+      <c r="C69" s="219"/>
       <c r="D69" s="173"/>
       <c r="E69" s="188"/>
       <c r="F69" s="173"/>
@@ -10076,17 +10080,17 @@
       <c r="J69" s="173"/>
       <c r="K69" s="173"/>
       <c r="L69" s="177"/>
-      <c r="M69" s="217"/>
-      <c r="N69" s="217"/>
-      <c r="O69" s="219"/>
-      <c r="P69" s="221"/>
+      <c r="M69" s="218"/>
+      <c r="N69" s="218"/>
+      <c r="O69" s="220"/>
+      <c r="P69" s="222"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A70" s="250" t="s">
-        <v>306</v>
+      <c r="A70" s="248" t="s">
+        <v>308</v>
       </c>
       <c r="B70" s="191"/>
-      <c r="C70" s="212" t="str">
+      <c r="C70" s="213" t="str">
         <f aca="false">DEC2HEX(D70,2)</f>
         <v>00</v>
       </c>
@@ -10094,38 +10098,38 @@
         <f aca="false">IF(E70=1,128,0)+IF(F70=1,64,0)+IF(G70=1,32,0)+IF(H70=1,16,0)+IF(I70=1,8,0)+IF(J70=1,4,0)+IF(K70=1,2,0)+IF(L70=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E70" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="254"/>
-      <c r="N70" s="254"/>
+      <c r="E70" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="252"/>
+      <c r="N70" s="252"/>
       <c r="O70" s="191"/>
-      <c r="P70" s="255"/>
+      <c r="P70" s="253"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A71" s="222" t="s">
-        <v>307</v>
+      <c r="A71" s="223" t="s">
+        <v>309</v>
       </c>
       <c r="B71" s="142"/>
       <c r="C71" s="20" t="str">
@@ -10160,14 +10164,14 @@
       <c r="L71" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M71" s="223"/>
-      <c r="N71" s="223"/>
+      <c r="M71" s="224"/>
+      <c r="N71" s="224"/>
       <c r="O71" s="142"/>
-      <c r="P71" s="225"/>
+      <c r="P71" s="226"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A72" s="222" t="s">
-        <v>308</v>
+      <c r="A72" s="223" t="s">
+        <v>310</v>
       </c>
       <c r="B72" s="142"/>
       <c r="C72" s="20" t="str">
@@ -10202,17 +10206,17 @@
       <c r="L72" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="223"/>
-      <c r="N72" s="223"/>
+      <c r="M72" s="224"/>
+      <c r="N72" s="224"/>
       <c r="O72" s="142"/>
-      <c r="P72" s="225"/>
+      <c r="P72" s="226"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A73" s="245" t="s">
-        <v>309</v>
-      </c>
-      <c r="B73" s="248"/>
-      <c r="C73" s="246" t="str">
+      <c r="A73" s="243" t="s">
+        <v>311</v>
+      </c>
+      <c r="B73" s="246"/>
+      <c r="C73" s="244" t="str">
         <f aca="false">DEC2HEX(D73,2)</f>
         <v>30</v>
       </c>
@@ -10220,7 +10224,7 @@
         <f aca="false">IF(E73=1,128,0)+IF(F73=1,64,0)+IF(G73=1,32,0)+IF(H73=1,16,0)+IF(I73=1,8,0)+IF(J73=1,4,0)+IF(K73=1,2,0)+IF(L73=1,1,0)</f>
         <v>48</v>
       </c>
-      <c r="E73" s="247" t="n">
+      <c r="E73" s="245" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="152" t="n">
@@ -10232,7 +10236,7 @@
       <c r="H73" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I73" s="247" t="n">
+      <c r="I73" s="245" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="152" t="n">
@@ -10244,17 +10248,17 @@
       <c r="L73" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="256"/>
-      <c r="N73" s="256"/>
-      <c r="O73" s="248"/>
-      <c r="P73" s="257"/>
+      <c r="M73" s="254"/>
+      <c r="N73" s="254"/>
+      <c r="O73" s="246"/>
+      <c r="P73" s="255"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A74" s="250" t="s">
-        <v>310</v>
+      <c r="A74" s="248" t="s">
+        <v>312</v>
       </c>
       <c r="B74" s="191"/>
-      <c r="C74" s="212" t="str">
+      <c r="C74" s="213" t="str">
         <f aca="false">DEC2HEX(D74,2)</f>
         <v>40</v>
       </c>
@@ -10262,38 +10266,38 @@
         <f aca="false">IF(E74=1,128,0)+IF(F74=1,64,0)+IF(G74=1,32,0)+IF(H74=1,16,0)+IF(I74=1,8,0)+IF(J74=1,4,0)+IF(K74=1,2,0)+IF(L74=1,1,0)</f>
         <v>64</v>
       </c>
-      <c r="E74" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="252" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="254"/>
-      <c r="N74" s="254"/>
+      <c r="E74" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="250" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="252"/>
+      <c r="N74" s="252"/>
       <c r="O74" s="191"/>
-      <c r="P74" s="255"/>
+      <c r="P74" s="253"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A75" s="222" t="s">
-        <v>311</v>
+      <c r="A75" s="223" t="s">
+        <v>313</v>
       </c>
       <c r="B75" s="142"/>
       <c r="C75" s="20" t="str">
@@ -10328,14 +10332,14 @@
       <c r="L75" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M75" s="223"/>
-      <c r="N75" s="223"/>
+      <c r="M75" s="224"/>
+      <c r="N75" s="224"/>
       <c r="O75" s="142"/>
-      <c r="P75" s="225"/>
+      <c r="P75" s="226"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A76" s="222" t="s">
-        <v>312</v>
+      <c r="A76" s="223" t="s">
+        <v>314</v>
       </c>
       <c r="B76" s="142"/>
       <c r="C76" s="20" t="str">
@@ -10370,17 +10374,17 @@
       <c r="L76" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="223"/>
-      <c r="N76" s="223"/>
+      <c r="M76" s="224"/>
+      <c r="N76" s="224"/>
       <c r="O76" s="142"/>
-      <c r="P76" s="225"/>
+      <c r="P76" s="226"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A77" s="245" t="s">
-        <v>313</v>
-      </c>
-      <c r="B77" s="248"/>
-      <c r="C77" s="246" t="str">
+      <c r="A77" s="243" t="s">
+        <v>315</v>
+      </c>
+      <c r="B77" s="246"/>
+      <c r="C77" s="244" t="str">
         <f aca="false">DEC2HEX(D77,2)</f>
         <v>70</v>
       </c>
@@ -10388,7 +10392,7 @@
         <f aca="false">IF(E77=1,128,0)+IF(F77=1,64,0)+IF(G77=1,32,0)+IF(H77=1,16,0)+IF(I77=1,8,0)+IF(J77=1,4,0)+IF(K77=1,2,0)+IF(L77=1,1,0)</f>
         <v>112</v>
       </c>
-      <c r="E77" s="247" t="n">
+      <c r="E77" s="245" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="152" t="n">
@@ -10400,7 +10404,7 @@
       <c r="H77" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I77" s="247" t="n">
+      <c r="I77" s="245" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="152" t="n">
@@ -10412,17 +10416,17 @@
       <c r="L77" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="256"/>
-      <c r="N77" s="256"/>
-      <c r="O77" s="248"/>
-      <c r="P77" s="257"/>
+      <c r="M77" s="254"/>
+      <c r="N77" s="254"/>
+      <c r="O77" s="246"/>
+      <c r="P77" s="255"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A78" s="250" t="s">
-        <v>314</v>
-      </c>
-      <c r="B78" s="258"/>
-      <c r="C78" s="212" t="str">
+      <c r="A78" s="248" t="s">
+        <v>316</v>
+      </c>
+      <c r="B78" s="256"/>
+      <c r="C78" s="213" t="str">
         <f aca="false">DEC2HEX(D78,2)</f>
         <v>01</v>
       </c>
@@ -10430,38 +10434,38 @@
         <f aca="false">IF(E78=1,128,0)+IF(F78=1,64,0)+IF(G78=1,32,0)+IF(H78=1,16,0)+IF(I78=1,8,0)+IF(J78=1,4,0)+IF(K78=1,2,0)+IF(L78=1,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E78" s="251" t="n">
+      <c r="E78" s="249" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="G78" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="252" t="n">
+      <c r="G78" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="250" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="L78" s="253" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" s="254"/>
-      <c r="N78" s="254"/>
+      <c r="L78" s="251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="252"/>
+      <c r="N78" s="252"/>
       <c r="O78" s="191"/>
-      <c r="P78" s="255"/>
+      <c r="P78" s="253"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A79" s="222" t="s">
-        <v>315</v>
+      <c r="A79" s="223" t="s">
+        <v>317</v>
       </c>
       <c r="B79" s="142"/>
       <c r="C79" s="20" t="str">
@@ -10496,11 +10500,11 @@
       <c r="L79" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="P79" s="225"/>
+      <c r="P79" s="226"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A80" s="222" t="s">
-        <v>316</v>
+      <c r="A80" s="223" t="s">
+        <v>318</v>
       </c>
       <c r="B80" s="142"/>
       <c r="C80" s="20" t="str">
@@ -10538,14 +10542,14 @@
       <c r="M80" s="10"/>
       <c r="N80" s="10"/>
       <c r="O80" s="142"/>
-      <c r="P80" s="225"/>
+      <c r="P80" s="226"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A81" s="245" t="s">
-        <v>317</v>
-      </c>
-      <c r="B81" s="248"/>
-      <c r="C81" s="246" t="str">
+      <c r="A81" s="243" t="s">
+        <v>319</v>
+      </c>
+      <c r="B81" s="246"/>
+      <c r="C81" s="244" t="str">
         <f aca="false">DEC2HEX(D81,2)</f>
         <v>31</v>
       </c>
@@ -10553,7 +10557,7 @@
         <f aca="false">IF(E81=1,128,0)+IF(F81=1,64,0)+IF(G81=1,32,0)+IF(H81=1,16,0)+IF(I81=1,8,0)+IF(J81=1,4,0)+IF(K81=1,2,0)+IF(L81=1,1,0)</f>
         <v>49</v>
       </c>
-      <c r="E81" s="247" t="n">
+      <c r="E81" s="245" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="152" t="n">
@@ -10565,7 +10569,7 @@
       <c r="H81" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="247" t="n">
+      <c r="I81" s="245" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="152" t="n">
@@ -10577,17 +10581,17 @@
       <c r="L81" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="M81" s="256"/>
-      <c r="N81" s="256"/>
-      <c r="O81" s="248"/>
-      <c r="P81" s="257"/>
+      <c r="M81" s="254"/>
+      <c r="N81" s="254"/>
+      <c r="O81" s="246"/>
+      <c r="P81" s="255"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A82" s="250" t="s">
-        <v>318</v>
+      <c r="A82" s="248" t="s">
+        <v>320</v>
       </c>
       <c r="B82" s="191"/>
-      <c r="C82" s="212" t="str">
+      <c r="C82" s="213" t="str">
         <f aca="false">DEC2HEX(D82,2)</f>
         <v>04</v>
       </c>
@@ -10595,40 +10599,40 @@
         <f aca="false">IF(E82=1,128,0)+IF(F82=1,64,0)+IF(G82=1,32,0)+IF(H82=1,16,0)+IF(I82=1,8,0)+IF(J82=1,4,0)+IF(K82=1,2,0)+IF(L82=1,1,0)</f>
         <v>4</v>
       </c>
-      <c r="E82" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="252" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="254"/>
-      <c r="N82" s="254"/>
+      <c r="E82" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="250" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="252"/>
+      <c r="N82" s="252"/>
       <c r="O82" s="191"/>
-      <c r="P82" s="255" t="s">
-        <v>319</v>
+      <c r="P82" s="253" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A83" s="222" t="s">
-        <v>320</v>
+      <c r="A83" s="223" t="s">
+        <v>322</v>
       </c>
       <c r="B83" s="142"/>
       <c r="C83" s="20" t="str">
@@ -10663,18 +10667,18 @@
       <c r="L83" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M83" s="223"/>
-      <c r="N83" s="223"/>
+      <c r="M83" s="224"/>
+      <c r="N83" s="224"/>
       <c r="O83" s="142"/>
-      <c r="P83" s="225" t="s">
-        <v>321</v>
+      <c r="P83" s="226" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A84" s="222" t="s">
-        <v>322</v>
-      </c>
-      <c r="B84" s="259"/>
+      <c r="A84" s="223" t="s">
+        <v>324</v>
+      </c>
+      <c r="B84" s="257"/>
       <c r="C84" s="17" t="str">
         <f aca="false">DEC2HEX(D84,2)</f>
         <v>54</v>
@@ -10707,18 +10711,18 @@
       <c r="L84" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="223"/>
-      <c r="N84" s="223"/>
-      <c r="O84" s="259"/>
-      <c r="P84" s="225" t="s">
-        <v>323</v>
+      <c r="M84" s="224"/>
+      <c r="N84" s="224"/>
+      <c r="O84" s="257"/>
+      <c r="P84" s="226" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A85" s="222" t="s">
-        <v>324</v>
-      </c>
-      <c r="B85" s="259"/>
+      <c r="A85" s="223" t="s">
+        <v>326</v>
+      </c>
+      <c r="B85" s="257"/>
       <c r="C85" s="17" t="str">
         <f aca="false">DEC2HEX(D85,2)</f>
         <v>84</v>
@@ -10751,17 +10755,17 @@
       <c r="L85" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="223"/>
-      <c r="N85" s="223"/>
-      <c r="O85" s="259"/>
-      <c r="P85" s="225"/>
+      <c r="M85" s="224"/>
+      <c r="N85" s="224"/>
+      <c r="O85" s="257"/>
+      <c r="P85" s="226"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A86" s="250" t="s">
-        <v>325</v>
+      <c r="A86" s="248" t="s">
+        <v>327</v>
       </c>
       <c r="B86" s="191"/>
-      <c r="C86" s="212" t="str">
+      <c r="C86" s="213" t="str">
         <f aca="false">DEC2HEX(D86,2)</f>
         <v>05</v>
       </c>
@@ -10769,43 +10773,43 @@
         <f aca="false">IF(E86=1,128,0)+IF(F86=1,64,0)+IF(G86=1,32,0)+IF(H86=1,16,0)+IF(I86=1,8,0)+IF(J86=1,4,0)+IF(K86=1,2,0)+IF(L86=1,1,0)</f>
         <v>5</v>
       </c>
-      <c r="E86" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="253" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="251" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="252" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="253" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" s="254"/>
-      <c r="N86" s="254"/>
+      <c r="E86" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="250" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="252"/>
+      <c r="N86" s="252"/>
       <c r="O86" s="191"/>
-      <c r="P86" s="255" t="s">
-        <v>326</v>
+      <c r="P86" s="253" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A87" s="245" t="s">
-        <v>327</v>
-      </c>
-      <c r="B87" s="248"/>
-      <c r="C87" s="246" t="str">
+      <c r="A87" s="243" t="s">
+        <v>329</v>
+      </c>
+      <c r="B87" s="246"/>
+      <c r="C87" s="244" t="str">
         <f aca="false">DEC2HEX(D87,2)</f>
         <v>45</v>
       </c>
@@ -10813,7 +10817,7 @@
         <f aca="false">IF(E87=1,128,0)+IF(F87=1,64,0)+IF(G87=1,32,0)+IF(H87=1,16,0)+IF(I87=1,8,0)+IF(J87=1,4,0)+IF(K87=1,2,0)+IF(L87=1,1,0)</f>
         <v>69</v>
       </c>
-      <c r="E87" s="247" t="n">
+      <c r="E87" s="245" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="152" t="n">
@@ -10825,7 +10829,7 @@
       <c r="H87" s="155" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="247" t="n">
+      <c r="I87" s="245" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="152" t="n">
@@ -10837,16 +10841,16 @@
       <c r="L87" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="M87" s="256"/>
-      <c r="N87" s="256"/>
-      <c r="O87" s="248"/>
-      <c r="P87" s="257" t="s">
-        <v>328</v>
+      <c r="M87" s="254"/>
+      <c r="N87" s="254"/>
+      <c r="O87" s="246"/>
+      <c r="P87" s="255" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A88" s="222" t="s">
-        <v>329</v>
+      <c r="A88" s="223" t="s">
+        <v>331</v>
       </c>
       <c r="B88" s="142"/>
       <c r="C88" s="17" t="str">
@@ -10881,17 +10885,17 @@
       <c r="L88" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M88" s="223"/>
-      <c r="N88" s="223"/>
+      <c r="M88" s="224"/>
+      <c r="N88" s="224"/>
       <c r="O88" s="142"/>
-      <c r="P88" s="225"/>
+      <c r="P88" s="226"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A89" s="245" t="s">
-        <v>330</v>
-      </c>
-      <c r="B89" s="248"/>
-      <c r="C89" s="246" t="str">
+      <c r="A89" s="243" t="s">
+        <v>332</v>
+      </c>
+      <c r="B89" s="246"/>
+      <c r="C89" s="244" t="str">
         <f aca="false">DEC2HEX(D89,2)</f>
         <v>37</v>
       </c>
@@ -10899,7 +10903,7 @@
         <f aca="false">IF(E89=1,128,0)+IF(F89=1,64,0)+IF(G89=1,32,0)+IF(H89=1,16,0)+IF(I89=1,8,0)+IF(J89=1,4,0)+IF(K89=1,2,0)+IF(L89=1,1,0)</f>
         <v>55</v>
       </c>
-      <c r="E89" s="247" t="n">
+      <c r="E89" s="245" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="152" t="n">
@@ -10911,7 +10915,7 @@
       <c r="H89" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="I89" s="247" t="n">
+      <c r="I89" s="245" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="152" t="n">
@@ -10923,13 +10927,13 @@
       <c r="L89" s="155" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="256"/>
-      <c r="N89" s="256"/>
-      <c r="O89" s="248"/>
-      <c r="P89" s="257"/>
+      <c r="M89" s="254"/>
+      <c r="N89" s="254"/>
+      <c r="O89" s="246"/>
+      <c r="P89" s="255"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A90" s="222"/>
+      <c r="A90" s="223"/>
       <c r="B90" s="142"/>
       <c r="C90" s="17" t="str">
         <f aca="false">DEC2HEX(D90,2)</f>
@@ -10947,15 +10951,15 @@
       <c r="J90" s="119"/>
       <c r="K90" s="119"/>
       <c r="L90" s="50"/>
-      <c r="M90" s="223"/>
-      <c r="N90" s="223"/>
+      <c r="M90" s="224"/>
+      <c r="N90" s="224"/>
       <c r="O90" s="142"/>
-      <c r="P90" s="225"/>
+      <c r="P90" s="226"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A91" s="245"/>
-      <c r="B91" s="248"/>
-      <c r="C91" s="246" t="str">
+      <c r="A91" s="243"/>
+      <c r="B91" s="246"/>
+      <c r="C91" s="244" t="str">
         <f aca="false">DEC2HEX(D91,2)</f>
         <v>00</v>
       </c>
@@ -10963,25 +10967,25 @@
         <f aca="false">IF(E91=1,128,0)+IF(F91=1,64,0)+IF(G91=1,32,0)+IF(H91=1,16,0)+IF(I91=1,8,0)+IF(J91=1,4,0)+IF(K91=1,2,0)+IF(L91=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E91" s="247"/>
+      <c r="E91" s="245"/>
       <c r="F91" s="152"/>
       <c r="G91" s="152"/>
       <c r="H91" s="155"/>
-      <c r="I91" s="247"/>
+      <c r="I91" s="245"/>
       <c r="J91" s="152"/>
       <c r="K91" s="152"/>
       <c r="L91" s="155"/>
-      <c r="M91" s="256"/>
-      <c r="N91" s="256"/>
-      <c r="O91" s="248"/>
-      <c r="P91" s="257"/>
+      <c r="M91" s="254"/>
+      <c r="N91" s="254"/>
+      <c r="O91" s="246"/>
+      <c r="P91" s="255"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="142"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -10996,12 +11000,12 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="3"/>
-      <c r="O93" s="260"/>
+      <c r="O93" s="258"/>
       <c r="P93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -11041,10 +11045,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>55</v>
@@ -11058,13 +11062,13 @@
       <c r="F1" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="261" t="s">
-        <v>334</v>
-      </c>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261" t="s">
-        <v>335</v>
+      <c r="G1" s="259" t="s">
+        <v>336</v>
+      </c>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
+      <c r="J1" s="259" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11078,26 +11082,26 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11111,13 +11115,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>122</v>
@@ -11127,10 +11131,10 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11147,25 +11151,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11182,25 +11186,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="K5" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11214,28 +11218,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11249,28 +11253,28 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11284,26 +11288,26 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11317,13 +11321,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>122</v>
@@ -11333,10 +11337,10 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11350,28 +11354,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11385,28 +11389,28 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11420,28 +11424,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11455,28 +11459,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
